--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="333">
   <si>
     <t>类型</t>
   </si>
@@ -450,10 +450,13 @@
     <t>炮台</t>
   </si>
   <si>
-    <t>建筑/光子炮</t>
-  </si>
-  <si>
-    <t>平常状态</t>
+    <t>建筑/炮台</t>
+  </si>
+  <si>
+    <t>p_jiqiangbao_d_01</t>
+  </si>
+  <si>
+    <t>show</t>
   </si>
   <si>
     <t>音效/explo1</t>
@@ -820,9 +823,6 @@
   </si>
   <si>
     <t>音效/Tmedheal</t>
-  </si>
-  <si>
-    <t>pao002</t>
   </si>
   <si>
     <t>特效/黄泡泡</t>
@@ -2230,7 +2230,7 @@
   <dimension ref="A1:U44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="9" style="1"/>
+    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
     <col min="4" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="7" width="30.75" customWidth="1"/>
     <col min="8" max="9" width="44.875" customWidth="1"/>
@@ -3587,11 +3587,14 @@
       <c r="E27" s="13" t="s">
         <v>27</v>
       </c>
+      <c r="F27" s="13" t="s">
+        <v>138</v>
+      </c>
       <c r="G27" s="19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I27" s="19">
         <v>1</v>
@@ -3602,8 +3605,8 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27" s="13" t="s">
-        <v>127</v>
+      <c r="L27" t="s">
+        <v>43</v>
       </c>
       <c r="M27" s="19">
         <v>1</v>
@@ -3615,13 +3618,13 @@
         <v>0</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q27" s="13">
         <v>3</v>
       </c>
       <c r="R27" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" s="13" customFormat="1" spans="1:18">
@@ -3629,19 +3632,19 @@
         <v>306</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C28" s="13">
         <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G28" s="19" t="b">
         <v>1</v>
@@ -3671,13 +3674,13 @@
         <v>0</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q28" s="13">
         <v>3</v>
       </c>
       <c r="R28" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" s="13" customFormat="1" spans="1:18">
@@ -3685,19 +3688,19 @@
         <v>307</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" s="13">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G29" s="19" t="b">
         <v>0</v>
@@ -3733,7 +3736,7 @@
         <v>3</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" s="13" customFormat="1" spans="1:18">
@@ -3741,25 +3744,25 @@
         <v>308</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="13">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G30" s="19" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I30" s="19">
         <v>1</v>
@@ -3789,7 +3792,7 @@
         <v>3</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" s="13" customFormat="1" spans="1:18">
@@ -3797,19 +3800,19 @@
         <v>309</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C31" s="13">
         <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>157</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>156</v>
       </c>
       <c r="G31" s="19" t="b">
         <v>1</v>
@@ -3839,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q31" s="13">
         <v>3</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" s="13" customFormat="1" spans="1:18">
@@ -3853,19 +3856,19 @@
         <v>310</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C32" s="13">
         <v>2</v>
       </c>
       <c r="D32" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>160</v>
       </c>
       <c r="G32" s="19" t="b">
         <v>1</v>
@@ -3895,13 +3898,13 @@
         <v>0</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q32" s="13">
         <v>4</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" s="13" customFormat="1" spans="1:18">
@@ -3909,20 +3912,20 @@
         <v>311</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C33" s="13">
         <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="G33" s="19" t="b">
         <v>1</v>
       </c>
@@ -3951,13 +3954,13 @@
         <v>0</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q33" s="13">
         <v>3</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="34" s="13" customFormat="1" spans="1:18">
@@ -3965,13 +3968,13 @@
         <v>312</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C34" s="13">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G34" s="19" t="b">
         <v>1</v>
@@ -3998,7 +4001,7 @@
         <v>1</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" s="11" customFormat="1" spans="1:17">
@@ -4006,7 +4009,7 @@
         <v>401</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" s="11">
         <v>2</v>
@@ -4056,7 +4059,7 @@
         <v>402</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" s="11">
         <v>2</v>
@@ -4106,7 +4109,7 @@
         <v>403</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C37" s="11">
         <v>2</v>
@@ -4159,13 +4162,13 @@
         <v>404</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C38" s="11">
         <v>1</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>41</v>
@@ -4209,7 +4212,7 @@
         <v>405</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4268,7 +4271,7 @@
         <v>406</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
@@ -4321,7 +4324,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4377,7 +4380,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4433,7 +4436,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4489,7 +4492,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4566,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>283</v>
@@ -4887,7 +4890,7 @@
         <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4929,22 +4932,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5435,7 +5438,7 @@
         <v>306</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C23" s="15">
         <v>35</v>
@@ -5458,7 +5461,7 @@
         <v>307</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="15">
         <v>35</v>
@@ -5481,7 +5484,7 @@
         <v>308</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="15">
         <v>35</v>
@@ -5504,7 +5507,7 @@
         <v>309</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C26" s="15">
         <v>20</v>
@@ -5527,7 +5530,7 @@
         <v>310</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C27" s="15">
         <v>30</v>
@@ -5550,7 +5553,7 @@
         <v>311</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C28" s="15">
         <v>30</v>
@@ -5573,7 +5576,7 @@
         <v>312</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="15">
         <v>15</v>
@@ -5616,22 +5619,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5708,7 +5711,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5785,7 +5788,7 @@
         <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -5805,7 +5808,7 @@
         <v>307</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -5828,7 +5831,7 @@
         <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -5848,7 +5851,7 @@
         <v>309</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -5868,7 +5871,7 @@
         <v>310</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13">
         <v>2.5</v>
@@ -5888,7 +5891,7 @@
         <v>311</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -5911,7 +5914,7 @@
         <v>312</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -5954,25 +5957,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5983,7 +5986,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -5998,7 +6001,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6009,10 +6012,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6024,7 +6027,7 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6035,7 +6038,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6050,7 +6053,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6061,10 +6064,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6076,7 +6079,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6087,10 +6090,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6099,10 +6102,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -6116,7 +6119,7 @@
         <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6128,7 +6131,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6139,10 +6142,10 @@
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D8" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6151,10 +6154,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6165,10 +6168,10 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6177,10 +6180,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6194,7 +6197,7 @@
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6217,10 +6220,10 @@
         <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6229,10 +6232,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6257,7 +6260,7 @@
         <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
         <v>97</v>
@@ -6269,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6283,7 +6286,7 @@
         <v>101</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D14" t="s">
         <v>97</v>
@@ -6295,10 +6298,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H14" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6309,7 +6312,7 @@
         <v>107</v>
       </c>
       <c r="C15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6321,10 +6324,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6335,10 +6338,10 @@
         <v>113</v>
       </c>
       <c r="C16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D16" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6350,7 +6353,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6358,13 +6361,13 @@
         <v>401</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6378,13 +6381,13 @@
         <v>402</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6398,13 +6401,13 @@
         <v>403</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6418,13 +6421,13 @@
         <v>404</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D20" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6436,7 +6439,7 @@
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6444,10 +6447,10 @@
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6462,7 +6465,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6470,10 +6473,10 @@
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C22" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6488,7 +6491,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6496,13 +6499,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C23" t="s">
         <v>81</v>
       </c>
       <c r="D23" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6522,10 +6525,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C24" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D24" t="s">
         <v>97</v>
@@ -6537,10 +6540,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H24" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6548,13 +6551,13 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6563,10 +6566,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H25" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6574,10 +6577,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D26" t="s">
         <v>97</v>
@@ -6589,10 +6592,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H26" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -6641,58 +6644,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -6730,7 +6733,7 @@
         <v>500</v>
       </c>
       <c r="O2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P2">
         <v>500</v>
@@ -6771,13 +6774,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M3">
         <v>2.5</v>
@@ -6786,7 +6789,7 @@
         <v>900</v>
       </c>
       <c r="O3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P3">
         <v>100</v>
@@ -6836,7 +6839,7 @@
         <v>1300</v>
       </c>
       <c r="O4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P4">
         <v>500</v>
@@ -6880,19 +6883,19 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N5">
         <v>300</v>
       </c>
       <c r="O5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P5">
         <v>100</v>
@@ -6933,7 +6936,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -6942,7 +6945,7 @@
         <v>500</v>
       </c>
       <c r="O6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P6">
         <v>300</v>
@@ -6983,13 +6986,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M7">
         <v>5</v>
@@ -6998,7 +7001,7 @@
         <v>800</v>
       </c>
       <c r="O7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -7039,13 +7042,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M8">
         <v>1</v>
@@ -7054,7 +7057,7 @@
         <v>300</v>
       </c>
       <c r="O8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P8">
         <v>600</v>
@@ -7095,7 +7098,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7104,7 +7107,7 @@
         <v>570</v>
       </c>
       <c r="O9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P9">
         <v>1030</v>
@@ -7145,7 +7148,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7154,7 +7157,7 @@
         <v>600</v>
       </c>
       <c r="O10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P10">
         <v>200</v>
@@ -7198,7 +7201,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7207,7 +7210,7 @@
         <v>500</v>
       </c>
       <c r="O11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P11">
         <v>900</v>
@@ -7254,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -7342,7 +7345,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -7351,7 +7354,7 @@
         <v>600</v>
       </c>
       <c r="O14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P14">
         <v>300</v>
@@ -7401,7 +7404,7 @@
         <v>1000</v>
       </c>
       <c r="O15" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P15">
         <v>100</v>
@@ -7442,13 +7445,13 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M16">
         <v>2.5</v>
@@ -7457,7 +7460,7 @@
         <v>530</v>
       </c>
       <c r="O16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P16">
         <v>100</v>
@@ -7710,7 +7713,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="s">
-        <v>261</v>
+        <v>29</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -7745,7 +7748,7 @@
         <v>306</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -7798,7 +7801,7 @@
         <v>307</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -7851,7 +7854,7 @@
         <v>308</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -7904,7 +7907,7 @@
         <v>309</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -7957,7 +7960,7 @@
         <v>310</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -8010,7 +8013,7 @@
         <v>311</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -8063,7 +8066,7 @@
         <v>312</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -8116,7 +8119,7 @@
         <v>401</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C29">
         <v>18</v>
@@ -8137,13 +8140,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
       <c r="L29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M29">
         <v>1</v>
@@ -8152,7 +8155,7 @@
         <v>300</v>
       </c>
       <c r="O29" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P29">
         <v>600</v>
@@ -8172,7 +8175,7 @@
         <v>402</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -8193,7 +8196,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8202,7 +8205,7 @@
         <v>570</v>
       </c>
       <c r="O30" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P30">
         <v>1030</v>
@@ -8222,7 +8225,7 @@
         <v>403</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -8243,7 +8246,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8252,7 +8255,7 @@
         <v>600</v>
       </c>
       <c r="O31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P31">
         <v>300</v>
@@ -8272,7 +8275,7 @@
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -8293,13 +8296,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M32">
         <v>4</v>
@@ -8308,7 +8311,7 @@
         <v>900</v>
       </c>
       <c r="O32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P32">
         <v>100</v>
@@ -8328,7 +8331,7 @@
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -8358,7 +8361,7 @@
         <v>1300</v>
       </c>
       <c r="O33" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P33">
         <v>500</v>
@@ -8378,7 +8381,7 @@
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8408,7 +8411,7 @@
         <v>500</v>
       </c>
       <c r="O34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P34">
         <v>500</v>
@@ -8428,7 +8431,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8449,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8458,7 +8461,7 @@
         <v>600</v>
       </c>
       <c r="O35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P35">
         <v>200</v>
@@ -8478,7 +8481,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8502,7 +8505,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M36">
         <v>5</v>
@@ -8511,7 +8514,7 @@
         <v>600</v>
       </c>
       <c r="O36" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P36">
         <v>300</v>
@@ -8531,7 +8534,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8555,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8564,7 +8567,7 @@
         <v>500</v>
       </c>
       <c r="O37" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P37">
         <v>900</v>
@@ -8584,7 +8587,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8640,7 +8643,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
         <v>264</v>
@@ -8717,7 +8720,7 @@
         <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -8728,7 +8731,7 @@
         <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -8739,7 +8742,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -8750,7 +8753,7 @@
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -8761,7 +8764,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -8772,7 +8775,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -8783,7 +8786,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -8794,7 +8797,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -8820,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>267</v>
@@ -8835,10 +8838,10 @@
         <v>270</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8849,7 +8852,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8875,7 +8878,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -8953,7 +8956,7 @@
         <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -8979,7 +8982,7 @@
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9069,13 +9072,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9126,7 +9129,7 @@
         <v>273</v>
       </c>
       <c r="B1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C1" t="s">
         <v>268</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="338">
   <si>
     <t>类型</t>
   </si>
@@ -243,6 +243,15 @@
     <t>音效/飞机声</t>
   </si>
   <si>
+    <t>p_plane_01</t>
+  </si>
+  <si>
+    <t>flight_04</t>
+  </si>
+  <si>
+    <t>slide</t>
+  </si>
+  <si>
     <t>可飞越障碍物</t>
   </si>
   <si>
@@ -748,6 +757,12 @@
   </si>
   <si>
     <t>攻击动作.播放速度</t>
+  </si>
+  <si>
+    <t>攻击动作.起始时刻秒</t>
+  </si>
+  <si>
+    <t>攻击动作.结束时刻秒</t>
   </si>
   <si>
     <t>str弹丸特效</t>
@@ -2814,7 +2829,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" ht="14.25" spans="1:18">
       <c r="A13">
         <v>206</v>
       </c>
@@ -2830,11 +2845,14 @@
       <c r="E13" t="s">
         <v>67</v>
       </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
       <c r="G13" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="I13" s="19">
         <v>1</v>
@@ -2843,19 +2861,19 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>62</v>
+        <v>2</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="M13" s="19">
         <v>1</v>
       </c>
       <c r="N13" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P13" t="s">
         <v>56</v>
@@ -2864,7 +2882,7 @@
         <v>5</v>
       </c>
       <c r="R13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -2872,19 +2890,19 @@
         <v>207</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14">
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G14" s="19" t="b">
         <v>1</v>
@@ -2914,7 +2932,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -2928,19 +2946,19 @@
         <v>208</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G15" s="19" t="b">
         <v>1</v>
@@ -2970,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q15">
         <v>2</v>
@@ -2984,25 +3002,25 @@
         <v>209</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G16" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I16" s="19">
         <v>1</v>
@@ -3014,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M16" s="19">
         <v>1</v>
@@ -3026,13 +3044,13 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q16">
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -3040,19 +3058,19 @@
         <v>210</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G17" s="19" t="b">
         <v>1</v>
@@ -3082,13 +3100,13 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
       <c r="R17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -3096,13 +3114,13 @@
         <v>211</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G18" s="19" t="b">
         <v>1</v>
@@ -3134,25 +3152,25 @@
         <v>212</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G19" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I19" s="19">
         <v>1</v>
@@ -3164,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M19" s="19">
         <v>1</v>
@@ -3176,13 +3194,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q19">
         <v>4</v>
       </c>
       <c r="R19" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -3190,25 +3208,25 @@
         <v>213</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G20" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I20" s="19">
         <v>1</v>
@@ -3220,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M20" s="19">
         <v>1</v>
@@ -3232,13 +3250,13 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q20">
         <v>4</v>
       </c>
       <c r="R20" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" customFormat="1" spans="1:18">
@@ -3246,19 +3264,19 @@
         <v>214</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G21" s="19" t="b">
         <v>1</v>
@@ -3288,13 +3306,13 @@
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
       <c r="R21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:18">
@@ -3302,19 +3320,19 @@
         <v>215</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G22" s="19" t="b">
         <v>1</v>
@@ -3350,7 +3368,7 @@
         <v>3</v>
       </c>
       <c r="R22" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" s="13" customFormat="1" spans="1:18">
@@ -3358,19 +3376,19 @@
         <v>301</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C23" s="13">
         <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E23" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G23" s="19" t="b">
         <v>1</v>
@@ -3388,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="13" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M23" s="19">
         <v>1</v>
@@ -3400,13 +3418,13 @@
         <v>0</v>
       </c>
       <c r="P23" s="13" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="Q23" s="13">
         <v>3</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" s="13" customFormat="1" spans="1:18">
@@ -3414,25 +3432,25 @@
         <v>302</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C24" s="13">
         <v>1</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G24" s="19" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="I24" s="19">
         <v>0.1</v>
@@ -3444,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="L24" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M24" s="19">
         <v>1</v>
@@ -3456,13 +3474,13 @@
         <v>0</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q24" s="13">
         <v>3</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" s="13" customFormat="1" spans="1:18">
@@ -3470,13 +3488,13 @@
         <v>303</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C25" s="13">
         <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E25" s="13" t="s">
         <v>27</v>
@@ -3506,13 +3524,13 @@
         <v>0</v>
       </c>
       <c r="P25" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q25" s="13">
         <v>3</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" s="13" customFormat="1" spans="1:18">
@@ -3520,19 +3538,19 @@
         <v>304</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C26" s="13">
         <v>1</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G26" s="19" t="b">
         <v>0</v>
@@ -3562,13 +3580,13 @@
         <v>0</v>
       </c>
       <c r="P26" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q26" s="13">
         <v>3</v>
       </c>
       <c r="R26" s="13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" s="13" customFormat="1" spans="1:18">
@@ -3576,25 +3594,25 @@
         <v>305</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C27" s="13">
         <v>3</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G27" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I27" s="19">
         <v>1</v>
@@ -3618,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="P27" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="Q27" s="13">
         <v>3</v>
       </c>
       <c r="R27" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" s="13" customFormat="1" spans="1:18">
@@ -3632,19 +3650,19 @@
         <v>306</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C28" s="13">
         <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G28" s="19" t="b">
         <v>1</v>
@@ -3674,13 +3692,13 @@
         <v>0</v>
       </c>
       <c r="P28" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q28" s="13">
         <v>3</v>
       </c>
       <c r="R28" s="13" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" s="13" customFormat="1" spans="1:18">
@@ -3688,25 +3706,25 @@
         <v>307</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C29" s="13">
         <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G29" s="19" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I29" s="19">
         <v>1</v>
@@ -3718,7 +3736,7 @@
         <v>4.73</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M29" s="19">
         <v>0.1</v>
@@ -3730,13 +3748,13 @@
         <v>0.17</v>
       </c>
       <c r="P29" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q29" s="13">
         <v>3</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" s="13" customFormat="1" spans="1:18">
@@ -3744,25 +3762,25 @@
         <v>308</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C30" s="13">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G30" s="19" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I30" s="19">
         <v>1</v>
@@ -3774,7 +3792,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M30" s="19">
         <v>1</v>
@@ -3786,13 +3804,13 @@
         <v>0</v>
       </c>
       <c r="P30" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Q30" s="13">
         <v>3</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" s="13" customFormat="1" spans="1:18">
@@ -3800,25 +3818,25 @@
         <v>309</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C31" s="13">
         <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G31" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I31" s="19">
         <v>1</v>
@@ -3830,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M31" s="19">
         <v>1</v>
@@ -3842,13 +3860,13 @@
         <v>0</v>
       </c>
       <c r="P31" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q31" s="13">
         <v>3</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" s="13" customFormat="1" spans="1:18">
@@ -3856,25 +3874,25 @@
         <v>310</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C32" s="13">
         <v>2</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G32" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I32" s="19">
         <v>1</v>
@@ -3886,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="13" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M32" s="19">
         <v>1</v>
@@ -3898,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="P32" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q32" s="13">
         <v>4</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" s="13" customFormat="1" spans="1:18">
@@ -3912,19 +3930,19 @@
         <v>311</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C33" s="13">
         <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>163</v>
-      </c>
       <c r="F33" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G33" s="19" t="b">
         <v>1</v>
@@ -3954,13 +3972,13 @@
         <v>0</v>
       </c>
       <c r="P33" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q33" s="13">
         <v>3</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" s="13" customFormat="1" spans="1:18">
@@ -3968,13 +3986,13 @@
         <v>312</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C34" s="13">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="G34" s="19" t="b">
         <v>1</v>
@@ -4001,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" s="11" customFormat="1" spans="1:17">
@@ -4009,16 +4027,16 @@
         <v>401</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C35" s="11">
         <v>2</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G35" s="19" t="b">
         <v>1</v>
@@ -4048,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q35" s="11">
         <v>2</v>
@@ -4059,16 +4077,16 @@
         <v>402</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C36" s="11">
         <v>2</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F36" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G36" s="19" t="b">
         <v>1</v>
@@ -4098,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="11" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q36" s="11">
         <v>2</v>
@@ -4109,7 +4127,7 @@
         <v>403</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C37" s="11">
         <v>2</v>
@@ -4162,13 +4180,13 @@
         <v>404</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C38" s="11">
         <v>1</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>41</v>
@@ -4212,7 +4230,7 @@
         <v>405</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4271,7 +4289,7 @@
         <v>406</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
@@ -4324,25 +4342,25 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G41" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I41" s="19">
         <v>1</v>
@@ -4354,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M41" s="19">
         <v>1</v>
@@ -4366,13 +4384,13 @@
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -4380,25 +4398,25 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F42" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G42" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I42" s="19">
         <v>1</v>
@@ -4410,7 +4428,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M42" s="19">
         <v>1</v>
@@ -4422,13 +4440,13 @@
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="Q42">
         <v>4</v>
       </c>
       <c r="R42" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -4436,19 +4454,19 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E43" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F43" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="G43" s="19" t="b">
         <v>1</v>
@@ -4478,13 +4496,13 @@
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q43">
         <v>2</v>
       </c>
       <c r="R43" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -4492,25 +4510,25 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E44" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G44" s="19" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I44" s="19">
         <v>1</v>
@@ -4522,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M44" s="19">
         <v>1</v>
@@ -4534,13 +4552,13 @@
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q44">
         <v>4</v>
       </c>
       <c r="R44" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4569,22 +4587,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4592,16 +4610,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4609,16 +4627,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4626,16 +4644,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4643,16 +4661,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D5" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4660,16 +4678,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E6" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4677,16 +4695,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E7" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4694,16 +4712,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C8" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E8" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4711,16 +4729,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E9" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4728,16 +4746,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D10" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E10" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4745,16 +4763,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="D11" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="E11" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4762,22 +4780,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C12" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4785,16 +4803,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C13" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D13" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4802,22 +4820,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C14" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D14" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4825,16 +4843,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E15" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4842,22 +4860,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C16" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4887,10 +4905,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4899,7 +4917,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4907,7 +4925,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4932,22 +4950,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5116,7 +5134,7 @@
         <v>207</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -5139,7 +5157,7 @@
         <v>208</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -5162,7 +5180,7 @@
         <v>209</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -5185,7 +5203,7 @@
         <v>210</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -5208,7 +5226,7 @@
         <v>211</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -5231,7 +5249,7 @@
         <v>212</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -5254,7 +5272,7 @@
         <v>213</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C15">
         <v>18</v>
@@ -5277,7 +5295,7 @@
         <v>214</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -5300,7 +5318,7 @@
         <v>215</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -5323,7 +5341,7 @@
         <v>301</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C18" s="15">
         <v>50</v>
@@ -5346,7 +5364,7 @@
         <v>302</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C19" s="15">
         <v>25</v>
@@ -5369,7 +5387,7 @@
         <v>303</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C20" s="15">
         <v>20</v>
@@ -5392,7 +5410,7 @@
         <v>304</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C21" s="15">
         <v>30</v>
@@ -5415,7 +5433,7 @@
         <v>305</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C22" s="15">
         <v>25</v>
@@ -5438,7 +5456,7 @@
         <v>306</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C23" s="15">
         <v>35</v>
@@ -5461,7 +5479,7 @@
         <v>307</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C24" s="15">
         <v>35</v>
@@ -5484,7 +5502,7 @@
         <v>308</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C25" s="15">
         <v>35</v>
@@ -5507,7 +5525,7 @@
         <v>309</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C26" s="15">
         <v>20</v>
@@ -5530,7 +5548,7 @@
         <v>310</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C27" s="15">
         <v>30</v>
@@ -5553,7 +5571,7 @@
         <v>311</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C28" s="15">
         <v>30</v>
@@ -5576,7 +5594,7 @@
         <v>312</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C29" s="15">
         <v>15</v>
@@ -5619,22 +5637,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5682,7 +5700,7 @@
         <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -5705,13 +5723,13 @@
         <v>302</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5728,7 +5746,7 @@
         <v>303</v>
       </c>
       <c r="B6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -5748,7 +5766,7 @@
         <v>304</v>
       </c>
       <c r="B7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -5768,7 +5786,7 @@
         <v>305</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8">
         <v>2.5</v>
@@ -5788,7 +5806,7 @@
         <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -5808,13 +5826,13 @@
         <v>307</v>
       </c>
       <c r="B10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E10">
         <v>0.05</v>
@@ -5831,7 +5849,7 @@
         <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -5851,7 +5869,7 @@
         <v>309</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -5871,7 +5889,7 @@
         <v>310</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C13">
         <v>2.5</v>
@@ -5891,7 +5909,7 @@
         <v>311</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -5914,7 +5932,7 @@
         <v>312</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -5957,25 +5975,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -5986,7 +6004,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6001,7 +6019,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6012,10 +6030,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6027,7 +6045,7 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6038,7 +6056,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6053,7 +6071,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6064,10 +6082,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" t="s">
         <v>206</v>
-      </c>
-      <c r="D5" t="s">
-        <v>203</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6079,7 +6097,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6090,10 +6108,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D6" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6102,13 +6120,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:8">
       <c r="A7">
         <v>206</v>
       </c>
@@ -6118,20 +6136,20 @@
       <c r="C7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" t="s">
-        <v>203</v>
+      <c r="D7" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="s">
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6139,13 +6157,13 @@
         <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6154,10 +6172,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6165,13 +6183,13 @@
         <v>208</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6180,10 +6198,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6191,13 +6209,13 @@
         <v>209</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6206,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:8">
@@ -6217,13 +6235,13 @@
         <v>210</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D11" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6232,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H11" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6243,7 +6261,7 @@
         <v>211</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6257,13 +6275,13 @@
         <v>212</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6272,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6283,13 +6301,13 @@
         <v>213</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6298,10 +6316,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H14" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6309,10 +6327,10 @@
         <v>214</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6324,10 +6342,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="H15" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6335,13 +6353,13 @@
         <v>215</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6353,7 +6371,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6361,13 +6379,13 @@
         <v>401</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D17" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6381,13 +6399,13 @@
         <v>402</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D18" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6401,13 +6419,13 @@
         <v>403</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D19" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6421,13 +6439,13 @@
         <v>404</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6439,7 +6457,7 @@
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6447,10 +6465,10 @@
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6465,7 +6483,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6473,10 +6491,10 @@
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6491,7 +6509,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6499,13 +6517,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6514,10 +6532,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -6525,13 +6543,13 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6540,10 +6558,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="H24" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6551,13 +6569,13 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D25" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6566,10 +6584,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H25" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6577,13 +6595,13 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6592,10 +6610,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H26" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -6608,7 +6626,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:U38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
@@ -6619,86 +6637,92 @@
     <col min="8" max="8" width="12.125" customWidth="1"/>
     <col min="9" max="9" width="21.5" customWidth="1"/>
     <col min="10" max="11" width="21.625" customWidth="1"/>
-    <col min="12" max="13" width="20.375" customWidth="1"/>
-    <col min="14" max="14" width="13.25" customWidth="1"/>
-    <col min="15" max="15" width="14.625" customWidth="1"/>
-    <col min="16" max="16" width="9.125" customWidth="1"/>
-    <col min="17" max="17" width="19.625" customWidth="1"/>
-    <col min="18" max="18" width="21.625" customWidth="1"/>
-    <col min="19" max="19" width="11.5" customWidth="1"/>
-    <col min="21" max="21" width="26" customWidth="1"/>
-    <col min="22" max="22" width="6.375" customWidth="1"/>
-    <col min="24" max="24" width="2.375" customWidth="1"/>
-    <col min="26" max="26" width="4.375" customWidth="1"/>
-    <col min="30" max="30" width="8.375" customWidth="1"/>
-    <col min="32" max="32" width="7.375" customWidth="1"/>
-    <col min="33" max="33" width="10.375" customWidth="1"/>
+    <col min="12" max="15" width="20.375" customWidth="1"/>
+    <col min="16" max="16" width="13.25" customWidth="1"/>
+    <col min="17" max="17" width="14.625" customWidth="1"/>
+    <col min="18" max="18" width="9.125" customWidth="1"/>
+    <col min="19" max="19" width="19.625" customWidth="1"/>
+    <col min="20" max="20" width="21.625" customWidth="1"/>
+    <col min="21" max="21" width="11.5" customWidth="1"/>
+    <col min="23" max="23" width="26" customWidth="1"/>
+    <col min="24" max="24" width="6.375" customWidth="1"/>
+    <col min="26" max="26" width="2.375" customWidth="1"/>
+    <col min="28" max="28" width="4.375" customWidth="1"/>
+    <col min="32" max="32" width="8.375" customWidth="1"/>
+    <col min="34" max="34" width="7.375" customWidth="1"/>
     <col min="35" max="35" width="10.375" customWidth="1"/>
-    <col min="37" max="37" width="6.375" customWidth="1"/>
-    <col min="38" max="38" width="8.375" customWidth="1"/>
-    <col min="39" max="39" width="12.625" customWidth="1"/>
+    <col min="37" max="37" width="10.375" customWidth="1"/>
+    <col min="39" max="39" width="6.375" customWidth="1"/>
+    <col min="40" max="40" width="8.375" customWidth="1"/>
+    <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" spans="1:19">
+    <row r="1" s="12" customFormat="1" spans="1:21">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
+        <v>247</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>201</v>
       </c>
@@ -6729,26 +6753,32 @@
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="N2">
-        <v>500</v>
-      </c>
-      <c r="O2" t="s">
-        <v>245</v>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
       </c>
       <c r="P2">
         <v>500</v>
       </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="b">
-        <v>0</v>
+      <c r="Q2" t="s">
+        <v>250</v>
+      </c>
+      <c r="R2">
+        <v>500</v>
       </c>
       <c r="S2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>202</v>
       </c>
@@ -6774,37 +6804,43 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" t="s">
-        <v>247</v>
+      <c r="L3">
+        <v>0</v>
       </c>
       <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>252</v>
+      </c>
+      <c r="O3">
         <v>2.5</v>
       </c>
-      <c r="N3">
+      <c r="P3">
         <v>900</v>
       </c>
-      <c r="O3" t="s">
-        <v>248</v>
-      </c>
-      <c r="P3">
+      <c r="Q3" t="s">
+        <v>253</v>
+      </c>
+      <c r="R3">
         <v>100</v>
       </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
       <c r="S3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>203</v>
       </c>
@@ -6835,26 +6871,32 @@
       <c r="K4">
         <v>2</v>
       </c>
-      <c r="N4">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="P4">
         <v>1300</v>
       </c>
-      <c r="O4" t="s">
-        <v>249</v>
-      </c>
-      <c r="P4">
+      <c r="Q4" t="s">
+        <v>254</v>
+      </c>
+      <c r="R4">
         <v>500</v>
       </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="b">
-        <v>0</v>
-      </c>
       <c r="S4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>204</v>
       </c>
@@ -6883,34 +6925,40 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
-      <c r="L5" t="s">
-        <v>247</v>
-      </c>
-      <c r="N5">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>252</v>
+      </c>
+      <c r="P5">
         <v>300</v>
       </c>
-      <c r="O5" t="s">
-        <v>251</v>
-      </c>
-      <c r="P5">
+      <c r="Q5" t="s">
+        <v>256</v>
+      </c>
+      <c r="R5">
         <v>100</v>
       </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="b">
-        <v>0</v>
-      </c>
       <c r="S5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>205</v>
       </c>
@@ -6936,31 +6984,37 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="N6">
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="P6">
         <v>500</v>
       </c>
-      <c r="O6" t="s">
-        <v>252</v>
-      </c>
-      <c r="P6">
+      <c r="Q6" t="s">
+        <v>257</v>
+      </c>
+      <c r="R6">
         <v>300</v>
       </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
       <c r="S6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:21">
       <c r="A7">
         <v>206</v>
       </c>
@@ -6985,43 +7039,49 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
-        <v>246</v>
+      <c r="J7" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7" t="s">
-        <v>247</v>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="M7">
+        <v>2</v>
+      </c>
+      <c r="N7" t="s">
+        <v>252</v>
+      </c>
+      <c r="O7">
         <v>5</v>
       </c>
-      <c r="N7">
+      <c r="P7">
         <v>800</v>
       </c>
-      <c r="O7" t="s">
-        <v>253</v>
-      </c>
-      <c r="P7">
+      <c r="Q7" t="s">
+        <v>258</v>
+      </c>
+      <c r="R7">
         <v>100</v>
       </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-      <c r="R7" t="b">
-        <v>1</v>
-      </c>
       <c r="S7" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:19">
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>207</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -7042,42 +7102,48 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8" t="s">
-        <v>247</v>
+      <c r="L8">
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>252</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
         <v>300</v>
       </c>
-      <c r="O8" t="s">
-        <v>255</v>
-      </c>
-      <c r="P8">
+      <c r="Q8" t="s">
+        <v>260</v>
+      </c>
+      <c r="R8">
         <v>600</v>
       </c>
-      <c r="Q8" t="b">
-        <v>0</v>
-      </c>
-      <c r="R8" t="b">
-        <v>1</v>
-      </c>
       <c r="S8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T8" t="b">
+        <v>1</v>
+      </c>
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>208</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -7098,36 +7164,42 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K9">
         <v>1</v>
       </c>
-      <c r="N9">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="P9">
         <v>570</v>
       </c>
-      <c r="O9" t="s">
-        <v>257</v>
-      </c>
-      <c r="P9">
+      <c r="Q9" t="s">
+        <v>262</v>
+      </c>
+      <c r="R9">
         <v>1030</v>
       </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="R9" t="b">
-        <v>0</v>
-      </c>
       <c r="S9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>209</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -7148,36 +7220,42 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="N10">
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="P10">
         <v>600</v>
       </c>
-      <c r="O10" t="s">
-        <v>252</v>
-      </c>
-      <c r="P10">
+      <c r="Q10" t="s">
+        <v>257</v>
+      </c>
+      <c r="R10">
         <v>200</v>
       </c>
-      <c r="Q10" t="b">
-        <v>0</v>
-      </c>
-      <c r="R10" t="b">
-        <v>0</v>
-      </c>
       <c r="S10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" customFormat="1" spans="1:19">
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:21">
       <c r="A11">
         <v>210</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C11">
         <v>35</v>
@@ -7201,36 +7279,42 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K11">
         <v>1</v>
       </c>
-      <c r="N11">
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="P11">
         <v>500</v>
       </c>
-      <c r="O11" t="s">
-        <v>258</v>
-      </c>
-      <c r="P11">
+      <c r="Q11" t="s">
+        <v>263</v>
+      </c>
+      <c r="R11">
         <v>900</v>
       </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
-      </c>
       <c r="S11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:21">
       <c r="A12">
         <v>211</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -7253,31 +7337,37 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>259</v>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12" t="b">
+      <c r="Q12" t="s">
+        <v>264</v>
+      </c>
+      <c r="R12">
         <v>0</v>
       </c>
       <c r="S12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:21">
       <c r="A13">
         <v>212</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -7300,28 +7390,34 @@
       <c r="K13">
         <v>1</v>
       </c>
-      <c r="N13">
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-      <c r="R13" t="b">
+      <c r="R13">
         <v>0</v>
       </c>
       <c r="S13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="1" spans="1:19">
+        <v>1</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:21">
       <c r="A14">
         <v>213</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -7344,37 +7440,43 @@
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="L14" t="s">
-        <v>247</v>
+      <c r="L14">
+        <v>0</v>
       </c>
       <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>252</v>
+      </c>
+      <c r="O14">
         <v>5</v>
       </c>
-      <c r="N14">
+      <c r="P14">
         <v>600</v>
       </c>
-      <c r="O14" t="s">
-        <v>260</v>
-      </c>
-      <c r="P14">
+      <c r="Q14" t="s">
+        <v>265</v>
+      </c>
+      <c r="R14">
         <v>300</v>
       </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-      <c r="R14" t="b">
-        <v>1</v>
-      </c>
       <c r="S14" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:19">
+      <c r="T14" t="b">
+        <v>1</v>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:21">
       <c r="A15">
         <v>214</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -7400,31 +7502,37 @@
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="N15">
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="P15">
         <v>1000</v>
       </c>
-      <c r="O15" t="s">
-        <v>261</v>
-      </c>
-      <c r="P15">
+      <c r="Q15" t="s">
+        <v>266</v>
+      </c>
+      <c r="R15">
         <v>100</v>
       </c>
-      <c r="Q15" t="b">
-        <v>0</v>
-      </c>
-      <c r="R15" t="b">
-        <v>0</v>
-      </c>
       <c r="S15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:21">
       <c r="A16">
         <v>215</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C16">
         <v>30</v>
@@ -7445,42 +7553,48 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="L16" t="s">
-        <v>247</v>
+      <c r="L16">
+        <v>0</v>
       </c>
       <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>252</v>
+      </c>
+      <c r="O16">
         <v>2.5</v>
       </c>
-      <c r="N16">
+      <c r="P16">
         <v>530</v>
       </c>
-      <c r="O16" t="s">
-        <v>251</v>
-      </c>
-      <c r="P16">
+      <c r="Q16" t="s">
+        <v>256</v>
+      </c>
+      <c r="R16">
         <v>100</v>
       </c>
-      <c r="Q16" t="b">
-        <v>0</v>
-      </c>
-      <c r="R16" t="b">
-        <v>1</v>
-      </c>
       <c r="S16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:19">
+      <c r="T16" t="b">
+        <v>1</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="13">
         <v>301</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -7509,31 +7623,37 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
         <v>0</v>
       </c>
       <c r="P17">
         <v>0</v>
       </c>
-      <c r="Q17" t="b">
-        <v>0</v>
-      </c>
-      <c r="R17" t="b">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
         <v>0</v>
       </c>
       <c r="S17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="13">
         <v>302</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -7562,31 +7682,37 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
         <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18" t="b">
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
         <v>0</v>
       </c>
       <c r="S18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="13">
         <v>303</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -7615,31 +7741,37 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
         <v>0</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
-      <c r="Q19" t="b">
-        <v>0</v>
-      </c>
-      <c r="R19" t="b">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
         <v>0</v>
       </c>
       <c r="S19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="13">
         <v>304</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -7668,31 +7800,37 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
         <v>0</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
-      <c r="Q20" t="b">
-        <v>0</v>
-      </c>
-      <c r="R20" t="b">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
         <v>0</v>
       </c>
       <c r="S20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>305</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -7718,37 +7856,43 @@
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" t="s">
-        <v>262</v>
+      <c r="L21">
+        <v>0</v>
       </c>
       <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>267</v>
+      </c>
+      <c r="O21">
         <v>4</v>
-      </c>
-      <c r="N21">
-        <v>400</v>
-      </c>
-      <c r="O21" t="s">
-        <v>263</v>
       </c>
       <c r="P21">
         <v>400</v>
       </c>
-      <c r="Q21" t="b">
-        <v>0</v>
-      </c>
-      <c r="R21" t="b">
-        <v>1</v>
+      <c r="Q21" t="s">
+        <v>268</v>
+      </c>
+      <c r="R21">
+        <v>400</v>
       </c>
       <c r="S21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="13">
         <v>306</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -7777,31 +7921,37 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
         <v>0</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
-      <c r="Q22" t="b">
-        <v>0</v>
-      </c>
-      <c r="R22" t="b">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
         <v>0</v>
       </c>
       <c r="S22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="13">
         <v>307</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -7830,31 +7980,37 @@
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
         <v>0</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23" t="b">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
         <v>0</v>
       </c>
       <c r="S23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="13">
         <v>308</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -7883,31 +8039,37 @@
       <c r="K24">
         <v>1</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
-      <c r="O24">
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
         <v>0</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
-      <c r="Q24" t="b">
-        <v>0</v>
-      </c>
-      <c r="R24" t="b">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
         <v>0</v>
       </c>
       <c r="S24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
       <c r="A25" s="13">
         <v>309</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -7936,31 +8098,37 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
         <v>0</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
-      <c r="Q25" t="b">
-        <v>0</v>
-      </c>
-      <c r="R25" t="b">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
         <v>0</v>
       </c>
       <c r="S25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
       <c r="A26" s="13">
         <v>310</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -7989,31 +8157,37 @@
       <c r="K26">
         <v>1</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
         <v>0</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
-      <c r="Q26" t="b">
-        <v>0</v>
-      </c>
-      <c r="R26" t="b">
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
         <v>0</v>
       </c>
       <c r="S26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
       <c r="A27" s="13">
         <v>311</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -8042,31 +8216,37 @@
       <c r="K27">
         <v>1</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>0</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
-      <c r="Q27" t="b">
-        <v>0</v>
-      </c>
-      <c r="R27" t="b">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
         <v>0</v>
       </c>
       <c r="S27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
       <c r="A28" s="13">
         <v>312</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -8095,31 +8275,37 @@
       <c r="K28">
         <v>1</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
         <v>0</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
-      <c r="Q28" t="b">
-        <v>0</v>
-      </c>
-      <c r="R28" t="b">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
         <v>0</v>
       </c>
       <c r="S28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
       <c r="A29">
         <v>401</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C29">
         <v>18</v>
@@ -8140,42 +8326,48 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
-      <c r="L29" t="s">
-        <v>247</v>
+      <c r="L29">
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>1</v>
-      </c>
-      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>252</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
         <v>300</v>
       </c>
-      <c r="O29" t="s">
-        <v>255</v>
-      </c>
-      <c r="P29">
+      <c r="Q29" t="s">
+        <v>260</v>
+      </c>
+      <c r="R29">
         <v>600</v>
       </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29" t="b">
-        <v>1</v>
-      </c>
       <c r="S29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
+      </c>
+      <c r="U29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>402</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -8196,36 +8388,42 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="N30">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="P30">
         <v>570</v>
       </c>
-      <c r="O30" t="s">
-        <v>257</v>
-      </c>
-      <c r="P30">
+      <c r="Q30" t="s">
+        <v>262</v>
+      </c>
+      <c r="R30">
         <v>1030</v>
       </c>
-      <c r="Q30" t="b">
-        <v>0</v>
-      </c>
-      <c r="R30" t="b">
-        <v>0</v>
-      </c>
       <c r="S30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
       <c r="A31">
         <v>403</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -8246,36 +8444,42 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="N31">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="P31">
         <v>600</v>
       </c>
-      <c r="O31" t="s">
-        <v>252</v>
-      </c>
-      <c r="P31">
+      <c r="Q31" t="s">
+        <v>257</v>
+      </c>
+      <c r="R31">
         <v>300</v>
       </c>
-      <c r="Q31" t="b">
-        <v>0</v>
-      </c>
-      <c r="R31" t="b">
-        <v>0</v>
-      </c>
       <c r="S31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
       <c r="A32" s="10">
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -8296,42 +8500,48 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
-      <c r="L32" t="s">
-        <v>247</v>
+      <c r="L32">
+        <v>0</v>
       </c>
       <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>252</v>
+      </c>
+      <c r="O32">
         <v>4</v>
       </c>
-      <c r="N32">
+      <c r="P32">
         <v>900</v>
       </c>
-      <c r="O32" t="s">
-        <v>248</v>
-      </c>
-      <c r="P32">
+      <c r="Q32" t="s">
+        <v>253</v>
+      </c>
+      <c r="R32">
         <v>100</v>
       </c>
-      <c r="Q32" t="b">
-        <v>0</v>
-      </c>
-      <c r="R32" t="b">
-        <v>1</v>
-      </c>
       <c r="S32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T32" t="b">
+        <v>1</v>
+      </c>
+      <c r="U32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
       <c r="A33" s="10">
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -8357,31 +8567,37 @@
       <c r="K33">
         <v>2</v>
       </c>
-      <c r="N33">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="P33">
         <v>1300</v>
       </c>
-      <c r="O33" t="s">
-        <v>249</v>
-      </c>
-      <c r="P33">
+      <c r="Q33" t="s">
+        <v>254</v>
+      </c>
+      <c r="R33">
         <v>500</v>
       </c>
-      <c r="Q33" t="b">
-        <v>0</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
-      </c>
       <c r="S33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
       <c r="A34" s="10">
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8407,31 +8623,37 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="N34">
-        <v>500</v>
-      </c>
-      <c r="O34" t="s">
-        <v>245</v>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
       </c>
       <c r="P34">
         <v>500</v>
       </c>
-      <c r="Q34" t="b">
-        <v>0</v>
-      </c>
-      <c r="R34" t="b">
-        <v>0</v>
+      <c r="Q34" t="s">
+        <v>250</v>
+      </c>
+      <c r="R34">
+        <v>500</v>
       </c>
       <c r="S34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
       <c r="A35" s="11">
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8452,36 +8674,42 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
-      <c r="N35">
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="P35">
         <v>600</v>
       </c>
-      <c r="O35" t="s">
-        <v>252</v>
-      </c>
-      <c r="P35">
+      <c r="Q35" t="s">
+        <v>257</v>
+      </c>
+      <c r="R35">
         <v>200</v>
       </c>
-      <c r="Q35" t="b">
-        <v>0</v>
-      </c>
-      <c r="R35" t="b">
-        <v>0</v>
-      </c>
       <c r="S35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
       <c r="A36" s="11">
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8504,37 +8732,43 @@
       <c r="K36">
         <v>1</v>
       </c>
-      <c r="L36" t="s">
-        <v>247</v>
+      <c r="L36">
+        <v>0</v>
       </c>
       <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>252</v>
+      </c>
+      <c r="O36">
         <v>5</v>
       </c>
-      <c r="N36">
+      <c r="P36">
         <v>600</v>
       </c>
-      <c r="O36" t="s">
-        <v>260</v>
-      </c>
-      <c r="P36">
+      <c r="Q36" t="s">
+        <v>265</v>
+      </c>
+      <c r="R36">
         <v>300</v>
       </c>
-      <c r="Q36" t="b">
-        <v>1</v>
-      </c>
-      <c r="R36" t="b">
-        <v>1</v>
-      </c>
       <c r="S36" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:19">
+      <c r="T36" t="b">
+        <v>1</v>
+      </c>
+      <c r="U36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
       <c r="A37" s="11">
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8558,36 +8792,42 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="N37">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="P37">
         <v>500</v>
       </c>
-      <c r="O37" t="s">
-        <v>258</v>
-      </c>
-      <c r="P37">
+      <c r="Q37" t="s">
+        <v>263</v>
+      </c>
+      <c r="R37">
         <v>900</v>
       </c>
-      <c r="Q37" t="b">
-        <v>0</v>
-      </c>
-      <c r="R37" t="b">
-        <v>0</v>
-      </c>
       <c r="S37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+        <v>0</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
       <c r="A38" s="11">
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8610,19 +8850,25 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="N38">
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>0</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
-      <c r="Q38" t="b">
-        <v>0</v>
-      </c>
-      <c r="R38" t="b">
+      <c r="R38">
         <v>0</v>
       </c>
       <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8643,10 +8889,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8665,7 +8911,7 @@
         <v>210</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -8676,7 +8922,7 @@
         <v>212</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -8687,7 +8933,7 @@
         <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -8698,7 +8944,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8709,7 +8955,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -8720,7 +8966,7 @@
         <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -8731,7 +8977,7 @@
         <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -8742,7 +8988,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -8753,7 +8999,7 @@
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -8764,7 +9010,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -8775,7 +9021,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -8786,7 +9032,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -8797,7 +9043,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -8823,25 +9069,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8852,7 +9098,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -8878,7 +9124,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -8904,7 +9150,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -8930,7 +9176,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -8953,10 +9199,10 @@
         <v>207</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -8979,10 +9225,10 @@
         <v>208</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9005,10 +9251,10 @@
         <v>210</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9031,10 +9277,10 @@
         <v>213</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9072,13 +9318,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9100,7 +9346,7 @@
         <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -9126,19 +9372,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" t="s">
         <v>273</v>
       </c>
-      <c r="B1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C1" t="s">
-        <v>268</v>
-      </c>
       <c r="D1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9146,7 +9392,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9163,7 +9409,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9180,7 +9426,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9197,7 +9443,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9214,7 +9460,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9231,7 +9477,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9248,7 +9494,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -498,7 +498,7 @@
     <t>建筑/机场</t>
   </si>
   <si>
-    <t>airport</t>
+    <t>airport_500_1mesh</t>
   </si>
   <si>
     <t>可产出飞机</t>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="339">
   <si>
     <t>类型</t>
   </si>
@@ -219,355 +219,358 @@
     <t>活动单位/工虫</t>
   </si>
   <si>
+    <t>语音/是男声年轻</t>
+  </si>
+  <si>
+    <t>待机</t>
+  </si>
+  <si>
+    <t>died</t>
+  </si>
+  <si>
+    <t>音效/zdrDth00</t>
+  </si>
+  <si>
+    <t>可采集资源，可变成建筑</t>
+  </si>
+  <si>
+    <t>飞机</t>
+  </si>
+  <si>
+    <t>活动单位/飞机</t>
+  </si>
+  <si>
+    <t>音效/飞机声</t>
+  </si>
+  <si>
+    <t>p_plane_01</t>
+  </si>
+  <si>
+    <t>flight_04</t>
+  </si>
+  <si>
+    <t>slide</t>
+  </si>
+  <si>
+    <t>可飞越障碍物</t>
+  </si>
+  <si>
+    <t>枪虫</t>
+  </si>
+  <si>
+    <t>活动单位/枪虫</t>
+  </si>
+  <si>
+    <t>音效/zhyWht01</t>
+  </si>
+  <si>
+    <t>m_78</t>
+  </si>
+  <si>
+    <t>音效/zhyDth00</t>
+  </si>
+  <si>
+    <t>近战虫</t>
+  </si>
+  <si>
+    <t>活动单位/近战虫</t>
+  </si>
+  <si>
+    <t>音效/ZZeWht00</t>
+  </si>
+  <si>
+    <t>chongmu_01</t>
+  </si>
+  <si>
+    <t>音效/ZZeDth00</t>
+  </si>
+  <si>
+    <t>幼虫</t>
+  </si>
+  <si>
+    <t>活动单位/幼虫</t>
+  </si>
+  <si>
+    <t>音效/ZLaWht00</t>
+  </si>
+  <si>
+    <t>幼虫已加动作</t>
+  </si>
+  <si>
+    <t>Armature|Armature.001|Take 001|BaseLayer</t>
+  </si>
+  <si>
+    <t>Armature|Armature.004|Take 001|BaseLayer</t>
+  </si>
+  <si>
+    <t>音效/ZLaDth00</t>
+  </si>
+  <si>
+    <t>可蜕变为其它活动单位</t>
+  </si>
+  <si>
+    <t>绿色坦克</t>
+  </si>
+  <si>
+    <t>活动单位/绿色坦克</t>
+  </si>
+  <si>
+    <t>音效/ZLaPss00</t>
+  </si>
+  <si>
+    <t>p_B_tank_01</t>
+  </si>
+  <si>
+    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
+  </si>
+  <si>
+    <t>光刺</t>
+  </si>
+  <si>
+    <t>活动单位/光刺</t>
+  </si>
+  <si>
+    <t>房虫</t>
+  </si>
+  <si>
+    <t>活动单位/房虫</t>
+  </si>
+  <si>
+    <t>音效/zovWht00</t>
+  </si>
+  <si>
+    <t>骨架|stand</t>
+  </si>
+  <si>
+    <t>骨架|death</t>
+  </si>
+  <si>
+    <t>音效/zovDth00</t>
+  </si>
+  <si>
+    <t>可增加活动单位上限</t>
+  </si>
+  <si>
+    <t>飞虫</t>
+  </si>
+  <si>
+    <t>活动单位/飞虫</t>
+  </si>
+  <si>
+    <t>音效/zmuWht01</t>
+  </si>
+  <si>
+    <t>飞虫-动作</t>
+  </si>
+  <si>
+    <t>音效/zmuDth00</t>
+  </si>
+  <si>
+    <t>可飞跃障碍物</t>
+  </si>
+  <si>
+    <t>医疗兵</t>
+  </si>
+  <si>
+    <t>活动单位/医疗兵</t>
+  </si>
+  <si>
+    <t>语音/TMdWht00</t>
+  </si>
+  <si>
+    <t>Dwarf Idle</t>
+  </si>
+  <si>
+    <t>语音/TMdDth00</t>
+  </si>
+  <si>
+    <t>可给友方单位恢复HP</t>
+  </si>
+  <si>
+    <t>防空兵</t>
+  </si>
+  <si>
+    <t>活动单位/防空兵</t>
+  </si>
+  <si>
+    <t>p_C_rpg_02</t>
+  </si>
+  <si>
+    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
+  </si>
+  <si>
+    <t>基地</t>
+  </si>
+  <si>
+    <t>建筑/基地</t>
+  </si>
+  <si>
+    <t>p_Base_02</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>explo4</t>
+  </si>
+  <si>
+    <t>可产出工程车</t>
+  </si>
+  <si>
+    <t>兵营</t>
+  </si>
+  <si>
+    <t>建筑/兵营</t>
+  </si>
+  <si>
+    <t>Factory_leaye</t>
+  </si>
+  <si>
+    <t>兵营空闲</t>
+  </si>
+  <si>
+    <t>Take 001</t>
+  </si>
+  <si>
+    <t>EXPLOMED</t>
+  </si>
+  <si>
+    <t>可产出枪兵和近战兵</t>
+  </si>
+  <si>
+    <t>民房</t>
+  </si>
+  <si>
+    <t>建筑/民房</t>
+  </si>
+  <si>
+    <t>地堡</t>
+  </si>
+  <si>
+    <t>建筑/地堡</t>
+  </si>
+  <si>
+    <t>地堡872面</t>
+  </si>
+  <si>
+    <t>高HP，可派遣步兵进入地堡</t>
+  </si>
+  <si>
+    <t>炮台</t>
+  </si>
+  <si>
+    <t>建筑/炮台</t>
+  </si>
+  <si>
+    <t>p_jiqiangbao_d_01</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>音效/explo1</t>
+  </si>
+  <si>
+    <t>克制除了坦克以外的一切单位</t>
+  </si>
+  <si>
+    <t>虫巢</t>
+  </si>
+  <si>
+    <t>建筑/虫巢</t>
+  </si>
+  <si>
+    <t>音效/zhaWht00</t>
+  </si>
+  <si>
+    <t>hatchery_skin</t>
+  </si>
+  <si>
+    <t>音效/ZBldgDth</t>
+  </si>
+  <si>
+    <t>可产出幼虫</t>
+  </si>
+  <si>
+    <t>机场</t>
+  </si>
+  <si>
+    <t>建筑/机场</t>
+  </si>
+  <si>
+    <t>airport_500_1mesh</t>
+  </si>
+  <si>
+    <t>可产出飞机</t>
+  </si>
+  <si>
+    <t>重车厂</t>
+  </si>
+  <si>
+    <t>建筑/重车厂</t>
+  </si>
+  <si>
+    <t>风扇飞</t>
+  </si>
+  <si>
+    <t>重车厂Idle</t>
+  </si>
+  <si>
+    <t>可产出三色坦克</t>
+  </si>
+  <si>
+    <t>虫营</t>
+  </si>
+  <si>
+    <t>建筑/虫营</t>
+  </si>
+  <si>
+    <t>音效/zspWht00</t>
+  </si>
+  <si>
+    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>飞塔</t>
+  </si>
+  <si>
+    <t>建筑/飞塔</t>
+  </si>
+  <si>
+    <t>音效/zscWht00</t>
+  </si>
+  <si>
+    <t>飞虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>拟态源</t>
+  </si>
+  <si>
+    <t>建筑/拟态源</t>
+  </si>
+  <si>
+    <t>绿色坦克的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>太岁</t>
+  </si>
+  <si>
+    <t>建筑/太岁</t>
+  </si>
+  <si>
+    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
+  </si>
+  <si>
+    <t>枪虫怪</t>
+  </si>
+  <si>
+    <t>近战虫怪</t>
+  </si>
+  <si>
+    <t>工怪</t>
+  </si>
+  <si>
     <t>音效/zdrWht00</t>
-  </si>
-  <si>
-    <t>待机</t>
-  </si>
-  <si>
-    <t>died</t>
-  </si>
-  <si>
-    <t>音效/zdrDth00</t>
-  </si>
-  <si>
-    <t>可采集资源，可变成建筑</t>
-  </si>
-  <si>
-    <t>飞机</t>
-  </si>
-  <si>
-    <t>活动单位/飞机</t>
-  </si>
-  <si>
-    <t>音效/飞机声</t>
-  </si>
-  <si>
-    <t>p_plane_01</t>
-  </si>
-  <si>
-    <t>flight_04</t>
-  </si>
-  <si>
-    <t>slide</t>
-  </si>
-  <si>
-    <t>可飞越障碍物</t>
-  </si>
-  <si>
-    <t>枪虫</t>
-  </si>
-  <si>
-    <t>活动单位/枪虫</t>
-  </si>
-  <si>
-    <t>音效/zhyWht01</t>
-  </si>
-  <si>
-    <t>m_78</t>
-  </si>
-  <si>
-    <t>音效/zhyDth00</t>
-  </si>
-  <si>
-    <t>近战虫</t>
-  </si>
-  <si>
-    <t>活动单位/近战虫</t>
-  </si>
-  <si>
-    <t>音效/ZZeWht00</t>
-  </si>
-  <si>
-    <t>chongmu_01</t>
-  </si>
-  <si>
-    <t>音效/ZZeDth00</t>
-  </si>
-  <si>
-    <t>幼虫</t>
-  </si>
-  <si>
-    <t>活动单位/幼虫</t>
-  </si>
-  <si>
-    <t>音效/ZLaWht00</t>
-  </si>
-  <si>
-    <t>幼虫已加动作</t>
-  </si>
-  <si>
-    <t>Armature|Armature.001|Take 001|BaseLayer</t>
-  </si>
-  <si>
-    <t>Armature|Armature.004|Take 001|BaseLayer</t>
-  </si>
-  <si>
-    <t>音效/ZLaDth00</t>
-  </si>
-  <si>
-    <t>可蜕变为其它活动单位</t>
-  </si>
-  <si>
-    <t>绿色坦克</t>
-  </si>
-  <si>
-    <t>活动单位/绿色坦克</t>
-  </si>
-  <si>
-    <t>音效/ZLaPss00</t>
-  </si>
-  <si>
-    <t>p_B_tank_01</t>
-  </si>
-  <si>
-    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
-  </si>
-  <si>
-    <t>光刺</t>
-  </si>
-  <si>
-    <t>活动单位/光刺</t>
-  </si>
-  <si>
-    <t>房虫</t>
-  </si>
-  <si>
-    <t>活动单位/房虫</t>
-  </si>
-  <si>
-    <t>音效/zovWht00</t>
-  </si>
-  <si>
-    <t>骨架|stand</t>
-  </si>
-  <si>
-    <t>骨架|death</t>
-  </si>
-  <si>
-    <t>音效/zovDth00</t>
-  </si>
-  <si>
-    <t>可增加活动单位上限</t>
-  </si>
-  <si>
-    <t>飞虫</t>
-  </si>
-  <si>
-    <t>活动单位/飞虫</t>
-  </si>
-  <si>
-    <t>音效/zmuWht01</t>
-  </si>
-  <si>
-    <t>飞虫-动作</t>
-  </si>
-  <si>
-    <t>音效/zmuDth00</t>
-  </si>
-  <si>
-    <t>可飞跃障碍物</t>
-  </si>
-  <si>
-    <t>医疗兵</t>
-  </si>
-  <si>
-    <t>活动单位/医疗兵</t>
-  </si>
-  <si>
-    <t>语音/TMdWht00</t>
-  </si>
-  <si>
-    <t>Dwarf Idle</t>
-  </si>
-  <si>
-    <t>语音/TMdDth00</t>
-  </si>
-  <si>
-    <t>可给友方单位恢复HP</t>
-  </si>
-  <si>
-    <t>防空兵</t>
-  </si>
-  <si>
-    <t>活动单位/防空兵</t>
-  </si>
-  <si>
-    <t>p_C_rpg_02</t>
-  </si>
-  <si>
-    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
-  </si>
-  <si>
-    <t>基地</t>
-  </si>
-  <si>
-    <t>建筑/基地</t>
-  </si>
-  <si>
-    <t>p_Base_02</t>
-  </si>
-  <si>
-    <t>die</t>
-  </si>
-  <si>
-    <t>explo4</t>
-  </si>
-  <si>
-    <t>可产出工程车</t>
-  </si>
-  <si>
-    <t>兵营</t>
-  </si>
-  <si>
-    <t>建筑/兵营</t>
-  </si>
-  <si>
-    <t>Factory_leaye</t>
-  </si>
-  <si>
-    <t>兵营空闲</t>
-  </si>
-  <si>
-    <t>Take 001</t>
-  </si>
-  <si>
-    <t>EXPLOMED</t>
-  </si>
-  <si>
-    <t>可产出枪兵和近战兵</t>
-  </si>
-  <si>
-    <t>民房</t>
-  </si>
-  <si>
-    <t>建筑/民房</t>
-  </si>
-  <si>
-    <t>地堡</t>
-  </si>
-  <si>
-    <t>建筑/地堡</t>
-  </si>
-  <si>
-    <t>地堡872面</t>
-  </si>
-  <si>
-    <t>高HP，可派遣步兵进入地堡</t>
-  </si>
-  <si>
-    <t>炮台</t>
-  </si>
-  <si>
-    <t>建筑/炮台</t>
-  </si>
-  <si>
-    <t>p_jiqiangbao_d_01</t>
-  </si>
-  <si>
-    <t>show</t>
-  </si>
-  <si>
-    <t>音效/explo1</t>
-  </si>
-  <si>
-    <t>克制除了坦克以外的一切单位</t>
-  </si>
-  <si>
-    <t>虫巢</t>
-  </si>
-  <si>
-    <t>建筑/虫巢</t>
-  </si>
-  <si>
-    <t>音效/zhaWht00</t>
-  </si>
-  <si>
-    <t>hatchery_skin</t>
-  </si>
-  <si>
-    <t>音效/ZBldgDth</t>
-  </si>
-  <si>
-    <t>可产出幼虫</t>
-  </si>
-  <si>
-    <t>机场</t>
-  </si>
-  <si>
-    <t>建筑/机场</t>
-  </si>
-  <si>
-    <t>airport_500_1mesh</t>
-  </si>
-  <si>
-    <t>可产出飞机</t>
-  </si>
-  <si>
-    <t>重车厂</t>
-  </si>
-  <si>
-    <t>建筑/重车厂</t>
-  </si>
-  <si>
-    <t>风扇飞</t>
-  </si>
-  <si>
-    <t>重车厂Idle</t>
-  </si>
-  <si>
-    <t>可产出三色坦克</t>
-  </si>
-  <si>
-    <t>虫营</t>
-  </si>
-  <si>
-    <t>建筑/虫营</t>
-  </si>
-  <si>
-    <t>音效/zspWht00</t>
-  </si>
-  <si>
-    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>飞塔</t>
-  </si>
-  <si>
-    <t>建筑/飞塔</t>
-  </si>
-  <si>
-    <t>音效/zscWht00</t>
-  </si>
-  <si>
-    <t>飞虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>拟态源</t>
-  </si>
-  <si>
-    <t>建筑/拟态源</t>
-  </si>
-  <si>
-    <t>绿色坦克的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>太岁</t>
-  </si>
-  <si>
-    <t>建筑/太岁</t>
-  </si>
-  <si>
-    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
-  </si>
-  <si>
-    <t>枪虫怪</t>
-  </si>
-  <si>
-    <t>近战虫怪</t>
-  </si>
-  <si>
-    <t>工怪</t>
   </si>
   <si>
     <t>枪兵怪</t>
@@ -4136,7 +4139,7 @@
         <v>59</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>61</v>
@@ -4180,13 +4183,13 @@
         <v>404</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C38" s="11">
         <v>1</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>41</v>
@@ -4230,7 +4233,7 @@
         <v>405</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4289,7 +4292,7 @@
         <v>406</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
@@ -4342,7 +4345,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4398,7 +4401,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4454,7 +4457,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4510,7 +4513,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4587,22 +4590,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4610,16 +4613,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4627,16 +4630,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4644,16 +4647,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4661,16 +4664,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4678,16 +4681,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4695,16 +4698,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" t="s">
         <v>305</v>
-      </c>
-      <c r="C7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4712,16 +4715,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4729,16 +4732,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" t="s">
         <v>310</v>
-      </c>
-      <c r="C9" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4746,16 +4749,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4763,16 +4766,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4780,22 +4783,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4803,16 +4806,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4820,22 +4823,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4843,16 +4846,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4860,22 +4863,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4905,10 +4908,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4917,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4925,7 +4928,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4950,22 +4953,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5140,7 +5143,7 @@
         <v>6</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>15</v>
@@ -5163,7 +5166,7 @@
         <v>3</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>12</v>
@@ -5637,22 +5640,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5729,7 +5732,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5975,25 +5978,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6004,7 +6007,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6019,7 +6022,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6030,10 +6033,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6045,7 +6048,7 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6056,7 +6059,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6071,7 +6074,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6082,10 +6085,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6097,7 +6100,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6108,10 +6111,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6120,10 +6123,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6149,7 +6152,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6160,10 +6163,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6172,10 +6175,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6186,10 +6189,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6198,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6215,7 +6218,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6238,10 +6241,10 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6250,10 +6253,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6278,7 +6281,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6290,10 +6293,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6304,7 +6307,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6316,10 +6319,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6330,7 +6333,7 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6342,10 +6345,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6356,10 +6359,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6371,7 +6374,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6382,10 +6385,10 @@
         <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6402,10 +6405,10 @@
         <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6422,10 +6425,10 @@
         <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6439,13 +6442,13 @@
         <v>404</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6457,7 +6460,7 @@
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6465,10 +6468,10 @@
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6483,7 +6486,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6491,10 +6494,10 @@
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6509,7 +6512,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6517,13 +6520,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6543,10 +6546,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6558,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6569,13 +6572,13 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6584,10 +6587,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6595,10 +6598,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6610,10 +6613,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6662,64 +6665,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6763,7 +6766,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6804,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -6816,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6825,7 +6828,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6881,7 +6884,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6925,7 +6928,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6937,13 +6940,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -6984,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -6999,7 +7002,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7052,7 +7055,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7061,7 +7064,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7102,7 +7105,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7114,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7123,7 +7126,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7164,7 +7167,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7179,7 +7182,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7220,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7235,7 +7238,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7279,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7294,7 +7297,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7347,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7447,7 +7450,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7456,7 +7459,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7512,7 +7515,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7553,7 +7556,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7565,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7574,7 +7577,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7863,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7872,7 +7875,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8326,7 +8329,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8338,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8347,7 +8350,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8388,7 +8391,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8403,7 +8406,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8444,7 +8447,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8459,7 +8462,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8479,7 +8482,7 @@
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -8500,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -8512,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8521,7 +8524,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8541,7 +8544,7 @@
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -8577,7 +8580,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8597,7 +8600,7 @@
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8633,7 +8636,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8653,7 +8656,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8674,7 +8677,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8689,7 +8692,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8709,7 +8712,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8739,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8748,7 +8751,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8768,7 +8771,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8792,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8807,7 +8810,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8827,7 +8830,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8889,10 +8892,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8944,7 +8947,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8955,7 +8958,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -8977,7 +8980,7 @@
         <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -8988,7 +8991,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -8999,7 +9002,7 @@
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -9010,7 +9013,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9021,7 +9024,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9032,7 +9035,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9043,7 +9046,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -9069,25 +9072,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9098,7 +9101,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9124,7 +9127,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9150,7 +9153,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9176,7 +9179,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9202,7 +9205,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9228,7 +9231,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9254,7 +9257,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9280,7 +9283,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9318,13 +9321,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9372,19 +9375,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9392,7 +9395,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9409,7 +9412,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9426,7 +9429,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9443,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9460,7 +9463,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9477,7 +9480,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9494,7 +9497,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="340">
   <si>
     <t>类型</t>
   </si>
@@ -147,442 +147,445 @@
     <t>语音/是女声可爱版</t>
   </si>
   <si>
+    <t>wajueji_model_1mesh_v3</t>
+  </si>
+  <si>
+    <t>TSCDth00</t>
+  </si>
+  <si>
+    <t>可采集资源，可建造建筑</t>
+  </si>
+  <si>
+    <t>枪兵</t>
+  </si>
+  <si>
+    <t>活动单位/枪兵</t>
+  </si>
+  <si>
+    <t>语音/是男声正经版</t>
+  </si>
+  <si>
+    <t>p_A_rifle_01</t>
+  </si>
+  <si>
+    <t>die01</t>
+  </si>
+  <si>
+    <t>TMaDth00</t>
+  </si>
+  <si>
+    <t>远程攻击</t>
+  </si>
+  <si>
+    <t>近战兵</t>
+  </si>
+  <si>
+    <t>活动单位/近战兵</t>
+  </si>
+  <si>
+    <t>tfbPss00</t>
+  </si>
+  <si>
+    <t>近战兵999面_Idle</t>
+  </si>
+  <si>
+    <t>TFbDth00</t>
+  </si>
+  <si>
+    <t>近程攻击</t>
+  </si>
+  <si>
+    <t>三色坦克</t>
+  </si>
+  <si>
+    <t>活动单位/三色坦克</t>
+  </si>
+  <si>
+    <t>音效/坦克行进声</t>
+  </si>
+  <si>
+    <t>die02</t>
+  </si>
+  <si>
+    <t>音效/TTaDth00</t>
+  </si>
+  <si>
+    <t>超远距离范围攻击，前摇较长，克制炮台。爆炸溅射可能会伤害己方单位。</t>
+  </si>
+  <si>
+    <t>工虫</t>
+  </si>
+  <si>
+    <t>活动单位/工虫</t>
+  </si>
+  <si>
+    <t>语音/是男声年轻</t>
+  </si>
+  <si>
+    <t>待机</t>
+  </si>
+  <si>
+    <t>died</t>
+  </si>
+  <si>
+    <t>音效/zdrDth00</t>
+  </si>
+  <si>
+    <t>可采集资源，可变成建筑</t>
+  </si>
+  <si>
+    <t>飞机</t>
+  </si>
+  <si>
+    <t>活动单位/飞机</t>
+  </si>
+  <si>
+    <t>音效/飞机声</t>
+  </si>
+  <si>
+    <t>p_plane_01</t>
+  </si>
+  <si>
+    <t>flight_04</t>
+  </si>
+  <si>
+    <t>slide</t>
+  </si>
+  <si>
+    <t>可飞越障碍物</t>
+  </si>
+  <si>
+    <t>枪虫</t>
+  </si>
+  <si>
+    <t>活动单位/枪虫</t>
+  </si>
+  <si>
+    <t>音效/zhyWht01</t>
+  </si>
+  <si>
+    <t>m_78</t>
+  </si>
+  <si>
+    <t>音效/zhyDth00</t>
+  </si>
+  <si>
+    <t>近战虫</t>
+  </si>
+  <si>
+    <t>活动单位/近战虫</t>
+  </si>
+  <si>
+    <t>音效/ZZeWht00</t>
+  </si>
+  <si>
+    <t>chongmu_01</t>
+  </si>
+  <si>
+    <t>音效/ZZeDth00</t>
+  </si>
+  <si>
+    <t>幼虫</t>
+  </si>
+  <si>
+    <t>活动单位/幼虫</t>
+  </si>
+  <si>
+    <t>音效/ZLaWht00</t>
+  </si>
+  <si>
+    <t>幼虫已加动作</t>
+  </si>
+  <si>
+    <t>Armature|Armature.001|Take 001|BaseLayer</t>
+  </si>
+  <si>
+    <t>Armature|Armature.004|Take 001|BaseLayer</t>
+  </si>
+  <si>
+    <t>音效/ZLaDth00</t>
+  </si>
+  <si>
+    <t>可蜕变为其它活动单位</t>
+  </si>
+  <si>
+    <t>绿色坦克</t>
+  </si>
+  <si>
+    <t>活动单位/绿色坦克</t>
+  </si>
+  <si>
+    <t>音效/ZLaPss00</t>
+  </si>
+  <si>
+    <t>p_B_tank_01</t>
+  </si>
+  <si>
+    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
+  </si>
+  <si>
+    <t>光刺</t>
+  </si>
+  <si>
+    <t>活动单位/光刺</t>
+  </si>
+  <si>
+    <t>房虫</t>
+  </si>
+  <si>
+    <t>活动单位/房虫</t>
+  </si>
+  <si>
+    <t>音效/zovWht00</t>
+  </si>
+  <si>
+    <t>骨架|stand</t>
+  </si>
+  <si>
+    <t>骨架|death</t>
+  </si>
+  <si>
+    <t>音效/zovDth00</t>
+  </si>
+  <si>
+    <t>可增加活动单位上限</t>
+  </si>
+  <si>
+    <t>飞虫</t>
+  </si>
+  <si>
+    <t>活动单位/飞虫</t>
+  </si>
+  <si>
+    <t>音效/zmuWht01</t>
+  </si>
+  <si>
+    <t>飞虫-动作</t>
+  </si>
+  <si>
+    <t>音效/zmuDth00</t>
+  </si>
+  <si>
+    <t>可飞跃障碍物</t>
+  </si>
+  <si>
+    <t>医疗兵</t>
+  </si>
+  <si>
+    <t>活动单位/医疗兵</t>
+  </si>
+  <si>
+    <t>语音/TMdWht00</t>
+  </si>
+  <si>
+    <t>Dwarf Idle</t>
+  </si>
+  <si>
+    <t>语音/TMdDth00</t>
+  </si>
+  <si>
+    <t>可给友方单位恢复HP</t>
+  </si>
+  <si>
+    <t>防空兵</t>
+  </si>
+  <si>
+    <t>活动单位/防空兵</t>
+  </si>
+  <si>
+    <t>p_C_rpg_02</t>
+  </si>
+  <si>
+    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
+  </si>
+  <si>
+    <t>基地</t>
+  </si>
+  <si>
+    <t>建筑/基地</t>
+  </si>
+  <si>
+    <t>p_Base_02</t>
+  </si>
+  <si>
+    <t>die</t>
+  </si>
+  <si>
+    <t>explo4</t>
+  </si>
+  <si>
+    <t>可产出工程车</t>
+  </si>
+  <si>
+    <t>兵营</t>
+  </si>
+  <si>
+    <t>建筑/兵营</t>
+  </si>
+  <si>
+    <t>Factory_leaye</t>
+  </si>
+  <si>
+    <t>兵营空闲</t>
+  </si>
+  <si>
+    <t>Take 001</t>
+  </si>
+  <si>
+    <t>EXPLOMED</t>
+  </si>
+  <si>
+    <t>可产出枪兵和近战兵</t>
+  </si>
+  <si>
+    <t>民房</t>
+  </si>
+  <si>
+    <t>建筑/民房</t>
+  </si>
+  <si>
+    <t>地堡</t>
+  </si>
+  <si>
+    <t>建筑/地堡</t>
+  </si>
+  <si>
+    <t>地堡872面</t>
+  </si>
+  <si>
+    <t>高HP，可派遣步兵进入地堡</t>
+  </si>
+  <si>
+    <t>炮台</t>
+  </si>
+  <si>
+    <t>建筑/炮台</t>
+  </si>
+  <si>
+    <t>p_jiqiangbao_d_01</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>音效/explo1</t>
+  </si>
+  <si>
+    <t>克制除了坦克以外的一切单位</t>
+  </si>
+  <si>
+    <t>虫巢</t>
+  </si>
+  <si>
+    <t>建筑/虫巢</t>
+  </si>
+  <si>
+    <t>音效/zhaWht00</t>
+  </si>
+  <si>
+    <t>hatchery_skin</t>
+  </si>
+  <si>
+    <t>音效/ZBldgDth</t>
+  </si>
+  <si>
+    <t>可产出幼虫</t>
+  </si>
+  <si>
+    <t>机场</t>
+  </si>
+  <si>
+    <t>建筑/机场</t>
+  </si>
+  <si>
+    <t>airport_500_1mesh</t>
+  </si>
+  <si>
+    <t>可产出飞机</t>
+  </si>
+  <si>
+    <t>重车厂</t>
+  </si>
+  <si>
+    <t>建筑/重车厂</t>
+  </si>
+  <si>
+    <t>风扇飞</t>
+  </si>
+  <si>
+    <t>重车厂Idle</t>
+  </si>
+  <si>
+    <t>可产出三色坦克</t>
+  </si>
+  <si>
+    <t>虫营</t>
+  </si>
+  <si>
+    <t>建筑/虫营</t>
+  </si>
+  <si>
+    <t>音效/zspWht00</t>
+  </si>
+  <si>
+    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>飞塔</t>
+  </si>
+  <si>
+    <t>建筑/飞塔</t>
+  </si>
+  <si>
+    <t>音效/zscWht00</t>
+  </si>
+  <si>
+    <t>飞虫的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>拟态源</t>
+  </si>
+  <si>
+    <t>建筑/拟态源</t>
+  </si>
+  <si>
+    <t>绿色坦克的前置建筑，只需1个就够了</t>
+  </si>
+  <si>
+    <t>太岁</t>
+  </si>
+  <si>
+    <t>建筑/太岁</t>
+  </si>
+  <si>
+    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
+  </si>
+  <si>
+    <t>枪虫怪</t>
+  </si>
+  <si>
+    <t>近战虫怪</t>
+  </si>
+  <si>
+    <t>工怪</t>
+  </si>
+  <si>
+    <t>音效/zdrWht00</t>
+  </si>
+  <si>
+    <t>枪兵怪</t>
+  </si>
+  <si>
+    <t>活动单位/步兵</t>
+  </si>
+  <si>
+    <t>近战兵怪</t>
+  </si>
+  <si>
+    <t>工程车怪</t>
+  </si>
+  <si>
     <t>wajueji_已绑定的模型</t>
-  </si>
-  <si>
-    <t>TSCDth00</t>
-  </si>
-  <si>
-    <t>可采集资源，可建造建筑</t>
-  </si>
-  <si>
-    <t>枪兵</t>
-  </si>
-  <si>
-    <t>活动单位/枪兵</t>
-  </si>
-  <si>
-    <t>语音/是男声正经版</t>
-  </si>
-  <si>
-    <t>p_A_rifle_01</t>
-  </si>
-  <si>
-    <t>die01</t>
-  </si>
-  <si>
-    <t>TMaDth00</t>
-  </si>
-  <si>
-    <t>远程攻击</t>
-  </si>
-  <si>
-    <t>近战兵</t>
-  </si>
-  <si>
-    <t>活动单位/近战兵</t>
-  </si>
-  <si>
-    <t>tfbPss00</t>
-  </si>
-  <si>
-    <t>近战兵999面_Idle</t>
-  </si>
-  <si>
-    <t>TFbDth00</t>
-  </si>
-  <si>
-    <t>近程攻击</t>
-  </si>
-  <si>
-    <t>三色坦克</t>
-  </si>
-  <si>
-    <t>活动单位/三色坦克</t>
-  </si>
-  <si>
-    <t>音效/坦克行进声</t>
-  </si>
-  <si>
-    <t>die02</t>
-  </si>
-  <si>
-    <t>音效/TTaDth00</t>
-  </si>
-  <si>
-    <t>超远距离范围攻击，前摇较长，克制炮台。爆炸溅射可能会伤害己方单位。</t>
-  </si>
-  <si>
-    <t>工虫</t>
-  </si>
-  <si>
-    <t>活动单位/工虫</t>
-  </si>
-  <si>
-    <t>语音/是男声年轻</t>
-  </si>
-  <si>
-    <t>待机</t>
-  </si>
-  <si>
-    <t>died</t>
-  </si>
-  <si>
-    <t>音效/zdrDth00</t>
-  </si>
-  <si>
-    <t>可采集资源，可变成建筑</t>
-  </si>
-  <si>
-    <t>飞机</t>
-  </si>
-  <si>
-    <t>活动单位/飞机</t>
-  </si>
-  <si>
-    <t>音效/飞机声</t>
-  </si>
-  <si>
-    <t>p_plane_01</t>
-  </si>
-  <si>
-    <t>flight_04</t>
-  </si>
-  <si>
-    <t>slide</t>
-  </si>
-  <si>
-    <t>可飞越障碍物</t>
-  </si>
-  <si>
-    <t>枪虫</t>
-  </si>
-  <si>
-    <t>活动单位/枪虫</t>
-  </si>
-  <si>
-    <t>音效/zhyWht01</t>
-  </si>
-  <si>
-    <t>m_78</t>
-  </si>
-  <si>
-    <t>音效/zhyDth00</t>
-  </si>
-  <si>
-    <t>近战虫</t>
-  </si>
-  <si>
-    <t>活动单位/近战虫</t>
-  </si>
-  <si>
-    <t>音效/ZZeWht00</t>
-  </si>
-  <si>
-    <t>chongmu_01</t>
-  </si>
-  <si>
-    <t>音效/ZZeDth00</t>
-  </si>
-  <si>
-    <t>幼虫</t>
-  </si>
-  <si>
-    <t>活动单位/幼虫</t>
-  </si>
-  <si>
-    <t>音效/ZLaWht00</t>
-  </si>
-  <si>
-    <t>幼虫已加动作</t>
-  </si>
-  <si>
-    <t>Armature|Armature.001|Take 001|BaseLayer</t>
-  </si>
-  <si>
-    <t>Armature|Armature.004|Take 001|BaseLayer</t>
-  </si>
-  <si>
-    <t>音效/ZLaDth00</t>
-  </si>
-  <si>
-    <t>可蜕变为其它活动单位</t>
-  </si>
-  <si>
-    <t>绿色坦克</t>
-  </si>
-  <si>
-    <t>活动单位/绿色坦克</t>
-  </si>
-  <si>
-    <t>音效/ZLaPss00</t>
-  </si>
-  <si>
-    <t>p_B_tank_01</t>
-  </si>
-  <si>
-    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
-  </si>
-  <si>
-    <t>光刺</t>
-  </si>
-  <si>
-    <t>活动单位/光刺</t>
-  </si>
-  <si>
-    <t>房虫</t>
-  </si>
-  <si>
-    <t>活动单位/房虫</t>
-  </si>
-  <si>
-    <t>音效/zovWht00</t>
-  </si>
-  <si>
-    <t>骨架|stand</t>
-  </si>
-  <si>
-    <t>骨架|death</t>
-  </si>
-  <si>
-    <t>音效/zovDth00</t>
-  </si>
-  <si>
-    <t>可增加活动单位上限</t>
-  </si>
-  <si>
-    <t>飞虫</t>
-  </si>
-  <si>
-    <t>活动单位/飞虫</t>
-  </si>
-  <si>
-    <t>音效/zmuWht01</t>
-  </si>
-  <si>
-    <t>飞虫-动作</t>
-  </si>
-  <si>
-    <t>音效/zmuDth00</t>
-  </si>
-  <si>
-    <t>可飞跃障碍物</t>
-  </si>
-  <si>
-    <t>医疗兵</t>
-  </si>
-  <si>
-    <t>活动单位/医疗兵</t>
-  </si>
-  <si>
-    <t>语音/TMdWht00</t>
-  </si>
-  <si>
-    <t>Dwarf Idle</t>
-  </si>
-  <si>
-    <t>语音/TMdDth00</t>
-  </si>
-  <si>
-    <t>可给友方单位恢复HP</t>
-  </si>
-  <si>
-    <t>防空兵</t>
-  </si>
-  <si>
-    <t>活动单位/防空兵</t>
-  </si>
-  <si>
-    <t>p_C_rpg_02</t>
-  </si>
-  <si>
-    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
-  </si>
-  <si>
-    <t>基地</t>
-  </si>
-  <si>
-    <t>建筑/基地</t>
-  </si>
-  <si>
-    <t>p_Base_02</t>
-  </si>
-  <si>
-    <t>die</t>
-  </si>
-  <si>
-    <t>explo4</t>
-  </si>
-  <si>
-    <t>可产出工程车</t>
-  </si>
-  <si>
-    <t>兵营</t>
-  </si>
-  <si>
-    <t>建筑/兵营</t>
-  </si>
-  <si>
-    <t>Factory_leaye</t>
-  </si>
-  <si>
-    <t>兵营空闲</t>
-  </si>
-  <si>
-    <t>Take 001</t>
-  </si>
-  <si>
-    <t>EXPLOMED</t>
-  </si>
-  <si>
-    <t>可产出枪兵和近战兵</t>
-  </si>
-  <si>
-    <t>民房</t>
-  </si>
-  <si>
-    <t>建筑/民房</t>
-  </si>
-  <si>
-    <t>地堡</t>
-  </si>
-  <si>
-    <t>建筑/地堡</t>
-  </si>
-  <si>
-    <t>地堡872面</t>
-  </si>
-  <si>
-    <t>高HP，可派遣步兵进入地堡</t>
-  </si>
-  <si>
-    <t>炮台</t>
-  </si>
-  <si>
-    <t>建筑/炮台</t>
-  </si>
-  <si>
-    <t>p_jiqiangbao_d_01</t>
-  </si>
-  <si>
-    <t>show</t>
-  </si>
-  <si>
-    <t>音效/explo1</t>
-  </si>
-  <si>
-    <t>克制除了坦克以外的一切单位</t>
-  </si>
-  <si>
-    <t>虫巢</t>
-  </si>
-  <si>
-    <t>建筑/虫巢</t>
-  </si>
-  <si>
-    <t>音效/zhaWht00</t>
-  </si>
-  <si>
-    <t>hatchery_skin</t>
-  </si>
-  <si>
-    <t>音效/ZBldgDth</t>
-  </si>
-  <si>
-    <t>可产出幼虫</t>
-  </si>
-  <si>
-    <t>机场</t>
-  </si>
-  <si>
-    <t>建筑/机场</t>
-  </si>
-  <si>
-    <t>airport_500_1mesh</t>
-  </si>
-  <si>
-    <t>可产出飞机</t>
-  </si>
-  <si>
-    <t>重车厂</t>
-  </si>
-  <si>
-    <t>建筑/重车厂</t>
-  </si>
-  <si>
-    <t>风扇飞</t>
-  </si>
-  <si>
-    <t>重车厂Idle</t>
-  </si>
-  <si>
-    <t>可产出三色坦克</t>
-  </si>
-  <si>
-    <t>虫营</t>
-  </si>
-  <si>
-    <t>建筑/虫营</t>
-  </si>
-  <si>
-    <t>音效/zspWht00</t>
-  </si>
-  <si>
-    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>飞塔</t>
-  </si>
-  <si>
-    <t>建筑/飞塔</t>
-  </si>
-  <si>
-    <t>音效/zscWht00</t>
-  </si>
-  <si>
-    <t>飞虫的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>拟态源</t>
-  </si>
-  <si>
-    <t>建筑/拟态源</t>
-  </si>
-  <si>
-    <t>绿色坦克的前置建筑，只需1个就够了</t>
-  </si>
-  <si>
-    <t>太岁</t>
-  </si>
-  <si>
-    <t>建筑/太岁</t>
-  </si>
-  <si>
-    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
-  </si>
-  <si>
-    <t>枪虫怪</t>
-  </si>
-  <si>
-    <t>近战虫怪</t>
-  </si>
-  <si>
-    <t>工怪</t>
-  </si>
-  <si>
-    <t>音效/zdrWht00</t>
-  </si>
-  <si>
-    <t>枪兵怪</t>
-  </si>
-  <si>
-    <t>活动单位/步兵</t>
-  </si>
-  <si>
-    <t>近战兵怪</t>
-  </si>
-  <si>
-    <t>工程车怪</t>
   </si>
   <si>
     <t>幼虫怪,</t>
@@ -4304,7 +4307,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>36</v>
+        <v>182</v>
       </c>
       <c r="G40" s="19" t="b">
         <v>1</v>
@@ -4345,7 +4348,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4401,7 +4404,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4457,7 +4460,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4513,7 +4516,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4590,22 +4593,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4613,16 +4616,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4630,16 +4633,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="C3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4647,16 +4650,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4664,16 +4667,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C5" t="s">
-        <v>300</v>
-      </c>
-      <c r="D5" t="s">
-        <v>301</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4681,16 +4684,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4698,16 +4701,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" t="s">
         <v>306</v>
-      </c>
-      <c r="C7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" t="s">
-        <v>296</v>
-      </c>
-      <c r="E7" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4715,16 +4718,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4732,16 +4735,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" t="s">
         <v>311</v>
-      </c>
-      <c r="C9" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4749,16 +4752,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4766,16 +4769,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4783,22 +4786,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4806,16 +4809,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4823,22 +4826,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D14" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4846,16 +4849,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E15" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4863,22 +4866,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4908,10 +4911,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4920,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4928,7 +4931,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4953,22 +4956,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5640,22 +5643,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5732,7 +5735,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5978,25 +5981,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6007,7 +6010,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6022,7 +6025,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6033,10 +6036,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6048,7 +6051,7 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6059,7 +6062,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6074,7 +6077,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6085,10 +6088,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6100,7 +6103,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6111,10 +6114,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6123,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6152,7 +6155,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6163,10 +6166,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6175,10 +6178,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6189,10 +6192,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6201,10 +6204,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6218,7 +6221,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6241,10 +6244,10 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6253,10 +6256,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6281,7 +6284,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6293,10 +6296,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6307,7 +6310,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6319,10 +6322,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6333,7 +6336,7 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6345,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6359,10 +6362,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6374,7 +6377,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6385,10 +6388,10 @@
         <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6405,10 +6408,10 @@
         <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6425,10 +6428,10 @@
         <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6445,10 +6448,10 @@
         <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6460,7 +6463,7 @@
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6471,7 +6474,7 @@
         <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6486,7 +6489,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6497,7 +6500,7 @@
         <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6512,7 +6515,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6520,13 +6523,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6546,10 +6549,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6561,10 +6564,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6572,13 +6575,13 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6587,10 +6590,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6598,10 +6601,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6613,10 +6616,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H26" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -6665,64 +6668,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6766,7 +6769,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6807,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -6819,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6828,7 +6831,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6884,7 +6887,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6928,7 +6931,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6940,13 +6943,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -6987,7 +6990,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7002,7 +7005,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7055,7 +7058,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7064,7 +7067,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7105,7 +7108,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7117,7 +7120,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7126,7 +7129,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7167,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7182,7 +7185,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7223,7 +7226,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7238,7 +7241,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7282,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7297,7 +7300,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7350,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7450,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7459,7 +7462,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7515,7 +7518,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7556,7 +7559,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7568,7 +7571,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7577,7 +7580,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7866,7 +7869,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7875,7 +7878,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8329,7 +8332,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8341,7 +8344,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8350,7 +8353,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8391,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8406,7 +8409,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8447,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8462,7 +8465,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8503,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -8515,7 +8518,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8524,7 +8527,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8580,7 +8583,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8636,7 +8639,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8656,7 +8659,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8677,7 +8680,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8692,7 +8695,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8712,7 +8715,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8742,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8751,7 +8754,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8771,7 +8774,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8795,7 +8798,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8810,7 +8813,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8830,7 +8833,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8892,10 +8895,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8947,7 +8950,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8958,7 +8961,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -9013,7 +9016,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9024,7 +9027,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9035,7 +9038,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9046,7 +9049,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -9072,25 +9075,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9101,7 +9104,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9127,7 +9130,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9153,7 +9156,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9179,7 +9182,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9205,7 +9208,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9231,7 +9234,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9257,7 +9260,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9283,7 +9286,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9321,13 +9324,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9375,19 +9378,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9395,7 +9398,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9412,7 +9415,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9429,7 +9432,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9446,7 +9449,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9463,7 +9466,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9480,7 +9483,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9497,7 +9500,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="341">
   <si>
     <t>类型</t>
   </si>
@@ -1121,6 +1121,9 @@
   </si>
   <si>
     <t>多玩家混战</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3</t>
   </si>
   <si>
     <t>圆坑混战</t>
@@ -4857,8 +4860,8 @@
       <c r="D15" t="s">
         <v>297</v>
       </c>
-      <c r="E15" t="s">
-        <v>306</v>
+      <c r="E15" s="4" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4866,22 +4869,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D16" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4897,6 +4900,7 @@
     <hyperlink ref="E16" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
     <hyperlink ref="G16" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
     <hyperlink ref="E13" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E15" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4923,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4931,7 +4935,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6857,7 +6861,7 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>5</v>
@@ -7093,7 +7097,7 @@
         <v>25</v>
       </c>
       <c r="D8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8">
         <v>6</v>
@@ -7155,7 +7159,7 @@
         <v>20</v>
       </c>
       <c r="D9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9">
         <v>3</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="340">
   <si>
     <t>类型</t>
   </si>
@@ -583,9 +583,6 @@
   </si>
   <si>
     <t>工程车怪</t>
-  </si>
-  <si>
-    <t>wajueji_已绑定的模型</t>
   </si>
   <si>
     <t>幼虫怪,</t>
@@ -4309,8 +4306,8 @@
       <c r="E40" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F40" s="11" t="s">
-        <v>182</v>
+      <c r="F40" t="s">
+        <v>36</v>
       </c>
       <c r="G40" s="19" t="b">
         <v>1</v>
@@ -4351,7 +4348,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4407,7 +4404,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4463,7 +4460,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4519,7 +4516,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4596,22 +4593,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>293</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4619,16 +4616,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" t="s">
         <v>295</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>296</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4636,16 +4633,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D3" t="s">
         <v>296</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4653,16 +4650,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" t="s">
         <v>300</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>301</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4670,16 +4667,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
         <v>301</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4687,16 +4684,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" t="s">
         <v>305</v>
-      </c>
-      <c r="C6" t="s">
-        <v>296</v>
-      </c>
-      <c r="D6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4704,16 +4701,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" t="s">
         <v>296</v>
       </c>
-      <c r="D7" t="s">
-        <v>297</v>
-      </c>
       <c r="E7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4721,16 +4718,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" t="s">
         <v>308</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>309</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>310</v>
-      </c>
-      <c r="E8" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4738,16 +4735,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" t="s">
         <v>309</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>310</v>
-      </c>
-      <c r="E9" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4755,16 +4752,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" t="s">
         <v>301</v>
       </c>
-      <c r="D10" t="s">
-        <v>302</v>
-      </c>
       <c r="E10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4772,16 +4769,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
+        <v>300</v>
+      </c>
+      <c r="D11" t="s">
         <v>301</v>
       </c>
-      <c r="D11" t="s">
-        <v>302</v>
-      </c>
       <c r="E11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4789,22 +4786,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" t="s">
         <v>315</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>316</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4812,16 +4809,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" t="s">
         <v>321</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>322</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4829,22 +4826,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
+        <v>324</v>
+      </c>
+      <c r="C14" t="s">
         <v>325</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>326</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="8" t="s">
         <v>329</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4852,16 +4849,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
+        <v>330</v>
+      </c>
+      <c r="C15" t="s">
+        <v>295</v>
+      </c>
+      <c r="D15" t="s">
+        <v>296</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="C15" t="s">
-        <v>296</v>
-      </c>
-      <c r="D15" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4869,22 +4866,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
+        <v>332</v>
+      </c>
+      <c r="C16" t="s">
         <v>333</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>334</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>337</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4915,10 +4912,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4927,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4935,7 +4932,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4960,22 +4957,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>191</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5647,22 +5644,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" t="s">
         <v>194</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>195</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>196</v>
-      </c>
-      <c r="G1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5739,7 +5736,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5985,25 +5982,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6014,7 +6011,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6029,7 +6026,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -6040,10 +6037,10 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" t="s">
         <v>207</v>
-      </c>
-      <c r="D3" t="s">
-        <v>208</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6055,7 +6052,7 @@
         <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6066,7 +6063,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6081,7 +6078,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6092,10 +6089,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6107,7 +6104,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6118,22 +6115,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>214</v>
-      </c>
-      <c r="H6" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6159,7 +6156,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6170,10 +6167,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6182,10 +6179,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" t="s">
         <v>218</v>
-      </c>
-      <c r="H8" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6196,22 +6193,22 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>220</v>
       </c>
-      <c r="D9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>221</v>
-      </c>
-      <c r="H9" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6225,7 +6222,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6248,22 +6245,22 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
+        <v>212</v>
+      </c>
+      <c r="D11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>213</v>
       </c>
-      <c r="D11" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>214</v>
-      </c>
-      <c r="H11" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6288,7 +6285,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6300,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
+        <v>224</v>
+      </c>
+      <c r="H13" t="s">
         <v>225</v>
-      </c>
-      <c r="H13" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6314,7 +6311,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6326,10 +6323,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" t="s">
         <v>228</v>
-      </c>
-      <c r="H14" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6340,22 +6337,22 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>230</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>231</v>
-      </c>
-      <c r="H15" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6366,10 +6363,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" t="s">
         <v>207</v>
-      </c>
-      <c r="D16" t="s">
-        <v>208</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6381,7 +6378,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6392,10 +6389,10 @@
         <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6412,10 +6409,10 @@
         <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6432,10 +6429,10 @@
         <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6452,10 +6449,10 @@
         <v>178</v>
       </c>
       <c r="C20" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" t="s">
         <v>207</v>
-      </c>
-      <c r="D20" t="s">
-        <v>208</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6467,7 +6464,7 @@
         <v>41</v>
       </c>
       <c r="H20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6478,7 +6475,7 @@
         <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6493,7 +6490,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6504,7 +6501,7 @@
         <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6519,7 +6516,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6527,13 +6524,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6553,10 +6550,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6568,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
+        <v>227</v>
+      </c>
+      <c r="H24" t="s">
         <v>228</v>
-      </c>
-      <c r="H24" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6579,25 +6576,25 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
         <v>213</v>
       </c>
-      <c r="D25" t="s">
-        <v>208</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>214</v>
-      </c>
-      <c r="H25" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6605,10 +6602,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6620,10 +6617,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
+        <v>224</v>
+      </c>
+      <c r="H26" t="s">
         <v>225</v>
-      </c>
-      <c r="H26" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -6672,64 +6669,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>250</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6773,7 +6770,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6814,19 +6811,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
+        <v>252</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
         <v>253</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>254</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6835,7 +6832,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6891,7 +6888,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6935,7 +6932,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6947,13 +6944,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -6994,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7009,7 +7006,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7062,7 +7059,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7071,7 +7068,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7112,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7124,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7133,7 +7130,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7174,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7189,7 +7186,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7230,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7245,7 +7242,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7289,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7304,7 +7301,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7357,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7457,7 +7454,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7466,7 +7463,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7522,7 +7519,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7563,19 +7560,19 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
+        <v>252</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
         <v>253</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>254</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7584,7 +7581,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7873,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7882,7 +7879,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8336,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8348,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8357,7 +8354,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8398,7 +8395,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8413,7 +8410,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8454,7 +8451,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8469,7 +8466,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8510,19 +8507,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
+        <v>252</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
         <v>253</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>254</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8531,7 +8528,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8587,7 +8584,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8643,7 +8640,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8663,7 +8660,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8684,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8699,7 +8696,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8719,7 +8716,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8749,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8758,7 +8755,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8778,7 +8775,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8802,7 +8799,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8817,7 +8814,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8837,7 +8834,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8899,10 +8896,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8954,7 +8951,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8965,7 +8962,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -9020,7 +9017,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9031,7 +9028,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9042,7 +9039,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9053,7 +9050,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -9079,25 +9076,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9108,7 +9105,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9134,7 +9131,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9160,7 +9157,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9186,7 +9183,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9212,7 +9209,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9238,7 +9235,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9264,7 +9261,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9290,7 +9287,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9328,13 +9325,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9382,19 +9379,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D1" t="s">
         <v>280</v>
       </c>
-      <c r="B1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>281</v>
-      </c>
-      <c r="E1" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9402,7 +9399,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9419,7 +9416,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9436,7 +9433,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9453,7 +9450,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9470,7 +9467,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9487,7 +9484,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9504,7 +9501,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="339">
   <si>
     <t>类型</t>
   </si>
@@ -574,9 +574,6 @@
   </si>
   <si>
     <t>枪兵怪</t>
-  </si>
-  <si>
-    <t>活动单位/步兵</t>
   </si>
   <si>
     <t>近战兵怪</t>
@@ -1858,7 +1855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1904,6 +1901,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1922,10 +1925,16 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2262,32 +2271,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" spans="1:18">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
+    <row r="1" s="20" customFormat="1" spans="1:18">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2296,42 +2305,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="19" customFormat="1" spans="1:17">
-      <c r="A2" s="19">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+    <row r="2" s="21" customFormat="1" spans="1:17">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="19">
-        <v>0</v>
-      </c>
-      <c r="G2" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="19">
+      <c r="C2" s="21">
+        <v>0</v>
+      </c>
+      <c r="G2" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="21">
         <v>1</v>
       </c>
       <c r="J2">
@@ -2340,33 +2349,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="19">
-        <v>1</v>
-      </c>
-      <c r="N2" s="19">
-        <v>0</v>
-      </c>
-      <c r="O2" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="19" customFormat="1" spans="1:17">
-      <c r="A3" s="19">
+      <c r="M2" s="21">
+        <v>1</v>
+      </c>
+      <c r="N2" s="21">
+        <v>0</v>
+      </c>
+      <c r="O2" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="21" customFormat="1" spans="1:17">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="19">
-        <v>0</v>
-      </c>
-      <c r="G3" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="19">
+      <c r="C3" s="21">
+        <v>0</v>
+      </c>
+      <c r="G3" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="21">
         <v>1</v>
       </c>
       <c r="J3">
@@ -2375,16 +2384,16 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="19">
-        <v>1</v>
-      </c>
-      <c r="N3" s="19">
-        <v>0</v>
-      </c>
-      <c r="O3" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="19">
+      <c r="M3" s="21">
+        <v>1</v>
+      </c>
+      <c r="N3" s="21">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="21">
         <v>0</v>
       </c>
     </row>
@@ -2401,10 +2410,10 @@
       <c r="D4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="19">
+      <c r="G4" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="21">
         <v>1</v>
       </c>
       <c r="J4">
@@ -2413,13 +2422,13 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="19">
-        <v>1</v>
-      </c>
-      <c r="N4" s="19">
-        <v>0</v>
-      </c>
-      <c r="O4" s="19">
+      <c r="M4" s="21">
+        <v>1</v>
+      </c>
+      <c r="N4" s="21">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21">
         <v>0</v>
       </c>
       <c r="Q4" s="13">
@@ -2439,10 +2448,10 @@
       <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="19">
+      <c r="G5" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="21">
         <v>1</v>
       </c>
       <c r="J5">
@@ -2451,13 +2460,13 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="19">
-        <v>1</v>
-      </c>
-      <c r="N5" s="19">
-        <v>0</v>
-      </c>
-      <c r="O5" s="19">
+      <c r="M5" s="21">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21">
+        <v>0</v>
+      </c>
+      <c r="O5" s="21">
         <v>0</v>
       </c>
       <c r="Q5" s="13">
@@ -2467,32 +2476,32 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="20" customFormat="1" spans="1:17">
-      <c r="A6" s="20">
+    <row r="6" s="22" customFormat="1" spans="1:17">
+      <c r="A6" s="22">
         <v>101</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="20">
-        <v>0</v>
-      </c>
-      <c r="D6" s="20" t="s">
+      <c r="C6" s="22">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="19" t="b">
+      <c r="G6" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="21">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2504,39 +2513,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="19">
-        <v>1</v>
-      </c>
-      <c r="N6" s="19">
-        <v>0</v>
-      </c>
-      <c r="O6" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="20" customFormat="1" spans="1:17">
-      <c r="A7" s="20">
+      <c r="M6" s="21">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21">
+        <v>0</v>
+      </c>
+      <c r="O6" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="22" customFormat="1" spans="1:17">
+      <c r="A7" s="22">
         <v>102</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="20">
-        <v>0</v>
-      </c>
-      <c r="D7" s="20" t="s">
+      <c r="C7" s="22">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="19">
+      <c r="G7" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="21">
         <v>1</v>
       </c>
       <c r="J7">
@@ -2545,16 +2554,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="19">
-        <v>1</v>
-      </c>
-      <c r="N7" s="19">
-        <v>0</v>
-      </c>
-      <c r="O7" s="19">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="20">
+      <c r="M7" s="21">
+        <v>1</v>
+      </c>
+      <c r="N7" s="21">
+        <v>0</v>
+      </c>
+      <c r="O7" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2577,13 +2586,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="19" t="b">
+      <c r="G8" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I8" s="21">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2595,13 +2604,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="19">
-        <v>1</v>
-      </c>
-      <c r="N8" s="19">
-        <v>0</v>
-      </c>
-      <c r="O8" s="19">
+      <c r="M8" s="21">
+        <v>1</v>
+      </c>
+      <c r="N8" s="21">
+        <v>0</v>
+      </c>
+      <c r="O8" s="21">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -2614,59 +2623,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
-      <c r="A9">
+    <row r="9" s="15" customFormat="1" spans="1:18">
+      <c r="A9" s="15">
         <v>202</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="C9" s="15">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="G9" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="19">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="I9" s="26">
+        <v>1</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0</v>
+      </c>
+      <c r="K9" s="15">
         <v>2</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="19">
-        <v>1</v>
-      </c>
-      <c r="N9" s="19">
-        <v>0</v>
-      </c>
-      <c r="O9" s="19">
-        <v>0</v>
-      </c>
-      <c r="P9" t="s">
+      <c r="M9" s="26">
+        <v>1</v>
+      </c>
+      <c r="N9" s="26">
+        <v>0</v>
+      </c>
+      <c r="O9" s="26">
+        <v>0</v>
+      </c>
+      <c r="P9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="15">
         <v>3</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R9" s="12" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2689,13 +2698,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="19" t="b">
+      <c r="G10" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="21">
         <v>1</v>
       </c>
       <c r="J10">
@@ -2707,13 +2716,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="19">
-        <v>1</v>
-      </c>
-      <c r="N10" s="19">
-        <v>0</v>
-      </c>
-      <c r="O10" s="19">
+      <c r="M10" s="21">
+        <v>1</v>
+      </c>
+      <c r="N10" s="21">
+        <v>0</v>
+      </c>
+      <c r="O10" s="21">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -2742,13 +2751,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="19" t="b">
+      <c r="G11" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="21">
         <v>1</v>
       </c>
       <c r="J11">
@@ -2760,13 +2769,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="19">
-        <v>1</v>
-      </c>
-      <c r="N11" s="19">
-        <v>0</v>
-      </c>
-      <c r="O11" s="19">
+      <c r="M11" s="21">
+        <v>1</v>
+      </c>
+      <c r="N11" s="21">
+        <v>0</v>
+      </c>
+      <c r="O11" s="21">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -2798,13 +2807,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="19" t="b">
+      <c r="G12" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="21">
         <v>1</v>
       </c>
       <c r="J12">
@@ -2816,13 +2825,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="19">
-        <v>1</v>
-      </c>
-      <c r="N12" s="19">
-        <v>0</v>
-      </c>
-      <c r="O12" s="19">
+      <c r="M12" s="21">
+        <v>1</v>
+      </c>
+      <c r="N12" s="21">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -2854,13 +2863,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="19" t="b">
+      <c r="G13" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="21">
         <v>1</v>
       </c>
       <c r="J13">
@@ -2872,13 +2881,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="19">
-        <v>1</v>
-      </c>
-      <c r="N13" s="19">
-        <v>1</v>
-      </c>
-      <c r="O13" s="19">
+      <c r="M13" s="21">
+        <v>1</v>
+      </c>
+      <c r="N13" s="21">
+        <v>1</v>
+      </c>
+      <c r="O13" s="21">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -2907,16 +2916,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="19" t="b">
+      <c r="G14" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="21">
         <v>1</v>
       </c>
       <c r="J14">
@@ -2928,13 +2937,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="19">
-        <v>1</v>
-      </c>
-      <c r="N14" s="19">
-        <v>0</v>
-      </c>
-      <c r="O14" s="19">
+      <c r="M14" s="21">
+        <v>1</v>
+      </c>
+      <c r="N14" s="21">
+        <v>0</v>
+      </c>
+      <c r="O14" s="21">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -2963,16 +2972,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="19" t="b">
+      <c r="G15" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="21">
         <v>1</v>
       </c>
       <c r="J15">
@@ -2984,13 +2993,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="19">
-        <v>1</v>
-      </c>
-      <c r="N15" s="19">
-        <v>0</v>
-      </c>
-      <c r="O15" s="19">
+      <c r="M15" s="21">
+        <v>1</v>
+      </c>
+      <c r="N15" s="21">
+        <v>0</v>
+      </c>
+      <c r="O15" s="21">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -3022,13 +3031,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="19" t="b">
+      <c r="G16" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="21">
         <v>1</v>
       </c>
       <c r="J16">
@@ -3040,13 +3049,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="19">
-        <v>1</v>
-      </c>
-      <c r="N16" s="19">
-        <v>0</v>
-      </c>
-      <c r="O16" s="19">
+      <c r="M16" s="21">
+        <v>1</v>
+      </c>
+      <c r="N16" s="21">
+        <v>0</v>
+      </c>
+      <c r="O16" s="21">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -3078,13 +3087,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="19" t="b">
+      <c r="G17" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="19">
+      <c r="I17" s="21">
         <v>1</v>
       </c>
       <c r="J17">
@@ -3096,13 +3105,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="19">
-        <v>1</v>
-      </c>
-      <c r="N17" s="19">
-        <v>0</v>
-      </c>
-      <c r="O17" s="19">
+      <c r="M17" s="21">
+        <v>1</v>
+      </c>
+      <c r="N17" s="21">
+        <v>0</v>
+      </c>
+      <c r="O17" s="21">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -3128,10 +3137,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="19">
+      <c r="G18" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="21">
         <v>1</v>
       </c>
       <c r="J18">
@@ -3140,13 +3149,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="19">
-        <v>1</v>
-      </c>
-      <c r="N18" s="19">
-        <v>0</v>
-      </c>
-      <c r="O18" s="19">
+      <c r="M18" s="21">
+        <v>1</v>
+      </c>
+      <c r="N18" s="21">
+        <v>0</v>
+      </c>
+      <c r="O18" s="21">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -3172,13 +3181,13 @@
       <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="19" t="b">
+      <c r="G19" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="19">
+      <c r="I19" s="21">
         <v>1</v>
       </c>
       <c r="J19">
@@ -3190,13 +3199,13 @@
       <c r="L19" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="19">
-        <v>1</v>
-      </c>
-      <c r="N19" s="19">
-        <v>0</v>
-      </c>
-      <c r="O19" s="19">
+      <c r="M19" s="21">
+        <v>1</v>
+      </c>
+      <c r="N19" s="21">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -3228,13 +3237,13 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="19" t="b">
+      <c r="G20" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="21">
         <v>1</v>
       </c>
       <c r="J20">
@@ -3246,13 +3255,13 @@
       <c r="L20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="19">
-        <v>1</v>
-      </c>
-      <c r="N20" s="19">
-        <v>0</v>
-      </c>
-      <c r="O20" s="19">
+      <c r="M20" s="21">
+        <v>1</v>
+      </c>
+      <c r="N20" s="21">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -3284,13 +3293,13 @@
       <c r="F21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" s="19" t="b">
+      <c r="G21" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="21">
         <v>1</v>
       </c>
       <c r="J21">
@@ -3302,13 +3311,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="19">
-        <v>1</v>
-      </c>
-      <c r="N21" s="19">
-        <v>0</v>
-      </c>
-      <c r="O21" s="19">
+      <c r="M21" s="21">
+        <v>1</v>
+      </c>
+      <c r="N21" s="21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="21">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -3340,13 +3349,13 @@
       <c r="F22" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="19" t="b">
+      <c r="G22" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="21">
         <v>1</v>
       </c>
       <c r="J22">
@@ -3358,13 +3367,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="19">
-        <v>1</v>
-      </c>
-      <c r="N22" s="19">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19">
+      <c r="M22" s="21">
+        <v>1</v>
+      </c>
+      <c r="N22" s="21">
+        <v>0</v>
+      </c>
+      <c r="O22" s="21">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -3396,13 +3405,13 @@
       <c r="F23" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="19" t="b">
+      <c r="G23" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="19">
+      <c r="I23" s="21">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3414,13 +3423,13 @@
       <c r="L23" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="19">
-        <v>1</v>
-      </c>
-      <c r="N23" s="19">
-        <v>0</v>
-      </c>
-      <c r="O23" s="19">
+      <c r="M23" s="21">
+        <v>1</v>
+      </c>
+      <c r="N23" s="21">
+        <v>0</v>
+      </c>
+      <c r="O23" s="21">
         <v>0</v>
       </c>
       <c r="P23" s="13" t="s">
@@ -3452,13 +3461,13 @@
       <c r="F24" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="19" t="b">
+      <c r="G24" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="21">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -3470,13 +3479,13 @@
       <c r="L24" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="19">
-        <v>1</v>
-      </c>
-      <c r="N24" s="19">
-        <v>0</v>
-      </c>
-      <c r="O24" s="19">
+      <c r="M24" s="21">
+        <v>1</v>
+      </c>
+      <c r="N24" s="21">
+        <v>0</v>
+      </c>
+      <c r="O24" s="21">
         <v>0</v>
       </c>
       <c r="P24" s="13" t="s">
@@ -3505,13 +3514,13 @@
       <c r="E25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="19" t="b">
+      <c r="G25" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="19">
+      <c r="I25" s="21">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3520,13 +3529,13 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="19">
-        <v>1</v>
-      </c>
-      <c r="N25" s="19">
-        <v>0</v>
-      </c>
-      <c r="O25" s="19">
+      <c r="M25" s="21">
+        <v>1</v>
+      </c>
+      <c r="N25" s="21">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21">
         <v>0</v>
       </c>
       <c r="P25" s="13" t="s">
@@ -3558,13 +3567,13 @@
       <c r="F26" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="19" t="b">
+      <c r="G26" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="19">
+      <c r="I26" s="21">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -3576,13 +3585,13 @@
       <c r="L26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="19">
-        <v>1</v>
-      </c>
-      <c r="N26" s="19">
-        <v>0</v>
-      </c>
-      <c r="O26" s="19">
+      <c r="M26" s="21">
+        <v>1</v>
+      </c>
+      <c r="N26" s="21">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21">
         <v>0</v>
       </c>
       <c r="P26" s="13" t="s">
@@ -3614,13 +3623,13 @@
       <c r="F27" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="19" t="b">
+      <c r="G27" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="19">
+      <c r="I27" s="21">
         <v>1</v>
       </c>
       <c r="J27">
@@ -3632,13 +3641,13 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="19">
-        <v>1</v>
-      </c>
-      <c r="N27" s="19">
-        <v>0</v>
-      </c>
-      <c r="O27" s="19">
+      <c r="M27" s="21">
+        <v>1</v>
+      </c>
+      <c r="N27" s="21">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21">
         <v>0</v>
       </c>
       <c r="P27" s="13" t="s">
@@ -3670,13 +3679,13 @@
       <c r="F28" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G28" s="19" t="b">
+      <c r="G28" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="13">
         <v>0</v>
       </c>
-      <c r="I28" s="19">
+      <c r="I28" s="21">
         <v>1</v>
       </c>
       <c r="J28">
@@ -3688,13 +3697,13 @@
       <c r="L28" s="13">
         <v>1</v>
       </c>
-      <c r="M28" s="19">
-        <v>1</v>
-      </c>
-      <c r="N28" s="19">
-        <v>0</v>
-      </c>
-      <c r="O28" s="19">
+      <c r="M28" s="21">
+        <v>1</v>
+      </c>
+      <c r="N28" s="21">
+        <v>0</v>
+      </c>
+      <c r="O28" s="21">
         <v>0</v>
       </c>
       <c r="P28" s="13" t="s">
@@ -3726,13 +3735,13 @@
       <c r="F29" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="19" t="b">
+      <c r="G29" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="19">
+      <c r="I29" s="21">
         <v>1</v>
       </c>
       <c r="J29">
@@ -3744,13 +3753,13 @@
       <c r="L29" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="21">
         <v>0.1</v>
       </c>
-      <c r="N29" s="19">
-        <v>0</v>
-      </c>
-      <c r="O29" s="19">
+      <c r="N29" s="21">
+        <v>0</v>
+      </c>
+      <c r="O29" s="21">
         <v>0.17</v>
       </c>
       <c r="P29" s="13" t="s">
@@ -3782,13 +3791,13 @@
       <c r="F30" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="19" t="b">
+      <c r="G30" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="21">
         <v>1</v>
       </c>
       <c r="J30">
@@ -3800,13 +3809,13 @@
       <c r="L30" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="M30" s="19">
-        <v>1</v>
-      </c>
-      <c r="N30" s="19">
-        <v>0</v>
-      </c>
-      <c r="O30" s="19">
+      <c r="M30" s="21">
+        <v>1</v>
+      </c>
+      <c r="N30" s="21">
+        <v>0</v>
+      </c>
+      <c r="O30" s="21">
         <v>0</v>
       </c>
       <c r="P30" s="13" t="s">
@@ -3838,13 +3847,13 @@
       <c r="F31" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="G31" s="19" t="b">
+      <c r="G31" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="19">
+      <c r="I31" s="21">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3856,13 +3865,13 @@
       <c r="L31" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M31" s="19">
-        <v>1</v>
-      </c>
-      <c r="N31" s="19">
-        <v>0</v>
-      </c>
-      <c r="O31" s="19">
+      <c r="M31" s="21">
+        <v>1</v>
+      </c>
+      <c r="N31" s="21">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21">
         <v>0</v>
       </c>
       <c r="P31" s="13" t="s">
@@ -3894,13 +3903,13 @@
       <c r="F32" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="G32" s="19" t="b">
+      <c r="G32" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="19">
+      <c r="I32" s="21">
         <v>1</v>
       </c>
       <c r="J32">
@@ -3912,13 +3921,13 @@
       <c r="L32" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="19">
-        <v>1</v>
-      </c>
-      <c r="N32" s="19">
-        <v>0</v>
-      </c>
-      <c r="O32" s="19">
+      <c r="M32" s="21">
+        <v>1</v>
+      </c>
+      <c r="N32" s="21">
+        <v>0</v>
+      </c>
+      <c r="O32" s="21">
         <v>0</v>
       </c>
       <c r="P32" s="13" t="s">
@@ -3950,13 +3959,13 @@
       <c r="F33" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="G33" s="19" t="b">
+      <c r="G33" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="13">
         <v>0</v>
       </c>
-      <c r="I33" s="19">
+      <c r="I33" s="21">
         <v>1</v>
       </c>
       <c r="J33">
@@ -3968,13 +3977,13 @@
       <c r="L33" s="13">
         <v>1</v>
       </c>
-      <c r="M33" s="19">
-        <v>1</v>
-      </c>
-      <c r="N33" s="19">
-        <v>0</v>
-      </c>
-      <c r="O33" s="19">
+      <c r="M33" s="21">
+        <v>1</v>
+      </c>
+      <c r="N33" s="21">
+        <v>0</v>
+      </c>
+      <c r="O33" s="21">
         <v>0</v>
       </c>
       <c r="P33" s="13" t="s">
@@ -4000,10 +4009,10 @@
       <c r="D34" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="G34" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="19">
+      <c r="G34" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="21">
         <v>1</v>
       </c>
       <c r="J34">
@@ -4012,13 +4021,13 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="19">
-        <v>1</v>
-      </c>
-      <c r="N34" s="19">
-        <v>0</v>
-      </c>
-      <c r="O34" s="19">
+      <c r="M34" s="21">
+        <v>1</v>
+      </c>
+      <c r="N34" s="21">
+        <v>0</v>
+      </c>
+      <c r="O34" s="21">
         <v>0</v>
       </c>
       <c r="Q34" s="13">
@@ -4032,7 +4041,7 @@
       <c r="A35" s="11">
         <v>401</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="28" t="s">
         <v>174</v>
       </c>
       <c r="C35" s="11">
@@ -4041,16 +4050,16 @@
       <c r="D35" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="19" t="b">
+      <c r="G35" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="19">
+      <c r="I35" s="21">
         <v>1</v>
       </c>
       <c r="J35">
@@ -4062,13 +4071,13 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="19">
-        <v>1</v>
-      </c>
-      <c r="N35" s="19">
-        <v>0</v>
-      </c>
-      <c r="O35" s="19">
+      <c r="M35" s="21">
+        <v>1</v>
+      </c>
+      <c r="N35" s="21">
+        <v>0</v>
+      </c>
+      <c r="O35" s="21">
         <v>0</v>
       </c>
       <c r="P35" s="11" t="s">
@@ -4082,7 +4091,7 @@
       <c r="A36" s="11">
         <v>402</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="28" t="s">
         <v>175</v>
       </c>
       <c r="C36" s="11">
@@ -4091,16 +4100,16 @@
       <c r="D36" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="F36" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="19" t="b">
+      <c r="G36" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="19">
+      <c r="I36" s="21">
         <v>1</v>
       </c>
       <c r="J36">
@@ -4112,13 +4121,13 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="19">
-        <v>1</v>
-      </c>
-      <c r="N36" s="19">
-        <v>0</v>
-      </c>
-      <c r="O36" s="19">
+      <c r="M36" s="21">
+        <v>1</v>
+      </c>
+      <c r="N36" s="21">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21">
         <v>0</v>
       </c>
       <c r="P36" s="11" t="s">
@@ -4132,7 +4141,7 @@
       <c r="A37" s="11">
         <v>403</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="28" t="s">
         <v>176</v>
       </c>
       <c r="C37" s="11">
@@ -4147,13 +4156,13 @@
       <c r="F37" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="19" t="b">
+      <c r="G37" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="19">
+      <c r="I37" s="21">
         <v>1</v>
       </c>
       <c r="J37">
@@ -4165,13 +4174,13 @@
       <c r="L37" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="19">
-        <v>1</v>
-      </c>
-      <c r="N37" s="19">
-        <v>0</v>
-      </c>
-      <c r="O37" s="19">
+      <c r="M37" s="21">
+        <v>1</v>
+      </c>
+      <c r="N37" s="21">
+        <v>0</v>
+      </c>
+      <c r="O37" s="21">
         <v>0</v>
       </c>
       <c r="P37" s="11" t="s">
@@ -4181,53 +4190,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="11" customFormat="1" spans="1:17">
-      <c r="A38" s="11">
+    <row r="38" s="23" customFormat="1" spans="1:17">
+      <c r="A38" s="23">
         <v>404</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C38" s="11">
-        <v>1</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E38" s="11" t="s">
+      <c r="C38" s="23">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="G38" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="11" t="s">
+      <c r="F38" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="19">
-        <v>1</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>0</v>
-      </c>
-      <c r="L38" s="11" t="s">
+      <c r="I38" s="26">
+        <v>1</v>
+      </c>
+      <c r="J38" s="15">
+        <v>0</v>
+      </c>
+      <c r="K38" s="15">
+        <v>2</v>
+      </c>
+      <c r="L38" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="19">
-        <v>1</v>
-      </c>
-      <c r="N38" s="19">
-        <v>0</v>
-      </c>
-      <c r="O38" s="19">
-        <v>0</v>
-      </c>
-      <c r="P38" s="11" t="s">
+      <c r="M38" s="26">
+        <v>1</v>
+      </c>
+      <c r="N38" s="26">
+        <v>0</v>
+      </c>
+      <c r="O38" s="26">
+        <v>0</v>
+      </c>
+      <c r="P38" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="11">
+      <c r="Q38" s="23">
         <v>3</v>
       </c>
     </row>
@@ -4235,8 +4247,8 @@
       <c r="A39" s="11">
         <v>405</v>
       </c>
-      <c r="B39" s="24" t="s">
-        <v>180</v>
+      <c r="B39" s="28" t="s">
+        <v>179</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4250,13 +4262,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="19" t="b">
+      <c r="G39" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="19">
+      <c r="I39" s="21">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4268,13 +4280,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="19">
-        <v>1</v>
-      </c>
-      <c r="N39" s="19">
-        <v>0</v>
-      </c>
-      <c r="O39" s="19">
+      <c r="M39" s="21">
+        <v>1</v>
+      </c>
+      <c r="N39" s="21">
+        <v>0</v>
+      </c>
+      <c r="O39" s="21">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -4294,8 +4306,8 @@
       <c r="A40" s="11">
         <v>406</v>
       </c>
-      <c r="B40" s="24" t="s">
-        <v>181</v>
+      <c r="B40" s="28" t="s">
+        <v>180</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
@@ -4309,13 +4321,13 @@
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="19" t="b">
+      <c r="G40" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H40" s="11">
         <v>0</v>
       </c>
-      <c r="I40" s="19">
+      <c r="I40" s="21">
         <v>1</v>
       </c>
       <c r="J40">
@@ -4327,13 +4339,13 @@
       <c r="L40" s="11">
         <v>3</v>
       </c>
-      <c r="M40" s="19">
-        <v>1</v>
-      </c>
-      <c r="N40" s="19">
-        <v>0</v>
-      </c>
-      <c r="O40" s="19">
+      <c r="M40" s="21">
+        <v>1</v>
+      </c>
+      <c r="N40" s="21">
+        <v>0</v>
+      </c>
+      <c r="O40" s="21">
         <v>0</v>
       </c>
       <c r="P40" s="11" t="s">
@@ -4348,7 +4360,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4362,13 +4374,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="19" t="b">
+      <c r="G41" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="19">
+      <c r="I41" s="21">
         <v>1</v>
       </c>
       <c r="J41">
@@ -4380,13 +4392,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="19">
-        <v>1</v>
-      </c>
-      <c r="N41" s="19">
-        <v>0</v>
-      </c>
-      <c r="O41" s="19">
+      <c r="M41" s="21">
+        <v>1</v>
+      </c>
+      <c r="N41" s="21">
+        <v>0</v>
+      </c>
+      <c r="O41" s="21">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -4404,7 +4416,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4418,13 +4430,13 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="19" t="b">
+      <c r="G42" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="19">
+      <c r="I42" s="21">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4436,13 +4448,13 @@
       <c r="L42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="19">
-        <v>1</v>
-      </c>
-      <c r="N42" s="19">
-        <v>0</v>
-      </c>
-      <c r="O42" s="19">
+      <c r="M42" s="21">
+        <v>1</v>
+      </c>
+      <c r="N42" s="21">
+        <v>0</v>
+      </c>
+      <c r="O42" s="21">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -4460,7 +4472,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4474,13 +4486,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="19" t="b">
+      <c r="G43" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="19">
+      <c r="I43" s="21">
         <v>1</v>
       </c>
       <c r="J43">
@@ -4492,13 +4504,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="19">
-        <v>1</v>
-      </c>
-      <c r="N43" s="19">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19">
+      <c r="M43" s="21">
+        <v>1</v>
+      </c>
+      <c r="N43" s="21">
+        <v>0</v>
+      </c>
+      <c r="O43" s="21">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -4516,7 +4528,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4530,13 +4542,13 @@
       <c r="F44" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="19" t="b">
+      <c r="G44" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="19">
+      <c r="I44" s="21">
         <v>1</v>
       </c>
       <c r="J44">
@@ -4548,13 +4560,13 @@
       <c r="L44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" s="19">
-        <v>1</v>
-      </c>
-      <c r="N44" s="19">
-        <v>0</v>
-      </c>
-      <c r="O44" s="19">
+      <c r="M44" s="21">
+        <v>1</v>
+      </c>
+      <c r="N44" s="21">
+        <v>0</v>
+      </c>
+      <c r="O44" s="21">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -4593,22 +4605,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4616,16 +4628,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" t="s">
         <v>294</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>295</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4633,16 +4645,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" t="s">
         <v>295</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="4" t="s">
         <v>296</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4650,16 +4662,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" t="s">
         <v>299</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>300</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4667,16 +4679,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D5" t="s">
         <v>300</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4684,16 +4696,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" t="s">
+        <v>294</v>
+      </c>
+      <c r="D6" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" t="s">
         <v>304</v>
-      </c>
-      <c r="C6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E6" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4701,16 +4713,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
+        <v>294</v>
+      </c>
+      <c r="D7" t="s">
         <v>295</v>
       </c>
-      <c r="D7" t="s">
-        <v>296</v>
-      </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4718,16 +4730,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C8" t="s">
         <v>307</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>308</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>309</v>
-      </c>
-      <c r="E8" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4735,16 +4747,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C9" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" t="s">
         <v>308</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>309</v>
-      </c>
-      <c r="E9" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4752,16 +4764,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D10" t="s">
         <v>300</v>
       </c>
-      <c r="D10" t="s">
-        <v>301</v>
-      </c>
       <c r="E10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4769,16 +4781,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C11" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" t="s">
         <v>300</v>
       </c>
-      <c r="D11" t="s">
-        <v>301</v>
-      </c>
       <c r="E11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4786,22 +4798,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12" t="s">
         <v>314</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>315</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4809,16 +4821,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
+        <v>319</v>
+      </c>
+      <c r="C13" t="s">
         <v>320</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>321</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4826,22 +4838,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" t="s">
         <v>324</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>325</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4849,16 +4861,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
+        <v>329</v>
+      </c>
+      <c r="C15" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" t="s">
+        <v>295</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="C15" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4866,22 +4878,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
+        <v>331</v>
+      </c>
+      <c r="C16" t="s">
         <v>332</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>333</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="4" t="s">
         <v>336</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4912,10 +4924,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4924,7 +4936,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4932,7 +4944,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4957,22 +4969,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5343,284 +5355,284 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="15" customFormat="1" spans="1:7">
-      <c r="A18" s="15">
+    <row r="18" s="17" customFormat="1" spans="1:7">
+      <c r="A18" s="17">
         <v>301</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="17">
         <v>50</v>
       </c>
-      <c r="D18" s="15">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
         <v>400</v>
       </c>
-      <c r="F18" s="15">
-        <v>0</v>
-      </c>
-      <c r="G18" s="17">
+      <c r="F18" s="17">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="15" customFormat="1" spans="1:7">
-      <c r="A19" s="15">
+    <row r="19" s="17" customFormat="1" spans="1:7">
+      <c r="A19" s="17">
         <v>302</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="17">
         <v>25</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="17">
         <v>9</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="17">
         <v>100</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="17">
         <v>303</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="15" customFormat="1" spans="1:7">
-      <c r="A20" s="15">
+    <row r="20" s="17" customFormat="1" spans="1:7">
+      <c r="A20" s="17">
         <v>303</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="17">
         <v>20</v>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="17">
         <v>3</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="17">
         <v>50</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="17">
         <v>301</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="19">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="15" customFormat="1" spans="1:7">
-      <c r="A21" s="15">
+    <row r="21" s="17" customFormat="1" spans="1:7">
+      <c r="A21" s="17">
         <v>304</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="17">
         <v>30</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="17">
         <v>11</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="17">
         <v>300</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="17">
         <v>301</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="15" customFormat="1" spans="1:7">
-      <c r="A22" s="15">
+    <row r="22" s="17" customFormat="1" spans="1:7">
+      <c r="A22" s="17">
         <v>305</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="15">
+      <c r="C22" s="17">
         <v>25</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="17">
         <v>8</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="17">
         <v>100</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="17">
         <v>303</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="15" customFormat="1" spans="1:7">
-      <c r="A23" s="15">
+    <row r="23" s="17" customFormat="1" spans="1:7">
+      <c r="A23" s="17">
         <v>306</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="17">
         <v>35</v>
       </c>
-      <c r="D23" s="15">
-        <v>0</v>
-      </c>
-      <c r="E23" s="15">
+      <c r="D23" s="17">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17">
         <v>200</v>
       </c>
-      <c r="F23" s="15">
-        <v>0</v>
-      </c>
-      <c r="G23" s="17">
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="15" customFormat="1" spans="1:7">
-      <c r="A24" s="15">
+    <row r="24" s="17" customFormat="1" spans="1:7">
+      <c r="A24" s="17">
         <v>307</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="17">
         <v>35</v>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="17">
         <v>12</v>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="17">
         <v>150</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="17">
         <v>302</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="15" customFormat="1" spans="1:7">
-      <c r="A25" s="15">
+    <row r="25" s="17" customFormat="1" spans="1:7">
+      <c r="A25" s="17">
         <v>308</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="17">
         <v>35</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="17">
         <v>12</v>
       </c>
-      <c r="E25" s="15">
+      <c r="E25" s="17">
         <v>150</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="17">
         <v>302</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="15" customFormat="1" spans="1:7">
-      <c r="A26" s="15">
+    <row r="26" s="17" customFormat="1" spans="1:7">
+      <c r="A26" s="17">
         <v>309</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="17">
         <v>20</v>
       </c>
-      <c r="D26" s="15">
+      <c r="D26" s="17">
         <v>10</v>
       </c>
-      <c r="E26" s="15">
+      <c r="E26" s="17">
         <v>80</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="17">
         <v>306</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="19">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="15" customFormat="1" spans="1:7">
-      <c r="A27" s="15">
+    <row r="27" s="17" customFormat="1" spans="1:7">
+      <c r="A27" s="17">
         <v>310</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="17">
         <v>30</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="17">
         <v>10</v>
       </c>
-      <c r="E27" s="15">
+      <c r="E27" s="17">
         <v>120</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="17">
         <v>309</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="15" customFormat="1" spans="1:7">
-      <c r="A28" s="15">
+    <row r="28" s="17" customFormat="1" spans="1:7">
+      <c r="A28" s="17">
         <v>311</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="17">
         <v>30</v>
       </c>
-      <c r="D28" s="15">
+      <c r="D28" s="17">
         <v>10</v>
       </c>
-      <c r="E28" s="15">
+      <c r="E28" s="17">
         <v>120</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="17">
         <v>309</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="15" customFormat="1" spans="1:7">
-      <c r="A29" s="15">
+    <row r="29" s="17" customFormat="1" spans="1:7">
+      <c r="A29" s="17">
         <v>312</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="15">
+      <c r="C29" s="17">
         <v>15</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="17">
         <v>2</v>
       </c>
-      <c r="E29" s="15">
+      <c r="E29" s="17">
         <v>15</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="17">
         <v>306</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="19">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="15" customFormat="1" spans="2:2">
-      <c r="B30" s="16"/>
+    <row r="30" s="17" customFormat="1" spans="2:2">
+      <c r="B30" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5644,22 +5656,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" t="s">
         <v>193</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>194</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>195</v>
-      </c>
-      <c r="G1" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5736,7 +5748,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5977,30 +5989,30 @@
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+    <row r="1" s="9" customFormat="1" spans="1:8">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="9" t="s">
         <v>202</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6011,7 +6023,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6026,33 +6038,33 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" s="15" customFormat="1" spans="1:8">
+      <c r="A3" s="15">
+        <v>202</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3">
-        <v>202</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="D3" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="15">
+        <v>0</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H3" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0.8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6063,7 +6075,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6078,7 +6090,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6089,10 +6101,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6104,7 +6116,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6115,22 +6127,22 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
         <v>212</v>
       </c>
-      <c r="D6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>213</v>
-      </c>
-      <c r="H6" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6156,7 +6168,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6167,10 +6179,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6179,10 +6191,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
+        <v>216</v>
+      </c>
+      <c r="H8" t="s">
         <v>217</v>
-      </c>
-      <c r="H8" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6193,22 +6205,22 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
         <v>219</v>
       </c>
-      <c r="D9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>220</v>
-      </c>
-      <c r="H9" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6222,7 +6234,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6245,22 +6257,22 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D11" t="s">
+        <v>206</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
         <v>212</v>
       </c>
-      <c r="D11" t="s">
-        <v>207</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>213</v>
-      </c>
-      <c r="H11" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6285,7 +6297,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6297,10 +6309,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
+        <v>223</v>
+      </c>
+      <c r="H13" t="s">
         <v>224</v>
-      </c>
-      <c r="H13" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6311,7 +6323,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6323,10 +6335,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" t="s">
         <v>227</v>
-      </c>
-      <c r="H14" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6337,22 +6349,22 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15" t="s">
         <v>229</v>
       </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>230</v>
-      </c>
-      <c r="H15" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6363,10 +6375,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" t="s">
         <v>206</v>
-      </c>
-      <c r="D16" t="s">
-        <v>207</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6378,7 +6390,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6389,10 +6401,10 @@
         <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6409,10 +6421,10 @@
         <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6429,42 +6441,42 @@
         <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D19" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="15" customFormat="1" spans="1:8">
+      <c r="A20" s="16">
+        <v>404</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="12" t="s">
         <v>207</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="10">
-        <v>404</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" t="s">
-        <v>207</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6472,10 +6484,10 @@
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6490,7 +6502,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6498,10 +6510,10 @@
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6516,7 +6528,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6524,13 +6536,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6550,10 +6562,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6565,10 +6577,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
+        <v>226</v>
+      </c>
+      <c r="H24" t="s">
         <v>227</v>
-      </c>
-      <c r="H24" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6576,25 +6588,25 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D25" t="s">
+        <v>206</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
         <v>212</v>
       </c>
-      <c r="D25" t="s">
-        <v>207</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>213</v>
-      </c>
-      <c r="H25" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6602,10 +6614,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6617,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
+        <v>223</v>
+      </c>
+      <c r="H26" t="s">
         <v>224</v>
-      </c>
-      <c r="H26" t="s">
-        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6669,64 +6681,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="F1" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="12" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>241</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="T1" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="U1" s="12" t="s">
         <v>249</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6770,7 +6782,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6811,19 +6823,19 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
+        <v>251</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
         <v>252</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>253</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6832,7 +6844,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6888,7 +6900,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6932,7 +6944,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6944,13 +6956,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -6991,7 +7003,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7006,7 +7018,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7059,7 +7071,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7068,7 +7080,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7109,7 +7121,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7121,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7130,7 +7142,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7171,7 +7183,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7186,7 +7198,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7227,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7242,7 +7254,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7286,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7301,7 +7313,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7354,7 +7366,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7454,7 +7466,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7463,7 +7475,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7519,7 +7531,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7560,19 +7572,19 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
+        <v>251</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
         <v>252</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16" t="s">
-        <v>253</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7581,7 +7593,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7870,7 +7882,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7879,7 +7891,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8333,7 +8345,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8345,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8354,7 +8366,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8395,7 +8407,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8410,7 +8422,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8451,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8466,7 +8478,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8507,19 +8519,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
+        <v>251</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
         <v>252</v>
-      </c>
-      <c r="K32">
-        <v>1</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32" t="s">
-        <v>253</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8528,7 +8540,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8548,7 +8560,7 @@
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -8584,7 +8596,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8604,7 +8616,7 @@
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8640,7 +8652,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8660,7 +8672,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8681,7 +8693,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8696,7 +8708,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8716,7 +8728,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8746,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8755,7 +8767,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8775,7 +8787,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8799,7 +8811,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8814,7 +8826,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8834,7 +8846,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8896,10 +8908,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8951,7 +8963,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8962,7 +8974,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -8995,7 +9007,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -9006,7 +9018,7 @@
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -9017,7 +9029,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9028,7 +9040,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9039,7 +9051,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9050,7 +9062,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -9076,25 +9088,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9105,7 +9117,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9131,7 +9143,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9157,7 +9169,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9183,7 +9195,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9209,7 +9221,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9235,7 +9247,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9261,7 +9273,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9287,7 +9299,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9325,13 +9337,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="9" t="s">
         <v>187</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9379,19 +9391,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1" t="s">
         <v>279</v>
       </c>
-      <c r="B1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>280</v>
-      </c>
-      <c r="E1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9399,7 +9411,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9416,7 +9428,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9433,7 +9445,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9450,7 +9462,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9467,7 +9479,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9484,7 +9496,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9501,7 +9513,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="340">
   <si>
     <t>类型</t>
   </si>
@@ -423,82 +423,85 @@
     <t>建筑/兵营</t>
   </si>
   <si>
-    <t>Factory_leaye</t>
+    <t>Factory_1mesh_model</t>
   </si>
   <si>
     <t>兵营空闲</t>
   </si>
   <si>
+    <t>兵营损毁</t>
+  </si>
+  <si>
+    <t>EXPLOMED</t>
+  </si>
+  <si>
+    <t>可产出枪兵和近战兵</t>
+  </si>
+  <si>
+    <t>民房</t>
+  </si>
+  <si>
+    <t>建筑/民房</t>
+  </si>
+  <si>
+    <t>地堡</t>
+  </si>
+  <si>
+    <t>建筑/地堡</t>
+  </si>
+  <si>
+    <t>地堡872面</t>
+  </si>
+  <si>
+    <t>高HP，可派遣步兵进入地堡</t>
+  </si>
+  <si>
+    <t>炮台</t>
+  </si>
+  <si>
+    <t>建筑/炮台</t>
+  </si>
+  <si>
+    <t>p_jiqiangbao_d_01</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>音效/explo1</t>
+  </si>
+  <si>
+    <t>克制除了坦克以外的一切单位</t>
+  </si>
+  <si>
+    <t>虫巢</t>
+  </si>
+  <si>
+    <t>建筑/虫巢</t>
+  </si>
+  <si>
+    <t>音效/zhaWht00</t>
+  </si>
+  <si>
+    <t>hatchery_skin</t>
+  </si>
+  <si>
+    <t>音效/ZBldgDth</t>
+  </si>
+  <si>
+    <t>可产出幼虫</t>
+  </si>
+  <si>
+    <t>机场</t>
+  </si>
+  <si>
+    <t>建筑/机场</t>
+  </si>
+  <si>
+    <t>airport_500_1mesh</t>
+  </si>
+  <si>
     <t>Take 001</t>
-  </si>
-  <si>
-    <t>EXPLOMED</t>
-  </si>
-  <si>
-    <t>可产出枪兵和近战兵</t>
-  </si>
-  <si>
-    <t>民房</t>
-  </si>
-  <si>
-    <t>建筑/民房</t>
-  </si>
-  <si>
-    <t>地堡</t>
-  </si>
-  <si>
-    <t>建筑/地堡</t>
-  </si>
-  <si>
-    <t>地堡872面</t>
-  </si>
-  <si>
-    <t>高HP，可派遣步兵进入地堡</t>
-  </si>
-  <si>
-    <t>炮台</t>
-  </si>
-  <si>
-    <t>建筑/炮台</t>
-  </si>
-  <si>
-    <t>p_jiqiangbao_d_01</t>
-  </si>
-  <si>
-    <t>show</t>
-  </si>
-  <si>
-    <t>音效/explo1</t>
-  </si>
-  <si>
-    <t>克制除了坦克以外的一切单位</t>
-  </si>
-  <si>
-    <t>虫巢</t>
-  </si>
-  <si>
-    <t>建筑/虫巢</t>
-  </si>
-  <si>
-    <t>音效/zhaWht00</t>
-  </si>
-  <si>
-    <t>hatchery_skin</t>
-  </si>
-  <si>
-    <t>音效/ZBldgDth</t>
-  </si>
-  <si>
-    <t>可产出幼虫</t>
-  </si>
-  <si>
-    <t>机场</t>
-  </si>
-  <si>
-    <t>建筑/机场</t>
-  </si>
-  <si>
-    <t>airport_500_1mesh</t>
   </si>
   <si>
     <t>可产出飞机</t>
@@ -1855,7 +1858,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1901,9 +1904,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1932,9 +1932,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2271,32 +2268,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="20" customFormat="1" spans="1:18">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="20" t="s">
+    <row r="1" s="19" customFormat="1" spans="1:18">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="19" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2305,42 +2302,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="21" customFormat="1" spans="1:17">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
+    <row r="2" s="20" customFormat="1" spans="1:17">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="21">
+      <c r="C2" s="20">
+        <v>0</v>
+      </c>
+      <c r="G2" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="20">
         <v>1</v>
       </c>
       <c r="J2">
@@ -2349,33 +2346,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="21">
-        <v>1</v>
-      </c>
-      <c r="N2" s="21">
-        <v>0</v>
-      </c>
-      <c r="O2" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="21" customFormat="1" spans="1:17">
-      <c r="A3" s="21">
+      <c r="M2" s="20">
+        <v>1</v>
+      </c>
+      <c r="N2" s="20">
+        <v>0</v>
+      </c>
+      <c r="O2" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="20" customFormat="1" spans="1:17">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="21">
-        <v>0</v>
-      </c>
-      <c r="G3" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="21">
+      <c r="C3" s="20">
+        <v>0</v>
+      </c>
+      <c r="G3" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="20">
         <v>1</v>
       </c>
       <c r="J3">
@@ -2384,16 +2381,16 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="21">
-        <v>1</v>
-      </c>
-      <c r="N3" s="21">
-        <v>0</v>
-      </c>
-      <c r="O3" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="21">
+      <c r="M3" s="20">
+        <v>1</v>
+      </c>
+      <c r="N3" s="20">
+        <v>0</v>
+      </c>
+      <c r="O3" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="20">
         <v>0</v>
       </c>
     </row>
@@ -2410,10 +2407,10 @@
       <c r="D4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="21">
+      <c r="G4" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="20">
         <v>1</v>
       </c>
       <c r="J4">
@@ -2422,13 +2419,13 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="21">
-        <v>1</v>
-      </c>
-      <c r="N4" s="21">
-        <v>0</v>
-      </c>
-      <c r="O4" s="21">
+      <c r="M4" s="20">
+        <v>1</v>
+      </c>
+      <c r="N4" s="20">
+        <v>0</v>
+      </c>
+      <c r="O4" s="20">
         <v>0</v>
       </c>
       <c r="Q4" s="13">
@@ -2448,10 +2445,10 @@
       <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="21">
+      <c r="G5" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20">
         <v>1</v>
       </c>
       <c r="J5">
@@ -2460,13 +2457,13 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="21">
-        <v>1</v>
-      </c>
-      <c r="N5" s="21">
-        <v>0</v>
-      </c>
-      <c r="O5" s="21">
+      <c r="M5" s="20">
+        <v>1</v>
+      </c>
+      <c r="N5" s="20">
+        <v>0</v>
+      </c>
+      <c r="O5" s="20">
         <v>0</v>
       </c>
       <c r="Q5" s="13">
@@ -2476,32 +2473,32 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="22" customFormat="1" spans="1:17">
-      <c r="A6" s="22">
+    <row r="6" s="21" customFormat="1" spans="1:17">
+      <c r="A6" s="21">
         <v>101</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="22">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="21">
+        <v>0</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="21" t="b">
+      <c r="G6" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="20">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2513,39 +2510,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="21">
-        <v>1</v>
-      </c>
-      <c r="N6" s="21">
-        <v>0</v>
-      </c>
-      <c r="O6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="22" customFormat="1" spans="1:17">
-      <c r="A7" s="22">
+      <c r="M6" s="20">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="21" customFormat="1" spans="1:17">
+      <c r="A7" s="21">
         <v>102</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="22">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="21">
+        <v>0</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="21">
+      <c r="G7" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="20">
         <v>1</v>
       </c>
       <c r="J7">
@@ -2554,16 +2551,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="21">
-        <v>1</v>
-      </c>
-      <c r="N7" s="21">
-        <v>0</v>
-      </c>
-      <c r="O7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="22">
+      <c r="M7" s="20">
+        <v>1</v>
+      </c>
+      <c r="N7" s="20">
+        <v>0</v>
+      </c>
+      <c r="O7" s="20">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="21">
         <v>0</v>
       </c>
     </row>
@@ -2586,13 +2583,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="21" t="b">
+      <c r="G8" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="20">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2604,13 +2601,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="21">
-        <v>1</v>
-      </c>
-      <c r="N8" s="21">
-        <v>0</v>
-      </c>
-      <c r="O8" s="21">
+      <c r="M8" s="20">
+        <v>1</v>
+      </c>
+      <c r="N8" s="20">
+        <v>0</v>
+      </c>
+      <c r="O8" s="20">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -2623,14 +2620,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="15" customFormat="1" spans="1:18">
-      <c r="A9" s="15">
+    <row r="9" s="12" customFormat="1" spans="1:18">
+      <c r="A9" s="12">
         <v>202</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="12">
         <v>1</v>
       </c>
       <c r="D9" s="12" t="s">
@@ -2642,37 +2639,37 @@
       <c r="F9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="26" t="b">
+      <c r="G9" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="26">
-        <v>1</v>
-      </c>
-      <c r="J9" s="15">
-        <v>0</v>
-      </c>
-      <c r="K9" s="15">
+      <c r="I9" s="22">
+        <v>1</v>
+      </c>
+      <c r="J9" s="12">
+        <v>0</v>
+      </c>
+      <c r="K9" s="12">
         <v>2</v>
       </c>
       <c r="L9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="26">
-        <v>1</v>
-      </c>
-      <c r="N9" s="26">
-        <v>0</v>
-      </c>
-      <c r="O9" s="26">
+      <c r="M9" s="22">
+        <v>1</v>
+      </c>
+      <c r="N9" s="22">
+        <v>0</v>
+      </c>
+      <c r="O9" s="22">
         <v>0</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="12">
         <v>3</v>
       </c>
       <c r="R9" s="12" t="s">
@@ -2698,13 +2695,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="21" t="b">
+      <c r="G10" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="20">
         <v>1</v>
       </c>
       <c r="J10">
@@ -2716,13 +2713,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="21">
-        <v>1</v>
-      </c>
-      <c r="N10" s="21">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21">
+      <c r="M10" s="20">
+        <v>1</v>
+      </c>
+      <c r="N10" s="20">
+        <v>0</v>
+      </c>
+      <c r="O10" s="20">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -2751,13 +2748,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="21" t="b">
+      <c r="G11" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="20">
         <v>1</v>
       </c>
       <c r="J11">
@@ -2769,13 +2766,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="21">
-        <v>1</v>
-      </c>
-      <c r="N11" s="21">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21">
+      <c r="M11" s="20">
+        <v>1</v>
+      </c>
+      <c r="N11" s="20">
+        <v>0</v>
+      </c>
+      <c r="O11" s="20">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -2807,13 +2804,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="21" t="b">
+      <c r="G12" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="20">
         <v>1</v>
       </c>
       <c r="J12">
@@ -2825,13 +2822,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="21">
-        <v>1</v>
-      </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="21">
+      <c r="M12" s="20">
+        <v>1</v>
+      </c>
+      <c r="N12" s="20">
+        <v>0</v>
+      </c>
+      <c r="O12" s="20">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -2863,13 +2860,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="21" t="b">
+      <c r="G13" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="20">
         <v>1</v>
       </c>
       <c r="J13">
@@ -2881,13 +2878,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="21">
-        <v>1</v>
-      </c>
-      <c r="N13" s="21">
-        <v>1</v>
-      </c>
-      <c r="O13" s="21">
+      <c r="M13" s="20">
+        <v>1</v>
+      </c>
+      <c r="N13" s="20">
+        <v>1</v>
+      </c>
+      <c r="O13" s="20">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -2916,16 +2913,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="21" t="b">
+      <c r="G14" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="20">
         <v>1</v>
       </c>
       <c r="J14">
@@ -2937,13 +2934,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="21">
-        <v>1</v>
-      </c>
-      <c r="N14" s="21">
-        <v>0</v>
-      </c>
-      <c r="O14" s="21">
+      <c r="M14" s="20">
+        <v>1</v>
+      </c>
+      <c r="N14" s="20">
+        <v>0</v>
+      </c>
+      <c r="O14" s="20">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -2972,16 +2969,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="21" t="b">
+      <c r="G15" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="20">
         <v>1</v>
       </c>
       <c r="J15">
@@ -2993,13 +2990,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="21">
-        <v>1</v>
-      </c>
-      <c r="N15" s="21">
-        <v>0</v>
-      </c>
-      <c r="O15" s="21">
+      <c r="M15" s="20">
+        <v>1</v>
+      </c>
+      <c r="N15" s="20">
+        <v>0</v>
+      </c>
+      <c r="O15" s="20">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -3031,13 +3028,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="21" t="b">
+      <c r="G16" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="20">
         <v>1</v>
       </c>
       <c r="J16">
@@ -3049,13 +3046,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="21">
-        <v>1</v>
-      </c>
-      <c r="N16" s="21">
-        <v>0</v>
-      </c>
-      <c r="O16" s="21">
+      <c r="M16" s="20">
+        <v>1</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0</v>
+      </c>
+      <c r="O16" s="20">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -3087,13 +3084,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="21" t="b">
+      <c r="G17" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="20">
         <v>1</v>
       </c>
       <c r="J17">
@@ -3105,13 +3102,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="21">
-        <v>1</v>
-      </c>
-      <c r="N17" s="21">
-        <v>0</v>
-      </c>
-      <c r="O17" s="21">
+      <c r="M17" s="20">
+        <v>1</v>
+      </c>
+      <c r="N17" s="20">
+        <v>0</v>
+      </c>
+      <c r="O17" s="20">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -3137,10 +3134,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="21">
+      <c r="G18" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="20">
         <v>1</v>
       </c>
       <c r="J18">
@@ -3149,13 +3146,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="21">
-        <v>1</v>
-      </c>
-      <c r="N18" s="21">
-        <v>0</v>
-      </c>
-      <c r="O18" s="21">
+      <c r="M18" s="20">
+        <v>1</v>
+      </c>
+      <c r="N18" s="20">
+        <v>0</v>
+      </c>
+      <c r="O18" s="20">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -3181,13 +3178,13 @@
       <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="21" t="b">
+      <c r="G19" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="20">
         <v>1</v>
       </c>
       <c r="J19">
@@ -3199,13 +3196,13 @@
       <c r="L19" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="21">
-        <v>1</v>
-      </c>
-      <c r="N19" s="21">
-        <v>0</v>
-      </c>
-      <c r="O19" s="21">
+      <c r="M19" s="20">
+        <v>1</v>
+      </c>
+      <c r="N19" s="20">
+        <v>0</v>
+      </c>
+      <c r="O19" s="20">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -3237,13 +3234,13 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="21" t="b">
+      <c r="G20" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="20">
         <v>1</v>
       </c>
       <c r="J20">
@@ -3255,13 +3252,13 @@
       <c r="L20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="21">
-        <v>1</v>
-      </c>
-      <c r="N20" s="21">
-        <v>0</v>
-      </c>
-      <c r="O20" s="21">
+      <c r="M20" s="20">
+        <v>1</v>
+      </c>
+      <c r="N20" s="20">
+        <v>0</v>
+      </c>
+      <c r="O20" s="20">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -3293,13 +3290,13 @@
       <c r="F21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" s="21" t="b">
+      <c r="G21" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="20">
         <v>1</v>
       </c>
       <c r="J21">
@@ -3311,13 +3308,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="21">
-        <v>1</v>
-      </c>
-      <c r="N21" s="21">
-        <v>0</v>
-      </c>
-      <c r="O21" s="21">
+      <c r="M21" s="20">
+        <v>1</v>
+      </c>
+      <c r="N21" s="20">
+        <v>0</v>
+      </c>
+      <c r="O21" s="20">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -3349,13 +3346,13 @@
       <c r="F22" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="21" t="b">
+      <c r="G22" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="20">
         <v>1</v>
       </c>
       <c r="J22">
@@ -3367,13 +3364,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="21">
-        <v>1</v>
-      </c>
-      <c r="N22" s="21">
-        <v>0</v>
-      </c>
-      <c r="O22" s="21">
+      <c r="M22" s="20">
+        <v>1</v>
+      </c>
+      <c r="N22" s="20">
+        <v>0</v>
+      </c>
+      <c r="O22" s="20">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -3405,13 +3402,13 @@
       <c r="F23" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="21" t="b">
+      <c r="G23" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="20">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3423,13 +3420,13 @@
       <c r="L23" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="21">
-        <v>1</v>
-      </c>
-      <c r="N23" s="21">
-        <v>0</v>
-      </c>
-      <c r="O23" s="21">
+      <c r="M23" s="20">
+        <v>1</v>
+      </c>
+      <c r="N23" s="20">
+        <v>0</v>
+      </c>
+      <c r="O23" s="20">
         <v>0</v>
       </c>
       <c r="P23" s="13" t="s">
@@ -3461,13 +3458,13 @@
       <c r="F24" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="21" t="b">
+      <c r="G24" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="20">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -3479,13 +3476,13 @@
       <c r="L24" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="21">
-        <v>1</v>
-      </c>
-      <c r="N24" s="21">
-        <v>0</v>
-      </c>
-      <c r="O24" s="21">
+      <c r="M24" s="20">
+        <v>1</v>
+      </c>
+      <c r="N24" s="20">
+        <v>0</v>
+      </c>
+      <c r="O24" s="20">
         <v>0</v>
       </c>
       <c r="P24" s="13" t="s">
@@ -3514,13 +3511,13 @@
       <c r="E25" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="21" t="b">
+      <c r="G25" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="20">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3529,13 +3526,13 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="21">
-        <v>1</v>
-      </c>
-      <c r="N25" s="21">
-        <v>0</v>
-      </c>
-      <c r="O25" s="21">
+      <c r="M25" s="20">
+        <v>1</v>
+      </c>
+      <c r="N25" s="20">
+        <v>0</v>
+      </c>
+      <c r="O25" s="20">
         <v>0</v>
       </c>
       <c r="P25" s="13" t="s">
@@ -3567,13 +3564,13 @@
       <c r="F26" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="21" t="b">
+      <c r="G26" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="20">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -3585,13 +3582,13 @@
       <c r="L26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="21">
-        <v>1</v>
-      </c>
-      <c r="N26" s="21">
-        <v>0</v>
-      </c>
-      <c r="O26" s="21">
+      <c r="M26" s="20">
+        <v>1</v>
+      </c>
+      <c r="N26" s="20">
+        <v>0</v>
+      </c>
+      <c r="O26" s="20">
         <v>0</v>
       </c>
       <c r="P26" s="13" t="s">
@@ -3623,13 +3620,13 @@
       <c r="F27" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="21" t="b">
+      <c r="G27" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="20">
         <v>1</v>
       </c>
       <c r="J27">
@@ -3641,13 +3638,13 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="21">
-        <v>1</v>
-      </c>
-      <c r="N27" s="21">
-        <v>0</v>
-      </c>
-      <c r="O27" s="21">
+      <c r="M27" s="20">
+        <v>1</v>
+      </c>
+      <c r="N27" s="20">
+        <v>0</v>
+      </c>
+      <c r="O27" s="20">
         <v>0</v>
       </c>
       <c r="P27" s="13" t="s">
@@ -3679,13 +3676,13 @@
       <c r="F28" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G28" s="21" t="b">
+      <c r="G28" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H28" s="13">
         <v>0</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="20">
         <v>1</v>
       </c>
       <c r="J28">
@@ -3697,13 +3694,13 @@
       <c r="L28" s="13">
         <v>1</v>
       </c>
-      <c r="M28" s="21">
-        <v>1</v>
-      </c>
-      <c r="N28" s="21">
-        <v>0</v>
-      </c>
-      <c r="O28" s="21">
+      <c r="M28" s="20">
+        <v>1</v>
+      </c>
+      <c r="N28" s="20">
+        <v>0</v>
+      </c>
+      <c r="O28" s="20">
         <v>0</v>
       </c>
       <c r="P28" s="13" t="s">
@@ -3735,13 +3732,13 @@
       <c r="F29" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="21" t="b">
+      <c r="G29" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="I29" s="21">
+        <v>154</v>
+      </c>
+      <c r="I29" s="20">
         <v>1</v>
       </c>
       <c r="J29">
@@ -3751,15 +3748,15 @@
         <v>4.73</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="M29" s="21">
+        <v>154</v>
+      </c>
+      <c r="M29" s="20">
         <v>0.1</v>
       </c>
-      <c r="N29" s="21">
-        <v>0</v>
-      </c>
-      <c r="O29" s="21">
+      <c r="N29" s="20">
+        <v>0</v>
+      </c>
+      <c r="O29" s="20">
         <v>0.17</v>
       </c>
       <c r="P29" s="13" t="s">
@@ -3769,7 +3766,7 @@
         <v>3</v>
       </c>
       <c r="R29" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" s="13" customFormat="1" spans="1:18">
@@ -3777,27 +3774,27 @@
         <v>308</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" s="13">
         <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E30" s="13" t="s">
         <v>27</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="21" t="b">
+        <v>158</v>
+      </c>
+      <c r="G30" s="20" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="I30" s="21">
+        <v>159</v>
+      </c>
+      <c r="I30" s="20">
         <v>1</v>
       </c>
       <c r="J30">
@@ -3807,15 +3804,15 @@
         <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="M30" s="21">
-        <v>1</v>
-      </c>
-      <c r="N30" s="21">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21">
+        <v>154</v>
+      </c>
+      <c r="M30" s="20">
+        <v>1</v>
+      </c>
+      <c r="N30" s="20">
+        <v>0</v>
+      </c>
+      <c r="O30" s="20">
         <v>0</v>
       </c>
       <c r="P30" s="13" t="s">
@@ -3825,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="R30" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" s="13" customFormat="1" spans="1:18">
@@ -3833,27 +3830,27 @@
         <v>309</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="13">
         <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="F31" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G31" s="21" t="b">
+      <c r="G31" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="20">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3865,13 +3862,13 @@
       <c r="L31" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M31" s="21">
-        <v>1</v>
-      </c>
-      <c r="N31" s="21">
-        <v>0</v>
-      </c>
-      <c r="O31" s="21">
+      <c r="M31" s="20">
+        <v>1</v>
+      </c>
+      <c r="N31" s="20">
+        <v>0</v>
+      </c>
+      <c r="O31" s="20">
         <v>0</v>
       </c>
       <c r="P31" s="13" t="s">
@@ -3881,7 +3878,7 @@
         <v>3</v>
       </c>
       <c r="R31" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" s="13" customFormat="1" spans="1:18">
@@ -3889,27 +3886,27 @@
         <v>310</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" s="13">
         <v>2</v>
       </c>
       <c r="D32" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="G32" s="21" t="b">
+      <c r="G32" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H32" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="20">
         <v>1</v>
       </c>
       <c r="J32">
@@ -3921,13 +3918,13 @@
       <c r="L32" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="21">
-        <v>1</v>
-      </c>
-      <c r="N32" s="21">
-        <v>0</v>
-      </c>
-      <c r="O32" s="21">
+      <c r="M32" s="20">
+        <v>1</v>
+      </c>
+      <c r="N32" s="20">
+        <v>0</v>
+      </c>
+      <c r="O32" s="20">
         <v>0</v>
       </c>
       <c r="P32" s="13" t="s">
@@ -3937,7 +3934,7 @@
         <v>4</v>
       </c>
       <c r="R32" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" s="13" customFormat="1" spans="1:18">
@@ -3945,27 +3942,27 @@
         <v>311</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="13">
         <v>2</v>
       </c>
       <c r="D33" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F33" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="G33" s="21" t="b">
+      <c r="G33" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H33" s="13">
         <v>0</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="20">
         <v>1</v>
       </c>
       <c r="J33">
@@ -3977,13 +3974,13 @@
       <c r="L33" s="13">
         <v>1</v>
       </c>
-      <c r="M33" s="21">
-        <v>1</v>
-      </c>
-      <c r="N33" s="21">
-        <v>0</v>
-      </c>
-      <c r="O33" s="21">
+      <c r="M33" s="20">
+        <v>1</v>
+      </c>
+      <c r="N33" s="20">
+        <v>0</v>
+      </c>
+      <c r="O33" s="20">
         <v>0</v>
       </c>
       <c r="P33" s="13" t="s">
@@ -3993,7 +3990,7 @@
         <v>3</v>
       </c>
       <c r="R33" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" s="13" customFormat="1" spans="1:18">
@@ -4001,18 +3998,18 @@
         <v>312</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" s="13">
         <v>2</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="G34" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="21">
+        <v>173</v>
+      </c>
+      <c r="G34" s="20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="20">
         <v>1</v>
       </c>
       <c r="J34">
@@ -4021,28 +4018,28 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="21">
-        <v>1</v>
-      </c>
-      <c r="N34" s="21">
-        <v>0</v>
-      </c>
-      <c r="O34" s="21">
+      <c r="M34" s="20">
+        <v>1</v>
+      </c>
+      <c r="N34" s="20">
+        <v>0</v>
+      </c>
+      <c r="O34" s="20">
         <v>0</v>
       </c>
       <c r="Q34" s="13">
         <v>1</v>
       </c>
       <c r="R34" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" s="11" customFormat="1" spans="1:17">
       <c r="A35" s="11">
         <v>401</v>
       </c>
-      <c r="B35" s="28" t="s">
-        <v>174</v>
+      <c r="B35" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="C35" s="11">
         <v>2</v>
@@ -4050,16 +4047,16 @@
       <c r="D35" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="21" t="b">
+      <c r="G35" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="20">
         <v>1</v>
       </c>
       <c r="J35">
@@ -4071,13 +4068,13 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="21">
-        <v>1</v>
-      </c>
-      <c r="N35" s="21">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21">
+      <c r="M35" s="20">
+        <v>1</v>
+      </c>
+      <c r="N35" s="20">
+        <v>0</v>
+      </c>
+      <c r="O35" s="20">
         <v>0</v>
       </c>
       <c r="P35" s="11" t="s">
@@ -4091,8 +4088,8 @@
       <c r="A36" s="11">
         <v>402</v>
       </c>
-      <c r="B36" s="28" t="s">
-        <v>175</v>
+      <c r="B36" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="C36" s="11">
         <v>2</v>
@@ -4100,16 +4097,16 @@
       <c r="D36" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="21" t="b">
+      <c r="G36" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="20">
         <v>1</v>
       </c>
       <c r="J36">
@@ -4121,13 +4118,13 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="21">
-        <v>1</v>
-      </c>
-      <c r="N36" s="21">
-        <v>0</v>
-      </c>
-      <c r="O36" s="21">
+      <c r="M36" s="20">
+        <v>1</v>
+      </c>
+      <c r="N36" s="20">
+        <v>0</v>
+      </c>
+      <c r="O36" s="20">
         <v>0</v>
       </c>
       <c r="P36" s="11" t="s">
@@ -4141,8 +4138,8 @@
       <c r="A37" s="11">
         <v>403</v>
       </c>
-      <c r="B37" s="28" t="s">
-        <v>176</v>
+      <c r="B37" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="C37" s="11">
         <v>2</v>
@@ -4151,18 +4148,18 @@
         <v>59</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="21" t="b">
+      <c r="G37" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="20">
         <v>1</v>
       </c>
       <c r="J37">
@@ -4174,13 +4171,13 @@
       <c r="L37" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="21">
-        <v>1</v>
-      </c>
-      <c r="N37" s="21">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21">
+      <c r="M37" s="20">
+        <v>1</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
         <v>0</v>
       </c>
       <c r="P37" s="11" t="s">
@@ -4190,56 +4187,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="23" customFormat="1" spans="1:17">
-      <c r="A38" s="23">
+    <row r="38" s="22" customFormat="1" spans="1:17">
+      <c r="A38" s="22">
         <v>404</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="23">
+      <c r="B38" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="C38" s="22">
         <v>1</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="22" t="s">
         <v>41</v>
       </c>
       <c r="F38" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="26" t="s">
+      <c r="G38" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="26">
-        <v>1</v>
-      </c>
-      <c r="J38" s="15">
-        <v>0</v>
-      </c>
-      <c r="K38" s="15">
+      <c r="I38" s="22">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12">
+        <v>0</v>
+      </c>
+      <c r="K38" s="12">
         <v>2</v>
       </c>
-      <c r="L38" s="26" t="s">
+      <c r="L38" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="26">
-        <v>1</v>
-      </c>
-      <c r="N38" s="26">
-        <v>0</v>
-      </c>
-      <c r="O38" s="26">
-        <v>0</v>
-      </c>
-      <c r="P38" s="26" t="s">
+      <c r="M38" s="22">
+        <v>1</v>
+      </c>
+      <c r="N38" s="22">
+        <v>0</v>
+      </c>
+      <c r="O38" s="22">
+        <v>0</v>
+      </c>
+      <c r="P38" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="23">
+      <c r="Q38" s="22">
         <v>3</v>
       </c>
     </row>
@@ -4247,8 +4244,8 @@
       <c r="A39" s="11">
         <v>405</v>
       </c>
-      <c r="B39" s="28" t="s">
-        <v>179</v>
+      <c r="B39" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -4262,13 +4259,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="21" t="b">
+      <c r="G39" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="20">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4280,13 +4277,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="21">
-        <v>1</v>
-      </c>
-      <c r="N39" s="21">
-        <v>0</v>
-      </c>
-      <c r="O39" s="21">
+      <c r="M39" s="20">
+        <v>1</v>
+      </c>
+      <c r="N39" s="20">
+        <v>0</v>
+      </c>
+      <c r="O39" s="20">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -4306,8 +4303,8 @@
       <c r="A40" s="11">
         <v>406</v>
       </c>
-      <c r="B40" s="28" t="s">
-        <v>180</v>
+      <c r="B40" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="C40" s="11">
         <v>1</v>
@@ -4321,13 +4318,13 @@
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="21" t="b">
+      <c r="G40" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H40" s="11">
         <v>0</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="20">
         <v>1</v>
       </c>
       <c r="J40">
@@ -4339,13 +4336,13 @@
       <c r="L40" s="11">
         <v>3</v>
       </c>
-      <c r="M40" s="21">
-        <v>1</v>
-      </c>
-      <c r="N40" s="21">
-        <v>0</v>
-      </c>
-      <c r="O40" s="21">
+      <c r="M40" s="20">
+        <v>1</v>
+      </c>
+      <c r="N40" s="20">
+        <v>0</v>
+      </c>
+      <c r="O40" s="20">
         <v>0</v>
       </c>
       <c r="P40" s="11" t="s">
@@ -4360,7 +4357,7 @@
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -4374,13 +4371,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="21" t="b">
+      <c r="G41" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="20">
         <v>1</v>
       </c>
       <c r="J41">
@@ -4392,13 +4389,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="21">
-        <v>1</v>
-      </c>
-      <c r="N41" s="21">
-        <v>0</v>
-      </c>
-      <c r="O41" s="21">
+      <c r="M41" s="20">
+        <v>1</v>
+      </c>
+      <c r="N41" s="20">
+        <v>0</v>
+      </c>
+      <c r="O41" s="20">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -4416,7 +4413,7 @@
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -4430,13 +4427,13 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="21" t="b">
+      <c r="G42" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="20">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4448,13 +4445,13 @@
       <c r="L42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="21">
-        <v>1</v>
-      </c>
-      <c r="N42" s="21">
-        <v>0</v>
-      </c>
-      <c r="O42" s="21">
+      <c r="M42" s="20">
+        <v>1</v>
+      </c>
+      <c r="N42" s="20">
+        <v>0</v>
+      </c>
+      <c r="O42" s="20">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -4472,7 +4469,7 @@
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C43">
         <v>2</v>
@@ -4486,13 +4483,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="21" t="b">
+      <c r="G43" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="20">
         <v>1</v>
       </c>
       <c r="J43">
@@ -4504,13 +4501,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="21">
-        <v>1</v>
-      </c>
-      <c r="N43" s="21">
-        <v>0</v>
-      </c>
-      <c r="O43" s="21">
+      <c r="M43" s="20">
+        <v>1</v>
+      </c>
+      <c r="N43" s="20">
+        <v>0</v>
+      </c>
+      <c r="O43" s="20">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -4528,7 +4525,7 @@
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -4542,13 +4539,13 @@
       <c r="F44" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="21" t="b">
+      <c r="G44" s="20" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="20">
         <v>1</v>
       </c>
       <c r="J44">
@@ -4560,13 +4557,13 @@
       <c r="L44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" s="21">
-        <v>1</v>
-      </c>
-      <c r="N44" s="21">
-        <v>0</v>
-      </c>
-      <c r="O44" s="21">
+      <c r="M44" s="20">
+        <v>1</v>
+      </c>
+      <c r="N44" s="20">
+        <v>0</v>
+      </c>
+      <c r="O44" s="20">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -4605,22 +4602,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4628,16 +4625,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4645,16 +4642,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4662,16 +4659,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4679,16 +4676,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="C5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4696,16 +4693,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4713,16 +4710,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" t="s">
         <v>305</v>
-      </c>
-      <c r="C7" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4730,16 +4727,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4747,16 +4744,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" t="s">
         <v>310</v>
-      </c>
-      <c r="C9" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4764,16 +4761,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4781,16 +4778,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4798,22 +4795,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4821,16 +4818,16 @@
         <v>101</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:7">
@@ -4838,22 +4835,22 @@
         <v>102</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4861,16 +4858,16 @@
         <v>201</v>
       </c>
       <c r="B15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C15" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D15" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:7">
@@ -4878,22 +4875,22 @@
         <v>202</v>
       </c>
       <c r="B16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -4924,10 +4921,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4936,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4944,7 +4941,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
   </sheetData>
@@ -4969,22 +4966,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5355,284 +5352,284 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="17" customFormat="1" spans="1:7">
-      <c r="A18" s="17">
+    <row r="18" s="16" customFormat="1" spans="1:7">
+      <c r="A18" s="16">
         <v>301</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>50</v>
       </c>
-      <c r="D18" s="17">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17">
+      <c r="D18" s="16">
+        <v>0</v>
+      </c>
+      <c r="E18" s="16">
         <v>400</v>
       </c>
-      <c r="F18" s="17">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19">
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="18">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="17" customFormat="1" spans="1:7">
-      <c r="A19" s="17">
+    <row r="19" s="16" customFormat="1" spans="1:7">
+      <c r="A19" s="16">
         <v>302</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>25</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <v>9</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>100</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <v>303</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="17" customFormat="1" spans="1:7">
-      <c r="A20" s="17">
+    <row r="20" s="16" customFormat="1" spans="1:7">
+      <c r="A20" s="16">
         <v>303</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="16">
         <v>20</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <v>3</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="16">
         <v>50</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="16">
         <v>301</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="17" customFormat="1" spans="1:7">
-      <c r="A21" s="17">
+    <row r="21" s="16" customFormat="1" spans="1:7">
+      <c r="A21" s="16">
         <v>304</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>30</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <v>11</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="16">
         <v>300</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="16">
         <v>301</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="17" customFormat="1" spans="1:7">
-      <c r="A22" s="17">
+    <row r="22" s="16" customFormat="1" spans="1:7">
+      <c r="A22" s="16">
         <v>305</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <v>25</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <v>8</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <v>100</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="16">
         <v>303</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="17" customFormat="1" spans="1:7">
-      <c r="A23" s="17">
+    <row r="23" s="16" customFormat="1" spans="1:7">
+      <c r="A23" s="16">
         <v>306</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="16">
         <v>35</v>
       </c>
-      <c r="D23" s="17">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17">
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16">
         <v>200</v>
       </c>
-      <c r="F23" s="17">
-        <v>0</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+      <c r="G23" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="17" customFormat="1" spans="1:7">
-      <c r="A24" s="17">
+    <row r="24" s="16" customFormat="1" spans="1:7">
+      <c r="A24" s="16">
         <v>307</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>35</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>12</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>150</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="16">
         <v>302</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="17" customFormat="1" spans="1:7">
-      <c r="A25" s="17">
+    <row r="25" s="16" customFormat="1" spans="1:7">
+      <c r="A25" s="16">
         <v>308</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C25" s="17">
+      <c r="B25" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" s="16">
         <v>35</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="16">
         <v>12</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>150</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="16">
         <v>302</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="17" customFormat="1" spans="1:7">
-      <c r="A26" s="17">
+    <row r="26" s="16" customFormat="1" spans="1:7">
+      <c r="A26" s="16">
         <v>309</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C26" s="17">
+      <c r="B26" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="16">
         <v>20</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="16">
         <v>10</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>80</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="16">
         <v>306</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="17" customFormat="1" spans="1:7">
-      <c r="A27" s="17">
+    <row r="27" s="16" customFormat="1" spans="1:7">
+      <c r="A27" s="16">
         <v>310</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C27" s="17">
+      <c r="B27" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="16">
         <v>30</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>10</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>120</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="16">
         <v>309</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="18">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="17" customFormat="1" spans="1:7">
-      <c r="A28" s="17">
+    <row r="28" s="16" customFormat="1" spans="1:7">
+      <c r="A28" s="16">
         <v>311</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C28" s="17">
+      <c r="B28" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="16">
         <v>30</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="16">
         <v>10</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="16">
         <v>120</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="16">
         <v>309</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="17" customFormat="1" spans="1:7">
-      <c r="A29" s="17">
+    <row r="29" s="16" customFormat="1" spans="1:7">
+      <c r="A29" s="16">
         <v>312</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C29" s="17">
+      <c r="B29" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C29" s="16">
         <v>15</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="16">
         <v>2</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="16">
         <v>15</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="16">
         <v>306</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="18">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="17" customFormat="1" spans="2:2">
-      <c r="B30" s="18"/>
+    <row r="30" s="16" customFormat="1" spans="2:2">
+      <c r="B30" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5656,22 +5653,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5748,7 +5745,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -5851,7 +5848,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>0.05</v>
@@ -5868,7 +5865,7 @@
         <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -5888,7 +5885,7 @@
         <v>309</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -5908,7 +5905,7 @@
         <v>310</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13">
         <v>2.5</v>
@@ -5928,7 +5925,7 @@
         <v>311</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -5951,7 +5948,7 @@
         <v>312</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -5994,25 +5991,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6023,7 +6020,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6038,33 +6035,33 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="3" s="15" customFormat="1" spans="1:8">
-      <c r="A3" s="15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" s="12" customFormat="1" spans="1:8">
+      <c r="A3" s="12">
         <v>202</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="15">
-        <v>0</v>
-      </c>
-      <c r="F3" s="15">
+        <v>207</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0</v>
+      </c>
+      <c r="F3" s="12">
         <v>0.8</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>41</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6075,7 +6072,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6090,7 +6087,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6101,10 +6098,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6116,7 +6113,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6127,10 +6124,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6139,10 +6136,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6168,7 +6165,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6179,10 +6176,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6191,10 +6188,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6205,10 +6202,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6217,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6234,7 +6231,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6257,10 +6254,10 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6269,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6297,7 +6294,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6309,10 +6306,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6323,7 +6320,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6335,10 +6332,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6349,7 +6346,7 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6361,10 +6358,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6375,10 +6372,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6390,7 +6387,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6398,13 +6395,13 @@
         <v>401</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6418,13 +6415,13 @@
         <v>402</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6438,45 +6435,45 @@
         <v>403</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D19" t="s">
+        <v>207</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="12" customFormat="1" spans="1:8">
+      <c r="A20" s="15">
+        <v>404</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="15" customFormat="1" spans="1:8">
-      <c r="A20" s="16">
-        <v>404</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>205</v>
-      </c>
       <c r="D20" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15">
+        <v>207</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12">
         <v>0.8</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>41</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6484,10 +6481,10 @@
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6502,7 +6499,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6510,10 +6507,10 @@
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6528,7 +6525,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6536,13 +6533,13 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6562,10 +6559,10 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6577,10 +6574,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6588,13 +6585,13 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6603,10 +6600,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6614,10 +6611,10 @@
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6629,10 +6626,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -6681,64 +6678,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J1" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K1" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L1" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N1" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O1" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P1" s="12" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q1" s="12" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R1" s="12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S1" s="12" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="T1" s="12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U1" s="12" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6782,7 +6779,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6823,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -6835,7 +6832,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6844,7 +6841,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6900,7 +6897,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6944,7 +6941,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6956,13 +6953,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -7003,7 +7000,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7018,7 +7015,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7071,7 +7068,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7080,7 +7077,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7121,7 +7118,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7133,7 +7130,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7142,7 +7139,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7183,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7198,7 +7195,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7239,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7254,7 +7251,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7298,7 +7295,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7313,7 +7310,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7366,7 +7363,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7466,7 +7463,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7475,7 +7472,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7531,7 +7528,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7572,7 +7569,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7584,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7593,7 +7590,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7882,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7891,7 +7888,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8029,7 +8026,7 @@
         <v>308</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -8088,7 +8085,7 @@
         <v>309</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -8147,7 +8144,7 @@
         <v>310</v>
       </c>
       <c r="B26" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -8206,7 +8203,7 @@
         <v>311</v>
       </c>
       <c r="B27" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -8265,7 +8262,7 @@
         <v>312</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -8324,7 +8321,7 @@
         <v>401</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C29">
         <v>18</v>
@@ -8345,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8357,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8366,7 +8363,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8386,7 +8383,7 @@
         <v>402</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -8407,7 +8404,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8422,7 +8419,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8442,7 +8439,7 @@
         <v>403</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -8463,7 +8460,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8478,7 +8475,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8498,7 +8495,7 @@
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -8519,7 +8516,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -8531,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8540,7 +8537,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8560,7 +8557,7 @@
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -8596,7 +8593,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8616,7 +8613,7 @@
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -8652,7 +8649,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8672,7 +8669,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -8693,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8708,7 +8705,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8728,7 +8725,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -8758,7 +8755,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8767,7 +8764,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8787,7 +8784,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -8811,7 +8808,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8826,7 +8823,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8846,7 +8843,7 @@
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8908,10 +8905,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8963,7 +8960,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -8974,7 +8971,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -8985,7 +8982,7 @@
         <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -8996,7 +8993,7 @@
         <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9">
         <v>15</v>
@@ -9007,7 +9004,7 @@
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C10">
         <v>20</v>
@@ -9018,7 +9015,7 @@
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C11">
         <v>25</v>
@@ -9029,7 +9026,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9040,7 +9037,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9051,7 +9048,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9062,7 +9059,7 @@
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C15">
         <v>45</v>
@@ -9088,25 +9085,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9117,7 +9114,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9143,7 +9140,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9169,7 +9166,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9195,7 +9192,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9221,7 +9218,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9247,7 +9244,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9273,7 +9270,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9299,7 +9296,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9337,13 +9334,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9391,19 +9388,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9411,7 +9408,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9428,7 +9425,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9445,7 +9442,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9462,7 +9459,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9479,7 +9476,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9496,7 +9493,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9513,7 +9510,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="341">
   <si>
     <t>类型</t>
   </si>
@@ -1061,6 +1061,12 @@
     <t>https://www.rtsgame.online/图片/地图/ditu4_8_高清.png</t>
   </si>
   <si>
+    <t>新手训练_防空战_人</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3</t>
+  </si>
+  <si>
     <t>四方对战</t>
   </si>
   <si>
@@ -1120,9 +1126,6 @@
     <t>多玩家混战</t>
   </si>
   <si>
-    <t>https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3</t>
-  </si>
-  <si>
     <t>圆坑混战</t>
   </si>
   <si>
@@ -1183,7 +1186,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1219,6 +1222,11 @@
       <sz val="10.5"/>
       <color rgb="FFE394DC"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1737,128 +1745,128 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1883,10 +1891,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1895,7 +1906,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
@@ -1904,7 +1915,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -1916,15 +1927,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1934,13 +1936,22 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2268,32 +2279,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="19" customFormat="1" spans="1:18">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="19" t="s">
+    <row r="1" s="20" customFormat="1" spans="1:18">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2302,42 +2313,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="L1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="20" customFormat="1" spans="1:17">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="23" t="s">
+    <row r="2" s="21" customFormat="1" spans="1:17">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="20">
-        <v>0</v>
-      </c>
-      <c r="G2" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="20">
+      <c r="C2" s="21">
+        <v>0</v>
+      </c>
+      <c r="G2" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="21">
         <v>1</v>
       </c>
       <c r="J2">
@@ -2346,33 +2357,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="20">
-        <v>1</v>
-      </c>
-      <c r="N2" s="20">
-        <v>0</v>
-      </c>
-      <c r="O2" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="20" customFormat="1" spans="1:17">
-      <c r="A3" s="20">
+      <c r="M2" s="21">
+        <v>1</v>
+      </c>
+      <c r="N2" s="21">
+        <v>0</v>
+      </c>
+      <c r="O2" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="21" customFormat="1" spans="1:17">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="20">
-        <v>0</v>
-      </c>
-      <c r="G3" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="20">
+      <c r="C3" s="21">
+        <v>0</v>
+      </c>
+      <c r="G3" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="21">
         <v>1</v>
       </c>
       <c r="J3">
@@ -2381,36 +2392,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="20">
-        <v>1</v>
-      </c>
-      <c r="N3" s="20">
-        <v>0</v>
-      </c>
-      <c r="O3" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="13" customFormat="1" spans="1:17">
-      <c r="A4" s="13">
+      <c r="M3" s="21">
+        <v>1</v>
+      </c>
+      <c r="N3" s="21">
+        <v>0</v>
+      </c>
+      <c r="O3" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="14" customFormat="1" spans="1:17">
+      <c r="A4" s="14">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="14">
         <v>2</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="20">
+      <c r="G4" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="21">
         <v>1</v>
       </c>
       <c r="J4">
@@ -2419,36 +2430,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="20">
-        <v>1</v>
-      </c>
-      <c r="N4" s="20">
-        <v>0</v>
-      </c>
-      <c r="O4" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="13" customFormat="1" spans="1:18">
-      <c r="A5" s="13">
+      <c r="M4" s="21">
+        <v>1</v>
+      </c>
+      <c r="N4" s="21">
+        <v>0</v>
+      </c>
+      <c r="O4" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="14" customFormat="1" spans="1:18">
+      <c r="A5" s="14">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="13">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="14">
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="20">
+      <c r="G5" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="21">
         <v>1</v>
       </c>
       <c r="J5">
@@ -2457,48 +2468,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="20">
-        <v>1</v>
-      </c>
-      <c r="N5" s="20">
-        <v>0</v>
-      </c>
-      <c r="O5" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="13">
-        <v>0</v>
-      </c>
-      <c r="R5" s="13" t="s">
+      <c r="M5" s="21">
+        <v>1</v>
+      </c>
+      <c r="N5" s="21">
+        <v>0</v>
+      </c>
+      <c r="O5" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>0</v>
+      </c>
+      <c r="R5" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="21" customFormat="1" spans="1:17">
-      <c r="A6" s="21">
+    <row r="6" s="22" customFormat="1" spans="1:17">
+      <c r="A6" s="22">
         <v>101</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="21">
-        <v>0</v>
-      </c>
-      <c r="D6" s="21" t="s">
+      <c r="C6" s="22">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="20" t="b">
+      <c r="G6" s="21" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="21">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2510,39 +2521,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="20">
-        <v>1</v>
-      </c>
-      <c r="N6" s="20">
-        <v>0</v>
-      </c>
-      <c r="O6" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="21" customFormat="1" spans="1:17">
-      <c r="A7" s="21">
+      <c r="M6" s="21">
+        <v>1</v>
+      </c>
+      <c r="N6" s="21">
+        <v>0</v>
+      </c>
+      <c r="O6" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="22" customFormat="1" spans="1:17">
+      <c r="A7" s="22">
         <v>102</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="21">
-        <v>0</v>
-      </c>
-      <c r="D7" s="21" t="s">
+      <c r="C7" s="22">
+        <v>0</v>
+      </c>
+      <c r="D7" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="20">
+      <c r="G7" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="21">
         <v>1</v>
       </c>
       <c r="J7">
@@ -2551,16 +2562,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="20">
-        <v>1</v>
-      </c>
-      <c r="N7" s="20">
-        <v>0</v>
-      </c>
-      <c r="O7" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="21">
+      <c r="M7" s="21">
+        <v>1</v>
+      </c>
+      <c r="N7" s="21">
+        <v>0</v>
+      </c>
+      <c r="O7" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="22">
         <v>0</v>
       </c>
     </row>
@@ -2583,13 +2594,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="20" t="b">
+      <c r="G8" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2601,13 +2612,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="20">
-        <v>1</v>
-      </c>
-      <c r="N8" s="20">
-        <v>0</v>
-      </c>
-      <c r="O8" s="20">
+      <c r="M8" s="21">
+        <v>1</v>
+      </c>
+      <c r="N8" s="21">
+        <v>0</v>
+      </c>
+      <c r="O8" s="21">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -2620,59 +2631,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="12" customFormat="1" spans="1:18">
-      <c r="A9" s="12">
+    <row r="9" s="13" customFormat="1" spans="1:18">
+      <c r="A9" s="13">
         <v>202</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="C9" s="13">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="12" t="s">
+      <c r="G9" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="22">
-        <v>1</v>
-      </c>
-      <c r="J9" s="12">
-        <v>0</v>
-      </c>
-      <c r="K9" s="12">
+      <c r="I9" s="23">
+        <v>1</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13">
         <v>2</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="22">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22">
-        <v>0</v>
-      </c>
-      <c r="O9" s="22">
-        <v>0</v>
-      </c>
-      <c r="P9" s="12" t="s">
+      <c r="M9" s="23">
+        <v>1</v>
+      </c>
+      <c r="N9" s="23">
+        <v>0</v>
+      </c>
+      <c r="O9" s="23">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="13">
         <v>3</v>
       </c>
-      <c r="R9" s="12" t="s">
+      <c r="R9" s="13" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2695,13 +2706,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="20" t="b">
+      <c r="G10" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="21">
         <v>1</v>
       </c>
       <c r="J10">
@@ -2713,13 +2724,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="20">
-        <v>1</v>
-      </c>
-      <c r="N10" s="20">
-        <v>0</v>
-      </c>
-      <c r="O10" s="20">
+      <c r="M10" s="21">
+        <v>1</v>
+      </c>
+      <c r="N10" s="21">
+        <v>0</v>
+      </c>
+      <c r="O10" s="21">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -2748,13 +2759,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="20" t="b">
+      <c r="G11" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="21">
         <v>1</v>
       </c>
       <c r="J11">
@@ -2766,13 +2777,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="20">
-        <v>1</v>
-      </c>
-      <c r="N11" s="20">
-        <v>0</v>
-      </c>
-      <c r="O11" s="20">
+      <c r="M11" s="21">
+        <v>1</v>
+      </c>
+      <c r="N11" s="21">
+        <v>0</v>
+      </c>
+      <c r="O11" s="21">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -2804,13 +2815,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="20" t="b">
+      <c r="G12" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="21">
         <v>1</v>
       </c>
       <c r="J12">
@@ -2822,13 +2833,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="20">
-        <v>1</v>
-      </c>
-      <c r="N12" s="20">
-        <v>0</v>
-      </c>
-      <c r="O12" s="20">
+      <c r="M12" s="21">
+        <v>1</v>
+      </c>
+      <c r="N12" s="21">
+        <v>0</v>
+      </c>
+      <c r="O12" s="21">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -2860,13 +2871,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="20" t="b">
+      <c r="G13" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="21">
         <v>1</v>
       </c>
       <c r="J13">
@@ -2878,13 +2889,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="20">
-        <v>1</v>
-      </c>
-      <c r="N13" s="20">
-        <v>1</v>
-      </c>
-      <c r="O13" s="20">
+      <c r="M13" s="21">
+        <v>1</v>
+      </c>
+      <c r="N13" s="21">
+        <v>1</v>
+      </c>
+      <c r="O13" s="21">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -2913,16 +2924,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="20" t="b">
+      <c r="G14" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="21">
         <v>1</v>
       </c>
       <c r="J14">
@@ -2934,13 +2945,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="20">
-        <v>1</v>
-      </c>
-      <c r="N14" s="20">
-        <v>0</v>
-      </c>
-      <c r="O14" s="20">
+      <c r="M14" s="21">
+        <v>1</v>
+      </c>
+      <c r="N14" s="21">
+        <v>0</v>
+      </c>
+      <c r="O14" s="21">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -2969,16 +2980,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="20" t="b">
+      <c r="G15" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="21">
         <v>1</v>
       </c>
       <c r="J15">
@@ -2990,13 +3001,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="20">
-        <v>1</v>
-      </c>
-      <c r="N15" s="20">
-        <v>0</v>
-      </c>
-      <c r="O15" s="20">
+      <c r="M15" s="21">
+        <v>1</v>
+      </c>
+      <c r="N15" s="21">
+        <v>0</v>
+      </c>
+      <c r="O15" s="21">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -3028,13 +3039,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="20" t="b">
+      <c r="G16" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="21">
         <v>1</v>
       </c>
       <c r="J16">
@@ -3046,13 +3057,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="20">
-        <v>1</v>
-      </c>
-      <c r="N16" s="20">
-        <v>0</v>
-      </c>
-      <c r="O16" s="20">
+      <c r="M16" s="21">
+        <v>1</v>
+      </c>
+      <c r="N16" s="21">
+        <v>0</v>
+      </c>
+      <c r="O16" s="21">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -3084,13 +3095,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="20" t="b">
+      <c r="G17" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="21">
         <v>1</v>
       </c>
       <c r="J17">
@@ -3102,13 +3113,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="20">
-        <v>1</v>
-      </c>
-      <c r="N17" s="20">
-        <v>0</v>
-      </c>
-      <c r="O17" s="20">
+      <c r="M17" s="21">
+        <v>1</v>
+      </c>
+      <c r="N17" s="21">
+        <v>0</v>
+      </c>
+      <c r="O17" s="21">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -3134,10 +3145,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="20">
+      <c r="G18" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="21">
         <v>1</v>
       </c>
       <c r="J18">
@@ -3146,13 +3157,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="20">
-        <v>1</v>
-      </c>
-      <c r="N18" s="20">
-        <v>0</v>
-      </c>
-      <c r="O18" s="20">
+      <c r="M18" s="21">
+        <v>1</v>
+      </c>
+      <c r="N18" s="21">
+        <v>0</v>
+      </c>
+      <c r="O18" s="21">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -3178,13 +3189,13 @@
       <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="20" t="b">
+      <c r="G19" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="21">
         <v>1</v>
       </c>
       <c r="J19">
@@ -3196,13 +3207,13 @@
       <c r="L19" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="20">
-        <v>1</v>
-      </c>
-      <c r="N19" s="20">
-        <v>0</v>
-      </c>
-      <c r="O19" s="20">
+      <c r="M19" s="21">
+        <v>1</v>
+      </c>
+      <c r="N19" s="21">
+        <v>0</v>
+      </c>
+      <c r="O19" s="21">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -3234,13 +3245,13 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="20" t="b">
+      <c r="G20" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="21">
         <v>1</v>
       </c>
       <c r="J20">
@@ -3252,13 +3263,13 @@
       <c r="L20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="20">
-        <v>1</v>
-      </c>
-      <c r="N20" s="20">
-        <v>0</v>
-      </c>
-      <c r="O20" s="20">
+      <c r="M20" s="21">
+        <v>1</v>
+      </c>
+      <c r="N20" s="21">
+        <v>0</v>
+      </c>
+      <c r="O20" s="21">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -3290,13 +3301,13 @@
       <c r="F21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" s="20" t="b">
+      <c r="G21" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="21">
         <v>1</v>
       </c>
       <c r="J21">
@@ -3308,13 +3319,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="20">
-        <v>1</v>
-      </c>
-      <c r="N21" s="20">
-        <v>0</v>
-      </c>
-      <c r="O21" s="20">
+      <c r="M21" s="21">
+        <v>1</v>
+      </c>
+      <c r="N21" s="21">
+        <v>0</v>
+      </c>
+      <c r="O21" s="21">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -3346,13 +3357,13 @@
       <c r="F22" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="20" t="b">
+      <c r="G22" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="21">
         <v>1</v>
       </c>
       <c r="J22">
@@ -3364,13 +3375,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="20">
-        <v>1</v>
-      </c>
-      <c r="N22" s="20">
-        <v>0</v>
-      </c>
-      <c r="O22" s="20">
+      <c r="M22" s="21">
+        <v>1</v>
+      </c>
+      <c r="N22" s="21">
+        <v>0</v>
+      </c>
+      <c r="O22" s="21">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -3383,32 +3394,32 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" s="13" customFormat="1" spans="1:18">
-      <c r="A23" s="13">
+    <row r="23" s="14" customFormat="1" spans="1:18">
+      <c r="A23" s="14">
         <v>301</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="13" t="s">
+      <c r="G23" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="21">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3417,54 +3428,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="13" t="s">
+      <c r="L23" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="20">
-        <v>1</v>
-      </c>
-      <c r="N23" s="20">
-        <v>0</v>
-      </c>
-      <c r="O23" s="20">
-        <v>0</v>
-      </c>
-      <c r="P23" s="13" t="s">
+      <c r="M23" s="21">
+        <v>1</v>
+      </c>
+      <c r="N23" s="21">
+        <v>0</v>
+      </c>
+      <c r="O23" s="21">
+        <v>0</v>
+      </c>
+      <c r="P23" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="Q23" s="13">
+      <c r="Q23" s="14">
         <v>3</v>
       </c>
-      <c r="R23" s="13" t="s">
+      <c r="R23" s="14" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="24" s="13" customFormat="1" spans="1:18">
-      <c r="A24" s="13">
+    <row r="24" s="14" customFormat="1" spans="1:18">
+      <c r="A24" s="14">
         <v>302</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="13">
-        <v>1</v>
-      </c>
-      <c r="D24" s="13" t="s">
+      <c r="C24" s="14">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F24" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="G24" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="21">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -3473,51 +3484,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="13" t="s">
+      <c r="L24" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="20">
-        <v>1</v>
-      </c>
-      <c r="N24" s="20">
-        <v>0</v>
-      </c>
-      <c r="O24" s="20">
-        <v>0</v>
-      </c>
-      <c r="P24" s="13" t="s">
+      <c r="M24" s="21">
+        <v>1</v>
+      </c>
+      <c r="N24" s="21">
+        <v>0</v>
+      </c>
+      <c r="O24" s="21">
+        <v>0</v>
+      </c>
+      <c r="P24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="Q24" s="13">
+      <c r="Q24" s="14">
         <v>3</v>
       </c>
-      <c r="R24" s="13" t="s">
+      <c r="R24" s="14" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="25" s="13" customFormat="1" spans="1:18">
-      <c r="A25" s="13">
+    <row r="25" s="14" customFormat="1" spans="1:18">
+      <c r="A25" s="14">
         <v>303</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="13">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="G25" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="21">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3526,51 +3537,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="20">
-        <v>1</v>
-      </c>
-      <c r="N25" s="20">
-        <v>0</v>
-      </c>
-      <c r="O25" s="20">
-        <v>0</v>
-      </c>
-      <c r="P25" s="13" t="s">
+      <c r="M25" s="21">
+        <v>1</v>
+      </c>
+      <c r="N25" s="21">
+        <v>0</v>
+      </c>
+      <c r="O25" s="21">
+        <v>0</v>
+      </c>
+      <c r="P25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="Q25" s="13">
+      <c r="Q25" s="14">
         <v>3</v>
       </c>
-      <c r="R25" s="13" t="s">
+      <c r="R25" s="14" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" s="13" customFormat="1" spans="1:18">
-      <c r="A26" s="13">
+    <row r="26" s="14" customFormat="1" spans="1:18">
+      <c r="A26" s="14">
         <v>304</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="13">
-        <v>1</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="C26" s="14">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="13" t="s">
+      <c r="E26" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="13" t="s">
+      <c r="F26" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13" t="s">
+      <c r="G26" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="21">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -3579,54 +3590,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="13" t="s">
+      <c r="L26" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="20">
-        <v>1</v>
-      </c>
-      <c r="N26" s="20">
-        <v>0</v>
-      </c>
-      <c r="O26" s="20">
-        <v>0</v>
-      </c>
-      <c r="P26" s="13" t="s">
+      <c r="M26" s="21">
+        <v>1</v>
+      </c>
+      <c r="N26" s="21">
+        <v>0</v>
+      </c>
+      <c r="O26" s="21">
+        <v>0</v>
+      </c>
+      <c r="P26" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="Q26" s="13">
+      <c r="Q26" s="14">
         <v>3</v>
       </c>
-      <c r="R26" s="13" t="s">
+      <c r="R26" s="14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" s="13" customFormat="1" spans="1:18">
-      <c r="A27" s="13">
+    <row r="27" s="14" customFormat="1" spans="1:18">
+      <c r="A27" s="14">
         <v>305</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="13" t="s">
+      <c r="G27" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="21">
         <v>1</v>
       </c>
       <c r="J27">
@@ -3638,51 +3649,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="20">
-        <v>1</v>
-      </c>
-      <c r="N27" s="20">
-        <v>0</v>
-      </c>
-      <c r="O27" s="20">
-        <v>0</v>
-      </c>
-      <c r="P27" s="13" t="s">
+      <c r="M27" s="21">
+        <v>1</v>
+      </c>
+      <c r="N27" s="21">
+        <v>0</v>
+      </c>
+      <c r="O27" s="21">
+        <v>0</v>
+      </c>
+      <c r="P27" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="Q27" s="13">
+      <c r="Q27" s="14">
         <v>3</v>
       </c>
-      <c r="R27" s="13" t="s">
+      <c r="R27" s="14" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="28" s="13" customFormat="1" spans="1:18">
-      <c r="A28" s="13">
+    <row r="28" s="14" customFormat="1" spans="1:18">
+      <c r="A28" s="14">
         <v>306</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="13" t="s">
+      <c r="F28" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G28" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="13">
-        <v>0</v>
-      </c>
-      <c r="I28" s="20">
+      <c r="G28" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="21">
         <v>1</v>
       </c>
       <c r="J28">
@@ -3691,54 +3702,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="13">
-        <v>1</v>
-      </c>
-      <c r="M28" s="20">
-        <v>1</v>
-      </c>
-      <c r="N28" s="20">
-        <v>0</v>
-      </c>
-      <c r="O28" s="20">
-        <v>0</v>
-      </c>
-      <c r="P28" s="13" t="s">
+      <c r="L28" s="14">
+        <v>1</v>
+      </c>
+      <c r="M28" s="21">
+        <v>1</v>
+      </c>
+      <c r="N28" s="21">
+        <v>0</v>
+      </c>
+      <c r="O28" s="21">
+        <v>0</v>
+      </c>
+      <c r="P28" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Q28" s="13">
+      <c r="Q28" s="14">
         <v>3</v>
       </c>
-      <c r="R28" s="13" t="s">
+      <c r="R28" s="14" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="29" s="13" customFormat="1" spans="1:18">
-      <c r="A29" s="13">
+    <row r="29" s="14" customFormat="1" spans="1:18">
+      <c r="A29" s="14">
         <v>307</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="13">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13" t="s">
+      <c r="G29" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="21">
         <v>1</v>
       </c>
       <c r="J29">
@@ -3747,54 +3758,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="13" t="s">
+      <c r="L29" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="20">
+      <c r="M29" s="21">
         <v>0.1</v>
       </c>
-      <c r="N29" s="20">
-        <v>0</v>
-      </c>
-      <c r="O29" s="20">
+      <c r="N29" s="21">
+        <v>0</v>
+      </c>
+      <c r="O29" s="21">
         <v>0.17</v>
       </c>
-      <c r="P29" s="13" t="s">
+      <c r="P29" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="Q29" s="13">
+      <c r="Q29" s="14">
         <v>3</v>
       </c>
-      <c r="R29" s="13" t="s">
+      <c r="R29" s="14" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" s="13" customFormat="1" spans="1:18">
-      <c r="A30" s="13">
+    <row r="30" s="14" customFormat="1" spans="1:18">
+      <c r="A30" s="14">
         <v>308</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="13">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="13" t="s">
+      <c r="E30" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="G30" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="13" t="s">
+      <c r="G30" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="21">
         <v>1</v>
       </c>
       <c r="J30">
@@ -3803,54 +3814,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="L30" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="M30" s="20">
-        <v>1</v>
-      </c>
-      <c r="N30" s="20">
-        <v>0</v>
-      </c>
-      <c r="O30" s="20">
-        <v>0</v>
-      </c>
-      <c r="P30" s="13" t="s">
+      <c r="M30" s="21">
+        <v>1</v>
+      </c>
+      <c r="N30" s="21">
+        <v>0</v>
+      </c>
+      <c r="O30" s="21">
+        <v>0</v>
+      </c>
+      <c r="P30" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="Q30" s="13">
+      <c r="Q30" s="14">
         <v>3</v>
       </c>
-      <c r="R30" s="13" t="s">
+      <c r="R30" s="14" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="31" s="13" customFormat="1" spans="1:18">
-      <c r="A31" s="13">
+    <row r="31" s="14" customFormat="1" spans="1:18">
+      <c r="A31" s="14">
         <v>309</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="14">
         <v>2</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="13" t="s">
+      <c r="G31" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="21">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3859,54 +3870,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="13" t="s">
+      <c r="L31" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="M31" s="20">
-        <v>1</v>
-      </c>
-      <c r="N31" s="20">
-        <v>0</v>
-      </c>
-      <c r="O31" s="20">
-        <v>0</v>
-      </c>
-      <c r="P31" s="13" t="s">
+      <c r="M31" s="21">
+        <v>1</v>
+      </c>
+      <c r="N31" s="21">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21">
+        <v>0</v>
+      </c>
+      <c r="P31" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Q31" s="13">
+      <c r="Q31" s="14">
         <v>3</v>
       </c>
-      <c r="R31" s="13" t="s">
+      <c r="R31" s="14" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" s="13" customFormat="1" spans="1:18">
-      <c r="A32" s="13">
+    <row r="32" s="14" customFormat="1" spans="1:18">
+      <c r="A32" s="14">
         <v>310</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="14">
         <v>2</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G32" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="13" t="s">
+      <c r="G32" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="21">
         <v>1</v>
       </c>
       <c r="J32">
@@ -3915,54 +3926,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="13" t="s">
+      <c r="L32" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="20">
-        <v>1</v>
-      </c>
-      <c r="N32" s="20">
-        <v>0</v>
-      </c>
-      <c r="O32" s="20">
-        <v>0</v>
-      </c>
-      <c r="P32" s="13" t="s">
+      <c r="M32" s="21">
+        <v>1</v>
+      </c>
+      <c r="N32" s="21">
+        <v>0</v>
+      </c>
+      <c r="O32" s="21">
+        <v>0</v>
+      </c>
+      <c r="P32" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Q32" s="13">
+      <c r="Q32" s="14">
         <v>4</v>
       </c>
-      <c r="R32" s="13" t="s">
+      <c r="R32" s="14" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="33" s="13" customFormat="1" spans="1:18">
-      <c r="A33" s="13">
+    <row r="33" s="14" customFormat="1" spans="1:18">
+      <c r="A33" s="14">
         <v>311</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="14">
         <v>2</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="13">
-        <v>0</v>
-      </c>
-      <c r="I33" s="20">
+      <c r="G33" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="21">
         <v>1</v>
       </c>
       <c r="J33">
@@ -3971,45 +3982,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="13">
-        <v>1</v>
-      </c>
-      <c r="M33" s="20">
-        <v>1</v>
-      </c>
-      <c r="N33" s="20">
-        <v>0</v>
-      </c>
-      <c r="O33" s="20">
-        <v>0</v>
-      </c>
-      <c r="P33" s="13" t="s">
+      <c r="L33" s="14">
+        <v>1</v>
+      </c>
+      <c r="M33" s="21">
+        <v>1</v>
+      </c>
+      <c r="N33" s="21">
+        <v>0</v>
+      </c>
+      <c r="O33" s="21">
+        <v>0</v>
+      </c>
+      <c r="P33" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="13">
+      <c r="Q33" s="14">
         <v>3</v>
       </c>
-      <c r="R33" s="13" t="s">
+      <c r="R33" s="14" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="34" s="13" customFormat="1" spans="1:18">
-      <c r="A34" s="13">
+    <row r="34" s="14" customFormat="1" spans="1:18">
+      <c r="A34" s="14">
         <v>312</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <v>2</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="20">
+      <c r="G34" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="21">
         <v>1</v>
       </c>
       <c r="J34">
@@ -4018,45 +4029,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="20">
-        <v>1</v>
-      </c>
-      <c r="N34" s="20">
-        <v>0</v>
-      </c>
-      <c r="O34" s="20">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="13">
-        <v>1</v>
-      </c>
-      <c r="R34" s="13" t="s">
+      <c r="M34" s="21">
+        <v>1</v>
+      </c>
+      <c r="N34" s="21">
+        <v>0</v>
+      </c>
+      <c r="O34" s="21">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="14">
+        <v>1</v>
+      </c>
+      <c r="R34" s="14" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" s="11" customFormat="1" spans="1:17">
-      <c r="A35" s="11">
+    <row r="35" s="12" customFormat="1" spans="1:17">
+      <c r="A35" s="12">
         <v>401</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="12">
         <v>2</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="F35" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="11" t="s">
+      <c r="G35" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="21">
         <v>1</v>
       </c>
       <c r="J35">
@@ -4068,45 +4079,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="20">
-        <v>1</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="20">
-        <v>0</v>
-      </c>
-      <c r="P35" s="11" t="s">
+      <c r="M35" s="21">
+        <v>1</v>
+      </c>
+      <c r="N35" s="21">
+        <v>0</v>
+      </c>
+      <c r="O35" s="21">
+        <v>0</v>
+      </c>
+      <c r="P35" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="11">
+      <c r="Q35" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="11" customFormat="1" spans="1:17">
-      <c r="A36" s="11">
+    <row r="36" s="12" customFormat="1" spans="1:17">
+      <c r="A36" s="12">
         <v>402</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="11">
+      <c r="C36" s="12">
         <v>2</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="27" t="s">
+      <c r="F36" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="11" t="s">
+      <c r="G36" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="20">
+      <c r="I36" s="21">
         <v>1</v>
       </c>
       <c r="J36">
@@ -4118,48 +4129,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="20">
-        <v>1</v>
-      </c>
-      <c r="N36" s="20">
-        <v>0</v>
-      </c>
-      <c r="O36" s="20">
-        <v>0</v>
-      </c>
-      <c r="P36" s="11" t="s">
+      <c r="M36" s="21">
+        <v>1</v>
+      </c>
+      <c r="N36" s="21">
+        <v>0</v>
+      </c>
+      <c r="O36" s="21">
+        <v>0</v>
+      </c>
+      <c r="P36" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="11">
+      <c r="Q36" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="11" customFormat="1" spans="1:17">
-      <c r="A37" s="11">
+    <row r="37" s="12" customFormat="1" spans="1:17">
+      <c r="A37" s="12">
         <v>403</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="12">
         <v>2</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="11" t="s">
+      <c r="G37" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="20">
+      <c r="I37" s="21">
         <v>1</v>
       </c>
       <c r="J37">
@@ -4168,83 +4179,83 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="20">
-        <v>1</v>
-      </c>
-      <c r="N37" s="20">
-        <v>0</v>
-      </c>
-      <c r="O37" s="20">
-        <v>0</v>
-      </c>
-      <c r="P37" s="11" t="s">
+      <c r="M37" s="21">
+        <v>1</v>
+      </c>
+      <c r="N37" s="21">
+        <v>0</v>
+      </c>
+      <c r="O37" s="21">
+        <v>0</v>
+      </c>
+      <c r="P37" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="11">
+      <c r="Q37" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="22" customFormat="1" spans="1:17">
-      <c r="A38" s="22">
+    <row r="38" s="23" customFormat="1" spans="1:17">
+      <c r="A38" s="23">
         <v>404</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="22">
-        <v>1</v>
-      </c>
-      <c r="D38" s="12" t="s">
+      <c r="C38" s="23">
+        <v>1</v>
+      </c>
+      <c r="D38" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E38" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="22" t="s">
+      <c r="G38" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="22">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12">
-        <v>0</v>
-      </c>
-      <c r="K38" s="12">
+      <c r="I38" s="23">
+        <v>1</v>
+      </c>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="13">
         <v>2</v>
       </c>
-      <c r="L38" s="22" t="s">
+      <c r="L38" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="22">
-        <v>1</v>
-      </c>
-      <c r="N38" s="22">
-        <v>0</v>
-      </c>
-      <c r="O38" s="22">
-        <v>0</v>
-      </c>
-      <c r="P38" s="22" t="s">
+      <c r="M38" s="23">
+        <v>1</v>
+      </c>
+      <c r="N38" s="23">
+        <v>0</v>
+      </c>
+      <c r="O38" s="23">
+        <v>0</v>
+      </c>
+      <c r="P38" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="22">
+      <c r="Q38" s="23">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="11" customFormat="1" spans="1:21">
-      <c r="A39" s="11">
+    <row r="39" s="12" customFormat="1" spans="1:21">
+      <c r="A39" s="12">
         <v>405</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="27" t="s">
         <v>180</v>
       </c>
       <c r="C39">
@@ -4259,13 +4270,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="20" t="b">
+      <c r="G39" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="20">
+      <c r="I39" s="21">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4277,13 +4288,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="20">
-        <v>1</v>
-      </c>
-      <c r="N39" s="20">
-        <v>0</v>
-      </c>
-      <c r="O39" s="20">
+      <c r="M39" s="21">
+        <v>1</v>
+      </c>
+      <c r="N39" s="21">
+        <v>0</v>
+      </c>
+      <c r="O39" s="21">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -4299,32 +4310,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="11" customFormat="1" spans="1:17">
-      <c r="A40" s="11">
+    <row r="40" s="12" customFormat="1" spans="1:17">
+      <c r="A40" s="12">
         <v>406</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="27" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="11">
-        <v>1</v>
-      </c>
-      <c r="D40" s="11" t="s">
+      <c r="C40" s="12">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="12" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="11">
-        <v>0</v>
-      </c>
-      <c r="I40" s="20">
+      <c r="G40" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12">
+        <v>0</v>
+      </c>
+      <c r="I40" s="21">
         <v>1</v>
       </c>
       <c r="J40">
@@ -4333,27 +4344,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="11">
+      <c r="L40" s="12">
         <v>3</v>
       </c>
-      <c r="M40" s="20">
-        <v>1</v>
-      </c>
-      <c r="N40" s="20">
-        <v>0</v>
-      </c>
-      <c r="O40" s="20">
-        <v>0</v>
-      </c>
-      <c r="P40" s="11" t="s">
+      <c r="M40" s="21">
+        <v>1</v>
+      </c>
+      <c r="N40" s="21">
+        <v>0</v>
+      </c>
+      <c r="O40" s="21">
+        <v>0</v>
+      </c>
+      <c r="P40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="11">
+      <c r="Q40" s="12">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="11">
+      <c r="A41" s="12">
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4371,13 +4382,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="20" t="b">
+      <c r="G41" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="21">
         <v>1</v>
       </c>
       <c r="J41">
@@ -4389,13 +4400,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="20">
-        <v>1</v>
-      </c>
-      <c r="N41" s="20">
-        <v>0</v>
-      </c>
-      <c r="O41" s="20">
+      <c r="M41" s="21">
+        <v>1</v>
+      </c>
+      <c r="N41" s="21">
+        <v>0</v>
+      </c>
+      <c r="O41" s="21">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -4409,7 +4420,7 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="11">
+      <c r="A42" s="12">
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -4427,13 +4438,13 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="20" t="b">
+      <c r="G42" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="20">
+      <c r="I42" s="21">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4445,13 +4456,13 @@
       <c r="L42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="20">
-        <v>1</v>
-      </c>
-      <c r="N42" s="20">
-        <v>0</v>
-      </c>
-      <c r="O42" s="20">
+      <c r="M42" s="21">
+        <v>1</v>
+      </c>
+      <c r="N42" s="21">
+        <v>0</v>
+      </c>
+      <c r="O42" s="21">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -4465,7 +4476,7 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="11">
+      <c r="A43" s="12">
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -4483,13 +4494,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="20" t="b">
+      <c r="G43" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="20">
+      <c r="I43" s="21">
         <v>1</v>
       </c>
       <c r="J43">
@@ -4501,13 +4512,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="20">
-        <v>1</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
-      <c r="O43" s="20">
+      <c r="M43" s="21">
+        <v>1</v>
+      </c>
+      <c r="N43" s="21">
+        <v>0</v>
+      </c>
+      <c r="O43" s="21">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -4521,7 +4532,7 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="11">
+      <c r="A44" s="12">
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4539,13 +4550,13 @@
       <c r="F44" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="20" t="b">
+      <c r="G44" s="21" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="20">
+      <c r="I44" s="21">
         <v>1</v>
       </c>
       <c r="J44">
@@ -4557,13 +4568,13 @@
       <c r="L44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" s="20">
-        <v>1</v>
-      </c>
-      <c r="N44" s="20">
-        <v>0</v>
-      </c>
-      <c r="O44" s="20">
+      <c r="M44" s="21">
+        <v>1</v>
+      </c>
+      <c r="N44" s="21">
+        <v>0</v>
+      </c>
+      <c r="O44" s="21">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -4586,7 +4597,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="21.375" customWidth="1"/>
@@ -4813,84 +4824,103 @@
         <v>319</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" ht="14.25" spans="1:7">
       <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2">
         <v>101</v>
       </c>
-      <c r="B13" t="s">
-        <v>320</v>
-      </c>
-      <c r="C13" t="s">
-        <v>321</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B14" t="s">
         <v>322</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="C14" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:7">
-      <c r="A14" s="2">
+      <c r="D14" t="s">
+        <v>324</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:7">
+      <c r="A15" s="2">
         <v>102</v>
       </c>
-      <c r="B14" t="s">
-        <v>324</v>
-      </c>
-      <c r="C14" t="s">
-        <v>325</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="B15" t="s">
         <v>326</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="C15" t="s">
         <v>327</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="D15" t="s">
         <v>328</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="E15" s="4" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="2">
+      <c r="F15" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2">
         <v>201</v>
-      </c>
-      <c r="B15" t="s">
-        <v>330</v>
-      </c>
-      <c r="C15" t="s">
-        <v>295</v>
-      </c>
-      <c r="D15" t="s">
-        <v>296</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:7">
-      <c r="A16" s="2">
-        <v>202</v>
       </c>
       <c r="B16" t="s">
         <v>332</v>
       </c>
       <c r="C16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D16" t="s">
+        <v>296</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:7">
+      <c r="A17" s="2">
+        <v>202</v>
+      </c>
+      <c r="B17" t="s">
         <v>333</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C17" t="s">
         <v>334</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="D17" t="s">
         <v>335</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="F17" s="6" t="s">
         <v>337</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -4900,13 +4930,14 @@
     <hyperlink ref="E5" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E4" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E12" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="E14" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
-    <hyperlink ref="G14" r:id="rId5" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
+    <hyperlink ref="E15" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="G15" r:id="rId5" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
     <hyperlink ref="G12" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
-    <hyperlink ref="E16" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="G16" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
-    <hyperlink ref="E13" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E15" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E17" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="G17" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
+    <hyperlink ref="E14" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E16" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E13" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4933,7 +4964,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4941,7 +4972,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -4985,16 +5016,16 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>4</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="14">
         <v>20</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="14">
         <v>1</v>
       </c>
       <c r="E2" s="2">
@@ -5352,284 +5383,284 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="16" customFormat="1" spans="1:7">
-      <c r="A18" s="16">
+    <row r="18" s="17" customFormat="1" spans="1:7">
+      <c r="A18" s="17">
         <v>301</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
         <v>50</v>
       </c>
-      <c r="D18" s="16">
-        <v>0</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="D18" s="17">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17">
         <v>400</v>
       </c>
-      <c r="F18" s="16">
-        <v>0</v>
-      </c>
-      <c r="G18" s="18">
+      <c r="F18" s="17">
+        <v>0</v>
+      </c>
+      <c r="G18" s="19">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="16" customFormat="1" spans="1:7">
-      <c r="A19" s="16">
+    <row r="19" s="17" customFormat="1" spans="1:7">
+      <c r="A19" s="17">
         <v>302</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <v>25</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <v>9</v>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="17">
         <v>100</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="17">
         <v>303</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="16" customFormat="1" spans="1:7">
-      <c r="A20" s="16">
+    <row r="20" s="17" customFormat="1" spans="1:7">
+      <c r="A20" s="17">
         <v>303</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <v>20</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <v>3</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="17">
         <v>50</v>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="17">
         <v>301</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="19">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="16" customFormat="1" spans="1:7">
-      <c r="A21" s="16">
+    <row r="21" s="17" customFormat="1" spans="1:7">
+      <c r="A21" s="17">
         <v>304</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <v>30</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <v>11</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="17">
         <v>300</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="17">
         <v>301</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="16" customFormat="1" spans="1:7">
-      <c r="A22" s="16">
+    <row r="22" s="17" customFormat="1" spans="1:7">
+      <c r="A22" s="17">
         <v>305</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <v>25</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <v>8</v>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="17">
         <v>100</v>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="17">
         <v>303</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="16" customFormat="1" spans="1:7">
-      <c r="A23" s="16">
+    <row r="23" s="17" customFormat="1" spans="1:7">
+      <c r="A23" s="17">
         <v>306</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <v>35</v>
       </c>
-      <c r="D23" s="16">
-        <v>0</v>
-      </c>
-      <c r="E23" s="16">
+      <c r="D23" s="17">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17">
         <v>200</v>
       </c>
-      <c r="F23" s="16">
-        <v>0</v>
-      </c>
-      <c r="G23" s="18">
+      <c r="F23" s="17">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="16" customFormat="1" spans="1:7">
-      <c r="A24" s="16">
+    <row r="24" s="17" customFormat="1" spans="1:7">
+      <c r="A24" s="17">
         <v>307</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <v>35</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>12</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>150</v>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <v>302</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="16" customFormat="1" spans="1:7">
-      <c r="A25" s="16">
+    <row r="25" s="17" customFormat="1" spans="1:7">
+      <c r="A25" s="17">
         <v>308</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="17">
         <v>35</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <v>12</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="17">
         <v>150</v>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="17">
         <v>302</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="19">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="16" customFormat="1" spans="1:7">
-      <c r="A26" s="16">
+    <row r="26" s="17" customFormat="1" spans="1:7">
+      <c r="A26" s="17">
         <v>309</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="17">
         <v>20</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>10</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="17">
         <v>80</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="17">
         <v>306</v>
       </c>
-      <c r="G26" s="18">
+      <c r="G26" s="19">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="16" customFormat="1" spans="1:7">
-      <c r="A27" s="16">
+    <row r="27" s="17" customFormat="1" spans="1:7">
+      <c r="A27" s="17">
         <v>310</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="17">
         <v>30</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="17">
         <v>10</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="17">
         <v>120</v>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="17">
         <v>309</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="16" customFormat="1" spans="1:7">
-      <c r="A28" s="16">
+    <row r="28" s="17" customFormat="1" spans="1:7">
+      <c r="A28" s="17">
         <v>311</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <v>30</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <v>10</v>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="17">
         <v>120</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="17">
         <v>309</v>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="19">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="16" customFormat="1" spans="1:7">
-      <c r="A29" s="16">
+    <row r="29" s="17" customFormat="1" spans="1:7">
+      <c r="A29" s="17">
         <v>312</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="17">
         <v>15</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="17">
         <v>2</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="17">
         <v>15</v>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="17">
         <v>306</v>
       </c>
-      <c r="G29" s="18">
+      <c r="G29" s="19">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="16" customFormat="1" spans="2:2">
-      <c r="B30" s="17"/>
+    <row r="30" s="17" customFormat="1" spans="2:2">
+      <c r="B30" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5672,10 +5703,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>20</v>
       </c>
       <c r="C2">
@@ -5692,10 +5723,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>4</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>22</v>
       </c>
       <c r="C3">
@@ -5881,10 +5912,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>309</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>161</v>
       </c>
       <c r="C12">
@@ -5901,10 +5932,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>310</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>165</v>
       </c>
       <c r="C13">
@@ -5921,10 +5952,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>311</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>169</v>
       </c>
       <c r="C14">
@@ -5944,10 +5975,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>312</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>172</v>
       </c>
       <c r="C15">
@@ -5964,8 +5995,8 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="14"/>
+      <c r="B16" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5986,29 +6017,29 @@
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:8">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" s="10" customFormat="1" spans="1:8">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6038,29 +6069,29 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="1" spans="1:8">
-      <c r="A3" s="12">
+    <row r="3" s="13" customFormat="1" spans="1:8">
+      <c r="A3" s="13">
         <v>202</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E3" s="12">
-        <v>0</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="E3" s="13">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
         <v>0.8</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="13" t="s">
         <v>208</v>
       </c>
     </row>
@@ -6450,34 +6481,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="12" customFormat="1" spans="1:8">
-      <c r="A20" s="15">
+    <row r="20" s="13" customFormat="1" spans="1:8">
+      <c r="A20" s="16">
         <v>404</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E20" s="12">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12">
+      <c r="E20" s="13">
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
         <v>0.8</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="13" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -6503,7 +6534,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -6529,7 +6560,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="11">
+      <c r="A23" s="12">
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -6555,7 +6586,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="11">
+      <c r="A24" s="12">
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -6581,7 +6612,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="11">
+      <c r="A25" s="12">
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -6607,7 +6638,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="11">
+      <c r="A26" s="12">
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -6673,68 +6704,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" spans="1:21">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" s="13" customFormat="1" spans="1:21">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="P1" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="Q1" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="R1" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="S1" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="T1" s="12" t="s">
+      <c r="T1" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="13" t="s">
         <v>250</v>
       </c>
     </row>
@@ -7606,10 +7637,10 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>301</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="15" t="s">
         <v>120</v>
       </c>
       <c r="C17">
@@ -7665,10 +7696,10 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>302</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>126</v>
       </c>
       <c r="C18">
@@ -7724,10 +7755,10 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>303</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="15" t="s">
         <v>133</v>
       </c>
       <c r="C19">
@@ -7783,10 +7814,10 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>304</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>135</v>
       </c>
       <c r="C20">
@@ -7904,10 +7935,10 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>306</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="15" t="s">
         <v>145</v>
       </c>
       <c r="C22">
@@ -7963,10 +7994,10 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>307</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>151</v>
       </c>
       <c r="C23">
@@ -8022,10 +8053,10 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>308</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="15" t="s">
         <v>156</v>
       </c>
       <c r="C24">
@@ -8081,10 +8112,10 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>309</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="15" t="s">
         <v>161</v>
       </c>
       <c r="C25">
@@ -8140,10 +8171,10 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>310</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="15" t="s">
         <v>165</v>
       </c>
       <c r="C26">
@@ -8199,10 +8230,10 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="13">
+      <c r="A27" s="14">
         <v>311</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="15" t="s">
         <v>169</v>
       </c>
       <c r="C27">
@@ -8258,10 +8289,10 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="13">
+      <c r="A28" s="14">
         <v>312</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="15" t="s">
         <v>172</v>
       </c>
       <c r="C28">
@@ -8491,7 +8522,7 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -8553,7 +8584,7 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -8609,7 +8640,7 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -8665,7 +8696,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="11">
+      <c r="A35" s="12">
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8721,7 +8752,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="11">
+      <c r="A36" s="12">
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -8780,7 +8811,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="11">
+      <c r="A37" s="12">
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -8839,7 +8870,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="11">
+      <c r="A38" s="12">
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -8989,7 +9020,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -9000,7 +9031,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -9011,7 +9042,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -9022,7 +9053,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -9033,7 +9064,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -9044,7 +9075,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="11">
+      <c r="A14" s="12">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -9055,7 +9086,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -9080,29 +9111,29 @@
     <col min="7" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="9" customFormat="1" spans="1:8">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" s="10" customFormat="1" spans="1:8">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>188</v>
       </c>
     </row>
@@ -9336,10 +9367,10 @@
       <c r="B1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>188</v>
       </c>
     </row>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="343">
   <si>
     <t>类型</t>
   </si>
@@ -595,6 +595,9 @@
   </si>
   <si>
     <t>房虫怪</t>
+  </si>
+  <si>
+    <t>防空兵怪</t>
   </si>
   <si>
     <t>备注</t>
@@ -1065,6 +1068,9 @@
   </si>
   <si>
     <t>https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3</t>
+  </si>
+  <si>
+    <t>新手训练_反防空战_虫</t>
   </si>
   <si>
     <t>四方对战</t>
@@ -2265,7 +2271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -4587,6 +4593,62 @@
         <v>103</v>
       </c>
     </row>
+    <row r="45" customFormat="1" spans="1:18">
+      <c r="A45" s="12">
+        <v>411</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="s">
+        <v>117</v>
+      </c>
+      <c r="E45" t="s">
+        <v>41</v>
+      </c>
+      <c r="F45" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H45" t="s">
+        <v>29</v>
+      </c>
+      <c r="I45" s="21">
+        <v>1</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1.33</v>
+      </c>
+      <c r="L45" t="s">
+        <v>43</v>
+      </c>
+      <c r="M45" s="21">
+        <v>1</v>
+      </c>
+      <c r="N45" s="21">
+        <v>0</v>
+      </c>
+      <c r="O45" s="21">
+        <v>0</v>
+      </c>
+      <c r="P45" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q45">
+        <v>3</v>
+      </c>
+      <c r="R45" t="s">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -4597,7 +4659,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="21.375" customWidth="1"/>
@@ -4613,22 +4675,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:5">
@@ -4636,16 +4698,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:5">
@@ -4653,16 +4715,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" t="s">
+        <v>296</v>
+      </c>
+      <c r="D3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="C3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4670,16 +4732,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4687,16 +4749,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="C5" t="s">
-        <v>300</v>
-      </c>
-      <c r="D5" t="s">
-        <v>301</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4704,16 +4766,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4721,16 +4783,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E7" t="s">
         <v>306</v>
-      </c>
-      <c r="C7" t="s">
-        <v>295</v>
-      </c>
-      <c r="D7" t="s">
-        <v>296</v>
-      </c>
-      <c r="E7" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4738,16 +4800,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4755,16 +4817,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E9" t="s">
         <v>311</v>
-      </c>
-      <c r="C9" t="s">
-        <v>308</v>
-      </c>
-      <c r="D9" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4772,16 +4834,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4789,16 +4851,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:7">
@@ -4806,22 +4868,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:7">
@@ -4829,98 +4891,117 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C13" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2">
         <v>101</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
+        <v>324</v>
+      </c>
+      <c r="C15" t="s">
+        <v>325</v>
+      </c>
+      <c r="D15" t="s">
+        <v>326</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:7">
+      <c r="A16" s="2">
+        <v>102</v>
+      </c>
+      <c r="B16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C16" t="s">
+        <v>329</v>
+      </c>
+      <c r="D16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2">
+        <v>201</v>
+      </c>
+      <c r="B17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C17" t="s">
+        <v>296</v>
+      </c>
+      <c r="D17" t="s">
+        <v>297</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="C14" t="s">
-        <v>323</v>
-      </c>
-      <c r="D14" t="s">
-        <v>324</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:7">
-      <c r="A15" s="2">
-        <v>102</v>
-      </c>
-      <c r="B15" t="s">
-        <v>326</v>
-      </c>
-      <c r="C15" t="s">
-        <v>327</v>
-      </c>
-      <c r="D15" t="s">
-        <v>328</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="2">
-        <v>201</v>
-      </c>
-      <c r="B16" t="s">
-        <v>332</v>
-      </c>
-      <c r="C16" t="s">
-        <v>295</v>
-      </c>
-      <c r="D16" t="s">
-        <v>296</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:7">
-      <c r="A17" s="2">
+    </row>
+    <row r="18" ht="14.25" spans="1:7">
+      <c r="A18" s="2">
         <v>202</v>
       </c>
-      <c r="B17" t="s">
-        <v>333</v>
-      </c>
-      <c r="C17" t="s">
-        <v>334</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B18" t="s">
         <v>335</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="C18" t="s">
         <v>336</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="D18" t="s">
         <v>337</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>338</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -4930,14 +5011,15 @@
     <hyperlink ref="E5" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E4" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E12" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="E15" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
-    <hyperlink ref="G15" r:id="rId5" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
+    <hyperlink ref="E16" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="G16" r:id="rId5" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
     <hyperlink ref="G12" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
-    <hyperlink ref="E17" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="G17" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
-    <hyperlink ref="E14" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E16" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E18" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="G18" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
+    <hyperlink ref="E15" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E17" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
     <hyperlink ref="E13" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E14" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -4952,10 +5034,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1"/>
     </row>
@@ -4964,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4972,7 +5054,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -4997,22 +5079,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
@@ -5684,22 +5766,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5776,7 +5858,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -6008,7 +6090,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9" style="1"/>
@@ -6022,25 +6104,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -6051,7 +6133,7 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -6066,7 +6148,7 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" s="13" customFormat="1" spans="1:8">
@@ -6077,10 +6159,10 @@
         <v>39</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E3" s="13">
         <v>0</v>
@@ -6092,7 +6174,7 @@
         <v>41</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -6103,7 +6185,7 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -6118,7 +6200,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -6129,10 +6211,10 @@
         <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6144,7 +6226,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6155,10 +6237,10 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6167,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -6196,7 +6278,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6207,10 +6289,10 @@
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6219,10 +6301,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6233,10 +6315,10 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6245,10 +6327,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6262,7 +6344,7 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6285,10 +6367,10 @@
         <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6297,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:6">
@@ -6325,7 +6407,7 @@
         <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D13" t="s">
         <v>100</v>
@@ -6337,10 +6419,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -6351,7 +6433,7 @@
         <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
         <v>100</v>
@@ -6363,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -6377,7 +6459,7 @@
         <v>110</v>
       </c>
       <c r="C15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -6389,10 +6471,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -6403,10 +6485,10 @@
         <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6418,7 +6500,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -6429,10 +6511,10 @@
         <v>175</v>
       </c>
       <c r="C17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6449,10 +6531,10 @@
         <v>176</v>
       </c>
       <c r="C18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D18" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6469,10 +6551,10 @@
         <v>177</v>
       </c>
       <c r="C19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6489,10 +6571,10 @@
         <v>179</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E20" s="13">
         <v>0</v>
@@ -6504,7 +6586,7 @@
         <v>41</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -6515,7 +6597,7 @@
         <v>180</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -6530,7 +6612,7 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -6541,7 +6623,7 @@
         <v>181</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6556,7 +6638,7 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -6570,7 +6652,7 @@
         <v>84</v>
       </c>
       <c r="D23" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6593,7 +6675,7 @@
         <v>183</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D24" t="s">
         <v>100</v>
@@ -6605,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="G24" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H24" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -6619,10 +6701,10 @@
         <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6631,10 +6713,10 @@
         <v>0</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H25" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -6645,7 +6727,7 @@
         <v>185</v>
       </c>
       <c r="C26" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D26" t="s">
         <v>100</v>
@@ -6657,10 +6739,36 @@
         <v>0</v>
       </c>
       <c r="G26" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H26" t="s">
-        <v>225</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" spans="1:8">
+      <c r="A27" s="12">
+        <v>411</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" t="s">
+        <v>207</v>
+      </c>
+      <c r="D27" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0.8</v>
+      </c>
+      <c r="G27" t="s">
+        <v>41</v>
+      </c>
+      <c r="H27" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -6673,7 +6781,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U38"/>
+  <dimension ref="A1:U39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
@@ -6709,64 +6817,64 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N1" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P1" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="R1" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="S1" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="T1" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U1" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -6810,7 +6918,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -6851,7 +6959,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -6863,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -6872,7 +6980,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -6928,7 +7036,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -6972,7 +7080,7 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -6984,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -7031,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7046,7 +7154,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7099,7 +7207,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7108,7 +7216,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7149,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7161,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7170,7 +7278,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7211,7 +7319,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7226,7 +7334,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7267,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7282,7 +7390,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7326,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7341,7 +7449,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -7394,7 +7502,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -7494,7 +7602,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -7503,7 +7611,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -7559,7 +7667,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -7600,7 +7708,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -7612,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -7621,7 +7729,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -7910,7 +8018,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -7919,7 +8027,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8373,7 +8481,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8385,7 +8493,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -8394,7 +8502,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -8435,7 +8543,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -8450,7 +8558,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -8491,7 +8599,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -8506,7 +8614,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -8547,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -8559,7 +8667,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -8568,7 +8676,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -8624,7 +8732,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -8680,7 +8788,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -8721,7 +8829,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -8736,7 +8844,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -8786,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -8795,7 +8903,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -8839,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -8854,7 +8962,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -8917,6 +9025,68 @@
       </c>
       <c r="U38" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="39" customFormat="1" spans="1:21">
+      <c r="A39" s="12">
+        <v>411</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>18</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0.4</v>
+      </c>
+      <c r="I39">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>253</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>254</v>
+      </c>
+      <c r="O39">
+        <v>2.5</v>
+      </c>
+      <c r="P39">
+        <v>530</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>258</v>
+      </c>
+      <c r="R39">
+        <v>100</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="b">
+        <v>1</v>
+      </c>
+      <c r="U39" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8928,7 +9098,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8936,10 +9106,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -8991,7 +9161,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -9002,7 +9172,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -9094,6 +9264,17 @@
       </c>
       <c r="C15">
         <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="12">
+        <v>411</v>
+      </c>
+      <c r="B16" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -9116,25 +9297,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -9145,7 +9326,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9171,7 +9352,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9197,7 +9378,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9223,7 +9404,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9249,7 +9430,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9275,7 +9456,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9301,7 +9482,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -9327,7 +9508,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -9365,13 +9546,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -9419,19 +9600,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -9439,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -9456,7 +9637,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -9473,7 +9654,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -9490,7 +9671,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -9507,7 +9688,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -9524,7 +9705,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -9541,7 +9722,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Buff" sheetId="10" r:id="rId9"/>
     <sheet name="战局" sheetId="11" r:id="rId10"/>
     <sheet name="服务器区" sheetId="12" r:id="rId11"/>
+    <sheet name="音乐" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="369">
   <si>
     <t>类型</t>
   </si>
@@ -1181,6 +1182,84 @@
   <si>
     <t>正式服，腾讯云北京</t>
   </si>
+  <si>
+    <t>编号</t>
+  </si>
+  <si>
+    <t>作者</t>
+  </si>
+  <si>
+    <t>版权</t>
+  </si>
+  <si>
+    <t>世界又恢复了和平</t>
+  </si>
+  <si>
+    <t>Suno AI、提示词作者</t>
+  </si>
+  <si>
+    <t>版权归Suno和提示词作者共有，使用权开放给所有人。</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3</t>
+  </si>
+  <si>
+    <t>世界又恢复了和平2</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3</t>
+  </si>
+  <si>
+    <t>战线崩溃</t>
+  </si>
+  <si>
+    <t>闪击战</t>
+  </si>
+  <si>
+    <t>后勤运营</t>
+  </si>
+  <si>
+    <t>重工业浪漫</t>
+  </si>
+  <si>
+    <t>定居</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/定居低音质.mp3</t>
+  </si>
+  <si>
+    <t>漂泊</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/漂泊低音质.mp3</t>
+  </si>
+  <si>
+    <t>Sample Killer</t>
+  </si>
+  <si>
+    <t>乌鸦Producer(QQ 2998975740)</t>
+  </si>
+  <si>
+    <t>版权归作者所有，通知作者后可共享商用（强制署名）。</t>
+  </si>
+  <si>
+    <t>Follow The Light</t>
+  </si>
+  <si>
+    <t>Desert</t>
+  </si>
+  <si>
+    <t>星联</t>
+  </si>
+  <si>
+    <t>EinhornN7獬羽柏(QQ 2990490699)</t>
+  </si>
+  <si>
+    <t>Space Fight</t>
+  </si>
+  <si>
+    <t>电波暴击(QQ 1106551898)</t>
+  </si>
 </sst>
 </file>
 
@@ -1192,7 +1271,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1211,7 +1290,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1219,20 +1298,26 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FFE394DC"/>
-      <name val="Consolas"/>
+      <sz val="12"/>
+      <color rgb="FF40485B"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1742,16 +1827,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1760,119 +1842,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1882,28 +1967,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1912,7 +2000,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
@@ -1921,7 +2009,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -1933,15 +2021,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1951,13 +2030,22 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2285,32 +2373,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="20" customFormat="1" spans="1:18">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="20" t="s">
+    <row r="1" s="21" customFormat="1" spans="1:18">
+      <c r="A1" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="21" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2319,42 +2407,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="21" customFormat="1" spans="1:17">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="24" t="s">
+    <row r="2" s="22" customFormat="1" spans="1:17">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="21">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="21">
+      <c r="C2" s="22">
+        <v>0</v>
+      </c>
+      <c r="G2" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="22">
         <v>1</v>
       </c>
       <c r="J2">
@@ -2363,33 +2451,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="21">
-        <v>1</v>
-      </c>
-      <c r="N2" s="21">
-        <v>0</v>
-      </c>
-      <c r="O2" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="21" customFormat="1" spans="1:17">
-      <c r="A3" s="21">
+      <c r="M2" s="22">
+        <v>1</v>
+      </c>
+      <c r="N2" s="22">
+        <v>0</v>
+      </c>
+      <c r="O2" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="22" customFormat="1" spans="1:17">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="21">
-        <v>0</v>
-      </c>
-      <c r="G3" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="21">
+      <c r="C3" s="22">
+        <v>0</v>
+      </c>
+      <c r="G3" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="22">
         <v>1</v>
       </c>
       <c r="J3">
@@ -2398,36 +2486,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="21">
-        <v>1</v>
-      </c>
-      <c r="N3" s="21">
-        <v>0</v>
-      </c>
-      <c r="O3" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="14" customFormat="1" spans="1:17">
-      <c r="A4" s="14">
+      <c r="M3" s="22">
+        <v>1</v>
+      </c>
+      <c r="N3" s="22">
+        <v>0</v>
+      </c>
+      <c r="O3" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="15" customFormat="1" spans="1:17">
+      <c r="A4" s="15">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <v>2</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="21">
+      <c r="G4" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="22">
         <v>1</v>
       </c>
       <c r="J4">
@@ -2436,36 +2524,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="21">
-        <v>1</v>
-      </c>
-      <c r="N4" s="21">
-        <v>0</v>
-      </c>
-      <c r="O4" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="14" customFormat="1" spans="1:18">
-      <c r="A5" s="14">
+      <c r="M4" s="22">
+        <v>1</v>
+      </c>
+      <c r="N4" s="22">
+        <v>0</v>
+      </c>
+      <c r="O4" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="15" customFormat="1" spans="1:18">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="14">
-        <v>0</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="15">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="21">
+      <c r="G5" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="22">
         <v>1</v>
       </c>
       <c r="J5">
@@ -2474,48 +2562,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="21">
-        <v>1</v>
-      </c>
-      <c r="N5" s="21">
-        <v>0</v>
-      </c>
-      <c r="O5" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="14">
-        <v>0</v>
-      </c>
-      <c r="R5" s="14" t="s">
+      <c r="M5" s="22">
+        <v>1</v>
+      </c>
+      <c r="N5" s="22">
+        <v>0</v>
+      </c>
+      <c r="O5" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="15">
+        <v>0</v>
+      </c>
+      <c r="R5" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="22" customFormat="1" spans="1:17">
-      <c r="A6" s="22">
+    <row r="6" s="23" customFormat="1" spans="1:17">
+      <c r="A6" s="23">
         <v>101</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="22">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22" t="s">
+      <c r="C6" s="23">
+        <v>0</v>
+      </c>
+      <c r="D6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="21" t="b">
+      <c r="G6" s="22" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I6" s="22">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2527,39 +2615,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="21">
-        <v>1</v>
-      </c>
-      <c r="N6" s="21">
-        <v>0</v>
-      </c>
-      <c r="O6" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="22" customFormat="1" spans="1:17">
-      <c r="A7" s="22">
+      <c r="M6" s="22">
+        <v>1</v>
+      </c>
+      <c r="N6" s="22">
+        <v>0</v>
+      </c>
+      <c r="O6" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="23" customFormat="1" spans="1:17">
+      <c r="A7" s="23">
         <v>102</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="22">
-        <v>0</v>
-      </c>
-      <c r="D7" s="22" t="s">
+      <c r="C7" s="23">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="21">
+      <c r="G7" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="22">
         <v>1</v>
       </c>
       <c r="J7">
@@ -2568,16 +2656,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="21">
-        <v>1</v>
-      </c>
-      <c r="N7" s="21">
-        <v>0</v>
-      </c>
-      <c r="O7" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="22">
+      <c r="M7" s="22">
+        <v>1</v>
+      </c>
+      <c r="N7" s="22">
+        <v>0</v>
+      </c>
+      <c r="O7" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="23">
         <v>0</v>
       </c>
     </row>
@@ -2600,13 +2688,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="21" t="b">
+      <c r="G8" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="22">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2618,13 +2706,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="21">
-        <v>1</v>
-      </c>
-      <c r="N8" s="21">
-        <v>0</v>
-      </c>
-      <c r="O8" s="21">
+      <c r="M8" s="22">
+        <v>1</v>
+      </c>
+      <c r="N8" s="22">
+        <v>0</v>
+      </c>
+      <c r="O8" s="22">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -2637,59 +2725,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="13" customFormat="1" spans="1:18">
-      <c r="A9" s="13">
+    <row r="9" s="14" customFormat="1" spans="1:18">
+      <c r="A9" s="14">
         <v>202</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="13">
-        <v>1</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="C9" s="14">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13" t="s">
+      <c r="G9" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="23">
-        <v>1</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0</v>
-      </c>
-      <c r="K9" s="13">
+      <c r="I9" s="24">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14">
         <v>2</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="23">
-        <v>1</v>
-      </c>
-      <c r="N9" s="23">
-        <v>0</v>
-      </c>
-      <c r="O9" s="23">
-        <v>0</v>
-      </c>
-      <c r="P9" s="13" t="s">
+      <c r="M9" s="24">
+        <v>1</v>
+      </c>
+      <c r="N9" s="24">
+        <v>0</v>
+      </c>
+      <c r="O9" s="24">
+        <v>0</v>
+      </c>
+      <c r="P9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="14">
         <v>3</v>
       </c>
-      <c r="R9" s="13" t="s">
+      <c r="R9" s="14" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2712,13 +2800,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="21" t="b">
+      <c r="G10" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="22">
         <v>1</v>
       </c>
       <c r="J10">
@@ -2730,13 +2818,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="21">
-        <v>1</v>
-      </c>
-      <c r="N10" s="21">
-        <v>0</v>
-      </c>
-      <c r="O10" s="21">
+      <c r="M10" s="22">
+        <v>1</v>
+      </c>
+      <c r="N10" s="22">
+        <v>0</v>
+      </c>
+      <c r="O10" s="22">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -2765,13 +2853,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="21" t="b">
+      <c r="G11" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="22">
         <v>1</v>
       </c>
       <c r="J11">
@@ -2783,13 +2871,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="21">
-        <v>1</v>
-      </c>
-      <c r="N11" s="21">
-        <v>0</v>
-      </c>
-      <c r="O11" s="21">
+      <c r="M11" s="22">
+        <v>1</v>
+      </c>
+      <c r="N11" s="22">
+        <v>0</v>
+      </c>
+      <c r="O11" s="22">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -2821,13 +2909,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="21" t="b">
+      <c r="G12" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <v>1</v>
       </c>
       <c r="J12">
@@ -2839,13 +2927,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="21">
-        <v>1</v>
-      </c>
-      <c r="N12" s="21">
-        <v>0</v>
-      </c>
-      <c r="O12" s="21">
+      <c r="M12" s="22">
+        <v>1</v>
+      </c>
+      <c r="N12" s="22">
+        <v>0</v>
+      </c>
+      <c r="O12" s="22">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -2877,13 +2965,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="21" t="b">
+      <c r="G13" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="22">
         <v>1</v>
       </c>
       <c r="J13">
@@ -2892,16 +2980,16 @@
       <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="21">
-        <v>1</v>
-      </c>
-      <c r="N13" s="21">
-        <v>1</v>
-      </c>
-      <c r="O13" s="21">
+      <c r="M13" s="22">
+        <v>1</v>
+      </c>
+      <c r="N13" s="22">
+        <v>1</v>
+      </c>
+      <c r="O13" s="22">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -2930,16 +3018,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="21" t="b">
+      <c r="G14" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="22">
         <v>1</v>
       </c>
       <c r="J14">
@@ -2951,13 +3039,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="21">
-        <v>1</v>
-      </c>
-      <c r="N14" s="21">
-        <v>0</v>
-      </c>
-      <c r="O14" s="21">
+      <c r="M14" s="22">
+        <v>1</v>
+      </c>
+      <c r="N14" s="22">
+        <v>0</v>
+      </c>
+      <c r="O14" s="22">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -2986,16 +3074,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="26" t="s">
+      <c r="F15" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="21" t="b">
+      <c r="G15" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="22">
         <v>1</v>
       </c>
       <c r="J15">
@@ -3007,13 +3095,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="21">
-        <v>1</v>
-      </c>
-      <c r="N15" s="21">
-        <v>0</v>
-      </c>
-      <c r="O15" s="21">
+      <c r="M15" s="22">
+        <v>1</v>
+      </c>
+      <c r="N15" s="22">
+        <v>0</v>
+      </c>
+      <c r="O15" s="22">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -3045,13 +3133,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="21" t="b">
+      <c r="G16" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="21">
+      <c r="I16" s="22">
         <v>1</v>
       </c>
       <c r="J16">
@@ -3063,13 +3151,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="21">
-        <v>1</v>
-      </c>
-      <c r="N16" s="21">
-        <v>0</v>
-      </c>
-      <c r="O16" s="21">
+      <c r="M16" s="22">
+        <v>1</v>
+      </c>
+      <c r="N16" s="22">
+        <v>0</v>
+      </c>
+      <c r="O16" s="22">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -3101,13 +3189,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="21" t="b">
+      <c r="G17" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="21">
+      <c r="I17" s="22">
         <v>1</v>
       </c>
       <c r="J17">
@@ -3119,13 +3207,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="21">
-        <v>1</v>
-      </c>
-      <c r="N17" s="21">
-        <v>0</v>
-      </c>
-      <c r="O17" s="21">
+      <c r="M17" s="22">
+        <v>1</v>
+      </c>
+      <c r="N17" s="22">
+        <v>0</v>
+      </c>
+      <c r="O17" s="22">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -3151,10 +3239,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="21">
+      <c r="G18" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="22">
         <v>1</v>
       </c>
       <c r="J18">
@@ -3163,13 +3251,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="21">
-        <v>1</v>
-      </c>
-      <c r="N18" s="21">
-        <v>0</v>
-      </c>
-      <c r="O18" s="21">
+      <c r="M18" s="22">
+        <v>1</v>
+      </c>
+      <c r="N18" s="22">
+        <v>0</v>
+      </c>
+      <c r="O18" s="22">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -3195,13 +3283,13 @@
       <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="21" t="b">
+      <c r="G19" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="22">
         <v>1</v>
       </c>
       <c r="J19">
@@ -3213,13 +3301,13 @@
       <c r="L19" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="21">
-        <v>1</v>
-      </c>
-      <c r="N19" s="21">
-        <v>0</v>
-      </c>
-      <c r="O19" s="21">
+      <c r="M19" s="22">
+        <v>1</v>
+      </c>
+      <c r="N19" s="22">
+        <v>0</v>
+      </c>
+      <c r="O19" s="22">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -3251,13 +3339,13 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="21" t="b">
+      <c r="G20" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="22">
         <v>1</v>
       </c>
       <c r="J20">
@@ -3269,13 +3357,13 @@
       <c r="L20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="21">
-        <v>1</v>
-      </c>
-      <c r="N20" s="21">
-        <v>0</v>
-      </c>
-      <c r="O20" s="21">
+      <c r="M20" s="22">
+        <v>1</v>
+      </c>
+      <c r="N20" s="22">
+        <v>0</v>
+      </c>
+      <c r="O20" s="22">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -3307,13 +3395,13 @@
       <c r="F21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" s="21" t="b">
+      <c r="G21" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="22">
         <v>1</v>
       </c>
       <c r="J21">
@@ -3325,13 +3413,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="21">
-        <v>1</v>
-      </c>
-      <c r="N21" s="21">
-        <v>0</v>
-      </c>
-      <c r="O21" s="21">
+      <c r="M21" s="22">
+        <v>1</v>
+      </c>
+      <c r="N21" s="22">
+        <v>0</v>
+      </c>
+      <c r="O21" s="22">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -3363,13 +3451,13 @@
       <c r="F22" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="21" t="b">
+      <c r="G22" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <v>1</v>
       </c>
       <c r="J22">
@@ -3381,13 +3469,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="21">
-        <v>1</v>
-      </c>
-      <c r="N22" s="21">
-        <v>0</v>
-      </c>
-      <c r="O22" s="21">
+      <c r="M22" s="22">
+        <v>1</v>
+      </c>
+      <c r="N22" s="22">
+        <v>0</v>
+      </c>
+      <c r="O22" s="22">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -3400,32 +3488,32 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" s="14" customFormat="1" spans="1:18">
-      <c r="A23" s="14">
+    <row r="23" s="15" customFormat="1" spans="1:18">
+      <c r="A23" s="15">
         <v>301</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="14" t="s">
+      <c r="G23" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="22">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3434,54 +3522,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="21">
-        <v>1</v>
-      </c>
-      <c r="N23" s="21">
-        <v>0</v>
-      </c>
-      <c r="O23" s="21">
-        <v>0</v>
-      </c>
-      <c r="P23" s="14" t="s">
+      <c r="M23" s="22">
+        <v>1</v>
+      </c>
+      <c r="N23" s="22">
+        <v>0</v>
+      </c>
+      <c r="O23" s="22">
+        <v>0</v>
+      </c>
+      <c r="P23" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="Q23" s="14">
+      <c r="Q23" s="15">
         <v>3</v>
       </c>
-      <c r="R23" s="14" t="s">
+      <c r="R23" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="24" s="14" customFormat="1" spans="1:18">
-      <c r="A24" s="14">
+    <row r="24" s="15" customFormat="1" spans="1:18">
+      <c r="A24" s="15">
         <v>302</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="14">
-        <v>1</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="C24" s="15">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="15" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="14" t="s">
+      <c r="G24" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="22">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -3490,51 +3578,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="14" t="s">
+      <c r="L24" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="21">
-        <v>1</v>
-      </c>
-      <c r="N24" s="21">
-        <v>0</v>
-      </c>
-      <c r="O24" s="21">
-        <v>0</v>
-      </c>
-      <c r="P24" s="14" t="s">
+      <c r="M24" s="22">
+        <v>1</v>
+      </c>
+      <c r="N24" s="22">
+        <v>0</v>
+      </c>
+      <c r="O24" s="22">
+        <v>0</v>
+      </c>
+      <c r="P24" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="Q24" s="14">
+      <c r="Q24" s="15">
         <v>3</v>
       </c>
-      <c r="R24" s="14" t="s">
+      <c r="R24" s="15" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="25" s="14" customFormat="1" spans="1:18">
-      <c r="A25" s="14">
+    <row r="25" s="15" customFormat="1" spans="1:18">
+      <c r="A25" s="15">
         <v>303</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="15">
+        <v>1</v>
+      </c>
+      <c r="D25" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="14" t="s">
+      <c r="G25" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="22">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3543,51 +3631,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="21">
-        <v>1</v>
-      </c>
-      <c r="N25" s="21">
-        <v>0</v>
-      </c>
-      <c r="O25" s="21">
-        <v>0</v>
-      </c>
-      <c r="P25" s="14" t="s">
+      <c r="M25" s="22">
+        <v>1</v>
+      </c>
+      <c r="N25" s="22">
+        <v>0</v>
+      </c>
+      <c r="O25" s="22">
+        <v>0</v>
+      </c>
+      <c r="P25" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="Q25" s="14">
+      <c r="Q25" s="15">
         <v>3</v>
       </c>
-      <c r="R25" s="14" t="s">
+      <c r="R25" s="15" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" s="14" customFormat="1" spans="1:18">
-      <c r="A26" s="14">
+    <row r="26" s="15" customFormat="1" spans="1:18">
+      <c r="A26" s="15">
         <v>304</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="14">
-        <v>1</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="15">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="14" t="s">
+      <c r="G26" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="22">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -3596,54 +3684,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="14" t="s">
+      <c r="L26" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="21">
-        <v>1</v>
-      </c>
-      <c r="N26" s="21">
-        <v>0</v>
-      </c>
-      <c r="O26" s="21">
-        <v>0</v>
-      </c>
-      <c r="P26" s="14" t="s">
+      <c r="M26" s="22">
+        <v>1</v>
+      </c>
+      <c r="N26" s="22">
+        <v>0</v>
+      </c>
+      <c r="O26" s="22">
+        <v>0</v>
+      </c>
+      <c r="P26" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="Q26" s="14">
+      <c r="Q26" s="15">
         <v>3</v>
       </c>
-      <c r="R26" s="14" t="s">
+      <c r="R26" s="15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" s="14" customFormat="1" spans="1:18">
-      <c r="A27" s="14">
+    <row r="27" s="15" customFormat="1" spans="1:18">
+      <c r="A27" s="15">
         <v>305</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="15">
         <v>3</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="14" t="s">
+      <c r="G27" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="22">
         <v>1</v>
       </c>
       <c r="J27">
@@ -3655,51 +3743,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="21">
-        <v>1</v>
-      </c>
-      <c r="N27" s="21">
-        <v>0</v>
-      </c>
-      <c r="O27" s="21">
-        <v>0</v>
-      </c>
-      <c r="P27" s="14" t="s">
+      <c r="M27" s="22">
+        <v>1</v>
+      </c>
+      <c r="N27" s="22">
+        <v>0</v>
+      </c>
+      <c r="O27" s="22">
+        <v>0</v>
+      </c>
+      <c r="P27" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="Q27" s="14">
+      <c r="Q27" s="15">
         <v>3</v>
       </c>
-      <c r="R27" s="14" t="s">
+      <c r="R27" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="28" s="14" customFormat="1" spans="1:18">
-      <c r="A28" s="14">
+    <row r="28" s="15" customFormat="1" spans="1:18">
+      <c r="A28" s="15">
         <v>306</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="15">
         <v>2</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="G28" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="14">
-        <v>0</v>
-      </c>
-      <c r="I28" s="21">
+      <c r="G28" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="22">
         <v>1</v>
       </c>
       <c r="J28">
@@ -3708,54 +3796,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="14">
-        <v>1</v>
-      </c>
-      <c r="M28" s="21">
-        <v>1</v>
-      </c>
-      <c r="N28" s="21">
-        <v>0</v>
-      </c>
-      <c r="O28" s="21">
-        <v>0</v>
-      </c>
-      <c r="P28" s="14" t="s">
+      <c r="L28" s="15">
+        <v>1</v>
+      </c>
+      <c r="M28" s="22">
+        <v>1</v>
+      </c>
+      <c r="N28" s="22">
+        <v>0</v>
+      </c>
+      <c r="O28" s="22">
+        <v>0</v>
+      </c>
+      <c r="P28" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="Q28" s="14">
+      <c r="Q28" s="15">
         <v>3</v>
       </c>
-      <c r="R28" s="14" t="s">
+      <c r="R28" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="29" s="14" customFormat="1" spans="1:18">
-      <c r="A29" s="14">
+    <row r="29" s="15" customFormat="1" spans="1:18">
+      <c r="A29" s="15">
         <v>307</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="14" t="s">
+      <c r="C29" s="15">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="14" t="s">
+      <c r="F29" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="14" t="s">
+      <c r="G29" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="22">
         <v>1</v>
       </c>
       <c r="J29">
@@ -3764,54 +3852,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="14" t="s">
+      <c r="L29" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M29" s="22">
         <v>0.1</v>
       </c>
-      <c r="N29" s="21">
-        <v>0</v>
-      </c>
-      <c r="O29" s="21">
+      <c r="N29" s="22">
+        <v>0</v>
+      </c>
+      <c r="O29" s="22">
         <v>0.17</v>
       </c>
-      <c r="P29" s="14" t="s">
+      <c r="P29" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="Q29" s="14">
+      <c r="Q29" s="15">
         <v>3</v>
       </c>
-      <c r="R29" s="14" t="s">
+      <c r="R29" s="15" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" s="14" customFormat="1" spans="1:18">
-      <c r="A30" s="14">
+    <row r="30" s="15" customFormat="1" spans="1:18">
+      <c r="A30" s="15">
         <v>308</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="14" t="s">
+      <c r="C30" s="15">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G30" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="G30" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="22">
         <v>1</v>
       </c>
       <c r="J30">
@@ -3820,54 +3908,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="14" t="s">
+      <c r="L30" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="M30" s="21">
-        <v>1</v>
-      </c>
-      <c r="N30" s="21">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21">
-        <v>0</v>
-      </c>
-      <c r="P30" s="14" t="s">
+      <c r="M30" s="22">
+        <v>1</v>
+      </c>
+      <c r="N30" s="22">
+        <v>0</v>
+      </c>
+      <c r="O30" s="22">
+        <v>0</v>
+      </c>
+      <c r="P30" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="Q30" s="14">
+      <c r="Q30" s="15">
         <v>3</v>
       </c>
-      <c r="R30" s="14" t="s">
+      <c r="R30" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="31" s="14" customFormat="1" spans="1:18">
-      <c r="A31" s="14">
+    <row r="31" s="15" customFormat="1" spans="1:18">
+      <c r="A31" s="15">
         <v>309</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C31" s="15">
         <v>2</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14" t="s">
+      <c r="G31" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="22">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3876,54 +3964,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="14" t="s">
+      <c r="L31" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="M31" s="21">
-        <v>1</v>
-      </c>
-      <c r="N31" s="21">
-        <v>0</v>
-      </c>
-      <c r="O31" s="21">
-        <v>0</v>
-      </c>
-      <c r="P31" s="14" t="s">
+      <c r="M31" s="22">
+        <v>1</v>
+      </c>
+      <c r="N31" s="22">
+        <v>0</v>
+      </c>
+      <c r="O31" s="22">
+        <v>0</v>
+      </c>
+      <c r="P31" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="Q31" s="14">
+      <c r="Q31" s="15">
         <v>3</v>
       </c>
-      <c r="R31" s="14" t="s">
+      <c r="R31" s="15" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" s="14" customFormat="1" spans="1:18">
-      <c r="A32" s="14">
+    <row r="32" s="15" customFormat="1" spans="1:18">
+      <c r="A32" s="15">
         <v>310</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C32" s="15">
         <v>2</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="G32" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="14" t="s">
+      <c r="G32" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="22">
         <v>1</v>
       </c>
       <c r="J32">
@@ -3932,54 +4020,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="14" t="s">
+      <c r="L32" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="21">
-        <v>1</v>
-      </c>
-      <c r="N32" s="21">
-        <v>0</v>
-      </c>
-      <c r="O32" s="21">
-        <v>0</v>
-      </c>
-      <c r="P32" s="14" t="s">
+      <c r="M32" s="22">
+        <v>1</v>
+      </c>
+      <c r="N32" s="22">
+        <v>0</v>
+      </c>
+      <c r="O32" s="22">
+        <v>0</v>
+      </c>
+      <c r="P32" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="Q32" s="14">
+      <c r="Q32" s="15">
         <v>4</v>
       </c>
-      <c r="R32" s="14" t="s">
+      <c r="R32" s="15" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="33" s="14" customFormat="1" spans="1:18">
-      <c r="A33" s="14">
+    <row r="33" s="15" customFormat="1" spans="1:18">
+      <c r="A33" s="15">
         <v>311</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="15">
         <v>2</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="14">
-        <v>0</v>
-      </c>
-      <c r="I33" s="21">
+      <c r="G33" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0</v>
+      </c>
+      <c r="I33" s="22">
         <v>1</v>
       </c>
       <c r="J33">
@@ -3988,45 +4076,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="14">
-        <v>1</v>
-      </c>
-      <c r="M33" s="21">
-        <v>1</v>
-      </c>
-      <c r="N33" s="21">
-        <v>0</v>
-      </c>
-      <c r="O33" s="21">
-        <v>0</v>
-      </c>
-      <c r="P33" s="14" t="s">
+      <c r="L33" s="15">
+        <v>1</v>
+      </c>
+      <c r="M33" s="22">
+        <v>1</v>
+      </c>
+      <c r="N33" s="22">
+        <v>0</v>
+      </c>
+      <c r="O33" s="22">
+        <v>0</v>
+      </c>
+      <c r="P33" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="14">
+      <c r="Q33" s="15">
         <v>3</v>
       </c>
-      <c r="R33" s="14" t="s">
+      <c r="R33" s="15" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="34" s="14" customFormat="1" spans="1:18">
-      <c r="A34" s="14">
+    <row r="34" s="15" customFormat="1" spans="1:18">
+      <c r="A34" s="15">
         <v>312</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C34" s="15">
         <v>2</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="21">
+      <c r="G34" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="22">
         <v>1</v>
       </c>
       <c r="J34">
@@ -4035,45 +4123,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="21">
-        <v>1</v>
-      </c>
-      <c r="N34" s="21">
-        <v>0</v>
-      </c>
-      <c r="O34" s="21">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="14">
-        <v>1</v>
-      </c>
-      <c r="R34" s="14" t="s">
+      <c r="M34" s="22">
+        <v>1</v>
+      </c>
+      <c r="N34" s="22">
+        <v>0</v>
+      </c>
+      <c r="O34" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>1</v>
+      </c>
+      <c r="R34" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" s="12" customFormat="1" spans="1:17">
-      <c r="A35" s="12">
+    <row r="35" s="13" customFormat="1" spans="1:17">
+      <c r="A35" s="13">
         <v>401</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="13">
         <v>2</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="26" t="s">
+      <c r="F35" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="12" t="s">
+      <c r="G35" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="22">
         <v>1</v>
       </c>
       <c r="J35">
@@ -4085,45 +4173,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="21">
-        <v>1</v>
-      </c>
-      <c r="N35" s="21">
-        <v>0</v>
-      </c>
-      <c r="O35" s="21">
-        <v>0</v>
-      </c>
-      <c r="P35" s="12" t="s">
+      <c r="M35" s="22">
+        <v>1</v>
+      </c>
+      <c r="N35" s="22">
+        <v>0</v>
+      </c>
+      <c r="O35" s="22">
+        <v>0</v>
+      </c>
+      <c r="P35" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="12">
+      <c r="Q35" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="12" customFormat="1" spans="1:17">
-      <c r="A36" s="12">
+    <row r="36" s="13" customFormat="1" spans="1:17">
+      <c r="A36" s="13">
         <v>402</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="13">
         <v>2</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="28" t="s">
+      <c r="F36" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="12" t="s">
+      <c r="G36" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="22">
         <v>1</v>
       </c>
       <c r="J36">
@@ -4135,48 +4223,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="21">
-        <v>1</v>
-      </c>
-      <c r="N36" s="21">
-        <v>0</v>
-      </c>
-      <c r="O36" s="21">
-        <v>0</v>
-      </c>
-      <c r="P36" s="12" t="s">
+      <c r="M36" s="22">
+        <v>1</v>
+      </c>
+      <c r="N36" s="22">
+        <v>0</v>
+      </c>
+      <c r="O36" s="22">
+        <v>0</v>
+      </c>
+      <c r="P36" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="12">
+      <c r="Q36" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="12" customFormat="1" spans="1:17">
-      <c r="A37" s="12">
+    <row r="37" s="13" customFormat="1" spans="1:17">
+      <c r="A37" s="13">
         <v>403</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="13">
         <v>2</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="12" t="s">
+      <c r="G37" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="22">
         <v>1</v>
       </c>
       <c r="J37">
@@ -4185,83 +4273,83 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="12" t="s">
+      <c r="L37" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="21">
-        <v>1</v>
-      </c>
-      <c r="N37" s="21">
-        <v>0</v>
-      </c>
-      <c r="O37" s="21">
-        <v>0</v>
-      </c>
-      <c r="P37" s="12" t="s">
+      <c r="M37" s="22">
+        <v>1</v>
+      </c>
+      <c r="N37" s="22">
+        <v>0</v>
+      </c>
+      <c r="O37" s="22">
+        <v>0</v>
+      </c>
+      <c r="P37" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="12">
+      <c r="Q37" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="23" customFormat="1" spans="1:17">
-      <c r="A38" s="23">
+    <row r="38" s="24" customFormat="1" spans="1:17">
+      <c r="A38" s="24">
         <v>404</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="23">
-        <v>1</v>
-      </c>
-      <c r="D38" s="13" t="s">
+      <c r="C38" s="24">
+        <v>1</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="23" t="s">
+      <c r="G38" s="24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="23">
-        <v>1</v>
-      </c>
-      <c r="J38" s="13">
-        <v>0</v>
-      </c>
-      <c r="K38" s="13">
+      <c r="I38" s="24">
+        <v>1</v>
+      </c>
+      <c r="J38" s="14">
+        <v>0</v>
+      </c>
+      <c r="K38" s="14">
         <v>2</v>
       </c>
-      <c r="L38" s="23" t="s">
+      <c r="L38" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="23">
-        <v>1</v>
-      </c>
-      <c r="N38" s="23">
-        <v>0</v>
-      </c>
-      <c r="O38" s="23">
-        <v>0</v>
-      </c>
-      <c r="P38" s="23" t="s">
+      <c r="M38" s="24">
+        <v>1</v>
+      </c>
+      <c r="N38" s="24">
+        <v>0</v>
+      </c>
+      <c r="O38" s="24">
+        <v>0</v>
+      </c>
+      <c r="P38" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="23">
+      <c r="Q38" s="24">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="12" customFormat="1" spans="1:21">
-      <c r="A39" s="12">
+    <row r="39" s="13" customFormat="1" spans="1:21">
+      <c r="A39" s="13">
         <v>405</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="28" t="s">
         <v>180</v>
       </c>
       <c r="C39">
@@ -4276,13 +4364,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="21" t="b">
+      <c r="G39" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="22">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4294,13 +4382,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="21">
-        <v>1</v>
-      </c>
-      <c r="N39" s="21">
-        <v>0</v>
-      </c>
-      <c r="O39" s="21">
+      <c r="M39" s="22">
+        <v>1</v>
+      </c>
+      <c r="N39" s="22">
+        <v>0</v>
+      </c>
+      <c r="O39" s="22">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -4316,32 +4404,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="12" customFormat="1" spans="1:17">
-      <c r="A40" s="12">
+    <row r="40" s="13" customFormat="1" spans="1:17">
+      <c r="A40" s="13">
         <v>406</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="12">
-        <v>1</v>
-      </c>
-      <c r="D40" s="12" t="s">
+      <c r="C40" s="13">
+        <v>1</v>
+      </c>
+      <c r="D40" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="12" t="s">
+      <c r="E40" s="13" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="12">
-        <v>0</v>
-      </c>
-      <c r="I40" s="21">
+      <c r="G40" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13">
+        <v>0</v>
+      </c>
+      <c r="I40" s="22">
         <v>1</v>
       </c>
       <c r="J40">
@@ -4350,27 +4438,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="12">
+      <c r="L40" s="13">
         <v>3</v>
       </c>
-      <c r="M40" s="21">
-        <v>1</v>
-      </c>
-      <c r="N40" s="21">
-        <v>0</v>
-      </c>
-      <c r="O40" s="21">
-        <v>0</v>
-      </c>
-      <c r="P40" s="12" t="s">
+      <c r="M40" s="22">
+        <v>1</v>
+      </c>
+      <c r="N40" s="22">
+        <v>0</v>
+      </c>
+      <c r="O40" s="22">
+        <v>0</v>
+      </c>
+      <c r="P40" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="12">
+      <c r="Q40" s="13">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="12">
+      <c r="A41" s="13">
         <v>407</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -4388,13 +4476,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="21" t="b">
+      <c r="G41" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="22">
         <v>1</v>
       </c>
       <c r="J41">
@@ -4406,13 +4494,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="21">
-        <v>1</v>
-      </c>
-      <c r="N41" s="21">
-        <v>0</v>
-      </c>
-      <c r="O41" s="21">
+      <c r="M41" s="22">
+        <v>1</v>
+      </c>
+      <c r="N41" s="22">
+        <v>0</v>
+      </c>
+      <c r="O41" s="22">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -4426,7 +4514,7 @@
       </c>
     </row>
     <row r="42" spans="1:18">
-      <c r="A42" s="12">
+      <c r="A42" s="13">
         <v>408</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -4444,13 +4532,13 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="21" t="b">
+      <c r="G42" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="22">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4462,13 +4550,13 @@
       <c r="L42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="21">
-        <v>1</v>
-      </c>
-      <c r="N42" s="21">
-        <v>0</v>
-      </c>
-      <c r="O42" s="21">
+      <c r="M42" s="22">
+        <v>1</v>
+      </c>
+      <c r="N42" s="22">
+        <v>0</v>
+      </c>
+      <c r="O42" s="22">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -4482,7 +4570,7 @@
       </c>
     </row>
     <row r="43" spans="1:18">
-      <c r="A43" s="12">
+      <c r="A43" s="13">
         <v>409</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -4500,13 +4588,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="21" t="b">
+      <c r="G43" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="21">
+      <c r="I43" s="22">
         <v>1</v>
       </c>
       <c r="J43">
@@ -4518,13 +4606,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="21">
-        <v>1</v>
-      </c>
-      <c r="N43" s="21">
-        <v>0</v>
-      </c>
-      <c r="O43" s="21">
+      <c r="M43" s="22">
+        <v>1</v>
+      </c>
+      <c r="N43" s="22">
+        <v>0</v>
+      </c>
+      <c r="O43" s="22">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -4538,7 +4626,7 @@
       </c>
     </row>
     <row r="44" spans="1:18">
-      <c r="A44" s="12">
+      <c r="A44" s="13">
         <v>410</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -4556,13 +4644,13 @@
       <c r="F44" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="21" t="b">
+      <c r="G44" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="22">
         <v>1</v>
       </c>
       <c r="J44">
@@ -4574,13 +4662,13 @@
       <c r="L44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" s="21">
-        <v>1</v>
-      </c>
-      <c r="N44" s="21">
-        <v>0</v>
-      </c>
-      <c r="O44" s="21">
+      <c r="M44" s="22">
+        <v>1</v>
+      </c>
+      <c r="N44" s="22">
+        <v>0</v>
+      </c>
+      <c r="O44" s="22">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -4594,7 +4682,7 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:18">
-      <c r="A45" s="12">
+      <c r="A45" s="13">
         <v>411</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -4612,13 +4700,13 @@
       <c r="F45" t="s">
         <v>118</v>
       </c>
-      <c r="G45" s="21" t="b">
+      <c r="G45" s="22" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="22">
         <v>1</v>
       </c>
       <c r="J45">
@@ -4630,13 +4718,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="21">
-        <v>1</v>
-      </c>
-      <c r="N45" s="21">
-        <v>0</v>
-      </c>
-      <c r="O45" s="21">
+      <c r="M45" s="22">
+        <v>1</v>
+      </c>
+      <c r="N45" s="22">
+        <v>0</v>
+      </c>
+      <c r="O45" s="22">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -4706,7 +4794,7 @@
       <c r="D2" t="s">
         <v>297</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4723,7 +4811,7 @@
       <c r="D3" t="s">
         <v>297</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4740,7 +4828,7 @@
       <c r="D4" t="s">
         <v>302</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4757,7 +4845,7 @@
       <c r="D5" t="s">
         <v>302</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4876,13 +4964,13 @@
       <c r="D12" t="s">
         <v>317</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="9" t="s">
         <v>320</v>
       </c>
     </row>
@@ -4890,7 +4978,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>321</v>
       </c>
       <c r="C13" t="s">
@@ -4899,17 +4987,17 @@
       <c r="D13" t="s">
         <v>302</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9"/>
     </row>
     <row r="14" ht="14.25" spans="1:7">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>323</v>
       </c>
       <c r="C14" t="s">
@@ -4918,11 +5006,11 @@
       <c r="D14" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
@@ -4937,7 +5025,7 @@
       <c r="D15" t="s">
         <v>326</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>327</v>
       </c>
     </row>
@@ -4954,13 +5042,13 @@
       <c r="D16" t="s">
         <v>330</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>333</v>
       </c>
     </row>
@@ -4977,7 +5065,7 @@
       <c r="D17" t="s">
         <v>297</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>322</v>
       </c>
     </row>
@@ -4994,13 +5082,13 @@
       <c r="D18" t="s">
         <v>337</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5063,6 +5151,314 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="18.25" customWidth="1"/>
+    <col min="3" max="3" width="35.25" customWidth="1"/>
+    <col min="4" max="4" width="52.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C5" t="s">
+        <v>347</v>
+      </c>
+      <c r="D5" t="s">
+        <v>348</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C6" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" t="s">
+        <v>347</v>
+      </c>
+      <c r="D9" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="10" ht="17.25" spans="1:5">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="11" ht="17.25" spans="1:5">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D11" t="s">
+        <v>362</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="12" ht="17.25" spans="1:5">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="D12" t="s">
+        <v>362</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" ht="17.25" spans="1:5">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="D13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" ht="17.25" spans="1:5">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="D14" t="s">
+        <v>362</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="2"/>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="2"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="2"/>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="2"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="2"/>
+      <c r="B19" s="7"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="2"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23" s="3"/>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="2"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" display="https://www.rtsgame.online/music/suno后勤运营低音质.mp3"/>
+    <hyperlink ref="E7" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
+    <hyperlink ref="E10" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
+    <hyperlink ref="E11" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="E12" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="E14" r:id="rId6" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E13" r:id="rId7" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E5" r:id="rId8" display="https://www.rtsgame.online/music/Suno_Edge_of_Collapse_2.mp3"/>
+    <hyperlink ref="E2" r:id="rId9" display="https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3" tooltip="https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3"/>
+    <hyperlink ref="E3" r:id="rId10" display="https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3" tooltip="https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3"/>
+    <hyperlink ref="E8" r:id="rId11" display="https://www.rtsgame.online/music/定居低音质.mp3"/>
+    <hyperlink ref="E9" r:id="rId12" display="https://www.rtsgame.online/music/漂泊低音质.mp3"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -5098,16 +5494,16 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="14">
+      <c r="A2" s="15">
         <v>4</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="15">
         <v>20</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="15">
         <v>1</v>
       </c>
       <c r="E2" s="2">
@@ -5465,284 +5861,284 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="17" customFormat="1" spans="1:7">
-      <c r="A18" s="17">
+    <row r="18" s="18" customFormat="1" spans="1:7">
+      <c r="A18" s="18">
         <v>301</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <v>50</v>
       </c>
-      <c r="D18" s="17">
-        <v>0</v>
-      </c>
-      <c r="E18" s="17">
+      <c r="D18" s="18">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18">
         <v>400</v>
       </c>
-      <c r="F18" s="17">
-        <v>0</v>
-      </c>
-      <c r="G18" s="19">
+      <c r="F18" s="18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="20">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="17" customFormat="1" spans="1:7">
-      <c r="A19" s="17">
+    <row r="19" s="18" customFormat="1" spans="1:7">
+      <c r="A19" s="18">
         <v>302</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <v>25</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <v>9</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <v>100</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="18">
         <v>303</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="17" customFormat="1" spans="1:7">
-      <c r="A20" s="17">
+    <row r="20" s="18" customFormat="1" spans="1:7">
+      <c r="A20" s="18">
         <v>303</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <v>20</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <v>3</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <v>50</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="18">
         <v>301</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="17" customFormat="1" spans="1:7">
-      <c r="A21" s="17">
+    <row r="21" s="18" customFormat="1" spans="1:7">
+      <c r="A21" s="18">
         <v>304</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <v>30</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <v>11</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="18">
         <v>300</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <v>301</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="17" customFormat="1" spans="1:7">
-      <c r="A22" s="17">
+    <row r="22" s="18" customFormat="1" spans="1:7">
+      <c r="A22" s="18">
         <v>305</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="18">
         <v>25</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="18">
         <v>8</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="18">
         <v>100</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="18">
         <v>303</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="17" customFormat="1" spans="1:7">
-      <c r="A23" s="17">
+    <row r="23" s="18" customFormat="1" spans="1:7">
+      <c r="A23" s="18">
         <v>306</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <v>35</v>
       </c>
-      <c r="D23" s="17">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17">
+      <c r="D23" s="18">
+        <v>0</v>
+      </c>
+      <c r="E23" s="18">
         <v>200</v>
       </c>
-      <c r="F23" s="17">
-        <v>0</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="F23" s="18">
+        <v>0</v>
+      </c>
+      <c r="G23" s="20">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="17" customFormat="1" spans="1:7">
-      <c r="A24" s="17">
+    <row r="24" s="18" customFormat="1" spans="1:7">
+      <c r="A24" s="18">
         <v>307</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <v>35</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="18">
         <v>12</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="18">
         <v>150</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="18">
         <v>302</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="17" customFormat="1" spans="1:7">
-      <c r="A25" s="17">
+    <row r="25" s="18" customFormat="1" spans="1:7">
+      <c r="A25" s="18">
         <v>308</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="18">
         <v>35</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="18">
         <v>12</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="18">
         <v>150</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="18">
         <v>302</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="17" customFormat="1" spans="1:7">
-      <c r="A26" s="17">
+    <row r="26" s="18" customFormat="1" spans="1:7">
+      <c r="A26" s="18">
         <v>309</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="18">
         <v>20</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="18">
         <v>10</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="18">
         <v>80</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="18">
         <v>306</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="17" customFormat="1" spans="1:7">
-      <c r="A27" s="17">
+    <row r="27" s="18" customFormat="1" spans="1:7">
+      <c r="A27" s="18">
         <v>310</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="18">
         <v>30</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="18">
         <v>10</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="18">
         <v>120</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="18">
         <v>309</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="17" customFormat="1" spans="1:7">
-      <c r="A28" s="17">
+    <row r="28" s="18" customFormat="1" spans="1:7">
+      <c r="A28" s="18">
         <v>311</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="18">
         <v>30</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="18">
         <v>10</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="18">
         <v>120</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="18">
         <v>309</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="20">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="17" customFormat="1" spans="1:7">
-      <c r="A29" s="17">
+    <row r="29" s="18" customFormat="1" spans="1:7">
+      <c r="A29" s="18">
         <v>312</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="18">
         <v>15</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="18">
         <v>2</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="18">
         <v>15</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="18">
         <v>306</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="20">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="17" customFormat="1" spans="2:2">
-      <c r="B30" s="18"/>
+    <row r="30" s="18" customFormat="1" spans="2:2">
+      <c r="B30" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5785,10 +6181,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
+      <c r="A2" s="15">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>20</v>
       </c>
       <c r="C2">
@@ -5805,10 +6201,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="14">
+      <c r="A3" s="15">
         <v>4</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C3">
@@ -5994,10 +6390,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="14">
+      <c r="A12" s="15">
         <v>309</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="15" t="s">
         <v>161</v>
       </c>
       <c r="C12">
@@ -6014,10 +6410,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="14">
+      <c r="A13" s="15">
         <v>310</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="15" t="s">
         <v>165</v>
       </c>
       <c r="C13">
@@ -6034,10 +6430,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="14">
+      <c r="A14" s="15">
         <v>311</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="15" t="s">
         <v>169</v>
       </c>
       <c r="C14">
@@ -6057,10 +6453,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="14">
+      <c r="A15" s="15">
         <v>312</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>172</v>
       </c>
       <c r="C15">
@@ -6077,8 +6473,8 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6099,29 +6495,29 @@
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" spans="1:8">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" s="11" customFormat="1" spans="1:8">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>204</v>
       </c>
     </row>
@@ -6151,29 +6547,29 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" s="13" customFormat="1" spans="1:8">
-      <c r="A3" s="13">
+    <row r="3" s="14" customFormat="1" spans="1:8">
+      <c r="A3" s="14">
         <v>202</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
         <v>0.8</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6265,7 +6661,7 @@
       <c r="C7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="8" t="s">
         <v>69</v>
       </c>
       <c r="E7">
@@ -6563,34 +6959,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="13" customFormat="1" spans="1:8">
-      <c r="A20" s="16">
+    <row r="20" s="14" customFormat="1" spans="1:8">
+      <c r="A20" s="17">
         <v>404</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="E20" s="13">
-        <v>0</v>
-      </c>
-      <c r="F20" s="13">
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
         <v>0.8</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="13" t="s">
+      <c r="H20" s="14" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="11">
+      <c r="A21" s="12">
         <v>405</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -6616,7 +7012,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="11">
+      <c r="A22" s="12">
         <v>406</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -6642,7 +7038,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="12">
+      <c r="A23" s="13">
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -6668,7 +7064,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="12">
+      <c r="A24" s="13">
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -6694,7 +7090,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="12">
+      <c r="A25" s="13">
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -6720,7 +7116,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="12">
+      <c r="A26" s="13">
         <v>410</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -6746,7 +7142,7 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="12">
+      <c r="A27" s="13">
         <v>411</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -6812,68 +7208,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" spans="1:21">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:21">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="14" t="s">
         <v>251</v>
       </c>
     </row>
@@ -7194,7 +7590,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="8" t="s">
         <v>70</v>
       </c>
       <c r="K7">
@@ -7745,10 +8141,10 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="14">
+      <c r="A17" s="15">
         <v>301</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="16" t="s">
         <v>120</v>
       </c>
       <c r="C17">
@@ -7804,10 +8200,10 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>302</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>126</v>
       </c>
       <c r="C18">
@@ -7863,10 +8259,10 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="14">
+      <c r="A19" s="15">
         <v>303</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="16" t="s">
         <v>133</v>
       </c>
       <c r="C19">
@@ -7922,10 +8318,10 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>304</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="16" t="s">
         <v>135</v>
       </c>
       <c r="C20">
@@ -8043,10 +8439,10 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>306</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>145</v>
       </c>
       <c r="C22">
@@ -8102,10 +8498,10 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="14">
+      <c r="A23" s="15">
         <v>307</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="16" t="s">
         <v>151</v>
       </c>
       <c r="C23">
@@ -8161,10 +8557,10 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="14">
+      <c r="A24" s="15">
         <v>308</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="16" t="s">
         <v>156</v>
       </c>
       <c r="C24">
@@ -8220,10 +8616,10 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="14">
+      <c r="A25" s="15">
         <v>309</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="16" t="s">
         <v>161</v>
       </c>
       <c r="C25">
@@ -8279,10 +8675,10 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="14">
+      <c r="A26" s="15">
         <v>310</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="16" t="s">
         <v>165</v>
       </c>
       <c r="C26">
@@ -8338,10 +8734,10 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="14">
+      <c r="A27" s="15">
         <v>311</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="16" t="s">
         <v>169</v>
       </c>
       <c r="C27">
@@ -8397,10 +8793,10 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="14">
+      <c r="A28" s="15">
         <v>312</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="B28" s="16" t="s">
         <v>172</v>
       </c>
       <c r="C28">
@@ -8630,7 +9026,7 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="11">
+      <c r="A32" s="12">
         <v>404</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -8692,7 +9088,7 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="11">
+      <c r="A33" s="12">
         <v>405</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -8748,7 +9144,7 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="11">
+      <c r="A34" s="12">
         <v>406</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -8804,7 +9200,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="12">
+      <c r="A35" s="13">
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -8860,7 +9256,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="12">
+      <c r="A36" s="13">
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -8919,7 +9315,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="12">
+      <c r="A37" s="13">
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -8978,7 +9374,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="12">
+      <c r="A38" s="13">
         <v>410</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -9028,7 +9424,7 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="12">
+      <c r="A39" s="13">
         <v>411</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -9190,7 +9586,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -9201,7 +9597,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -9212,7 +9608,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -9223,7 +9619,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="12">
+      <c r="A12" s="13">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -9234,7 +9630,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="12">
+      <c r="A13" s="13">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -9245,7 +9641,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="12">
+      <c r="A14" s="13">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -9256,7 +9652,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="12">
+      <c r="A15" s="13">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -9267,7 +9663,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="12">
+      <c r="A16" s="13">
         <v>411</v>
       </c>
       <c r="B16" t="s">
@@ -9292,29 +9688,29 @@
     <col min="7" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="1" spans="1:8">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" s="11" customFormat="1" spans="1:8">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>189</v>
       </c>
     </row>
@@ -9548,10 +9944,10 @@
       <c r="B1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>189</v>
       </c>
     </row>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="371">
   <si>
     <t>类型</t>
   </si>
@@ -1201,13 +1201,13 @@
     <t>版权归Suno和提示词作者共有，使用权开放给所有人。</t>
   </si>
   <si>
-    <t>https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3</t>
+    <t>https://www.rtsgame.online/music/suno世界又恢复了和平低音质.mp3</t>
   </si>
   <si>
     <t>世界又恢复了和平2</t>
   </si>
   <si>
-    <t>https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3</t>
+    <t>https://www.rtsgame.online/music/suno世界又恢复了和平2低音质.mp3</t>
   </si>
   <si>
     <t>战线崩溃</t>
@@ -1220,6 +1220,12 @@
   </si>
   <si>
     <t>重工业浪漫</t>
+  </si>
+  <si>
+    <t>援军到达战场</t>
+  </si>
+  <si>
+    <t>https://www.rtsgame.online/music/援军到达战场低音质.mp3</t>
   </si>
   <si>
     <t>定居</t>
@@ -1967,6 +1973,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
@@ -1974,9 +1983,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4794,7 +4800,7 @@
       <c r="D2" t="s">
         <v>297</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4811,7 +4817,7 @@
       <c r="D3" t="s">
         <v>297</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>298</v>
       </c>
     </row>
@@ -4828,7 +4834,7 @@
       <c r="D4" t="s">
         <v>302</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4845,7 +4851,7 @@
       <c r="D5" t="s">
         <v>302</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>303</v>
       </c>
     </row>
@@ -4964,7 +4970,7 @@
       <c r="D12" t="s">
         <v>317</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>318</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -4987,7 +4993,7 @@
       <c r="D13" t="s">
         <v>302</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>322</v>
       </c>
       <c r="F13" s="8"/>
@@ -5006,7 +5012,7 @@
       <c r="D14" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>322</v>
       </c>
       <c r="F14" s="8"/>
@@ -5025,7 +5031,7 @@
       <c r="D15" t="s">
         <v>326</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5042,7 +5048,7 @@
       <c r="D16" t="s">
         <v>330</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="E16" s="4" t="s">
         <v>331</v>
       </c>
       <c r="F16" s="8" t="s">
@@ -5065,7 +5071,7 @@
       <c r="D17" t="s">
         <v>297</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>322</v>
       </c>
     </row>
@@ -5082,13 +5088,13 @@
       <c r="D18" t="s">
         <v>337</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="3" t="s">
         <v>338</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="4" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5154,7 +5160,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="2" max="2" width="18.25" customWidth="1"/>
@@ -5209,7 +5215,7 @@
       <c r="D3" t="s">
         <v>348</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5243,7 +5249,7 @@
       <c r="D5" t="s">
         <v>348</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>311</v>
       </c>
     </row>
@@ -5260,7 +5266,7 @@
       <c r="D6" t="s">
         <v>348</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>298</v>
       </c>
     </row>
@@ -5277,7 +5283,7 @@
       <c r="D7" t="s">
         <v>348</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>303</v>
       </c>
     </row>
@@ -5285,7 +5291,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>356</v>
       </c>
       <c r="C8" t="s">
@@ -5294,7 +5300,7 @@
       <c r="D8" t="s">
         <v>348</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>357</v>
       </c>
     </row>
@@ -5311,25 +5317,25 @@
       <c r="D9" t="s">
         <v>348</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="10" ht="17.25" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
+        <v>347</v>
+      </c>
+      <c r="D10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>361</v>
-      </c>
-      <c r="D10" t="s">
-        <v>362</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
@@ -5337,16 +5343,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>361</v>
-      </c>
       <c r="D11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:5">
@@ -5354,16 +5360,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D12" t="s">
         <v>364</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="D12" t="s">
-        <v>362</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>338</v>
+      <c r="E12" s="4" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
@@ -5371,16 +5377,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C13" s="5" t="s">
         <v>366</v>
       </c>
+      <c r="C13" s="6" t="s">
+        <v>363</v>
+      </c>
       <c r="D13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
@@ -5390,18 +5396,32 @@
       <c r="B14" t="s">
         <v>367</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>368</v>
       </c>
       <c r="D14" t="s">
-        <v>362</v>
-      </c>
-      <c r="E14" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" ht="17.25" spans="1:5">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="2"/>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="2"/>
@@ -5412,47 +5432,46 @@
     <row r="18" spans="1:1">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:1">
       <c r="A19" s="2"/>
-      <c r="B19" s="7"/>
-    </row>
-    <row r="20" spans="1:5">
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" s="2"/>
       <c r="B20" s="7"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:1">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="2"/>
+      <c r="B21" s="7"/>
+      <c r="E21" s="4"/>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:1">
       <c r="A23" s="2"/>
-      <c r="B23"/>
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:1">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="2"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E6" r:id="rId1" display="https://www.rtsgame.online/music/suno后勤运营低音质.mp3"/>
-    <hyperlink ref="E7" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
-    <hyperlink ref="E10" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="E11" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
-    <hyperlink ref="E12" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="E14" r:id="rId6" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E13" r:id="rId7" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E8" r:id="rId2" display="https://www.rtsgame.online/music/援军到达战场低音质.mp3" tooltip="https://www.rtsgame.online/music/援军到达战场低音质.mp3"/>
+    <hyperlink ref="E11" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
+    <hyperlink ref="E12" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="E13" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="E15" r:id="rId6" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E14" r:id="rId7" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
     <hyperlink ref="E5" r:id="rId8" display="https://www.rtsgame.online/music/Suno_Edge_of_Collapse_2.mp3"/>
-    <hyperlink ref="E2" r:id="rId9" display="https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3" tooltip="https://www.rtsgame.online/music/世界又恢复了和平低音质.mp3"/>
-    <hyperlink ref="E3" r:id="rId10" display="https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3" tooltip="https://www.rtsgame.online/music/世界又恢复了和平2低音质.mp3"/>
-    <hyperlink ref="E8" r:id="rId11" display="https://www.rtsgame.online/music/定居低音质.mp3"/>
-    <hyperlink ref="E9" r:id="rId12" display="https://www.rtsgame.online/music/漂泊低音质.mp3"/>
+    <hyperlink ref="E2" r:id="rId9" display="https://www.rtsgame.online/music/suno世界又恢复了和平低音质.mp3" tooltip="https://www.rtsgame.online/music/suno世界又恢复了和平低音质.mp3"/>
+    <hyperlink ref="E3" r:id="rId10" display="https://www.rtsgame.online/music/suno世界又恢复了和平2低音质.mp3" tooltip="https://www.rtsgame.online/music/suno世界又恢复了和平2低音质.mp3"/>
+    <hyperlink ref="E9" r:id="rId11" display="https://www.rtsgame.online/music/定居低音质.mp3"/>
+    <hyperlink ref="E10" r:id="rId12" display="https://www.rtsgame.online/music/漂泊低音质.mp3"/>
+    <hyperlink ref="E7" r:id="rId13" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="11"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="373">
   <si>
     <t>类型</t>
   </si>
@@ -923,6 +923,9 @@
   </si>
   <si>
     <t>Https高清贴图</t>
+  </si>
+  <si>
+    <t>玩家同阵营</t>
   </si>
   <si>
     <t>新手训练_战备运营_人</t>
@@ -1128,6 +1131,9 @@
   </si>
   <si>
     <t>https://www.rtsgame.online/图片/地图/ditu4_1_高清.png</t>
+  </si>
+  <si>
+    <t>中央防守_合作模式</t>
   </si>
   <si>
     <t>多玩家混战</t>
@@ -2435,7 +2441,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="22" customFormat="1" spans="1:17">
+    <row r="2" s="22" customFormat="1" spans="1:18">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2470,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="22" customFormat="1" spans="1:17">
+    <row r="3" s="22" customFormat="1" spans="1:18">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2505,7 +2511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" s="15" customFormat="1" spans="1:17">
+    <row r="4" s="15" customFormat="1" spans="1:18">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -2584,7 +2590,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="23" customFormat="1" spans="1:17">
+    <row r="6" s="23" customFormat="1" spans="1:18">
       <c r="A6" s="23">
         <v>101</v>
       </c>
@@ -2634,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="23" customFormat="1" spans="1:17">
+    <row r="7" s="23" customFormat="1" spans="1:18">
       <c r="A7" s="23">
         <v>102</v>
       </c>
@@ -3232,7 +3238,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:17">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>211</v>
       </c>
@@ -4048,7 +4054,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" s="15" customFormat="1" spans="1:18">
+    <row r="33" s="15" customFormat="1" spans="1:21">
       <c r="A33" s="15">
         <v>311</v>
       </c>
@@ -4104,7 +4110,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="34" s="15" customFormat="1" spans="1:18">
+    <row r="34" s="15" customFormat="1" spans="1:21">
       <c r="A34" s="15">
         <v>312</v>
       </c>
@@ -4145,7 +4151,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="35" s="13" customFormat="1" spans="1:17">
+    <row r="35" s="13" customFormat="1" spans="1:21">
       <c r="A35" s="13">
         <v>401</v>
       </c>
@@ -4195,7 +4201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="13" customFormat="1" spans="1:17">
+    <row r="36" s="13" customFormat="1" spans="1:21">
       <c r="A36" s="13">
         <v>402</v>
       </c>
@@ -4245,7 +4251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="13" customFormat="1" spans="1:17">
+    <row r="37" s="13" customFormat="1" spans="1:21">
       <c r="A37" s="13">
         <v>403</v>
       </c>
@@ -4298,7 +4304,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="24" customFormat="1" spans="1:17">
+    <row r="38" s="24" customFormat="1" spans="1:21">
       <c r="A38" s="24">
         <v>404</v>
       </c>
@@ -4410,7 +4416,7 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="13" customFormat="1" spans="1:17">
+    <row r="40" s="13" customFormat="1" spans="1:21">
       <c r="A40" s="13">
         <v>406</v>
       </c>
@@ -4463,7 +4469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:21">
       <c r="A41" s="13">
         <v>407</v>
       </c>
@@ -4519,7 +4525,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:21">
       <c r="A42" s="13">
         <v>408</v>
       </c>
@@ -4575,7 +4581,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:21">
       <c r="A43" s="13">
         <v>409</v>
       </c>
@@ -4631,7 +4637,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:21">
       <c r="A44" s="13">
         <v>410</v>
       </c>
@@ -4687,7 +4693,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:18">
+    <row r="45" customFormat="1" spans="1:21">
       <c r="A45" s="13">
         <v>411</v>
       </c>
@@ -4753,8 +4759,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="21.375" customWidth="1"/>
     <col min="3" max="3" width="34.875" customWidth="1"/>
@@ -4762,9 +4768,10 @@
     <col min="5" max="5" width="85.25" customWidth="1"/>
     <col min="6" max="6" width="54.25" customWidth="1"/>
     <col min="7" max="7" width="57.375" customWidth="1"/>
+    <col min="8" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4786,316 +4793,396 @@
       <c r="G1" s="1" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:5">
+      <c r="H1" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:5">
+        <v>299</v>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="H3" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>304</v>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>305</v>
+      </c>
+      <c r="C5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C5" t="s">
-        <v>301</v>
-      </c>
-      <c r="D5" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="H5" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>307</v>
+      </c>
+      <c r="H6" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>308</v>
+      </c>
+      <c r="C7" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" t="s">
         <v>307</v>
       </c>
-      <c r="C7" t="s">
-        <v>296</v>
-      </c>
-      <c r="D7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="H7" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>312</v>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" t="s">
+        <v>311</v>
+      </c>
+      <c r="E9" t="s">
         <v>312</v>
       </c>
-      <c r="C9" t="s">
-        <v>309</v>
-      </c>
-      <c r="D9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E9" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E10" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>307</v>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E11" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" spans="1:7">
+        <v>307</v>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" spans="1:8">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C12" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:7">
+        <v>321</v>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:8">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
-    </row>
-    <row r="14" ht="14.25" spans="1:7">
+      <c r="H13" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:8">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="C14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D14" t="s">
+        <v>303</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="C14" t="s">
-        <v>301</v>
-      </c>
-      <c r="D14" t="s">
-        <v>302</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="H14" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="2">
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D15" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:7">
+        <v>328</v>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:8">
       <c r="A16" s="2">
         <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D16" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>334</v>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:8">
       <c r="A17" s="2">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>335</v>
+      </c>
+      <c r="C17" t="s">
+        <v>317</v>
+      </c>
+      <c r="D17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2">
         <v>201</v>
       </c>
-      <c r="B17" t="s">
-        <v>334</v>
-      </c>
-      <c r="C17" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="B18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C18" t="s">
         <v>297</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:7">
-      <c r="A18" s="2">
+      <c r="D18" t="s">
+        <v>298</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:8">
+      <c r="A19" s="2">
         <v>202</v>
       </c>
-      <c r="B18" t="s">
-        <v>335</v>
-      </c>
-      <c r="C18" t="s">
-        <v>336</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="B19" t="s">
         <v>337</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="C19" t="s">
         <v>338</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="D19" t="s">
         <v>339</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>340</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5105,15 +5192,17 @@
     <hyperlink ref="E5" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E4" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E12" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="E16" r:id="rId4" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
-    <hyperlink ref="G16" r:id="rId5" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
-    <hyperlink ref="G12" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
-    <hyperlink ref="E18" r:id="rId7" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="G18" r:id="rId8" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
-    <hyperlink ref="E15" r:id="rId9" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E17" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="E13" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="E14" r:id="rId10" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="G12" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
+    <hyperlink ref="E19" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="G19" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
+    <hyperlink ref="E15" r:id="rId7" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E18" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E13" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="G16" r:id="rId9" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
+    <hyperlink ref="E16" r:id="rId10" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="E14" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E17" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
+    <hyperlink ref="G17" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5135,20 +5224,20 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -5170,16 +5259,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>292</v>
@@ -5190,16 +5279,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5207,16 +5296,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3" t="s">
         <v>350</v>
       </c>
-      <c r="C3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D3" t="s">
-        <v>348</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5224,16 +5313,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5241,16 +5330,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5258,16 +5347,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5275,16 +5364,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5292,16 +5381,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5309,16 +5398,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5326,16 +5415,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C10" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
@@ -5343,16 +5432,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:5">
@@ -5360,16 +5449,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>363</v>
-      </c>
       <c r="D12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
@@ -5377,16 +5466,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" t="s">
         <v>366</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="D13" t="s">
-        <v>364</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
@@ -5394,16 +5483,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:5">
@@ -5411,31 +5500,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D15" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:5">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:5">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:5">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:5">
       <c r="A20" s="2"/>
       <c r="B20" s="7"/>
     </row>
@@ -5444,17 +5533,17 @@
       <c r="B21" s="7"/>
       <c r="E21" s="4"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:5">
       <c r="A22" s="2"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:5">
       <c r="A23" s="2"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2"/>
       <c r="E24" s="4"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:5">
       <c r="A25" s="2"/>
     </row>
   </sheetData>
@@ -6156,7 +6245,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="18" customFormat="1" spans="2:2">
+    <row r="30" s="18" customFormat="1" spans="1:7">
       <c r="B30" s="19"/>
     </row>
   </sheetData>
@@ -6491,7 +6580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:7">
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
     </row>
@@ -6800,7 +6889,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:6">
+    <row r="12" customFormat="1" spans="1:8">
       <c r="A12">
         <v>211</v>
       </c>
@@ -6918,7 +7007,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>401</v>
       </c>
@@ -6938,7 +7027,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>402</v>
       </c>
@@ -6958,7 +7047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>403</v>
       </c>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="376">
   <si>
     <t>类型</t>
   </si>
@@ -586,6 +586,159 @@
     <t>工程车怪</t>
   </si>
   <si>
+    <t>幼虫怪</t>
+  </si>
+  <si>
+    <t>飞虫怪</t>
+  </si>
+  <si>
+    <t>绿色坦克怪</t>
+  </si>
+  <si>
+    <t>房虫怪</t>
+  </si>
+  <si>
+    <t>防空兵怪</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>消耗晶体矿</t>
+  </si>
+  <si>
+    <t>消耗燃气矿</t>
+  </si>
+  <si>
+    <t>初始HP</t>
+  </si>
+  <si>
+    <t>前置单位</t>
+  </si>
+  <si>
+    <t>耗时帧</t>
+  </si>
+  <si>
+    <t>f半边长</t>
+  </si>
+  <si>
+    <t>建造动作.名字或索引</t>
+  </si>
+  <si>
+    <t>建造动作.播放速度</t>
+  </si>
+  <si>
+    <t>建造动作.起始时刻秒</t>
+  </si>
+  <si>
+    <t>建造动作.结束时刻秒</t>
+  </si>
+  <si>
+    <t>兵营建造</t>
+  </si>
+  <si>
+    <t>入场语音</t>
+  </si>
+  <si>
+    <t>走路动作.名字或索引</t>
+  </si>
+  <si>
+    <t>走路动作.起始时刻秒</t>
+  </si>
+  <si>
+    <t>走路动作.结束时刻秒</t>
+  </si>
+  <si>
+    <t>普通走语音</t>
+  </si>
+  <si>
+    <t>强行走语音</t>
+  </si>
+  <si>
+    <t>语音/工程车准备就绪女声可爱版</t>
+  </si>
+  <si>
+    <t>语音/明白女声可爱版</t>
+  </si>
+  <si>
+    <t>语音/准备战斗男声正经版</t>
+  </si>
+  <si>
+    <t>run</t>
+  </si>
+  <si>
+    <t>语音/明白男声正经版</t>
+  </si>
+  <si>
+    <t>tfbRdy00</t>
+  </si>
+  <si>
+    <t>语音/ttardy00</t>
+  </si>
+  <si>
+    <t>语音/坦克明白</t>
+  </si>
+  <si>
+    <t>音效/zdrRdy00</t>
+  </si>
+  <si>
+    <t>音效/zdrYes00</t>
+  </si>
+  <si>
+    <t>音效/zdrYes01</t>
+  </si>
+  <si>
+    <t>语音/飞机明白</t>
+  </si>
+  <si>
+    <t>音效/zhyRdy00</t>
+  </si>
+  <si>
+    <t>音效/zhyYes00</t>
+  </si>
+  <si>
+    <t>音效/zhyYes01</t>
+  </si>
+  <si>
+    <t>音效/ZZeRdy00</t>
+  </si>
+  <si>
+    <t>音效/ZZeYes00</t>
+  </si>
+  <si>
+    <t>音效/ZZeYes01</t>
+  </si>
+  <si>
+    <t>Armature|Armature.002|Take 001|BaseLayer</t>
+  </si>
+  <si>
+    <t>音效/zovRdy00</t>
+  </si>
+  <si>
+    <t>音效/zovYes00</t>
+  </si>
+  <si>
+    <t>音效/zovYes01</t>
+  </si>
+  <si>
+    <t>音效/zmuRdy00</t>
+  </si>
+  <si>
+    <t>音效/zmuYes00</t>
+  </si>
+  <si>
+    <t>音效/zmuYes01</t>
+  </si>
+  <si>
+    <t>语音/TMdRdy00</t>
+  </si>
+  <si>
+    <t>语音/TMdYes00</t>
+  </si>
+  <si>
+    <t>语音/TMdYes01</t>
+  </si>
+  <si>
     <t>幼虫怪,</t>
   </si>
   <si>
@@ -593,150 +746,6 @@
   </si>
   <si>
     <t>绿色坦克怪,</t>
-  </si>
-  <si>
-    <t>房虫怪</t>
-  </si>
-  <si>
-    <t>防空兵怪</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>消耗晶体矿</t>
-  </si>
-  <si>
-    <t>消耗燃气矿</t>
-  </si>
-  <si>
-    <t>初始HP</t>
-  </si>
-  <si>
-    <t>前置单位</t>
-  </si>
-  <si>
-    <t>耗时帧</t>
-  </si>
-  <si>
-    <t>f半边长</t>
-  </si>
-  <si>
-    <t>建造动作.名字或索引</t>
-  </si>
-  <si>
-    <t>建造动作.播放速度</t>
-  </si>
-  <si>
-    <t>建造动作.起始时刻秒</t>
-  </si>
-  <si>
-    <t>建造动作.结束时刻秒</t>
-  </si>
-  <si>
-    <t>兵营建造</t>
-  </si>
-  <si>
-    <t>入场语音</t>
-  </si>
-  <si>
-    <t>走路动作.名字或索引</t>
-  </si>
-  <si>
-    <t>走路动作.起始时刻秒</t>
-  </si>
-  <si>
-    <t>走路动作.结束时刻秒</t>
-  </si>
-  <si>
-    <t>普通走语音</t>
-  </si>
-  <si>
-    <t>强行走语音</t>
-  </si>
-  <si>
-    <t>语音/工程车准备就绪女声可爱版</t>
-  </si>
-  <si>
-    <t>语音/明白女声可爱版</t>
-  </si>
-  <si>
-    <t>语音/准备战斗男声正经版</t>
-  </si>
-  <si>
-    <t>run</t>
-  </si>
-  <si>
-    <t>语音/明白男声正经版</t>
-  </si>
-  <si>
-    <t>tfbRdy00</t>
-  </si>
-  <si>
-    <t>语音/ttardy00</t>
-  </si>
-  <si>
-    <t>语音/坦克明白</t>
-  </si>
-  <si>
-    <t>音效/zdrRdy00</t>
-  </si>
-  <si>
-    <t>音效/zdrYes00</t>
-  </si>
-  <si>
-    <t>音效/zdrYes01</t>
-  </si>
-  <si>
-    <t>语音/飞机明白</t>
-  </si>
-  <si>
-    <t>音效/zhyRdy00</t>
-  </si>
-  <si>
-    <t>音效/zhyYes00</t>
-  </si>
-  <si>
-    <t>音效/zhyYes01</t>
-  </si>
-  <si>
-    <t>音效/ZZeRdy00</t>
-  </si>
-  <si>
-    <t>音效/ZZeYes00</t>
-  </si>
-  <si>
-    <t>音效/ZZeYes01</t>
-  </si>
-  <si>
-    <t>Armature|Armature.002|Take 001|BaseLayer</t>
-  </si>
-  <si>
-    <t>音效/zovRdy00</t>
-  </si>
-  <si>
-    <t>音效/zovYes00</t>
-  </si>
-  <si>
-    <t>音效/zovYes01</t>
-  </si>
-  <si>
-    <t>音效/zmuRdy00</t>
-  </si>
-  <si>
-    <t>音效/zmuYes00</t>
-  </si>
-  <si>
-    <t>音效/zmuYes01</t>
-  </si>
-  <si>
-    <t>语音/TMdRdy00</t>
-  </si>
-  <si>
-    <t>语音/TMdYes00</t>
-  </si>
-  <si>
-    <t>语音/TMdYes01</t>
   </si>
   <si>
     <t>f警戒距离</t>
@@ -4779,22 +4788,22 @@
         <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:8">
@@ -4802,16 +4811,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H2" s="2" t="b">
         <v>0</v>
@@ -4822,16 +4831,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C3" t="s">
         <v>300</v>
       </c>
-      <c r="C3" t="s">
-        <v>297</v>
-      </c>
       <c r="D3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H3" s="2" t="b">
         <v>0</v>
@@ -4842,16 +4851,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C4" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H4" s="2" t="b">
         <v>0</v>
@@ -4862,16 +4871,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
         <v>305</v>
       </c>
-      <c r="C5" t="s">
-        <v>302</v>
-      </c>
       <c r="D5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="H5" s="2" t="b">
         <v>0</v>
@@ -4882,16 +4891,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H6" s="2" t="b">
         <v>0</v>
@@ -4902,16 +4911,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C7" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D7" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H7" s="2" t="b">
         <v>0</v>
@@ -4922,16 +4931,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C8" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D8" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H8" s="2" t="b">
         <v>0</v>
@@ -4942,16 +4951,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
         <v>313</v>
       </c>
-      <c r="C9" t="s">
-        <v>310</v>
-      </c>
       <c r="D9" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E9" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H9" s="2" t="b">
         <v>0</v>
@@ -4962,16 +4971,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E10" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H10" s="2" t="b">
         <v>0</v>
@@ -4982,16 +4991,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H11" s="2" t="b">
         <v>0</v>
@@ -5002,22 +5011,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C12" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D12" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H12" s="2" t="b">
         <v>0</v>
@@ -5028,16 +5037,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D13" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="9"/>
@@ -5050,16 +5059,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C14" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D14" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
@@ -5072,16 +5081,16 @@
         <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="H15" s="2" t="b">
         <v>0</v>
@@ -5092,22 +5101,22 @@
         <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H16" s="2" t="b">
         <v>0</v>
@@ -5118,22 +5127,22 @@
         <v>103</v>
       </c>
       <c r="B17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C17" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D17" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="H17" s="2" t="b">
         <v>1</v>
@@ -5144,16 +5153,16 @@
         <v>201</v>
       </c>
       <c r="B18" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C18" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="H18" s="2" t="b">
         <v>0</v>
@@ -5164,22 +5173,22 @@
         <v>202</v>
       </c>
       <c r="B19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C19" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="D19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H19" s="2" t="b">
         <v>0</v>
@@ -5217,7 +5226,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>187</v>
@@ -5229,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5237,7 +5246,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5259,19 +5268,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5279,16 +5288,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5296,16 +5305,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C3" t="s">
         <v>352</v>
       </c>
-      <c r="C3" t="s">
-        <v>349</v>
-      </c>
       <c r="D3" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5313,16 +5322,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C4" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -5330,16 +5339,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -5347,16 +5356,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C6" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D6" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -5364,16 +5373,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C7" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -5381,16 +5390,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D8" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5398,16 +5407,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C9" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5415,16 +5424,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C10" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D10" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
@@ -5432,16 +5441,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:5">
@@ -5449,16 +5458,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D12" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
@@ -5466,16 +5475,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
+        <v>371</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>365</v>
-      </c>
       <c r="D13" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
@@ -5483,16 +5492,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" t="s">
         <v>369</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D14" t="s">
-        <v>366</v>
-      </c>
       <c r="E14" s="4" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:5">
@@ -5500,16 +5509,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7150,7 +7159,7 @@
         <v>407</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="C23" t="s">
         <v>84</v>
@@ -7176,7 +7185,7 @@
         <v>408</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C24" t="s">
         <v>227</v>
@@ -7202,7 +7211,7 @@
         <v>409</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="C25" t="s">
         <v>213</v>
@@ -7324,61 +7333,61 @@
         <v>187</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J1" s="11" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="P1" s="14" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="R1" s="14" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="T1" s="14" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="U1" s="14" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -7422,7 +7431,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -7463,7 +7472,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -7475,7 +7484,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -7484,7 +7493,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -7540,7 +7549,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -7584,25 +7593,25 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
+        <v>260</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
         <v>257</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>254</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -7643,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -7658,7 +7667,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -7711,7 +7720,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -7720,7 +7729,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -7761,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -7773,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -7782,7 +7791,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -7823,7 +7832,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -7838,7 +7847,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -7879,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -7894,7 +7903,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -7938,7 +7947,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -7953,7 +7962,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -8006,7 +8015,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -8106,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -8115,7 +8124,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -8171,7 +8180,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -8212,7 +8221,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -8224,7 +8233,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -8233,7 +8242,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -8522,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -8531,7 +8540,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -8985,7 +8994,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -8997,7 +9006,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -9006,7 +9015,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -9047,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -9062,7 +9071,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -9103,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -9118,7 +9127,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -9159,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -9171,7 +9180,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -9180,7 +9189,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -9236,7 +9245,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -9292,7 +9301,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -9312,7 +9321,7 @@
         <v>407</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -9333,7 +9342,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -9348,7 +9357,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -9368,7 +9377,7 @@
         <v>408</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -9398,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -9407,7 +9416,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -9427,7 +9436,7 @@
         <v>409</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -9451,7 +9460,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -9466,7 +9475,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -9557,7 +9566,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -9569,7 +9578,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="O39">
         <v>2.5</v>
@@ -9578,7 +9587,7 @@
         <v>530</v>
       </c>
       <c r="Q39" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -9613,7 +9622,7 @@
         <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -9665,7 +9674,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -9676,7 +9685,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -9731,7 +9740,7 @@
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="C12">
         <v>10</v>
@@ -9742,7 +9751,7 @@
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C13">
         <v>20</v>
@@ -9753,7 +9762,7 @@
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -9804,16 +9813,16 @@
         <v>187</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>188</v>
@@ -9830,7 +9839,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -9856,7 +9865,7 @@
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -9882,7 +9891,7 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -9908,7 +9917,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -9934,7 +9943,7 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -9960,7 +9969,7 @@
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -9986,7 +9995,7 @@
         <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -10012,7 +10021,7 @@
         <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -10104,19 +10113,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B1" t="s">
         <v>187</v>
       </c>
       <c r="C1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -10124,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -10141,7 +10150,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -10158,7 +10167,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -10175,7 +10184,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -10192,7 +10201,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -10209,7 +10218,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -10226,7 +10235,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="377">
   <si>
     <t>类型</t>
   </si>
@@ -1084,6 +1084,9 @@
   </si>
   <si>
     <t>新手训练_反防空战_虫</t>
+  </si>
+  <si>
+    <t>新手训练_苔蔓回血_虫</t>
   </si>
   <si>
     <t>四方对战</t>
@@ -4768,7 +4771,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="21.375" customWidth="1"/>
@@ -5076,47 +5079,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" ht="14.25" spans="1:8">
       <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2">
         <v>101</v>
       </c>
-      <c r="B15" t="s">
-        <v>328</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="B16" t="s">
         <v>329</v>
       </c>
-      <c r="D15" t="s">
+      <c r="C16" t="s">
         <v>330</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="D16" t="s">
         <v>331</v>
       </c>
-      <c r="H15" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="2">
-        <v>102</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="E16" s="3" t="s">
         <v>332</v>
-      </c>
-      <c r="C16" t="s">
-        <v>333</v>
-      </c>
-      <c r="D16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>337</v>
       </c>
       <c r="H16" s="2" t="b">
         <v>0</v>
@@ -5124,73 +5123,99 @@
     </row>
     <row r="17" ht="14.25" spans="1:8">
       <c r="A17" s="2">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>333</v>
+      </c>
+      <c r="C17" t="s">
+        <v>334</v>
+      </c>
+      <c r="D17" t="s">
+        <v>335</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:8">
+      <c r="A18" s="2">
         <v>103</v>
-      </c>
-      <c r="B17" t="s">
-        <v>338</v>
-      </c>
-      <c r="C17" t="s">
-        <v>320</v>
-      </c>
-      <c r="D17" t="s">
-        <v>321</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="H17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="2">
-        <v>201</v>
       </c>
       <c r="B18" t="s">
         <v>339</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="D18" t="s">
-        <v>301</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="H18" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
         <v>340</v>
       </c>
       <c r="C19" t="s">
+        <v>300</v>
+      </c>
+      <c r="D19" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:8">
+      <c r="A20" s="2">
+        <v>202</v>
+      </c>
+      <c r="B20" t="s">
         <v>341</v>
       </c>
-      <c r="D19" t="s">
+      <c r="C20" t="s">
         <v>342</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="D20" t="s">
         <v>343</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="E20" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="F20" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="H19" s="2" t="b">
+      <c r="G20" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="H20" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5202,16 +5227,17 @@
     <hyperlink ref="E4" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E12" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
     <hyperlink ref="G12" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
-    <hyperlink ref="E19" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="G19" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
-    <hyperlink ref="E15" r:id="rId7" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E18" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E20" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="G20" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
+    <hyperlink ref="E16" r:id="rId7" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E19" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
     <hyperlink ref="E13" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="G16" r:id="rId9" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
-    <hyperlink ref="E16" r:id="rId10" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="G17" r:id="rId9" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
+    <hyperlink ref="E17" r:id="rId10" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
     <hyperlink ref="E14" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="E17" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="G17" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
+    <hyperlink ref="E18" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
+    <hyperlink ref="G18" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
+    <hyperlink ref="E15" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5238,7 +5264,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5246,7 +5272,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5268,16 +5294,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>295</v>
@@ -5288,16 +5314,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5305,16 +5331,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5322,13 +5348,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E4" t="s">
         <v>310</v>
@@ -5339,13 +5365,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>315</v>
@@ -5356,13 +5382,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>302</v>
@@ -5373,13 +5399,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>307</v>
@@ -5390,16 +5416,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5407,16 +5433,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5424,16 +5450,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
@@ -5441,13 +5467,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>322</v>
@@ -5458,16 +5484,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" t="s">
         <v>370</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D12" t="s">
-        <v>369</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
@@ -5475,16 +5501,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
@@ -5492,13 +5518,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>326</v>
@@ -5509,16 +5535,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:5">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="378">
   <si>
     <t>类型</t>
   </si>
@@ -1087,6 +1087,9 @@
   </si>
   <si>
     <t>新手训练_苔蔓回血_虫</t>
+  </si>
+  <si>
+    <t>新手训练_躲坦克前摇_人</t>
   </si>
   <si>
     <t>四方对战</t>
@@ -4771,7 +4774,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="21.375" customWidth="1"/>
@@ -5101,47 +5104,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" ht="14.25" spans="1:8">
       <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" t="s">
+        <v>305</v>
+      </c>
+      <c r="D16" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2">
         <v>101</v>
       </c>
-      <c r="B16" t="s">
-        <v>329</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="B17" t="s">
         <v>330</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C17" t="s">
         <v>331</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="D17" t="s">
         <v>332</v>
       </c>
-      <c r="H16" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="1:8">
-      <c r="A17" s="2">
-        <v>102</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="E17" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="C17" t="s">
-        <v>334</v>
-      </c>
-      <c r="D17" t="s">
-        <v>335</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>338</v>
       </c>
       <c r="H17" s="2" t="b">
         <v>0</v>
@@ -5149,73 +5148,99 @@
     </row>
     <row r="18" ht="14.25" spans="1:8">
       <c r="A18" s="2">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" t="s">
+        <v>335</v>
+      </c>
+      <c r="D18" t="s">
+        <v>336</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:8">
+      <c r="A19" s="2">
         <v>103</v>
-      </c>
-      <c r="B18" t="s">
-        <v>339</v>
-      </c>
-      <c r="C18" t="s">
-        <v>320</v>
-      </c>
-      <c r="D18" t="s">
-        <v>321</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="H18" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="2">
-        <v>201</v>
       </c>
       <c r="B19" t="s">
         <v>340</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="D19" t="s">
-        <v>301</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>324</v>
       </c>
       <c r="H19" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" spans="1:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
         <v>341</v>
       </c>
       <c r="C20" t="s">
+        <v>300</v>
+      </c>
+      <c r="D20" t="s">
+        <v>301</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="1:8">
+      <c r="A21" s="2">
+        <v>202</v>
+      </c>
+      <c r="B21" t="s">
         <v>342</v>
       </c>
-      <c r="D20" t="s">
+      <c r="C21" t="s">
         <v>343</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="D21" t="s">
         <v>344</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="E21" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="F21" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="H20" s="2" t="b">
+      <c r="G21" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="H21" s="2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5227,17 +5252,18 @@
     <hyperlink ref="E4" r:id="rId2" display="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3" tooltip="https://www.rtsgame.online/music/suno重工业浪漫低音质.mp3"/>
     <hyperlink ref="E12" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
     <hyperlink ref="G12" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
-    <hyperlink ref="E20" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
-    <hyperlink ref="G20" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
-    <hyperlink ref="E16" r:id="rId7" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
-    <hyperlink ref="E19" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E21" r:id="rId5" display="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Desert - 低音质.mp3"/>
+    <hyperlink ref="G21" r:id="rId6" display="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu_boss2_高清.png"/>
+    <hyperlink ref="E17" r:id="rId7" display="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3" tooltip="https://www.rtsgame.online/music/电波暴击 - SPACE FIGHT 低音质.mp3"/>
+    <hyperlink ref="E20" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
     <hyperlink ref="E13" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="G17" r:id="rId9" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
-    <hyperlink ref="E17" r:id="rId10" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
+    <hyperlink ref="G18" r:id="rId9" display="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png" tooltip="https://www.rtsgame.online/图片/地图/ditu4_1_高清.png"/>
+    <hyperlink ref="E18" r:id="rId10" display="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Follow The Light - 低音质.mp3"/>
     <hyperlink ref="E14" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
-    <hyperlink ref="E18" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
-    <hyperlink ref="G18" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
+    <hyperlink ref="E19" r:id="rId3" display="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3" tooltip="https://www.rtsgame.online/music/乌鸦Producer - Sample Killer - 低音质.mp3"/>
+    <hyperlink ref="G19" r:id="rId4" display="https://www.rtsgame.online/图片/地图/ditu4_8_高清.png"/>
     <hyperlink ref="E15" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
+    <hyperlink ref="E16" r:id="rId8" display="https://www.rtsgame.online/music/星联-已注册版权-獬羽柏-低音质 .mp3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5264,7 +5290,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5272,7 +5298,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -5294,16 +5320,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>295</v>
@@ -5314,16 +5340,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5331,16 +5357,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5348,13 +5374,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E4" t="s">
         <v>310</v>
@@ -5365,13 +5391,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>315</v>
@@ -5382,13 +5408,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>302</v>
@@ -5399,13 +5425,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>307</v>
@@ -5416,16 +5442,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5433,16 +5459,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -5450,16 +5476,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
@@ -5467,13 +5493,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>322</v>
@@ -5484,16 +5510,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12" t="s">
         <v>371</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D12" t="s">
-        <v>370</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
@@ -5501,16 +5527,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D13" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
@@ -5518,13 +5544,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>326</v>
@@ -5535,16 +5561,16 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D15" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:5">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="9"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="单位" sheetId="3" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="战局" sheetId="11" r:id="rId10"/>
     <sheet name="服务器区" sheetId="12" r:id="rId11"/>
     <sheet name="音乐" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="399">
   <si>
     <t>类型</t>
   </si>
@@ -1287,6 +1288,69 @@
   <si>
     <t>电波暴击(QQ 1106551898)</t>
   </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>中文</t>
+  </si>
+  <si>
+    <t>英文</t>
+  </si>
+  <si>
+    <t>Key版本不匹配</t>
+  </si>
+  <si>
+    <t>版本不匹配</t>
+  </si>
+  <si>
+    <t>Version Mismatch</t>
+  </si>
+  <si>
+    <t>Key 进来了</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 进来了</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Entered</t>
+  </si>
+  <si>
+    <t>Key 离开了</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 离开了</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Left</t>
+  </si>
+  <si>
+    <t>Key 说</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 说</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Said</t>
+  </si>
+  <si>
+    <t>Key敌人</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Key请稍后再说</t>
+  </si>
+  <si>
+    <t>请稍后再说</t>
+  </si>
+  <si>
+    <t>Please speak again later.</t>
+  </si>
 </sst>
 </file>
 
@@ -1298,10 +1362,53 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFE394DC"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2329"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1337,17 +1444,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFE394DC"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="4"/>
@@ -1358,19 +1454,6 @@
     <font>
       <sz val="11"/>
       <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1508,12 +1591,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FFE394DC"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -1854,157 +1931,151 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2012,13 +2083,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -2027,52 +2119,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2389,7 +2481,7 @@
   <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="8" customWidth="1"/>
     <col min="4" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="7" width="30.75" customWidth="1"/>
     <col min="8" max="9" width="44.875" customWidth="1"/>
@@ -2400,32 +2492,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="21" customFormat="1" spans="1:18">
-      <c r="A1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="21" t="s">
+    <row r="1" s="26" customFormat="1" spans="1:18">
+      <c r="A1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -2434,42 +2526,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="21" t="s">
+      <c r="L1" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="M1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="21" t="s">
+      <c r="N1" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="21" t="s">
+      <c r="Q1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="21" t="s">
+      <c r="R1" s="26" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="22" customFormat="1" spans="1:18">
-      <c r="A2" s="22">
-        <v>1</v>
-      </c>
-      <c r="B2" s="25" t="s">
+    <row r="2" s="27" customFormat="1" spans="1:18">
+      <c r="A2" s="27">
+        <v>1</v>
+      </c>
+      <c r="B2" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="22">
-        <v>0</v>
-      </c>
-      <c r="G2" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="22">
+      <c r="C2" s="27">
+        <v>0</v>
+      </c>
+      <c r="G2" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="27">
         <v>1</v>
       </c>
       <c r="J2">
@@ -2478,33 +2570,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="22">
-        <v>1</v>
-      </c>
-      <c r="N2" s="22">
-        <v>0</v>
-      </c>
-      <c r="O2" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="22" customFormat="1" spans="1:18">
-      <c r="A3" s="22">
+      <c r="M2" s="27">
+        <v>1</v>
+      </c>
+      <c r="N2" s="27">
+        <v>0</v>
+      </c>
+      <c r="O2" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="27" customFormat="1" spans="1:18">
+      <c r="A3" s="27">
         <v>2</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="22">
-        <v>0</v>
-      </c>
-      <c r="G3" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="22">
+      <c r="C3" s="27">
+        <v>0</v>
+      </c>
+      <c r="G3" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="27">
         <v>1</v>
       </c>
       <c r="J3">
@@ -2513,36 +2605,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="22">
-        <v>1</v>
-      </c>
-      <c r="N3" s="22">
-        <v>0</v>
-      </c>
-      <c r="O3" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="15" customFormat="1" spans="1:18">
-      <c r="A4" s="15">
+      <c r="M3" s="27">
+        <v>1</v>
+      </c>
+      <c r="N3" s="27">
+        <v>0</v>
+      </c>
+      <c r="O3" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="20" customFormat="1" spans="1:18">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="20">
         <v>2</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="22">
+      <c r="G4" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="27">
         <v>1</v>
       </c>
       <c r="J4">
@@ -2551,36 +2643,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="22">
-        <v>1</v>
-      </c>
-      <c r="N4" s="22">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="15" customFormat="1" spans="1:18">
-      <c r="A5" s="15">
+      <c r="M4" s="27">
+        <v>1</v>
+      </c>
+      <c r="N4" s="27">
+        <v>0</v>
+      </c>
+      <c r="O4" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="20" customFormat="1" spans="1:18">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="15">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="20">
+        <v>0</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="22">
+      <c r="G5" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="27">
         <v>1</v>
       </c>
       <c r="J5">
@@ -2589,48 +2681,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="22">
-        <v>1</v>
-      </c>
-      <c r="N5" s="22">
-        <v>0</v>
-      </c>
-      <c r="O5" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="15">
-        <v>0</v>
-      </c>
-      <c r="R5" s="15" t="s">
+      <c r="M5" s="27">
+        <v>1</v>
+      </c>
+      <c r="N5" s="27">
+        <v>0</v>
+      </c>
+      <c r="O5" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>0</v>
+      </c>
+      <c r="R5" s="20" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="23" customFormat="1" spans="1:18">
-      <c r="A6" s="23">
+    <row r="6" s="28" customFormat="1" spans="1:18">
+      <c r="A6" s="28">
         <v>101</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="23">
-        <v>0</v>
-      </c>
-      <c r="D6" s="23" t="s">
+      <c r="C6" s="28">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="22" t="b">
+      <c r="G6" s="27" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="27">
         <v>1</v>
       </c>
       <c r="J6">
@@ -2642,39 +2734,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="22">
-        <v>1</v>
-      </c>
-      <c r="N6" s="22">
-        <v>0</v>
-      </c>
-      <c r="O6" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="23" customFormat="1" spans="1:18">
-      <c r="A7" s="23">
+      <c r="M6" s="27">
+        <v>1</v>
+      </c>
+      <c r="N6" s="27">
+        <v>0</v>
+      </c>
+      <c r="O6" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="28" customFormat="1" spans="1:18">
+      <c r="A7" s="28">
         <v>102</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="23">
-        <v>0</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="C7" s="28">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="22">
+      <c r="G7" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="27">
         <v>1</v>
       </c>
       <c r="J7">
@@ -2683,16 +2775,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="22">
-        <v>1</v>
-      </c>
-      <c r="N7" s="22">
-        <v>0</v>
-      </c>
-      <c r="O7" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="23">
+      <c r="M7" s="27">
+        <v>1</v>
+      </c>
+      <c r="N7" s="27">
+        <v>0</v>
+      </c>
+      <c r="O7" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="28">
         <v>0</v>
       </c>
     </row>
@@ -2700,7 +2792,7 @@
       <c r="A8">
         <v>201</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C8">
@@ -2715,13 +2807,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="22" t="b">
+      <c r="G8" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="27">
         <v>1</v>
       </c>
       <c r="J8">
@@ -2733,13 +2825,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="22">
-        <v>1</v>
-      </c>
-      <c r="N8" s="22">
-        <v>0</v>
-      </c>
-      <c r="O8" s="22">
+      <c r="M8" s="27">
+        <v>1</v>
+      </c>
+      <c r="N8" s="27">
+        <v>0</v>
+      </c>
+      <c r="O8" s="27">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -2752,59 +2844,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="14" customFormat="1" spans="1:18">
-      <c r="A9" s="14">
+    <row r="9" s="19" customFormat="1" spans="1:18">
+      <c r="A9" s="19">
         <v>202</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="14">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="19">
+        <v>1</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="24">
-        <v>1</v>
-      </c>
-      <c r="J9" s="14">
-        <v>0</v>
-      </c>
-      <c r="K9" s="14">
+      <c r="I9" s="29">
+        <v>1</v>
+      </c>
+      <c r="J9" s="19">
+        <v>0</v>
+      </c>
+      <c r="K9" s="19">
         <v>2</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="24">
-        <v>1</v>
-      </c>
-      <c r="N9" s="24">
-        <v>0</v>
-      </c>
-      <c r="O9" s="24">
-        <v>0</v>
-      </c>
-      <c r="P9" s="14" t="s">
+      <c r="M9" s="29">
+        <v>1</v>
+      </c>
+      <c r="N9" s="29">
+        <v>0</v>
+      </c>
+      <c r="O9" s="29">
+        <v>0</v>
+      </c>
+      <c r="P9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="19">
         <v>3</v>
       </c>
-      <c r="R9" s="14" t="s">
+      <c r="R9" s="19" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2812,7 +2904,7 @@
       <c r="A10">
         <v>203</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C10">
@@ -2827,13 +2919,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="22" t="b">
+      <c r="G10" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="27">
         <v>1</v>
       </c>
       <c r="J10">
@@ -2845,13 +2937,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="22">
-        <v>1</v>
-      </c>
-      <c r="N10" s="22">
-        <v>0</v>
-      </c>
-      <c r="O10" s="22">
+      <c r="M10" s="27">
+        <v>1</v>
+      </c>
+      <c r="N10" s="27">
+        <v>0</v>
+      </c>
+      <c r="O10" s="27">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -2868,7 +2960,7 @@
       <c r="A11">
         <v>204</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C11">
@@ -2880,13 +2972,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="22" t="b">
+      <c r="G11" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="27">
         <v>1</v>
       </c>
       <c r="J11">
@@ -2898,13 +2990,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="22">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22">
-        <v>0</v>
-      </c>
-      <c r="O11" s="22">
+      <c r="M11" s="27">
+        <v>1</v>
+      </c>
+      <c r="N11" s="27">
+        <v>0</v>
+      </c>
+      <c r="O11" s="27">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -2921,7 +3013,7 @@
       <c r="A12">
         <v>205</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C12">
@@ -2936,13 +3028,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="22" t="b">
+      <c r="G12" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="27">
         <v>1</v>
       </c>
       <c r="J12">
@@ -2954,13 +3046,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="22">
-        <v>1</v>
-      </c>
-      <c r="N12" s="22">
-        <v>0</v>
-      </c>
-      <c r="O12" s="22">
+      <c r="M12" s="27">
+        <v>1</v>
+      </c>
+      <c r="N12" s="27">
+        <v>0</v>
+      </c>
+      <c r="O12" s="27">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -2977,7 +3069,7 @@
       <c r="A13">
         <v>206</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C13">
@@ -2992,13 +3084,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="22" t="b">
+      <c r="G13" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="27">
         <v>1</v>
       </c>
       <c r="J13">
@@ -3007,16 +3099,16 @@
       <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13" s="8" t="s">
+      <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="22">
-        <v>1</v>
-      </c>
-      <c r="N13" s="22">
-        <v>1</v>
-      </c>
-      <c r="O13" s="22">
+      <c r="M13" s="27">
+        <v>1</v>
+      </c>
+      <c r="N13" s="27">
+        <v>1</v>
+      </c>
+      <c r="O13" s="27">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -3033,7 +3125,7 @@
       <c r="A14">
         <v>207</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C14">
@@ -3045,16 +3137,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="22" t="b">
+      <c r="G14" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="27">
         <v>1</v>
       </c>
       <c r="J14">
@@ -3066,13 +3158,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="22">
-        <v>1</v>
-      </c>
-      <c r="N14" s="22">
-        <v>0</v>
-      </c>
-      <c r="O14" s="22">
+      <c r="M14" s="27">
+        <v>1</v>
+      </c>
+      <c r="N14" s="27">
+        <v>0</v>
+      </c>
+      <c r="O14" s="27">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -3089,7 +3181,7 @@
       <c r="A15">
         <v>208</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C15">
@@ -3101,16 +3193,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="22" t="b">
+      <c r="G15" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="27">
         <v>1</v>
       </c>
       <c r="J15">
@@ -3122,13 +3214,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="22">
-        <v>1</v>
-      </c>
-      <c r="N15" s="22">
-        <v>0</v>
-      </c>
-      <c r="O15" s="22">
+      <c r="M15" s="27">
+        <v>1</v>
+      </c>
+      <c r="N15" s="27">
+        <v>0</v>
+      </c>
+      <c r="O15" s="27">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -3145,7 +3237,7 @@
       <c r="A16">
         <v>209</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C16">
@@ -3160,13 +3252,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="22" t="b">
+      <c r="G16" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="27">
         <v>1</v>
       </c>
       <c r="J16">
@@ -3178,13 +3270,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="22">
-        <v>1</v>
-      </c>
-      <c r="N16" s="22">
-        <v>0</v>
-      </c>
-      <c r="O16" s="22">
+      <c r="M16" s="27">
+        <v>1</v>
+      </c>
+      <c r="N16" s="27">
+        <v>0</v>
+      </c>
+      <c r="O16" s="27">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -3201,7 +3293,7 @@
       <c r="A17">
         <v>210</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C17">
@@ -3216,13 +3308,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="22" t="b">
+      <c r="G17" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="27">
         <v>1</v>
       </c>
       <c r="J17">
@@ -3234,13 +3326,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="22">
-        <v>1</v>
-      </c>
-      <c r="N17" s="22">
-        <v>0</v>
-      </c>
-      <c r="O17" s="22">
+      <c r="M17" s="27">
+        <v>1</v>
+      </c>
+      <c r="N17" s="27">
+        <v>0</v>
+      </c>
+      <c r="O17" s="27">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -3257,7 +3349,7 @@
       <c r="A18">
         <v>211</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C18">
@@ -3266,10 +3358,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="22">
+      <c r="G18" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27">
         <v>1</v>
       </c>
       <c r="J18">
@@ -3278,13 +3370,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="22">
-        <v>1</v>
-      </c>
-      <c r="N18" s="22">
-        <v>0</v>
-      </c>
-      <c r="O18" s="22">
+      <c r="M18" s="27">
+        <v>1</v>
+      </c>
+      <c r="N18" s="27">
+        <v>0</v>
+      </c>
+      <c r="O18" s="27">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -3295,7 +3387,7 @@
       <c r="A19">
         <v>212</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C19">
@@ -3310,13 +3402,13 @@
       <c r="F19" t="s">
         <v>97</v>
       </c>
-      <c r="G19" s="22" t="b">
+      <c r="G19" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>100</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="27">
         <v>1</v>
       </c>
       <c r="J19">
@@ -3328,13 +3420,13 @@
       <c r="L19" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="22">
-        <v>1</v>
-      </c>
-      <c r="N19" s="22">
-        <v>0</v>
-      </c>
-      <c r="O19" s="22">
+      <c r="M19" s="27">
+        <v>1</v>
+      </c>
+      <c r="N19" s="27">
+        <v>0</v>
+      </c>
+      <c r="O19" s="27">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -3351,7 +3443,7 @@
       <c r="A20">
         <v>213</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C20">
@@ -3366,13 +3458,13 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="22" t="b">
+      <c r="G20" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="27">
         <v>1</v>
       </c>
       <c r="J20">
@@ -3384,13 +3476,13 @@
       <c r="L20" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="22">
-        <v>1</v>
-      </c>
-      <c r="N20" s="22">
-        <v>0</v>
-      </c>
-      <c r="O20" s="22">
+      <c r="M20" s="27">
+        <v>1</v>
+      </c>
+      <c r="N20" s="27">
+        <v>0</v>
+      </c>
+      <c r="O20" s="27">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -3407,7 +3499,7 @@
       <c r="A21">
         <v>214</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C21">
@@ -3422,13 +3514,13 @@
       <c r="F21" t="s">
         <v>113</v>
       </c>
-      <c r="G21" s="22" t="b">
+      <c r="G21" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="27">
         <v>1</v>
       </c>
       <c r="J21">
@@ -3440,13 +3532,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="22">
-        <v>1</v>
-      </c>
-      <c r="N21" s="22">
-        <v>0</v>
-      </c>
-      <c r="O21" s="22">
+      <c r="M21" s="27">
+        <v>1</v>
+      </c>
+      <c r="N21" s="27">
+        <v>0</v>
+      </c>
+      <c r="O21" s="27">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -3463,7 +3555,7 @@
       <c r="A22">
         <v>215</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C22">
@@ -3478,13 +3570,13 @@
       <c r="F22" t="s">
         <v>118</v>
       </c>
-      <c r="G22" s="22" t="b">
+      <c r="G22" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="27">
         <v>1</v>
       </c>
       <c r="J22">
@@ -3496,13 +3588,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="22">
-        <v>1</v>
-      </c>
-      <c r="N22" s="22">
-        <v>0</v>
-      </c>
-      <c r="O22" s="22">
+      <c r="M22" s="27">
+        <v>1</v>
+      </c>
+      <c r="N22" s="27">
+        <v>0</v>
+      </c>
+      <c r="O22" s="27">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -3515,32 +3607,32 @@
         <v>119</v>
       </c>
     </row>
-    <row r="23" s="15" customFormat="1" spans="1:18">
-      <c r="A23" s="15">
+    <row r="23" s="20" customFormat="1" spans="1:18">
+      <c r="A23" s="20">
         <v>301</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="s">
+      <c r="C23" s="20">
+        <v>1</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="G23" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15" t="s">
+      <c r="G23" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="27">
         <v>1</v>
       </c>
       <c r="J23">
@@ -3549,54 +3641,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="15" t="s">
+      <c r="L23" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="M23" s="22">
-        <v>1</v>
-      </c>
-      <c r="N23" s="22">
-        <v>0</v>
-      </c>
-      <c r="O23" s="22">
-        <v>0</v>
-      </c>
-      <c r="P23" s="15" t="s">
+      <c r="M23" s="27">
+        <v>1</v>
+      </c>
+      <c r="N23" s="27">
+        <v>0</v>
+      </c>
+      <c r="O23" s="27">
+        <v>0</v>
+      </c>
+      <c r="P23" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="20">
         <v>3</v>
       </c>
-      <c r="R23" s="15" t="s">
+      <c r="R23" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="24" s="15" customFormat="1" spans="1:18">
-      <c r="A24" s="15">
+    <row r="24" s="20" customFormat="1" spans="1:18">
+      <c r="A24" s="20">
         <v>302</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="15">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="s">
+      <c r="C24" s="20">
+        <v>1</v>
+      </c>
+      <c r="D24" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="15" t="s">
+      <c r="G24" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="27">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -3605,51 +3697,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="15" t="s">
+      <c r="L24" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="M24" s="22">
-        <v>1</v>
-      </c>
-      <c r="N24" s="22">
-        <v>0</v>
-      </c>
-      <c r="O24" s="22">
-        <v>0</v>
-      </c>
-      <c r="P24" s="15" t="s">
+      <c r="M24" s="27">
+        <v>1</v>
+      </c>
+      <c r="N24" s="27">
+        <v>0</v>
+      </c>
+      <c r="O24" s="27">
+        <v>0</v>
+      </c>
+      <c r="P24" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q24" s="15">
+      <c r="Q24" s="20">
         <v>3</v>
       </c>
-      <c r="R24" s="15" t="s">
+      <c r="R24" s="20" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="25" s="15" customFormat="1" spans="1:18">
-      <c r="A25" s="15">
+    <row r="25" s="20" customFormat="1" spans="1:18">
+      <c r="A25" s="20">
         <v>303</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15" t="s">
+      <c r="C25" s="20">
+        <v>1</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="15" t="s">
+      <c r="G25" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="27">
         <v>1</v>
       </c>
       <c r="J25">
@@ -3658,51 +3750,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="22">
-        <v>1</v>
-      </c>
-      <c r="N25" s="22">
-        <v>0</v>
-      </c>
-      <c r="O25" s="22">
-        <v>0</v>
-      </c>
-      <c r="P25" s="15" t="s">
+      <c r="M25" s="27">
+        <v>1</v>
+      </c>
+      <c r="N25" s="27">
+        <v>0</v>
+      </c>
+      <c r="O25" s="27">
+        <v>0</v>
+      </c>
+      <c r="P25" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q25" s="15">
+      <c r="Q25" s="20">
         <v>3</v>
       </c>
-      <c r="R25" s="15" t="s">
+      <c r="R25" s="20" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="26" s="15" customFormat="1" spans="1:18">
-      <c r="A26" s="15">
+    <row r="26" s="20" customFormat="1" spans="1:18">
+      <c r="A26" s="20">
         <v>304</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="C26" s="15">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="s">
+      <c r="C26" s="20">
+        <v>1</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="G26" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="15" t="s">
+      <c r="G26" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="27">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -3711,54 +3803,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="22">
-        <v>1</v>
-      </c>
-      <c r="N26" s="22">
-        <v>0</v>
-      </c>
-      <c r="O26" s="22">
-        <v>0</v>
-      </c>
-      <c r="P26" s="15" t="s">
+      <c r="M26" s="27">
+        <v>1</v>
+      </c>
+      <c r="N26" s="27">
+        <v>0</v>
+      </c>
+      <c r="O26" s="27">
+        <v>0</v>
+      </c>
+      <c r="P26" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q26" s="15">
+      <c r="Q26" s="20">
         <v>3</v>
       </c>
-      <c r="R26" s="15" t="s">
+      <c r="R26" s="20" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" s="15" customFormat="1" spans="1:18">
-      <c r="A27" s="15">
+    <row r="27" s="20" customFormat="1" spans="1:18">
+      <c r="A27" s="20">
         <v>305</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="20">
         <v>3</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G27" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15" t="s">
+      <c r="G27" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="27">
         <v>1</v>
       </c>
       <c r="J27">
@@ -3770,51 +3862,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="22">
-        <v>1</v>
-      </c>
-      <c r="N27" s="22">
-        <v>0</v>
-      </c>
-      <c r="O27" s="22">
-        <v>0</v>
-      </c>
-      <c r="P27" s="15" t="s">
+      <c r="M27" s="27">
+        <v>1</v>
+      </c>
+      <c r="N27" s="27">
+        <v>0</v>
+      </c>
+      <c r="O27" s="27">
+        <v>0</v>
+      </c>
+      <c r="P27" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="Q27" s="15">
+      <c r="Q27" s="20">
         <v>3</v>
       </c>
-      <c r="R27" s="15" t="s">
+      <c r="R27" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="28" s="15" customFormat="1" spans="1:18">
-      <c r="A28" s="15">
+    <row r="28" s="20" customFormat="1" spans="1:18">
+      <c r="A28" s="20">
         <v>306</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="20">
         <v>2</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="G28" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
-      </c>
-      <c r="I28" s="22">
+      <c r="G28" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="20">
+        <v>0</v>
+      </c>
+      <c r="I28" s="27">
         <v>1</v>
       </c>
       <c r="J28">
@@ -3823,54 +3915,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="15">
-        <v>1</v>
-      </c>
-      <c r="M28" s="22">
-        <v>1</v>
-      </c>
-      <c r="N28" s="22">
-        <v>0</v>
-      </c>
-      <c r="O28" s="22">
-        <v>0</v>
-      </c>
-      <c r="P28" s="15" t="s">
+      <c r="L28" s="20">
+        <v>1</v>
+      </c>
+      <c r="M28" s="27">
+        <v>1</v>
+      </c>
+      <c r="N28" s="27">
+        <v>0</v>
+      </c>
+      <c r="O28" s="27">
+        <v>0</v>
+      </c>
+      <c r="P28" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="Q28" s="15">
+      <c r="Q28" s="20">
         <v>3</v>
       </c>
-      <c r="R28" s="15" t="s">
+      <c r="R28" s="20" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="29" s="15" customFormat="1" spans="1:18">
-      <c r="A29" s="15">
+    <row r="29" s="20" customFormat="1" spans="1:18">
+      <c r="A29" s="20">
         <v>307</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="15">
-        <v>1</v>
-      </c>
-      <c r="D29" s="15" t="s">
+      <c r="C29" s="20">
+        <v>1</v>
+      </c>
+      <c r="D29" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="G29" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="15" t="s">
+      <c r="G29" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="27">
         <v>1</v>
       </c>
       <c r="J29">
@@ -3879,54 +3971,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="L29" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="22">
+      <c r="M29" s="27">
         <v>0.1</v>
       </c>
-      <c r="N29" s="22">
-        <v>0</v>
-      </c>
-      <c r="O29" s="22">
+      <c r="N29" s="27">
+        <v>0</v>
+      </c>
+      <c r="O29" s="27">
         <v>0.17</v>
       </c>
-      <c r="P29" s="15" t="s">
+      <c r="P29" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q29" s="15">
+      <c r="Q29" s="20">
         <v>3</v>
       </c>
-      <c r="R29" s="15" t="s">
+      <c r="R29" s="20" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="30" s="15" customFormat="1" spans="1:18">
-      <c r="A30" s="15">
+    <row r="30" s="20" customFormat="1" spans="1:18">
+      <c r="A30" s="20">
         <v>308</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
-      </c>
-      <c r="D30" s="15" t="s">
+      <c r="C30" s="20">
+        <v>1</v>
+      </c>
+      <c r="D30" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G30" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="G30" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="27">
         <v>1</v>
       </c>
       <c r="J30">
@@ -3935,54 +4027,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="L30" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="M30" s="22">
-        <v>1</v>
-      </c>
-      <c r="N30" s="22">
-        <v>0</v>
-      </c>
-      <c r="O30" s="22">
-        <v>0</v>
-      </c>
-      <c r="P30" s="15" t="s">
+      <c r="M30" s="27">
+        <v>1</v>
+      </c>
+      <c r="N30" s="27">
+        <v>0</v>
+      </c>
+      <c r="O30" s="27">
+        <v>0</v>
+      </c>
+      <c r="P30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="Q30" s="15">
+      <c r="Q30" s="20">
         <v>3</v>
       </c>
-      <c r="R30" s="15" t="s">
+      <c r="R30" s="20" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="31" s="15" customFormat="1" spans="1:18">
-      <c r="A31" s="15">
+    <row r="31" s="20" customFormat="1" spans="1:18">
+      <c r="A31" s="20">
         <v>309</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C31" s="15">
+      <c r="C31" s="20">
         <v>2</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="G31" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="G31" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="27">
         <v>1</v>
       </c>
       <c r="J31">
@@ -3991,54 +4083,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="L31" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="M31" s="22">
-        <v>1</v>
-      </c>
-      <c r="N31" s="22">
-        <v>0</v>
-      </c>
-      <c r="O31" s="22">
-        <v>0</v>
-      </c>
-      <c r="P31" s="15" t="s">
+      <c r="M31" s="27">
+        <v>1</v>
+      </c>
+      <c r="N31" s="27">
+        <v>0</v>
+      </c>
+      <c r="O31" s="27">
+        <v>0</v>
+      </c>
+      <c r="P31" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="Q31" s="15">
+      <c r="Q31" s="20">
         <v>3</v>
       </c>
-      <c r="R31" s="15" t="s">
+      <c r="R31" s="20" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="32" s="15" customFormat="1" spans="1:18">
-      <c r="A32" s="15">
+    <row r="32" s="20" customFormat="1" spans="1:18">
+      <c r="A32" s="20">
         <v>310</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="20">
         <v>2</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="G32" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="15" t="s">
+      <c r="G32" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="27">
         <v>1</v>
       </c>
       <c r="J32">
@@ -4047,54 +4139,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="15" t="s">
+      <c r="L32" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="22">
-        <v>1</v>
-      </c>
-      <c r="N32" s="22">
-        <v>0</v>
-      </c>
-      <c r="O32" s="22">
-        <v>0</v>
-      </c>
-      <c r="P32" s="15" t="s">
+      <c r="M32" s="27">
+        <v>1</v>
+      </c>
+      <c r="N32" s="27">
+        <v>0</v>
+      </c>
+      <c r="O32" s="27">
+        <v>0</v>
+      </c>
+      <c r="P32" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="Q32" s="15">
+      <c r="Q32" s="20">
         <v>4</v>
       </c>
-      <c r="R32" s="15" t="s">
+      <c r="R32" s="20" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="33" s="15" customFormat="1" spans="1:21">
-      <c r="A33" s="15">
+    <row r="33" s="20" customFormat="1" spans="1:21">
+      <c r="A33" s="20">
         <v>311</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="C33" s="15">
+      <c r="C33" s="20">
         <v>2</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>0</v>
-      </c>
-      <c r="I33" s="22">
+      <c r="G33" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="20">
+        <v>0</v>
+      </c>
+      <c r="I33" s="27">
         <v>1</v>
       </c>
       <c r="J33">
@@ -4103,45 +4195,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="15">
-        <v>1</v>
-      </c>
-      <c r="M33" s="22">
-        <v>1</v>
-      </c>
-      <c r="N33" s="22">
-        <v>0</v>
-      </c>
-      <c r="O33" s="22">
-        <v>0</v>
-      </c>
-      <c r="P33" s="15" t="s">
+      <c r="L33" s="20">
+        <v>1</v>
+      </c>
+      <c r="M33" s="27">
+        <v>1</v>
+      </c>
+      <c r="N33" s="27">
+        <v>0</v>
+      </c>
+      <c r="O33" s="27">
+        <v>0</v>
+      </c>
+      <c r="P33" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="Q33" s="15">
+      <c r="Q33" s="20">
         <v>3</v>
       </c>
-      <c r="R33" s="15" t="s">
+      <c r="R33" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="34" s="15" customFormat="1" spans="1:21">
-      <c r="A34" s="15">
+    <row r="34" s="20" customFormat="1" spans="1:21">
+      <c r="A34" s="20">
         <v>312</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="C34" s="15">
+      <c r="C34" s="20">
         <v>2</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="G34" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="22">
+      <c r="G34" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="27">
         <v>1</v>
       </c>
       <c r="J34">
@@ -4150,45 +4242,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="22">
-        <v>1</v>
-      </c>
-      <c r="N34" s="22">
-        <v>0</v>
-      </c>
-      <c r="O34" s="22">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="15">
-        <v>1</v>
-      </c>
-      <c r="R34" s="15" t="s">
+      <c r="M34" s="27">
+        <v>1</v>
+      </c>
+      <c r="N34" s="27">
+        <v>0</v>
+      </c>
+      <c r="O34" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="20">
+        <v>1</v>
+      </c>
+      <c r="R34" s="20" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="35" s="13" customFormat="1" spans="1:21">
-      <c r="A35" s="13">
+    <row r="35" s="18" customFormat="1" spans="1:21">
+      <c r="A35" s="18">
         <v>401</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C35" s="13">
+      <c r="C35" s="18">
         <v>2</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="27" t="s">
+      <c r="F35" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="13" t="s">
+      <c r="G35" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="27">
         <v>1</v>
       </c>
       <c r="J35">
@@ -4200,45 +4292,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="22">
-        <v>1</v>
-      </c>
-      <c r="N35" s="22">
-        <v>0</v>
-      </c>
-      <c r="O35" s="22">
-        <v>0</v>
-      </c>
-      <c r="P35" s="13" t="s">
+      <c r="M35" s="27">
+        <v>1</v>
+      </c>
+      <c r="N35" s="27">
+        <v>0</v>
+      </c>
+      <c r="O35" s="27">
+        <v>0</v>
+      </c>
+      <c r="P35" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="13">
+      <c r="Q35" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="13" customFormat="1" spans="1:21">
-      <c r="A36" s="13">
+    <row r="36" s="18" customFormat="1" spans="1:21">
+      <c r="A36" s="18">
         <v>402</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="18">
         <v>2</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="13" t="s">
+      <c r="G36" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="27">
         <v>1</v>
       </c>
       <c r="J36">
@@ -4250,48 +4342,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="22">
-        <v>1</v>
-      </c>
-      <c r="N36" s="22">
-        <v>0</v>
-      </c>
-      <c r="O36" s="22">
-        <v>0</v>
-      </c>
-      <c r="P36" s="13" t="s">
+      <c r="M36" s="27">
+        <v>1</v>
+      </c>
+      <c r="N36" s="27">
+        <v>0</v>
+      </c>
+      <c r="O36" s="27">
+        <v>0</v>
+      </c>
+      <c r="P36" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="13">
+      <c r="Q36" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="13" customFormat="1" spans="1:21">
-      <c r="A37" s="13">
+    <row r="37" s="18" customFormat="1" spans="1:21">
+      <c r="A37" s="18">
         <v>403</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="C37" s="13">
+      <c r="C37" s="18">
         <v>2</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="13" t="s">
+      <c r="G37" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="27">
         <v>1</v>
       </c>
       <c r="J37">
@@ -4300,83 +4392,83 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="13" t="s">
+      <c r="L37" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="22">
-        <v>1</v>
-      </c>
-      <c r="N37" s="22">
-        <v>0</v>
-      </c>
-      <c r="O37" s="22">
-        <v>0</v>
-      </c>
-      <c r="P37" s="13" t="s">
+      <c r="M37" s="27">
+        <v>1</v>
+      </c>
+      <c r="N37" s="27">
+        <v>0</v>
+      </c>
+      <c r="O37" s="27">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="13">
+      <c r="Q37" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="24" customFormat="1" spans="1:21">
-      <c r="A38" s="24">
+    <row r="38" s="29" customFormat="1" spans="1:21">
+      <c r="A38" s="29">
         <v>404</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="C38" s="24">
-        <v>1</v>
-      </c>
-      <c r="D38" s="14" t="s">
+      <c r="C38" s="29">
+        <v>1</v>
+      </c>
+      <c r="D38" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="24" t="s">
+      <c r="G38" s="29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="24">
-        <v>1</v>
-      </c>
-      <c r="J38" s="14">
-        <v>0</v>
-      </c>
-      <c r="K38" s="14">
+      <c r="I38" s="29">
+        <v>1</v>
+      </c>
+      <c r="J38" s="19">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19">
         <v>2</v>
       </c>
-      <c r="L38" s="24" t="s">
+      <c r="L38" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="24">
-        <v>1</v>
-      </c>
-      <c r="N38" s="24">
-        <v>0</v>
-      </c>
-      <c r="O38" s="24">
-        <v>0</v>
-      </c>
-      <c r="P38" s="24" t="s">
+      <c r="M38" s="29">
+        <v>1</v>
+      </c>
+      <c r="N38" s="29">
+        <v>0</v>
+      </c>
+      <c r="O38" s="29">
+        <v>0</v>
+      </c>
+      <c r="P38" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="24">
+      <c r="Q38" s="29">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="13" customFormat="1" spans="1:21">
-      <c r="A39" s="13">
+    <row r="39" s="18" customFormat="1" spans="1:21">
+      <c r="A39" s="18">
         <v>405</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="33" t="s">
         <v>180</v>
       </c>
       <c r="C39">
@@ -4391,13 +4483,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="22" t="b">
+      <c r="G39" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="27">
         <v>1</v>
       </c>
       <c r="J39">
@@ -4409,13 +4501,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="22">
-        <v>1</v>
-      </c>
-      <c r="N39" s="22">
-        <v>0</v>
-      </c>
-      <c r="O39" s="22">
+      <c r="M39" s="27">
+        <v>1</v>
+      </c>
+      <c r="N39" s="27">
+        <v>0</v>
+      </c>
+      <c r="O39" s="27">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -4431,32 +4523,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="13" customFormat="1" spans="1:21">
-      <c r="A40" s="13">
+    <row r="40" s="18" customFormat="1" spans="1:21">
+      <c r="A40" s="18">
         <v>406</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="13">
-        <v>1</v>
-      </c>
-      <c r="D40" s="13" t="s">
+      <c r="C40" s="18">
+        <v>1</v>
+      </c>
+      <c r="D40" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="13" t="s">
+      <c r="E40" s="18" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="13">
-        <v>0</v>
-      </c>
-      <c r="I40" s="22">
+      <c r="G40" s="27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="18">
+        <v>0</v>
+      </c>
+      <c r="I40" s="27">
         <v>1</v>
       </c>
       <c r="J40">
@@ -4465,30 +4557,30 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="18">
         <v>3</v>
       </c>
-      <c r="M40" s="22">
-        <v>1</v>
-      </c>
-      <c r="N40" s="22">
-        <v>0</v>
-      </c>
-      <c r="O40" s="22">
-        <v>0</v>
-      </c>
-      <c r="P40" s="13" t="s">
+      <c r="M40" s="27">
+        <v>1</v>
+      </c>
+      <c r="N40" s="27">
+        <v>0</v>
+      </c>
+      <c r="O40" s="27">
+        <v>0</v>
+      </c>
+      <c r="P40" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="13">
+      <c r="Q40" s="18">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="13">
+      <c r="A41" s="18">
         <v>407</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="8" t="s">
         <v>182</v>
       </c>
       <c r="C41">
@@ -4503,13 +4595,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="22" t="b">
+      <c r="G41" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="27">
         <v>1</v>
       </c>
       <c r="J41">
@@ -4521,13 +4613,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="22">
-        <v>1</v>
-      </c>
-      <c r="N41" s="22">
-        <v>0</v>
-      </c>
-      <c r="O41" s="22">
+      <c r="M41" s="27">
+        <v>1</v>
+      </c>
+      <c r="N41" s="27">
+        <v>0</v>
+      </c>
+      <c r="O41" s="27">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -4541,10 +4633,10 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="13">
+      <c r="A42" s="18">
         <v>408</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="8" t="s">
         <v>183</v>
       </c>
       <c r="C42">
@@ -4559,13 +4651,13 @@
       <c r="F42" t="s">
         <v>107</v>
       </c>
-      <c r="G42" s="22" t="b">
+      <c r="G42" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>100</v>
       </c>
-      <c r="I42" s="22">
+      <c r="I42" s="27">
         <v>1</v>
       </c>
       <c r="J42">
@@ -4577,13 +4669,13 @@
       <c r="L42" t="s">
         <v>101</v>
       </c>
-      <c r="M42" s="22">
-        <v>1</v>
-      </c>
-      <c r="N42" s="22">
-        <v>0</v>
-      </c>
-      <c r="O42" s="22">
+      <c r="M42" s="27">
+        <v>1</v>
+      </c>
+      <c r="N42" s="27">
+        <v>0</v>
+      </c>
+      <c r="O42" s="27">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -4597,10 +4689,10 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="13">
+      <c r="A43" s="18">
         <v>409</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="8" t="s">
         <v>184</v>
       </c>
       <c r="C43">
@@ -4615,13 +4707,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="22" t="b">
+      <c r="G43" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="22">
+      <c r="I43" s="27">
         <v>1</v>
       </c>
       <c r="J43">
@@ -4633,13 +4725,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="22">
-        <v>1</v>
-      </c>
-      <c r="N43" s="22">
-        <v>0</v>
-      </c>
-      <c r="O43" s="22">
+      <c r="M43" s="27">
+        <v>1</v>
+      </c>
+      <c r="N43" s="27">
+        <v>0</v>
+      </c>
+      <c r="O43" s="27">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -4653,10 +4745,10 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="13">
+      <c r="A44" s="18">
         <v>410</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="8" t="s">
         <v>185</v>
       </c>
       <c r="C44">
@@ -4671,13 +4763,13 @@
       <c r="F44" t="s">
         <v>97</v>
       </c>
-      <c r="G44" s="22" t="b">
+      <c r="G44" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>100</v>
       </c>
-      <c r="I44" s="22">
+      <c r="I44" s="27">
         <v>1</v>
       </c>
       <c r="J44">
@@ -4689,13 +4781,13 @@
       <c r="L44" t="s">
         <v>101</v>
       </c>
-      <c r="M44" s="22">
-        <v>1</v>
-      </c>
-      <c r="N44" s="22">
-        <v>0</v>
-      </c>
-      <c r="O44" s="22">
+      <c r="M44" s="27">
+        <v>1</v>
+      </c>
+      <c r="N44" s="27">
+        <v>0</v>
+      </c>
+      <c r="O44" s="27">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -4709,10 +4801,10 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="13">
+      <c r="A45" s="18">
         <v>411</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="8" t="s">
         <v>186</v>
       </c>
       <c r="C45">
@@ -4727,13 +4819,13 @@
       <c r="F45" t="s">
         <v>118</v>
       </c>
-      <c r="G45" s="22" t="b">
+      <c r="G45" s="27" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="22">
+      <c r="I45" s="27">
         <v>1</v>
       </c>
       <c r="J45">
@@ -4745,13 +4837,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="22">
-        <v>1</v>
-      </c>
-      <c r="N45" s="22">
-        <v>0</v>
-      </c>
-      <c r="O45" s="22">
+      <c r="M45" s="27">
+        <v>1</v>
+      </c>
+      <c r="N45" s="27">
+        <v>0</v>
+      </c>
+      <c r="O45" s="27">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -4786,37 +4878,37 @@
     <col min="8" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:8">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" s="8" customFormat="1" spans="1:8">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>299</v>
       </c>
       <c r="C2" t="s">
@@ -4825,18 +4917,18 @@
       <c r="D2" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="H2" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
-      <c r="A3" s="2">
+      <c r="H2" s="9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="8" customFormat="1" spans="1:8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="9" t="s">
         <v>303</v>
       </c>
       <c r="C3" t="s">
@@ -4845,15 +4937,15 @@
       <c r="D3" t="s">
         <v>301</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="H3" s="2" t="b">
+      <c r="H3" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -4865,15 +4957,15 @@
       <c r="D4" t="s">
         <v>306</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="H4" s="2" t="b">
+      <c r="H4" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -4885,15 +4977,15 @@
       <c r="D5" t="s">
         <v>306</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="H5" s="2" t="b">
+      <c r="H5" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -4908,12 +5000,12 @@
       <c r="E6" t="s">
         <v>310</v>
       </c>
-      <c r="H6" s="2" t="b">
+      <c r="H6" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -4928,12 +5020,12 @@
       <c r="E7" t="s">
         <v>310</v>
       </c>
-      <c r="H7" s="2" t="b">
+      <c r="H7" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -4948,12 +5040,12 @@
       <c r="E8" t="s">
         <v>315</v>
       </c>
-      <c r="H8" s="2" t="b">
+      <c r="H8" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -4968,12 +5060,12 @@
       <c r="E9" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="2" t="b">
+      <c r="H9" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -4988,12 +5080,12 @@
       <c r="E10" t="s">
         <v>310</v>
       </c>
-      <c r="H10" s="2" t="b">
+      <c r="H10" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -5008,12 +5100,12 @@
       <c r="E11" t="s">
         <v>310</v>
       </c>
-      <c r="H11" s="2" t="b">
+      <c r="H11" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="2">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -5025,24 +5117,24 @@
       <c r="D12" t="s">
         <v>321</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="H12" s="2" t="b">
+      <c r="H12" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="2">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>325</v>
       </c>
       <c r="C13" t="s">
@@ -5051,20 +5143,20 @@
       <c r="D13" t="s">
         <v>306</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="2" t="b">
+      <c r="F13" s="6"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="2">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>327</v>
       </c>
       <c r="C14" t="s">
@@ -5073,20 +5165,20 @@
       <c r="D14" t="s">
         <v>306</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="2" t="b">
+      <c r="F14" s="6"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="2">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>328</v>
       </c>
       <c r="C15" t="s">
@@ -5095,20 +5187,20 @@
       <c r="D15" t="s">
         <v>306</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="2" t="b">
+      <c r="F15" s="6"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="2">
+      <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>329</v>
       </c>
       <c r="C16" t="s">
@@ -5117,17 +5209,17 @@
       <c r="D16" t="s">
         <v>306</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="2" t="b">
+      <c r="F16" s="6"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2">
+      <c r="A17" s="9">
         <v>101</v>
       </c>
       <c r="B17" t="s">
@@ -5139,15 +5231,15 @@
       <c r="D17" t="s">
         <v>332</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="H17" s="2" t="b">
+      <c r="H17" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="2">
+      <c r="A18" s="9">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -5159,21 +5251,21 @@
       <c r="D18" t="s">
         <v>336</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="H18" s="2" t="b">
+      <c r="H18" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="2">
+      <c r="A19" s="9">
         <v>103</v>
       </c>
       <c r="B19" t="s">
@@ -5185,21 +5277,21 @@
       <c r="D19" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="H19" s="2" t="b">
+      <c r="H19" s="9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="2">
+      <c r="A20" s="9">
         <v>201</v>
       </c>
       <c r="B20" t="s">
@@ -5211,15 +5303,15 @@
       <c r="D20" t="s">
         <v>301</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="H20" s="2" t="b">
+      <c r="H20" s="9" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="2">
+      <c r="A21" s="9">
         <v>202</v>
       </c>
       <c r="B21" t="s">
@@ -5231,16 +5323,16 @@
       <c r="D21" t="s">
         <v>344</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="H21" s="2" t="b">
+      <c r="H21" s="9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5277,19 +5369,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="1"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>348</v>
       </c>
     </row>
@@ -5319,24 +5411,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>350</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="2">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -5348,12 +5440,12 @@
       <c r="D2" t="s">
         <v>355</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="10" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -5365,12 +5457,12 @@
       <c r="D3" t="s">
         <v>355</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="11" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -5387,7 +5479,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -5399,15 +5491,15 @@
       <c r="D5" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="11" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
         <v>361</v>
       </c>
       <c r="C6" t="s">
@@ -5416,15 +5508,15 @@
       <c r="D6" t="s">
         <v>355</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="12" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="9" t="s">
         <v>362</v>
       </c>
       <c r="C7" t="s">
@@ -5433,15 +5525,15 @@
       <c r="D7" t="s">
         <v>355</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="11" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="9" t="s">
         <v>363</v>
       </c>
       <c r="C8" t="s">
@@ -5450,12 +5542,12 @@
       <c r="D8" t="s">
         <v>355</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="11" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -5467,12 +5559,12 @@
       <c r="D9" t="s">
         <v>355</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="11" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -5484,128 +5576,128 @@
       <c r="D10" t="s">
         <v>355</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="11" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="11" ht="17.25" spans="1:5">
-      <c r="A11" s="2">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>369</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="13" t="s">
         <v>370</v>
       </c>
       <c r="D11" t="s">
         <v>371</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="10" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="12" ht="17.25" spans="1:5">
-      <c r="A12" s="2">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>372</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="13" t="s">
         <v>370</v>
       </c>
       <c r="D12" t="s">
         <v>371</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="11" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:5">
-      <c r="A13" s="2">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
       <c r="B13" t="s">
         <v>373</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="13" t="s">
         <v>370</v>
       </c>
       <c r="D13" t="s">
         <v>371</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="10" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="14" ht="17.25" spans="1:5">
-      <c r="A14" s="2">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>374</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="13" t="s">
         <v>375</v>
       </c>
       <c r="D14" t="s">
         <v>371</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="11" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="15" ht="17.25" spans="1:5">
-      <c r="A15" s="2">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>376</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="13" t="s">
         <v>377</v>
       </c>
       <c r="D15" t="s">
         <v>371</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="10" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
+      <c r="A16" s="9"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
+      <c r="A17" s="9"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
+      <c r="A18" s="9"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
+      <c r="A19" s="9"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="7"/>
-      <c r="E21" s="4"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="3"/>
+      <c r="E21" s="11"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2"/>
+      <c r="A22" s="9"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2"/>
+      <c r="A23" s="9"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2"/>
-      <c r="E24" s="4"/>
+      <c r="A24" s="9"/>
+      <c r="E24" s="11"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2"/>
+      <c r="A25" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5628,60 +5720,154 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="255.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="14.25" spans="1:3">
+      <c r="A2" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C6" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9" style="1"/>
+    <col min="2" max="2" width="9" style="8"/>
     <col min="3" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" s="8" customFormat="1" spans="1:7">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="8" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="15">
+    <row r="2" s="8" customFormat="1" spans="1:7">
+      <c r="A2" s="20">
         <v>4</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="20">
         <v>20</v>
       </c>
-      <c r="D2" s="15">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="D2" s="20">
+        <v>1</v>
+      </c>
+      <c r="E2" s="9">
+        <v>1</v>
+      </c>
+      <c r="F2" s="9">
+        <v>0</v>
+      </c>
+      <c r="G2" s="9">
         <v>200</v>
       </c>
     </row>
@@ -5689,7 +5875,7 @@
       <c r="A3">
         <v>201</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C3">
@@ -5704,7 +5890,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="9">
         <v>100</v>
       </c>
     </row>
@@ -5712,7 +5898,7 @@
       <c r="A4">
         <v>202</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C4">
@@ -5727,7 +5913,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="9">
         <v>100</v>
       </c>
     </row>
@@ -5735,7 +5921,7 @@
       <c r="A5">
         <v>203</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C5">
@@ -5750,7 +5936,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="9">
         <v>110</v>
       </c>
     </row>
@@ -5758,7 +5944,7 @@
       <c r="A6">
         <v>204</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C6">
@@ -5773,7 +5959,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="9">
         <v>200</v>
       </c>
     </row>
@@ -5781,7 +5967,7 @@
       <c r="A7">
         <v>205</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C7">
@@ -5796,7 +5982,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="9">
         <v>90</v>
       </c>
     </row>
@@ -5804,7 +5990,7 @@
       <c r="A8">
         <v>206</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C8">
@@ -5819,7 +6005,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="9">
         <v>200</v>
       </c>
     </row>
@@ -5827,7 +6013,7 @@
       <c r="A9">
         <v>207</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C9">
@@ -5842,7 +6028,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="9">
         <v>100</v>
       </c>
     </row>
@@ -5850,7 +6036,7 @@
       <c r="A10">
         <v>208</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C10">
@@ -5865,7 +6051,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="9">
         <v>90</v>
       </c>
     </row>
@@ -5873,7 +6059,7 @@
       <c r="A11">
         <v>209</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C11">
@@ -5888,7 +6074,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5896,7 +6082,7 @@
       <c r="A12">
         <v>210</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C12">
@@ -5911,7 +6097,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="9">
         <v>180</v>
       </c>
     </row>
@@ -5919,7 +6105,7 @@
       <c r="A13">
         <v>211</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C13">
@@ -5934,7 +6120,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="9">
         <v>0</v>
       </c>
     </row>
@@ -5942,7 +6128,7 @@
       <c r="A14">
         <v>212</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C14">
@@ -5957,7 +6143,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="9">
         <v>100</v>
       </c>
     </row>
@@ -5965,7 +6151,7 @@
       <c r="A15">
         <v>213</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C15">
@@ -5980,7 +6166,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="9">
         <v>180</v>
       </c>
     </row>
@@ -5988,7 +6174,7 @@
       <c r="A16">
         <v>214</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C16">
@@ -6003,7 +6189,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="9">
         <v>110</v>
       </c>
     </row>
@@ -6011,7 +6197,7 @@
       <c r="A17">
         <v>215</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C17">
@@ -6026,288 +6212,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="9">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="18" customFormat="1" spans="1:7">
-      <c r="A18" s="18">
+    <row r="18" s="23" customFormat="1" spans="1:7">
+      <c r="A18" s="23">
         <v>301</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="23">
         <v>50</v>
       </c>
-      <c r="D18" s="18">
-        <v>0</v>
-      </c>
-      <c r="E18" s="18">
+      <c r="D18" s="23">
+        <v>0</v>
+      </c>
+      <c r="E18" s="23">
         <v>400</v>
       </c>
-      <c r="F18" s="18">
-        <v>0</v>
-      </c>
-      <c r="G18" s="20">
+      <c r="F18" s="23">
+        <v>0</v>
+      </c>
+      <c r="G18" s="25">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="18" customFormat="1" spans="1:7">
-      <c r="A19" s="18">
+    <row r="19" s="23" customFormat="1" spans="1:7">
+      <c r="A19" s="23">
         <v>302</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="23">
         <v>25</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="23">
         <v>9</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="23">
         <v>100</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="23">
         <v>303</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="25">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="18" customFormat="1" spans="1:7">
-      <c r="A20" s="18">
+    <row r="20" s="23" customFormat="1" spans="1:7">
+      <c r="A20" s="23">
         <v>303</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="23">
         <v>20</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="23">
         <v>3</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="23">
         <v>50</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="23">
         <v>301</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="25">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="18" customFormat="1" spans="1:7">
-      <c r="A21" s="18">
+    <row r="21" s="23" customFormat="1" spans="1:7">
+      <c r="A21" s="23">
         <v>304</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="23">
         <v>30</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="23">
         <v>11</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="23">
         <v>300</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="23">
         <v>301</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="25">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="18" customFormat="1" spans="1:7">
-      <c r="A22" s="18">
+    <row r="22" s="23" customFormat="1" spans="1:7">
+      <c r="A22" s="23">
         <v>305</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="23">
         <v>25</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="23">
         <v>8</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="23">
         <v>100</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="23">
         <v>303</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="25">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="18" customFormat="1" spans="1:7">
-      <c r="A23" s="18">
+    <row r="23" s="23" customFormat="1" spans="1:7">
+      <c r="A23" s="23">
         <v>306</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="24" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="23">
         <v>35</v>
       </c>
-      <c r="D23" s="18">
-        <v>0</v>
-      </c>
-      <c r="E23" s="18">
+      <c r="D23" s="23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="23">
         <v>200</v>
       </c>
-      <c r="F23" s="18">
-        <v>0</v>
-      </c>
-      <c r="G23" s="20">
+      <c r="F23" s="23">
+        <v>0</v>
+      </c>
+      <c r="G23" s="25">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="18" customFormat="1" spans="1:7">
-      <c r="A24" s="18">
+    <row r="24" s="23" customFormat="1" spans="1:7">
+      <c r="A24" s="23">
         <v>307</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="23">
         <v>35</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="23">
         <v>12</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="23">
         <v>150</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="23">
         <v>302</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="25">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="18" customFormat="1" spans="1:7">
-      <c r="A25" s="18">
+    <row r="25" s="23" customFormat="1" spans="1:7">
+      <c r="A25" s="23">
         <v>308</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="24" t="s">
         <v>156</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="23">
         <v>35</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="23">
         <v>12</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="23">
         <v>150</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="23">
         <v>302</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="25">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="18" customFormat="1" spans="1:7">
-      <c r="A26" s="18">
+    <row r="26" s="23" customFormat="1" spans="1:7">
+      <c r="A26" s="23">
         <v>309</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="23">
         <v>20</v>
       </c>
-      <c r="D26" s="18">
+      <c r="D26" s="23">
         <v>10</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="23">
         <v>80</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="23">
         <v>306</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="25">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="18" customFormat="1" spans="1:7">
-      <c r="A27" s="18">
+    <row r="27" s="23" customFormat="1" spans="1:7">
+      <c r="A27" s="23">
         <v>310</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="23">
         <v>30</v>
       </c>
-      <c r="D27" s="18">
+      <c r="D27" s="23">
         <v>10</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="23">
         <v>120</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="23">
         <v>309</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="25">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="18" customFormat="1" spans="1:7">
-      <c r="A28" s="18">
+    <row r="28" s="23" customFormat="1" spans="1:7">
+      <c r="A28" s="23">
         <v>311</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="24" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="23">
         <v>30</v>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="23">
         <v>10</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="23">
         <v>120</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="23">
         <v>309</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="25">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="18" customFormat="1" spans="1:7">
-      <c r="A29" s="18">
+    <row r="29" s="23" customFormat="1" spans="1:7">
+      <c r="A29" s="23">
         <v>312</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="C29" s="18">
+      <c r="C29" s="23">
         <v>15</v>
       </c>
-      <c r="D29" s="18">
+      <c r="D29" s="23">
         <v>2</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="23">
         <v>15</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="23">
         <v>306</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="25">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="18" customFormat="1" spans="1:7">
-      <c r="B30" s="19"/>
+    <row r="30" s="23" customFormat="1" spans="1:7">
+      <c r="B30" s="24"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6336,7 +6522,7 @@
       <c r="C1" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>194</v>
       </c>
       <c r="E1" t="s">
@@ -6350,10 +6536,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
+      <c r="A2" s="20">
         <v>3</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="20" t="s">
         <v>20</v>
       </c>
       <c r="C2">
@@ -6370,10 +6556,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="15">
+      <c r="A3" s="20">
         <v>4</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="20" t="s">
         <v>22</v>
       </c>
       <c r="C3">
@@ -6559,10 +6745,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="15">
+      <c r="A12" s="20">
         <v>309</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="20" t="s">
         <v>161</v>
       </c>
       <c r="C12">
@@ -6579,10 +6765,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="15">
+      <c r="A13" s="20">
         <v>310</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="20" t="s">
         <v>165</v>
       </c>
       <c r="C13">
@@ -6599,10 +6785,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="15">
+      <c r="A14" s="20">
         <v>311</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="20" t="s">
         <v>169</v>
       </c>
       <c r="C14">
@@ -6622,10 +6808,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="15">
+      <c r="A15" s="20">
         <v>312</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="20" t="s">
         <v>172</v>
       </c>
       <c r="C15">
@@ -6642,8 +6828,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6658,35 +6844,35 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="9" style="1"/>
+    <col min="2" max="2" width="9" style="8"/>
     <col min="3" max="3" width="30.75" customWidth="1"/>
     <col min="4" max="6" width="44.875" customWidth="1"/>
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" spans="1:8">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+    <row r="1" s="16" customFormat="1" spans="1:8">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="16" t="s">
         <v>204</v>
       </c>
     </row>
@@ -6694,7 +6880,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C2" t="s">
@@ -6716,29 +6902,29 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" s="14" customFormat="1" spans="1:8">
-      <c r="A3" s="14">
+    <row r="3" s="19" customFormat="1" spans="1:8">
+      <c r="A3" s="19">
         <v>202</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E3" s="14">
-        <v>0</v>
-      </c>
-      <c r="F3" s="14">
+      <c r="E3" s="19">
+        <v>0</v>
+      </c>
+      <c r="F3" s="19">
         <v>0.8</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="19" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6746,7 +6932,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
@@ -6772,7 +6958,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C5" t="s">
@@ -6798,7 +6984,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C6" t="s">
@@ -6824,13 +7010,13 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>69</v>
       </c>
       <c r="E7">
@@ -6850,7 +7036,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
@@ -6876,7 +7062,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C9" t="s">
@@ -6902,7 +7088,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
@@ -6928,7 +7114,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C11" t="s">
@@ -6954,7 +7140,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E12">
@@ -6968,7 +7154,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C13" t="s">
@@ -6994,7 +7180,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C14" t="s">
@@ -7020,7 +7206,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C15" t="s">
@@ -7046,7 +7232,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C16" t="s">
@@ -7072,7 +7258,7 @@
       <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="8" t="s">
         <v>175</v>
       </c>
       <c r="C17" t="s">
@@ -7092,7 +7278,7 @@
       <c r="A18">
         <v>402</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="8" t="s">
         <v>176</v>
       </c>
       <c r="C18" t="s">
@@ -7112,7 +7298,7 @@
       <c r="A19">
         <v>403</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="8" t="s">
         <v>177</v>
       </c>
       <c r="C19" t="s">
@@ -7128,37 +7314,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="14" customFormat="1" spans="1:8">
-      <c r="A20" s="17">
+    <row r="20" s="19" customFormat="1" spans="1:8">
+      <c r="A20" s="22">
         <v>404</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E20" s="14">
-        <v>0</v>
-      </c>
-      <c r="F20" s="14">
+      <c r="E20" s="19">
+        <v>0</v>
+      </c>
+      <c r="F20" s="19">
         <v>0.8</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="19" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="12">
+      <c r="A21" s="17">
         <v>405</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
         <v>180</v>
       </c>
       <c r="C21" t="s">
@@ -7181,10 +7367,10 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="12">
+      <c r="A22" s="17">
         <v>406</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="8" t="s">
         <v>181</v>
       </c>
       <c r="C22" t="s">
@@ -7207,10 +7393,10 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="13">
+      <c r="A23" s="18">
         <v>407</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="8" t="s">
         <v>233</v>
       </c>
       <c r="C23" t="s">
@@ -7233,10 +7419,10 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="13">
+      <c r="A24" s="18">
         <v>408</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C24" t="s">
@@ -7259,10 +7445,10 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="13">
+      <c r="A25" s="18">
         <v>409</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="8" t="s">
         <v>235</v>
       </c>
       <c r="C25" t="s">
@@ -7285,10 +7471,10 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="13">
+      <c r="A26" s="18">
         <v>410</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="8" t="s">
         <v>185</v>
       </c>
       <c r="C26" t="s">
@@ -7311,10 +7497,10 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="13">
+      <c r="A27" s="18">
         <v>411</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="8" t="s">
         <v>186</v>
       </c>
       <c r="C27" t="s">
@@ -7350,7 +7536,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="8" customWidth="1"/>
     <col min="3" max="4" width="9.875" customWidth="1"/>
     <col min="5" max="6" width="8.125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -7377,68 +7563,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" spans="1:21">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+    <row r="1" s="19" customFormat="1" spans="1:21">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="16" t="s">
         <v>243</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="T1" s="14" t="s">
+      <c r="T1" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="19" t="s">
         <v>254</v>
       </c>
     </row>
@@ -7446,7 +7632,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C2">
@@ -7502,7 +7688,7 @@
       <c r="A3">
         <v>202</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C3">
@@ -7564,7 +7750,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C4">
@@ -7620,7 +7806,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>52</v>
       </c>
       <c r="C5">
@@ -7682,7 +7868,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C6">
@@ -7738,7 +7924,7 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C7">
@@ -7759,7 +7945,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>70</v>
       </c>
       <c r="K7">
@@ -7800,7 +7986,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="8" t="s">
         <v>72</v>
       </c>
       <c r="C8">
@@ -7862,7 +8048,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C9">
@@ -7918,7 +8104,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="8" t="s">
         <v>82</v>
       </c>
       <c r="C10">
@@ -7974,7 +8160,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="8" t="s">
         <v>90</v>
       </c>
       <c r="C11">
@@ -8033,7 +8219,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C12">
@@ -8086,7 +8272,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="8" t="s">
         <v>97</v>
       </c>
       <c r="C13">
@@ -8136,7 +8322,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="8" t="s">
         <v>104</v>
       </c>
       <c r="C14">
@@ -8195,7 +8381,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="8" t="s">
         <v>110</v>
       </c>
       <c r="C15">
@@ -8251,7 +8437,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C16">
@@ -8310,10 +8496,10 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="15">
+      <c r="A17" s="20">
         <v>301</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="21" t="s">
         <v>120</v>
       </c>
       <c r="C17">
@@ -8369,10 +8555,10 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="15">
+      <c r="A18" s="20">
         <v>302</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="21" t="s">
         <v>126</v>
       </c>
       <c r="C18">
@@ -8428,10 +8614,10 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="15">
+      <c r="A19" s="20">
         <v>303</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="21" t="s">
         <v>133</v>
       </c>
       <c r="C19">
@@ -8487,10 +8673,10 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="15">
+      <c r="A20" s="20">
         <v>304</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C20">
@@ -8549,7 +8735,7 @@
       <c r="A21">
         <v>305</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
         <v>139</v>
       </c>
       <c r="C21">
@@ -8608,10 +8794,10 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="15">
+      <c r="A22" s="20">
         <v>306</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="21" t="s">
         <v>145</v>
       </c>
       <c r="C22">
@@ -8667,10 +8853,10 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="15">
+      <c r="A23" s="20">
         <v>307</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="21" t="s">
         <v>151</v>
       </c>
       <c r="C23">
@@ -8726,10 +8912,10 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="15">
+      <c r="A24" s="20">
         <v>308</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C24">
@@ -8785,10 +8971,10 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="15">
+      <c r="A25" s="20">
         <v>309</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="21" t="s">
         <v>161</v>
       </c>
       <c r="C25">
@@ -8844,10 +9030,10 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="15">
+      <c r="A26" s="20">
         <v>310</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="21" t="s">
         <v>165</v>
       </c>
       <c r="C26">
@@ -8903,10 +9089,10 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="15">
+      <c r="A27" s="20">
         <v>311</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="21" t="s">
         <v>169</v>
       </c>
       <c r="C27">
@@ -8962,10 +9148,10 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="15">
+      <c r="A28" s="20">
         <v>312</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="21" t="s">
         <v>172</v>
       </c>
       <c r="C28">
@@ -9024,7 +9210,7 @@
       <c r="A29">
         <v>401</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="8" t="s">
         <v>175</v>
       </c>
       <c r="C29">
@@ -9086,7 +9272,7 @@
       <c r="A30">
         <v>402</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="8" t="s">
         <v>176</v>
       </c>
       <c r="C30">
@@ -9142,7 +9328,7 @@
       <c r="A31">
         <v>403</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="8" t="s">
         <v>177</v>
       </c>
       <c r="C31">
@@ -9195,10 +9381,10 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="12">
+      <c r="A32" s="17">
         <v>404</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="8" t="s">
         <v>179</v>
       </c>
       <c r="C32">
@@ -9257,10 +9443,10 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="12">
+      <c r="A33" s="17">
         <v>405</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="8" t="s">
         <v>180</v>
       </c>
       <c r="C33">
@@ -9313,10 +9499,10 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="12">
+      <c r="A34" s="17">
         <v>406</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="8" t="s">
         <v>181</v>
       </c>
       <c r="C34">
@@ -9369,10 +9555,10 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="13">
+      <c r="A35" s="18">
         <v>407</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="8" t="s">
         <v>233</v>
       </c>
       <c r="C35">
@@ -9425,10 +9611,10 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="13">
+      <c r="A36" s="18">
         <v>408</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C36">
@@ -9484,10 +9670,10 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="13">
+      <c r="A37" s="18">
         <v>409</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="8" t="s">
         <v>235</v>
       </c>
       <c r="C37">
@@ -9543,10 +9729,10 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="13">
+      <c r="A38" s="18">
         <v>410</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="8" t="s">
         <v>185</v>
       </c>
       <c r="C38">
@@ -9593,10 +9779,10 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="13">
+      <c r="A39" s="18">
         <v>411</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="8" t="s">
         <v>186</v>
       </c>
       <c r="C39">
@@ -9755,7 +9941,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="12">
+      <c r="A9" s="17">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -9766,7 +9952,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="12">
+      <c r="A10" s="17">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -9777,7 +9963,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="12">
+      <c r="A11" s="17">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -9788,7 +9974,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="13">
+      <c r="A12" s="18">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -9799,7 +9985,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13">
+      <c r="A13" s="18">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -9810,7 +9996,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="13">
+      <c r="A14" s="18">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -9821,7 +10007,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="13">
+      <c r="A15" s="18">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -9832,7 +10018,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="13">
+      <c r="A16" s="18">
         <v>411</v>
       </c>
       <c r="B16" t="s">
@@ -9857,29 +10043,29 @@
     <col min="7" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="11" customFormat="1" spans="1:8">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+    <row r="1" s="16" customFormat="1" spans="1:8">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="16" t="s">
         <v>280</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="16" t="s">
         <v>189</v>
       </c>
     </row>
@@ -10107,16 +10293,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="16" t="s">
         <v>189</v>
       </c>
     </row>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1097" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="623">
   <si>
     <t>类型</t>
   </si>
@@ -1514,7 +1514,7 @@
     <t>，祝贺你消灭了敌人，但你的地堡也快不行了。&lt;color=#a0ff50&gt;医疗兵&lt;/color&gt;可以修复地堡。</t>
   </si>
   <si>
-    <t>Congratulations on eliminating the enemies, but your bunker is almost destroyed. &lt;color=#a0ff50&gt;Medics&lt;/color&gt; can repair the bunker.</t>
+    <t>,Congratulations on eliminating the enemies, but your bunker is almost destroyed. &lt;color=#a0ff50&gt;Medics&lt;/color&gt; can repair the bunker.</t>
   </si>
   <si>
     <t>Key点击选中医疗兵</t>
@@ -1888,7 +1888,7 @@
     <t>In this training, you will learn how to use the &lt;color=#a0ff50&gt; Bunker&lt;/color&gt;, &lt;color=#a0ff50&gt;Medic&lt;/color&gt;, &lt;color=#a0ff50&gt;Tank&lt;/color&gt; and &lt;color=#a0ff50&gt;Aircraft&lt;/color&gt;.</t>
   </si>
   <si>
-    <t>Key好的</t>
+    <t>Key好的。</t>
   </si>
   <si>
     <t>好的。</t>
@@ -2180,7 +2180,7 @@
     <t>玩家：</t>
   </si>
   <si>
-    <t>Player:</t>
+    <t xml:space="preserve">Player: </t>
   </si>
   <si>
     <t>Key总教官：凌云</t>
@@ -2244,6 +2244,9 @@
   </si>
   <si>
     <t>Hive Bug: Hulu</t>
+  </si>
+  <si>
+    <t>Key内有{0}人</t>
   </si>
 </sst>
 </file>
@@ -2976,7 +2979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2999,12 +3002,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3033,6 +3030,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -3407,7 +3407,7 @@
   <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="12.75" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="13" customWidth="1"/>
     <col min="4" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="7" width="30.75" customWidth="1"/>
     <col min="8" max="9" width="44.875" customWidth="1"/>
@@ -3418,32 +3418,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="18" customFormat="1" spans="1:18">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
+    <row r="1" s="16" customFormat="1" spans="1:18">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -3452,42 +3452,42 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="18" t="s">
+      <c r="M1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="Q1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="18" t="s">
+      <c r="R1" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="35" customFormat="1" spans="1:18">
-      <c r="A2" s="35">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+    <row r="2" s="34" customFormat="1" spans="1:18">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="35">
-        <v>0</v>
-      </c>
-      <c r="G2" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="35">
+      <c r="C2" s="34">
+        <v>0</v>
+      </c>
+      <c r="G2" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="34">
         <v>1</v>
       </c>
       <c r="J2">
@@ -3496,33 +3496,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="35">
-        <v>1</v>
-      </c>
-      <c r="N2" s="35">
-        <v>0</v>
-      </c>
-      <c r="O2" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="35" customFormat="1" spans="1:18">
-      <c r="A3" s="35">
+      <c r="M2" s="34">
+        <v>1</v>
+      </c>
+      <c r="N2" s="34">
+        <v>0</v>
+      </c>
+      <c r="O2" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="34" customFormat="1" spans="1:18">
+      <c r="A3" s="34">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="35">
-        <v>0</v>
-      </c>
-      <c r="G3" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="35">
+      <c r="C3" s="34">
+        <v>0</v>
+      </c>
+      <c r="G3" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="34">
         <v>1</v>
       </c>
       <c r="J3">
@@ -3531,36 +3531,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="35">
-        <v>1</v>
-      </c>
-      <c r="N3" s="35">
-        <v>0</v>
-      </c>
-      <c r="O3" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="30" customFormat="1" spans="1:18">
-      <c r="A4" s="30">
+      <c r="M3" s="34">
+        <v>1</v>
+      </c>
+      <c r="N3" s="34">
+        <v>0</v>
+      </c>
+      <c r="O3" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="29" customFormat="1" spans="1:18">
+      <c r="A4" s="29">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="29">
         <v>2</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="35">
+      <c r="G4" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="34">
         <v>1</v>
       </c>
       <c r="J4">
@@ -3569,36 +3569,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="35">
-        <v>1</v>
-      </c>
-      <c r="N4" s="35">
-        <v>0</v>
-      </c>
-      <c r="O4" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="30" customFormat="1" spans="1:18">
-      <c r="A5" s="30">
+      <c r="M4" s="34">
+        <v>1</v>
+      </c>
+      <c r="N4" s="34">
+        <v>0</v>
+      </c>
+      <c r="O4" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="29" customFormat="1" spans="1:18">
+      <c r="A5" s="29">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="30">
-        <v>0</v>
-      </c>
-      <c r="D5" s="30" t="s">
+      <c r="C5" s="29">
+        <v>0</v>
+      </c>
+      <c r="D5" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="35">
+      <c r="G5" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="34">
         <v>1</v>
       </c>
       <c r="J5">
@@ -3607,48 +3607,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="35">
-        <v>1</v>
-      </c>
-      <c r="N5" s="35">
-        <v>0</v>
-      </c>
-      <c r="O5" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="30">
-        <v>0</v>
-      </c>
-      <c r="R5" s="30" t="s">
+      <c r="M5" s="34">
+        <v>1</v>
+      </c>
+      <c r="N5" s="34">
+        <v>0</v>
+      </c>
+      <c r="O5" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="29">
+        <v>0</v>
+      </c>
+      <c r="R5" s="29" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="36" customFormat="1" spans="1:18">
-      <c r="A6" s="36">
+    <row r="6" s="35" customFormat="1" spans="1:18">
+      <c r="A6" s="35">
         <v>101</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="36">
-        <v>0</v>
-      </c>
-      <c r="D6" s="36" t="s">
+      <c r="C6" s="35">
+        <v>0</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="35" t="b">
+      <c r="G6" s="34" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="34">
         <v>1</v>
       </c>
       <c r="J6">
@@ -3660,39 +3660,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="35">
-        <v>1</v>
-      </c>
-      <c r="N6" s="35">
-        <v>0</v>
-      </c>
-      <c r="O6" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="36" customFormat="1" spans="1:18">
-      <c r="A7" s="36">
+      <c r="M6" s="34">
+        <v>1</v>
+      </c>
+      <c r="N6" s="34">
+        <v>0</v>
+      </c>
+      <c r="O6" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="35" customFormat="1" spans="1:18">
+      <c r="A7" s="35">
         <v>102</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="36">
-        <v>0</v>
-      </c>
-      <c r="D7" s="36" t="s">
+      <c r="C7" s="35">
+        <v>0</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="35">
+      <c r="G7" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="34">
         <v>1</v>
       </c>
       <c r="J7">
@@ -3701,16 +3701,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="35">
-        <v>1</v>
-      </c>
-      <c r="N7" s="35">
-        <v>0</v>
-      </c>
-      <c r="O7" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="36">
+      <c r="M7" s="34">
+        <v>1</v>
+      </c>
+      <c r="N7" s="34">
+        <v>0</v>
+      </c>
+      <c r="O7" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="35">
         <v>0</v>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       <c r="A8">
         <v>201</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>33</v>
       </c>
       <c r="C8">
@@ -3733,13 +3733,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="35" t="b">
+      <c r="G8" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <v>1</v>
       </c>
       <c r="J8">
@@ -3751,13 +3751,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="35">
-        <v>1</v>
-      </c>
-      <c r="N8" s="35">
-        <v>0</v>
-      </c>
-      <c r="O8" s="35">
+      <c r="M8" s="34">
+        <v>1</v>
+      </c>
+      <c r="N8" s="34">
+        <v>0</v>
+      </c>
+      <c r="O8" s="34">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -3770,59 +3770,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="29" customFormat="1" spans="1:18">
-      <c r="A9" s="29">
+    <row r="9" s="28" customFormat="1" spans="1:18">
+      <c r="A9" s="28">
         <v>202</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="29">
-        <v>1</v>
-      </c>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="28">
+        <v>1</v>
+      </c>
+      <c r="D9" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="29" t="s">
+      <c r="G9" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="37">
-        <v>1</v>
-      </c>
-      <c r="J9" s="29">
-        <v>0</v>
-      </c>
-      <c r="K9" s="29">
+      <c r="I9" s="36">
+        <v>1</v>
+      </c>
+      <c r="J9" s="28">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28">
         <v>2</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="37">
-        <v>1</v>
-      </c>
-      <c r="N9" s="37">
-        <v>0</v>
-      </c>
-      <c r="O9" s="37">
-        <v>0</v>
-      </c>
-      <c r="P9" s="29" t="s">
+      <c r="M9" s="36">
+        <v>1</v>
+      </c>
+      <c r="N9" s="36">
+        <v>0</v>
+      </c>
+      <c r="O9" s="36">
+        <v>0</v>
+      </c>
+      <c r="P9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="29">
+      <c r="Q9" s="28">
         <v>3</v>
       </c>
-      <c r="R9" s="29" t="s">
+      <c r="R9" s="28" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       <c r="A10">
         <v>203</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>46</v>
       </c>
       <c r="C10">
@@ -3845,13 +3845,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="35" t="b">
+      <c r="G10" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <v>1</v>
       </c>
       <c r="J10">
@@ -3863,13 +3863,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="35">
-        <v>1</v>
-      </c>
-      <c r="N10" s="35">
-        <v>0</v>
-      </c>
-      <c r="O10" s="35">
+      <c r="M10" s="34">
+        <v>1</v>
+      </c>
+      <c r="N10" s="34">
+        <v>0</v>
+      </c>
+      <c r="O10" s="34">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -3886,7 +3886,7 @@
       <c r="A11">
         <v>204</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C11">
@@ -3898,13 +3898,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="35" t="b">
+      <c r="G11" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <v>1</v>
       </c>
       <c r="J11">
@@ -3916,13 +3916,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="35">
-        <v>1</v>
-      </c>
-      <c r="N11" s="35">
-        <v>0</v>
-      </c>
-      <c r="O11" s="35">
+      <c r="M11" s="34">
+        <v>1</v>
+      </c>
+      <c r="N11" s="34">
+        <v>0</v>
+      </c>
+      <c r="O11" s="34">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -3939,7 +3939,7 @@
       <c r="A12">
         <v>205</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>58</v>
       </c>
       <c r="C12">
@@ -3954,13 +3954,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="35" t="b">
+      <c r="G12" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <v>1</v>
       </c>
       <c r="J12">
@@ -3972,13 +3972,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="35">
-        <v>1</v>
-      </c>
-      <c r="N12" s="35">
-        <v>0</v>
-      </c>
-      <c r="O12" s="35">
+      <c r="M12" s="34">
+        <v>1</v>
+      </c>
+      <c r="N12" s="34">
+        <v>0</v>
+      </c>
+      <c r="O12" s="34">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -3995,7 +3995,7 @@
       <c r="A13">
         <v>206</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C13">
@@ -4010,13 +4010,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="35" t="b">
+      <c r="G13" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <v>1</v>
       </c>
       <c r="J13">
@@ -4028,13 +4028,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="35">
-        <v>1</v>
-      </c>
-      <c r="N13" s="35">
-        <v>1</v>
-      </c>
-      <c r="O13" s="35">
+      <c r="M13" s="34">
+        <v>1</v>
+      </c>
+      <c r="N13" s="34">
+        <v>1</v>
+      </c>
+      <c r="O13" s="34">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -4051,7 +4051,7 @@
       <c r="A14">
         <v>207</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C14">
@@ -4063,16 +4063,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="38" t="s">
+      <c r="F14" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="35" t="b">
+      <c r="G14" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <v>1</v>
       </c>
       <c r="J14">
@@ -4084,13 +4084,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="35">
-        <v>1</v>
-      </c>
-      <c r="N14" s="35">
-        <v>0</v>
-      </c>
-      <c r="O14" s="35">
+      <c r="M14" s="34">
+        <v>1</v>
+      </c>
+      <c r="N14" s="34">
+        <v>0</v>
+      </c>
+      <c r="O14" s="34">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -4107,7 +4107,7 @@
       <c r="A15">
         <v>208</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C15">
@@ -4119,16 +4119,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="35" t="b">
+      <c r="G15" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <v>1</v>
       </c>
       <c r="J15">
@@ -4140,13 +4140,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="35">
-        <v>1</v>
-      </c>
-      <c r="N15" s="35">
-        <v>0</v>
-      </c>
-      <c r="O15" s="35">
+      <c r="M15" s="34">
+        <v>1</v>
+      </c>
+      <c r="N15" s="34">
+        <v>0</v>
+      </c>
+      <c r="O15" s="34">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -4163,7 +4163,7 @@
       <c r="A16">
         <v>209</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>82</v>
       </c>
       <c r="C16">
@@ -4178,13 +4178,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="35" t="b">
+      <c r="G16" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <v>1</v>
       </c>
       <c r="J16">
@@ -4196,13 +4196,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="35">
-        <v>1</v>
-      </c>
-      <c r="N16" s="35">
-        <v>0</v>
-      </c>
-      <c r="O16" s="35">
+      <c r="M16" s="34">
+        <v>1</v>
+      </c>
+      <c r="N16" s="34">
+        <v>0</v>
+      </c>
+      <c r="O16" s="34">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -4219,7 +4219,7 @@
       <c r="A17">
         <v>210</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>90</v>
       </c>
       <c r="C17">
@@ -4234,13 +4234,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="35" t="b">
+      <c r="G17" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <v>1</v>
       </c>
       <c r="J17">
@@ -4252,13 +4252,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="35">
-        <v>1</v>
-      </c>
-      <c r="N17" s="35">
-        <v>0</v>
-      </c>
-      <c r="O17" s="35">
+      <c r="M17" s="34">
+        <v>1</v>
+      </c>
+      <c r="N17" s="34">
+        <v>0</v>
+      </c>
+      <c r="O17" s="34">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -4275,7 +4275,7 @@
       <c r="A18">
         <v>211</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>95</v>
       </c>
       <c r="C18">
@@ -4284,10 +4284,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="35">
+      <c r="G18" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="34">
         <v>1</v>
       </c>
       <c r="J18">
@@ -4296,13 +4296,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="35">
-        <v>1</v>
-      </c>
-      <c r="N18" s="35">
-        <v>0</v>
-      </c>
-      <c r="O18" s="35">
+      <c r="M18" s="34">
+        <v>1</v>
+      </c>
+      <c r="N18" s="34">
+        <v>0</v>
+      </c>
+      <c r="O18" s="34">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -4313,7 +4313,7 @@
       <c r="A19">
         <v>212</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>97</v>
       </c>
       <c r="C19">
@@ -4328,13 +4328,13 @@
       <c r="F19" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="35" t="b">
+      <c r="G19" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <v>1</v>
       </c>
       <c r="J19">
@@ -4346,13 +4346,13 @@
       <c r="L19" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="35">
-        <v>1</v>
-      </c>
-      <c r="N19" s="35">
-        <v>0</v>
-      </c>
-      <c r="O19" s="35">
+      <c r="M19" s="34">
+        <v>1</v>
+      </c>
+      <c r="N19" s="34">
+        <v>0</v>
+      </c>
+      <c r="O19" s="34">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -4369,7 +4369,7 @@
       <c r="A20">
         <v>213</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>105</v>
       </c>
       <c r="C20">
@@ -4384,13 +4384,13 @@
       <c r="F20" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="35" t="b">
+      <c r="G20" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <v>1</v>
       </c>
       <c r="J20">
@@ -4402,13 +4402,13 @@
       <c r="L20" t="s">
         <v>102</v>
       </c>
-      <c r="M20" s="35">
-        <v>1</v>
-      </c>
-      <c r="N20" s="35">
-        <v>0</v>
-      </c>
-      <c r="O20" s="35">
+      <c r="M20" s="34">
+        <v>1</v>
+      </c>
+      <c r="N20" s="34">
+        <v>0</v>
+      </c>
+      <c r="O20" s="34">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -4425,7 +4425,7 @@
       <c r="A21">
         <v>214</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>111</v>
       </c>
       <c r="C21">
@@ -4440,13 +4440,13 @@
       <c r="F21" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="35" t="b">
+      <c r="G21" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="34">
         <v>1</v>
       </c>
       <c r="J21">
@@ -4458,13 +4458,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="35">
-        <v>1</v>
-      </c>
-      <c r="N21" s="35">
-        <v>0</v>
-      </c>
-      <c r="O21" s="35">
+      <c r="M21" s="34">
+        <v>1</v>
+      </c>
+      <c r="N21" s="34">
+        <v>0</v>
+      </c>
+      <c r="O21" s="34">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -4481,7 +4481,7 @@
       <c r="A22">
         <v>215</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>117</v>
       </c>
       <c r="C22">
@@ -4496,13 +4496,13 @@
       <c r="F22" t="s">
         <v>119</v>
       </c>
-      <c r="G22" s="35" t="b">
+      <c r="G22" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="34">
         <v>1</v>
       </c>
       <c r="J22">
@@ -4514,13 +4514,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="35">
-        <v>1</v>
-      </c>
-      <c r="N22" s="35">
-        <v>0</v>
-      </c>
-      <c r="O22" s="35">
+      <c r="M22" s="34">
+        <v>1</v>
+      </c>
+      <c r="N22" s="34">
+        <v>0</v>
+      </c>
+      <c r="O22" s="34">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -4533,32 +4533,32 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="30" customFormat="1" spans="1:18">
-      <c r="A23" s="30">
+    <row r="23" s="29" customFormat="1" spans="1:18">
+      <c r="A23" s="29">
         <v>301</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="30">
-        <v>1</v>
-      </c>
-      <c r="D23" s="30" t="s">
+      <c r="C23" s="29">
+        <v>1</v>
+      </c>
+      <c r="D23" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="E23" s="30" t="s">
+      <c r="E23" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="30" t="s">
+      <c r="F23" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="30" t="s">
+      <c r="G23" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <v>1</v>
       </c>
       <c r="J23">
@@ -4567,54 +4567,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="30" t="s">
+      <c r="L23" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="M23" s="35">
-        <v>1</v>
-      </c>
-      <c r="N23" s="35">
-        <v>0</v>
-      </c>
-      <c r="O23" s="35">
-        <v>0</v>
-      </c>
-      <c r="P23" s="30" t="s">
+      <c r="M23" s="34">
+        <v>1</v>
+      </c>
+      <c r="N23" s="34">
+        <v>0</v>
+      </c>
+      <c r="O23" s="34">
+        <v>0</v>
+      </c>
+      <c r="P23" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="Q23" s="30">
+      <c r="Q23" s="29">
         <v>3</v>
       </c>
-      <c r="R23" s="30" t="s">
+      <c r="R23" s="29" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" s="30" customFormat="1" spans="1:18">
-      <c r="A24" s="30">
+    <row r="24" s="29" customFormat="1" spans="1:18">
+      <c r="A24" s="29">
         <v>302</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="30">
-        <v>1</v>
-      </c>
-      <c r="D24" s="30" t="s">
+      <c r="C24" s="29">
+        <v>1</v>
+      </c>
+      <c r="D24" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="E24" s="30" t="s">
+      <c r="E24" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="30" t="s">
+      <c r="F24" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="G24" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="30" t="s">
+      <c r="G24" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="34">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -4623,51 +4623,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="30" t="s">
+      <c r="L24" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="M24" s="35">
-        <v>1</v>
-      </c>
-      <c r="N24" s="35">
-        <v>0</v>
-      </c>
-      <c r="O24" s="35">
-        <v>0</v>
-      </c>
-      <c r="P24" s="30" t="s">
+      <c r="M24" s="34">
+        <v>1</v>
+      </c>
+      <c r="N24" s="34">
+        <v>0</v>
+      </c>
+      <c r="O24" s="34">
+        <v>0</v>
+      </c>
+      <c r="P24" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q24" s="30">
+      <c r="Q24" s="29">
         <v>3</v>
       </c>
-      <c r="R24" s="30" t="s">
+      <c r="R24" s="29" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" s="30" customFormat="1" spans="1:18">
-      <c r="A25" s="30">
+    <row r="25" s="29" customFormat="1" spans="1:18">
+      <c r="A25" s="29">
         <v>303</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="30">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30" t="s">
+      <c r="C25" s="29">
+        <v>1</v>
+      </c>
+      <c r="D25" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="E25" s="30" t="s">
+      <c r="E25" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="30" t="s">
+      <c r="G25" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="34">
         <v>1</v>
       </c>
       <c r="J25">
@@ -4676,51 +4676,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="35">
-        <v>1</v>
-      </c>
-      <c r="N25" s="35">
-        <v>0</v>
-      </c>
-      <c r="O25" s="35">
-        <v>0</v>
-      </c>
-      <c r="P25" s="30" t="s">
+      <c r="M25" s="34">
+        <v>1</v>
+      </c>
+      <c r="N25" s="34">
+        <v>0</v>
+      </c>
+      <c r="O25" s="34">
+        <v>0</v>
+      </c>
+      <c r="P25" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q25" s="30">
+      <c r="Q25" s="29">
         <v>3</v>
       </c>
-      <c r="R25" s="30" t="s">
+      <c r="R25" s="29" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="26" s="30" customFormat="1" spans="1:18">
-      <c r="A26" s="30">
+    <row r="26" s="29" customFormat="1" spans="1:18">
+      <c r="A26" s="29">
         <v>304</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="30">
-        <v>1</v>
-      </c>
-      <c r="D26" s="30" t="s">
+      <c r="C26" s="29">
+        <v>1</v>
+      </c>
+      <c r="D26" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="30" t="s">
+      <c r="E26" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="29" t="s">
         <v>138</v>
       </c>
-      <c r="G26" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="30" t="s">
+      <c r="G26" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="34">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -4729,54 +4729,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="30" t="s">
+      <c r="L26" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="35">
-        <v>1</v>
-      </c>
-      <c r="N26" s="35">
-        <v>0</v>
-      </c>
-      <c r="O26" s="35">
-        <v>0</v>
-      </c>
-      <c r="P26" s="30" t="s">
+      <c r="M26" s="34">
+        <v>1</v>
+      </c>
+      <c r="N26" s="34">
+        <v>0</v>
+      </c>
+      <c r="O26" s="34">
+        <v>0</v>
+      </c>
+      <c r="P26" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q26" s="30">
+      <c r="Q26" s="29">
         <v>3</v>
       </c>
-      <c r="R26" s="30" t="s">
+      <c r="R26" s="29" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="27" s="30" customFormat="1" spans="1:18">
-      <c r="A27" s="30">
+    <row r="27" s="29" customFormat="1" spans="1:18">
+      <c r="A27" s="29">
         <v>305</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="29">
         <v>3</v>
       </c>
-      <c r="D27" s="30" t="s">
+      <c r="D27" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="30" t="s">
+      <c r="E27" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="30" t="s">
+      <c r="F27" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="30" t="s">
+      <c r="G27" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="34">
         <v>1</v>
       </c>
       <c r="J27">
@@ -4788,51 +4788,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="35">
-        <v>1</v>
-      </c>
-      <c r="N27" s="35">
-        <v>0</v>
-      </c>
-      <c r="O27" s="35">
-        <v>0</v>
-      </c>
-      <c r="P27" s="30" t="s">
+      <c r="M27" s="34">
+        <v>1</v>
+      </c>
+      <c r="N27" s="34">
+        <v>0</v>
+      </c>
+      <c r="O27" s="34">
+        <v>0</v>
+      </c>
+      <c r="P27" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="Q27" s="30">
+      <c r="Q27" s="29">
         <v>3</v>
       </c>
-      <c r="R27" s="30" t="s">
+      <c r="R27" s="29" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="28" s="30" customFormat="1" spans="1:18">
-      <c r="A28" s="30">
+    <row r="28" s="29" customFormat="1" spans="1:18">
+      <c r="A28" s="29">
         <v>306</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="29">
         <v>2</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="30" t="s">
+      <c r="E28" s="29" t="s">
         <v>148</v>
       </c>
-      <c r="F28" s="30" t="s">
+      <c r="F28" s="29" t="s">
         <v>149</v>
       </c>
-      <c r="G28" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="30">
-        <v>0</v>
-      </c>
-      <c r="I28" s="35">
+      <c r="G28" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="29">
+        <v>0</v>
+      </c>
+      <c r="I28" s="34">
         <v>1</v>
       </c>
       <c r="J28">
@@ -4841,54 +4841,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="30">
-        <v>1</v>
-      </c>
-      <c r="M28" s="35">
-        <v>1</v>
-      </c>
-      <c r="N28" s="35">
-        <v>0</v>
-      </c>
-      <c r="O28" s="35">
-        <v>0</v>
-      </c>
-      <c r="P28" s="30" t="s">
+      <c r="L28" s="29">
+        <v>1</v>
+      </c>
+      <c r="M28" s="34">
+        <v>1</v>
+      </c>
+      <c r="N28" s="34">
+        <v>0</v>
+      </c>
+      <c r="O28" s="34">
+        <v>0</v>
+      </c>
+      <c r="P28" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="Q28" s="30">
+      <c r="Q28" s="29">
         <v>3</v>
       </c>
-      <c r="R28" s="30" t="s">
+      <c r="R28" s="29" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="29" s="30" customFormat="1" spans="1:18">
-      <c r="A29" s="30">
+    <row r="29" s="29" customFormat="1" spans="1:18">
+      <c r="A29" s="29">
         <v>307</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="30">
-        <v>1</v>
-      </c>
-      <c r="D29" s="30" t="s">
+      <c r="C29" s="29">
+        <v>1</v>
+      </c>
+      <c r="D29" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="30" t="s">
+      <c r="E29" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="30" t="s">
+      <c r="F29" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="G29" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="30" t="s">
+      <c r="G29" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="34">
         <v>1</v>
       </c>
       <c r="J29">
@@ -4897,54 +4897,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="30" t="s">
+      <c r="L29" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="34">
         <v>0.1</v>
       </c>
-      <c r="N29" s="35">
-        <v>0</v>
-      </c>
-      <c r="O29" s="35">
+      <c r="N29" s="34">
+        <v>0</v>
+      </c>
+      <c r="O29" s="34">
         <v>0.17</v>
       </c>
-      <c r="P29" s="30" t="s">
+      <c r="P29" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q29" s="30">
+      <c r="Q29" s="29">
         <v>3</v>
       </c>
-      <c r="R29" s="30" t="s">
+      <c r="R29" s="29" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="30" s="30" customFormat="1" spans="1:18">
-      <c r="A30" s="30">
+    <row r="30" s="29" customFormat="1" spans="1:18">
+      <c r="A30" s="29">
         <v>308</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C30" s="30">
-        <v>1</v>
-      </c>
-      <c r="D30" s="30" t="s">
+      <c r="C30" s="29">
+        <v>1</v>
+      </c>
+      <c r="D30" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="30" t="s">
+      <c r="E30" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="30" t="s">
+      <c r="F30" s="29" t="s">
         <v>159</v>
       </c>
-      <c r="G30" s="35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="30" t="s">
+      <c r="G30" s="34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="34">
         <v>1</v>
       </c>
       <c r="J30">
@@ -4953,54 +4953,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="30" t="s">
+      <c r="L30" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="M30" s="35">
-        <v>1</v>
-      </c>
-      <c r="N30" s="35">
-        <v>0</v>
-      </c>
-      <c r="O30" s="35">
-        <v>0</v>
-      </c>
-      <c r="P30" s="30" t="s">
+      <c r="M30" s="34">
+        <v>1</v>
+      </c>
+      <c r="N30" s="34">
+        <v>0</v>
+      </c>
+      <c r="O30" s="34">
+        <v>0</v>
+      </c>
+      <c r="P30" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="Q30" s="30">
+      <c r="Q30" s="29">
         <v>3</v>
       </c>
-      <c r="R30" s="30" t="s">
+      <c r="R30" s="29" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="31" s="30" customFormat="1" spans="1:18">
-      <c r="A31" s="30">
+    <row r="31" s="29" customFormat="1" spans="1:18">
+      <c r="A31" s="29">
         <v>309</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="29">
         <v>2</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="29" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="G31" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="30" t="s">
+      <c r="G31" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="34">
         <v>1</v>
       </c>
       <c r="J31">
@@ -5009,54 +5009,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="30" t="s">
+      <c r="L31" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="M31" s="35">
-        <v>1</v>
-      </c>
-      <c r="N31" s="35">
-        <v>0</v>
-      </c>
-      <c r="O31" s="35">
-        <v>0</v>
-      </c>
-      <c r="P31" s="30" t="s">
+      <c r="M31" s="34">
+        <v>1</v>
+      </c>
+      <c r="N31" s="34">
+        <v>0</v>
+      </c>
+      <c r="O31" s="34">
+        <v>0</v>
+      </c>
+      <c r="P31" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="Q31" s="30">
+      <c r="Q31" s="29">
         <v>3</v>
       </c>
-      <c r="R31" s="30" t="s">
+      <c r="R31" s="29" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" s="30" customFormat="1" spans="1:18">
-      <c r="A32" s="30">
+    <row r="32" s="29" customFormat="1" spans="1:18">
+      <c r="A32" s="29">
         <v>310</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="29">
         <v>2</v>
       </c>
-      <c r="D32" s="30" t="s">
+      <c r="D32" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="G32" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="30" t="s">
+      <c r="G32" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="34">
         <v>1</v>
       </c>
       <c r="J32">
@@ -5065,54 +5065,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="30" t="s">
+      <c r="L32" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="M32" s="35">
-        <v>1</v>
-      </c>
-      <c r="N32" s="35">
-        <v>0</v>
-      </c>
-      <c r="O32" s="35">
-        <v>0</v>
-      </c>
-      <c r="P32" s="30" t="s">
+      <c r="M32" s="34">
+        <v>1</v>
+      </c>
+      <c r="N32" s="34">
+        <v>0</v>
+      </c>
+      <c r="O32" s="34">
+        <v>0</v>
+      </c>
+      <c r="P32" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="Q32" s="30">
+      <c r="Q32" s="29">
         <v>4</v>
       </c>
-      <c r="R32" s="30" t="s">
+      <c r="R32" s="29" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="33" s="30" customFormat="1" spans="1:21">
-      <c r="A33" s="30">
+    <row r="33" s="29" customFormat="1" spans="1:21">
+      <c r="A33" s="29">
         <v>311</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="29">
         <v>2</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="E33" s="30" t="s">
+      <c r="E33" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="F33" s="30" t="s">
+      <c r="F33" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="G33" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="30">
-        <v>0</v>
-      </c>
-      <c r="I33" s="35">
+      <c r="G33" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="29">
+        <v>0</v>
+      </c>
+      <c r="I33" s="34">
         <v>1</v>
       </c>
       <c r="J33">
@@ -5121,45 +5121,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="30">
-        <v>1</v>
-      </c>
-      <c r="M33" s="35">
-        <v>1</v>
-      </c>
-      <c r="N33" s="35">
-        <v>0</v>
-      </c>
-      <c r="O33" s="35">
-        <v>0</v>
-      </c>
-      <c r="P33" s="30" t="s">
+      <c r="L33" s="29">
+        <v>1</v>
+      </c>
+      <c r="M33" s="34">
+        <v>1</v>
+      </c>
+      <c r="N33" s="34">
+        <v>0</v>
+      </c>
+      <c r="O33" s="34">
+        <v>0</v>
+      </c>
+      <c r="P33" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="Q33" s="30">
+      <c r="Q33" s="29">
         <v>3</v>
       </c>
-      <c r="R33" s="30" t="s">
+      <c r="R33" s="29" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" s="30" customFormat="1" spans="1:21">
-      <c r="A34" s="30">
+    <row r="34" s="29" customFormat="1" spans="1:21">
+      <c r="A34" s="29">
         <v>312</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="29">
         <v>2</v>
       </c>
-      <c r="D34" s="30" t="s">
+      <c r="D34" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="35">
+      <c r="G34" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="34">
         <v>1</v>
       </c>
       <c r="J34">
@@ -5168,45 +5168,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="35">
-        <v>1</v>
-      </c>
-      <c r="N34" s="35">
-        <v>0</v>
-      </c>
-      <c r="O34" s="35">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="30">
-        <v>1</v>
-      </c>
-      <c r="R34" s="30" t="s">
+      <c r="M34" s="34">
+        <v>1</v>
+      </c>
+      <c r="N34" s="34">
+        <v>0</v>
+      </c>
+      <c r="O34" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>1</v>
+      </c>
+      <c r="R34" s="29" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="35" s="28" customFormat="1" spans="1:21">
-      <c r="A35" s="28">
+    <row r="35" s="27" customFormat="1" spans="1:21">
+      <c r="A35" s="27">
         <v>401</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <v>2</v>
       </c>
-      <c r="D35" s="28" t="s">
+      <c r="D35" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="38" t="s">
+      <c r="F35" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="28" t="s">
+      <c r="G35" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="34">
         <v>1</v>
       </c>
       <c r="J35">
@@ -5218,45 +5218,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="35">
-        <v>1</v>
-      </c>
-      <c r="N35" s="35">
-        <v>0</v>
-      </c>
-      <c r="O35" s="35">
-        <v>0</v>
-      </c>
-      <c r="P35" s="28" t="s">
+      <c r="M35" s="34">
+        <v>1</v>
+      </c>
+      <c r="N35" s="34">
+        <v>0</v>
+      </c>
+      <c r="O35" s="34">
+        <v>0</v>
+      </c>
+      <c r="P35" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="28">
+      <c r="Q35" s="27">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="28" customFormat="1" spans="1:21">
-      <c r="A36" s="28">
+    <row r="36" s="27" customFormat="1" spans="1:21">
+      <c r="A36" s="27">
         <v>402</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <v>2</v>
       </c>
-      <c r="D36" s="28" t="s">
+      <c r="D36" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="39" t="s">
+      <c r="F36" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="28" t="s">
+      <c r="G36" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="34">
         <v>1</v>
       </c>
       <c r="J36">
@@ -5268,48 +5268,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="35">
-        <v>1</v>
-      </c>
-      <c r="N36" s="35">
-        <v>0</v>
-      </c>
-      <c r="O36" s="35">
-        <v>0</v>
-      </c>
-      <c r="P36" s="28" t="s">
+      <c r="M36" s="34">
+        <v>1</v>
+      </c>
+      <c r="N36" s="34">
+        <v>0</v>
+      </c>
+      <c r="O36" s="34">
+        <v>0</v>
+      </c>
+      <c r="P36" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="28">
+      <c r="Q36" s="27">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="28" customFormat="1" spans="1:21">
-      <c r="A37" s="28">
+    <row r="37" s="27" customFormat="1" spans="1:21">
+      <c r="A37" s="27">
         <v>403</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <v>2</v>
       </c>
-      <c r="D37" s="28" t="s">
+      <c r="D37" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="28" t="s">
+      <c r="E37" s="27" t="s">
         <v>182</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F37" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="28" t="s">
+      <c r="G37" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="35">
+      <c r="I37" s="34">
         <v>1</v>
       </c>
       <c r="J37">
@@ -5318,83 +5318,83 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="28" t="s">
+      <c r="L37" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="35">
-        <v>1</v>
-      </c>
-      <c r="N37" s="35">
-        <v>0</v>
-      </c>
-      <c r="O37" s="35">
-        <v>0</v>
-      </c>
-      <c r="P37" s="28" t="s">
+      <c r="M37" s="34">
+        <v>1</v>
+      </c>
+      <c r="N37" s="34">
+        <v>0</v>
+      </c>
+      <c r="O37" s="34">
+        <v>0</v>
+      </c>
+      <c r="P37" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="28">
+      <c r="Q37" s="27">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="37" customFormat="1" spans="1:21">
-      <c r="A38" s="37">
+    <row r="38" s="36" customFormat="1" spans="1:21">
+      <c r="A38" s="36">
         <v>404</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C38" s="37">
-        <v>1</v>
-      </c>
-      <c r="D38" s="29" t="s">
+      <c r="C38" s="36">
+        <v>1</v>
+      </c>
+      <c r="D38" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="37" t="s">
+      <c r="E38" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="37" t="s">
+      <c r="G38" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="37">
-        <v>1</v>
-      </c>
-      <c r="J38" s="29">
-        <v>0</v>
-      </c>
-      <c r="K38" s="29">
+      <c r="I38" s="36">
+        <v>1</v>
+      </c>
+      <c r="J38" s="28">
+        <v>0</v>
+      </c>
+      <c r="K38" s="28">
         <v>2</v>
       </c>
-      <c r="L38" s="37" t="s">
+      <c r="L38" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="37">
-        <v>1</v>
-      </c>
-      <c r="N38" s="37">
-        <v>0</v>
-      </c>
-      <c r="O38" s="37">
-        <v>0</v>
-      </c>
-      <c r="P38" s="37" t="s">
+      <c r="M38" s="36">
+        <v>1</v>
+      </c>
+      <c r="N38" s="36">
+        <v>0</v>
+      </c>
+      <c r="O38" s="36">
+        <v>0</v>
+      </c>
+      <c r="P38" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="37">
+      <c r="Q38" s="36">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="28" customFormat="1" spans="1:21">
-      <c r="A39" s="28">
+    <row r="39" s="27" customFormat="1" spans="1:21">
+      <c r="A39" s="27">
         <v>405</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="15" t="s">
         <v>184</v>
       </c>
       <c r="C39">
@@ -5409,13 +5409,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="35" t="b">
+      <c r="G39" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="34">
         <v>1</v>
       </c>
       <c r="J39">
@@ -5427,13 +5427,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="35">
-        <v>1</v>
-      </c>
-      <c r="N39" s="35">
-        <v>0</v>
-      </c>
-      <c r="O39" s="35">
+      <c r="M39" s="34">
+        <v>1</v>
+      </c>
+      <c r="N39" s="34">
+        <v>0</v>
+      </c>
+      <c r="O39" s="34">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -5449,32 +5449,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="28" customFormat="1" spans="1:21">
-      <c r="A40" s="28">
+    <row r="40" s="27" customFormat="1" spans="1:21">
+      <c r="A40" s="27">
         <v>406</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C40" s="28">
-        <v>1</v>
-      </c>
-      <c r="D40" s="28" t="s">
+      <c r="C40" s="27">
+        <v>1</v>
+      </c>
+      <c r="D40" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="E40" s="27" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="35" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="28">
-        <v>0</v>
-      </c>
-      <c r="I40" s="35">
+      <c r="G40" s="34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="27">
+        <v>0</v>
+      </c>
+      <c r="I40" s="34">
         <v>1</v>
       </c>
       <c r="J40">
@@ -5483,30 +5483,30 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="28">
+      <c r="L40" s="27">
         <v>3</v>
       </c>
-      <c r="M40" s="35">
-        <v>1</v>
-      </c>
-      <c r="N40" s="35">
-        <v>0</v>
-      </c>
-      <c r="O40" s="35">
-        <v>0</v>
-      </c>
-      <c r="P40" s="28" t="s">
+      <c r="M40" s="34">
+        <v>1</v>
+      </c>
+      <c r="N40" s="34">
+        <v>0</v>
+      </c>
+      <c r="O40" s="34">
+        <v>0</v>
+      </c>
+      <c r="P40" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="28">
+      <c r="Q40" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="28">
+      <c r="A41" s="27">
         <v>407</v>
       </c>
-      <c r="B41" s="15" t="s">
+      <c r="B41" s="13" t="s">
         <v>186</v>
       </c>
       <c r="C41">
@@ -5521,13 +5521,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="35" t="b">
+      <c r="G41" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="34">
         <v>1</v>
       </c>
       <c r="J41">
@@ -5539,13 +5539,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="35">
-        <v>1</v>
-      </c>
-      <c r="N41" s="35">
-        <v>0</v>
-      </c>
-      <c r="O41" s="35">
+      <c r="M41" s="34">
+        <v>1</v>
+      </c>
+      <c r="N41" s="34">
+        <v>0</v>
+      </c>
+      <c r="O41" s="34">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -5559,10 +5559,10 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="28">
+      <c r="A42" s="27">
         <v>408</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>187</v>
       </c>
       <c r="C42">
@@ -5577,13 +5577,13 @@
       <c r="F42" t="s">
         <v>108</v>
       </c>
-      <c r="G42" s="35" t="b">
+      <c r="G42" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>101</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="34">
         <v>1</v>
       </c>
       <c r="J42">
@@ -5595,13 +5595,13 @@
       <c r="L42" t="s">
         <v>102</v>
       </c>
-      <c r="M42" s="35">
-        <v>1</v>
-      </c>
-      <c r="N42" s="35">
-        <v>0</v>
-      </c>
-      <c r="O42" s="35">
+      <c r="M42" s="34">
+        <v>1</v>
+      </c>
+      <c r="N42" s="34">
+        <v>0</v>
+      </c>
+      <c r="O42" s="34">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -5615,10 +5615,10 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="28">
+      <c r="A43" s="27">
         <v>409</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>188</v>
       </c>
       <c r="C43">
@@ -5633,13 +5633,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="35" t="b">
+      <c r="G43" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="35">
+      <c r="I43" s="34">
         <v>1</v>
       </c>
       <c r="J43">
@@ -5651,13 +5651,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="35">
-        <v>1</v>
-      </c>
-      <c r="N43" s="35">
-        <v>0</v>
-      </c>
-      <c r="O43" s="35">
+      <c r="M43" s="34">
+        <v>1</v>
+      </c>
+      <c r="N43" s="34">
+        <v>0</v>
+      </c>
+      <c r="O43" s="34">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -5671,10 +5671,10 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="28">
+      <c r="A44" s="27">
         <v>410</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>189</v>
       </c>
       <c r="C44">
@@ -5689,13 +5689,13 @@
       <c r="F44" t="s">
         <v>100</v>
       </c>
-      <c r="G44" s="35" t="b">
+      <c r="G44" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>101</v>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="34">
         <v>1</v>
       </c>
       <c r="J44">
@@ -5707,13 +5707,13 @@
       <c r="L44" t="s">
         <v>102</v>
       </c>
-      <c r="M44" s="35">
-        <v>1</v>
-      </c>
-      <c r="N44" s="35">
-        <v>0</v>
-      </c>
-      <c r="O44" s="35">
+      <c r="M44" s="34">
+        <v>1</v>
+      </c>
+      <c r="N44" s="34">
+        <v>0</v>
+      </c>
+      <c r="O44" s="34">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -5727,10 +5727,10 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="28">
+      <c r="A45" s="27">
         <v>411</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>190</v>
       </c>
       <c r="C45">
@@ -5745,13 +5745,13 @@
       <c r="F45" t="s">
         <v>119</v>
       </c>
-      <c r="G45" s="35" t="b">
+      <c r="G45" s="34" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="34">
         <v>1</v>
       </c>
       <c r="J45">
@@ -5763,13 +5763,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="35">
-        <v>1</v>
-      </c>
-      <c r="N45" s="35">
-        <v>0</v>
-      </c>
-      <c r="O45" s="35">
+      <c r="M45" s="34">
+        <v>1</v>
+      </c>
+      <c r="N45" s="34">
+        <v>0</v>
+      </c>
+      <c r="O45" s="34">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -5804,37 +5804,37 @@
     <col min="8" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1" spans="1:8">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" s="13" customFormat="1" spans="1:8">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>330</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>334</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="13" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="2" s="15" customFormat="1" spans="1:8">
-      <c r="A2" s="19">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
+    <row r="2" s="13" customFormat="1" spans="1:8">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>336</v>
       </c>
       <c r="C2" t="s">
@@ -5843,18 +5843,18 @@
       <c r="D2" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
         <v>339</v>
       </c>
-      <c r="H2" s="19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="15" customFormat="1" spans="1:8">
-      <c r="A3" s="19">
+      <c r="H2" s="18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="13" customFormat="1" spans="1:8">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>340</v>
       </c>
       <c r="C3" t="s">
@@ -5863,15 +5863,15 @@
       <c r="D3" t="s">
         <v>338</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="19" t="b">
+      <c r="H3" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -5883,15 +5883,15 @@
       <c r="D4" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="H4" s="19" t="b">
+      <c r="H4" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -5903,15 +5903,15 @@
       <c r="D5" t="s">
         <v>343</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="H5" s="19" t="b">
+      <c r="H5" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -5926,12 +5926,12 @@
       <c r="E6" t="s">
         <v>347</v>
       </c>
-      <c r="H6" s="19" t="b">
+      <c r="H6" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -5946,12 +5946,12 @@
       <c r="E7" t="s">
         <v>347</v>
       </c>
-      <c r="H7" s="19" t="b">
+      <c r="H7" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -5966,12 +5966,12 @@
       <c r="E8" t="s">
         <v>352</v>
       </c>
-      <c r="H8" s="19" t="b">
+      <c r="H8" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -5986,12 +5986,12 @@
       <c r="E9" t="s">
         <v>352</v>
       </c>
-      <c r="H9" s="19" t="b">
+      <c r="H9" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -6006,12 +6006,12 @@
       <c r="E10" t="s">
         <v>347</v>
       </c>
-      <c r="H10" s="19" t="b">
+      <c r="H10" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -6026,12 +6026,12 @@
       <c r="E11" t="s">
         <v>347</v>
       </c>
-      <c r="H11" s="19" t="b">
+      <c r="H11" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -6043,21 +6043,21 @@
       <c r="D12" t="s">
         <v>358</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="21" t="s">
         <v>359</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="24" t="s">
         <v>361</v>
       </c>
-      <c r="H12" s="19" t="b">
+      <c r="H12" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -6069,17 +6069,17 @@
       <c r="D13" t="s">
         <v>343</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="22" t="s">
         <v>363</v>
       </c>
       <c r="F13" s="6"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="19" t="b">
+      <c r="G13" s="24"/>
+      <c r="H13" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -6091,17 +6091,17 @@
       <c r="D14" t="s">
         <v>343</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="22" t="s">
         <v>363</v>
       </c>
       <c r="F14" s="6"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="19" t="b">
+      <c r="G14" s="24"/>
+      <c r="H14" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -6113,17 +6113,17 @@
       <c r="D15" t="s">
         <v>343</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="22" t="s">
         <v>363</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="19" t="b">
+      <c r="G15" s="24"/>
+      <c r="H15" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="19">
+      <c r="A16" s="18">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -6135,17 +6135,17 @@
       <c r="D16" t="s">
         <v>343</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="22" t="s">
         <v>363</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="19" t="b">
+      <c r="G16" s="24"/>
+      <c r="H16" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="19">
+      <c r="A17" s="18">
         <v>101</v>
       </c>
       <c r="B17" t="s">
@@ -6157,15 +6157,15 @@
       <c r="D17" t="s">
         <v>369</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="H17" s="19" t="b">
+      <c r="H17" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="19">
+      <c r="A18" s="18">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -6177,21 +6177,21 @@
       <c r="D18" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="22" t="s">
         <v>374</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G18" s="26" t="s">
+      <c r="G18" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="H18" s="19" t="b">
+      <c r="H18" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="19">
+      <c r="A19" s="18">
         <v>103</v>
       </c>
       <c r="B19" t="s">
@@ -6203,21 +6203,21 @@
       <c r="D19" t="s">
         <v>358</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="21" t="s">
         <v>359</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="G19" s="24" t="s">
         <v>361</v>
       </c>
-      <c r="H19" s="19" t="b">
+      <c r="H19" s="18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="19">
+      <c r="A20" s="18">
         <v>201</v>
       </c>
       <c r="B20" t="s">
@@ -6229,15 +6229,15 @@
       <c r="D20" t="s">
         <v>338</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="22" t="s">
         <v>363</v>
       </c>
-      <c r="H20" s="19" t="b">
+      <c r="H20" s="18" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="19">
+      <c r="A21" s="18">
         <v>202</v>
       </c>
       <c r="B21" t="s">
@@ -6249,16 +6249,16 @@
       <c r="D21" t="s">
         <v>381</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="21" t="s">
         <v>382</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G21" s="23" t="s">
+      <c r="G21" s="22" t="s">
         <v>384</v>
       </c>
-      <c r="H21" s="19" t="b">
+      <c r="H21" s="18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6295,19 +6295,19 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="15"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="19">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>385</v>
       </c>
     </row>
@@ -6337,67 +6337,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>389</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
-      <c r="A2" s="19">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="21" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="19">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="22" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="19">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="19" t="s">
         <v>392</v>
       </c>
       <c r="E4" t="s">
@@ -6405,225 +6405,225 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:5">
-      <c r="A5" s="19">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="22" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:5">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="23" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:5">
-      <c r="A7" s="19">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="22" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:5">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="22" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:5">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="22" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:5">
-      <c r="A10" s="19">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="22" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
-      <c r="A11" s="19">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>410</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="21" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:5">
-      <c r="A12" s="19">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="22" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:5">
-      <c r="A13" s="19">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>416</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="21" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:5">
-      <c r="A14" s="19">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="22" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:5">
-      <c r="A15" s="19">
+      <c r="A15" s="18">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>422</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="21" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="19"/>
+      <c r="A16" s="18"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="19"/>
+      <c r="A17" s="18"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="19"/>
+      <c r="A18" s="18"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="19"/>
+      <c r="A19" s="18"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="19"/>
+      <c r="A20" s="18"/>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="19"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="3"/>
-      <c r="E21" s="23"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="19"/>
+      <c r="A22" s="18"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="19"/>
+      <c r="A23" s="18"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="19"/>
-      <c r="E24" s="23"/>
+      <c r="A24" s="18"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="19"/>
+      <c r="A25" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6649,7 +6649,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C92"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28.875" customWidth="1"/>
@@ -6837,10 +6837,10 @@
       <c r="A17" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>474</v>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       <c r="B20" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="9" t="s">
         <v>483</v>
       </c>
     </row>
@@ -7021,10 +7021,10 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>523</v>
       </c>
       <c r="C34" t="s">
@@ -7032,10 +7032,10 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="10" t="s">
         <v>525</v>
       </c>
       <c r="C35" t="s">
@@ -7043,10 +7043,10 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>226</v>
       </c>
       <c r="C36" t="s">
@@ -7054,10 +7054,10 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="11" t="s">
         <v>197</v>
       </c>
       <c r="C37" t="s">
@@ -7065,10 +7065,10 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>530</v>
       </c>
       <c r="C38" t="s">
@@ -7076,10 +7076,10 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>532</v>
       </c>
       <c r="C39" t="s">
@@ -7087,10 +7087,10 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="13" t="s">
         <v>198</v>
       </c>
       <c r="C40" t="s">
@@ -7098,10 +7098,10 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="14" t="s">
         <v>199</v>
       </c>
       <c r="C41" t="s">
@@ -7109,10 +7109,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="13" t="s">
         <v>200</v>
       </c>
       <c r="C42" t="s">
@@ -7120,10 +7120,10 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="B43" s="13" t="s">
         <v>201</v>
       </c>
       <c r="C43" t="s">
@@ -7131,10 +7131,10 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="13" t="s">
         <v>202</v>
       </c>
       <c r="C44" t="s">
@@ -7142,10 +7142,10 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="13" t="s">
         <v>203</v>
       </c>
       <c r="C45" t="s">
@@ -7153,10 +7153,10 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="13" t="s">
         <v>204</v>
       </c>
       <c r="C46" t="s">
@@ -7164,10 +7164,10 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="B47" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C47" t="s">
@@ -7175,10 +7175,10 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="13" t="s">
         <v>206</v>
       </c>
       <c r="C48" t="s">
@@ -7186,10 +7186,10 @@
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="B49" s="13" t="s">
         <v>207</v>
       </c>
       <c r="C49" t="s">
@@ -7197,10 +7197,10 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="13" t="s">
         <v>208</v>
       </c>
       <c r="C50" t="s">
@@ -7208,10 +7208,10 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="15" t="s">
+      <c r="A51" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B51" s="15" t="s">
+      <c r="B51" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C51" t="s">
@@ -7219,10 +7219,10 @@
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="15" t="s">
+      <c r="B52" s="13" t="s">
         <v>209</v>
       </c>
       <c r="C52" t="s">
@@ -7230,10 +7230,10 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="15" t="s">
+      <c r="A53" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="B53" s="15" t="s">
+      <c r="B53" s="13" t="s">
         <v>210</v>
       </c>
       <c r="C53" t="s">
@@ -7241,10 +7241,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="15" t="s">
+      <c r="A54" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="13" t="s">
         <v>211</v>
       </c>
       <c r="C54" t="s">
@@ -7252,10 +7252,10 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="11" t="s">
         <v>212</v>
       </c>
       <c r="C55" t="s">
@@ -7263,10 +7263,10 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="11" t="s">
         <v>213</v>
       </c>
       <c r="C56" t="s">
@@ -7274,10 +7274,10 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="11" t="s">
         <v>214</v>
       </c>
       <c r="C57" t="s">
@@ -7285,10 +7285,10 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="11" t="s">
         <v>215</v>
       </c>
       <c r="C58" t="s">
@@ -7296,10 +7296,10 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="11" t="s">
         <v>216</v>
       </c>
       <c r="C59" t="s">
@@ -7307,10 +7307,10 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="11" t="s">
         <v>217</v>
       </c>
       <c r="C60" t="s">
@@ -7318,10 +7318,10 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="11" t="s">
         <v>218</v>
       </c>
       <c r="C61" t="s">
@@ -7329,10 +7329,10 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="11" t="s">
         <v>219</v>
       </c>
       <c r="C62" t="s">
@@ -7340,10 +7340,10 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="11" t="s">
         <v>165</v>
       </c>
       <c r="C63" t="s">
@@ -7351,10 +7351,10 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="11" t="s">
         <v>170</v>
       </c>
       <c r="C64" t="s">
@@ -7362,10 +7362,10 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="11" t="s">
         <v>174</v>
       </c>
       <c r="C65" t="s">
@@ -7373,10 +7373,10 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="11" t="s">
         <v>220</v>
       </c>
       <c r="C66" t="s">
@@ -7384,10 +7384,10 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="15" t="s">
         <v>262</v>
       </c>
       <c r="C67" t="s">
@@ -7395,10 +7395,10 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="15" t="s">
         <v>263</v>
       </c>
       <c r="C68" t="s">
@@ -7406,10 +7406,10 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="15" t="s">
         <v>564</v>
       </c>
       <c r="C69" t="s">
@@ -7417,10 +7417,10 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="18" t="s">
+      <c r="A70" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="16" t="s">
         <v>265</v>
       </c>
       <c r="C70" t="s">
@@ -7428,10 +7428,10 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="B71" s="17" t="s">
+      <c r="B71" s="15" t="s">
         <v>266</v>
       </c>
       <c r="C71" t="s">
@@ -7439,10 +7439,10 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C72" t="s">
@@ -7450,10 +7450,10 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="15" t="s">
+      <c r="A73" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="B73" s="15" t="s">
+      <c r="B73" s="13" t="s">
         <v>569</v>
       </c>
       <c r="C73" t="s">
@@ -7461,10 +7461,10 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B74" s="15" t="s">
+      <c r="B74" s="13" t="s">
         <v>571</v>
       </c>
       <c r="C74" t="s">
@@ -7472,10 +7472,10 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B75" s="15" t="s">
+      <c r="B75" s="13" t="s">
         <v>573</v>
       </c>
       <c r="C75" t="s">
@@ -7483,10 +7483,10 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C76" t="s">
@@ -7494,10 +7494,10 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C77" t="s">
@@ -7667,6 +7667,11 @@
       </c>
       <c r="C92" t="s">
         <v>621</v>
+      </c>
+    </row>
+    <row r="93" ht="14.25" spans="1:3">
+      <c r="A93" s="17" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -7681,54 +7686,54 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9" style="15"/>
+    <col min="2" max="2" width="9" style="13"/>
     <col min="3" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="15" customFormat="1" spans="1:7">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
+    <row r="1" s="13" customFormat="1" spans="1:7">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="13" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="2" s="15" customFormat="1" spans="1:7">
-      <c r="A2" s="30">
+    <row r="2" s="13" customFormat="1" spans="1:7">
+      <c r="A2" s="29">
         <v>4</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="29">
         <v>20</v>
       </c>
-      <c r="D2" s="30">
-        <v>1</v>
-      </c>
-      <c r="E2" s="19">
-        <v>1</v>
-      </c>
-      <c r="F2" s="19">
-        <v>0</v>
-      </c>
-      <c r="G2" s="19">
+      <c r="D2" s="29">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18">
+        <v>1</v>
+      </c>
+      <c r="F2" s="18">
+        <v>0</v>
+      </c>
+      <c r="G2" s="18">
         <v>200</v>
       </c>
     </row>
@@ -7736,7 +7741,7 @@
       <c r="A3">
         <v>201</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>198</v>
       </c>
       <c r="C3">
@@ -7751,7 +7756,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="18">
         <v>100</v>
       </c>
     </row>
@@ -7759,7 +7764,7 @@
       <c r="A4">
         <v>202</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>199</v>
       </c>
       <c r="C4">
@@ -7774,7 +7779,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="18">
         <v>100</v>
       </c>
     </row>
@@ -7782,7 +7787,7 @@
       <c r="A5">
         <v>203</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>200</v>
       </c>
       <c r="C5">
@@ -7797,7 +7802,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="18">
         <v>110</v>
       </c>
     </row>
@@ -7805,7 +7810,7 @@
       <c r="A6">
         <v>204</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>201</v>
       </c>
       <c r="C6">
@@ -7820,7 +7825,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>200</v>
       </c>
     </row>
@@ -7828,7 +7833,7 @@
       <c r="A7">
         <v>205</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>202</v>
       </c>
       <c r="C7">
@@ -7843,7 +7848,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="18">
         <v>90</v>
       </c>
     </row>
@@ -7851,7 +7856,7 @@
       <c r="A8">
         <v>206</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>203</v>
       </c>
       <c r="C8">
@@ -7866,7 +7871,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="18">
         <v>200</v>
       </c>
     </row>
@@ -7874,7 +7879,7 @@
       <c r="A9">
         <v>207</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>204</v>
       </c>
       <c r="C9">
@@ -7889,7 +7894,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="18">
         <v>100</v>
       </c>
     </row>
@@ -7897,7 +7902,7 @@
       <c r="A10">
         <v>208</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C10">
@@ -7912,7 +7917,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="18">
         <v>90</v>
       </c>
     </row>
@@ -7920,7 +7925,7 @@
       <c r="A11">
         <v>209</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>206</v>
       </c>
       <c r="C11">
@@ -7935,7 +7940,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="18">
         <v>0</v>
       </c>
     </row>
@@ -7943,7 +7948,7 @@
       <c r="A12">
         <v>210</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>207</v>
       </c>
       <c r="C12">
@@ -7958,7 +7963,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <v>180</v>
       </c>
     </row>
@@ -7966,7 +7971,7 @@
       <c r="A13">
         <v>211</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>208</v>
       </c>
       <c r="C13">
@@ -7981,7 +7986,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <v>0</v>
       </c>
     </row>
@@ -7989,7 +7994,7 @@
       <c r="A14">
         <v>212</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C14">
@@ -8004,7 +8009,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <v>100</v>
       </c>
     </row>
@@ -8012,7 +8017,7 @@
       <c r="A15">
         <v>213</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>209</v>
       </c>
       <c r="C15">
@@ -8027,7 +8032,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>180</v>
       </c>
     </row>
@@ -8035,7 +8040,7 @@
       <c r="A16">
         <v>214</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>210</v>
       </c>
       <c r="C16">
@@ -8050,7 +8055,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="18">
         <v>110</v>
       </c>
     </row>
@@ -8058,7 +8063,7 @@
       <c r="A17">
         <v>215</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>211</v>
       </c>
       <c r="C17">
@@ -8073,288 +8078,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="32" customFormat="1" spans="1:7">
-      <c r="A18" s="32">
+    <row r="18" s="31" customFormat="1" spans="1:7">
+      <c r="A18" s="31">
         <v>301</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="31">
         <v>50</v>
       </c>
-      <c r="D18" s="32">
-        <v>0</v>
-      </c>
-      <c r="E18" s="32">
+      <c r="D18" s="31">
+        <v>0</v>
+      </c>
+      <c r="E18" s="31">
         <v>400</v>
       </c>
-      <c r="F18" s="32">
-        <v>0</v>
-      </c>
-      <c r="G18" s="34">
+      <c r="F18" s="31">
+        <v>0</v>
+      </c>
+      <c r="G18" s="33">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="32" customFormat="1" spans="1:7">
-      <c r="A19" s="32">
+    <row r="19" s="31" customFormat="1" spans="1:7">
+      <c r="A19" s="31">
         <v>302</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="31">
         <v>25</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="31">
         <v>9</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="31">
         <v>100</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>303</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="33">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="32" customFormat="1" spans="1:7">
-      <c r="A20" s="32">
+    <row r="20" s="31" customFormat="1" spans="1:7">
+      <c r="A20" s="31">
         <v>303</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="32">
+      <c r="C20" s="31">
         <v>20</v>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="31">
         <v>3</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="31">
         <v>50</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="31">
         <v>301</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="33">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="32" customFormat="1" spans="1:7">
-      <c r="A21" s="32">
+    <row r="21" s="31" customFormat="1" spans="1:7">
+      <c r="A21" s="31">
         <v>304</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="31">
         <v>30</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="31">
         <v>11</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <v>300</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="31">
         <v>301</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="33">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="32" customFormat="1" spans="1:7">
-      <c r="A22" s="32">
+    <row r="22" s="31" customFormat="1" spans="1:7">
+      <c r="A22" s="31">
         <v>305</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="31">
         <v>25</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="31">
         <v>8</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="31">
         <v>100</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="31">
         <v>303</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="33">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="32" customFormat="1" spans="1:7">
-      <c r="A23" s="32">
+    <row r="23" s="31" customFormat="1" spans="1:7">
+      <c r="A23" s="31">
         <v>306</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="32">
+      <c r="C23" s="31">
         <v>35</v>
       </c>
-      <c r="D23" s="32">
-        <v>0</v>
-      </c>
-      <c r="E23" s="32">
+      <c r="D23" s="31">
+        <v>0</v>
+      </c>
+      <c r="E23" s="31">
         <v>200</v>
       </c>
-      <c r="F23" s="32">
-        <v>0</v>
-      </c>
-      <c r="G23" s="34">
+      <c r="F23" s="31">
+        <v>0</v>
+      </c>
+      <c r="G23" s="33">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="32" customFormat="1" spans="1:7">
-      <c r="A24" s="32">
+    <row r="24" s="31" customFormat="1" spans="1:7">
+      <c r="A24" s="31">
         <v>307</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="31">
         <v>35</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="31">
         <v>12</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="31">
         <v>150</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="31">
         <v>302</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="33">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="32" customFormat="1" spans="1:7">
-      <c r="A25" s="32">
+    <row r="25" s="31" customFormat="1" spans="1:7">
+      <c r="A25" s="31">
         <v>308</v>
       </c>
-      <c r="B25" s="33" t="s">
+      <c r="B25" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="31">
         <v>35</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="31">
         <v>12</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="31">
         <v>150</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="31">
         <v>302</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="33">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="32" customFormat="1" spans="1:7">
-      <c r="A26" s="32">
+    <row r="26" s="31" customFormat="1" spans="1:7">
+      <c r="A26" s="31">
         <v>309</v>
       </c>
-      <c r="B26" s="33" t="s">
+      <c r="B26" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>20</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="31">
         <v>10</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="31">
         <v>80</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="31">
         <v>306</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="33">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="32" customFormat="1" spans="1:7">
-      <c r="A27" s="32">
+    <row r="27" s="31" customFormat="1" spans="1:7">
+      <c r="A27" s="31">
         <v>310</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B27" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="31">
         <v>30</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="31">
         <v>10</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="31">
         <v>120</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="31">
         <v>309</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="33">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="32" customFormat="1" spans="1:7">
-      <c r="A28" s="32">
+    <row r="28" s="31" customFormat="1" spans="1:7">
+      <c r="A28" s="31">
         <v>311</v>
       </c>
-      <c r="B28" s="33" t="s">
+      <c r="B28" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="31">
         <v>30</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="31">
         <v>10</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="31">
         <v>120</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="31">
         <v>309</v>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="33">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="32" customFormat="1" spans="1:7">
-      <c r="A29" s="32">
+    <row r="29" s="31" customFormat="1" spans="1:7">
+      <c r="A29" s="31">
         <v>312</v>
       </c>
-      <c r="B29" s="33" t="s">
+      <c r="B29" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="31">
         <v>15</v>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="31">
         <v>2</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="31">
         <v>15</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="31">
         <v>306</v>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="33">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="32" customFormat="1" spans="1:7">
-      <c r="B30" s="33"/>
+    <row r="30" s="31" customFormat="1" spans="1:7">
+      <c r="B30" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8383,7 +8388,7 @@
       <c r="C1" t="s">
         <v>221</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>222</v>
       </c>
       <c r="E1" t="s">
@@ -8397,10 +8402,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="30">
+      <c r="A2" s="29">
         <v>3</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="29" t="s">
         <v>226</v>
       </c>
       <c r="C2">
@@ -8417,10 +8422,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="30">
+      <c r="A3" s="29">
         <v>4</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="29" t="s">
         <v>197</v>
       </c>
       <c r="C3">
@@ -8606,10 +8611,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="30">
+      <c r="A12" s="29">
         <v>309</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="29" t="s">
         <v>165</v>
       </c>
       <c r="C12">
@@ -8626,10 +8631,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="30">
+      <c r="A13" s="29">
         <v>310</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="29" t="s">
         <v>170</v>
       </c>
       <c r="C13">
@@ -8646,10 +8651,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="30">
+      <c r="A14" s="29">
         <v>311</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="29" t="s">
         <v>174</v>
       </c>
       <c r="C14">
@@ -8669,10 +8674,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="30">
+      <c r="A15" s="29">
         <v>312</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="29" t="s">
         <v>220</v>
       </c>
       <c r="C15">
@@ -8689,8 +8694,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8705,35 +8710,35 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="9" style="15"/>
+    <col min="2" max="2" width="9" style="13"/>
     <col min="3" max="3" width="30.75" customWidth="1"/>
     <col min="4" max="6" width="44.875" customWidth="1"/>
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" spans="1:8">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:8">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>233</v>
       </c>
     </row>
@@ -8741,7 +8746,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>198</v>
       </c>
       <c r="C2" t="s">
@@ -8763,29 +8768,29 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3" s="29" customFormat="1" spans="1:8">
-      <c r="A3" s="29">
+    <row r="3" s="28" customFormat="1" spans="1:8">
+      <c r="A3" s="28">
         <v>202</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="E3" s="29">
-        <v>0</v>
-      </c>
-      <c r="F3" s="29">
+      <c r="E3" s="28">
+        <v>0</v>
+      </c>
+      <c r="F3" s="28">
         <v>0.8</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="28" t="s">
         <v>238</v>
       </c>
     </row>
@@ -8793,7 +8798,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>200</v>
       </c>
       <c r="C4" t="s">
@@ -8819,7 +8824,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>201</v>
       </c>
       <c r="C5" t="s">
@@ -8845,7 +8850,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>202</v>
       </c>
       <c r="C6" t="s">
@@ -8871,7 +8876,7 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>203</v>
       </c>
       <c r="C7" t="s">
@@ -8897,7 +8902,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>204</v>
       </c>
       <c r="C8" t="s">
@@ -8923,7 +8928,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C9" t="s">
@@ -8949,7 +8954,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>206</v>
       </c>
       <c r="C10" t="s">
@@ -8975,7 +8980,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>207</v>
       </c>
       <c r="C11" t="s">
@@ -9001,7 +9006,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>208</v>
       </c>
       <c r="E12">
@@ -9015,7 +9020,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C13" t="s">
@@ -9041,7 +9046,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>209</v>
       </c>
       <c r="C14" t="s">
@@ -9067,7 +9072,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>210</v>
       </c>
       <c r="C15" t="s">
@@ -9093,7 +9098,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>211</v>
       </c>
       <c r="C16" t="s">
@@ -9119,7 +9124,7 @@
       <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C17" t="s">
@@ -9139,7 +9144,7 @@
       <c r="A18">
         <v>402</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>263</v>
       </c>
       <c r="C18" t="s">
@@ -9159,7 +9164,7 @@
       <c r="A19">
         <v>403</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C19" t="s">
@@ -9175,37 +9180,37 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="29" customFormat="1" spans="1:8">
-      <c r="A20" s="31">
+    <row r="20" s="28" customFormat="1" spans="1:8">
+      <c r="A20" s="30">
         <v>404</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="E20" s="29">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29">
+      <c r="E20" s="28">
+        <v>0</v>
+      </c>
+      <c r="F20" s="28">
         <v>0.8</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="28" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="27">
+      <c r="A21" s="26">
         <v>405</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>266</v>
       </c>
       <c r="C21" t="s">
@@ -9228,10 +9233,10 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="27">
+      <c r="A22" s="26">
         <v>406</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>267</v>
       </c>
       <c r="C22" t="s">
@@ -9254,10 +9259,10 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="28">
+      <c r="A23" s="27">
         <v>407</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C23" t="s">
@@ -9280,10 +9285,10 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="28">
+      <c r="A24" s="27">
         <v>408</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C24" t="s">
@@ -9306,10 +9311,10 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="28">
+      <c r="A25" s="27">
         <v>409</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="13" t="s">
         <v>270</v>
       </c>
       <c r="C25" t="s">
@@ -9332,10 +9337,10 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="28">
+      <c r="A26" s="27">
         <v>410</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C26" t="s">
@@ -9358,10 +9363,10 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="28">
+      <c r="A27" s="27">
         <v>411</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C27" t="s">
@@ -9397,7 +9402,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="15" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="13" customWidth="1"/>
     <col min="3" max="4" width="9.875" customWidth="1"/>
     <col min="5" max="6" width="8.125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -9424,68 +9429,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="29" customFormat="1" spans="1:21">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" s="28" customFormat="1" spans="1:21">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="28" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="G1" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="29" t="s">
+      <c r="H1" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="I1" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="K1" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="28" t="s">
         <v>285</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="Q1" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="R1" s="29" t="s">
+      <c r="R1" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="28" t="s">
         <v>290</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="U1" s="28" t="s">
         <v>291</v>
       </c>
     </row>
@@ -9493,7 +9498,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>198</v>
       </c>
       <c r="C2">
@@ -9549,7 +9554,7 @@
       <c r="A3">
         <v>202</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>199</v>
       </c>
       <c r="C3">
@@ -9611,7 +9616,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>200</v>
       </c>
       <c r="C4">
@@ -9667,7 +9672,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>201</v>
       </c>
       <c r="C5">
@@ -9729,7 +9734,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>202</v>
       </c>
       <c r="C6">
@@ -9785,7 +9790,7 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>203</v>
       </c>
       <c r="C7">
@@ -9847,7 +9852,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>204</v>
       </c>
       <c r="C8">
@@ -9909,7 +9914,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>205</v>
       </c>
       <c r="C9">
@@ -9965,7 +9970,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>206</v>
       </c>
       <c r="C10">
@@ -10021,7 +10026,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>207</v>
       </c>
       <c r="C11">
@@ -10080,7 +10085,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>208</v>
       </c>
       <c r="C12">
@@ -10133,7 +10138,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="13" t="s">
         <v>100</v>
       </c>
       <c r="C13">
@@ -10183,7 +10188,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>209</v>
       </c>
       <c r="C14">
@@ -10242,7 +10247,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>210</v>
       </c>
       <c r="C15">
@@ -10298,7 +10303,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="13" t="s">
         <v>211</v>
       </c>
       <c r="C16">
@@ -10357,10 +10362,10 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="30">
+      <c r="A17" s="29">
         <v>301</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>212</v>
       </c>
       <c r="C17">
@@ -10416,10 +10421,10 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="30">
+      <c r="A18" s="29">
         <v>302</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>213</v>
       </c>
       <c r="C18">
@@ -10475,10 +10480,10 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="30">
+      <c r="A19" s="29">
         <v>303</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>214</v>
       </c>
       <c r="C19">
@@ -10534,10 +10539,10 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="30">
+      <c r="A20" s="29">
         <v>304</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="11" t="s">
         <v>215</v>
       </c>
       <c r="C20">
@@ -10596,7 +10601,7 @@
       <c r="A21">
         <v>305</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="13" t="s">
         <v>216</v>
       </c>
       <c r="C21">
@@ -10655,10 +10660,10 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="30">
+      <c r="A22" s="29">
         <v>306</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="11" t="s">
         <v>217</v>
       </c>
       <c r="C22">
@@ -10714,10 +10719,10 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="30">
+      <c r="A23" s="29">
         <v>307</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="11" t="s">
         <v>218</v>
       </c>
       <c r="C23">
@@ -10773,10 +10778,10 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="30">
+      <c r="A24" s="29">
         <v>308</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="11" t="s">
         <v>219</v>
       </c>
       <c r="C24">
@@ -10832,10 +10837,10 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="30">
+      <c r="A25" s="29">
         <v>309</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="11" t="s">
         <v>165</v>
       </c>
       <c r="C25">
@@ -10891,10 +10896,10 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="30">
+      <c r="A26" s="29">
         <v>310</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="11" t="s">
         <v>170</v>
       </c>
       <c r="C26">
@@ -10950,10 +10955,10 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="30">
+      <c r="A27" s="29">
         <v>311</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="11" t="s">
         <v>174</v>
       </c>
       <c r="C27">
@@ -11009,10 +11014,10 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="30">
+      <c r="A28" s="29">
         <v>312</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="11" t="s">
         <v>220</v>
       </c>
       <c r="C28">
@@ -11071,7 +11076,7 @@
       <c r="A29">
         <v>401</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C29">
@@ -11133,7 +11138,7 @@
       <c r="A30">
         <v>402</v>
       </c>
-      <c r="B30" s="15" t="s">
+      <c r="B30" s="13" t="s">
         <v>263</v>
       </c>
       <c r="C30">
@@ -11189,7 +11194,7 @@
       <c r="A31">
         <v>403</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="13" t="s">
         <v>264</v>
       </c>
       <c r="C31">
@@ -11242,10 +11247,10 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="27">
+      <c r="A32" s="26">
         <v>404</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="13" t="s">
         <v>265</v>
       </c>
       <c r="C32">
@@ -11304,10 +11309,10 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="27">
+      <c r="A33" s="26">
         <v>405</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="13" t="s">
         <v>266</v>
       </c>
       <c r="C33">
@@ -11360,10 +11365,10 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="27">
+      <c r="A34" s="26">
         <v>406</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="13" t="s">
         <v>267</v>
       </c>
       <c r="C34">
@@ -11416,10 +11421,10 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="28">
+      <c r="A35" s="27">
         <v>407</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="13" t="s">
         <v>268</v>
       </c>
       <c r="C35">
@@ -11472,10 +11477,10 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="28">
+      <c r="A36" s="27">
         <v>408</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="13" t="s">
         <v>269</v>
       </c>
       <c r="C36">
@@ -11531,10 +11536,10 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="28">
+      <c r="A37" s="27">
         <v>409</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="13" t="s">
         <v>270</v>
       </c>
       <c r="C37">
@@ -11590,10 +11595,10 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="28">
+      <c r="A38" s="27">
         <v>410</v>
       </c>
-      <c r="B38" s="15" t="s">
+      <c r="B38" s="13" t="s">
         <v>271</v>
       </c>
       <c r="C38">
@@ -11640,10 +11645,10 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="28">
+      <c r="A39" s="27">
         <v>411</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="13" t="s">
         <v>272</v>
       </c>
       <c r="C39">
@@ -11802,7 +11807,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="27">
+      <c r="A9" s="26">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -11813,7 +11818,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="27">
+      <c r="A10" s="26">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -11824,7 +11829,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="27">
+      <c r="A11" s="26">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -11835,7 +11840,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="28">
+      <c r="A12" s="27">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -11846,7 +11851,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="28">
+      <c r="A13" s="27">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -11857,7 +11862,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -11868,7 +11873,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -11879,7 +11884,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>411</v>
       </c>
       <c r="B16" t="s">
@@ -11904,29 +11909,29 @@
     <col min="7" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" spans="1:8">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:8">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="14" t="s">
         <v>193</v>
       </c>
     </row>
@@ -12154,16 +12159,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>193</v>
       </c>
     </row>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="630">
   <si>
     <t>类型</t>
   </si>
@@ -584,7 +584,7 @@
     <t>Key近战虫怪</t>
   </si>
   <si>
-    <t>Key工怪</t>
+    <t>Key工虫怪</t>
   </si>
   <si>
     <t>音效/zdrWht00</t>
@@ -1586,7 +1586,7 @@
     <t>，炮台群对步兵有压倒性的优势。您可以试试攻城利器：&lt;color=#a0ff50&gt;坦克&lt;/color&gt;。</t>
   </si>
   <si>
-    <t>Gun emplacements have an overwhelming advantage against infantry. You can try using a siege weapon: the &lt;color=#a0ff50&gt;Tank&lt;/color&gt;.</t>
+    <t>,Gun emplacements have an overwhelming advantage against infantry. You can try using a siege weapon: the &lt;color=#a0ff50&gt;Tank&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key坦克可以在炮台的射程外攻击</t>
@@ -1622,7 +1622,7 @@
     <t>，坦克拥有射程优势，可以在炮台的射程外攻击。但是坦克爆炸溅射会伤害己方单位，并且前摇很长，会遭到小兵克制。现在请看效果。</t>
   </si>
   <si>
-    <t>Tanks have a range advantage and can attack from beyond the gun emplacements' firing range. However, tank explosion splash damage will harm friendly units, and their long attack wind-up makes them vulnerable to enemy grunts. Now watch the effect.</t>
+    <t>,Tanks have a range advantage and can attack from beyond the gun emplacements' firing range. However, tank explosion splash damage will harm friendly units, and their long attack wind-up makes them vulnerable to enemy grunts. Now watch the effect.</t>
   </si>
   <si>
     <t>Key敌方近战虫无法防空</t>
@@ -1706,7 +1706,7 @@
     <t>请单击选中飞机，然后点击下方的&lt;color=#a0ff50&gt;强行走&lt;/color&gt;按钮，让飞机停止攻击并移动到炮台射程外。</t>
   </si>
   <si>
-    <t>Click to select the aircraft, then click the &lt;color=#a0ff50&gt;Force Move&lt;/color&gt; button below to make the aircraft stop attacking and move outside the gun emplacements' firing range.</t>
+    <t>Click to select the aircraft, then click the &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; button below to make the aircraft stop attacking and move outside the gun emplacements' firing range.</t>
   </si>
   <si>
     <t>Key强行走的过程中不会攻击敌人</t>
@@ -1981,7 +1981,7 @@
     <t>Light Spiker</t>
   </si>
   <si>
-    <t>Hive Bug</t>
+    <t>Population Drone</t>
   </si>
   <si>
     <t>Flying Bug</t>
@@ -2033,9 +2033,6 @@
   </si>
   <si>
     <t>Melee Bug Mutant</t>
-  </si>
-  <si>
-    <t>Key工虫怪</t>
   </si>
   <si>
     <t>工虫怪</t>
@@ -2246,7 +2243,103 @@
     <t>Hive Bug: Hulu</t>
   </si>
   <si>
-    <t>Key内有{0}人</t>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>内有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{0}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人</t>
+    </r>
+  </si>
+  <si>
+    <t>{0} units inside</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>资源</t>
+    </r>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
+    <t>Resources</t>
+  </si>
+  <si>
+    <t>Key准备开火</t>
+  </si>
+  <si>
+    <t>准备开火</t>
+  </si>
+  <si>
+    <t>Ready to Fire</t>
   </si>
 </sst>
 </file>
@@ -2979,7 +3072,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3032,6 +3125,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -3474,20 +3573,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="34" customFormat="1" spans="1:18">
-      <c r="A2" s="34">
+    <row r="2" s="36" customFormat="1" spans="1:18">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="34">
-        <v>0</v>
-      </c>
-      <c r="G2" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="34">
+      <c r="C2" s="36">
+        <v>0</v>
+      </c>
+      <c r="G2" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="36">
         <v>1</v>
       </c>
       <c r="J2">
@@ -3496,33 +3595,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="34">
-        <v>1</v>
-      </c>
-      <c r="N2" s="34">
-        <v>0</v>
-      </c>
-      <c r="O2" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="34" customFormat="1" spans="1:18">
-      <c r="A3" s="34">
+      <c r="M2" s="36">
+        <v>1</v>
+      </c>
+      <c r="N2" s="36">
+        <v>0</v>
+      </c>
+      <c r="O2" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="36" customFormat="1" spans="1:18">
+      <c r="A3" s="36">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="34">
-        <v>0</v>
-      </c>
-      <c r="G3" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="34">
+      <c r="C3" s="36">
+        <v>0</v>
+      </c>
+      <c r="G3" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="36">
         <v>1</v>
       </c>
       <c r="J3">
@@ -3531,36 +3630,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="34">
-        <v>1</v>
-      </c>
-      <c r="N3" s="34">
-        <v>0</v>
-      </c>
-      <c r="O3" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="29" customFormat="1" spans="1:18">
-      <c r="A4" s="29">
+      <c r="M3" s="36">
+        <v>1</v>
+      </c>
+      <c r="N3" s="36">
+        <v>0</v>
+      </c>
+      <c r="O3" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="31" customFormat="1" spans="1:18">
+      <c r="A4" s="31">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="31">
         <v>2</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="34">
+      <c r="G4" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="36">
         <v>1</v>
       </c>
       <c r="J4">
@@ -3569,36 +3668,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="34">
-        <v>1</v>
-      </c>
-      <c r="N4" s="34">
-        <v>0</v>
-      </c>
-      <c r="O4" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="29" customFormat="1" spans="1:18">
-      <c r="A5" s="29">
+      <c r="M4" s="36">
+        <v>1</v>
+      </c>
+      <c r="N4" s="36">
+        <v>0</v>
+      </c>
+      <c r="O4" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="31" customFormat="1" spans="1:18">
+      <c r="A5" s="31">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="29">
-        <v>0</v>
-      </c>
-      <c r="D5" s="29" t="s">
+      <c r="C5" s="31">
+        <v>0</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="34">
+      <c r="G5" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="36">
         <v>1</v>
       </c>
       <c r="J5">
@@ -3607,48 +3706,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="34">
-        <v>1</v>
-      </c>
-      <c r="N5" s="34">
-        <v>0</v>
-      </c>
-      <c r="O5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="29">
-        <v>0</v>
-      </c>
-      <c r="R5" s="29" t="s">
+      <c r="M5" s="36">
+        <v>1</v>
+      </c>
+      <c r="N5" s="36">
+        <v>0</v>
+      </c>
+      <c r="O5" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="31">
+        <v>0</v>
+      </c>
+      <c r="R5" s="31" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="35" customFormat="1" spans="1:18">
-      <c r="A6" s="35">
+    <row r="6" s="37" customFormat="1" spans="1:18">
+      <c r="A6" s="37">
         <v>101</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="35">
-        <v>0</v>
-      </c>
-      <c r="D6" s="35" t="s">
+      <c r="C6" s="37">
+        <v>0</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="34" t="b">
+      <c r="G6" s="36" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="36">
         <v>1</v>
       </c>
       <c r="J6">
@@ -3660,39 +3759,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="34">
-        <v>1</v>
-      </c>
-      <c r="N6" s="34">
-        <v>0</v>
-      </c>
-      <c r="O6" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="35" customFormat="1" spans="1:18">
-      <c r="A7" s="35">
+      <c r="M6" s="36">
+        <v>1</v>
+      </c>
+      <c r="N6" s="36">
+        <v>0</v>
+      </c>
+      <c r="O6" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="37" customFormat="1" spans="1:18">
+      <c r="A7" s="37">
         <v>102</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="35">
-        <v>0</v>
-      </c>
-      <c r="D7" s="35" t="s">
+      <c r="C7" s="37">
+        <v>0</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="34">
+      <c r="G7" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="36">
         <v>1</v>
       </c>
       <c r="J7">
@@ -3701,16 +3800,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="34">
-        <v>1</v>
-      </c>
-      <c r="N7" s="34">
-        <v>0</v>
-      </c>
-      <c r="O7" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="35">
+      <c r="M7" s="36">
+        <v>1</v>
+      </c>
+      <c r="N7" s="36">
+        <v>0</v>
+      </c>
+      <c r="O7" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="37">
         <v>0</v>
       </c>
     </row>
@@ -3733,13 +3832,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="34" t="b">
+      <c r="G8" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="36">
         <v>1</v>
       </c>
       <c r="J8">
@@ -3751,13 +3850,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="34">
-        <v>1</v>
-      </c>
-      <c r="N8" s="34">
-        <v>0</v>
-      </c>
-      <c r="O8" s="34">
+      <c r="M8" s="36">
+        <v>1</v>
+      </c>
+      <c r="N8" s="36">
+        <v>0</v>
+      </c>
+      <c r="O8" s="36">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -3770,59 +3869,59 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="28" customFormat="1" spans="1:18">
-      <c r="A9" s="28">
+    <row r="9" s="30" customFormat="1" spans="1:18">
+      <c r="A9" s="30">
         <v>202</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="28">
-        <v>1</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="C9" s="30">
+        <v>1</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="28" t="s">
+      <c r="G9" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="36">
-        <v>1</v>
-      </c>
-      <c r="J9" s="28">
-        <v>0</v>
-      </c>
-      <c r="K9" s="28">
+      <c r="I9" s="38">
+        <v>1</v>
+      </c>
+      <c r="J9" s="30">
+        <v>0</v>
+      </c>
+      <c r="K9" s="30">
         <v>2</v>
       </c>
-      <c r="L9" s="28" t="s">
+      <c r="L9" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="36">
-        <v>1</v>
-      </c>
-      <c r="N9" s="36">
-        <v>0</v>
-      </c>
-      <c r="O9" s="36">
-        <v>0</v>
-      </c>
-      <c r="P9" s="28" t="s">
+      <c r="M9" s="38">
+        <v>1</v>
+      </c>
+      <c r="N9" s="38">
+        <v>0</v>
+      </c>
+      <c r="O9" s="38">
+        <v>0</v>
+      </c>
+      <c r="P9" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="30">
         <v>3</v>
       </c>
-      <c r="R9" s="28" t="s">
+      <c r="R9" s="30" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3845,13 +3944,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="34" t="b">
+      <c r="G10" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="36">
         <v>1</v>
       </c>
       <c r="J10">
@@ -3863,13 +3962,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="34">
-        <v>1</v>
-      </c>
-      <c r="N10" s="34">
-        <v>0</v>
-      </c>
-      <c r="O10" s="34">
+      <c r="M10" s="36">
+        <v>1</v>
+      </c>
+      <c r="N10" s="36">
+        <v>0</v>
+      </c>
+      <c r="O10" s="36">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -3898,13 +3997,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="34" t="b">
+      <c r="G11" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="36">
         <v>1</v>
       </c>
       <c r="J11">
@@ -3916,13 +4015,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="34">
-        <v>1</v>
-      </c>
-      <c r="N11" s="34">
-        <v>0</v>
-      </c>
-      <c r="O11" s="34">
+      <c r="M11" s="36">
+        <v>1</v>
+      </c>
+      <c r="N11" s="36">
+        <v>0</v>
+      </c>
+      <c r="O11" s="36">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -3954,13 +4053,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34" t="b">
+      <c r="G12" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="36">
         <v>1</v>
       </c>
       <c r="J12">
@@ -3972,13 +4071,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="34">
-        <v>1</v>
-      </c>
-      <c r="N12" s="34">
-        <v>0</v>
-      </c>
-      <c r="O12" s="34">
+      <c r="M12" s="36">
+        <v>1</v>
+      </c>
+      <c r="N12" s="36">
+        <v>0</v>
+      </c>
+      <c r="O12" s="36">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -4010,13 +4109,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="34" t="b">
+      <c r="G13" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="36">
         <v>1</v>
       </c>
       <c r="J13">
@@ -4028,13 +4127,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="34">
-        <v>1</v>
-      </c>
-      <c r="N13" s="34">
-        <v>1</v>
-      </c>
-      <c r="O13" s="34">
+      <c r="M13" s="36">
+        <v>1</v>
+      </c>
+      <c r="N13" s="36">
+        <v>1</v>
+      </c>
+      <c r="O13" s="36">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -4063,16 +4162,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="34" t="b">
+      <c r="G14" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="36">
         <v>1</v>
       </c>
       <c r="J14">
@@ -4084,13 +4183,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="34">
-        <v>1</v>
-      </c>
-      <c r="N14" s="34">
-        <v>0</v>
-      </c>
-      <c r="O14" s="34">
+      <c r="M14" s="36">
+        <v>1</v>
+      </c>
+      <c r="N14" s="36">
+        <v>0</v>
+      </c>
+      <c r="O14" s="36">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -4119,16 +4218,16 @@
       <c r="E15" t="s">
         <v>79</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="G15" s="34" t="b">
+      <c r="G15" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="36">
         <v>1</v>
       </c>
       <c r="J15">
@@ -4140,13 +4239,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="34">
-        <v>1</v>
-      </c>
-      <c r="N15" s="34">
-        <v>0</v>
-      </c>
-      <c r="O15" s="34">
+      <c r="M15" s="36">
+        <v>1</v>
+      </c>
+      <c r="N15" s="36">
+        <v>0</v>
+      </c>
+      <c r="O15" s="36">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -4178,13 +4277,13 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="34" t="b">
+      <c r="G16" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="34">
+      <c r="I16" s="36">
         <v>1</v>
       </c>
       <c r="J16">
@@ -4196,13 +4295,13 @@
       <c r="L16" t="s">
         <v>87</v>
       </c>
-      <c r="M16" s="34">
-        <v>1</v>
-      </c>
-      <c r="N16" s="34">
-        <v>0</v>
-      </c>
-      <c r="O16" s="34">
+      <c r="M16" s="36">
+        <v>1</v>
+      </c>
+      <c r="N16" s="36">
+        <v>0</v>
+      </c>
+      <c r="O16" s="36">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -4234,13 +4333,13 @@
       <c r="F17" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="34" t="b">
+      <c r="G17" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="34">
+      <c r="I17" s="36">
         <v>1</v>
       </c>
       <c r="J17">
@@ -4252,13 +4351,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="34">
-        <v>1</v>
-      </c>
-      <c r="N17" s="34">
-        <v>0</v>
-      </c>
-      <c r="O17" s="34">
+      <c r="M17" s="36">
+        <v>1</v>
+      </c>
+      <c r="N17" s="36">
+        <v>0</v>
+      </c>
+      <c r="O17" s="36">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -4284,10 +4383,10 @@
       <c r="D18" t="s">
         <v>96</v>
       </c>
-      <c r="G18" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="34">
+      <c r="G18" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="36">
         <v>1</v>
       </c>
       <c r="J18">
@@ -4296,13 +4395,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="34">
-        <v>1</v>
-      </c>
-      <c r="N18" s="34">
-        <v>0</v>
-      </c>
-      <c r="O18" s="34">
+      <c r="M18" s="36">
+        <v>1</v>
+      </c>
+      <c r="N18" s="36">
+        <v>0</v>
+      </c>
+      <c r="O18" s="36">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -4328,13 +4427,13 @@
       <c r="F19" t="s">
         <v>100</v>
       </c>
-      <c r="G19" s="34" t="b">
+      <c r="G19" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="36">
         <v>1</v>
       </c>
       <c r="J19">
@@ -4346,13 +4445,13 @@
       <c r="L19" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="34">
-        <v>1</v>
-      </c>
-      <c r="N19" s="34">
-        <v>0</v>
-      </c>
-      <c r="O19" s="34">
+      <c r="M19" s="36">
+        <v>1</v>
+      </c>
+      <c r="N19" s="36">
+        <v>0</v>
+      </c>
+      <c r="O19" s="36">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -4384,13 +4483,13 @@
       <c r="F20" t="s">
         <v>108</v>
       </c>
-      <c r="G20" s="34" t="b">
+      <c r="G20" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>101</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="36">
         <v>1</v>
       </c>
       <c r="J20">
@@ -4402,13 +4501,13 @@
       <c r="L20" t="s">
         <v>102</v>
       </c>
-      <c r="M20" s="34">
-        <v>1</v>
-      </c>
-      <c r="N20" s="34">
-        <v>0</v>
-      </c>
-      <c r="O20" s="34">
+      <c r="M20" s="36">
+        <v>1</v>
+      </c>
+      <c r="N20" s="36">
+        <v>0</v>
+      </c>
+      <c r="O20" s="36">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -4440,13 +4539,13 @@
       <c r="F21" t="s">
         <v>114</v>
       </c>
-      <c r="G21" s="34" t="b">
+      <c r="G21" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="36">
         <v>1</v>
       </c>
       <c r="J21">
@@ -4458,13 +4557,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="34">
-        <v>1</v>
-      </c>
-      <c r="N21" s="34">
-        <v>0</v>
-      </c>
-      <c r="O21" s="34">
+      <c r="M21" s="36">
+        <v>1</v>
+      </c>
+      <c r="N21" s="36">
+        <v>0</v>
+      </c>
+      <c r="O21" s="36">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -4496,13 +4595,13 @@
       <c r="F22" t="s">
         <v>119</v>
       </c>
-      <c r="G22" s="34" t="b">
+      <c r="G22" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="36">
         <v>1</v>
       </c>
       <c r="J22">
@@ -4514,13 +4613,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="34">
-        <v>1</v>
-      </c>
-      <c r="N22" s="34">
-        <v>0</v>
-      </c>
-      <c r="O22" s="34">
+      <c r="M22" s="36">
+        <v>1</v>
+      </c>
+      <c r="N22" s="36">
+        <v>0</v>
+      </c>
+      <c r="O22" s="36">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -4533,32 +4632,32 @@
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="29" customFormat="1" spans="1:18">
-      <c r="A23" s="29">
+    <row r="23" s="31" customFormat="1" spans="1:18">
+      <c r="A23" s="31">
         <v>301</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="29">
-        <v>1</v>
-      </c>
-      <c r="D23" s="29" t="s">
+      <c r="C23" s="31">
+        <v>1</v>
+      </c>
+      <c r="D23" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="29" t="s">
+      <c r="F23" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="29" t="s">
+      <c r="G23" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="36">
         <v>1</v>
       </c>
       <c r="J23">
@@ -4567,54 +4666,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="29" t="s">
+      <c r="L23" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="M23" s="34">
-        <v>1</v>
-      </c>
-      <c r="N23" s="34">
-        <v>0</v>
-      </c>
-      <c r="O23" s="34">
-        <v>0</v>
-      </c>
-      <c r="P23" s="29" t="s">
+      <c r="M23" s="36">
+        <v>1</v>
+      </c>
+      <c r="N23" s="36">
+        <v>0</v>
+      </c>
+      <c r="O23" s="36">
+        <v>0</v>
+      </c>
+      <c r="P23" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="Q23" s="29">
+      <c r="Q23" s="31">
         <v>3</v>
       </c>
-      <c r="R23" s="29" t="s">
+      <c r="R23" s="31" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="24" s="29" customFormat="1" spans="1:18">
-      <c r="A24" s="29">
+    <row r="24" s="31" customFormat="1" spans="1:18">
+      <c r="A24" s="31">
         <v>302</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="29">
-        <v>1</v>
-      </c>
-      <c r="D24" s="29" t="s">
+      <c r="C24" s="31">
+        <v>1</v>
+      </c>
+      <c r="D24" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="29" t="s">
+      <c r="F24" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="G24" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="29" t="s">
+      <c r="G24" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="36">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -4623,51 +4722,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="29" t="s">
+      <c r="L24" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="M24" s="34">
-        <v>1</v>
-      </c>
-      <c r="N24" s="34">
-        <v>0</v>
-      </c>
-      <c r="O24" s="34">
-        <v>0</v>
-      </c>
-      <c r="P24" s="29" t="s">
+      <c r="M24" s="36">
+        <v>1</v>
+      </c>
+      <c r="N24" s="36">
+        <v>0</v>
+      </c>
+      <c r="O24" s="36">
+        <v>0</v>
+      </c>
+      <c r="P24" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="31">
         <v>3</v>
       </c>
-      <c r="R24" s="29" t="s">
+      <c r="R24" s="31" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="25" s="29" customFormat="1" spans="1:18">
-      <c r="A25" s="29">
+    <row r="25" s="31" customFormat="1" spans="1:18">
+      <c r="A25" s="31">
         <v>303</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="29">
-        <v>1</v>
-      </c>
-      <c r="D25" s="29" t="s">
+      <c r="C25" s="31">
+        <v>1</v>
+      </c>
+      <c r="D25" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="29" t="s">
+      <c r="G25" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="36">
         <v>1</v>
       </c>
       <c r="J25">
@@ -4676,51 +4775,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="34">
-        <v>1</v>
-      </c>
-      <c r="N25" s="34">
-        <v>0</v>
-      </c>
-      <c r="O25" s="34">
-        <v>0</v>
-      </c>
-      <c r="P25" s="29" t="s">
+      <c r="M25" s="36">
+        <v>1</v>
+      </c>
+      <c r="N25" s="36">
+        <v>0</v>
+      </c>
+      <c r="O25" s="36">
+        <v>0</v>
+      </c>
+      <c r="P25" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="31">
         <v>3</v>
       </c>
-      <c r="R25" s="29" t="s">
+      <c r="R25" s="31" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="26" s="29" customFormat="1" spans="1:18">
-      <c r="A26" s="29">
+    <row r="26" s="31" customFormat="1" spans="1:18">
+      <c r="A26" s="31">
         <v>304</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C26" s="29">
-        <v>1</v>
-      </c>
-      <c r="D26" s="29" t="s">
+      <c r="C26" s="31">
+        <v>1</v>
+      </c>
+      <c r="D26" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="29" t="s">
+      <c r="F26" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="G26" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="29" t="s">
+      <c r="G26" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="36">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -4729,54 +4828,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="L26" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="34">
-        <v>1</v>
-      </c>
-      <c r="N26" s="34">
-        <v>0</v>
-      </c>
-      <c r="O26" s="34">
-        <v>0</v>
-      </c>
-      <c r="P26" s="29" t="s">
+      <c r="M26" s="36">
+        <v>1</v>
+      </c>
+      <c r="N26" s="36">
+        <v>0</v>
+      </c>
+      <c r="O26" s="36">
+        <v>0</v>
+      </c>
+      <c r="P26" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="Q26" s="29">
+      <c r="Q26" s="31">
         <v>3</v>
       </c>
-      <c r="R26" s="29" t="s">
+      <c r="R26" s="31" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="27" s="29" customFormat="1" spans="1:18">
-      <c r="A27" s="29">
+    <row r="27" s="31" customFormat="1" spans="1:18">
+      <c r="A27" s="31">
         <v>305</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="31">
         <v>3</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="G27" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="29" t="s">
+      <c r="G27" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="36">
         <v>1</v>
       </c>
       <c r="J27">
@@ -4788,51 +4887,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="34">
-        <v>1</v>
-      </c>
-      <c r="N27" s="34">
-        <v>0</v>
-      </c>
-      <c r="O27" s="34">
-        <v>0</v>
-      </c>
-      <c r="P27" s="29" t="s">
+      <c r="M27" s="36">
+        <v>1</v>
+      </c>
+      <c r="N27" s="36">
+        <v>0</v>
+      </c>
+      <c r="O27" s="36">
+        <v>0</v>
+      </c>
+      <c r="P27" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="Q27" s="29">
+      <c r="Q27" s="31">
         <v>3</v>
       </c>
-      <c r="R27" s="29" t="s">
+      <c r="R27" s="31" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="28" s="29" customFormat="1" spans="1:18">
-      <c r="A28" s="29">
+    <row r="28" s="31" customFormat="1" spans="1:18">
+      <c r="A28" s="31">
         <v>306</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="31">
         <v>2</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="G28" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="29">
-        <v>0</v>
-      </c>
-      <c r="I28" s="34">
+      <c r="G28" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="31">
+        <v>0</v>
+      </c>
+      <c r="I28" s="36">
         <v>1</v>
       </c>
       <c r="J28">
@@ -4841,54 +4940,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="29">
-        <v>1</v>
-      </c>
-      <c r="M28" s="34">
-        <v>1</v>
-      </c>
-      <c r="N28" s="34">
-        <v>0</v>
-      </c>
-      <c r="O28" s="34">
-        <v>0</v>
-      </c>
-      <c r="P28" s="29" t="s">
+      <c r="L28" s="31">
+        <v>1</v>
+      </c>
+      <c r="M28" s="36">
+        <v>1</v>
+      </c>
+      <c r="N28" s="36">
+        <v>0</v>
+      </c>
+      <c r="O28" s="36">
+        <v>0</v>
+      </c>
+      <c r="P28" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="Q28" s="29">
+      <c r="Q28" s="31">
         <v>3</v>
       </c>
-      <c r="R28" s="29" t="s">
+      <c r="R28" s="31" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="29" s="29" customFormat="1" spans="1:18">
-      <c r="A29" s="29">
+    <row r="29" s="31" customFormat="1" spans="1:18">
+      <c r="A29" s="31">
         <v>307</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="29">
-        <v>1</v>
-      </c>
-      <c r="D29" s="29" t="s">
+      <c r="C29" s="31">
+        <v>1</v>
+      </c>
+      <c r="D29" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="29" t="s">
+      <c r="F29" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="G29" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="29" t="s">
+      <c r="G29" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="I29" s="34">
+      <c r="I29" s="36">
         <v>1</v>
       </c>
       <c r="J29">
@@ -4897,54 +4996,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="29" t="s">
+      <c r="L29" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="M29" s="34">
+      <c r="M29" s="36">
         <v>0.1</v>
       </c>
-      <c r="N29" s="34">
-        <v>0</v>
-      </c>
-      <c r="O29" s="34">
+      <c r="N29" s="36">
+        <v>0</v>
+      </c>
+      <c r="O29" s="36">
         <v>0.17</v>
       </c>
-      <c r="P29" s="29" t="s">
+      <c r="P29" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="Q29" s="29">
+      <c r="Q29" s="31">
         <v>3</v>
       </c>
-      <c r="R29" s="29" t="s">
+      <c r="R29" s="31" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="30" s="29" customFormat="1" spans="1:18">
-      <c r="A30" s="29">
+    <row r="30" s="31" customFormat="1" spans="1:18">
+      <c r="A30" s="31">
         <v>308</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C30" s="29">
-        <v>1</v>
-      </c>
-      <c r="D30" s="29" t="s">
+      <c r="C30" s="31">
+        <v>1</v>
+      </c>
+      <c r="D30" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="G30" s="34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="29" t="s">
+      <c r="G30" s="36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="36">
         <v>1</v>
       </c>
       <c r="J30">
@@ -4953,54 +5052,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="29" t="s">
+      <c r="L30" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="M30" s="34">
-        <v>1</v>
-      </c>
-      <c r="N30" s="34">
-        <v>0</v>
-      </c>
-      <c r="O30" s="34">
-        <v>0</v>
-      </c>
-      <c r="P30" s="29" t="s">
+      <c r="M30" s="36">
+        <v>1</v>
+      </c>
+      <c r="N30" s="36">
+        <v>0</v>
+      </c>
+      <c r="O30" s="36">
+        <v>0</v>
+      </c>
+      <c r="P30" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="Q30" s="29">
+      <c r="Q30" s="31">
         <v>3</v>
       </c>
-      <c r="R30" s="29" t="s">
+      <c r="R30" s="31" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="31" s="29" customFormat="1" spans="1:18">
-      <c r="A31" s="29">
+    <row r="31" s="31" customFormat="1" spans="1:18">
+      <c r="A31" s="31">
         <v>309</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="31">
         <v>2</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="F31" s="29" t="s">
+      <c r="F31" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="G31" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="29" t="s">
+      <c r="G31" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="36">
         <v>1</v>
       </c>
       <c r="J31">
@@ -5009,54 +5108,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="29" t="s">
+      <c r="L31" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="M31" s="34">
-        <v>1</v>
-      </c>
-      <c r="N31" s="34">
-        <v>0</v>
-      </c>
-      <c r="O31" s="34">
-        <v>0</v>
-      </c>
-      <c r="P31" s="29" t="s">
+      <c r="M31" s="36">
+        <v>1</v>
+      </c>
+      <c r="N31" s="36">
+        <v>0</v>
+      </c>
+      <c r="O31" s="36">
+        <v>0</v>
+      </c>
+      <c r="P31" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="Q31" s="29">
+      <c r="Q31" s="31">
         <v>3</v>
       </c>
-      <c r="R31" s="29" t="s">
+      <c r="R31" s="31" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" s="29" customFormat="1" spans="1:18">
-      <c r="A32" s="29">
+    <row r="32" s="31" customFormat="1" spans="1:18">
+      <c r="A32" s="31">
         <v>310</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="31">
         <v>2</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="G32" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="29" t="s">
+      <c r="G32" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="I32" s="34">
+      <c r="I32" s="36">
         <v>1</v>
       </c>
       <c r="J32">
@@ -5065,54 +5164,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="29" t="s">
+      <c r="L32" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="M32" s="34">
-        <v>1</v>
-      </c>
-      <c r="N32" s="34">
-        <v>0</v>
-      </c>
-      <c r="O32" s="34">
-        <v>0</v>
-      </c>
-      <c r="P32" s="29" t="s">
+      <c r="M32" s="36">
+        <v>1</v>
+      </c>
+      <c r="N32" s="36">
+        <v>0</v>
+      </c>
+      <c r="O32" s="36">
+        <v>0</v>
+      </c>
+      <c r="P32" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="Q32" s="29">
+      <c r="Q32" s="31">
         <v>4</v>
       </c>
-      <c r="R32" s="29" t="s">
+      <c r="R32" s="31" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="33" s="29" customFormat="1" spans="1:21">
-      <c r="A33" s="29">
+    <row r="33" s="31" customFormat="1" spans="1:21">
+      <c r="A33" s="31">
         <v>311</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="31">
         <v>2</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="G33" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="29">
-        <v>0</v>
-      </c>
-      <c r="I33" s="34">
+      <c r="G33" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="31">
+        <v>0</v>
+      </c>
+      <c r="I33" s="36">
         <v>1</v>
       </c>
       <c r="J33">
@@ -5121,45 +5220,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="29">
-        <v>1</v>
-      </c>
-      <c r="M33" s="34">
-        <v>1</v>
-      </c>
-      <c r="N33" s="34">
-        <v>0</v>
-      </c>
-      <c r="O33" s="34">
-        <v>0</v>
-      </c>
-      <c r="P33" s="29" t="s">
+      <c r="L33" s="31">
+        <v>1</v>
+      </c>
+      <c r="M33" s="36">
+        <v>1</v>
+      </c>
+      <c r="N33" s="36">
+        <v>0</v>
+      </c>
+      <c r="O33" s="36">
+        <v>0</v>
+      </c>
+      <c r="P33" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="Q33" s="29">
+      <c r="Q33" s="31">
         <v>3</v>
       </c>
-      <c r="R33" s="29" t="s">
+      <c r="R33" s="31" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" s="29" customFormat="1" spans="1:21">
-      <c r="A34" s="29">
+    <row r="34" s="31" customFormat="1" spans="1:21">
+      <c r="A34" s="31">
         <v>312</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="31">
         <v>2</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="G34" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="34">
+      <c r="G34" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="36">
         <v>1</v>
       </c>
       <c r="J34">
@@ -5168,45 +5267,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="34">
-        <v>1</v>
-      </c>
-      <c r="N34" s="34">
-        <v>0</v>
-      </c>
-      <c r="O34" s="34">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="29">
-        <v>1</v>
-      </c>
-      <c r="R34" s="29" t="s">
+      <c r="M34" s="36">
+        <v>1</v>
+      </c>
+      <c r="N34" s="36">
+        <v>0</v>
+      </c>
+      <c r="O34" s="36">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="31">
+        <v>1</v>
+      </c>
+      <c r="R34" s="31" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="35" s="27" customFormat="1" spans="1:21">
-      <c r="A35" s="27">
+    <row r="35" s="29" customFormat="1" spans="1:21">
+      <c r="A35" s="29">
         <v>401</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="29">
         <v>2</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="37" t="s">
+      <c r="F35" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="27" t="s">
+      <c r="G35" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="36">
         <v>1</v>
       </c>
       <c r="J35">
@@ -5218,45 +5317,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="34">
-        <v>1</v>
-      </c>
-      <c r="N35" s="34">
-        <v>0</v>
-      </c>
-      <c r="O35" s="34">
-        <v>0</v>
-      </c>
-      <c r="P35" s="27" t="s">
+      <c r="M35" s="36">
+        <v>1</v>
+      </c>
+      <c r="N35" s="36">
+        <v>0</v>
+      </c>
+      <c r="O35" s="36">
+        <v>0</v>
+      </c>
+      <c r="P35" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="27">
+      <c r="Q35" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="27" customFormat="1" spans="1:21">
-      <c r="A36" s="27">
+    <row r="36" s="29" customFormat="1" spans="1:21">
+      <c r="A36" s="29">
         <v>402</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="29">
         <v>2</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="F36" s="38" t="s">
+      <c r="F36" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="G36" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="27" t="s">
+      <c r="G36" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="36">
         <v>1</v>
       </c>
       <c r="J36">
@@ -5268,48 +5367,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="34">
-        <v>1</v>
-      </c>
-      <c r="N36" s="34">
-        <v>0</v>
-      </c>
-      <c r="O36" s="34">
-        <v>0</v>
-      </c>
-      <c r="P36" s="27" t="s">
+      <c r="M36" s="36">
+        <v>1</v>
+      </c>
+      <c r="N36" s="36">
+        <v>0</v>
+      </c>
+      <c r="O36" s="36">
+        <v>0</v>
+      </c>
+      <c r="P36" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="Q36" s="27">
+      <c r="Q36" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="27" customFormat="1" spans="1:21">
-      <c r="A37" s="27">
+    <row r="37" s="29" customFormat="1" spans="1:21">
+      <c r="A37" s="29">
         <v>403</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="29">
         <v>2</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="27" t="s">
+      <c r="E37" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="F37" s="27" t="s">
+      <c r="F37" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="27" t="s">
+      <c r="G37" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="34">
+      <c r="I37" s="36">
         <v>1</v>
       </c>
       <c r="J37">
@@ -5318,80 +5417,80 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="27" t="s">
+      <c r="L37" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="34">
-        <v>1</v>
-      </c>
-      <c r="N37" s="34">
-        <v>0</v>
-      </c>
-      <c r="O37" s="34">
-        <v>0</v>
-      </c>
-      <c r="P37" s="27" t="s">
+      <c r="M37" s="36">
+        <v>1</v>
+      </c>
+      <c r="N37" s="36">
+        <v>0</v>
+      </c>
+      <c r="O37" s="36">
+        <v>0</v>
+      </c>
+      <c r="P37" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="27">
+      <c r="Q37" s="29">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="36" customFormat="1" spans="1:21">
-      <c r="A38" s="36">
+    <row r="38" s="38" customFormat="1" spans="1:21">
+      <c r="A38" s="38">
         <v>404</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C38" s="36">
-        <v>1</v>
-      </c>
-      <c r="D38" s="28" t="s">
+      <c r="C38" s="38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="36" t="s">
+      <c r="E38" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="28" t="s">
+      <c r="F38" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="36" t="s">
+      <c r="G38" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="36">
-        <v>1</v>
-      </c>
-      <c r="J38" s="28">
-        <v>0</v>
-      </c>
-      <c r="K38" s="28">
+      <c r="I38" s="38">
+        <v>1</v>
+      </c>
+      <c r="J38" s="30">
+        <v>0</v>
+      </c>
+      <c r="K38" s="30">
         <v>2</v>
       </c>
-      <c r="L38" s="36" t="s">
+      <c r="L38" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="36">
-        <v>1</v>
-      </c>
-      <c r="N38" s="36">
-        <v>0</v>
-      </c>
-      <c r="O38" s="36">
-        <v>0</v>
-      </c>
-      <c r="P38" s="36" t="s">
+      <c r="M38" s="38">
+        <v>1</v>
+      </c>
+      <c r="N38" s="38">
+        <v>0</v>
+      </c>
+      <c r="O38" s="38">
+        <v>0</v>
+      </c>
+      <c r="P38" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="36">
+      <c r="Q38" s="38">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="27" customFormat="1" spans="1:21">
-      <c r="A39" s="27">
+    <row r="39" s="29" customFormat="1" spans="1:21">
+      <c r="A39" s="29">
         <v>405</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -5409,13 +5508,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="34" t="b">
+      <c r="G39" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="34">
+      <c r="I39" s="36">
         <v>1</v>
       </c>
       <c r="J39">
@@ -5427,13 +5526,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="34">
-        <v>1</v>
-      </c>
-      <c r="N39" s="34">
-        <v>0</v>
-      </c>
-      <c r="O39" s="34">
+      <c r="M39" s="36">
+        <v>1</v>
+      </c>
+      <c r="N39" s="36">
+        <v>0</v>
+      </c>
+      <c r="O39" s="36">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -5449,32 +5548,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="27" customFormat="1" spans="1:21">
-      <c r="A40" s="27">
+    <row r="40" s="29" customFormat="1" spans="1:21">
+      <c r="A40" s="29">
         <v>406</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C40" s="27">
-        <v>1</v>
-      </c>
-      <c r="D40" s="27" t="s">
+      <c r="C40" s="29">
+        <v>1</v>
+      </c>
+      <c r="D40" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="E40" s="29" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="34" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="27">
-        <v>0</v>
-      </c>
-      <c r="I40" s="34">
+      <c r="G40" s="36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="29">
+        <v>0</v>
+      </c>
+      <c r="I40" s="36">
         <v>1</v>
       </c>
       <c r="J40">
@@ -5483,27 +5582,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="27">
+      <c r="L40" s="29">
         <v>3</v>
       </c>
-      <c r="M40" s="34">
-        <v>1</v>
-      </c>
-      <c r="N40" s="34">
-        <v>0</v>
-      </c>
-      <c r="O40" s="34">
-        <v>0</v>
-      </c>
-      <c r="P40" s="27" t="s">
+      <c r="M40" s="36">
+        <v>1</v>
+      </c>
+      <c r="N40" s="36">
+        <v>0</v>
+      </c>
+      <c r="O40" s="36">
+        <v>0</v>
+      </c>
+      <c r="P40" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="27">
+      <c r="Q40" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="27">
+      <c r="A41" s="29">
         <v>407</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -5521,13 +5620,13 @@
       <c r="F41" t="s">
         <v>85</v>
       </c>
-      <c r="G41" s="34" t="b">
+      <c r="G41" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>86</v>
       </c>
-      <c r="I41" s="34">
+      <c r="I41" s="36">
         <v>1</v>
       </c>
       <c r="J41">
@@ -5539,13 +5638,13 @@
       <c r="L41" t="s">
         <v>87</v>
       </c>
-      <c r="M41" s="34">
-        <v>1</v>
-      </c>
-      <c r="N41" s="34">
-        <v>0</v>
-      </c>
-      <c r="O41" s="34">
+      <c r="M41" s="36">
+        <v>1</v>
+      </c>
+      <c r="N41" s="36">
+        <v>0</v>
+      </c>
+      <c r="O41" s="36">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -5559,7 +5658,7 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="27">
+      <c r="A42" s="29">
         <v>408</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -5577,13 +5676,13 @@
       <c r="F42" t="s">
         <v>108</v>
       </c>
-      <c r="G42" s="34" t="b">
+      <c r="G42" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>101</v>
       </c>
-      <c r="I42" s="34">
+      <c r="I42" s="36">
         <v>1</v>
       </c>
       <c r="J42">
@@ -5595,13 +5694,13 @@
       <c r="L42" t="s">
         <v>102</v>
       </c>
-      <c r="M42" s="34">
-        <v>1</v>
-      </c>
-      <c r="N42" s="34">
-        <v>0</v>
-      </c>
-      <c r="O42" s="34">
+      <c r="M42" s="36">
+        <v>1</v>
+      </c>
+      <c r="N42" s="36">
+        <v>0</v>
+      </c>
+      <c r="O42" s="36">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -5615,7 +5714,7 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="27">
+      <c r="A43" s="29">
         <v>409</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -5633,13 +5732,13 @@
       <c r="F43" t="s">
         <v>93</v>
       </c>
-      <c r="G43" s="34" t="b">
+      <c r="G43" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="34">
+      <c r="I43" s="36">
         <v>1</v>
       </c>
       <c r="J43">
@@ -5651,13 +5750,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="34">
-        <v>1</v>
-      </c>
-      <c r="N43" s="34">
-        <v>0</v>
-      </c>
-      <c r="O43" s="34">
+      <c r="M43" s="36">
+        <v>1</v>
+      </c>
+      <c r="N43" s="36">
+        <v>0</v>
+      </c>
+      <c r="O43" s="36">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -5671,7 +5770,7 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="27">
+      <c r="A44" s="29">
         <v>410</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -5689,13 +5788,13 @@
       <c r="F44" t="s">
         <v>100</v>
       </c>
-      <c r="G44" s="34" t="b">
+      <c r="G44" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>101</v>
       </c>
-      <c r="I44" s="34">
+      <c r="I44" s="36">
         <v>1</v>
       </c>
       <c r="J44">
@@ -5707,13 +5806,13 @@
       <c r="L44" t="s">
         <v>102</v>
       </c>
-      <c r="M44" s="34">
-        <v>1</v>
-      </c>
-      <c r="N44" s="34">
-        <v>0</v>
-      </c>
-      <c r="O44" s="34">
+      <c r="M44" s="36">
+        <v>1</v>
+      </c>
+      <c r="N44" s="36">
+        <v>0</v>
+      </c>
+      <c r="O44" s="36">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -5727,7 +5826,7 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="27">
+      <c r="A45" s="29">
         <v>411</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -5745,13 +5844,13 @@
       <c r="F45" t="s">
         <v>119</v>
       </c>
-      <c r="G45" s="34" t="b">
+      <c r="G45" s="36" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="34">
+      <c r="I45" s="36">
         <v>1</v>
       </c>
       <c r="J45">
@@ -5763,13 +5862,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="34">
-        <v>1</v>
-      </c>
-      <c r="N45" s="34">
-        <v>0</v>
-      </c>
-      <c r="O45" s="34">
+      <c r="M45" s="36">
+        <v>1</v>
+      </c>
+      <c r="N45" s="36">
+        <v>0</v>
+      </c>
+      <c r="O45" s="36">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -5831,10 +5930,10 @@
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:8">
-      <c r="A2" s="18">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>336</v>
       </c>
       <c r="C2" t="s">
@@ -5843,18 +5942,18 @@
       <c r="D2" t="s">
         <v>338</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="25" t="s">
         <v>339</v>
       </c>
-      <c r="H2" s="18" t="b">
+      <c r="H2" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" s="13" customFormat="1" spans="1:8">
-      <c r="A3" s="18">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="20" t="s">
         <v>340</v>
       </c>
       <c r="C3" t="s">
@@ -5863,15 +5962,15 @@
       <c r="D3" t="s">
         <v>338</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="24" t="s">
         <v>339</v>
       </c>
-      <c r="H3" s="18" t="b">
+      <c r="H3" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="18">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -5883,15 +5982,15 @@
       <c r="D4" t="s">
         <v>343</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="24" t="s">
         <v>344</v>
       </c>
-      <c r="H4" s="18" t="b">
+      <c r="H4" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="18">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -5903,15 +6002,15 @@
       <c r="D5" t="s">
         <v>343</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="24" t="s">
         <v>344</v>
       </c>
-      <c r="H5" s="18" t="b">
+      <c r="H5" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="18">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -5926,12 +6025,12 @@
       <c r="E6" t="s">
         <v>347</v>
       </c>
-      <c r="H6" s="18" t="b">
+      <c r="H6" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="18">
+      <c r="A7" s="20">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -5946,12 +6045,12 @@
       <c r="E7" t="s">
         <v>347</v>
       </c>
-      <c r="H7" s="18" t="b">
+      <c r="H7" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="18">
+      <c r="A8" s="20">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -5966,12 +6065,12 @@
       <c r="E8" t="s">
         <v>352</v>
       </c>
-      <c r="H8" s="18" t="b">
+      <c r="H8" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="18">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -5986,12 +6085,12 @@
       <c r="E9" t="s">
         <v>352</v>
       </c>
-      <c r="H9" s="18" t="b">
+      <c r="H9" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="18">
+      <c r="A10" s="20">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -6006,12 +6105,12 @@
       <c r="E10" t="s">
         <v>347</v>
       </c>
-      <c r="H10" s="18" t="b">
+      <c r="H10" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="18">
+      <c r="A11" s="20">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -6026,12 +6125,12 @@
       <c r="E11" t="s">
         <v>347</v>
       </c>
-      <c r="H11" s="18" t="b">
+      <c r="H11" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="18">
+      <c r="A12" s="20">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -6043,21 +6142,21 @@
       <c r="D12" t="s">
         <v>358</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="23" t="s">
         <v>359</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="G12" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="H12" s="18" t="b">
+      <c r="H12" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="18">
+      <c r="A13" s="20">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -6069,17 +6168,17 @@
       <c r="D13" t="s">
         <v>343</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="24" t="s">
         <v>363</v>
       </c>
       <c r="F13" s="6"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="18" t="b">
+      <c r="G13" s="26"/>
+      <c r="H13" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="18">
+      <c r="A14" s="20">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -6091,17 +6190,17 @@
       <c r="D14" t="s">
         <v>343</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>363</v>
       </c>
       <c r="F14" s="6"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="18" t="b">
+      <c r="G14" s="26"/>
+      <c r="H14" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="18">
+      <c r="A15" s="20">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -6113,17 +6212,17 @@
       <c r="D15" t="s">
         <v>343</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="24" t="s">
         <v>363</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="18" t="b">
+      <c r="G15" s="26"/>
+      <c r="H15" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="18">
+      <c r="A16" s="20">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -6135,17 +6234,17 @@
       <c r="D16" t="s">
         <v>343</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="24" t="s">
         <v>363</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="18" t="b">
+      <c r="G16" s="26"/>
+      <c r="H16" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="18">
+      <c r="A17" s="20">
         <v>101</v>
       </c>
       <c r="B17" t="s">
@@ -6157,15 +6256,15 @@
       <c r="D17" t="s">
         <v>369</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="23" t="s">
         <v>370</v>
       </c>
-      <c r="H17" s="18" t="b">
+      <c r="H17" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="18">
+      <c r="A18" s="20">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -6177,21 +6276,21 @@
       <c r="D18" t="s">
         <v>373</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="24" t="s">
         <v>374</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="G18" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="H18" s="18" t="b">
+      <c r="H18" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="18">
+      <c r="A19" s="20">
         <v>103</v>
       </c>
       <c r="B19" t="s">
@@ -6203,21 +6302,21 @@
       <c r="D19" t="s">
         <v>358</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="23" t="s">
         <v>359</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="G19" s="24" t="s">
+      <c r="G19" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="H19" s="18" t="b">
+      <c r="H19" s="20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="18">
+      <c r="A20" s="20">
         <v>201</v>
       </c>
       <c r="B20" t="s">
@@ -6229,15 +6328,15 @@
       <c r="D20" t="s">
         <v>338</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="H20" s="18" t="b">
+      <c r="H20" s="20" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="18">
+      <c r="A21" s="20">
         <v>202</v>
       </c>
       <c r="B21" t="s">
@@ -6249,16 +6348,16 @@
       <c r="D21" t="s">
         <v>381</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="23" t="s">
         <v>382</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="24" t="s">
         <v>384</v>
       </c>
-      <c r="H21" s="18" t="b">
+      <c r="H21" s="20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6304,10 +6403,10 @@
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="18">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
         <v>385</v>
       </c>
     </row>
@@ -6354,50 +6453,50 @@
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
-      <c r="A2" s="18">
-        <v>1</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="20">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="23" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="18">
+      <c r="A3" s="20">
         <v>2</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="24" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="18">
+      <c r="A4" s="20">
         <v>3</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="21" t="s">
         <v>392</v>
       </c>
       <c r="E4" t="s">
@@ -6405,225 +6504,225 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:5">
-      <c r="A5" s="18">
+      <c r="A5" s="20">
         <v>4</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="21" t="s">
         <v>398</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="24" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:5">
-      <c r="A6" s="18">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="25" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:5">
-      <c r="A7" s="18">
+      <c r="A7" s="20">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="24" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:5">
-      <c r="A8" s="18">
+      <c r="A8" s="20">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>404</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="24" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:5">
-      <c r="A9" s="18">
+      <c r="A9" s="20">
         <v>8</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="21" t="s">
         <v>406</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="24" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:5">
-      <c r="A10" s="18">
+      <c r="A10" s="20">
         <v>9</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="22" t="s">
         <v>391</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="21" t="s">
         <v>392</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="24" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
-      <c r="A11" s="18">
+      <c r="A11" s="20">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="21" t="s">
         <v>410</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="23" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:5">
-      <c r="A12" s="18">
+      <c r="A12" s="20">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="24" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:5">
-      <c r="A13" s="18">
+      <c r="A13" s="20">
         <v>12</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="22" t="s">
         <v>411</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="23" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:5">
-      <c r="A14" s="18">
+      <c r="A14" s="20">
         <v>13</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>418</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="21" t="s">
         <v>419</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="24" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:5">
-      <c r="A15" s="18">
+      <c r="A15" s="20">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="21" t="s">
         <v>421</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="23" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="18"/>
+      <c r="A16" s="20"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="18"/>
+      <c r="A17" s="20"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="18"/>
+      <c r="A18" s="20"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="18"/>
+      <c r="A19" s="20"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="18"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="18"/>
+      <c r="A21" s="20"/>
       <c r="B21" s="3"/>
-      <c r="E21" s="22"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="18"/>
+      <c r="A22" s="20"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="18"/>
+      <c r="A23" s="20"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="18"/>
-      <c r="E24" s="22"/>
+      <c r="A24" s="20"/>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="18"/>
+      <c r="A25" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6649,7 +6748,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28.875" customWidth="1"/>
@@ -7407,13 +7506,13 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="15" t="s">
         <v>563</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="C69" t="s">
         <v>564</v>
-      </c>
-      <c r="C69" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7424,7 +7523,7 @@
         <v>265</v>
       </c>
       <c r="C70" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7435,7 +7534,7 @@
         <v>266</v>
       </c>
       <c r="C71" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7446,7 +7545,7 @@
         <v>267</v>
       </c>
       <c r="C72" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7454,10 +7553,10 @@
         <v>186</v>
       </c>
       <c r="B73" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="C73" t="s">
         <v>569</v>
-      </c>
-      <c r="C73" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7465,10 +7564,10 @@
         <v>187</v>
       </c>
       <c r="B74" s="13" t="s">
+        <v>570</v>
+      </c>
+      <c r="C74" t="s">
         <v>571</v>
-      </c>
-      <c r="C74" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7476,10 +7575,10 @@
         <v>188</v>
       </c>
       <c r="B75" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="C75" t="s">
         <v>573</v>
-      </c>
-      <c r="C75" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="76" spans="1:3">
@@ -7490,7 +7589,7 @@
         <v>271</v>
       </c>
       <c r="C76" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="77" spans="1:3">
@@ -7501,177 +7600,205 @@
         <v>272</v>
       </c>
       <c r="C77" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
+        <v>576</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>577</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="C78" t="s">
         <v>578</v>
-      </c>
-      <c r="C78" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="79" ht="14.25" spans="1:3">
       <c r="A79" t="s">
+        <v>579</v>
+      </c>
+      <c r="B79" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="C79" t="s">
         <v>581</v>
-      </c>
-      <c r="C79" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="1:3">
       <c r="A80" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B80" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="C80" t="s">
         <v>584</v>
-      </c>
-      <c r="C80" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="81" ht="14.25" spans="1:3">
       <c r="A81" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B81" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="C81" t="s">
         <v>587</v>
-      </c>
-      <c r="C81" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="82" ht="14.25" spans="1:3">
       <c r="A82" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B82" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="C82" s="8" t="s">
         <v>590</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="83" ht="14.25" spans="1:3">
       <c r="A83" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B83" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="C83" s="8" t="s">
         <v>593</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="84" ht="14.25" spans="1:3">
       <c r="A84" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="C84" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="85" ht="14.25" spans="1:3">
       <c r="A85" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B85" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="B85" s="5" t="s">
+      <c r="C85" s="8" t="s">
         <v>599</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="86" ht="14.25" spans="1:3">
       <c r="A86" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B86" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="C86" s="8" t="s">
         <v>602</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="87" ht="14.25" spans="1:3">
       <c r="A87" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="C87" t="s">
         <v>605</v>
-      </c>
-      <c r="C87" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="88" ht="14.25" spans="1:3">
       <c r="A88" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="B88" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="C88" t="s">
         <v>608</v>
-      </c>
-      <c r="C88" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="89" ht="14.25" spans="1:3">
       <c r="A89" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B89" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="C89" t="s">
         <v>611</v>
-      </c>
-      <c r="C89" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="90" ht="14.25" spans="1:3">
       <c r="A90" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="C90" t="s">
         <v>614</v>
-      </c>
-      <c r="C90" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="91" ht="14.25" spans="1:3">
       <c r="A91" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B91" s="6" t="s">
         <v>616</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="C91" t="s">
         <v>617</v>
-      </c>
-      <c r="C91" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="92" ht="14.25" spans="1:3">
       <c r="A92" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="B92" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="C92" t="s">
         <v>620</v>
       </c>
-      <c r="C92" t="s">
+    </row>
+    <row r="93" ht="14.25" spans="1:3">
+      <c r="A93" s="6" t="s">
         <v>621</v>
       </c>
-    </row>
-    <row r="93" ht="14.25" spans="1:3">
-      <c r="A93" s="17" t="s">
+      <c r="B93" s="5" t="s">
         <v>622</v>
+      </c>
+      <c r="C93" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="94" ht="14.25" spans="1:3">
+      <c r="A94" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C94" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="95" ht="14.25" spans="1:3">
+      <c r="A95" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -7715,25 +7842,25 @@
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:7">
-      <c r="A2" s="29">
+      <c r="A2" s="31">
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="31">
         <v>20</v>
       </c>
-      <c r="D2" s="29">
-        <v>1</v>
-      </c>
-      <c r="E2" s="18">
-        <v>1</v>
-      </c>
-      <c r="F2" s="18">
-        <v>0</v>
-      </c>
-      <c r="G2" s="18">
+      <c r="D2" s="31">
+        <v>1</v>
+      </c>
+      <c r="E2" s="20">
+        <v>1</v>
+      </c>
+      <c r="F2" s="20">
+        <v>0</v>
+      </c>
+      <c r="G2" s="20">
         <v>200</v>
       </c>
     </row>
@@ -7756,7 +7883,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G3" s="20">
         <v>100</v>
       </c>
     </row>
@@ -7779,7 +7906,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="20">
         <v>100</v>
       </c>
     </row>
@@ -7802,7 +7929,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="20">
         <v>110</v>
       </c>
     </row>
@@ -7825,7 +7952,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <v>200</v>
       </c>
     </row>
@@ -7848,7 +7975,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <v>90</v>
       </c>
     </row>
@@ -7871,7 +7998,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <v>200</v>
       </c>
     </row>
@@ -7894,7 +8021,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <v>100</v>
       </c>
     </row>
@@ -7917,7 +8044,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="20">
         <v>90</v>
       </c>
     </row>
@@ -7940,7 +8067,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <v>0</v>
       </c>
     </row>
@@ -7963,7 +8090,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <v>180</v>
       </c>
     </row>
@@ -7986,7 +8113,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="20">
         <v>0</v>
       </c>
     </row>
@@ -8009,7 +8136,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="20">
         <v>100</v>
       </c>
     </row>
@@ -8032,7 +8159,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="20">
         <v>180</v>
       </c>
     </row>
@@ -8055,7 +8182,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="20">
         <v>110</v>
       </c>
     </row>
@@ -8078,288 +8205,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="20">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="31" customFormat="1" spans="1:7">
-      <c r="A18" s="31">
+    <row r="18" s="33" customFormat="1" spans="1:7">
+      <c r="A18" s="33">
         <v>301</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="33">
         <v>50</v>
       </c>
-      <c r="D18" s="31">
-        <v>0</v>
-      </c>
-      <c r="E18" s="31">
+      <c r="D18" s="33">
+        <v>0</v>
+      </c>
+      <c r="E18" s="33">
         <v>400</v>
       </c>
-      <c r="F18" s="31">
-        <v>0</v>
-      </c>
-      <c r="G18" s="33">
+      <c r="F18" s="33">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="31" customFormat="1" spans="1:7">
-      <c r="A19" s="31">
+    <row r="19" s="33" customFormat="1" spans="1:7">
+      <c r="A19" s="33">
         <v>302</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="34" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="33">
         <v>25</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="33">
         <v>9</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="33">
         <v>100</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="33">
         <v>303</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="35">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="31" customFormat="1" spans="1:7">
-      <c r="A20" s="31">
+    <row r="20" s="33" customFormat="1" spans="1:7">
+      <c r="A20" s="33">
         <v>303</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="33">
         <v>20</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="33">
         <v>3</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="33">
         <v>50</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="33">
         <v>301</v>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="35">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="31" customFormat="1" spans="1:7">
-      <c r="A21" s="31">
+    <row r="21" s="33" customFormat="1" spans="1:7">
+      <c r="A21" s="33">
         <v>304</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="33">
         <v>30</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="33">
         <v>11</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="33">
         <v>300</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="33">
         <v>301</v>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="35">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="31" customFormat="1" spans="1:7">
-      <c r="A22" s="31">
+    <row r="22" s="33" customFormat="1" spans="1:7">
+      <c r="A22" s="33">
         <v>305</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="33">
         <v>25</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="33">
         <v>8</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="33">
         <v>100</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="33">
         <v>303</v>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="35">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="31" customFormat="1" spans="1:7">
-      <c r="A23" s="31">
+    <row r="23" s="33" customFormat="1" spans="1:7">
+      <c r="A23" s="33">
         <v>306</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="33">
         <v>35</v>
       </c>
-      <c r="D23" s="31">
-        <v>0</v>
-      </c>
-      <c r="E23" s="31">
+      <c r="D23" s="33">
+        <v>0</v>
+      </c>
+      <c r="E23" s="33">
         <v>200</v>
       </c>
-      <c r="F23" s="31">
-        <v>0</v>
-      </c>
-      <c r="G23" s="33">
+      <c r="F23" s="33">
+        <v>0</v>
+      </c>
+      <c r="G23" s="35">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="31" customFormat="1" spans="1:7">
-      <c r="A24" s="31">
+    <row r="24" s="33" customFormat="1" spans="1:7">
+      <c r="A24" s="33">
         <v>307</v>
       </c>
-      <c r="B24" s="32" t="s">
+      <c r="B24" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="33">
         <v>35</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="33">
         <v>12</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="33">
         <v>150</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="33">
         <v>302</v>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="35">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="31" customFormat="1" spans="1:7">
-      <c r="A25" s="31">
+    <row r="25" s="33" customFormat="1" spans="1:7">
+      <c r="A25" s="33">
         <v>308</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="34" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="33">
         <v>35</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="33">
         <v>12</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="33">
         <v>150</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="33">
         <v>302</v>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="35">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="31" customFormat="1" spans="1:7">
-      <c r="A26" s="31">
+    <row r="26" s="33" customFormat="1" spans="1:7">
+      <c r="A26" s="33">
         <v>309</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="33">
         <v>20</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="33">
         <v>10</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="33">
         <v>80</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="33">
         <v>306</v>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="35">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="31" customFormat="1" spans="1:7">
-      <c r="A27" s="31">
+    <row r="27" s="33" customFormat="1" spans="1:7">
+      <c r="A27" s="33">
         <v>310</v>
       </c>
-      <c r="B27" s="32" t="s">
+      <c r="B27" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="33">
         <v>30</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="33">
         <v>10</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="33">
         <v>120</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="33">
         <v>309</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="35">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="31" customFormat="1" spans="1:7">
-      <c r="A28" s="31">
+    <row r="28" s="33" customFormat="1" spans="1:7">
+      <c r="A28" s="33">
         <v>311</v>
       </c>
-      <c r="B28" s="32" t="s">
+      <c r="B28" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="33">
         <v>30</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="33">
         <v>10</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="33">
         <v>120</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="33">
         <v>309</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="35">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="31" customFormat="1" spans="1:7">
-      <c r="A29" s="31">
+    <row r="29" s="33" customFormat="1" spans="1:7">
+      <c r="A29" s="33">
         <v>312</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="33">
         <v>15</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="33">
         <v>2</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="33">
         <v>15</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="33">
         <v>306</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="35">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="31" customFormat="1" spans="1:7">
-      <c r="B30" s="32"/>
+    <row r="30" s="33" customFormat="1" spans="1:7">
+      <c r="B30" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8402,10 +8529,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="29">
+      <c r="A2" s="31">
         <v>3</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="31" t="s">
         <v>226</v>
       </c>
       <c r="C2">
@@ -8422,10 +8549,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29">
+      <c r="A3" s="31">
         <v>4</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="31" t="s">
         <v>197</v>
       </c>
       <c r="C3">
@@ -8611,10 +8738,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="29">
+      <c r="A12" s="31">
         <v>309</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="31" t="s">
         <v>165</v>
       </c>
       <c r="C12">
@@ -8631,10 +8758,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="29">
+      <c r="A13" s="31">
         <v>310</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="31" t="s">
         <v>170</v>
       </c>
       <c r="C13">
@@ -8651,10 +8778,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="29">
+      <c r="A14" s="31">
         <v>311</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="31" t="s">
         <v>174</v>
       </c>
       <c r="C14">
@@ -8674,10 +8801,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="29">
+      <c r="A15" s="31">
         <v>312</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="31" t="s">
         <v>220</v>
       </c>
       <c r="C15">
@@ -8694,8 +8821,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="29"/>
-      <c r="B16" s="29"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8768,29 +8895,29 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3" s="28" customFormat="1" spans="1:8">
-      <c r="A3" s="28">
+    <row r="3" s="30" customFormat="1" spans="1:8">
+      <c r="A3" s="30">
         <v>202</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="E3" s="28">
-        <v>0</v>
-      </c>
-      <c r="F3" s="28">
+      <c r="E3" s="30">
+        <v>0</v>
+      </c>
+      <c r="F3" s="30">
         <v>0.8</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="30" t="s">
         <v>238</v>
       </c>
     </row>
@@ -9180,34 +9307,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="28" customFormat="1" spans="1:8">
-      <c r="A20" s="30">
+    <row r="20" s="30" customFormat="1" spans="1:8">
+      <c r="A20" s="32">
         <v>404</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="30" t="s">
         <v>237</v>
       </c>
-      <c r="E20" s="28">
-        <v>0</v>
-      </c>
-      <c r="F20" s="28">
+      <c r="E20" s="30">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30">
         <v>0.8</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="G20" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="H20" s="30" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="26">
+      <c r="A21" s="28">
         <v>405</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -9233,7 +9360,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="26">
+      <c r="A22" s="28">
         <v>406</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -9259,7 +9386,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="27">
+      <c r="A23" s="29">
         <v>407</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -9285,7 +9412,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="27">
+      <c r="A24" s="29">
         <v>408</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -9311,7 +9438,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="27">
+      <c r="A25" s="29">
         <v>409</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -9337,7 +9464,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="27">
+      <c r="A26" s="29">
         <v>410</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -9363,7 +9490,7 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="27">
+      <c r="A27" s="29">
         <v>411</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -9429,68 +9556,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="28" customFormat="1" spans="1:21">
-      <c r="A1" s="28" t="s">
+    <row r="1" s="30" customFormat="1" spans="1:21">
+      <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="30" t="s">
         <v>273</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="30" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="30" t="s">
         <v>279</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="L1" s="28" t="s">
+      <c r="L1" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="N1" s="28" t="s">
+      <c r="N1" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="Q1" s="28" t="s">
+      <c r="Q1" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="R1" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="S1" s="30" t="s">
         <v>289</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="T1" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="30" t="s">
         <v>291</v>
       </c>
     </row>
@@ -10362,7 +10489,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="29">
+      <c r="A17" s="31">
         <v>301</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -10421,7 +10548,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="29">
+      <c r="A18" s="31">
         <v>302</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -10480,7 +10607,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="29">
+      <c r="A19" s="31">
         <v>303</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -10539,7 +10666,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="29">
+      <c r="A20" s="31">
         <v>304</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -10660,7 +10787,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="29">
+      <c r="A22" s="31">
         <v>306</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -10719,7 +10846,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="29">
+      <c r="A23" s="31">
         <v>307</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -10778,7 +10905,7 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="29">
+      <c r="A24" s="31">
         <v>308</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -10837,7 +10964,7 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="29">
+      <c r="A25" s="31">
         <v>309</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -10896,7 +11023,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="29">
+      <c r="A26" s="31">
         <v>310</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -10955,7 +11082,7 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="29">
+      <c r="A27" s="31">
         <v>311</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -11014,7 +11141,7 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="29">
+      <c r="A28" s="31">
         <v>312</v>
       </c>
       <c r="B28" s="11" t="s">
@@ -11247,7 +11374,7 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="26">
+      <c r="A32" s="28">
         <v>404</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -11309,7 +11436,7 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="26">
+      <c r="A33" s="28">
         <v>405</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -11365,7 +11492,7 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="26">
+      <c r="A34" s="28">
         <v>406</v>
       </c>
       <c r="B34" s="13" t="s">
@@ -11421,7 +11548,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="27">
+      <c r="A35" s="29">
         <v>407</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -11477,7 +11604,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="27">
+      <c r="A36" s="29">
         <v>408</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -11536,7 +11663,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="27">
+      <c r="A37" s="29">
         <v>409</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -11595,7 +11722,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="27">
+      <c r="A38" s="29">
         <v>410</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -11645,7 +11772,7 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="27">
+      <c r="A39" s="29">
         <v>411</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -11807,7 +11934,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="26">
+      <c r="A9" s="28">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -11818,7 +11945,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="26">
+      <c r="A10" s="28">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -11829,7 +11956,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="26">
+      <c r="A11" s="28">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -11840,7 +11967,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="27">
+      <c r="A12" s="29">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -11851,7 +11978,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="27">
+      <c r="A13" s="29">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -11862,7 +11989,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="27">
+      <c r="A14" s="29">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -11873,7 +12000,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="27">
+      <c r="A15" s="29">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -11884,7 +12011,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="27">
+      <c r="A16" s="29">
         <v>411</v>
       </c>
       <c r="B16" t="s">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="639">
   <si>
     <t>类型</t>
   </si>
@@ -92,7 +92,7 @@
     <t>受击高度</t>
   </si>
   <si>
-    <t>描述</t>
+    <t>描述Key</t>
   </si>
   <si>
     <t>Key特效</t>
@@ -113,7 +113,7 @@
     <t>建筑/方墩</t>
   </si>
   <si>
-    <t>永久阻挡，不会损坏</t>
+    <t>MiaoShu_FangDun</t>
   </si>
   <si>
     <t>Key晶体矿</t>
@@ -155,7 +155,7 @@
     <t>TSCDth00</t>
   </si>
   <si>
-    <t>可采集资源，可建造建筑</t>
+    <t>MiaoShu_GongChengChe</t>
   </si>
   <si>
     <t>Key枪兵</t>
@@ -176,7 +176,7 @@
     <t>TMaDth00</t>
   </si>
   <si>
-    <t>远程攻击</t>
+    <t>MiaoShu_QiangBing</t>
   </si>
   <si>
     <t>Key近战兵</t>
@@ -194,7 +194,7 @@
     <t>TFbDth00</t>
   </si>
   <si>
-    <t>近程攻击</t>
+    <t>MiaoShu_JinZhanBing</t>
   </si>
   <si>
     <t>Key三色坦克</t>
@@ -212,7 +212,7 @@
     <t>音效/TTaDth00</t>
   </si>
   <si>
-    <t>超远距离范围攻击，前摇较长，克制炮台。爆炸溅射可能会伤害己方单位。</t>
+    <t>MiaoShu_SanSeTanKe</t>
   </si>
   <si>
     <t>Key工虫</t>
@@ -233,7 +233,7 @@
     <t>音效/zdrDth00</t>
   </si>
   <si>
-    <t>可采集资源，可变成建筑</t>
+    <t>MiaoShu_GongChong</t>
   </si>
   <si>
     <t>Key飞机</t>
@@ -254,7 +254,7 @@
     <t>slide</t>
   </si>
   <si>
-    <t>可飞越障碍物</t>
+    <t>MiaoShu_FeiJi</t>
   </si>
   <si>
     <t>Key枪虫</t>
@@ -272,6 +272,9 @@
     <t>音效/zhyDth00</t>
   </si>
   <si>
+    <t>MiaoShu_QiangChong</t>
+  </si>
+  <si>
     <t>Key近战虫</t>
   </si>
   <si>
@@ -287,6 +290,9 @@
     <t>音效/ZZeDth00</t>
   </si>
   <si>
+    <t>MiaoShu_JinZhanChong</t>
+  </si>
+  <si>
     <t>Key幼虫</t>
   </si>
   <si>
@@ -308,7 +314,7 @@
     <t>音效/ZLaDth00</t>
   </si>
   <si>
-    <t>可蜕变为其它活动单位</t>
+    <t>MiaoShu_YouChong</t>
   </si>
   <si>
     <t>Key绿色坦克</t>
@@ -323,7 +329,7 @@
     <t>p_B_tank_01</t>
   </si>
   <si>
-    <t>超远距离发射光刺，光刺会遭到障碍物阻挡。</t>
+    <t>MiaoShu_LvSeTanKe</t>
   </si>
   <si>
     <t>Key光刺</t>
@@ -353,7 +359,7 @@
     <t>音效/zovDth00</t>
   </si>
   <si>
-    <t>可增加活动单位上限</t>
+    <t>MiaoShu_FangChong</t>
   </si>
   <si>
     <t>Key飞虫</t>
@@ -371,7 +377,7 @@
     <t>音效/zmuDth00</t>
   </si>
   <si>
-    <t>可飞跃障碍物</t>
+    <t>MiaoShu_FeiChong</t>
   </si>
   <si>
     <t>Key医疗兵</t>
@@ -389,7 +395,7 @@
     <t>语音/TMdDth00</t>
   </si>
   <si>
-    <t>可给友方单位恢复HP</t>
+    <t>MiaoShu_YiLiaoBing</t>
   </si>
   <si>
     <t>Key防空兵</t>
@@ -401,7 +407,7 @@
     <t>p_C_rpg_02</t>
   </si>
   <si>
-    <t>远程对空范围攻击，爆炸溅射会伤害己方单位，不可对地攻击</t>
+    <t>MiaoShu_FangKongBing</t>
   </si>
   <si>
     <t>Key基地</t>
@@ -419,7 +425,7 @@
     <t>explo4</t>
   </si>
   <si>
-    <t>可产出工程车</t>
+    <t>MiaoShu_JiDi</t>
   </si>
   <si>
     <t>Key兵营</t>
@@ -440,7 +446,7 @@
     <t>EXPLOMED</t>
   </si>
   <si>
-    <t>可产出枪兵和近战兵</t>
+    <t>MiaoShu_BingYing</t>
   </si>
   <si>
     <t>Key民房</t>
@@ -449,6 +455,9 @@
     <t>建筑/民房</t>
   </si>
   <si>
+    <t>MiaoShu_MinFang</t>
+  </si>
+  <si>
     <t>Key地堡</t>
   </si>
   <si>
@@ -458,7 +467,7 @@
     <t>地堡872面</t>
   </si>
   <si>
-    <t>高HP，可派遣步兵进入地堡</t>
+    <t>MiaoShu_DiBao</t>
   </si>
   <si>
     <t>Key炮台</t>
@@ -476,7 +485,7 @@
     <t>音效/explo1</t>
   </si>
   <si>
-    <t>克制除了坦克以外的一切单位</t>
+    <t>MiaoShu_PaoTai</t>
   </si>
   <si>
     <t>Key虫巢</t>
@@ -494,7 +503,7 @@
     <t>音效/ZBldgDth</t>
   </si>
   <si>
-    <t>可产出幼虫</t>
+    <t>MiaoShu_ChongChao</t>
   </si>
   <si>
     <t>Key机场</t>
@@ -509,7 +518,7 @@
     <t>Take 001</t>
   </si>
   <si>
-    <t>可产出飞机</t>
+    <t>MiaoShu_JiChang</t>
   </si>
   <si>
     <t>Key重车厂</t>
@@ -524,7 +533,7 @@
     <t>重车厂Idle</t>
   </si>
   <si>
-    <t>可产出三色坦克</t>
+    <t>MiaoShu_ZhongCheChang</t>
   </si>
   <si>
     <t>Key虫营</t>
@@ -539,7 +548,7 @@
     <t>虫营</t>
   </si>
   <si>
-    <t>近战虫和枪虫的前置建筑，只需1个就够了</t>
+    <t>MiaoShu_ChongYing</t>
   </si>
   <si>
     <t>Key飞塔</t>
@@ -554,7 +563,7 @@
     <t>飞塔</t>
   </si>
   <si>
-    <t>飞虫的前置建筑，只需1个就够了</t>
+    <t>MiaoShu_FeiTa</t>
   </si>
   <si>
     <t>Key拟态源</t>
@@ -566,7 +575,7 @@
     <t>拟态源</t>
   </si>
   <si>
-    <t>绿色坦克的前置建筑，只需1个就够了</t>
+    <t>MiaoShu_NiTaiYuan</t>
   </si>
   <si>
     <t>Key太岁</t>
@@ -575,7 +584,7 @@
     <t>建筑/太岁</t>
   </si>
   <si>
-    <t>可扩张苔蔓(wàn)，扩张完成后可分裂另一个太岁</t>
+    <t>MiaoShu_TaiSui</t>
   </si>
   <si>
     <t>Key枪虫怪</t>
@@ -2244,6 +2253,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>Key</t>
     </r>
     <r>
@@ -2262,7 +2277,7 @@
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
-      <t>{0}</t>
+      <t>{}</t>
     </r>
     <r>
       <rPr>
@@ -2291,7 +2306,7 @@
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
-      <t>{0}</t>
+      <t>{}</t>
     </r>
     <r>
       <rPr>
@@ -2304,7 +2319,7 @@
     </r>
   </si>
   <si>
-    <t>{0} units inside</t>
+    <t>{} units inside</t>
   </si>
   <si>
     <r>
@@ -2340,6 +2355,24 @@
   </si>
   <si>
     <t>Ready to Fire</t>
+  </si>
+  <si>
+    <t>Key强行走向目标位置</t>
+  </si>
+  <si>
+    <t>强行走向目标位置</t>
+  </si>
+  <si>
+    <t>Force move to target location</t>
+  </si>
+  <si>
+    <t>Key没有空闲的工程车或工虫</t>
+  </si>
+  <si>
+    <t>没有空闲的工程车或工虫</t>
+  </si>
+  <si>
+    <t>No idle Construction Vehicles or Worker Larvae</t>
   </si>
 </sst>
 </file>
@@ -2435,6 +2468,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -2455,13 +2495,6 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2942,10 +2975,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -3133,39 +3166,42 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -3181,9 +3217,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3573,20 +3606,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="36" customFormat="1" spans="1:18">
-      <c r="A2" s="36">
+    <row r="2" s="37" customFormat="1" spans="1:18">
+      <c r="A2" s="37">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="36">
-        <v>0</v>
-      </c>
-      <c r="G2" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="36">
+      <c r="C2" s="37">
+        <v>0</v>
+      </c>
+      <c r="G2" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="37">
         <v>1</v>
       </c>
       <c r="J2">
@@ -3595,33 +3628,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="36">
-        <v>1</v>
-      </c>
-      <c r="N2" s="36">
-        <v>0</v>
-      </c>
-      <c r="O2" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="36" customFormat="1" spans="1:18">
-      <c r="A3" s="36">
+      <c r="M2" s="37">
+        <v>1</v>
+      </c>
+      <c r="N2" s="37">
+        <v>0</v>
+      </c>
+      <c r="O2" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="37" customFormat="1" spans="1:18">
+      <c r="A3" s="37">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="36">
-        <v>0</v>
-      </c>
-      <c r="G3" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="36">
+      <c r="C3" s="37">
+        <v>0</v>
+      </c>
+      <c r="G3" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="37">
         <v>1</v>
       </c>
       <c r="J3">
@@ -3630,36 +3663,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="36">
-        <v>1</v>
-      </c>
-      <c r="N3" s="36">
-        <v>0</v>
-      </c>
-      <c r="O3" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="31" customFormat="1" spans="1:18">
-      <c r="A4" s="31">
+      <c r="M3" s="37">
+        <v>1</v>
+      </c>
+      <c r="N3" s="37">
+        <v>0</v>
+      </c>
+      <c r="O3" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="32" customFormat="1" spans="1:18">
+      <c r="A4" s="32">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>2</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D4" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="36">
+      <c r="G4" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="37">
         <v>1</v>
       </c>
       <c r="J4">
@@ -3668,36 +3701,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="36">
-        <v>1</v>
-      </c>
-      <c r="N4" s="36">
-        <v>0</v>
-      </c>
-      <c r="O4" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="31" customFormat="1" spans="1:18">
-      <c r="A5" s="31">
+      <c r="M4" s="37">
+        <v>1</v>
+      </c>
+      <c r="N4" s="37">
+        <v>0</v>
+      </c>
+      <c r="O4" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A5" s="32">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="31">
-        <v>0</v>
-      </c>
-      <c r="D5" s="31" t="s">
+      <c r="C5" s="32">
+        <v>0</v>
+      </c>
+      <c r="D5" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="36">
+      <c r="G5" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="37">
         <v>1</v>
       </c>
       <c r="J5">
@@ -3706,48 +3739,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="36">
-        <v>1</v>
-      </c>
-      <c r="N5" s="36">
-        <v>0</v>
-      </c>
-      <c r="O5" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="31">
-        <v>0</v>
-      </c>
-      <c r="R5" s="31" t="s">
+      <c r="M5" s="37">
+        <v>1</v>
+      </c>
+      <c r="N5" s="37">
+        <v>0</v>
+      </c>
+      <c r="O5" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="32">
+        <v>0</v>
+      </c>
+      <c r="R5" s="23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="37" customFormat="1" spans="1:18">
-      <c r="A6" s="37">
+    <row r="6" s="38" customFormat="1" spans="1:18">
+      <c r="A6" s="38">
         <v>101</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="37">
-        <v>0</v>
-      </c>
-      <c r="D6" s="37" t="s">
+      <c r="C6" s="38">
+        <v>0</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="36" t="b">
+      <c r="G6" s="37" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="37">
         <v>1</v>
       </c>
       <c r="J6">
@@ -3759,39 +3792,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="36">
-        <v>1</v>
-      </c>
-      <c r="N6" s="36">
-        <v>0</v>
-      </c>
-      <c r="O6" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="37" customFormat="1" spans="1:18">
-      <c r="A7" s="37">
+      <c r="M6" s="37">
+        <v>1</v>
+      </c>
+      <c r="N6" s="37">
+        <v>0</v>
+      </c>
+      <c r="O6" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="38" customFormat="1" spans="1:18">
+      <c r="A7" s="38">
         <v>102</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="37">
-        <v>0</v>
-      </c>
-      <c r="D7" s="37" t="s">
+      <c r="C7" s="38">
+        <v>0</v>
+      </c>
+      <c r="D7" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="36">
+      <c r="G7" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="37">
         <v>1</v>
       </c>
       <c r="J7">
@@ -3800,20 +3833,20 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="36">
-        <v>1</v>
-      </c>
-      <c r="N7" s="36">
-        <v>0</v>
-      </c>
-      <c r="O7" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="M7" s="37">
+        <v>1</v>
+      </c>
+      <c r="N7" s="37">
+        <v>0</v>
+      </c>
+      <c r="O7" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" spans="1:18">
       <c r="A8">
         <v>201</v>
       </c>
@@ -3832,13 +3865,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="36" t="b">
+      <c r="G8" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="37">
         <v>1</v>
       </c>
       <c r="J8">
@@ -3850,13 +3883,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="36">
-        <v>1</v>
-      </c>
-      <c r="N8" s="36">
-        <v>0</v>
-      </c>
-      <c r="O8" s="36">
+      <c r="M8" s="37">
+        <v>1</v>
+      </c>
+      <c r="N8" s="37">
+        <v>0</v>
+      </c>
+      <c r="O8" s="37">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -3865,67 +3898,67 @@
       <c r="Q8">
         <v>3</v>
       </c>
-      <c r="R8" t="s">
+      <c r="R8" s="23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="30" customFormat="1" spans="1:18">
-      <c r="A9" s="30">
+    <row r="9" s="31" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A9" s="31">
         <v>202</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="30">
-        <v>1</v>
-      </c>
-      <c r="D9" s="30" t="s">
+      <c r="C9" s="31">
+        <v>1</v>
+      </c>
+      <c r="D9" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="30" t="s">
+      <c r="F9" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="30" t="s">
+      <c r="G9" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="38">
-        <v>1</v>
-      </c>
-      <c r="J9" s="30">
-        <v>0</v>
-      </c>
-      <c r="K9" s="30">
+      <c r="I9" s="21">
+        <v>1</v>
+      </c>
+      <c r="J9" s="31">
+        <v>0</v>
+      </c>
+      <c r="K9" s="31">
         <v>2</v>
       </c>
-      <c r="L9" s="30" t="s">
+      <c r="L9" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="38">
-        <v>1</v>
-      </c>
-      <c r="N9" s="38">
-        <v>0</v>
-      </c>
-      <c r="O9" s="38">
-        <v>0</v>
-      </c>
-      <c r="P9" s="30" t="s">
+      <c r="M9" s="21">
+        <v>1</v>
+      </c>
+      <c r="N9" s="21">
+        <v>0</v>
+      </c>
+      <c r="O9" s="21">
+        <v>0</v>
+      </c>
+      <c r="P9" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="30">
+      <c r="Q9" s="31">
         <v>3</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="R9" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" ht="14.25" spans="1:18">
       <c r="A10">
         <v>203</v>
       </c>
@@ -3944,13 +3977,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="36" t="b">
+      <c r="G10" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="36">
+      <c r="I10" s="37">
         <v>1</v>
       </c>
       <c r="J10">
@@ -3962,13 +3995,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="36">
-        <v>1</v>
-      </c>
-      <c r="N10" s="36">
-        <v>0</v>
-      </c>
-      <c r="O10" s="36">
+      <c r="M10" s="37">
+        <v>1</v>
+      </c>
+      <c r="N10" s="37">
+        <v>0</v>
+      </c>
+      <c r="O10" s="37">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -3977,11 +4010,11 @@
       <c r="Q10">
         <v>3</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" ht="14.25" spans="1:18">
       <c r="A11">
         <v>204</v>
       </c>
@@ -3997,13 +4030,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="36" t="b">
+      <c r="G11" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="36">
+      <c r="I11" s="37">
         <v>1</v>
       </c>
       <c r="J11">
@@ -4015,13 +4048,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="36">
-        <v>1</v>
-      </c>
-      <c r="N11" s="36">
-        <v>0</v>
-      </c>
-      <c r="O11" s="36">
+      <c r="M11" s="37">
+        <v>1</v>
+      </c>
+      <c r="N11" s="37">
+        <v>0</v>
+      </c>
+      <c r="O11" s="37">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -4030,11 +4063,11 @@
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" t="s">
+      <c r="R11" s="23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" ht="14.25" spans="1:18">
       <c r="A12">
         <v>205</v>
       </c>
@@ -4053,13 +4086,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="36" t="b">
+      <c r="G12" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="37">
         <v>1</v>
       </c>
       <c r="J12">
@@ -4071,13 +4104,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="36">
-        <v>1</v>
-      </c>
-      <c r="N12" s="36">
-        <v>0</v>
-      </c>
-      <c r="O12" s="36">
+      <c r="M12" s="37">
+        <v>1</v>
+      </c>
+      <c r="N12" s="37">
+        <v>0</v>
+      </c>
+      <c r="O12" s="37">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -4086,7 +4119,7 @@
       <c r="Q12">
         <v>2</v>
       </c>
-      <c r="R12" t="s">
+      <c r="R12" s="23" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4109,13 +4142,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="36" t="b">
+      <c r="G13" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="36">
+      <c r="I13" s="37">
         <v>1</v>
       </c>
       <c r="J13">
@@ -4127,13 +4160,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="36">
-        <v>1</v>
-      </c>
-      <c r="N13" s="36">
-        <v>1</v>
-      </c>
-      <c r="O13" s="36">
+      <c r="M13" s="37">
+        <v>1</v>
+      </c>
+      <c r="N13" s="37">
+        <v>1</v>
+      </c>
+      <c r="O13" s="37">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -4142,11 +4175,11 @@
       <c r="Q13">
         <v>5</v>
       </c>
-      <c r="R13" t="s">
+      <c r="R13" s="23" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" ht="14.25" spans="1:18">
       <c r="A14">
         <v>207</v>
       </c>
@@ -4165,13 +4198,13 @@
       <c r="F14" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="36" t="b">
+      <c r="G14" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="36">
+      <c r="I14" s="37">
         <v>1</v>
       </c>
       <c r="J14">
@@ -4183,13 +4216,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="36">
-        <v>1</v>
-      </c>
-      <c r="N14" s="36">
-        <v>0</v>
-      </c>
-      <c r="O14" s="36">
+      <c r="M14" s="37">
+        <v>1</v>
+      </c>
+      <c r="N14" s="37">
+        <v>0</v>
+      </c>
+      <c r="O14" s="37">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -4198,36 +4231,36 @@
       <c r="Q14">
         <v>2</v>
       </c>
-      <c r="R14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="R14" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:18">
       <c r="A15">
         <v>208</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="G15" s="36" t="b">
+        <v>81</v>
+      </c>
+      <c r="G15" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="36">
+      <c r="I15" s="37">
         <v>1</v>
       </c>
       <c r="J15">
@@ -4239,51 +4272,51 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="36">
-        <v>1</v>
-      </c>
-      <c r="N15" s="36">
-        <v>0</v>
-      </c>
-      <c r="O15" s="36">
+      <c r="M15" s="37">
+        <v>1</v>
+      </c>
+      <c r="N15" s="37">
+        <v>0</v>
+      </c>
+      <c r="O15" s="37">
         <v>0</v>
       </c>
       <c r="P15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q15">
         <v>2</v>
       </c>
-      <c r="R15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+      <c r="R15" s="23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:18">
       <c r="A16">
         <v>209</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
-      </c>
-      <c r="G16" s="36" t="b">
+        <v>87</v>
+      </c>
+      <c r="G16" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>86</v>
-      </c>
-      <c r="I16" s="36">
+        <v>88</v>
+      </c>
+      <c r="I16" s="37">
         <v>1</v>
       </c>
       <c r="J16">
@@ -4293,53 +4326,53 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>87</v>
-      </c>
-      <c r="M16" s="36">
-        <v>1</v>
-      </c>
-      <c r="N16" s="36">
-        <v>0</v>
-      </c>
-      <c r="O16" s="36">
+        <v>89</v>
+      </c>
+      <c r="M16" s="37">
+        <v>1</v>
+      </c>
+      <c r="N16" s="37">
+        <v>0</v>
+      </c>
+      <c r="O16" s="37">
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q16">
         <v>1</v>
       </c>
-      <c r="R16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+      <c r="R16" s="23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="1:18">
       <c r="A17">
         <v>210</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G17" s="36" t="b">
+        <v>95</v>
+      </c>
+      <c r="G17" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="36">
+      <c r="I17" s="37">
         <v>1</v>
       </c>
       <c r="J17">
@@ -4351,23 +4384,23 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="36">
-        <v>1</v>
-      </c>
-      <c r="N17" s="36">
-        <v>0</v>
-      </c>
-      <c r="O17" s="36">
+      <c r="M17" s="37">
+        <v>1</v>
+      </c>
+      <c r="N17" s="37">
+        <v>0</v>
+      </c>
+      <c r="O17" s="37">
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q17">
         <v>2</v>
       </c>
-      <c r="R17" t="s">
-        <v>94</v>
+      <c r="R17" s="23" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -4375,18 +4408,18 @@
         <v>211</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="36">
+        <v>98</v>
+      </c>
+      <c r="G18" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="37">
         <v>1</v>
       </c>
       <c r="J18">
@@ -4395,45 +4428,45 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="36">
-        <v>1</v>
-      </c>
-      <c r="N18" s="36">
-        <v>0</v>
-      </c>
-      <c r="O18" s="36">
+      <c r="M18" s="37">
+        <v>1</v>
+      </c>
+      <c r="N18" s="37">
+        <v>0</v>
+      </c>
+      <c r="O18" s="37">
         <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" ht="14.25" spans="1:18">
       <c r="A19">
         <v>212</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G19" s="36" t="b">
+        <v>102</v>
+      </c>
+      <c r="G19" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="36">
+        <v>103</v>
+      </c>
+      <c r="I19" s="37">
         <v>1</v>
       </c>
       <c r="J19">
@@ -4443,53 +4476,53 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>102</v>
-      </c>
-      <c r="M19" s="36">
-        <v>1</v>
-      </c>
-      <c r="N19" s="36">
-        <v>0</v>
-      </c>
-      <c r="O19" s="36">
+        <v>104</v>
+      </c>
+      <c r="M19" s="37">
+        <v>1</v>
+      </c>
+      <c r="N19" s="37">
+        <v>0</v>
+      </c>
+      <c r="O19" s="37">
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q19">
         <v>4</v>
       </c>
-      <c r="R19" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+      <c r="R19" s="23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" ht="14.25" spans="1:18">
       <c r="A20">
         <v>213</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="36" t="b">
+        <v>110</v>
+      </c>
+      <c r="G20" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" s="36">
+        <v>103</v>
+      </c>
+      <c r="I20" s="37">
         <v>1</v>
       </c>
       <c r="J20">
@@ -4499,53 +4532,53 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>102</v>
-      </c>
-      <c r="M20" s="36">
-        <v>1</v>
-      </c>
-      <c r="N20" s="36">
-        <v>0</v>
-      </c>
-      <c r="O20" s="36">
+        <v>104</v>
+      </c>
+      <c r="M20" s="37">
+        <v>1</v>
+      </c>
+      <c r="N20" s="37">
+        <v>0</v>
+      </c>
+      <c r="O20" s="37">
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q20">
         <v>4</v>
       </c>
-      <c r="R20" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="21" customFormat="1" spans="1:18">
+      <c r="R20" s="23" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="14.25" spans="1:18">
       <c r="A21">
         <v>214</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F21" t="s">
-        <v>114</v>
-      </c>
-      <c r="G21" s="36" t="b">
+        <v>116</v>
+      </c>
+      <c r="G21" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="36">
+      <c r="I21" s="37">
         <v>1</v>
       </c>
       <c r="J21">
@@ -4557,51 +4590,51 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="36">
-        <v>1</v>
-      </c>
-      <c r="N21" s="36">
-        <v>0</v>
-      </c>
-      <c r="O21" s="36">
+      <c r="M21" s="37">
+        <v>1</v>
+      </c>
+      <c r="N21" s="37">
+        <v>0</v>
+      </c>
+      <c r="O21" s="37">
         <v>0</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q21">
         <v>3</v>
       </c>
-      <c r="R21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:18">
+      <c r="R21" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="14.25" spans="1:18">
       <c r="A22">
         <v>215</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>119</v>
-      </c>
-      <c r="G22" s="36" t="b">
+        <v>121</v>
+      </c>
+      <c r="G22" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="36">
+      <c r="I22" s="37">
         <v>1</v>
       </c>
       <c r="J22">
@@ -4613,13 +4646,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="36">
-        <v>1</v>
-      </c>
-      <c r="N22" s="36">
-        <v>0</v>
-      </c>
-      <c r="O22" s="36">
+      <c r="M22" s="37">
+        <v>1</v>
+      </c>
+      <c r="N22" s="37">
+        <v>0</v>
+      </c>
+      <c r="O22" s="37">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -4628,36 +4661,36 @@
       <c r="Q22">
         <v>3</v>
       </c>
-      <c r="R22" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="23" s="31" customFormat="1" spans="1:18">
-      <c r="A23" s="31">
+      <c r="R22" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A23" s="32">
         <v>301</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="31">
-        <v>1</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="E23" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="32">
+        <v>1</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="G23" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="31" t="s">
+      <c r="F23" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="G23" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="36">
+      <c r="I23" s="37">
         <v>1</v>
       </c>
       <c r="J23">
@@ -4666,54 +4699,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="M23" s="36">
-        <v>1</v>
-      </c>
-      <c r="N23" s="36">
-        <v>0</v>
-      </c>
-      <c r="O23" s="36">
-        <v>0</v>
-      </c>
-      <c r="P23" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q23" s="31">
+      <c r="L23" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="M23" s="37">
+        <v>1</v>
+      </c>
+      <c r="N23" s="37">
+        <v>0</v>
+      </c>
+      <c r="O23" s="37">
+        <v>0</v>
+      </c>
+      <c r="P23" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q23" s="32">
         <v>3</v>
       </c>
-      <c r="R23" s="31" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="24" s="31" customFormat="1" spans="1:18">
-      <c r="A24" s="31">
+      <c r="R23" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A24" s="32">
         <v>302</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="31">
-        <v>1</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="E24" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="32">
+        <v>1</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="I24" s="36">
+      <c r="F24" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" s="37">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -4722,160 +4755,160 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="M24" s="36">
-        <v>1</v>
-      </c>
-      <c r="N24" s="36">
-        <v>0</v>
-      </c>
-      <c r="O24" s="36">
-        <v>0</v>
-      </c>
-      <c r="P24" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q24" s="31">
+      <c r="L24" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="M24" s="37">
+        <v>1</v>
+      </c>
+      <c r="N24" s="37">
+        <v>0</v>
+      </c>
+      <c r="O24" s="37">
+        <v>0</v>
+      </c>
+      <c r="P24" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q24" s="32">
         <v>3</v>
       </c>
-      <c r="R24" s="31" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" s="31" customFormat="1" spans="1:18">
-      <c r="A25" s="31">
+      <c r="R24" s="23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A25" s="32">
         <v>303</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="32">
+        <v>1</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="37">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="M25" s="37">
+        <v>1</v>
+      </c>
+      <c r="N25" s="37">
+        <v>0</v>
+      </c>
+      <c r="O25" s="37">
+        <v>0</v>
+      </c>
+      <c r="P25" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C25" s="31">
-        <v>1</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="31" t="s">
+      <c r="Q25" s="32">
+        <v>3</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A26" s="32">
+        <v>304</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C26" s="32">
+        <v>1</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="31" t="s">
+      <c r="F26" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="G26" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="36">
-        <v>1</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="M25" s="36">
-        <v>1</v>
-      </c>
-      <c r="N25" s="36">
-        <v>0</v>
-      </c>
-      <c r="O25" s="36">
-        <v>0</v>
-      </c>
-      <c r="P25" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q25" s="31">
+      <c r="I26" s="37">
+        <v>0.05</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="M26" s="37">
+        <v>1</v>
+      </c>
+      <c r="N26" s="37">
+        <v>0</v>
+      </c>
+      <c r="O26" s="37">
+        <v>0</v>
+      </c>
+      <c r="P26" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q26" s="32">
         <v>3</v>
       </c>
-      <c r="R25" s="31" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="26" s="31" customFormat="1" spans="1:18">
-      <c r="A26" s="31">
-        <v>304</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="31">
-        <v>1</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" s="31" t="s">
+      <c r="R26" s="23" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A27" s="32">
+        <v>305</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="32">
+        <v>3</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G26" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="I26" s="36">
-        <v>0.05</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="M26" s="36">
-        <v>1</v>
-      </c>
-      <c r="N26" s="36">
-        <v>0</v>
-      </c>
-      <c r="O26" s="36">
-        <v>0</v>
-      </c>
-      <c r="P26" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q26" s="31">
-        <v>3</v>
-      </c>
-      <c r="R26" s="31" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" s="31" customFormat="1" spans="1:18">
-      <c r="A27" s="31">
-        <v>305</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" s="31">
-        <v>3</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="G27" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="I27" s="36">
+      <c r="F27" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="37">
         <v>1</v>
       </c>
       <c r="J27">
@@ -4887,51 +4920,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="36">
-        <v>1</v>
-      </c>
-      <c r="N27" s="36">
-        <v>0</v>
-      </c>
-      <c r="O27" s="36">
-        <v>0</v>
-      </c>
-      <c r="P27" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q27" s="31">
+      <c r="M27" s="37">
+        <v>1</v>
+      </c>
+      <c r="N27" s="37">
+        <v>0</v>
+      </c>
+      <c r="O27" s="37">
+        <v>0</v>
+      </c>
+      <c r="P27" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q27" s="32">
         <v>3</v>
       </c>
-      <c r="R27" s="31" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="28" s="31" customFormat="1" spans="1:18">
-      <c r="A28" s="31">
+      <c r="R27" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A28" s="32">
         <v>306</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="31">
+        <v>149</v>
+      </c>
+      <c r="C28" s="32">
         <v>2</v>
       </c>
-      <c r="D28" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="31">
-        <v>0</v>
-      </c>
-      <c r="I28" s="36">
+      <c r="D28" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="G28" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="32">
+        <v>0</v>
+      </c>
+      <c r="I28" s="37">
         <v>1</v>
       </c>
       <c r="J28">
@@ -4940,54 +4973,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="31">
-        <v>1</v>
-      </c>
-      <c r="M28" s="36">
-        <v>1</v>
-      </c>
-      <c r="N28" s="36">
-        <v>0</v>
-      </c>
-      <c r="O28" s="36">
-        <v>0</v>
-      </c>
-      <c r="P28" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q28" s="31">
+      <c r="L28" s="32">
+        <v>1</v>
+      </c>
+      <c r="M28" s="37">
+        <v>1</v>
+      </c>
+      <c r="N28" s="37">
+        <v>0</v>
+      </c>
+      <c r="O28" s="37">
+        <v>0</v>
+      </c>
+      <c r="P28" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q28" s="32">
         <v>3</v>
       </c>
-      <c r="R28" s="31" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="29" s="31" customFormat="1" spans="1:18">
-      <c r="A29" s="31">
+      <c r="R28" s="23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A29" s="32">
         <v>307</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="C29" s="31">
-        <v>1</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="32">
+        <v>1</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E29" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="I29" s="36">
+      <c r="F29" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="G29" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="37">
         <v>1</v>
       </c>
       <c r="J29">
@@ -4996,110 +5029,110 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="M29" s="36">
+      <c r="L29" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="M29" s="37">
         <v>0.1</v>
       </c>
-      <c r="N29" s="36">
-        <v>0</v>
-      </c>
-      <c r="O29" s="36">
+      <c r="N29" s="37">
+        <v>0</v>
+      </c>
+      <c r="O29" s="37">
         <v>0.17</v>
       </c>
-      <c r="P29" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q29" s="31">
+      <c r="P29" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q29" s="32">
         <v>3</v>
       </c>
-      <c r="R29" s="31" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" s="31" customFormat="1" spans="1:18">
-      <c r="A30" s="31">
+      <c r="R29" s="23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A30" s="32">
         <v>308</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C30" s="31">
-        <v>1</v>
-      </c>
-      <c r="D30" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C30" s="32">
+        <v>1</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="G30" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="I30" s="37">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+      <c r="L30" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="G30" s="36" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="I30" s="36">
-        <v>1</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="M30" s="36">
-        <v>1</v>
-      </c>
-      <c r="N30" s="36">
-        <v>0</v>
-      </c>
-      <c r="O30" s="36">
-        <v>0</v>
-      </c>
-      <c r="P30" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="Q30" s="31">
+      <c r="M30" s="37">
+        <v>1</v>
+      </c>
+      <c r="N30" s="37">
+        <v>0</v>
+      </c>
+      <c r="O30" s="37">
+        <v>0</v>
+      </c>
+      <c r="P30" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q30" s="32">
         <v>3</v>
       </c>
-      <c r="R30" s="31" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="31" s="31" customFormat="1" spans="1:18">
-      <c r="A31" s="31">
+      <c r="R30" s="23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A31" s="32">
         <v>309</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C31" s="31">
+        <v>165</v>
+      </c>
+      <c r="C31" s="32">
         <v>2</v>
       </c>
-      <c r="D31" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G31" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="I31" s="36">
+      <c r="D31" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="E31" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="G31" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="I31" s="37">
         <v>1</v>
       </c>
       <c r="J31">
@@ -5108,54 +5141,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="M31" s="36">
-        <v>1</v>
-      </c>
-      <c r="N31" s="36">
-        <v>0</v>
-      </c>
-      <c r="O31" s="36">
-        <v>0</v>
-      </c>
-      <c r="P31" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q31" s="31">
+      <c r="L31" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="37">
+        <v>1</v>
+      </c>
+      <c r="N31" s="37">
+        <v>0</v>
+      </c>
+      <c r="O31" s="37">
+        <v>0</v>
+      </c>
+      <c r="P31" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q31" s="32">
         <v>3</v>
       </c>
-      <c r="R31" s="31" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="32" s="31" customFormat="1" spans="1:18">
-      <c r="A32" s="31">
+      <c r="R31" s="23" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A32" s="32">
         <v>310</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="C32" s="31">
+        <v>170</v>
+      </c>
+      <c r="C32" s="32">
         <v>2</v>
       </c>
-      <c r="D32" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="E32" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="G32" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="I32" s="36">
+      <c r="D32" s="32" t="s">
+        <v>171</v>
+      </c>
+      <c r="E32" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="G32" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="I32" s="37">
         <v>1</v>
       </c>
       <c r="J32">
@@ -5164,148 +5197,148 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="M32" s="36">
-        <v>1</v>
-      </c>
-      <c r="N32" s="36">
-        <v>0</v>
-      </c>
-      <c r="O32" s="36">
-        <v>0</v>
-      </c>
-      <c r="P32" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q32" s="31">
+      <c r="L32" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="M32" s="37">
+        <v>1</v>
+      </c>
+      <c r="N32" s="37">
+        <v>0</v>
+      </c>
+      <c r="O32" s="37">
+        <v>0</v>
+      </c>
+      <c r="P32" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q32" s="32">
         <v>4</v>
       </c>
-      <c r="R32" s="31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="33" s="31" customFormat="1" spans="1:21">
-      <c r="A33" s="31">
+      <c r="R32" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="33" s="32" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A33" s="32">
         <v>311</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="32">
+        <v>2</v>
+      </c>
+      <c r="D33" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="C33" s="31">
+      <c r="F33" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="G33" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="32">
+        <v>0</v>
+      </c>
+      <c r="I33" s="37">
+        <v>1</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33" s="32">
+        <v>1</v>
+      </c>
+      <c r="M33" s="37">
+        <v>1</v>
+      </c>
+      <c r="N33" s="37">
+        <v>0</v>
+      </c>
+      <c r="O33" s="37">
+        <v>0</v>
+      </c>
+      <c r="P33" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q33" s="32">
+        <v>3</v>
+      </c>
+      <c r="R33" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" s="32" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A34" s="32">
+        <v>312</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" s="32">
         <v>2</v>
       </c>
-      <c r="D33" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="E33" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="G33" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="31">
-        <v>0</v>
-      </c>
-      <c r="I33" s="36">
-        <v>1</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33" s="31">
-        <v>1</v>
-      </c>
-      <c r="M33" s="36">
-        <v>1</v>
-      </c>
-      <c r="N33" s="36">
-        <v>0</v>
-      </c>
-      <c r="O33" s="36">
-        <v>0</v>
-      </c>
-      <c r="P33" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q33" s="31">
-        <v>3</v>
-      </c>
-      <c r="R33" s="31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" s="31" customFormat="1" spans="1:21">
-      <c r="A34" s="31">
-        <v>312</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C34" s="31">
+      <c r="D34" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="37">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="37">
+        <v>1</v>
+      </c>
+      <c r="N34" s="37">
+        <v>0</v>
+      </c>
+      <c r="O34" s="37">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="32">
+        <v>1</v>
+      </c>
+      <c r="R34" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="35" s="20" customFormat="1" spans="1:21">
+      <c r="A35" s="20">
+        <v>401</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C35" s="20">
         <v>2</v>
       </c>
-      <c r="D34" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="36">
-        <v>1</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="M34" s="36">
-        <v>1</v>
-      </c>
-      <c r="N34" s="36">
-        <v>0</v>
-      </c>
-      <c r="O34" s="36">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="31">
-        <v>1</v>
-      </c>
-      <c r="R34" s="31" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="35" s="29" customFormat="1" spans="1:21">
-      <c r="A35" s="29">
-        <v>401</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="C35" s="29">
-        <v>2</v>
-      </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="20" t="s">
         <v>73</v>
       </c>
       <c r="F35" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="29" t="s">
+      <c r="G35" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>1</v>
       </c>
       <c r="J35">
@@ -5317,45 +5350,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="36">
-        <v>1</v>
-      </c>
-      <c r="N35" s="36">
-        <v>0</v>
-      </c>
-      <c r="O35" s="36">
-        <v>0</v>
-      </c>
-      <c r="P35" s="29" t="s">
+      <c r="M35" s="37">
+        <v>1</v>
+      </c>
+      <c r="N35" s="37">
+        <v>0</v>
+      </c>
+      <c r="O35" s="37">
+        <v>0</v>
+      </c>
+      <c r="P35" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="29">
+      <c r="Q35" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="29" customFormat="1" spans="1:21">
-      <c r="A36" s="29">
+    <row r="36" s="20" customFormat="1" spans="1:21">
+      <c r="A36" s="20">
         <v>402</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="C36" s="29">
+        <v>183</v>
+      </c>
+      <c r="C36" s="20">
         <v>2</v>
       </c>
-      <c r="D36" s="29" t="s">
-        <v>78</v>
+      <c r="D36" s="20" t="s">
+        <v>79</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="G36" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="G36" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>1</v>
       </c>
       <c r="J36">
@@ -5367,48 +5400,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="36">
-        <v>1</v>
-      </c>
-      <c r="N36" s="36">
-        <v>0</v>
-      </c>
-      <c r="O36" s="36">
-        <v>0</v>
-      </c>
-      <c r="P36" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q36" s="29">
+      <c r="M36" s="37">
+        <v>1</v>
+      </c>
+      <c r="N36" s="37">
+        <v>0</v>
+      </c>
+      <c r="O36" s="37">
+        <v>0</v>
+      </c>
+      <c r="P36" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q36" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="29" customFormat="1" spans="1:21">
-      <c r="A37" s="29">
+    <row r="37" s="20" customFormat="1" spans="1:21">
+      <c r="A37" s="20">
         <v>403</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>181</v>
-      </c>
-      <c r="C37" s="29">
+        <v>184</v>
+      </c>
+      <c r="C37" s="20">
         <v>2</v>
       </c>
-      <c r="D37" s="29" t="s">
+      <c r="D37" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="F37" s="29" t="s">
+      <c r="E37" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="29" t="s">
+      <c r="G37" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="36">
+      <c r="I37" s="37">
         <v>1</v>
       </c>
       <c r="J37">
@@ -5417,84 +5450,84 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="29" t="s">
+      <c r="L37" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="36">
-        <v>1</v>
-      </c>
-      <c r="N37" s="36">
-        <v>0</v>
-      </c>
-      <c r="O37" s="36">
-        <v>0</v>
-      </c>
-      <c r="P37" s="29" t="s">
+      <c r="M37" s="37">
+        <v>1</v>
+      </c>
+      <c r="N37" s="37">
+        <v>0</v>
+      </c>
+      <c r="O37" s="37">
+        <v>0</v>
+      </c>
+      <c r="P37" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="29">
+      <c r="Q37" s="20">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="38" customFormat="1" spans="1:21">
-      <c r="A38" s="38">
+    <row r="38" s="21" customFormat="1" spans="1:21">
+      <c r="A38" s="21">
         <v>404</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C38" s="38">
-        <v>1</v>
-      </c>
-      <c r="D38" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="21">
+        <v>1</v>
+      </c>
+      <c r="D38" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="38" t="s">
+      <c r="E38" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="30" t="s">
+      <c r="F38" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="38" t="s">
+      <c r="G38" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="38">
-        <v>1</v>
-      </c>
-      <c r="J38" s="30">
-        <v>0</v>
-      </c>
-      <c r="K38" s="30">
+      <c r="I38" s="21">
+        <v>1</v>
+      </c>
+      <c r="J38" s="31">
+        <v>0</v>
+      </c>
+      <c r="K38" s="31">
         <v>2</v>
       </c>
-      <c r="L38" s="38" t="s">
+      <c r="L38" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="38">
-        <v>1</v>
-      </c>
-      <c r="N38" s="38">
-        <v>0</v>
-      </c>
-      <c r="O38" s="38">
-        <v>0</v>
-      </c>
-      <c r="P38" s="38" t="s">
+      <c r="M38" s="21">
+        <v>1</v>
+      </c>
+      <c r="N38" s="21">
+        <v>0</v>
+      </c>
+      <c r="O38" s="21">
+        <v>0</v>
+      </c>
+      <c r="P38" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="38">
+      <c r="Q38" s="21">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="29" customFormat="1" spans="1:21">
-      <c r="A39" s="29">
+    <row r="39" s="20" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A39" s="20">
         <v>405</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -5508,13 +5541,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="36" t="b">
+      <c r="G39" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="36">
+      <c r="I39" s="37">
         <v>1</v>
       </c>
       <c r="J39">
@@ -5526,13 +5559,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="36">
-        <v>1</v>
-      </c>
-      <c r="N39" s="36">
-        <v>0</v>
-      </c>
-      <c r="O39" s="36">
+      <c r="M39" s="37">
+        <v>1</v>
+      </c>
+      <c r="N39" s="37">
+        <v>0</v>
+      </c>
+      <c r="O39" s="37">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -5541,39 +5574,37 @@
       <c r="Q39">
         <v>3</v>
       </c>
-      <c r="R39" t="s">
-        <v>51</v>
-      </c>
+      <c r="R39" s="23"/>
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="29" customFormat="1" spans="1:21">
-      <c r="A40" s="29">
+    <row r="40" s="20" customFormat="1" spans="1:21">
+      <c r="A40" s="20">
         <v>406</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="C40" s="29">
-        <v>1</v>
-      </c>
-      <c r="D40" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="20">
+        <v>1</v>
+      </c>
+      <c r="D40" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="20" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="36" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="29">
-        <v>0</v>
-      </c>
-      <c r="I40" s="36">
+      <c r="G40" s="37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="20">
+        <v>0</v>
+      </c>
+      <c r="I40" s="37">
         <v>1</v>
       </c>
       <c r="J40">
@@ -5582,51 +5613,51 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="29">
+      <c r="L40" s="20">
         <v>3</v>
       </c>
-      <c r="M40" s="36">
-        <v>1</v>
-      </c>
-      <c r="N40" s="36">
-        <v>0</v>
-      </c>
-      <c r="O40" s="36">
-        <v>0</v>
-      </c>
-      <c r="P40" s="29" t="s">
+      <c r="M40" s="37">
+        <v>1</v>
+      </c>
+      <c r="N40" s="37">
+        <v>0</v>
+      </c>
+      <c r="O40" s="37">
+        <v>0</v>
+      </c>
+      <c r="P40" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="29">
+      <c r="Q40" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="29">
+      <c r="A41" s="20">
         <v>407</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>85</v>
-      </c>
-      <c r="G41" s="36" t="b">
+        <v>87</v>
+      </c>
+      <c r="G41" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>86</v>
-      </c>
-      <c r="I41" s="36">
+        <v>88</v>
+      </c>
+      <c r="I41" s="37">
         <v>1</v>
       </c>
       <c r="J41">
@@ -5636,53 +5667,50 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>87</v>
-      </c>
-      <c r="M41" s="36">
-        <v>1</v>
-      </c>
-      <c r="N41" s="36">
-        <v>0</v>
-      </c>
-      <c r="O41" s="36">
+        <v>89</v>
+      </c>
+      <c r="M41" s="37">
+        <v>1</v>
+      </c>
+      <c r="N41" s="37">
+        <v>0</v>
+      </c>
+      <c r="O41" s="37">
         <v>0</v>
       </c>
       <c r="P41" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
-      <c r="R41" t="s">
-        <v>89</v>
-      </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="29">
+      <c r="A42" s="20">
         <v>408</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <v>2</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F42" t="s">
-        <v>108</v>
-      </c>
-      <c r="G42" s="36" t="b">
+        <v>110</v>
+      </c>
+      <c r="G42" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>101</v>
-      </c>
-      <c r="I42" s="36">
+        <v>103</v>
+      </c>
+      <c r="I42" s="37">
         <v>1</v>
       </c>
       <c r="J42">
@@ -5692,53 +5720,50 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>102</v>
-      </c>
-      <c r="M42" s="36">
-        <v>1</v>
-      </c>
-      <c r="N42" s="36">
-        <v>0</v>
-      </c>
-      <c r="O42" s="36">
+        <v>104</v>
+      </c>
+      <c r="M42" s="37">
+        <v>1</v>
+      </c>
+      <c r="N42" s="37">
+        <v>0</v>
+      </c>
+      <c r="O42" s="37">
         <v>0</v>
       </c>
       <c r="P42" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q42">
         <v>4</v>
       </c>
-      <c r="R42" t="s">
-        <v>110</v>
-      </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="29">
+      <c r="A43" s="20">
         <v>409</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C43">
         <v>2</v>
       </c>
       <c r="D43" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E43" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F43" t="s">
-        <v>93</v>
-      </c>
-      <c r="G43" s="36" t="b">
+        <v>95</v>
+      </c>
+      <c r="G43" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="36">
+      <c r="I43" s="37">
         <v>1</v>
       </c>
       <c r="J43">
@@ -5750,51 +5775,48 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="36">
-        <v>1</v>
-      </c>
-      <c r="N43" s="36">
-        <v>0</v>
-      </c>
-      <c r="O43" s="36">
+      <c r="M43" s="37">
+        <v>1</v>
+      </c>
+      <c r="N43" s="37">
+        <v>0</v>
+      </c>
+      <c r="O43" s="37">
         <v>0</v>
       </c>
       <c r="P43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q43">
         <v>2</v>
       </c>
-      <c r="R43" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="29">
+      <c r="A44" s="20">
         <v>410</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F44" t="s">
-        <v>100</v>
-      </c>
-      <c r="G44" s="36" t="b">
+        <v>102</v>
+      </c>
+      <c r="G44" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>101</v>
-      </c>
-      <c r="I44" s="36">
+        <v>103</v>
+      </c>
+      <c r="I44" s="37">
         <v>1</v>
       </c>
       <c r="J44">
@@ -5804,53 +5826,50 @@
         <v>0</v>
       </c>
       <c r="L44" t="s">
-        <v>102</v>
-      </c>
-      <c r="M44" s="36">
-        <v>1</v>
-      </c>
-      <c r="N44" s="36">
-        <v>0</v>
-      </c>
-      <c r="O44" s="36">
+        <v>104</v>
+      </c>
+      <c r="M44" s="37">
+        <v>1</v>
+      </c>
+      <c r="N44" s="37">
+        <v>0</v>
+      </c>
+      <c r="O44" s="37">
         <v>0</v>
       </c>
       <c r="P44" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q44">
         <v>4</v>
       </c>
-      <c r="R44" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="29">
+      <c r="A45" s="20">
         <v>411</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E45" t="s">
         <v>41</v>
       </c>
       <c r="F45" t="s">
-        <v>119</v>
-      </c>
-      <c r="G45" s="36" t="b">
+        <v>121</v>
+      </c>
+      <c r="G45" s="37" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="36">
+      <c r="I45" s="37">
         <v>1</v>
       </c>
       <c r="J45">
@@ -5862,13 +5881,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="36">
-        <v>1</v>
-      </c>
-      <c r="N45" s="36">
-        <v>0</v>
-      </c>
-      <c r="O45" s="36">
+      <c r="M45" s="37">
+        <v>1</v>
+      </c>
+      <c r="N45" s="37">
+        <v>0</v>
+      </c>
+      <c r="O45" s="37">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -5876,9 +5895,6 @@
       </c>
       <c r="Q45">
         <v>3</v>
-      </c>
-      <c r="R45" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5908,456 +5924,456 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:8">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>336</v>
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>339</v>
       </c>
       <c r="C2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>339</v>
-      </c>
-      <c r="H2" s="20" t="b">
+        <v>341</v>
+      </c>
+      <c r="E2" s="27" t="s">
+        <v>342</v>
+      </c>
+      <c r="H2" s="22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" s="13" customFormat="1" spans="1:8">
-      <c r="A3" s="20">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="C3" t="s">
         <v>340</v>
       </c>
-      <c r="C3" t="s">
-        <v>337</v>
-      </c>
       <c r="D3" t="s">
-        <v>338</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="H3" s="20" t="b">
+        <v>341</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>342</v>
+      </c>
+      <c r="H3" s="22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="20">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C4" t="s">
+        <v>345</v>
+      </c>
+      <c r="D4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="H4" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="22">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>345</v>
+      </c>
+      <c r="D5" t="s">
+        <v>346</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="H5" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="22">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>349</v>
+      </c>
+      <c r="C6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D6" t="s">
         <v>341</v>
       </c>
-      <c r="C4" t="s">
-        <v>342</v>
-      </c>
-      <c r="D4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="H4" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="20">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="E6" t="s">
+        <v>350</v>
+      </c>
+      <c r="H6" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H7" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="22">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" t="s">
+        <v>353</v>
+      </c>
+      <c r="D8" t="s">
+        <v>354</v>
+      </c>
+      <c r="E8" t="s">
+        <v>355</v>
+      </c>
+      <c r="H8" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="22">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>353</v>
+      </c>
+      <c r="D9" t="s">
+        <v>354</v>
+      </c>
+      <c r="E9" t="s">
+        <v>355</v>
+      </c>
+      <c r="H9" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="22">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>357</v>
+      </c>
+      <c r="C10" t="s">
         <v>345</v>
       </c>
-      <c r="C5" t="s">
-        <v>342</v>
-      </c>
-      <c r="D5" t="s">
-        <v>343</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="H5" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="20">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="D10" t="s">
         <v>346</v>
       </c>
-      <c r="C6" t="s">
-        <v>337</v>
-      </c>
-      <c r="D6" t="s">
-        <v>338</v>
-      </c>
-      <c r="E6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H6" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="20">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>348</v>
-      </c>
-      <c r="C7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" t="s">
-        <v>338</v>
-      </c>
-      <c r="E7" t="s">
-        <v>347</v>
-      </c>
-      <c r="H7" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="20">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>349</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E10" t="s">
         <v>350</v>
       </c>
-      <c r="D8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E8" t="s">
-        <v>352</v>
-      </c>
-      <c r="H8" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="20">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="H10" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="22">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>358</v>
+      </c>
+      <c r="C11" t="s">
+        <v>345</v>
+      </c>
+      <c r="D11" t="s">
+        <v>346</v>
+      </c>
+      <c r="E11" t="s">
         <v>350</v>
       </c>
-      <c r="D9" t="s">
-        <v>351</v>
-      </c>
-      <c r="E9" t="s">
-        <v>352</v>
-      </c>
-      <c r="H9" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="20">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>354</v>
-      </c>
-      <c r="C10" t="s">
-        <v>342</v>
-      </c>
-      <c r="D10" t="s">
-        <v>343</v>
-      </c>
-      <c r="E10" t="s">
-        <v>347</v>
-      </c>
-      <c r="H10" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="20">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D11" t="s">
-        <v>343</v>
-      </c>
-      <c r="E11" t="s">
-        <v>347</v>
-      </c>
-      <c r="H11" s="20" t="b">
+      <c r="H11" s="22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="20">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C12" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D12" t="s">
-        <v>358</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>359</v>
+        <v>361</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>362</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="H12" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="1:8">
+      <c r="A13" s="22">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="s">
+        <v>345</v>
+      </c>
+      <c r="D13" t="s">
+        <v>346</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" spans="1:8">
+      <c r="A14" s="22">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C14" t="s">
+        <v>345</v>
+      </c>
+      <c r="D14" t="s">
+        <v>346</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="1:8">
+      <c r="A15" s="22">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" t="s">
+        <v>345</v>
+      </c>
+      <c r="D15" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" spans="1:8">
+      <c r="A16" s="22">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C16" t="s">
+        <v>345</v>
+      </c>
+      <c r="D16" t="s">
+        <v>346</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="22">
+        <v>101</v>
+      </c>
+      <c r="B17" t="s">
+        <v>370</v>
+      </c>
+      <c r="C17" t="s">
+        <v>371</v>
+      </c>
+      <c r="D17" t="s">
+        <v>372</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="H17" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" spans="1:8">
+      <c r="A18" s="22">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>374</v>
+      </c>
+      <c r="C18" t="s">
+        <v>375</v>
+      </c>
+      <c r="D18" t="s">
+        <v>376</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="H18" s="22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="1:8">
+      <c r="A19" s="22">
+        <v>103</v>
+      </c>
+      <c r="B19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" t="s">
         <v>360</v>
       </c>
-      <c r="G12" s="26" t="s">
+      <c r="D19" t="s">
         <v>361</v>
       </c>
-      <c r="H12" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="20">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="E19" s="25" t="s">
         <v>362</v>
       </c>
-      <c r="C13" t="s">
-        <v>342</v>
-      </c>
-      <c r="D13" t="s">
-        <v>343</v>
-      </c>
-      <c r="E13" s="24" t="s">
+      <c r="F19" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="20">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="G19" s="28" t="s">
         <v>364</v>
       </c>
-      <c r="C14" t="s">
-        <v>342</v>
-      </c>
-      <c r="D14" t="s">
-        <v>343</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="20">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C15" t="s">
-        <v>342</v>
-      </c>
-      <c r="D15" t="s">
-        <v>343</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="20">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="H19" s="22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="22">
+        <v>201</v>
+      </c>
+      <c r="B20" t="s">
+        <v>381</v>
+      </c>
+      <c r="C20" t="s">
+        <v>340</v>
+      </c>
+      <c r="D20" t="s">
+        <v>341</v>
+      </c>
+      <c r="E20" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="C16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D16" t="s">
-        <v>343</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="20">
-        <v>101</v>
-      </c>
-      <c r="B17" t="s">
-        <v>367</v>
-      </c>
-      <c r="C17" t="s">
-        <v>368</v>
-      </c>
-      <c r="D17" t="s">
-        <v>369</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="H17" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="20">
-        <v>102</v>
-      </c>
-      <c r="B18" t="s">
-        <v>371</v>
-      </c>
-      <c r="C18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D18" t="s">
-        <v>373</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>374</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>376</v>
-      </c>
-      <c r="H18" s="20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="20">
-        <v>103</v>
-      </c>
-      <c r="B19" t="s">
-        <v>377</v>
-      </c>
-      <c r="C19" t="s">
-        <v>357</v>
-      </c>
-      <c r="D19" t="s">
-        <v>358</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="G19" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="H19" s="20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="20">
-        <v>201</v>
-      </c>
-      <c r="B20" t="s">
-        <v>378</v>
-      </c>
-      <c r="C20" t="s">
-        <v>337</v>
-      </c>
-      <c r="D20" t="s">
-        <v>338</v>
-      </c>
-      <c r="E20" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="H20" s="20" t="b">
+      <c r="H20" s="22" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="20">
+      <c r="A21" s="22">
         <v>202</v>
       </c>
       <c r="B21" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C21" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="D21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>382</v>
+        <v>384</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>385</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="G21" s="24" t="s">
-        <v>384</v>
-      </c>
-      <c r="H21" s="20" t="b">
+        <v>386</v>
+      </c>
+      <c r="G21" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="H21" s="22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6395,19 +6411,19 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="13" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>385</v>
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6415,7 +6431,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -6437,292 +6453,292 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
-      <c r="A2" s="20">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>390</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E2" s="23" t="s">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>393</v>
       </c>
+      <c r="C2" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="20">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E3" s="24" t="s">
+      <c r="D3" s="23" t="s">
         <v>395</v>
       </c>
+      <c r="E3" s="26" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="20">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>392</v>
+      <c r="B4" s="23" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>395</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:5">
-      <c r="A5" s="20">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>399</v>
+      <c r="B5" s="23" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:5">
-      <c r="A6" s="20">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>401</v>
+      <c r="B6" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:5">
-      <c r="A7" s="20">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>403</v>
+      <c r="B7" s="23" t="s">
+        <v>405</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:5">
-      <c r="A8" s="20">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
-      <c r="B8" s="21" t="s">
-        <v>404</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>405</v>
+      <c r="B8" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E8" s="26" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:5">
-      <c r="A9" s="20">
+      <c r="A9" s="22">
         <v>8</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>407</v>
+      <c r="B9" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:5">
-      <c r="A10" s="20">
+      <c r="A10" s="22">
         <v>9</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>409</v>
+      <c r="B10" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>395</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
-      <c r="A11" s="20">
+      <c r="A11" s="22">
         <v>10</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="E11" s="23" t="s">
+      <c r="B11" s="23" t="s">
         <v>413</v>
       </c>
+      <c r="C11" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="12" ht="14.25" spans="1:5">
-      <c r="A12" s="20">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>414</v>
       </c>
-      <c r="C12" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="E12" s="24" t="s">
+      <c r="D12" s="23" t="s">
         <v>415</v>
       </c>
+      <c r="E12" s="26" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="13" ht="14.25" spans="1:5">
-      <c r="A13" s="20">
+      <c r="A13" s="22">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>417</v>
+      <c r="B13" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:5">
-      <c r="A14" s="20">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>419</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>420</v>
+      <c r="B14" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:5">
-      <c r="A15" s="20">
+      <c r="A15" s="22">
         <v>14</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>422</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>423</v>
+      <c r="B15" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>425</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>415</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="20"/>
+      <c r="A16" s="22"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="20"/>
+      <c r="A17" s="22"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="20"/>
+      <c r="A18" s="22"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="20"/>
+      <c r="A19" s="22"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="20"/>
+      <c r="A20" s="22"/>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="20"/>
+      <c r="A21" s="22"/>
       <c r="B21" s="3"/>
-      <c r="E21" s="24"/>
+      <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="20"/>
+      <c r="A22" s="22"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="20"/>
+      <c r="A23" s="22"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="20"/>
-      <c r="E24" s="24"/>
+      <c r="A24" s="22"/>
+      <c r="E24" s="26"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="20"/>
+      <c r="A25" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6748,7 +6764,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="28.875" customWidth="1"/>
@@ -6758,365 +6774,365 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="14.25" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C3" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="5" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="5" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:3">
       <c r="A7" s="5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" ht="28.5" spans="1:3">
       <c r="A8" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B8" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" ht="25.5" spans="1:3">
       <c r="A9" s="5" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10" ht="27" spans="1:3">
       <c r="A10" s="5" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" ht="27" spans="1:3">
       <c r="A11" s="5" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" ht="25.5" spans="1:3">
       <c r="A12" s="5" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="13" ht="27" spans="1:3">
       <c r="A13" s="5" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14" ht="57" spans="1:3">
       <c r="A14" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" ht="25.5" spans="1:3">
       <c r="A15" s="5" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" ht="41.25" spans="1:3">
       <c r="A16" s="5" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" ht="66.75" spans="1:3">
       <c r="A17" s="5" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" ht="27" spans="1:3">
       <c r="A18" s="5" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:3">
       <c r="A19" s="5" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="1:3">
       <c r="A20" s="5" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:3">
       <c r="A21" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" ht="38.25" spans="1:3">
       <c r="A22" s="5" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" ht="25.5" spans="1:3">
       <c r="A23" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="24" ht="14.25" spans="1:3">
       <c r="A24" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:3">
       <c r="A25" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:3">
       <c r="A26" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="27" ht="41.25" spans="1:3">
       <c r="A27" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:3">
       <c r="A28" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="1:3">
       <c r="A29" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" ht="57" spans="1:3">
       <c r="A30" s="5" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="1:3">
       <c r="A31" s="6" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="32" ht="14.25" spans="1:3">
       <c r="A32" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="1:3">
       <c r="A33" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -7124,10 +7140,10 @@
         <v>18</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C34" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -7135,21 +7151,21 @@
         <v>19</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C35" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="11" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C36" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -7157,10 +7173,10 @@
         <v>22</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C37" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -7168,10 +7184,10 @@
         <v>25</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C38" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -7179,10 +7195,10 @@
         <v>31</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C39" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -7190,10 +7206,10 @@
         <v>33</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -7201,10 +7217,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -7212,10 +7228,10 @@
         <v>46</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C42" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -7223,10 +7239,10 @@
         <v>52</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C43" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -7234,10 +7250,10 @@
         <v>58</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C44" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -7245,10 +7261,10 @@
         <v>65</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -7256,550 +7272,587 @@
         <v>72</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C46" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C47" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C48" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C50" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C51" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="13" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C53" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C54" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C55" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C56" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C57" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C58" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="11" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C59" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="11" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C60" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="11" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C61" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="11" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C62" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="11" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C63" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C64" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="11" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="11" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C66" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="15" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C67" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C68" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="15" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C69" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="16" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C70" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="15" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C71" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C72" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C73" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C74" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="13" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C75" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C76" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="13" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C77" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C78" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="79" ht="14.25" spans="1:3">
       <c r="A79" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C79" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="1:3">
       <c r="A80" s="6" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C80" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
     <row r="81" ht="14.25" spans="1:3">
       <c r="A81" s="6" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C81" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
     </row>
     <row r="82" ht="14.25" spans="1:3">
       <c r="A82" s="6" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" ht="14.25" spans="1:3">
       <c r="A83" s="6" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="84" ht="14.25" spans="1:3">
       <c r="A84" s="6" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
     </row>
     <row r="85" ht="14.25" spans="1:3">
       <c r="A85" s="6" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
     </row>
     <row r="86" ht="14.25" spans="1:3">
       <c r="A86" s="6" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="87" ht="14.25" spans="1:3">
       <c r="A87" s="6" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C87" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="88" ht="14.25" spans="1:3">
       <c r="A88" s="6" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C88" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="89" ht="14.25" spans="1:3">
       <c r="A89" s="6" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C89" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="90" ht="14.25" spans="1:3">
       <c r="A90" s="6" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C90" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
     </row>
     <row r="91" ht="14.25" spans="1:3">
       <c r="A91" s="6" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C91" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="92" ht="14.25" spans="1:3">
       <c r="A92" s="6" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C92" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="93" ht="14.25" spans="1:3">
       <c r="A93" s="6" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C93" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="94" ht="14.25" spans="1:3">
       <c r="A94" s="6" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C94" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
     </row>
     <row r="95" ht="14.25" spans="1:3">
-      <c r="A95" s="17" t="s">
-        <v>627</v>
-      </c>
-      <c r="B95" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="C95" s="19" t="s">
-        <v>629</v>
-      </c>
+      <c r="A95" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="96" ht="14.25" spans="1:3">
+      <c r="A96" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C96" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="97" ht="14.25" spans="1:3">
+      <c r="A97" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>637</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="20"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="20"/>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" s="20"/>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="21"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7823,44 +7876,44 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:7">
-      <c r="A2" s="31">
+      <c r="A2" s="32">
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="C2" s="31">
+        <v>200</v>
+      </c>
+      <c r="C2" s="32">
         <v>20</v>
       </c>
-      <c r="D2" s="31">
-        <v>1</v>
-      </c>
-      <c r="E2" s="20">
-        <v>1</v>
-      </c>
-      <c r="F2" s="20">
-        <v>0</v>
-      </c>
-      <c r="G2" s="20">
+      <c r="D2" s="32">
+        <v>1</v>
+      </c>
+      <c r="E2" s="22">
+        <v>1</v>
+      </c>
+      <c r="F2" s="22">
+        <v>0</v>
+      </c>
+      <c r="G2" s="22">
         <v>200</v>
       </c>
     </row>
@@ -7869,7 +7922,7 @@
         <v>201</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -7883,7 +7936,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="22">
         <v>100</v>
       </c>
     </row>
@@ -7892,7 +7945,7 @@
         <v>202</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -7906,7 +7959,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <v>100</v>
       </c>
     </row>
@@ -7915,7 +7968,7 @@
         <v>203</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C5">
         <v>8</v>
@@ -7929,7 +7982,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="22">
         <v>110</v>
       </c>
     </row>
@@ -7938,7 +7991,7 @@
         <v>204</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C6">
         <v>20</v>
@@ -7952,7 +8005,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="22">
         <v>200</v>
       </c>
     </row>
@@ -7961,7 +8014,7 @@
         <v>205</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7975,7 +8028,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="22">
         <v>90</v>
       </c>
     </row>
@@ -7984,7 +8037,7 @@
         <v>206</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -7998,7 +8051,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="22">
         <v>200</v>
       </c>
     </row>
@@ -8007,7 +8060,7 @@
         <v>207</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -8021,7 +8074,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="22">
         <v>100</v>
       </c>
     </row>
@@ -8030,7 +8083,7 @@
         <v>208</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -8044,7 +8097,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="22">
         <v>90</v>
       </c>
     </row>
@@ -8053,7 +8106,7 @@
         <v>209</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -8067,7 +8120,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="22">
         <v>0</v>
       </c>
     </row>
@@ -8076,7 +8129,7 @@
         <v>210</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C12">
         <v>15</v>
@@ -8090,7 +8143,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <v>180</v>
       </c>
     </row>
@@ -8099,7 +8152,7 @@
         <v>211</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -8113,7 +8166,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <v>0</v>
       </c>
     </row>
@@ -8122,7 +8175,7 @@
         <v>212</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14">
         <v>18</v>
@@ -8136,7 +8189,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="22">
         <v>100</v>
       </c>
     </row>
@@ -8145,7 +8198,7 @@
         <v>213</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C15">
         <v>18</v>
@@ -8159,7 +8212,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <v>180</v>
       </c>
     </row>
@@ -8168,7 +8221,7 @@
         <v>214</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -8182,7 +8235,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <v>110</v>
       </c>
     </row>
@@ -8191,7 +8244,7 @@
         <v>215</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -8205,288 +8258,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="22">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="33" customFormat="1" spans="1:7">
-      <c r="A18" s="33">
+    <row r="18" s="34" customFormat="1" spans="1:7">
+      <c r="A18" s="34">
         <v>301</v>
       </c>
-      <c r="B18" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="C18" s="33">
+      <c r="B18" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="34">
         <v>50</v>
       </c>
-      <c r="D18" s="33">
-        <v>0</v>
-      </c>
-      <c r="E18" s="33">
+      <c r="D18" s="34">
+        <v>0</v>
+      </c>
+      <c r="E18" s="34">
         <v>400</v>
       </c>
-      <c r="F18" s="33">
-        <v>0</v>
-      </c>
-      <c r="G18" s="35">
+      <c r="F18" s="34">
+        <v>0</v>
+      </c>
+      <c r="G18" s="36">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="33" customFormat="1" spans="1:7">
-      <c r="A19" s="33">
+    <row r="19" s="34" customFormat="1" spans="1:7">
+      <c r="A19" s="34">
         <v>302</v>
       </c>
-      <c r="B19" s="34" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" s="33">
+      <c r="B19" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="C19" s="34">
         <v>25</v>
       </c>
-      <c r="D19" s="33">
+      <c r="D19" s="34">
         <v>9</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E19" s="34">
         <v>100</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <v>303</v>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="36">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="33" customFormat="1" spans="1:7">
-      <c r="A20" s="33">
+    <row r="20" s="34" customFormat="1" spans="1:7">
+      <c r="A20" s="34">
         <v>303</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="C20" s="33">
+      <c r="B20" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="C20" s="34">
         <v>20</v>
       </c>
-      <c r="D20" s="33">
+      <c r="D20" s="34">
         <v>3</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="34">
         <v>50</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="34">
         <v>301</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="36">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="33" customFormat="1" spans="1:7">
-      <c r="A21" s="33">
+    <row r="21" s="34" customFormat="1" spans="1:7">
+      <c r="A21" s="34">
         <v>304</v>
       </c>
-      <c r="B21" s="34" t="s">
-        <v>215</v>
-      </c>
-      <c r="C21" s="33">
+      <c r="B21" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C21" s="34">
         <v>30</v>
       </c>
-      <c r="D21" s="33">
+      <c r="D21" s="34">
         <v>11</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E21" s="34">
         <v>300</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <v>301</v>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="36">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="33" customFormat="1" spans="1:7">
-      <c r="A22" s="33">
+    <row r="22" s="34" customFormat="1" spans="1:7">
+      <c r="A22" s="34">
         <v>305</v>
       </c>
-      <c r="B22" s="34" t="s">
-        <v>216</v>
-      </c>
-      <c r="C22" s="33">
+      <c r="B22" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C22" s="34">
         <v>25</v>
       </c>
-      <c r="D22" s="33">
+      <c r="D22" s="34">
         <v>8</v>
       </c>
-      <c r="E22" s="33">
+      <c r="E22" s="34">
         <v>100</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <v>303</v>
       </c>
-      <c r="G22" s="35">
+      <c r="G22" s="36">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="33" customFormat="1" spans="1:7">
-      <c r="A23" s="33">
+    <row r="23" s="34" customFormat="1" spans="1:7">
+      <c r="A23" s="34">
         <v>306</v>
       </c>
-      <c r="B23" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="C23" s="33">
+      <c r="B23" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="34">
         <v>35</v>
       </c>
-      <c r="D23" s="33">
-        <v>0</v>
-      </c>
-      <c r="E23" s="33">
+      <c r="D23" s="34">
+        <v>0</v>
+      </c>
+      <c r="E23" s="34">
         <v>200</v>
       </c>
-      <c r="F23" s="33">
-        <v>0</v>
-      </c>
-      <c r="G23" s="35">
+      <c r="F23" s="34">
+        <v>0</v>
+      </c>
+      <c r="G23" s="36">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="33" customFormat="1" spans="1:7">
-      <c r="A24" s="33">
+    <row r="24" s="34" customFormat="1" spans="1:7">
+      <c r="A24" s="34">
         <v>307</v>
       </c>
-      <c r="B24" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="C24" s="33">
+      <c r="B24" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="34">
         <v>35</v>
       </c>
-      <c r="D24" s="33">
+      <c r="D24" s="34">
         <v>12</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="34">
         <v>150</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <v>302</v>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="36">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="33" customFormat="1" spans="1:7">
-      <c r="A25" s="33">
+    <row r="25" s="34" customFormat="1" spans="1:7">
+      <c r="A25" s="34">
         <v>308</v>
       </c>
-      <c r="B25" s="34" t="s">
-        <v>219</v>
-      </c>
-      <c r="C25" s="33">
+      <c r="B25" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="34">
         <v>35</v>
       </c>
-      <c r="D25" s="33">
+      <c r="D25" s="34">
         <v>12</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="34">
         <v>150</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <v>302</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="33" customFormat="1" spans="1:7">
-      <c r="A26" s="33">
+    <row r="26" s="34" customFormat="1" spans="1:7">
+      <c r="A26" s="34">
         <v>309</v>
       </c>
-      <c r="B26" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C26" s="33">
+      <c r="B26" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="34">
         <v>20</v>
       </c>
-      <c r="D26" s="33">
+      <c r="D26" s="34">
         <v>10</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="34">
         <v>80</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="34">
         <v>306</v>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="36">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="33" customFormat="1" spans="1:7">
-      <c r="A27" s="33">
+    <row r="27" s="34" customFormat="1" spans="1:7">
+      <c r="A27" s="34">
         <v>310</v>
       </c>
-      <c r="B27" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C27" s="33">
+      <c r="B27" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C27" s="34">
         <v>30</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>10</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>120</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>309</v>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="36">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="33" customFormat="1" spans="1:7">
-      <c r="A28" s="33">
+    <row r="28" s="34" customFormat="1" spans="1:7">
+      <c r="A28" s="34">
         <v>311</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="33">
+      <c r="B28" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C28" s="34">
         <v>30</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>10</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>120</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>309</v>
       </c>
-      <c r="G28" s="35">
+      <c r="G28" s="36">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="33" customFormat="1" spans="1:7">
-      <c r="A29" s="33">
+    <row r="29" s="34" customFormat="1" spans="1:7">
+      <c r="A29" s="34">
         <v>312</v>
       </c>
-      <c r="B29" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="C29" s="33">
+      <c r="B29" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="34">
         <v>15</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="34">
         <v>2</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <v>15</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <v>306</v>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="36">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="33" customFormat="1" spans="1:7">
-      <c r="B30" s="34"/>
+    <row r="30" s="34" customFormat="1" spans="1:7">
+      <c r="B30" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8510,30 +8563,30 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="31">
+      <c r="A2" s="32">
         <v>3</v>
       </c>
-      <c r="B2" s="31" t="s">
-        <v>226</v>
+      <c r="B2" s="32" t="s">
+        <v>229</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -8549,11 +8602,11 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="31">
+      <c r="A3" s="32">
         <v>4</v>
       </c>
-      <c r="B3" s="31" t="s">
-        <v>197</v>
+      <c r="B3" s="32" t="s">
+        <v>200</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -8573,7 +8626,7 @@
         <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -8596,13 +8649,13 @@
         <v>302</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -8619,7 +8672,7 @@
         <v>303</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -8639,7 +8692,7 @@
         <v>304</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -8659,7 +8712,7 @@
         <v>305</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C8">
         <v>2.5</v>
@@ -8679,7 +8732,7 @@
         <v>306</v>
       </c>
       <c r="B9" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -8699,13 +8752,13 @@
         <v>307</v>
       </c>
       <c r="B10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>0.05</v>
@@ -8722,7 +8775,7 @@
         <v>308</v>
       </c>
       <c r="B11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -8738,11 +8791,11 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="31">
+      <c r="A12" s="32">
         <v>309</v>
       </c>
-      <c r="B12" s="31" t="s">
-        <v>165</v>
+      <c r="B12" s="32" t="s">
+        <v>168</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -8758,11 +8811,11 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="31">
+      <c r="A13" s="32">
         <v>310</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>170</v>
+      <c r="B13" s="32" t="s">
+        <v>173</v>
       </c>
       <c r="C13">
         <v>2.5</v>
@@ -8778,11 +8831,11 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="31">
+      <c r="A14" s="32">
         <v>311</v>
       </c>
-      <c r="B14" s="31" t="s">
-        <v>174</v>
+      <c r="B14" s="32" t="s">
+        <v>177</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -8801,11 +8854,11 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="31">
+      <c r="A15" s="32">
         <v>312</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>220</v>
+      <c r="B15" s="32" t="s">
+        <v>223</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -8821,8 +8874,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8848,25 +8901,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8874,10 +8927,10 @@
         <v>201</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -8892,33 +8945,33 @@
         <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="3" s="30" customFormat="1" spans="1:8">
-      <c r="A3" s="30">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="3" s="31" customFormat="1" spans="1:8">
+      <c r="A3" s="31">
         <v>202</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E3" s="30">
-        <v>0</v>
-      </c>
-      <c r="F3" s="30">
+        <v>202</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="E3" s="31">
+        <v>0</v>
+      </c>
+      <c r="F3" s="31">
         <v>0.8</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="30" t="s">
-        <v>238</v>
+      <c r="H3" s="31" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -8926,10 +8979,10 @@
         <v>203</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -8944,7 +8997,7 @@
         <v>41</v>
       </c>
       <c r="H4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -8952,13 +9005,13 @@
         <v>204</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D5" t="s">
         <v>240</v>
-      </c>
-      <c r="D5" t="s">
-        <v>237</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -8970,7 +9023,7 @@
         <v>54</v>
       </c>
       <c r="H5" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -8978,13 +9031,13 @@
         <v>205</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -8993,10 +9046,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:8">
@@ -9004,7 +9057,7 @@
         <v>206</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C7" t="s">
         <v>67</v>
@@ -9022,7 +9075,7 @@
         <v>67</v>
       </c>
       <c r="H7" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -9030,13 +9083,13 @@
         <v>207</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C8" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -9045,10 +9098,10 @@
         <v>0.7</v>
       </c>
       <c r="G8" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H8" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -9056,13 +9109,13 @@
         <v>208</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C9" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -9071,10 +9124,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="H9" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -9082,13 +9135,13 @@
         <v>209</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -9097,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customFormat="1" spans="1:8">
@@ -9108,13 +9161,13 @@
         <v>210</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -9123,10 +9176,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="H11" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="12" customFormat="1" spans="1:8">
@@ -9134,7 +9187,7 @@
         <v>211</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -9148,13 +9201,13 @@
         <v>212</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -9163,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="H13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" customFormat="1" spans="1:8">
@@ -9174,13 +9227,13 @@
         <v>213</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -9189,10 +9242,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="H14" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" customFormat="1" spans="1:8">
@@ -9200,10 +9253,10 @@
         <v>214</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -9215,10 +9268,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="H15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="16" customFormat="1" spans="1:8">
@@ -9226,13 +9279,13 @@
         <v>215</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -9244,7 +9297,7 @@
         <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -9252,13 +9305,13 @@
         <v>401</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C17" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -9272,13 +9325,13 @@
         <v>402</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -9292,56 +9345,56 @@
         <v>403</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C19" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" t="s">
+        <v>240</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="31" customFormat="1" spans="1:8">
+      <c r="A20" s="33">
+        <v>404</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>240</v>
+      </c>
+      <c r="E20" s="31">
+        <v>0</v>
+      </c>
+      <c r="F20" s="31">
+        <v>0.8</v>
+      </c>
+      <c r="G20" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="30">
+        <v>405</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C21" t="s">
         <v>242</v>
-      </c>
-      <c r="D19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="30" customFormat="1" spans="1:8">
-      <c r="A20" s="32">
-        <v>404</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D20" s="30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E20" s="30">
-        <v>0</v>
-      </c>
-      <c r="F20" s="30">
-        <v>0.8</v>
-      </c>
-      <c r="G20" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="28">
-        <v>405</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>266</v>
-      </c>
-      <c r="C21" t="s">
-        <v>239</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -9356,18 +9409,18 @@
         <v>41</v>
       </c>
       <c r="H21" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="28">
+      <c r="A22" s="30">
         <v>406</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C22" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -9382,21 +9435,21 @@
         <v>35</v>
       </c>
       <c r="H22" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="29">
+      <c r="A23" s="20">
         <v>407</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -9405,102 +9458,102 @@
         <v>0</v>
       </c>
       <c r="G23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="29">
+      <c r="A24" s="20">
         <v>408</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C24" t="s">
+        <v>259</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24" t="s">
+        <v>260</v>
+      </c>
+      <c r="H24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="20">
+        <v>409</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25" t="s">
+        <v>246</v>
+      </c>
+      <c r="H25" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="20">
+        <v>410</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" t="s">
         <v>256</v>
       </c>
-      <c r="D24" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="D26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" t="s">
         <v>257</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H26" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="29">
-        <v>409</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="C25" t="s">
-        <v>242</v>
-      </c>
-      <c r="D25" t="s">
-        <v>237</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
-        <v>0</v>
-      </c>
-      <c r="G25" t="s">
-        <v>243</v>
-      </c>
-      <c r="H25" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="29">
-        <v>410</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C26" t="s">
-        <v>253</v>
-      </c>
-      <c r="D26" t="s">
-        <v>101</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" t="s">
-        <v>254</v>
-      </c>
-      <c r="H26" t="s">
-        <v>255</v>
-      </c>
-    </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="29">
+      <c r="A27" s="20">
         <v>411</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C27" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -9512,7 +9565,7 @@
         <v>41</v>
       </c>
       <c r="H27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -9556,69 +9609,69 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="30" customFormat="1" spans="1:21">
-      <c r="A1" s="30" t="s">
+    <row r="1" s="31" customFormat="1" spans="1:21">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>273</v>
-      </c>
-      <c r="D1" s="30" t="s">
-        <v>274</v>
-      </c>
-      <c r="E1" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="F1" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="D1" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="E1" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="F1" s="31" t="s">
         <v>279</v>
       </c>
+      <c r="G1" s="31" t="s">
+        <v>280</v>
+      </c>
+      <c r="H1" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="I1" s="31" t="s">
+        <v>282</v>
+      </c>
       <c r="J1" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="L1" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="M1" s="30" t="s">
         <v>283</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="K1" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="L1" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="M1" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="N1" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="O1" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="P1" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="Q1" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="R1" s="31" t="s">
         <v>291</v>
+      </c>
+      <c r="S1" s="31" t="s">
+        <v>292</v>
+      </c>
+      <c r="T1" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="U1" s="31" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -9626,7 +9679,7 @@
         <v>201</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C2">
         <v>12</v>
@@ -9662,7 +9715,7 @@
         <v>500</v>
       </c>
       <c r="Q2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="R2">
         <v>500</v>
@@ -9682,7 +9735,7 @@
         <v>202</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C3">
         <v>20</v>
@@ -9703,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K3">
         <v>1</v>
@@ -9715,7 +9768,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O3">
         <v>2.5</v>
@@ -9724,7 +9777,7 @@
         <v>900</v>
       </c>
       <c r="Q3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="R3">
         <v>100</v>
@@ -9744,7 +9797,7 @@
         <v>203</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C4">
         <v>15</v>
@@ -9780,7 +9833,7 @@
         <v>1300</v>
       </c>
       <c r="Q4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="R4">
         <v>500</v>
@@ -9800,7 +9853,7 @@
         <v>204</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C5">
         <v>35</v>
@@ -9824,25 +9877,25 @@
         <v>5000</v>
       </c>
       <c r="J5" t="s">
+        <v>300</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
         <v>297</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>294</v>
       </c>
       <c r="P5">
         <v>300</v>
       </c>
       <c r="Q5" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -9862,7 +9915,7 @@
         <v>205</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -9883,7 +9936,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -9898,7 +9951,7 @@
         <v>500</v>
       </c>
       <c r="Q6" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="R6">
         <v>300</v>
@@ -9918,7 +9971,7 @@
         <v>206</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -9951,7 +10004,7 @@
         <v>2</v>
       </c>
       <c r="N7" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -9960,7 +10013,7 @@
         <v>800</v>
       </c>
       <c r="Q7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -9980,7 +10033,7 @@
         <v>207</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C8">
         <v>25</v>
@@ -10001,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -10013,7 +10066,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O8">
         <v>1</v>
@@ -10022,7 +10075,7 @@
         <v>300</v>
       </c>
       <c r="Q8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="R8">
         <v>600</v>
@@ -10042,7 +10095,7 @@
         <v>208</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -10063,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K9">
         <v>1</v>
@@ -10078,7 +10131,7 @@
         <v>570</v>
       </c>
       <c r="Q9" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="R9">
         <v>1030</v>
@@ -10098,7 +10151,7 @@
         <v>209</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -10119,7 +10172,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -10134,7 +10187,7 @@
         <v>600</v>
       </c>
       <c r="Q10" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="R10">
         <v>200</v>
@@ -10154,7 +10207,7 @@
         <v>210</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C11">
         <v>35</v>
@@ -10178,7 +10231,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -10193,7 +10246,7 @@
         <v>500</v>
       </c>
       <c r="Q11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="R11">
         <v>900</v>
@@ -10213,7 +10266,7 @@
         <v>211</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -10246,7 +10299,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -10266,7 +10319,7 @@
         <v>212</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -10316,7 +10369,7 @@
         <v>213</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C14">
         <v>30</v>
@@ -10346,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O14">
         <v>5</v>
@@ -10355,7 +10408,7 @@
         <v>600</v>
       </c>
       <c r="Q14" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="R14">
         <v>300</v>
@@ -10375,7 +10428,7 @@
         <v>214</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C15">
         <v>20</v>
@@ -10411,7 +10464,7 @@
         <v>1000</v>
       </c>
       <c r="Q15" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -10431,7 +10484,7 @@
         <v>215</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C16">
         <v>30</v>
@@ -10452,7 +10505,7 @@
         <v>1000</v>
       </c>
       <c r="J16" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -10464,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O16">
         <v>2.5</v>
@@ -10473,7 +10526,7 @@
         <v>530</v>
       </c>
       <c r="Q16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -10489,11 +10542,11 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="31">
+      <c r="A17" s="32">
         <v>301</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -10548,11 +10601,11 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="31">
+      <c r="A18" s="32">
         <v>302</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -10607,11 +10660,11 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="31">
+      <c r="A19" s="32">
         <v>303</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -10666,11 +10719,11 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="31">
+      <c r="A20" s="32">
         <v>304</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C20">
         <v>20</v>
@@ -10729,7 +10782,7 @@
         <v>305</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C21">
         <v>20</v>
@@ -10762,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="N21" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -10771,7 +10824,7 @@
         <v>400</v>
       </c>
       <c r="Q21" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="R21">
         <v>400</v>
@@ -10787,11 +10840,11 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="31">
+      <c r="A22" s="32">
         <v>306</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -10846,11 +10899,11 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="31">
+      <c r="A23" s="32">
         <v>307</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -10905,11 +10958,11 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="31">
+      <c r="A24" s="32">
         <v>308</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -10964,11 +11017,11 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="31">
+      <c r="A25" s="32">
         <v>309</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -11023,11 +11076,11 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="31">
+      <c r="A26" s="32">
         <v>310</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -11082,11 +11135,11 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="31">
+      <c r="A27" s="32">
         <v>311</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -11141,11 +11194,11 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="31">
+      <c r="A28" s="32">
         <v>312</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -11204,7 +11257,7 @@
         <v>401</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C29">
         <v>18</v>
@@ -11225,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="J29" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -11237,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O29">
         <v>1</v>
@@ -11246,7 +11299,7 @@
         <v>300</v>
       </c>
       <c r="Q29" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="R29">
         <v>600</v>
@@ -11266,7 +11319,7 @@
         <v>402</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C30">
         <v>13</v>
@@ -11287,7 +11340,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -11302,7 +11355,7 @@
         <v>570</v>
       </c>
       <c r="Q30" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="R30">
         <v>1030</v>
@@ -11322,7 +11375,7 @@
         <v>403</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -11343,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -11358,7 +11411,7 @@
         <v>600</v>
       </c>
       <c r="Q31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="R31">
         <v>300</v>
@@ -11374,11 +11427,11 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="28">
+      <c r="A32" s="30">
         <v>404</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C32">
         <v>20</v>
@@ -11399,7 +11452,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -11411,7 +11464,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O32">
         <v>4</v>
@@ -11420,7 +11473,7 @@
         <v>900</v>
       </c>
       <c r="Q32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -11436,11 +11489,11 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="28">
+      <c r="A33" s="30">
         <v>405</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C33">
         <v>15</v>
@@ -11476,7 +11529,7 @@
         <v>1300</v>
       </c>
       <c r="Q33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="R33">
         <v>500</v>
@@ -11492,11 +11545,11 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="28">
+      <c r="A34" s="30">
         <v>406</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C34">
         <v>12</v>
@@ -11532,7 +11585,7 @@
         <v>500</v>
       </c>
       <c r="Q34" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="R34">
         <v>500</v>
@@ -11548,11 +11601,11 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="29">
+      <c r="A35" s="20">
         <v>407</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -11573,7 +11626,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -11588,7 +11641,7 @@
         <v>600</v>
       </c>
       <c r="Q35" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="R35">
         <v>200</v>
@@ -11604,11 +11657,11 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="29">
+      <c r="A36" s="20">
         <v>408</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C36">
         <v>30</v>
@@ -11638,7 +11691,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O36">
         <v>5</v>
@@ -11647,7 +11700,7 @@
         <v>600</v>
       </c>
       <c r="Q36" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="R36">
         <v>300</v>
@@ -11663,11 +11716,11 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="29">
+      <c r="A37" s="20">
         <v>409</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C37">
         <v>35</v>
@@ -11691,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -11706,7 +11759,7 @@
         <v>500</v>
       </c>
       <c r="Q37" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="R37">
         <v>900</v>
@@ -11722,11 +11775,11 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="29">
+      <c r="A38" s="20">
         <v>410</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -11772,11 +11825,11 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="29">
+      <c r="A39" s="20">
         <v>411</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C39">
         <v>30</v>
@@ -11797,7 +11850,7 @@
         <v>1000</v>
       </c>
       <c r="J39" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -11809,7 +11862,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="O39">
         <v>2.5</v>
@@ -11818,7 +11871,7 @@
         <v>530</v>
       </c>
       <c r="Q39" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -11850,10 +11903,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -11861,7 +11914,7 @@
         <v>204</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C2">
         <v>60</v>
@@ -11872,7 +11925,7 @@
         <v>210</v>
       </c>
       <c r="B3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C3">
         <v>30</v>
@@ -11883,7 +11936,7 @@
         <v>212</v>
       </c>
       <c r="B4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C4">
         <v>45</v>
@@ -11894,7 +11947,7 @@
         <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -11905,7 +11958,7 @@
         <v>401</v>
       </c>
       <c r="B6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C6">
         <v>15</v>
@@ -11916,7 +11969,7 @@
         <v>402</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -11927,95 +11980,95 @@
         <v>403</v>
       </c>
       <c r="B8" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C8">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="28">
+      <c r="A9" s="30">
         <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C9">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="28">
+      <c r="A10" s="30">
         <v>405</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C10">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="28">
+      <c r="A11" s="30">
         <v>406</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C11">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="29">
+      <c r="A12" s="20">
         <v>407</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C12">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="29">
+      <c r="A13" s="20">
         <v>408</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C13">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="29">
+      <c r="A14" s="20">
         <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C14">
         <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="29">
+      <c r="A15" s="20">
         <v>410</v>
       </c>
       <c r="B15" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C15">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="29">
+      <c r="A16" s="20">
         <v>411</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C16">
         <v>25</v>
@@ -12041,25 +12094,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -12067,10 +12120,10 @@
         <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -12093,10 +12146,10 @@
         <v>203</v>
       </c>
       <c r="B3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -12119,10 +12172,10 @@
         <v>204</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -12145,10 +12198,10 @@
         <v>206</v>
       </c>
       <c r="B5" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -12171,10 +12224,10 @@
         <v>207</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -12197,10 +12250,10 @@
         <v>208</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -12223,10 +12276,10 @@
         <v>210</v>
       </c>
       <c r="B8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C8" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -12249,10 +12302,10 @@
         <v>213</v>
       </c>
       <c r="B9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -12290,13 +12343,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -12304,7 +12357,7 @@
         <v>203</v>
       </c>
       <c r="B2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -12318,7 +12371,7 @@
         <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C3">
         <v>25</v>
@@ -12344,19 +12397,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C1" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -12364,7 +12417,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C2">
         <v>4</v>
@@ -12381,7 +12434,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -12398,7 +12451,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -12415,7 +12468,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -12432,7 +12485,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -12449,7 +12502,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C7">
         <v>8</v>
@@ -12466,7 +12519,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C8">
         <v>8</v>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1106" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="651">
   <si>
     <t>类型</t>
   </si>
@@ -1475,10 +1475,10 @@
     <t>Key说</t>
   </si>
   <si>
-    <t xml:space="preserve"> 说</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Said</t>
+    <t xml:space="preserve"> 说：</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Said:</t>
   </si>
   <si>
     <t>Key敌人</t>
@@ -2373,6 +2373,68 @@
   </si>
   <si>
     <t>No idle Construction Vehicles or Worker Larvae</t>
+  </si>
+  <si>
+    <t>Key缺少{}不能采集</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">缺少 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">{} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，不能采集</t>
+    </r>
+  </si>
+  <si>
+    <t>Cannot gather resources without {}.</t>
+  </si>
+  <si>
+    <t>Key巡逻</t>
+  </si>
+  <si>
+    <t>巡逻</t>
+  </si>
+  <si>
+    <t>Patrol</t>
+  </si>
+  <si>
+    <t>Key停止巡逻</t>
+  </si>
+  <si>
+    <t>停止巡逻</t>
+  </si>
+  <si>
+    <t>Stop Patrol</t>
+  </si>
+  <si>
+    <t>Key正在卸矿</t>
+  </si>
+  <si>
+    <t>正在卸矿</t>
+  </si>
+  <si>
+    <t>Unloading Minerals</t>
   </si>
 </sst>
 </file>
@@ -3163,7 +3225,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
@@ -7829,14 +7891,58 @@
       </c>
     </row>
     <row r="97" ht="14.25" spans="1:3">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="6" t="s">
         <v>636</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="5" t="s">
         <v>637</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C97" s="9" t="s">
         <v>638</v>
+      </c>
+    </row>
+    <row r="98" ht="14.25" spans="1:3">
+      <c r="A98" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="99" ht="14.25" spans="1:3">
+      <c r="A99" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="C99" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="100" ht="14.25" spans="1:3">
+      <c r="A100" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="C100" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="101" ht="14.25" spans="1:3">
+      <c r="A101" s="17" t="s">
+        <v>648</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>649</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>650</v>
       </c>
     </row>
     <row r="124" spans="2:2">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="822">
   <si>
     <t>类型</t>
   </si>
@@ -1706,7 +1706,7 @@
     </r>
   </si>
   <si>
-    <t>Combat units will automatically attack enemies within their alert range, but you can use &lt;color=#a0ff50&gt;Force Move&lt;/color&gt; to manually interrupt their attacks.</t>
+    <t>Combat units will automatically attack enemies within their alert range, but you can use &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; to manually interrupt their attacks.</t>
   </si>
   <si>
     <t>Key然后点击下方的强行走按钮</t>
@@ -2008,7 +2008,7 @@
     <t>Barracks</t>
   </si>
   <si>
-    <t>Civilian House</t>
+    <t>Supply Depots</t>
   </si>
   <si>
     <t>Bunker</t>
@@ -2319,7 +2319,7 @@
     </r>
   </si>
   <si>
-    <t>{} units inside</t>
+    <t>{} unit(s) inside</t>
   </si>
   <si>
     <r>
@@ -2435,6 +2435,733 @@
   </si>
   <si>
     <t>Unloading Minerals</t>
+  </si>
+  <si>
+    <t>Key没找到空闲的工虫</t>
+  </si>
+  <si>
+    <t>没找到空闲的工虫</t>
+  </si>
+  <si>
+    <t>No idle Worker Larva found.</t>
+  </si>
+  <si>
+    <t>Key没找到空闲的工程车</t>
+  </si>
+  <si>
+    <t>没找到空闲的工程车</t>
+  </si>
+  <si>
+    <t>No idle Construction Vehicle found.</t>
+  </si>
+  <si>
+    <t>Key如何指挥反空降作战？</t>
+  </si>
+  <si>
+    <t>如何指挥反空降作战？</t>
+  </si>
+  <si>
+    <t>How to Command Anti-Airborne Operations?</t>
+  </si>
+  <si>
+    <t>Key在途中击落敌方</t>
+  </si>
+  <si>
+    <r>
+      <t>，在途中击落敌方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>房虫</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后，其运送的敌方单位就会变得非常虚弱，趁机一鼓作气消灭它们！</t>
+    </r>
+  </si>
+  <si>
+    <t>,After shooting down the enemy &lt;color=#a0ff50&gt;Population Drone&lt;/color&gt; mid-flight, the enemy units it carries will be severely weakened—seize the moment and wipe them out in one fell swoop!</t>
+  </si>
+  <si>
+    <t>Key我试试。</t>
+  </si>
+  <si>
+    <t>我试试。</t>
+  </si>
+  <si>
+    <t>Let me give it a try.</t>
+  </si>
+  <si>
+    <t>Key击落房虫……</t>
+  </si>
+  <si>
+    <t>击落&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，并且消灭其运送的敌方单位</t>
+  </si>
+  <si>
+    <t>Shoot down the &lt;color=#a0ff50&gt;Population Drone&lt;/color&gt; and eliminate the enemy units it transports.</t>
+  </si>
+  <si>
+    <t>Key这都能输，不可思议！</t>
+  </si>
+  <si>
+    <t>这都能输，不可思议！</t>
+  </si>
+  <si>
+    <t>How could we lose this? Unbelievable!</t>
+  </si>
+  <si>
+    <t>Key玩家的操作你别猜。</t>
+  </si>
+  <si>
+    <t>玩家的操作你别猜。</t>
+  </si>
+  <si>
+    <t>Never try to second-guess a player’s moves.</t>
+  </si>
+  <si>
+    <t>Key您已经掌握了反空降战术……</t>
+  </si>
+  <si>
+    <t>您已经掌握了反空降战术，可在今后的作战中择机运用。</t>
+  </si>
+  <si>
+    <t>You have mastered anti-airborne tactics—feel free to deploy them opportunistically in future battles.</t>
+  </si>
+  <si>
+    <t>Key谨遵恩师教诲。</t>
+  </si>
+  <si>
+    <t>谨遵恩师教诲。</t>
+  </si>
+  <si>
+    <t>I shall follow your teachings closely, Master.</t>
+  </si>
+  <si>
+    <t>Key即时战略游戏的操作……</t>
+  </si>
+  <si>
+    <t>即时战略游戏的操作并不复杂，老年间便有四句童谣：
+    &lt;color=#a0ff50&gt;工程车&lt;/color&gt;，造&lt;color=#a0ff50&gt;基地&lt;/color&gt;；
+    基地又产工程车。
+    工程车，造&lt;color=#a0ff50&gt;兵营&lt;/color&gt;，
+    兵营产兵欢乐多！</t>
+  </si>
+  <si>
+    <t>The controls of a real-time strategy game aren’t complicated. Back in the day, there was a little nursery rhyme that went like this:
+    "&lt;color=#a0ff50&gt;Construction Vehicle&lt;/color&gt;, build the &lt;color=#a0ff50&gt;Command Center&lt;/color&gt;;
+    The Command Center spawns more Construction Vehicles.
+    Construction Vehicle, build the &lt;color=#a0ff50&gt;Barracks&lt;/color&gt;,
+    Barracks pump out troops—endless joy for us all!"</t>
+  </si>
+  <si>
+    <t>Key听说还能造地堡炮台……</t>
+  </si>
+  <si>
+    <t>听说工程车还可以造&lt;color=#a0ff50&gt;地堡&lt;/color&gt;和&lt;color=#a0ff50&gt;炮台&lt;/color&gt;，我也要试试。</t>
+  </si>
+  <si>
+    <t>I heard Construction Vehicles can also build &lt;color=#a0ff50&gt; Bunkers&lt;/color&gt; and &lt;color=#a0ff50&gt; Gun Turrets&lt;/color&gt;. I want to give that a shot too.</t>
+  </si>
+  <si>
+    <t>Key造完基地应该……</t>
+  </si>
+  <si>
+    <t>造完基地应该先安排工程车去采集&lt;color=#a0ff50&gt;晶体矿&lt;/color&gt;和&lt;color=#a0ff50&gt;燃气矿&lt;/color&gt;，这是一切生产建造的基础。此外建造&lt;color=#a0ff50&gt;民房&lt;/color&gt;可以提升活动单位上限。</t>
+  </si>
+  <si>
+    <t>Once the Command Center is built, you should first send Construction Vehicles to harvest &lt;color=#a0ff50&gt; Crystal Ore&lt;/color&gt; and &lt;color=#a0ff50&gt; Gas Ore&lt;/color&gt;—this is the foundation of all production and construction. Additionally, building &lt;color=#a0ff50&gt; Supply Depots&lt;/color&gt; increases your mobile unit cap.</t>
+  </si>
+  <si>
+    <t>Key我想单手拖动选中……</t>
+  </si>
+  <si>
+    <t>我只想单手操作，拖动视口 和 选中多个单位 如何操作呢？</t>
+  </si>
+  <si>
+    <t>I only want to play with one hand. How do I pan the viewport and select multiple units?</t>
+  </si>
+  <si>
+    <t>Key拖动地面就可以……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  拖动地面就可以移动视口，此外设置（齿轮图标）界面还有视口镜头投影切换、放大、缩小按钮。当然也支持双指缩放视口。
+  先点击右边&lt;color=#a0ff50&gt;框选&lt;/color&gt;按钮，然后在屏幕中拖动，即可&lt;color=#a0ff50&gt;框选&lt;/color&gt;多个单位。在设置（齿轮图标）界面中可以切换菱形&lt;color=#a0ff50&gt;框选&lt;/color&gt;或方形&lt;color=#a0ff50&gt;框选&lt;/color&gt;。
+  全程只要单手握持手机单指操作即可。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Drag the ground to move the viewport. Moreover, the Settings (gear icon) menu has buttons for switching viewport projection, zooming in, and zooming out. Pinch-to-zoom is also supported.
+   First, tap the &lt;color=#a0ff50&gt;Box Select&lt;/color&gt; button on the right, then drag across the screen to &lt;color=#a0ff50&gt;box-select&lt;/color&gt; multiple units. You can switch between diamond-shaped and square &lt;color=#a0ff50&gt;box selection&lt;/color&gt; modes in the Settings (gear icon) menu.
+ The entire process can be done with one hand holding the phone and a single finger operating."</t>
+  </si>
+  <si>
+    <t>Key只用一只手就能玩……</t>
+  </si>
+  <si>
+    <t>只用一只手就能玩的RTS即时战略游戏，那岂不是跟刷短视频一样轻松？我一定要体验一下！</t>
+  </si>
+  <si>
+    <t>An RTS game you can play with one hand? That’s as effortless as scrolling through short videos! I definitely need to give it a try!</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Key走你</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>!</t>
+    </r>
+  </si>
+  <si>
+    <t>走你!</t>
+  </si>
+  <si>
+    <t>Let’s go!</t>
+  </si>
+  <si>
+    <t>Key欢迎来到……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>欢迎来到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>即时战略指挥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，现在您要接受基础的训练</t>
+    </r>
+  </si>
+  <si>
+    <t>Welcome to &lt;color=#a0ff50&gt;Real-Time Strategy Command&lt;/color&gt;. You will now receive basic training.</t>
+  </si>
+  <si>
+    <t>Key造基地方法……</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;基地&lt;/color&gt;按钮，再点击空白地面，稍后就能造出一个基地</t>
+  </si>
+  <si>
+    <t>Please tap the &lt;color=#a0ff50&gt;Construction Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Command Center&lt;/color&gt; button, then tap an empty spot on the ground. A Command Center will be built shortly.</t>
+  </si>
+  <si>
+    <t>Key造活动单位方法……</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;工程车&lt;/color&gt;按钮，稍后会在基地旁造出一个工程车</t>
+  </si>
+  <si>
+    <t>Please tap the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Construction Vehicle&lt;/color&gt; button. A Construction Vehicle will spawn next to the Command Center shortly.</t>
+  </si>
+  <si>
+    <t>Key工程车移动方法……</t>
+  </si>
+  <si>
+    <t>现在您有工程车了，点击选中您的&lt;color=#a0ff50&gt;工程车&lt;/color&gt;，再点击空旷地面，命令它走向目标点</t>
+  </si>
+  <si>
+    <t>Now you have a Construction Vehicle. Tap to select your &lt;color=#a0ff50&gt;Construction Vehicle&lt;/color&gt;, then tap an open area on the ground to order it to move to the target location.</t>
+  </si>
+  <si>
+    <t>Key工程车采集晶体矿……</t>
+  </si>
+  <si>
+    <t>很好！现在给您刷了一个&lt;color=#a0ff50&gt;晶体矿&lt;/color&gt;，请点击晶体矿，让工程车在晶体矿和基地之间搬运晶体矿</t>
+  </si>
+  <si>
+    <t>Well done! A patch of &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; has been spawned for you. Tap the Crystal Ore to send the Construction Vehicle to transport ore between the Crystal Ore deposit and the Command Center.</t>
+  </si>
+  <si>
+    <t>Key工程车采集燃气矿……</t>
+  </si>
+  <si>
+    <t>很好！您的工程车正在采集晶体矿，请等他把晶体矿运回基地。现在，请先点&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;，再选中另一辆工程车去采集&lt;color=#a0ff50&gt;燃气矿&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Great! Your Construction Vehicle is harvesting Crystal Ore—wait for it to deliver the ore back to the Command Center. Now, please tap &lt;color=#a0ff50&gt;Deselect&lt;/color&gt; first, then select another Construction Vehicle to harvest &lt;color=#a0ff50&gt;Gas Ore&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Key工程车晶体矿已运到基地……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>您的工程车已把第一批晶体矿运到基地，请查看左上角</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>晶体矿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>数量变化</t>
+    </r>
+  </si>
+  <si>
+    <t>Your Construction Vehicle has delivered the first batch of Crystal Ore to the Command Center. Check the &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; count in the top-left corner to see the change.</t>
+  </si>
+  <si>
+    <t>Key工程车造民房……</t>
+  </si>
+  <si>
+    <t>等您存够20晶体矿后，请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;民房&lt;/color&gt;按钮，再点击一次空旷地面</t>
+  </si>
+  <si>
+    <t>Once you have saved up 20 Crystal Ore, tap the &lt;color=#a0ff50&gt;Construction Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Supply Depot&lt;/color&gt; button, then tap an open spot on the ground again.</t>
+  </si>
+  <si>
+    <t>Key民房可提高活动单位上限……</t>
+  </si>
+  <si>
+    <t>很好，民房可以提升您的活动单位数量上限</t>
+  </si>
+  <si>
+    <t>Excellent—Supply Depots increase your mobile unit cap.</t>
+  </si>
+  <si>
+    <t>Key工程车造兵营……</t>
+  </si>
+  <si>
+    <t>等您存够30晶体矿后，请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;兵营&lt;/color&gt;按钮，再点击一次空旷地面，就能造出一个兵营</t>
+  </si>
+  <si>
+    <t>Once you have saved up 30 Crystal Ore, tap the &lt;color=#a0ff50&gt;Construction Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Barracks&lt;/color&gt; button, then tap an open spot on the ground again to build a Barracks.</t>
+  </si>
+  <si>
+    <t>Key兵营可产枪兵……</t>
+  </si>
+  <si>
+    <t>很好，兵营可以产出&lt;color=#a0ff50&gt;枪兵&lt;/color&gt;和&lt;color=#a0ff50&gt;近战兵&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Well done—the Barracks can produce &lt;color=#a0ff50&gt;Riflemen&lt;/color&gt; and &lt;color=#a0ff50&gt;Melee Infantry&lt;/color&gt;.</t>
+  </si>
+  <si>
+    <t>Key兵营造枪兵方法……</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;枪兵&lt;/color&gt;按钮，10秒后会在兵营旁造出一个枪兵</t>
+  </si>
+  <si>
+    <t>Please tap the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Rifleman&lt;/color&gt; button. A Rifleman will spawn next to the Barracks in 10 seconds.</t>
+  </si>
+  <si>
+    <t>Key枪兵移动方法……</t>
+  </si>
+  <si>
+    <t>点击选中您的枪兵，再点击地面，可以指挥他走向目标处</t>
+  </si>
+  <si>
+    <t>Tap to select your Rifleman, then tap the ground to command it to move to the target location.</t>
+  </si>
+  <si>
+    <t>Key让枪兵打怪……</t>
+  </si>
+  <si>
+    <t>现在已在左边给您刷了一个怪，控制兵走到怪附近，兵会自动打怪。您可以点右下角&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;，然后拖动地面看看怪在哪里</t>
+  </si>
+  <si>
+    <t>An enemy unit has been spawned on the left side for you. Move your troops near the enemy, and they will attack automatically. You can tap &lt;color=#a0ff50&gt;Deselect&lt;/color&gt; in the bottom-right corner, then drag the ground to locate the enemy.</t>
+  </si>
+  <si>
+    <t>Key多造兵去围攻敌人……</t>
+  </si>
+  <si>
+    <t>您的兵阵亡了。可以多造点兵去围攻敌人</t>
+  </si>
+  <si>
+    <t>Your troops have been defeated. You can build more troops to siege the enemy.</t>
+  </si>
+  <si>
+    <t>Key造地堡防守……</t>
+  </si>
+  <si>
+    <t>恭喜您消灭了敌人！现在左边给您刷了更多的怪。您可以造&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;地堡&lt;/color&gt;，让兵进入地堡中，立足防守，再伺机进攻</t>
+  </si>
+  <si>
+    <t>Congratulations on eliminating the enemy! More enemy units have been spawned on the left side for you. You can build &lt;color=#a0ff50&gt; Bunkers&lt;/color&gt; under &lt;color=#a0ff50&gt;Construction Units&lt;/color&gt;, garrison your troops inside to hold your ground defensively, then wait for the right moment to launch a counterattack.</t>
+  </si>
+  <si>
+    <t>Key您胜利是天才！</t>
+  </si>
+  <si>
+    <t>您取得了胜利！您真是指挥天才！</t>
+  </si>
+  <si>
+    <t>You have achieved victory! What a brilliant commander you are!</t>
+  </si>
+  <si>
+    <t>Key你的悟性很高……</t>
+  </si>
+  <si>
+    <t>，你的悟性很高，10分钟就完成了其他学员一个月才能完成的训练，为师甚是欣慰！</t>
+  </si>
+  <si>
+    <t>, You are an incredibly fast learner—you completed the training that takes other students a whole month in just 10 minutes. Your master is truly delighted!</t>
+  </si>
+  <si>
+    <t>Key我这都是些什么同学啊……</t>
+  </si>
+  <si>
+    <t>……我这都是些什么同学啊，这么简单的操作还要学一个月吗？</t>
+  </si>
+  <si>
+    <t>...What kind of classmates do I have? How can it take them a whole month to learn such simple controls?</t>
+  </si>
+  <si>
+    <t>Key世风不古……</t>
+  </si>
+  <si>
+    <t>唉，谁说不是呢！如今世风不古。遥想20年前，比你悟性更高的指挥天才比比皆是，大家经常自发研究切磋指挥技艺，更有无数学员的水平远超教官。实在令人怀念……</t>
+  </si>
+  <si>
+    <t>Sigh, tell me about it! The current generation just isn’t what it used to be. Thinking back to 20 years ago, there were countless commander prodigies with even greater aptitude than yours. Everyone would spontaneously study and exchange command skills, and countless students were far more skilled than their instructors. Those were truly the days...</t>
+  </si>
+  <si>
+    <t>Key这些前辈果真……</t>
+  </si>
+  <si>
+    <t>这些前辈果真如此厉害吗？学生倒是想领教领教！</t>
+  </si>
+  <si>
+    <t>Were those seniors really that amazing? This student would love to test their mettle!</t>
+  </si>
+  <si>
+    <t>Key克制关系……</t>
+  </si>
+  <si>
+    <t>在&lt;color=#a0ff50&gt;多人联机混战&lt;/color&gt;和&lt;color=#a0ff50&gt;其他人的多人战局列表&lt;/color&gt;可能会遇到他们，不要轻敌。要善用战斗单位的克制关系：
+  小兵 克制 坦克
+  坦克 克制 地堡和炮台
+  地堡和炮台 克制 小兵</t>
+  </si>
+  <si>
+    <t>In &lt;color=#a0ff50&gt;Multiplayer FFA&lt;/color&gt; and &lt;color=#a0ff50&gt;Other Players' Multiplayer Match List&lt;/color&gt;, you might run into them—never underestimate your opponents. Make good use of the unit counter relationships:
+    Infantry counter Tanks.
+    Tanks counter Bunkers and Gun Turrets
+    Bunkers and Gun Turrets counter Infantry</t>
+  </si>
+  <si>
+    <t>Key这些克制关系是怎么……</t>
+  </si>
+  <si>
+    <t>这些克制关系是怎么产生的呢？</t>
+  </si>
+  <si>
+    <t>How do these counter relationships work?</t>
+  </si>
+  <si>
+    <t>Key坦克和近战兵……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    坦克虽然伤害最高，但是价格昂贵，攻击前摇最久，移动速度最慢；&lt;color=#a0ff50&gt;前摇开始后炸点无法改变&lt;/color&gt;，敌方单位很容易躲开炸点，此外坦克炸点的爆炸溅射会伤害附近的己方单位。
+    近战兵移动速度快，攻击速度快，价格便宜，很容易躲开坦克炸点，也很容易在坦克攻击前摇结束之前将坦克打掉。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Although Tanks have the highest damage output, they are expensive, have the longest attack wind-up, and are the slowest-moving units; &lt;color=#a0ff50&gt;Once the attack wind-up starts, the blast point cannot be changed&lt;/color&gt;, so enemy units can easily dodge it. Additionally, the splash damage from the tank’s blast point will harm friendly units nearby.
+  Melee Infantry are fast-moving, quick to attack, and cheap. They can easily dodge tank blast points and take down tanks before the attack wind-up is complete.</t>
+  </si>
+  <si>
+    <t>Key坦克优势……</t>
+  </si>
+  <si>
+    <t>坦克，攻击距离最远，可以&lt;color=#a0ff50&gt;在炮台和地堡内单位的射程外攻击&lt;/color&gt;，是拆除建筑的利器。</t>
+  </si>
+  <si>
+    <t>Tanks have the longest attack range—they can &lt;color=#a0ff50&gt; attack from outside the range of Bunker and Gun Turret garrisons&lt;/color&gt;, making them excellent at destroying structures.</t>
+  </si>
+  <si>
+    <t>Key炮台介绍……</t>
+  </si>
+  <si>
+    <t>炮台价格便宜，攻击速度快，攻击距离仅次于坦克，集中放置后可对快速移动的敌方小兵群体造成有效伤害。</t>
+  </si>
+  <si>
+    <t>Gun Turrets are cheap, have a fast attack speed, and their attack range is second only to Tanks. When placed in groups, they can deal effective damage to swarms of fast-moving enemy infantry.</t>
+  </si>
+  <si>
+    <t>Key我会在实战中体会摸索。</t>
+  </si>
+  <si>
+    <t>我会在实战中体会摸索。</t>
+  </si>
+  <si>
+    <t>I will learn and adapt through actual combat.</t>
+  </si>
+  <si>
+    <t>Key推荐防守战和攻坚战……</t>
+  </si>
+  <si>
+    <t>一个人的时候，可以试试&lt;color=#a0ff50&gt;防守战&lt;/color&gt;，有助于体会炮台、坦克、地堡的特点。也可以试试&lt;color=#a0ff50&gt;攻坚战&lt;/color&gt;，练习步兵与坦克的配合</t>
+  </si>
+  <si>
+    <t>When playing alone, you can try &lt;color=#a0ff50&gt; Defensive Battles&lt;/color&gt; to better understand the characteristics of Gun Turrets, Tanks, and Bunkers. You can also try &lt;color=#a0ff50&gt; Assault Battles&lt;/color&gt; to practice coordinating Infantry and Tanks.</t>
+  </si>
+  <si>
+    <t>Key训练失败鼓励……</t>
+  </si>
+  <si>
+    <t>这只是一次训练，不必过于在意。失败是成功之母，待情绪平复可以再试一次。</t>
+  </si>
+  <si>
+    <t>This was just a training session—don’t dwell on it too much. Failure is the mother of success. You can try again when you’re feeling calmer.</t>
+  </si>
+  <si>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有阻挡</t>
+    </r>
+  </si>
+  <si>
+    <t>有阻挡</t>
+  </si>
+  <si>
+    <t>Obstructed</t>
+  </si>
+  <si>
+    <t>Key晶体矿不足</t>
+  </si>
+  <si>
+    <t>晶体矿不足</t>
+  </si>
+  <si>
+    <t>Insufficient Crystal Ore</t>
+  </si>
+  <si>
+    <t>Key燃气矿不足</t>
+  </si>
+  <si>
+    <t>燃气矿不足</t>
+  </si>
+  <si>
+    <t>Insufficient Gas Ore</t>
+  </si>
+  <si>
+    <t>Key燃气矿不足，不能解锁</t>
+  </si>
+  <si>
+    <t>燃气矿不足，不能解锁</t>
+  </si>
+  <si>
+    <t>Insufficient Gas Ore. Unlocking unavailable</t>
+  </si>
+  <si>
+    <t>Key晶体矿不足，不能解锁</t>
+  </si>
+  <si>
+    <t>晶体矿不足，不能解锁</t>
+  </si>
+  <si>
+    <t>Insufficient Crystal Ore. Unlocking unavailable</t>
+  </si>
+  <si>
+    <t>Key蜕变进度{}/{}</t>
+  </si>
+  <si>
+    <r>
+      <t>蜕变进度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}/{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Metamorphosis Progress {}/{}</t>
+  </si>
+  <si>
+    <t>Key待造队列{},当前单位进度{}/{}</t>
+  </si>
+  <si>
+    <r>
+      <t>待造队列</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{},</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当前单位进度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}/{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Queue Pending Construction {}, Current Unit Progress {}/{}</t>
+  </si>
+  <si>
+    <t>Key走向建造点</t>
+  </si>
+  <si>
+    <t>走向建造点</t>
+  </si>
+  <si>
+    <t>Key造完了</t>
+  </si>
+  <si>
+    <t>造完了</t>
+  </si>
+  <si>
+    <t>Key建造完成</t>
+  </si>
+  <si>
+    <t>建造完成</t>
+  </si>
+  <si>
+    <t>Key民房不足</t>
+  </si>
+  <si>
+    <t>民房不足</t>
+  </si>
+  <si>
+    <t>Key房虫不足</t>
+  </si>
+  <si>
+    <t>房虫不足</t>
+  </si>
+  <si>
+    <t>Key正在建造</t>
+  </si>
+  <si>
+    <t>正在建造</t>
   </si>
 </sst>
 </file>
@@ -2530,13 +3257,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="4"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -2557,6 +3277,13 @@
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3037,10 +3764,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -3167,7 +3894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3219,6 +3946,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3226,44 +3956,44 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="6" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
@@ -3279,6 +4009,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3668,20 +4401,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="37" customFormat="1" spans="1:18">
-      <c r="A2" s="37">
+    <row r="2" s="38" customFormat="1" spans="1:18">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="37">
-        <v>0</v>
-      </c>
-      <c r="G2" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="37">
+      <c r="C2" s="38">
+        <v>0</v>
+      </c>
+      <c r="G2" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="38">
         <v>1</v>
       </c>
       <c r="J2">
@@ -3690,33 +4423,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="37">
-        <v>1</v>
-      </c>
-      <c r="N2" s="37">
-        <v>0</v>
-      </c>
-      <c r="O2" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="37" customFormat="1" spans="1:18">
-      <c r="A3" s="37">
+      <c r="M2" s="38">
+        <v>1</v>
+      </c>
+      <c r="N2" s="38">
+        <v>0</v>
+      </c>
+      <c r="O2" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="38" customFormat="1" spans="1:18">
+      <c r="A3" s="38">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="37">
-        <v>0</v>
-      </c>
-      <c r="G3" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="37">
+      <c r="C3" s="38">
+        <v>0</v>
+      </c>
+      <c r="G3" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="38">
         <v>1</v>
       </c>
       <c r="J3">
@@ -3725,36 +4458,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="37">
-        <v>1</v>
-      </c>
-      <c r="N3" s="37">
-        <v>0</v>
-      </c>
-      <c r="O3" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="32" customFormat="1" spans="1:18">
-      <c r="A4" s="32">
+      <c r="M3" s="38">
+        <v>1</v>
+      </c>
+      <c r="N3" s="38">
+        <v>0</v>
+      </c>
+      <c r="O3" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="33" customFormat="1" spans="1:18">
+      <c r="A4" s="33">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <v>2</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="37">
+      <c r="G4" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="38">
         <v>1</v>
       </c>
       <c r="J4">
@@ -3763,36 +4496,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="37">
-        <v>1</v>
-      </c>
-      <c r="N4" s="37">
-        <v>0</v>
-      </c>
-      <c r="O4" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A5" s="32">
+      <c r="M4" s="38">
+        <v>1</v>
+      </c>
+      <c r="N4" s="38">
+        <v>0</v>
+      </c>
+      <c r="O4" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A5" s="33">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="32">
-        <v>0</v>
-      </c>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="33">
+        <v>0</v>
+      </c>
+      <c r="D5" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="37">
+      <c r="G5" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="38">
         <v>1</v>
       </c>
       <c r="J5">
@@ -3801,48 +4534,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="37">
-        <v>1</v>
-      </c>
-      <c r="N5" s="37">
-        <v>0</v>
-      </c>
-      <c r="O5" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="32">
+      <c r="M5" s="38">
+        <v>1</v>
+      </c>
+      <c r="N5" s="38">
+        <v>0</v>
+      </c>
+      <c r="O5" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="33">
         <v>0</v>
       </c>
       <c r="R5" s="23" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="38" customFormat="1" spans="1:18">
-      <c r="A6" s="38">
+    <row r="6" s="39" customFormat="1" spans="1:18">
+      <c r="A6" s="39">
         <v>101</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="38">
-        <v>0</v>
-      </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="39">
+        <v>0</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="37" t="b">
+      <c r="G6" s="38" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="38">
         <v>1</v>
       </c>
       <c r="J6">
@@ -3854,39 +4587,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="37">
-        <v>1</v>
-      </c>
-      <c r="N6" s="37">
-        <v>0</v>
-      </c>
-      <c r="O6" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="38" customFormat="1" spans="1:18">
-      <c r="A7" s="38">
+      <c r="M6" s="38">
+        <v>1</v>
+      </c>
+      <c r="N6" s="38">
+        <v>0</v>
+      </c>
+      <c r="O6" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="39" customFormat="1" spans="1:18">
+      <c r="A7" s="39">
         <v>102</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="38">
-        <v>0</v>
-      </c>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="39">
+        <v>0</v>
+      </c>
+      <c r="D7" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="37">
+      <c r="G7" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="38">
         <v>1</v>
       </c>
       <c r="J7">
@@ -3895,16 +4628,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="37">
-        <v>1</v>
-      </c>
-      <c r="N7" s="37">
-        <v>0</v>
-      </c>
-      <c r="O7" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="38">
+      <c r="M7" s="38">
+        <v>1</v>
+      </c>
+      <c r="N7" s="38">
+        <v>0</v>
+      </c>
+      <c r="O7" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="39">
         <v>0</v>
       </c>
     </row>
@@ -3927,13 +4660,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="37" t="b">
+      <c r="G8" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="38">
         <v>1</v>
       </c>
       <c r="J8">
@@ -3945,13 +4678,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="37">
-        <v>1</v>
-      </c>
-      <c r="N8" s="37">
-        <v>0</v>
-      </c>
-      <c r="O8" s="37">
+      <c r="M8" s="38">
+        <v>1</v>
+      </c>
+      <c r="N8" s="38">
+        <v>0</v>
+      </c>
+      <c r="O8" s="38">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -3964,56 +4697,56 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="31" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A9" s="31">
+    <row r="9" s="32" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A9" s="32">
         <v>202</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="31">
-        <v>1</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="32">
+        <v>1</v>
+      </c>
+      <c r="D9" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="G9" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="21">
-        <v>1</v>
-      </c>
-      <c r="J9" s="31">
-        <v>0</v>
-      </c>
-      <c r="K9" s="31">
+      <c r="I9" s="40">
+        <v>1</v>
+      </c>
+      <c r="J9" s="32">
+        <v>0</v>
+      </c>
+      <c r="K9" s="32">
         <v>2</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L9" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="21">
-        <v>1</v>
-      </c>
-      <c r="N9" s="21">
-        <v>0</v>
-      </c>
-      <c r="O9" s="21">
-        <v>0</v>
-      </c>
-      <c r="P9" s="31" t="s">
+      <c r="M9" s="40">
+        <v>1</v>
+      </c>
+      <c r="N9" s="40">
+        <v>0</v>
+      </c>
+      <c r="O9" s="40">
+        <v>0</v>
+      </c>
+      <c r="P9" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="31">
+      <c r="Q9" s="32">
         <v>3</v>
       </c>
       <c r="R9" s="23" t="s">
@@ -4039,13 +4772,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="37" t="b">
+      <c r="G10" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="38">
         <v>1</v>
       </c>
       <c r="J10">
@@ -4057,13 +4790,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="37">
-        <v>1</v>
-      </c>
-      <c r="N10" s="37">
-        <v>0</v>
-      </c>
-      <c r="O10" s="37">
+      <c r="M10" s="38">
+        <v>1</v>
+      </c>
+      <c r="N10" s="38">
+        <v>0</v>
+      </c>
+      <c r="O10" s="38">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -4092,13 +4825,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="37" t="b">
+      <c r="G11" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="38">
         <v>1</v>
       </c>
       <c r="J11">
@@ -4110,13 +4843,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="37">
-        <v>1</v>
-      </c>
-      <c r="N11" s="37">
-        <v>0</v>
-      </c>
-      <c r="O11" s="37">
+      <c r="M11" s="38">
+        <v>1</v>
+      </c>
+      <c r="N11" s="38">
+        <v>0</v>
+      </c>
+      <c r="O11" s="38">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -4148,13 +4881,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="37" t="b">
+      <c r="G12" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="38">
         <v>1</v>
       </c>
       <c r="J12">
@@ -4166,13 +4899,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="37">
-        <v>1</v>
-      </c>
-      <c r="N12" s="37">
-        <v>0</v>
-      </c>
-      <c r="O12" s="37">
+      <c r="M12" s="38">
+        <v>1</v>
+      </c>
+      <c r="N12" s="38">
+        <v>0</v>
+      </c>
+      <c r="O12" s="38">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -4204,13 +4937,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="37" t="b">
+      <c r="G13" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="38">
         <v>1</v>
       </c>
       <c r="J13">
@@ -4222,13 +4955,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="37">
-        <v>1</v>
-      </c>
-      <c r="N13" s="37">
-        <v>1</v>
-      </c>
-      <c r="O13" s="37">
+      <c r="M13" s="38">
+        <v>1</v>
+      </c>
+      <c r="N13" s="38">
+        <v>1</v>
+      </c>
+      <c r="O13" s="38">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -4257,16 +4990,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="37" t="b">
+      <c r="G14" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <v>1</v>
       </c>
       <c r="J14">
@@ -4278,13 +5011,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="37">
-        <v>1</v>
-      </c>
-      <c r="N14" s="37">
-        <v>0</v>
-      </c>
-      <c r="O14" s="37">
+      <c r="M14" s="38">
+        <v>1</v>
+      </c>
+      <c r="N14" s="38">
+        <v>0</v>
+      </c>
+      <c r="O14" s="38">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -4313,16 +5046,16 @@
       <c r="E15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="39" t="s">
+      <c r="F15" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="37" t="b">
+      <c r="G15" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="38">
         <v>1</v>
       </c>
       <c r="J15">
@@ -4334,13 +5067,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="37">
-        <v>1</v>
-      </c>
-      <c r="N15" s="37">
-        <v>0</v>
-      </c>
-      <c r="O15" s="37">
+      <c r="M15" s="38">
+        <v>1</v>
+      </c>
+      <c r="N15" s="38">
+        <v>0</v>
+      </c>
+      <c r="O15" s="38">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -4372,13 +5105,13 @@
       <c r="F16" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="37" t="b">
+      <c r="G16" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="38">
         <v>1</v>
       </c>
       <c r="J16">
@@ -4390,13 +5123,13 @@
       <c r="L16" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="37">
-        <v>1</v>
-      </c>
-      <c r="N16" s="37">
-        <v>0</v>
-      </c>
-      <c r="O16" s="37">
+      <c r="M16" s="38">
+        <v>1</v>
+      </c>
+      <c r="N16" s="38">
+        <v>0</v>
+      </c>
+      <c r="O16" s="38">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -4428,13 +5161,13 @@
       <c r="F17" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="37" t="b">
+      <c r="G17" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="38">
         <v>1</v>
       </c>
       <c r="J17">
@@ -4446,13 +5179,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="37">
-        <v>1</v>
-      </c>
-      <c r="N17" s="37">
-        <v>0</v>
-      </c>
-      <c r="O17" s="37">
+      <c r="M17" s="38">
+        <v>1</v>
+      </c>
+      <c r="N17" s="38">
+        <v>0</v>
+      </c>
+      <c r="O17" s="38">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -4478,10 +5211,10 @@
       <c r="D18" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="37">
+      <c r="G18" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="38">
         <v>1</v>
       </c>
       <c r="J18">
@@ -4490,13 +5223,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="37">
-        <v>1</v>
-      </c>
-      <c r="N18" s="37">
-        <v>0</v>
-      </c>
-      <c r="O18" s="37">
+      <c r="M18" s="38">
+        <v>1</v>
+      </c>
+      <c r="N18" s="38">
+        <v>0</v>
+      </c>
+      <c r="O18" s="38">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -4522,13 +5255,13 @@
       <c r="F19" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="37" t="b">
+      <c r="G19" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="38">
         <v>1</v>
       </c>
       <c r="J19">
@@ -4540,13 +5273,13 @@
       <c r="L19" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="37">
-        <v>1</v>
-      </c>
-      <c r="N19" s="37">
-        <v>0</v>
-      </c>
-      <c r="O19" s="37">
+      <c r="M19" s="38">
+        <v>1</v>
+      </c>
+      <c r="N19" s="38">
+        <v>0</v>
+      </c>
+      <c r="O19" s="38">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -4578,13 +5311,13 @@
       <c r="F20" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="37" t="b">
+      <c r="G20" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="38">
         <v>1</v>
       </c>
       <c r="J20">
@@ -4596,13 +5329,13 @@
       <c r="L20" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="37">
-        <v>1</v>
-      </c>
-      <c r="N20" s="37">
-        <v>0</v>
-      </c>
-      <c r="O20" s="37">
+      <c r="M20" s="38">
+        <v>1</v>
+      </c>
+      <c r="N20" s="38">
+        <v>0</v>
+      </c>
+      <c r="O20" s="38">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -4634,13 +5367,13 @@
       <c r="F21" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="37" t="b">
+      <c r="G21" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="38">
         <v>1</v>
       </c>
       <c r="J21">
@@ -4652,13 +5385,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="37">
-        <v>1</v>
-      </c>
-      <c r="N21" s="37">
-        <v>0</v>
-      </c>
-      <c r="O21" s="37">
+      <c r="M21" s="38">
+        <v>1</v>
+      </c>
+      <c r="N21" s="38">
+        <v>0</v>
+      </c>
+      <c r="O21" s="38">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -4690,13 +5423,13 @@
       <c r="F22" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="37" t="b">
+      <c r="G22" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="37">
+      <c r="I22" s="38">
         <v>1</v>
       </c>
       <c r="J22">
@@ -4708,13 +5441,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="37">
-        <v>1</v>
-      </c>
-      <c r="N22" s="37">
-        <v>0</v>
-      </c>
-      <c r="O22" s="37">
+      <c r="M22" s="38">
+        <v>1</v>
+      </c>
+      <c r="N22" s="38">
+        <v>0</v>
+      </c>
+      <c r="O22" s="38">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -4727,32 +5460,32 @@
         <v>122</v>
       </c>
     </row>
-    <row r="23" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A23" s="32">
+    <row r="23" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A23" s="33">
         <v>301</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="32">
-        <v>1</v>
-      </c>
-      <c r="D23" s="32" t="s">
+      <c r="C23" s="33">
+        <v>1</v>
+      </c>
+      <c r="D23" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="32" t="s">
+      <c r="G23" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="38">
         <v>1</v>
       </c>
       <c r="J23">
@@ -4761,54 +5494,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="32" t="s">
+      <c r="L23" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="M23" s="37">
-        <v>1</v>
-      </c>
-      <c r="N23" s="37">
-        <v>0</v>
-      </c>
-      <c r="O23" s="37">
-        <v>0</v>
-      </c>
-      <c r="P23" s="32" t="s">
+      <c r="M23" s="38">
+        <v>1</v>
+      </c>
+      <c r="N23" s="38">
+        <v>0</v>
+      </c>
+      <c r="O23" s="38">
+        <v>0</v>
+      </c>
+      <c r="P23" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="33">
         <v>3</v>
       </c>
       <c r="R23" s="23" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A24" s="32">
+    <row r="24" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A24" s="33">
         <v>302</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="32">
-        <v>1</v>
-      </c>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="33">
+        <v>1</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="G24" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="32" t="s">
+      <c r="G24" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="38">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -4817,51 +5550,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="M24" s="37">
-        <v>1</v>
-      </c>
-      <c r="N24" s="37">
-        <v>0</v>
-      </c>
-      <c r="O24" s="37">
-        <v>0</v>
-      </c>
-      <c r="P24" s="32" t="s">
+      <c r="M24" s="38">
+        <v>1</v>
+      </c>
+      <c r="N24" s="38">
+        <v>0</v>
+      </c>
+      <c r="O24" s="38">
+        <v>0</v>
+      </c>
+      <c r="P24" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>3</v>
       </c>
       <c r="R24" s="23" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A25" s="32">
+    <row r="25" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A25" s="33">
         <v>303</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="32">
-        <v>1</v>
-      </c>
-      <c r="D25" s="32" t="s">
+      <c r="C25" s="33">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="32" t="s">
+      <c r="G25" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="38">
         <v>1</v>
       </c>
       <c r="J25">
@@ -4870,51 +5603,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="37">
-        <v>1</v>
-      </c>
-      <c r="N25" s="37">
-        <v>0</v>
-      </c>
-      <c r="O25" s="37">
-        <v>0</v>
-      </c>
-      <c r="P25" s="32" t="s">
+      <c r="M25" s="38">
+        <v>1</v>
+      </c>
+      <c r="N25" s="38">
+        <v>0</v>
+      </c>
+      <c r="O25" s="38">
+        <v>0</v>
+      </c>
+      <c r="P25" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>3</v>
       </c>
       <c r="R25" s="23" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A26" s="32">
+    <row r="26" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A26" s="33">
         <v>304</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="32">
-        <v>1</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="C26" s="33">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="32" t="s">
+      <c r="G26" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="38">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -4923,54 +5656,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="32" t="s">
+      <c r="L26" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="37">
-        <v>1</v>
-      </c>
-      <c r="N26" s="37">
-        <v>0</v>
-      </c>
-      <c r="O26" s="37">
-        <v>0</v>
-      </c>
-      <c r="P26" s="32" t="s">
+      <c r="M26" s="38">
+        <v>1</v>
+      </c>
+      <c r="N26" s="38">
+        <v>0</v>
+      </c>
+      <c r="O26" s="38">
+        <v>0</v>
+      </c>
+      <c r="P26" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Q26" s="32">
+      <c r="Q26" s="33">
         <v>3</v>
       </c>
       <c r="R26" s="23" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A27" s="32">
+    <row r="27" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A27" s="33">
         <v>305</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>3</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="33" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="33" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="32" t="s">
+      <c r="G27" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="38">
         <v>1</v>
       </c>
       <c r="J27">
@@ -4982,51 +5715,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="37">
-        <v>1</v>
-      </c>
-      <c r="N27" s="37">
-        <v>0</v>
-      </c>
-      <c r="O27" s="37">
-        <v>0</v>
-      </c>
-      <c r="P27" s="32" t="s">
+      <c r="M27" s="38">
+        <v>1</v>
+      </c>
+      <c r="N27" s="38">
+        <v>0</v>
+      </c>
+      <c r="O27" s="38">
+        <v>0</v>
+      </c>
+      <c r="P27" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="33">
         <v>3</v>
       </c>
       <c r="R27" s="23" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="28" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A28" s="32">
+    <row r="28" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A28" s="33">
         <v>306</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>2</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="G28" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="32">
-        <v>0</v>
-      </c>
-      <c r="I28" s="37">
+      <c r="G28" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="33">
+        <v>0</v>
+      </c>
+      <c r="I28" s="38">
         <v>1</v>
       </c>
       <c r="J28">
@@ -5035,54 +5768,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="32">
-        <v>1</v>
-      </c>
-      <c r="M28" s="37">
-        <v>1</v>
-      </c>
-      <c r="N28" s="37">
-        <v>0</v>
-      </c>
-      <c r="O28" s="37">
-        <v>0</v>
-      </c>
-      <c r="P28" s="32" t="s">
+      <c r="L28" s="33">
+        <v>1</v>
+      </c>
+      <c r="M28" s="38">
+        <v>1</v>
+      </c>
+      <c r="N28" s="38">
+        <v>0</v>
+      </c>
+      <c r="O28" s="38">
+        <v>0</v>
+      </c>
+      <c r="P28" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="33">
         <v>3</v>
       </c>
       <c r="R28" s="23" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A29" s="32">
+    <row r="29" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A29" s="33">
         <v>307</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="32">
-        <v>1</v>
-      </c>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="33">
+        <v>1</v>
+      </c>
+      <c r="D29" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="G29" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="32" t="s">
+      <c r="G29" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="38">
         <v>1</v>
       </c>
       <c r="J29">
@@ -5091,54 +5824,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="32" t="s">
+      <c r="L29" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <v>0.1</v>
       </c>
-      <c r="N29" s="37">
-        <v>0</v>
-      </c>
-      <c r="O29" s="37">
+      <c r="N29" s="38">
+        <v>0</v>
+      </c>
+      <c r="O29" s="38">
         <v>0.17</v>
       </c>
-      <c r="P29" s="32" t="s">
+      <c r="P29" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="33">
         <v>3</v>
       </c>
       <c r="R29" s="23" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A30" s="32">
+    <row r="30" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A30" s="33">
         <v>308</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="32">
-        <v>1</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="33">
+        <v>1</v>
+      </c>
+      <c r="D30" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="32" t="s">
+      <c r="G30" s="38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="38">
         <v>1</v>
       </c>
       <c r="J30">
@@ -5147,54 +5880,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="32" t="s">
+      <c r="L30" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="M30" s="37">
-        <v>1</v>
-      </c>
-      <c r="N30" s="37">
-        <v>0</v>
-      </c>
-      <c r="O30" s="37">
-        <v>0</v>
-      </c>
-      <c r="P30" s="32" t="s">
+      <c r="M30" s="38">
+        <v>1</v>
+      </c>
+      <c r="N30" s="38">
+        <v>0</v>
+      </c>
+      <c r="O30" s="38">
+        <v>0</v>
+      </c>
+      <c r="P30" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="33">
         <v>3</v>
       </c>
       <c r="R30" s="23" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A31" s="32">
+    <row r="31" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A31" s="33">
         <v>309</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="33">
         <v>2</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="32" t="s">
+      <c r="G31" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="38">
         <v>1</v>
       </c>
       <c r="J31">
@@ -5203,54 +5936,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="32" t="s">
+      <c r="L31" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="M31" s="37">
-        <v>1</v>
-      </c>
-      <c r="N31" s="37">
-        <v>0</v>
-      </c>
-      <c r="O31" s="37">
-        <v>0</v>
-      </c>
-      <c r="P31" s="32" t="s">
+      <c r="M31" s="38">
+        <v>1</v>
+      </c>
+      <c r="N31" s="38">
+        <v>0</v>
+      </c>
+      <c r="O31" s="38">
+        <v>0</v>
+      </c>
+      <c r="P31" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="Q31" s="32">
+      <c r="Q31" s="33">
         <v>3</v>
       </c>
       <c r="R31" s="23" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="32" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A32" s="32">
+    <row r="32" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A32" s="33">
         <v>310</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="33">
         <v>2</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="G32" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="32" t="s">
+      <c r="G32" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="38">
         <v>1</v>
       </c>
       <c r="J32">
@@ -5259,54 +5992,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="32" t="s">
+      <c r="L32" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="M32" s="37">
-        <v>1</v>
-      </c>
-      <c r="N32" s="37">
-        <v>0</v>
-      </c>
-      <c r="O32" s="37">
-        <v>0</v>
-      </c>
-      <c r="P32" s="32" t="s">
+      <c r="M32" s="38">
+        <v>1</v>
+      </c>
+      <c r="N32" s="38">
+        <v>0</v>
+      </c>
+      <c r="O32" s="38">
+        <v>0</v>
+      </c>
+      <c r="P32" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="Q32" s="32">
+      <c r="Q32" s="33">
         <v>4</v>
       </c>
       <c r="R32" s="23" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="33" s="32" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A33" s="32">
+    <row r="33" s="33" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A33" s="33">
         <v>311</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>2</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="F33" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="G33" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="32">
-        <v>0</v>
-      </c>
-      <c r="I33" s="37">
+      <c r="G33" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="33">
+        <v>0</v>
+      </c>
+      <c r="I33" s="38">
         <v>1</v>
       </c>
       <c r="J33">
@@ -5315,45 +6048,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="32">
-        <v>1</v>
-      </c>
-      <c r="M33" s="37">
-        <v>1</v>
-      </c>
-      <c r="N33" s="37">
-        <v>0</v>
-      </c>
-      <c r="O33" s="37">
-        <v>0</v>
-      </c>
-      <c r="P33" s="32" t="s">
+      <c r="L33" s="33">
+        <v>1</v>
+      </c>
+      <c r="M33" s="38">
+        <v>1</v>
+      </c>
+      <c r="N33" s="38">
+        <v>0</v>
+      </c>
+      <c r="O33" s="38">
+        <v>0</v>
+      </c>
+      <c r="P33" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="33">
         <v>3</v>
       </c>
       <c r="R33" s="23" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" s="32" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A34" s="32">
+    <row r="34" s="33" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A34" s="33">
         <v>312</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>2</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="G34" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="37">
+      <c r="G34" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="38">
         <v>1</v>
       </c>
       <c r="J34">
@@ -5362,45 +6095,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="37">
-        <v>1</v>
-      </c>
-      <c r="N34" s="37">
-        <v>0</v>
-      </c>
-      <c r="O34" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="32">
+      <c r="M34" s="38">
+        <v>1</v>
+      </c>
+      <c r="N34" s="38">
+        <v>0</v>
+      </c>
+      <c r="O34" s="38">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="33">
         <v>1</v>
       </c>
       <c r="R34" s="23" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="35" s="20" customFormat="1" spans="1:21">
-      <c r="A35" s="20">
+    <row r="35" s="31" customFormat="1" spans="1:21">
+      <c r="A35" s="31">
         <v>401</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="31">
         <v>2</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="39" t="s">
+      <c r="F35" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="20" t="s">
+      <c r="G35" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="38">
         <v>1</v>
       </c>
       <c r="J35">
@@ -5412,45 +6145,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="37">
-        <v>1</v>
-      </c>
-      <c r="N35" s="37">
-        <v>0</v>
-      </c>
-      <c r="O35" s="37">
-        <v>0</v>
-      </c>
-      <c r="P35" s="20" t="s">
+      <c r="M35" s="38">
+        <v>1</v>
+      </c>
+      <c r="N35" s="38">
+        <v>0</v>
+      </c>
+      <c r="O35" s="38">
+        <v>0</v>
+      </c>
+      <c r="P35" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="20">
+      <c r="Q35" s="31">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="20" customFormat="1" spans="1:21">
-      <c r="A36" s="20">
+    <row r="36" s="31" customFormat="1" spans="1:21">
+      <c r="A36" s="31">
         <v>402</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="31">
         <v>2</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="40" t="s">
+      <c r="F36" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="20" t="s">
+      <c r="G36" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="38">
         <v>1</v>
       </c>
       <c r="J36">
@@ -5462,48 +6195,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="37">
-        <v>1</v>
-      </c>
-      <c r="N36" s="37">
-        <v>0</v>
-      </c>
-      <c r="O36" s="37">
-        <v>0</v>
-      </c>
-      <c r="P36" s="20" t="s">
+      <c r="M36" s="38">
+        <v>1</v>
+      </c>
+      <c r="N36" s="38">
+        <v>0</v>
+      </c>
+      <c r="O36" s="38">
+        <v>0</v>
+      </c>
+      <c r="P36" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="Q36" s="20">
+      <c r="Q36" s="31">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="20" customFormat="1" spans="1:21">
-      <c r="A37" s="20">
+    <row r="37" s="31" customFormat="1" spans="1:21">
+      <c r="A37" s="31">
         <v>403</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="31">
         <v>2</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F37" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="20" t="s">
+      <c r="G37" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="37">
+      <c r="I37" s="38">
         <v>1</v>
       </c>
       <c r="J37">
@@ -5512,80 +6245,80 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="20" t="s">
+      <c r="L37" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="37">
-        <v>1</v>
-      </c>
-      <c r="N37" s="37">
-        <v>0</v>
-      </c>
-      <c r="O37" s="37">
-        <v>0</v>
-      </c>
-      <c r="P37" s="20" t="s">
+      <c r="M37" s="38">
+        <v>1</v>
+      </c>
+      <c r="N37" s="38">
+        <v>0</v>
+      </c>
+      <c r="O37" s="38">
+        <v>0</v>
+      </c>
+      <c r="P37" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="20">
+      <c r="Q37" s="31">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="21" customFormat="1" spans="1:21">
-      <c r="A38" s="21">
+    <row r="38" s="40" customFormat="1" spans="1:21">
+      <c r="A38" s="40">
         <v>404</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="21">
-        <v>1</v>
-      </c>
-      <c r="D38" s="31" t="s">
+      <c r="C38" s="40">
+        <v>1</v>
+      </c>
+      <c r="D38" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="21" t="s">
+      <c r="G38" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="21">
-        <v>1</v>
-      </c>
-      <c r="J38" s="31">
-        <v>0</v>
-      </c>
-      <c r="K38" s="31">
+      <c r="I38" s="40">
+        <v>1</v>
+      </c>
+      <c r="J38" s="32">
+        <v>0</v>
+      </c>
+      <c r="K38" s="32">
         <v>2</v>
       </c>
-      <c r="L38" s="21" t="s">
+      <c r="L38" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="21">
-        <v>1</v>
-      </c>
-      <c r="N38" s="21">
-        <v>0</v>
-      </c>
-      <c r="O38" s="21">
-        <v>0</v>
-      </c>
-      <c r="P38" s="21" t="s">
+      <c r="M38" s="40">
+        <v>1</v>
+      </c>
+      <c r="N38" s="40">
+        <v>0</v>
+      </c>
+      <c r="O38" s="40">
+        <v>0</v>
+      </c>
+      <c r="P38" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="21">
+      <c r="Q38" s="40">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="20" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A39" s="20">
+    <row r="39" s="31" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A39" s="31">
         <v>405</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -5603,13 +6336,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="37" t="b">
+      <c r="G39" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="37">
+      <c r="I39" s="38">
         <v>1</v>
       </c>
       <c r="J39">
@@ -5621,13 +6354,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="37">
-        <v>1</v>
-      </c>
-      <c r="N39" s="37">
-        <v>0</v>
-      </c>
-      <c r="O39" s="37">
+      <c r="M39" s="38">
+        <v>1</v>
+      </c>
+      <c r="N39" s="38">
+        <v>0</v>
+      </c>
+      <c r="O39" s="38">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -5641,32 +6374,32 @@
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="20" customFormat="1" spans="1:21">
-      <c r="A40" s="20">
+    <row r="40" s="31" customFormat="1" spans="1:21">
+      <c r="A40" s="31">
         <v>406</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="20">
-        <v>1</v>
-      </c>
-      <c r="D40" s="20" t="s">
+      <c r="C40" s="31">
+        <v>1</v>
+      </c>
+      <c r="D40" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="31" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="20">
-        <v>0</v>
-      </c>
-      <c r="I40" s="37">
+      <c r="G40" s="38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="31">
+        <v>0</v>
+      </c>
+      <c r="I40" s="38">
         <v>1</v>
       </c>
       <c r="J40">
@@ -5675,27 +6408,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="20">
+      <c r="L40" s="31">
         <v>3</v>
       </c>
-      <c r="M40" s="37">
-        <v>1</v>
-      </c>
-      <c r="N40" s="37">
-        <v>0</v>
-      </c>
-      <c r="O40" s="37">
-        <v>0</v>
-      </c>
-      <c r="P40" s="20" t="s">
+      <c r="M40" s="38">
+        <v>1</v>
+      </c>
+      <c r="N40" s="38">
+        <v>0</v>
+      </c>
+      <c r="O40" s="38">
+        <v>0</v>
+      </c>
+      <c r="P40" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="20">
+      <c r="Q40" s="31">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="20">
+      <c r="A41" s="31">
         <v>407</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -5713,13 +6446,13 @@
       <c r="F41" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="37" t="b">
+      <c r="G41" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>88</v>
       </c>
-      <c r="I41" s="37">
+      <c r="I41" s="38">
         <v>1</v>
       </c>
       <c r="J41">
@@ -5731,13 +6464,13 @@
       <c r="L41" t="s">
         <v>89</v>
       </c>
-      <c r="M41" s="37">
-        <v>1</v>
-      </c>
-      <c r="N41" s="37">
-        <v>0</v>
-      </c>
-      <c r="O41" s="37">
+      <c r="M41" s="38">
+        <v>1</v>
+      </c>
+      <c r="N41" s="38">
+        <v>0</v>
+      </c>
+      <c r="O41" s="38">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -5748,7 +6481,7 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="20">
+      <c r="A42" s="31">
         <v>408</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -5766,13 +6499,13 @@
       <c r="F42" t="s">
         <v>110</v>
       </c>
-      <c r="G42" s="37" t="b">
+      <c r="G42" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="38">
         <v>1</v>
       </c>
       <c r="J42">
@@ -5784,13 +6517,13 @@
       <c r="L42" t="s">
         <v>104</v>
       </c>
-      <c r="M42" s="37">
-        <v>1</v>
-      </c>
-      <c r="N42" s="37">
-        <v>0</v>
-      </c>
-      <c r="O42" s="37">
+      <c r="M42" s="38">
+        <v>1</v>
+      </c>
+      <c r="N42" s="38">
+        <v>0</v>
+      </c>
+      <c r="O42" s="38">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -5801,7 +6534,7 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="20">
+      <c r="A43" s="31">
         <v>409</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -5819,13 +6552,13 @@
       <c r="F43" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="37" t="b">
+      <c r="G43" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="37">
+      <c r="I43" s="38">
         <v>1</v>
       </c>
       <c r="J43">
@@ -5837,13 +6570,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="37">
-        <v>1</v>
-      </c>
-      <c r="N43" s="37">
-        <v>0</v>
-      </c>
-      <c r="O43" s="37">
+      <c r="M43" s="38">
+        <v>1</v>
+      </c>
+      <c r="N43" s="38">
+        <v>0</v>
+      </c>
+      <c r="O43" s="38">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -5854,7 +6587,7 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="20">
+      <c r="A44" s="31">
         <v>410</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -5872,13 +6605,13 @@
       <c r="F44" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="37" t="b">
+      <c r="G44" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="38">
         <v>1</v>
       </c>
       <c r="J44">
@@ -5890,13 +6623,13 @@
       <c r="L44" t="s">
         <v>104</v>
       </c>
-      <c r="M44" s="37">
-        <v>1</v>
-      </c>
-      <c r="N44" s="37">
-        <v>0</v>
-      </c>
-      <c r="O44" s="37">
+      <c r="M44" s="38">
+        <v>1</v>
+      </c>
+      <c r="N44" s="38">
+        <v>0</v>
+      </c>
+      <c r="O44" s="38">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -5907,7 +6640,7 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="20">
+      <c r="A45" s="31">
         <v>411</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -5925,13 +6658,13 @@
       <c r="F45" t="s">
         <v>121</v>
       </c>
-      <c r="G45" s="37" t="b">
+      <c r="G45" s="38" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="37">
+      <c r="I45" s="38">
         <v>1</v>
       </c>
       <c r="J45">
@@ -5943,13 +6676,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="37">
-        <v>1</v>
-      </c>
-      <c r="N45" s="37">
-        <v>0</v>
-      </c>
-      <c r="O45" s="37">
+      <c r="M45" s="38">
+        <v>1</v>
+      </c>
+      <c r="N45" s="38">
+        <v>0</v>
+      </c>
+      <c r="O45" s="38">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -6826,11 +7559,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C129"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="28.875" customWidth="1"/>
-    <col min="2" max="2" width="44.5" customWidth="1"/>
+    <col min="1" max="1" width="30.875" customWidth="1"/>
+    <col min="2" max="2" width="78.75" customWidth="1"/>
     <col min="3" max="3" width="255.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6922,7 +7655,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="9" ht="25.5" spans="1:3">
+    <row r="9" ht="14.25" spans="1:3">
       <c r="A9" s="5" t="s">
         <v>451</v>
       </c>
@@ -6933,7 +7666,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="10" ht="27" spans="1:3">
+    <row r="10" ht="14.25" spans="1:3">
       <c r="A10" s="5" t="s">
         <v>454</v>
       </c>
@@ -6955,7 +7688,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="12" ht="25.5" spans="1:3">
+    <row r="12" ht="14.25" spans="1:3">
       <c r="A12" s="5" t="s">
         <v>460</v>
       </c>
@@ -6966,7 +7699,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="13" ht="27" spans="1:3">
+    <row r="13" ht="14.25" spans="1:3">
       <c r="A13" s="5" t="s">
         <v>463</v>
       </c>
@@ -6977,7 +7710,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="14" ht="57" spans="1:3">
+    <row r="14" ht="28.5" spans="1:3">
       <c r="A14" t="s">
         <v>466</v>
       </c>
@@ -6988,7 +7721,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="15" ht="25.5" spans="1:3">
+    <row r="15" ht="14.25" spans="1:3">
       <c r="A15" s="5" t="s">
         <v>469</v>
       </c>
@@ -6999,7 +7732,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="16" ht="41.25" spans="1:3">
+    <row r="16" ht="27" spans="1:3">
       <c r="A16" s="5" t="s">
         <v>472</v>
       </c>
@@ -7010,7 +7743,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="17" ht="66.75" spans="1:3">
+    <row r="17" ht="41.25" spans="1:3">
       <c r="A17" s="5" t="s">
         <v>475</v>
       </c>
@@ -7021,7 +7754,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="18" ht="27" spans="1:3">
+    <row r="18" ht="14.25" spans="1:3">
       <c r="A18" s="5" t="s">
         <v>478</v>
       </c>
@@ -7065,7 +7798,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="22" ht="38.25" spans="1:3">
+    <row r="22" ht="25.5" spans="1:3">
       <c r="A22" s="5" t="s">
         <v>490</v>
       </c>
@@ -7076,7 +7809,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="23" ht="25.5" spans="1:3">
+    <row r="23" ht="14.25" spans="1:3">
       <c r="A23" t="s">
         <v>493</v>
       </c>
@@ -7120,7 +7853,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="27" ht="41.25" spans="1:3">
+    <row r="27" ht="27" spans="1:3">
       <c r="A27" s="5" t="s">
         <v>505</v>
       </c>
@@ -7153,7 +7886,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="30" ht="57" spans="1:3">
+    <row r="30" ht="28.5" spans="1:3">
       <c r="A30" s="5" t="s">
         <v>514</v>
       </c>
@@ -7935,30 +8668,646 @@
       </c>
     </row>
     <row r="101" ht="14.25" spans="1:3">
-      <c r="A101" s="17" t="s">
+      <c r="A101" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="8" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="124" spans="2:2">
-      <c r="B124" s="20"/>
-    </row>
-    <row r="125" spans="2:2">
-      <c r="B125" s="20"/>
-    </row>
-    <row r="126" spans="2:2">
-      <c r="B126" s="20"/>
-    </row>
-    <row r="127" spans="2:2">
-      <c r="B127" s="21"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="20"/>
+    <row r="102" ht="14.25" spans="1:3">
+      <c r="A102" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="C102" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="103" ht="14.25" spans="1:3">
+      <c r="A103" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C103" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="104" ht="14.25" spans="1:3">
+      <c r="A104" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="105" ht="27" spans="1:3">
+      <c r="A105" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="106" ht="14.25" spans="1:3">
+      <c r="A106" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="107" ht="14.25" spans="1:3">
+      <c r="A107" t="s">
+        <v>666</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="108" ht="14.25" spans="1:3">
+      <c r="A108" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="109" ht="14.25" spans="1:3">
+      <c r="A109" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="110" ht="14.25" spans="1:3">
+      <c r="A110" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="111" ht="14.25" spans="1:3">
+      <c r="A111" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="112" ht="71.25" spans="1:3">
+      <c r="A112" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="B112" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="113" ht="14.25" spans="1:3">
+      <c r="A113" t="s">
+        <v>684</v>
+      </c>
+      <c r="B113" t="s">
+        <v>685</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="114" ht="40.5" spans="1:3">
+      <c r="A114" t="s">
+        <v>687</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>688</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="115" ht="14.25" spans="1:3">
+      <c r="A115" t="s">
+        <v>690</v>
+      </c>
+      <c r="B115" t="s">
+        <v>691</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="116" ht="81" spans="1:3">
+      <c r="A116" t="s">
+        <v>693</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="117" ht="14.25" spans="1:3">
+      <c r="A117" t="s">
+        <v>696</v>
+      </c>
+      <c r="B117" t="s">
+        <v>697</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="118" ht="14.25" spans="1:3">
+      <c r="A118" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="119" ht="14.25" spans="1:3">
+      <c r="A119" t="s">
+        <v>702</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>703</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="120" ht="14.25" spans="1:3">
+      <c r="A120" t="s">
+        <v>705</v>
+      </c>
+      <c r="B120" t="s">
+        <v>706</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="121" ht="27" spans="1:3">
+      <c r="A121" t="s">
+        <v>708</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="122" ht="27" spans="1:3">
+      <c r="A122" t="s">
+        <v>711</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="123" ht="27" spans="1:3">
+      <c r="A123" t="s">
+        <v>714</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="124" ht="28.5" spans="1:3">
+      <c r="A124" t="s">
+        <v>717</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="125" ht="14.25" spans="1:3">
+      <c r="A125" t="s">
+        <v>720</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>721</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="126" ht="28.5" spans="1:3">
+      <c r="A126" t="s">
+        <v>723</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="127" ht="14.25" spans="1:3">
+      <c r="A127" t="s">
+        <v>726</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="128" ht="28.5" spans="1:3">
+      <c r="A128" t="s">
+        <v>729</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="129" ht="14.25" spans="1:3">
+      <c r="A129" t="s">
+        <v>732</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="130" ht="27" spans="1:3">
+      <c r="A130" t="s">
+        <v>735</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="131" ht="14.25" spans="1:3">
+      <c r="A131" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="132" ht="27" spans="1:3">
+      <c r="A132" t="s">
+        <v>741</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="133" ht="14.25" spans="1:3">
+      <c r="A133" t="s">
+        <v>744</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="134" ht="28.5" spans="1:3">
+      <c r="A134" t="s">
+        <v>747</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="135" ht="14.25" spans="1:3">
+      <c r="A135" t="s">
+        <v>750</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="136" ht="14.25" spans="1:3">
+      <c r="A136" t="s">
+        <v>753</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="137" ht="14.25" spans="1:3">
+      <c r="A137" t="s">
+        <v>756</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="138" ht="28.5" spans="1:3">
+      <c r="A138" t="s">
+        <v>759</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="139" ht="14.25" spans="1:3">
+      <c r="A139" t="s">
+        <v>762</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="140" ht="67.5" spans="1:3">
+      <c r="A140" t="s">
+        <v>765</v>
+      </c>
+      <c r="B140" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="141" ht="14.25" spans="1:3">
+      <c r="A141" t="s">
+        <v>768</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="142" ht="67.5" spans="1:3">
+      <c r="A142" t="s">
+        <v>771</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>772</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="143" ht="27" spans="1:3">
+      <c r="A143" t="s">
+        <v>774</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="144" ht="25.5" spans="1:3">
+      <c r="A144" t="s">
+        <v>777</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>778</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="145" ht="14.25" spans="1:3">
+      <c r="A145" s="5" t="s">
+        <v>780</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>781</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="146" ht="28.5" spans="1:3">
+      <c r="A146" s="6" t="s">
+        <v>783</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>784</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="147" ht="14.25" spans="1:3">
+      <c r="A147" t="s">
+        <v>786</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="148" ht="14.25" spans="1:3">
+      <c r="A148" s="18" t="s">
+        <v>789</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="C148" s="20" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="149" ht="14.25" spans="1:3">
+      <c r="A149" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>793</v>
+      </c>
+      <c r="C149" s="20" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="150" ht="14.25" spans="1:3">
+      <c r="A150" s="21" t="s">
+        <v>795</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="C150" s="20" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="151" ht="14.25" spans="1:3">
+      <c r="A151" s="21" t="s">
+        <v>798</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>799</v>
+      </c>
+      <c r="C151" s="20" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="152" ht="14.25" spans="1:3">
+      <c r="A152" s="21" t="s">
+        <v>801</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="C152" s="20" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="153" ht="14.25" spans="1:3">
+      <c r="A153" s="21" t="s">
+        <v>804</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>805</v>
+      </c>
+      <c r="C153" s="20" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="154" ht="14.25" spans="1:3">
+      <c r="A154" s="21" t="s">
+        <v>807</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>808</v>
+      </c>
+      <c r="C154" s="20" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="155" ht="14.25" spans="1:3">
+      <c r="A155" s="21" t="s">
+        <v>810</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="156" ht="14.25" spans="1:3">
+      <c r="A156" s="21" t="s">
+        <v>812</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="157" ht="14.25" spans="1:3">
+      <c r="A157" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="158" ht="14.25" spans="1:3">
+      <c r="A158" s="21" t="s">
+        <v>816</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="159" ht="14.25" spans="1:3">
+      <c r="A159" s="21" t="s">
+        <v>818</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="160" ht="14.25" spans="1:3">
+      <c r="A160" s="21" t="s">
+        <v>820</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>821</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8001,16 +9350,16 @@
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:7">
-      <c r="A2" s="32">
+      <c r="A2" s="33">
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="33">
         <v>20</v>
       </c>
-      <c r="D2" s="32">
+      <c r="D2" s="33">
         <v>1</v>
       </c>
       <c r="E2" s="22">
@@ -8368,284 +9717,284 @@
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="34" customFormat="1" spans="1:7">
-      <c r="A18" s="34">
+    <row r="18" s="35" customFormat="1" spans="1:7">
+      <c r="A18" s="35">
         <v>301</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="35">
         <v>50</v>
       </c>
-      <c r="D18" s="34">
-        <v>0</v>
-      </c>
-      <c r="E18" s="34">
+      <c r="D18" s="35">
+        <v>0</v>
+      </c>
+      <c r="E18" s="35">
         <v>400</v>
       </c>
-      <c r="F18" s="34">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36">
+      <c r="F18" s="35">
+        <v>0</v>
+      </c>
+      <c r="G18" s="37">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="34" customFormat="1" spans="1:7">
-      <c r="A19" s="34">
+    <row r="19" s="35" customFormat="1" spans="1:7">
+      <c r="A19" s="35">
         <v>302</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="36" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="35">
         <v>25</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="35">
         <v>9</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="35">
         <v>100</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="35">
         <v>303</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="37">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="34" customFormat="1" spans="1:7">
-      <c r="A20" s="34">
+    <row r="20" s="35" customFormat="1" spans="1:7">
+      <c r="A20" s="35">
         <v>303</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>217</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="35">
         <v>20</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="35">
         <v>3</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="35">
         <v>50</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="35">
         <v>301</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="37">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="34" customFormat="1" spans="1:7">
-      <c r="A21" s="34">
+    <row r="21" s="35" customFormat="1" spans="1:7">
+      <c r="A21" s="35">
         <v>304</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="35">
         <v>30</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="35">
         <v>11</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="35">
         <v>300</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="35">
         <v>301</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="37">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="34" customFormat="1" spans="1:7">
-      <c r="A22" s="34">
+    <row r="22" s="35" customFormat="1" spans="1:7">
+      <c r="A22" s="35">
         <v>305</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="35">
         <v>25</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="35">
         <v>8</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="35">
         <v>100</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="35">
         <v>303</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="37">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="34" customFormat="1" spans="1:7">
-      <c r="A23" s="34">
+    <row r="23" s="35" customFormat="1" spans="1:7">
+      <c r="A23" s="35">
         <v>306</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="36" t="s">
         <v>220</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="35">
         <v>35</v>
       </c>
-      <c r="D23" s="34">
-        <v>0</v>
-      </c>
-      <c r="E23" s="34">
+      <c r="D23" s="35">
+        <v>0</v>
+      </c>
+      <c r="E23" s="35">
         <v>200</v>
       </c>
-      <c r="F23" s="34">
-        <v>0</v>
-      </c>
-      <c r="G23" s="36">
+      <c r="F23" s="35">
+        <v>0</v>
+      </c>
+      <c r="G23" s="37">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="34" customFormat="1" spans="1:7">
-      <c r="A24" s="34">
+    <row r="24" s="35" customFormat="1" spans="1:7">
+      <c r="A24" s="35">
         <v>307</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="35">
         <v>35</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="35">
         <v>12</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="35">
         <v>150</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="35">
         <v>302</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="37">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="34" customFormat="1" spans="1:7">
-      <c r="A25" s="34">
+    <row r="25" s="35" customFormat="1" spans="1:7">
+      <c r="A25" s="35">
         <v>308</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="36" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="35">
         <v>35</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="35">
         <v>12</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="35">
         <v>150</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="35">
         <v>302</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="37">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="34" customFormat="1" spans="1:7">
-      <c r="A26" s="34">
+    <row r="26" s="35" customFormat="1" spans="1:7">
+      <c r="A26" s="35">
         <v>309</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="36" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="35">
         <v>20</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="35">
         <v>10</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="35">
         <v>80</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="35">
         <v>306</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="37">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="34" customFormat="1" spans="1:7">
-      <c r="A27" s="34">
+    <row r="27" s="35" customFormat="1" spans="1:7">
+      <c r="A27" s="35">
         <v>310</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="36" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="35">
         <v>30</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="35">
         <v>10</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="35">
         <v>120</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <v>309</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="37">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="34" customFormat="1" spans="1:7">
-      <c r="A28" s="34">
+    <row r="28" s="35" customFormat="1" spans="1:7">
+      <c r="A28" s="35">
         <v>311</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="35">
         <v>30</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="35">
         <v>10</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="35">
         <v>120</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <v>309</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="37">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="34" customFormat="1" spans="1:7">
-      <c r="A29" s="34">
+    <row r="29" s="35" customFormat="1" spans="1:7">
+      <c r="A29" s="35">
         <v>312</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="36" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="35">
         <v>15</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="35">
         <v>2</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="35">
         <v>15</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <v>306</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="37">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="34" customFormat="1" spans="1:7">
-      <c r="B30" s="35"/>
+    <row r="30" s="35" customFormat="1" spans="1:7">
+      <c r="B30" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8688,10 +10037,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="32">
+      <c r="A2" s="33">
         <v>3</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="33" t="s">
         <v>229</v>
       </c>
       <c r="C2">
@@ -8708,10 +10057,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="32">
+      <c r="A3" s="33">
         <v>4</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="33" t="s">
         <v>200</v>
       </c>
       <c r="C3">
@@ -8897,10 +10246,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="32">
+      <c r="A12" s="33">
         <v>309</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>168</v>
       </c>
       <c r="C12">
@@ -8917,10 +10266,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="32">
+      <c r="A13" s="33">
         <v>310</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="33" t="s">
         <v>173</v>
       </c>
       <c r="C13">
@@ -8937,10 +10286,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="32">
+      <c r="A14" s="33">
         <v>311</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="33" t="s">
         <v>177</v>
       </c>
       <c r="C14">
@@ -8960,10 +10309,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="32">
+      <c r="A15" s="33">
         <v>312</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="33" t="s">
         <v>223</v>
       </c>
       <c r="C15">
@@ -8980,8 +10329,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="33"/>
+      <c r="B16" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9054,29 +10403,29 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" s="31" customFormat="1" spans="1:8">
-      <c r="A3" s="31">
+    <row r="3" s="32" customFormat="1" spans="1:8">
+      <c r="A3" s="32">
         <v>202</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="31">
-        <v>0</v>
-      </c>
-      <c r="F3" s="31">
+      <c r="E3" s="32">
+        <v>0</v>
+      </c>
+      <c r="F3" s="32">
         <v>0.8</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="32" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9466,29 +10815,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="31" customFormat="1" spans="1:8">
-      <c r="A20" s="33">
+    <row r="20" s="32" customFormat="1" spans="1:8">
+      <c r="A20" s="34">
         <v>404</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="E20" s="31">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
+      <c r="E20" s="32">
+        <v>0</v>
+      </c>
+      <c r="F20" s="32">
         <v>0.8</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="32" t="s">
         <v>241</v>
       </c>
     </row>
@@ -9545,7 +10894,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="20">
+      <c r="A23" s="31">
         <v>407</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -9571,7 +10920,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="20">
+      <c r="A24" s="31">
         <v>408</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -9597,7 +10946,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="20">
+      <c r="A25" s="31">
         <v>409</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -9623,7 +10972,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="20">
+      <c r="A26" s="31">
         <v>410</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -9649,7 +10998,7 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="20">
+      <c r="A27" s="31">
         <v>411</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -9715,68 +11064,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" spans="1:21">
-      <c r="A1" s="31" t="s">
+    <row r="1" s="32" customFormat="1" spans="1:21">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="32" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="32" t="s">
         <v>278</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="32" t="s">
         <v>279</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="32" t="s">
         <v>280</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>281</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="32" t="s">
         <v>282</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="32" t="s">
         <v>286</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="32" t="s">
         <v>287</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="32" t="s">
         <v>288</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="Q1" s="31" t="s">
+      <c r="Q1" s="32" t="s">
         <v>290</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="32" t="s">
         <v>291</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="32" t="s">
         <v>292</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="32" t="s">
         <v>293</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="32" t="s">
         <v>294</v>
       </c>
     </row>
@@ -10648,7 +11997,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="32">
+      <c r="A17" s="33">
         <v>301</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -10707,7 +12056,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="32">
+      <c r="A18" s="33">
         <v>302</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -10766,7 +12115,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="32">
+      <c r="A19" s="33">
         <v>303</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -10825,7 +12174,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="32">
+      <c r="A20" s="33">
         <v>304</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -10946,7 +12295,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="32">
+      <c r="A22" s="33">
         <v>306</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -11005,7 +12354,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="32">
+      <c r="A23" s="33">
         <v>307</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -11064,7 +12413,7 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="32">
+      <c r="A24" s="33">
         <v>308</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -11123,7 +12472,7 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="32">
+      <c r="A25" s="33">
         <v>309</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -11182,7 +12531,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="32">
+      <c r="A26" s="33">
         <v>310</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -11241,7 +12590,7 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="32">
+      <c r="A27" s="33">
         <v>311</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -11300,7 +12649,7 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="32">
+      <c r="A28" s="33">
         <v>312</v>
       </c>
       <c r="B28" s="11" t="s">
@@ -11707,7 +13056,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="20">
+      <c r="A35" s="31">
         <v>407</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -11763,7 +13112,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="20">
+      <c r="A36" s="31">
         <v>408</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -11822,7 +13171,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="20">
+      <c r="A37" s="31">
         <v>409</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -11881,7 +13230,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="20">
+      <c r="A38" s="31">
         <v>410</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -11931,7 +13280,7 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="20">
+      <c r="A39" s="31">
         <v>411</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -12126,7 +13475,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="20">
+      <c r="A12" s="31">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -12137,7 +13486,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="20">
+      <c r="A13" s="31">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -12148,7 +13497,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="20">
+      <c r="A14" s="31">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -12159,7 +13508,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="20">
+      <c r="A15" s="31">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -12170,7 +13519,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="20">
+      <c r="A16" s="31">
         <v>411</v>
       </c>
       <c r="B16" t="s">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1083">
   <si>
     <t>类型</t>
   </si>
@@ -1616,7 +1616,7 @@
     <t>Do NOT enter the gun emplacements' firing range!</t>
   </si>
   <si>
-    <t>Key你不早说</t>
+    <t>Key你不早说……</t>
   </si>
   <si>
     <t>你不早说？</t>
@@ -2468,6 +2468,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>，在途中击落敌方</t>
     </r>
     <r>
@@ -3015,6 +3021,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>Key</t>
     </r>
     <r>
@@ -3074,6 +3086,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>蜕变进度</t>
     </r>
     <r>
@@ -3094,6 +3112,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>待造队列</t>
     </r>
     <r>
@@ -3134,12 +3158,18 @@
     <t>走向建造点</t>
   </si>
   <si>
+    <t>Proceed to Construction Site</t>
+  </si>
+  <si>
     <t>Key造完了</t>
   </si>
   <si>
     <t>造完了</t>
   </si>
   <si>
+    <t>Construction Complete</t>
+  </si>
+  <si>
     <t>Key建造完成</t>
   </si>
   <si>
@@ -3152,16 +3182,1125 @@
     <t>民房不足</t>
   </si>
   <si>
+    <t>Insufficient Civilian Housing</t>
+  </si>
+  <si>
     <t>Key房虫不足</t>
   </si>
   <si>
     <t>房虫不足</t>
   </si>
   <si>
+    <t>Insufficient Population Drones</t>
+  </si>
+  <si>
     <t>Key正在建造</t>
   </si>
   <si>
     <t>正在建造</t>
+  </si>
+  <si>
+    <t>Under Construction</t>
+  </si>
+  <si>
+    <t>Key现在给你一批防空兵……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现在给你一批防空兵。先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>框选</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全部，然后点击飞虫附近的空白地面，进攻飞虫。优势在我！</t>
+    </r>
+  </si>
+  <si>
+    <t>You have been assigned a squad of anti-air units. First &lt;color=#a0ff50&gt; box-select&lt;/color&gt; all of them, then click the empty ground near the flying drones to order an attack. We hold the advantage!</t>
+  </si>
+  <si>
+    <t>Key先框选全部防空兵……</t>
+  </si>
+  <si>
+    <t>先&lt;color=#a0ff50&gt;框选全部防空兵&lt;/color&gt;，然后点击飞虫附近的空白地面，进攻飞虫。优势在我！</t>
+  </si>
+  <si>
+    <t>First &lt;color=#a0ff50&gt; box-select all anti-air units&lt;/color&gt;, then click the empty ground near the flying drones to order an attack. We hold the advantage!</t>
+  </si>
+  <si>
+    <t>Key防空战胜利……</t>
+  </si>
+  <si>
+    <t>您胜利了！您真是防空天才！</t>
+  </si>
+  <si>
+    <t>You win! What an anti-air ace you are!</t>
+  </si>
+  <si>
+    <t>Key防空兵不可对地……</t>
+  </si>
+  <si>
+    <t>防空兵对空大范围高伤害（不分敌我），不能攻击地面单位，需要其他单位保护。</t>
+  </si>
+  <si>
+    <t>Anti-air units deal massive area damage to airborne targets (friend or foe alike). They cannot attack ground units and must be protected by other friendly forces.</t>
+  </si>
+  <si>
+    <t>Key我会注意。</t>
+  </si>
+  <si>
+    <t>我会注意。</t>
+  </si>
+  <si>
+    <t>I’ll keep that in mind.</t>
+  </si>
+  <si>
+    <t>Key敌方布置了防空兵……</t>
+  </si>
+  <si>
+    <t>敌方布置了防空兵，我方飞虫损失惨重。</t>
+  </si>
+  <si>
+    <t>The enemy has deployed anti-air units, and our flying drones are sustaining heavy casualties.</t>
+  </si>
+  <si>
+    <t>Key防空兵移动缓慢……</t>
+  </si>
+  <si>
+    <t>防空兵&lt;color=#a0ff50&gt;移动缓慢，攻击前摇时间长，前摇过程中炸点不可改变位置&lt;/color&gt;。只要手动操作飞虫避开空中炸点再找机会攻击，就有希望击败他们。</t>
+  </si>
+  <si>
+    <t>Anti-air units &lt;color=#a0ff50&gt;move slowly and have a long attack wind-up. Once the wind-up initiates, the blast point cannot be repositioned&lt;/color&gt;. You can defeat them by manually maneuvering your flying drones to dodge the airborne blast points, then seizing the chance to counterattack.</t>
+  </si>
+  <si>
+    <t>Key具体如何操作呢？</t>
+  </si>
+  <si>
+    <t>具体如何操作呢？</t>
+  </si>
+  <si>
+    <t>How exactly should I execute this?</t>
+  </si>
+  <si>
+    <t>Key所有飞虫在后方……</t>
+  </si>
+  <si>
+    <t>所有飞虫在后方安全地区聚拢，然后派一只飞虫用&lt;color=#a0ff50&gt;强行走&lt;/color&gt;吸引一个防空兵过来，群起而狙之。然后等飞虫自动恢复血量。如此反复，直至击败所有防空兵。</t>
+  </si>
+  <si>
+    <t>Gather all flying drones in a safe rear area. Then send a single drone to &lt;color=#a0ff50&gt;force-march&lt;/color&gt; and lure one anti-air unit over, then focus fire to take it down. After that, wait for the flying drones to regenerate HP automatically. Repeat this process until all enemy anti-air units are eliminated.</t>
+  </si>
+  <si>
+    <t>Key好的，我试试看。</t>
+  </si>
+  <si>
+    <t>好的，我试试看。</t>
+  </si>
+  <si>
+    <t>Got it, let’s give it a shot.</t>
+  </si>
+  <si>
+    <t>Key反防空战胜利……</t>
+  </si>
+  <si>
+    <t>您胜利了！您真是微操天才！</t>
+  </si>
+  <si>
+    <t>You win! You’re a micro-operation genius!</t>
+  </si>
+  <si>
+    <t>Key我没看错你的悟性很强……</t>
+  </si>
+  <si>
+    <t>我果然没看错，你的悟性很强！</t>
+  </si>
+  <si>
+    <t>I knew I was right about you—you’re a fast learner!</t>
+  </si>
+  <si>
+    <t>Key您英材施教……</t>
+  </si>
+  <si>
+    <t>您因材施教，总能点醒弟子困顿之处。弟子能有今日，皆因您引路人做得好，这份教导之恩，弟子铭记于心！</t>
+  </si>
+  <si>
+    <t>You tailor your teaching to the student, always clearing up the confusion that plagues your disciples. I wouldn’t be where I am today without your guidance as a mentor. I shall forever remember this debt of gratitude for your teachings!</t>
+  </si>
+  <si>
+    <t>Key反防空战失败……</t>
+  </si>
+  <si>
+    <t>您失败了！您需要继续练习反防空技巧。</t>
+  </si>
+  <si>
+    <t>You lose! You need more practice with anti-AA counter tactics.</t>
+  </si>
+  <si>
+    <t>Key再打防空战……</t>
+  </si>
+  <si>
+    <t>可以点右上角&lt;color=#a0ff50&gt;离开场景&lt;/color&gt;离开，然后再次点击&lt;color=#a0ff50&gt;反防空战&lt;/color&gt;，就可以重新来过。</t>
+  </si>
+  <si>
+    <t>You can click &lt;color=#a0ff50&gt;Exit Scene&lt;/color&gt; in the top-right corner to leave, then click &lt;color=#a0ff50&gt;Anti-AA Counter Battle&lt;/color&gt; again to restart the mission.</t>
+  </si>
+  <si>
+    <t>Key敌方飞虫进攻我方炮台……</t>
+  </si>
+  <si>
+    <t>，敌方飞虫进攻我方炮台，我方损失惨重。</t>
+  </si>
+  <si>
+    <t>, Enemy flying drones are assaulting our artillery emplacements; we are sustaining heavy casualties.</t>
+  </si>
+  <si>
+    <t>Key没有吧？</t>
+  </si>
+  <si>
+    <t>没有吧？</t>
+  </si>
+  <si>
+    <t>Really?</t>
+  </si>
+  <si>
+    <t>Key现在请看……</t>
+  </si>
+  <si>
+    <t>现在请看（无需操作）：</t>
+  </si>
+  <si>
+    <t>Now observe (no action required):</t>
+  </si>
+  <si>
+    <t>Key飞虫炮台无需操作……</t>
+  </si>
+  <si>
+    <t>敌方飞虫进攻我方炮台（此过程您无需操作）</t>
+  </si>
+  <si>
+    <t>Enemy flying drones are assaulting our artillery emplacements (no action required on your part during this phase)</t>
+  </si>
+  <si>
+    <t>Key传授闪避技巧……</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，今日要传授你一门重要的闪避技巧。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>看，前方有一辆敌方坦克。坦克虽然伤害极高，但攻击前摇时间很长，且前摇开始后炸点位置无法改变。</t>
+    </r>
+  </si>
+  <si>
+    <t>, Today I will teach you an essential evasion technique.\nLook, there is an enemy tank ahead. While the tank deals devastating damage, it has an extremely long attack wind-up, and once the wind-up begins, the blast point cannot be repositioned.</t>
+  </si>
+  <si>
+    <t>Key那弟子该如何应对？</t>
+  </si>
+  <si>
+    <t>那弟子该如何应对？</t>
+  </si>
+  <si>
+    <t>What should this disciple do to counter it?</t>
+  </si>
+  <si>
+    <t>Key当坦克开始攻击前摇……</t>
+  </si>
+  <si>
+    <r>
+      <t>当坦克开始攻击前摇时，地面上会出现炸点特效。仔细观察，一旦看到炸点特效出现，立刻使用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强行走</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>身法，让枪兵迅速离开炸点位置。躲开炸点后，点击坦克附近的空白地面，让枪兵继续攻击坦克。如此反复，便能以弱胜强。</t>
+    </r>
+  </si>
+  <si>
+    <t>When the tank initiates its attack wind-up, a blast point visual cue will appear on the ground. Watch closely—once you see the blast point appear, immediately use the &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; maneuver to move your riflemen out of the blast zone quickly.After dodging the blast, click the empty ground near the tank to order the riflemen to resume their attack. Repeat this process, and you can defeat the stronger enemy with your weaker units.</t>
+  </si>
+  <si>
+    <t>Key谨记枪兵挑坦克心法……</t>
+  </si>
+  <si>
+    <t>谨记此心法：&lt;color=#a0ff50&gt;观察炸点特效 → 强行走离开炸点 → 立刻继续攻击&lt;/color&gt;。此乃枪兵对抗坦克的生存之道！</t>
+  </si>
+  <si>
+    <t>Commit this core principle to memory: &lt;color=#a0ff50&gt;Spot the blast point visual cue → Force Move away from the blast point → Resume attacking immediately&lt;/color&gt;. This is the survival strategy for riflemen facing off against tanks!</t>
+  </si>
+  <si>
+    <t>Key点枪兵再点击坦克……</t>
+  </si>
+  <si>
+    <t>点击选中枪兵，再点击坦克附近的空白地面，让枪兵攻击坦克。仔细观察地面上的炸点特效，一旦看到炸点出现，立即使用&lt;color=#a0ff50&gt;强行走&lt;/color&gt;身法离开炸点位置，然后点击坦克附近的空白地面继续攻击</t>
+  </si>
+  <si>
+    <t>Click to select the riflemen, then click the empty ground near the tank to order them to attack. Watch the ground carefully for the blast point visual cue—once it appears, use &lt;color=#a0ff50&gt;Force Move&lt;/color&gt; to move away from the blast zone at once, then click the empty ground near the tank to continue the attack.</t>
+  </si>
+  <si>
+    <t>Key枪兵挑坦克失败……</t>
+  </si>
+  <si>
+    <t>您失败了！您需要继续练习闪避技巧。</t>
+  </si>
+  <si>
+    <t>You lose! You need more practice with evasion techniques.</t>
+  </si>
+  <si>
+    <t>Key枪兵败切记……</t>
+  </si>
+  <si>
+    <t>，枪兵已败。切记，面对强敌，闪避为先。仔细观察炸点特效，善用强行走身法躲开坦克炸点，方能在战场上立于不败之地。</t>
+  </si>
+  <si>
+    <t>, your riflemen have been defeated. Remember this: when facing a superior foe, evasion comes first. Watch closely for the blast point visual cue and master the Force March maneuver to dodge the tank’s blasts—only then can you prevail on the battlefield.</t>
+  </si>
+  <si>
+    <t>Key弟子谨记前辈教诲。</t>
+  </si>
+  <si>
+    <t>弟子谨记前辈教诲。</t>
+  </si>
+  <si>
+    <t>This disciple shall heed the elder’s teachings.</t>
+  </si>
+  <si>
+    <t>Key清兵挑坦克胜利……</t>
+  </si>
+  <si>
+    <t>Key少侠领悟枪兵对抗坦克……</t>
+  </si>
+  <si>
+    <r>
+      <t>，你已领悟枪兵对抗坦克的闪避心法。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>切记，面对强敌，闪避比硬拼更为重要。仔细观察炸点特效，善用强行走身法躲开坦克炸点，你的枪兵便能在这险恶的战场上存活更久。</t>
+    </r>
+  </si>
+  <si>
+    <t>, you have mastered the evasion strategy for riflemen against tanks.Remember: when facing a stronger enemy, evasion is far more important than a head-on confrontation. Watch closely for the blast point visual cue and master the Force March maneuver to dodge the tank’s blasts, and your riflemen will survive longer on this perilous battlefield.</t>
+  </si>
+  <si>
+    <t>Key弟子谨记教诲心法……</t>
+  </si>
+  <si>
+    <t>弟子谨记前辈教诲，定当善用此心法。</t>
+  </si>
+  <si>
+    <t>This disciple shall heed the elder’s teachings and make good use of this strategy.</t>
+  </si>
+  <si>
+    <t>Key人类即将入侵……</t>
+  </si>
+  <si>
+    <t>情报显示：敌人已发现我们的巢穴入口，即将入侵，请做好准备。</t>
+  </si>
+  <si>
+    <t>Key我仅受过简单训练……</t>
+  </si>
+  <si>
+    <t>可是我仅受过简单的指挥训练。</t>
+  </si>
+  <si>
+    <t>Key资源管够……</t>
+  </si>
+  <si>
+    <t>我们会提供足够的初始晶体矿和燃气矿，你&lt;color=#a0ff50&gt;不用再从零开始采集&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key还是没把握……</t>
+  </si>
+  <si>
+    <t>我还是没有把握。</t>
+  </si>
+  <si>
+    <t>Key传授速成口诀……</t>
+  </si>
+  <si>
+    <t>我会传授你指挥实战速成口诀，三分钟即可成为实战高手。</t>
+  </si>
+  <si>
+    <t>Key真有这种口诀……</t>
+  </si>
+  <si>
+    <t>真有这种口诀的话就应该在训练战时告诉我啊！</t>
+  </si>
+  <si>
+    <t>Key只有在实战中才有用……</t>
+  </si>
+  <si>
+    <t>实战口诀只有在九死一生的实战中才有用！</t>
+  </si>
+  <si>
+    <t>Key九死一生……</t>
+  </si>
+  <si>
+    <t>九死一生？形势严峻啊，我会全力以赴的!</t>
+  </si>
+  <si>
+    <r>
+      <t>Key1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个虫巢只能照顾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>……</t>
+    </r>
+  </si>
+  <si>
+    <t>1个虫巢只能照顾&lt;color=#a0ff50&gt;3只幼虫&lt;/color&gt;。&lt;color=#a0ff50&gt;让工虫变异更多的虫巢&lt;/color&gt;，才有更多的幼虫可供蜕变。&lt;color=#a0ff50&gt;多蜕变房虫&lt;/color&gt;，增加活动单位上限。</t>
+  </si>
+  <si>
+    <t>Key一定要在数量……</t>
+  </si>
+  <si>
+    <t>就是一定要在数量上占据优势吗？</t>
+  </si>
+  <si>
+    <t>Key进攻就是最好的防守……</t>
+  </si>
+  <si>
+    <t>是的，进攻就是最好的防守。派出地面单位堵住敌人的通道，再派出飞虫越过障碍物空袭敌人。</t>
+  </si>
+  <si>
+    <t>Key也不是很复杂……</t>
+  </si>
+  <si>
+    <t>OK，也不是很复杂。我有信心完成任务！</t>
+  </si>
+  <si>
+    <t>Key防守战只要守住……</t>
+  </si>
+  <si>
+    <t>防守战：只要守住，就是胜利！</t>
+  </si>
+  <si>
+    <t>Key多造虫巢……</t>
+  </si>
+  <si>
+    <t>5秒后将出现第1波敌人。多造虫巢和房虫，多造近战虫枪虫和飞虫，一定要在数量上压倒敌人！</t>
+  </si>
+  <si>
+    <t>Key前期不用采集……</t>
+  </si>
+  <si>
+    <t>&lt;color=#a0ff50&gt;前期不用采集资源&lt;/color&gt;。多造虫巢和房虫，多造近战虫枪虫和飞虫，一定要在数量上压制敌人！</t>
+  </si>
+  <si>
+    <t>Key第{}波敌人正向您走来</t>
+  </si>
+  <si>
+    <t>第{}波敌人正向您走来</t>
+  </si>
+  <si>
+    <t>Key虫族将进攻基地……</t>
+  </si>
+  <si>
+    <t>情报显示：将有大量敌方单位进攻我方基地，请做好准备。</t>
+  </si>
+  <si>
+    <t>Key坦克超远超高伤害……</t>
+  </si>
+  <si>
+    <t>&lt;color=#a0ff50&gt;坦克&lt;/color&gt;可以超远距离造成超高伤害，而且是范围伤害，但是坦克锁定炮弹落点后有超长前摇时长，前摇结束后，敌方目标可能已经远离炮弹落点。炮弹落点附近的我方单位也会受到伤害。</t>
+  </si>
+  <si>
+    <t>Key有点鸡肋的感觉……</t>
+  </si>
+  <si>
+    <t>有点鸡肋的感觉，不是红警中的高速坦克，与星际中的攻城坦克也有些不同。感觉更像帝国里的投石车。</t>
+  </si>
+  <si>
+    <t>Key有一种叫炮台的……</t>
+  </si>
+  <si>
+    <t>…不知道你在说什么…有一种叫&lt;color=#a0ff50&gt;炮台&lt;/color&gt;的建筑单位，攻击距离很远，仅次于坦克；前摇时长很短，可以快速攻击；缺陷是伤害较低；不过多造点集中防守某一块区域还是很实用的。</t>
+  </si>
+  <si>
+    <t>Key坦克炮台就能……</t>
+  </si>
+  <si>
+    <t>看来&lt;color=#a0ff50&gt;只要有坦克和炮台就能守住&lt;/color&gt;对吗？</t>
+  </si>
+  <si>
+    <t>Key是的能守住……</t>
+  </si>
+  <si>
+    <t>是的，这是其他指挥官总结的经验。大概&lt;color=#a0ff50&gt;10个炮台和5辆坦克沿墙边布置就能守住&lt;/color&gt;。当然还有其他多种可行的防守方法，要靠你自行摸索。</t>
+  </si>
+  <si>
+    <t>Key5秒出现虫族怪……</t>
+  </si>
+  <si>
+    <t>5秒后将出现第1波怪。您可以沿右边墙边造炮台、布置坦克、造地堡、让兵进驻地堡。</t>
+  </si>
+  <si>
+    <t>Key沿右边迷宫出口……</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>前期不用采集资源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。沿右边迷宫出口墙边布置一排</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炮台</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，再放置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坦克</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/color&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加强防御。</t>
+    </r>
+  </si>
+  <si>
+    <t>Key总算报仇了！</t>
+  </si>
+  <si>
+    <t>总算报仇了！</t>
+  </si>
+  <si>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>以后坦克不能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>……</t>
+    </r>
+  </si>
+  <si>
+    <t>以后坦克不能再单独行动了，一定要带上步兵。</t>
+  </si>
+  <si>
+    <t>是，指挥官！</t>
+  </si>
+  <si>
+    <t>Key该听你的直接回去……</t>
+  </si>
+  <si>
+    <t>早知如此就该听你的直接回去！</t>
+  </si>
+  <si>
+    <t>Key现在说什么都……</t>
+  </si>
+  <si>
+    <t>现在说什么都晚了（惨叫）。</t>
+  </si>
+  <si>
+    <t>Key下次先攻击虫巢……</t>
+  </si>
+  <si>
+    <t>可以试试操作慢一点，先进攻&lt;color=#a0ff50&gt;右下角的虫巢&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key只能下次再试试了。</t>
+  </si>
+  <si>
+    <t>Key下次先攻击基地……</t>
+  </si>
+  <si>
+    <t>可以试试操作慢一点，先进攻&lt;color=#a0ff50&gt;右下角的基地&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key坦克连失联……</t>
+  </si>
+  <si>
+    <t>，我的一个坦克连在调查&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;时失联，请前往营救。</t>
+  </si>
+  <si>
+    <t>Key没有步兵保护吗……</t>
+  </si>
+  <si>
+    <t>坦克没有步兵保护吗？</t>
+  </si>
+  <si>
+    <t>Key两个班的兵力……</t>
+  </si>
+  <si>
+    <t>是的，步兵刚刚到位，两个班的兵力，现在全部交给你指挥。</t>
+  </si>
+  <si>
+    <t>Key虫巢是什么？</t>
+  </si>
+  <si>
+    <t>虫巢是什么？</t>
+  </si>
+  <si>
+    <t>Key虫巢苔蔓……</t>
+  </si>
+  <si>
+    <t>侦察机传回的视频表明：虫巢周围会形成&lt;color=#a0ff50&gt;苔蔓(wàn)&lt;/color&gt;，苔蔓上的虫类单位移动速度会变快，并且回血速度也会加快。应该&lt;color=#a0ff50&gt;避免在苔蔓上与虫类单位交战&lt;/color&gt;。
+    据1985年《普通话异读词审音表》：\n苔蔓(&lt;color=#a0ff50&gt;wàn&lt;/color&gt;)、蔓(màn)延</t>
+  </si>
+  <si>
+    <t>Key坦克凭空消失……</t>
+  </si>
+  <si>
+    <t>一个坦克连应该有10辆坦克吧？这么多钢铁疙瘩能凭空消失吗？</t>
+  </si>
+  <si>
+    <t>Key不放弃任何人……</t>
+  </si>
+  <si>
+    <t>现在人手紧缺，我不能做任何行动上的承诺。但我个人会竭尽全力，不放弃任何一个人。</t>
+  </si>
+  <si>
+    <t>Key我会尽力而为的。</t>
+  </si>
+  <si>
+    <t>我会尽力而为的。</t>
+  </si>
+  <si>
+    <t>Key多想克制……</t>
+  </si>
+  <si>
+    <r>
+      <t>要多用脑子，要多想。记住兵种克制关系：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;color=#a0ff50&gt;小兵 克制 坦克</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>坦克 克制 炮台</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炮台 克制 小兵&lt;/color&gt;</t>
+    </r>
+  </si>
+  <si>
+    <t>Key早记住坦克步兵……</t>
+  </si>
+  <si>
+    <t>这我早就记住了，否则我也不会疑惑为什么坦克没有步兵保护。</t>
+  </si>
+  <si>
+    <t>Key相信你归来……</t>
+  </si>
+  <si>
+    <t>我相信你的能力，你一定能平安归来!</t>
+  </si>
+  <si>
+    <t>Key无工程车打虫巢……</t>
+  </si>
+  <si>
+    <t>此局没有工程车。&lt;color=#a0ff50&gt;右下方的敌方虫巢防守薄弱&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key谢谢你救了我们。</t>
+  </si>
+  <si>
+    <t>谢谢你救了我们。</t>
+  </si>
+  <si>
+    <t>Key你们怎么会在……</t>
+  </si>
+  <si>
+    <t>你们怎么会在虫巢里？</t>
+  </si>
+  <si>
+    <t>Key仿佛做梦……</t>
+  </si>
+  <si>
+    <t>我也不知道，仿佛做了一场梦，什么都不记得了。</t>
+  </si>
+  <si>
+    <t>Key我护送你……</t>
+  </si>
+  <si>
+    <t>现在我的部队会护送你们回基地。到时候再仔细回忆一下。</t>
+  </si>
+  <si>
+    <t>Key两个虫巢……</t>
+  </si>
+  <si>
+    <t>上面还有两个虫巢，我要炸掉它们再回去。</t>
+  </si>
+  <si>
+    <t>Key虫巢有炮台把守……</t>
+  </si>
+  <si>
+    <t>上面的虫巢有敌方的炮台把守，我们过不去。</t>
+  </si>
+  <si>
+    <t>Key我的坦克专门……</t>
+  </si>
+  <si>
+    <t>我的坦克专门克制炮台。&lt;color=#a0ff50&gt;坦克的射程略远于炮台&lt;/color&gt;。一辆坦克就能全灭它们，何况我现在有十辆。</t>
+  </si>
+  <si>
+    <t>Key坦克接受我指挥……</t>
+  </si>
+  <si>
+    <t>好的，但是坦克要接受我的指挥，我的步兵会保护坦克。</t>
+  </si>
+  <si>
+    <t>Key是明白指挥官……</t>
+  </si>
+  <si>
+    <t>是！明白！指挥官！</t>
+  </si>
+  <si>
+    <t>Key消灭虫巢……</t>
+  </si>
+  <si>
+    <t>消灭上方两个敌方虫巢，控制好步兵保护您的坦克。&lt;color=#a0ff50&gt;让坦克在地方炮台的射程外攻击&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key好消息拟态……</t>
+  </si>
+  <si>
+    <t>，有一个好消息，我们的幼虫经过千万次的模仿，基本掌握了拟态复制人类三色坦克的方法。</t>
+  </si>
+  <si>
+    <t>Key还有坏消息……</t>
+  </si>
+  <si>
+    <t>太好了……那么接下来肯定还有一个坏消息吧？</t>
+  </si>
+  <si>
+    <t>Key绿色坦克遭……</t>
+  </si>
+  <si>
+    <t>是的，蜕变出的第一批&lt;color = #a0ff50&gt;绿色坦克&lt;/color&gt;的虫巢已遭人类攻占。</t>
+  </si>
+  <si>
+    <t>Key绿色坦克打不过……</t>
+  </si>
+  <si>
+    <t>绿色坦克看来仍然打不过人类的部队啊！</t>
+  </si>
+  <si>
+    <t>Key绿色坦克劣势……</t>
+  </si>
+  <si>
+    <t>绿色坦克攻击距离远，但是面对贴近的人类步兵却处于劣势。此外绿色坦克发射出的光刺会被障碍物阻挡。现在人类的科学家正在研究我们的绿色坦克。</t>
+  </si>
+  <si>
+    <t>Key我现在去救它们。</t>
+  </si>
+  <si>
+    <t>我现在去救它们。</t>
+  </si>
+  <si>
+    <t>Key无工虫打基地……</t>
+  </si>
+  <si>
+    <t>此局没有工虫。&lt;color=#a0ff50&gt;右下方的敌方基地防守薄弱&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key你们怎么会在基地里？</t>
+  </si>
+  <si>
+    <t>你们怎么会在基地里？</t>
+  </si>
+  <si>
+    <t>Key护送回虫巢……</t>
+  </si>
+  <si>
+    <t>现在我的部队会护送你们回虫巢。到时候再仔细回忆一下。</t>
+  </si>
+  <si>
+    <t>Key炸掉基地……</t>
+  </si>
+  <si>
+    <t>上面还有两个基地，我要炸掉它们再回去。</t>
+  </si>
+  <si>
+    <t>Key基地有炮台……</t>
+  </si>
+  <si>
+    <t>上面的基地有敌方的炮台把守，我们过不去。</t>
+  </si>
+  <si>
+    <t>Key我克制炮台……</t>
+  </si>
+  <si>
+    <t>我专门克制炮台。&lt;color=#a0ff50&gt;坦克的射程略远于炮台&lt;/color&gt;。一辆坦克就能全灭它们，何况我们现在有十辆。</t>
+  </si>
+  <si>
+    <t>Key我保护你们……</t>
+  </si>
+  <si>
+    <t>好的，但是你们要接受我的指挥，我的部队会保护你们。</t>
+  </si>
+  <si>
+    <t>Key消灭上方基地……</t>
+  </si>
+  <si>
+    <t>消灭上方两个敌方基地，控制好其它单位保护您的坦克。坦克的射程略远于炮台，&lt;color=#a0ff50&gt;不要让坦克进入敌方炮台的射程&lt;/color&gt;。</t>
+  </si>
+  <si>
+    <t>Key无坦克遇炮台……</t>
+  </si>
+  <si>
+    <t>没有坦克又遇到大片敌方炮台怎么办？</t>
+  </si>
+  <si>
+    <t>Key绕道空降……</t>
+  </si>
+  <si>
+    <t>，可以让&lt;color=#a0ff50&gt;房虫&lt;/color&gt;运送战斗单位越过障碍物绕到炮台后方，实施空降作战。</t>
+  </si>
+  <si>
+    <t>Key近战虫进房虫……</t>
+  </si>
+  <si>
+    <t>请先点击选中&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再点击一次&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，可让近战虫进入房虫。</t>
+  </si>
+  <si>
+    <t>Key放下近战虫……</t>
+  </si>
+  <si>
+    <t>很好，请点击选中&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，让它跃过左侧的障碍物到达左上角的敌方建筑附近，然后点击下方&lt;color=#a0ff50&gt;离开房虫&lt;/color&gt;图标，放下近战虫攻击敌方建筑</t>
+  </si>
+  <si>
+    <t>Key要远离敌方炮台。</t>
+  </si>
+  <si>
+    <t>要远离敌方炮台。</t>
+  </si>
+  <si>
+    <t>Key已掌握空空降……</t>
+  </si>
+  <si>
+    <t>您已经掌握了空降战术，但此战术风险较高，遭敌方拦截时会非常被动。可在今后的作战中择机运用。</t>
+  </si>
+  <si>
+    <t>Key没看错你天才……</t>
+  </si>
+  <si>
+    <t>，我果然没有看错你，你是一个指挥天才！</t>
+  </si>
+  <si>
+    <t>Key都快打完了……</t>
+  </si>
+  <si>
+    <t>都快打完了你才来？</t>
+  </si>
+  <si>
+    <t>Key兵家常事……</t>
+  </si>
+  <si>
+    <t>胜败乃兵家常事，我仍然看好你的潜力！</t>
+  </si>
+  <si>
+    <t>Key八个方向都……</t>
+  </si>
+  <si>
+    <t>，八个方向都会有敌人向你进攻！</t>
+  </si>
+  <si>
+    <t>Key谁敢欺负咱俩……</t>
+  </si>
+  <si>
+    <t>要战便战！谁敢欺负咱俩？</t>
+  </si>
+  <si>
+    <t>Key星河孤守歌……</t>
+  </si>
+  <si>
+    <t>教官让我转给你1000晶体矿，如果不够就只能现场采集。你先顶住，我马上去找援军支援你！我现在赠你《星河孤守歌》与你共勉：
+     星河擂战鼓，虫影蔽天帷。
+     孤城锁铁衣，硝烟裂云楣。
+     血浸山河脊，骨铸不摧碑。
+     待我踏风雪，元帅载曦归！
+               ————文小言AI</t>
+  </si>
+  <si>
+    <t>Key像临阵逃脱……</t>
+  </si>
+  <si>
+    <t>！……这说的什么玩意？听起来还有点像临阵脱逃的说辞！
+  好吧，我一定守住！</t>
+  </si>
+  <si>
+    <t>Key守中央基地……</t>
+  </si>
+  <si>
+    <t>守护中央&lt;color=#a0ff50&gt;基地&lt;/color&gt;，否则任务失败。</t>
+  </si>
+  <si>
+    <t>Key援军来了。</t>
+  </si>
+  <si>
+    <t>援军来了。</t>
+  </si>
+  <si>
+    <t>Key来得正是时候……</t>
+  </si>
+  <si>
+    <t>来得正是时候，这回定要出口恶气！</t>
+  </si>
+  <si>
+    <t>Key胜利就在眼前……</t>
+  </si>
+  <si>
+    <t>守护中央&lt;color=#a0ff50&gt;基地&lt;/color&gt;，胜利就在眼前。</t>
   </si>
 </sst>
 </file>
@@ -3174,7 +4313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3419,6 +4558,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFD6D6DD"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -3925,6 +5070,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -3949,16 +5097,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -4334,7 +5479,7 @@
   <dimension ref="A1:U45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="12.75" style="13" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="14" customWidth="1"/>
     <col min="4" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="7" width="30.75" customWidth="1"/>
     <col min="8" max="9" width="44.875" customWidth="1"/>
@@ -4345,32 +5490,32 @@
     <col min="18" max="18" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" spans="1:18">
-      <c r="A1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="16" t="s">
+    <row r="1" s="17" customFormat="1" spans="1:18">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -4379,25 +5524,25 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="O1" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="P1" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="16" t="s">
+      <c r="Q1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="16" t="s">
+      <c r="R1" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4405,7 +5550,7 @@
       <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="38">
@@ -4440,7 +5585,7 @@
       <c r="A3" s="38">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="38">
@@ -4475,7 +5620,7 @@
       <c r="A4" s="33">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="33">
@@ -4513,7 +5658,7 @@
       <c r="A5" s="33">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="33">
@@ -4554,7 +5699,7 @@
       <c r="A6" s="39">
         <v>101</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C6" s="39">
@@ -4604,7 +5749,7 @@
       <c r="A7" s="39">
         <v>102</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C7" s="39">
@@ -4645,7 +5790,7 @@
       <c r="A8">
         <v>201</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C8">
@@ -4701,7 +5846,7 @@
       <c r="A9" s="32">
         <v>202</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C9" s="32">
@@ -4757,7 +5902,7 @@
       <c r="A10">
         <v>203</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C10">
@@ -4813,7 +5958,7 @@
       <c r="A11">
         <v>204</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C11">
@@ -4866,7 +6011,7 @@
       <c r="A12">
         <v>205</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C12">
@@ -4922,7 +6067,7 @@
       <c r="A13">
         <v>206</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C13">
@@ -4978,7 +6123,7 @@
       <c r="A14">
         <v>207</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C14">
@@ -5034,7 +6179,7 @@
       <c r="A15">
         <v>208</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>78</v>
       </c>
       <c r="C15">
@@ -5090,7 +6235,7 @@
       <c r="A16">
         <v>209</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C16">
@@ -5146,7 +6291,7 @@
       <c r="A17">
         <v>210</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>92</v>
       </c>
       <c r="C17">
@@ -5202,7 +6347,7 @@
       <c r="A18">
         <v>211</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>97</v>
       </c>
       <c r="C18">
@@ -5240,7 +6385,7 @@
       <c r="A19">
         <v>212</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C19">
@@ -5296,7 +6441,7 @@
       <c r="A20">
         <v>213</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>107</v>
       </c>
       <c r="C20">
@@ -5352,7 +6497,7 @@
       <c r="A21">
         <v>214</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>113</v>
       </c>
       <c r="C21">
@@ -5408,7 +6553,7 @@
       <c r="A22">
         <v>215</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>119</v>
       </c>
       <c r="C22">
@@ -5464,7 +6609,7 @@
       <c r="A23" s="33">
         <v>301</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>123</v>
       </c>
       <c r="C23" s="33">
@@ -5520,7 +6665,7 @@
       <c r="A24" s="33">
         <v>302</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>129</v>
       </c>
       <c r="C24" s="33">
@@ -5576,7 +6721,7 @@
       <c r="A25" s="33">
         <v>303</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>136</v>
       </c>
       <c r="C25" s="33">
@@ -5626,7 +6771,7 @@
       <c r="A26" s="33">
         <v>304</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>139</v>
       </c>
       <c r="C26" s="33">
@@ -5682,7 +6827,7 @@
       <c r="A27" s="33">
         <v>305</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>143</v>
       </c>
       <c r="C27" s="33">
@@ -5738,7 +6883,7 @@
       <c r="A28" s="33">
         <v>306</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>149</v>
       </c>
       <c r="C28" s="33">
@@ -5794,7 +6939,7 @@
       <c r="A29" s="33">
         <v>307</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>155</v>
       </c>
       <c r="C29" s="33">
@@ -5850,7 +6995,7 @@
       <c r="A30" s="33">
         <v>308</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>160</v>
       </c>
       <c r="C30" s="33">
@@ -5906,7 +7051,7 @@
       <c r="A31" s="33">
         <v>309</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>165</v>
       </c>
       <c r="C31" s="33">
@@ -5962,7 +7107,7 @@
       <c r="A32" s="33">
         <v>310</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>170</v>
       </c>
       <c r="C32" s="33">
@@ -6018,7 +7163,7 @@
       <c r="A33" s="33">
         <v>311</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>175</v>
       </c>
       <c r="C33" s="33">
@@ -6074,7 +7219,7 @@
       <c r="A34" s="33">
         <v>312</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>179</v>
       </c>
       <c r="C34" s="33">
@@ -6115,7 +7260,7 @@
       <c r="A35" s="31">
         <v>401</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="B35" s="16" t="s">
         <v>182</v>
       </c>
       <c r="C35" s="31">
@@ -6165,7 +7310,7 @@
       <c r="A36" s="31">
         <v>402</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="B36" s="16" t="s">
         <v>183</v>
       </c>
       <c r="C36" s="31">
@@ -6215,7 +7360,7 @@
       <c r="A37" s="31">
         <v>403</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="16" t="s">
         <v>184</v>
       </c>
       <c r="C37" s="31">
@@ -6268,7 +7413,7 @@
       <c r="A38" s="40">
         <v>404</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>186</v>
       </c>
       <c r="C38" s="40">
@@ -6321,7 +7466,7 @@
       <c r="A39" s="31">
         <v>405</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="16" t="s">
         <v>187</v>
       </c>
       <c r="C39">
@@ -6378,7 +7523,7 @@
       <c r="A40" s="31">
         <v>406</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B40" s="16" t="s">
         <v>188</v>
       </c>
       <c r="C40" s="31">
@@ -6431,7 +7576,7 @@
       <c r="A41" s="31">
         <v>407</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="14" t="s">
         <v>189</v>
       </c>
       <c r="C41">
@@ -6484,7 +7629,7 @@
       <c r="A42" s="31">
         <v>408</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>190</v>
       </c>
       <c r="C42">
@@ -6537,7 +7682,7 @@
       <c r="A43" s="31">
         <v>409</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>191</v>
       </c>
       <c r="C43">
@@ -6590,7 +7735,7 @@
       <c r="A44" s="31">
         <v>410</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>192</v>
       </c>
       <c r="C44">
@@ -6643,7 +7788,7 @@
       <c r="A45" s="31">
         <v>411</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="14" t="s">
         <v>193</v>
       </c>
       <c r="C45">
@@ -6714,33 +7859,33 @@
     <col min="8" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" spans="1:8">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:8">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>333</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>334</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>337</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1" spans="1:8">
+    <row r="2" s="14" customFormat="1" spans="1:8">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -6760,7 +7905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="13" customFormat="1" spans="1:8">
+    <row r="3" s="14" customFormat="1" spans="1:8">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -7205,13 +8350,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="13"/>
+      <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="22">
@@ -7247,19 +8392,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>335</v>
       </c>
     </row>
@@ -7559,7 +8704,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C276"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.875" customWidth="1"/>
@@ -7788,7 +8933,7 @@
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="10" t="s">
         <v>487</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -7931,10 +9076,10 @@
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="11" t="s">
         <v>526</v>
       </c>
       <c r="C34" t="s">
@@ -7942,10 +9087,10 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="11" t="s">
         <v>528</v>
       </c>
       <c r="C35" t="s">
@@ -7953,10 +9098,10 @@
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>530</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>229</v>
       </c>
       <c r="C36" t="s">
@@ -7964,10 +9109,10 @@
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>200</v>
       </c>
       <c r="C37" t="s">
@@ -7975,10 +9120,10 @@
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>533</v>
       </c>
       <c r="C38" t="s">
@@ -7986,10 +9131,10 @@
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="13" t="s">
         <v>535</v>
       </c>
       <c r="C39" t="s">
@@ -7997,10 +9142,10 @@
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>201</v>
       </c>
       <c r="C40" t="s">
@@ -8008,10 +9153,10 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="15" t="s">
         <v>202</v>
       </c>
       <c r="C41" t="s">
@@ -8019,10 +9164,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>203</v>
       </c>
       <c r="C42" t="s">
@@ -8030,10 +9175,10 @@
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>204</v>
       </c>
       <c r="C43" t="s">
@@ -8041,10 +9186,10 @@
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>205</v>
       </c>
       <c r="C44" t="s">
@@ -8052,10 +9197,10 @@
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="14" t="s">
         <v>206</v>
       </c>
       <c r="C45" t="s">
@@ -8063,10 +9208,10 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="14" t="s">
         <v>207</v>
       </c>
       <c r="C46" t="s">
@@ -8074,10 +9219,10 @@
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="14" t="s">
         <v>208</v>
       </c>
       <c r="C47" t="s">
@@ -8085,10 +9230,10 @@
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="14" t="s">
         <v>209</v>
       </c>
       <c r="C48" t="s">
@@ -8096,10 +9241,10 @@
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="14" t="s">
         <v>210</v>
       </c>
       <c r="C49" t="s">
@@ -8107,10 +9252,10 @@
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="14" t="s">
         <v>211</v>
       </c>
       <c r="C50" t="s">
@@ -8118,10 +9263,10 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C51" t="s">
@@ -8129,10 +9274,10 @@
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="14" t="s">
         <v>212</v>
       </c>
       <c r="C52" t="s">
@@ -8140,10 +9285,10 @@
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="14" t="s">
         <v>213</v>
       </c>
       <c r="C53" t="s">
@@ -8151,10 +9296,10 @@
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="14" t="s">
         <v>214</v>
       </c>
       <c r="C54" t="s">
@@ -8162,10 +9307,10 @@
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="12" t="s">
         <v>215</v>
       </c>
       <c r="C55" t="s">
@@ -8173,10 +9318,10 @@
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="12" t="s">
         <v>216</v>
       </c>
       <c r="C56" t="s">
@@ -8184,10 +9329,10 @@
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="12" t="s">
         <v>217</v>
       </c>
       <c r="C57" t="s">
@@ -8195,10 +9340,10 @@
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>218</v>
       </c>
       <c r="C58" t="s">
@@ -8206,10 +9351,10 @@
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="12" t="s">
         <v>219</v>
       </c>
       <c r="C59" t="s">
@@ -8217,10 +9362,10 @@
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="12" t="s">
         <v>220</v>
       </c>
       <c r="C60" t="s">
@@ -8228,10 +9373,10 @@
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="12" t="s">
         <v>221</v>
       </c>
       <c r="C61" t="s">
@@ -8239,10 +9384,10 @@
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="12" t="s">
         <v>222</v>
       </c>
       <c r="C62" t="s">
@@ -8250,10 +9395,10 @@
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="12" t="s">
         <v>168</v>
       </c>
       <c r="C63" t="s">
@@ -8261,10 +9406,10 @@
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="12" t="s">
         <v>173</v>
       </c>
       <c r="C64" t="s">
@@ -8272,10 +9417,10 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="12" t="s">
         <v>177</v>
       </c>
       <c r="C65" t="s">
@@ -8283,10 +9428,10 @@
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C66" t="s">
@@ -8294,10 +9439,10 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B67" s="15" t="s">
+      <c r="B67" s="16" t="s">
         <v>265</v>
       </c>
       <c r="C67" t="s">
@@ -8305,10 +9450,10 @@
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B68" s="15" t="s">
+      <c r="B68" s="16" t="s">
         <v>266</v>
       </c>
       <c r="C68" t="s">
@@ -8316,10 +9461,10 @@
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="B69" s="15" t="s">
+      <c r="B69" s="16" t="s">
         <v>566</v>
       </c>
       <c r="C69" t="s">
@@ -8327,10 +9472,10 @@
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B70" s="16" t="s">
+      <c r="B70" s="17" t="s">
         <v>268</v>
       </c>
       <c r="C70" t="s">
@@ -8338,10 +9483,10 @@
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="B71" s="15" t="s">
+      <c r="B71" s="16" t="s">
         <v>269</v>
       </c>
       <c r="C71" t="s">
@@ -8349,10 +9494,10 @@
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B72" s="15" t="s">
+      <c r="B72" s="16" t="s">
         <v>270</v>
       </c>
       <c r="C72" t="s">
@@ -8360,10 +9505,10 @@
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="14" t="s">
         <v>571</v>
       </c>
       <c r="C73" t="s">
@@ -8371,10 +9516,10 @@
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="14" t="s">
         <v>573</v>
       </c>
       <c r="C74" t="s">
@@ -8382,10 +9527,10 @@
       </c>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="14" t="s">
         <v>575</v>
       </c>
       <c r="C75" t="s">
@@ -8393,10 +9538,10 @@
       </c>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C76" t="s">
@@ -8404,10 +9549,10 @@
       </c>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="14" t="s">
         <v>275</v>
       </c>
       <c r="C77" t="s">
@@ -8792,7 +9937,7 @@
       <c r="A112" s="5" t="s">
         <v>681</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="18" t="s">
         <v>682</v>
       </c>
       <c r="C112" s="8" t="s">
@@ -8814,7 +9959,7 @@
       <c r="A114" t="s">
         <v>687</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="B114" s="18" t="s">
         <v>688</v>
       </c>
       <c r="C114" s="8" t="s">
@@ -8836,7 +9981,7 @@
       <c r="A116" t="s">
         <v>693</v>
       </c>
-      <c r="B116" s="17" t="s">
+      <c r="B116" s="18" t="s">
         <v>694</v>
       </c>
       <c r="C116" s="8" t="s">
@@ -9100,7 +10245,7 @@
       <c r="A140" t="s">
         <v>765</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B140" s="18" t="s">
         <v>766</v>
       </c>
       <c r="C140" s="8" t="s">
@@ -9122,7 +10267,7 @@
       <c r="A142" t="s">
         <v>771</v>
       </c>
-      <c r="B142" s="17" t="s">
+      <c r="B142" s="18" t="s">
         <v>772</v>
       </c>
       <c r="C142" s="8" t="s">
@@ -9185,128 +10330,1158 @@
       </c>
     </row>
     <row r="148" ht="14.25" spans="1:3">
-      <c r="A148" s="18" t="s">
+      <c r="A148" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="B148" s="19" t="s">
+      <c r="B148" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="C148" s="20" t="s">
+      <c r="C148" s="19" t="s">
         <v>791</v>
       </c>
     </row>
     <row r="149" ht="14.25" spans="1:3">
-      <c r="A149" s="21" t="s">
+      <c r="A149" s="6" t="s">
         <v>792</v>
       </c>
-      <c r="B149" s="19" t="s">
+      <c r="B149" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="C149" s="20" t="s">
+      <c r="C149" s="19" t="s">
         <v>794</v>
       </c>
     </row>
     <row r="150" ht="14.25" spans="1:3">
-      <c r="A150" s="21" t="s">
+      <c r="A150" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="B150" s="19" t="s">
+      <c r="B150" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="C150" s="20" t="s">
+      <c r="C150" s="19" t="s">
         <v>797</v>
       </c>
     </row>
     <row r="151" ht="14.25" spans="1:3">
-      <c r="A151" s="21" t="s">
+      <c r="A151" s="6" t="s">
         <v>798</v>
       </c>
-      <c r="B151" s="19" t="s">
+      <c r="B151" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="C151" s="20" t="s">
+      <c r="C151" s="19" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="152" ht="14.25" spans="1:3">
-      <c r="A152" s="21" t="s">
+      <c r="A152" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="B152" s="19" t="s">
+      <c r="B152" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="C152" s="20" t="s">
+      <c r="C152" s="19" t="s">
         <v>803</v>
       </c>
     </row>
     <row r="153" ht="14.25" spans="1:3">
-      <c r="A153" s="21" t="s">
+      <c r="A153" s="6" t="s">
         <v>804</v>
       </c>
-      <c r="B153" s="19" t="s">
+      <c r="B153" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="C153" s="20" t="s">
+      <c r="C153" s="19" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="154" ht="14.25" spans="1:3">
-      <c r="A154" s="21" t="s">
+      <c r="A154" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="B154" s="19" t="s">
+      <c r="B154" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="C154" s="20" t="s">
+      <c r="C154" s="19" t="s">
         <v>809</v>
       </c>
     </row>
     <row r="155" ht="14.25" spans="1:3">
-      <c r="A155" s="21" t="s">
+      <c r="A155" s="6" t="s">
         <v>810</v>
       </c>
-      <c r="B155" s="19" t="s">
+      <c r="B155" s="5" t="s">
         <v>811</v>
       </c>
+      <c r="C155" s="19" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="156" ht="14.25" spans="1:3">
-      <c r="A156" s="21" t="s">
-        <v>812</v>
-      </c>
-      <c r="B156" s="19" t="s">
+      <c r="A156" s="6" t="s">
         <v>813</v>
       </c>
+      <c r="B156" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="157" ht="14.25" spans="1:3">
-      <c r="A157" s="21" t="s">
-        <v>814</v>
-      </c>
-      <c r="B157" s="19" t="s">
+      <c r="A157" s="6" t="s">
+        <v>816</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>817</v>
+      </c>
+      <c r="C157" s="19" t="s">
         <v>815</v>
       </c>
     </row>
     <row r="158" ht="14.25" spans="1:3">
-      <c r="A158" s="21" t="s">
-        <v>816</v>
-      </c>
-      <c r="B158" s="19" t="s">
-        <v>817</v>
+      <c r="A158" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>819</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>820</v>
       </c>
     </row>
     <row r="159" ht="14.25" spans="1:3">
-      <c r="A159" s="21" t="s">
-        <v>818</v>
-      </c>
-      <c r="B159" s="19" t="s">
-        <v>819</v>
+      <c r="A159" s="6" t="s">
+        <v>821</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>823</v>
       </c>
     </row>
     <row r="160" ht="14.25" spans="1:3">
-      <c r="A160" s="21" t="s">
-        <v>820</v>
-      </c>
-      <c r="B160" s="19" t="s">
-        <v>821</v>
+      <c r="A160" s="6" t="s">
+        <v>824</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>825</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="161" ht="27" spans="1:3">
+      <c r="A161" t="s">
+        <v>827</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="162" ht="14.25" spans="1:3">
+      <c r="A162" t="s">
+        <v>830</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="163" ht="14.25" spans="1:3">
+      <c r="A163" t="s">
+        <v>833</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>834</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="164" ht="14.25" spans="1:3">
+      <c r="A164" t="s">
+        <v>836</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>837</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="165" ht="14.25" spans="1:3">
+      <c r="A165" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>840</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="166" ht="14.25" spans="1:3">
+      <c r="A166" t="s">
+        <v>842</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="167" ht="28.5" spans="1:3">
+      <c r="A167" t="s">
+        <v>845</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="168" ht="14.25" spans="1:3">
+      <c r="A168" t="s">
+        <v>848</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="169" ht="28.5" spans="1:3">
+      <c r="A169" t="s">
+        <v>851</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>852</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="170" ht="14.25" spans="1:3">
+      <c r="A170" t="s">
+        <v>854</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="171" ht="14.25" spans="1:3">
+      <c r="A171" t="s">
+        <v>857</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="172" ht="14.25" spans="1:3">
+      <c r="A172" t="s">
+        <v>860</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="173" ht="25.5" spans="1:3">
+      <c r="A173" t="s">
+        <v>863</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>864</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="174" ht="14.25" spans="1:3">
+      <c r="A174" t="s">
+        <v>866</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="175" ht="28.5" spans="1:3">
+      <c r="A175" t="s">
+        <v>869</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>870</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="176" ht="14.25" spans="1:3">
+      <c r="A176" t="s">
+        <v>872</v>
+      </c>
+      <c r="B176" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="177" ht="14.25" spans="1:3">
+      <c r="A177" t="s">
+        <v>875</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>876</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="178" ht="14.25" spans="1:3">
+      <c r="A178" t="s">
+        <v>878</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="C178" s="8" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="179" ht="14.25" spans="1:3">
+      <c r="A179" t="s">
+        <v>881</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="180" ht="27" spans="1:3">
+      <c r="A180" t="s">
+        <v>884</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="181" ht="14.25" spans="1:3">
+      <c r="A181" t="s">
+        <v>887</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>888</v>
+      </c>
+      <c r="C181" s="8" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="182" ht="39.75" spans="1:3">
+      <c r="A182" t="s">
+        <v>890</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="C182" s="8" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="183" ht="27" spans="1:3">
+      <c r="A183" t="s">
+        <v>893</v>
+      </c>
+      <c r="B183" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="184" ht="39.75" spans="1:3">
+      <c r="A184" t="s">
+        <v>896</v>
+      </c>
+      <c r="B184" s="6" t="s">
+        <v>897</v>
+      </c>
+      <c r="C184" s="8" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="185" ht="14.25" spans="1:3">
+      <c r="A185" t="s">
+        <v>899</v>
+      </c>
+      <c r="B185" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="C185" s="8" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="186" ht="25.5" spans="1:3">
+      <c r="A186" t="s">
+        <v>902</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="C186" s="8" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="187" ht="14.25" spans="1:3">
+      <c r="A187" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="B187" s="6" t="s">
+        <v>906</v>
+      </c>
+      <c r="C187" s="8" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="188" ht="14.25" spans="1:3">
+      <c r="A188" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="B188" s="6" t="s">
+        <v>858</v>
+      </c>
+      <c r="C188" s="8" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="189" ht="28.5" spans="1:3">
+      <c r="A189" t="s">
+        <v>909</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="C189" s="8" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="190" ht="14.25" spans="1:3">
+      <c r="A190" t="s">
+        <v>912</v>
+      </c>
+      <c r="B190" s="6" t="s">
+        <v>913</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="191" ht="14.25" spans="1:3">
+      <c r="A191" s="10" t="s">
+        <v>915</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3">
+      <c r="A192" t="s">
+        <v>917</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="193" ht="14.25" spans="1:2">
+      <c r="A193" t="s">
+        <v>919</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" t="s">
+        <v>921</v>
+      </c>
+      <c r="B194" s="10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="195" ht="14.25" spans="1:2">
+      <c r="A195" s="10" t="s">
+        <v>923</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="196" ht="14.25" spans="1:2">
+      <c r="A196" s="10" t="s">
+        <v>925</v>
+      </c>
+      <c r="B196" s="10" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="197" ht="14.25" spans="1:2">
+      <c r="A197" s="10" t="s">
+        <v>927</v>
+      </c>
+      <c r="B197" s="10" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="198" ht="14.25" spans="1:2">
+      <c r="A198" s="10" t="s">
+        <v>929</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="199" ht="41.25" spans="1:2">
+      <c r="A199" s="20" t="s">
+        <v>931</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25" spans="1:2">
+      <c r="A200" s="10" t="s">
+        <v>933</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25" spans="1:2">
+      <c r="A201" s="10" t="s">
+        <v>935</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25" spans="1:2">
+      <c r="A202" s="10" t="s">
+        <v>937</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" t="s">
+        <v>939</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25" spans="1:2">
+      <c r="A204" t="s">
+        <v>941</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="205" ht="27" spans="1:2">
+      <c r="A205" t="s">
+        <v>943</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="206" ht="14.25" spans="1:2">
+      <c r="A206" t="s">
+        <v>945</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" t="s">
+        <v>947</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="208" ht="39.75" spans="1:2">
+      <c r="A208" t="s">
+        <v>949</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="209" ht="25.5" spans="1:2">
+      <c r="A209" t="s">
+        <v>951</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="210" ht="39.75" spans="1:2">
+      <c r="A210" t="s">
+        <v>953</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="211" ht="14.25" spans="1:2">
+      <c r="A211" t="s">
+        <v>955</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="212" ht="28.5" spans="1:2">
+      <c r="A212" t="s">
+        <v>957</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="213" ht="14.25" spans="1:2">
+      <c r="A213" t="s">
+        <v>959</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="214" ht="28.5" spans="1:2">
+      <c r="A214" t="s">
+        <v>961</v>
+      </c>
+      <c r="B214" s="20" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="215" ht="14.25" spans="1:2">
+      <c r="A215" s="10" t="s">
+        <v>963</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="216" ht="14.25" spans="1:2">
+      <c r="A216" s="20" t="s">
+        <v>965</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="B217" s="10" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="218" ht="14.25" spans="1:2">
+      <c r="A218" s="10" t="s">
+        <v>968</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25" spans="1:2">
+      <c r="A219" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25" spans="1:2">
+      <c r="A220" t="s">
+        <v>972</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25" spans="1:2">
+      <c r="A221" s="10" t="s">
+        <v>974</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25" spans="1:2">
+      <c r="A222" s="10" t="s">
+        <v>975</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="223" ht="14.25" spans="1:2">
+      <c r="A223" s="10" t="s">
+        <v>977</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" t="s">
+        <v>979</v>
+      </c>
+      <c r="B224" s="10" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" t="s">
+        <v>981</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" t="s">
+        <v>983</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="227" ht="67.5" spans="1:2">
+      <c r="A227" t="s">
+        <v>985</v>
+      </c>
+      <c r="B227" s="21" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25" spans="1:2">
+      <c r="A228" s="10" t="s">
+        <v>987</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" t="s">
+        <v>989</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" t="s">
+        <v>991</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="231" ht="28.5" spans="1:2">
+      <c r="A231" t="s">
+        <v>993</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" t="s">
+        <v>995</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="233" ht="14.25" spans="1:2">
+      <c r="A233" s="10" t="s">
+        <v>997</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="234" ht="14.25" spans="1:2">
+      <c r="A234" t="s">
+        <v>999</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="241" ht="27" spans="1:2">
+      <c r="A241" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="244" ht="28.5" spans="1:2">
+      <c r="A244" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="246" ht="14.25" spans="1:2">
+      <c r="A246" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="247" ht="14.25" spans="1:2">
+      <c r="A247" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="249" ht="25.5" spans="1:2">
+      <c r="A249" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="251" ht="14.25" spans="1:2">
+      <c r="A251" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="256" ht="27" spans="1:2">
+      <c r="A256" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="258" ht="28.5" spans="1:2">
+      <c r="A258" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="260" ht="14.25" spans="1:2">
+      <c r="A260" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="261" ht="27" spans="1:2">
+      <c r="A261" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="262" ht="28.5" spans="1:2">
+      <c r="A262" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="264" ht="25.5" spans="1:2">
+      <c r="A264" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B267" s="10" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B269" s="10" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="270" ht="94.5" spans="1:2">
+      <c r="A270" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B270" s="21" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="271" ht="27" spans="1:2">
+      <c r="A271" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B271" s="21" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="272" ht="14.25" spans="1:2">
+      <c r="A272" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B272" s="10" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="273" ht="14.25" spans="1:2">
+      <c r="B273" s="10" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B275" s="10" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="276" ht="14.25" spans="1:2">
+      <c r="A276" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>1082</v>
       </c>
     </row>
   </sheetData>
@@ -9321,39 +11496,39 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="2" width="9" style="13"/>
+    <col min="2" max="2" width="9" style="14"/>
     <col min="3" max="4" width="10.875" customWidth="1"/>
     <col min="5" max="5" width="7.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" spans="1:7">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+    <row r="1" s="14" customFormat="1" spans="1:7">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="2" s="13" customFormat="1" spans="1:7">
+    <row r="2" s="14" customFormat="1" spans="1:7">
       <c r="A2" s="33">
         <v>4</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>200</v>
       </c>
       <c r="C2" s="33">
@@ -9376,7 +11551,7 @@
       <c r="A3">
         <v>201</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>201</v>
       </c>
       <c r="C3">
@@ -9399,7 +11574,7 @@
       <c r="A4">
         <v>202</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>202</v>
       </c>
       <c r="C4">
@@ -9422,7 +11597,7 @@
       <c r="A5">
         <v>203</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>203</v>
       </c>
       <c r="C5">
@@ -9445,7 +11620,7 @@
       <c r="A6">
         <v>204</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>204</v>
       </c>
       <c r="C6">
@@ -9468,7 +11643,7 @@
       <c r="A7">
         <v>205</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>205</v>
       </c>
       <c r="C7">
@@ -9491,7 +11666,7 @@
       <c r="A8">
         <v>206</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>206</v>
       </c>
       <c r="C8">
@@ -9514,7 +11689,7 @@
       <c r="A9">
         <v>207</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>207</v>
       </c>
       <c r="C9">
@@ -9537,7 +11712,7 @@
       <c r="A10">
         <v>208</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>208</v>
       </c>
       <c r="C10">
@@ -9560,7 +11735,7 @@
       <c r="A11">
         <v>209</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>209</v>
       </c>
       <c r="C11">
@@ -9583,7 +11758,7 @@
       <c r="A12">
         <v>210</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>210</v>
       </c>
       <c r="C12">
@@ -9606,7 +11781,7 @@
       <c r="A13">
         <v>211</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>211</v>
       </c>
       <c r="C13">
@@ -9629,7 +11804,7 @@
       <c r="A14">
         <v>212</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C14">
@@ -9652,7 +11827,7 @@
       <c r="A15">
         <v>213</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>212</v>
       </c>
       <c r="C15">
@@ -9675,7 +11850,7 @@
       <c r="A16">
         <v>214</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>213</v>
       </c>
       <c r="C16">
@@ -9698,7 +11873,7 @@
       <c r="A17">
         <v>215</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>214</v>
       </c>
       <c r="C17">
@@ -10023,7 +12198,7 @@
       <c r="C1" t="s">
         <v>224</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>225</v>
       </c>
       <c r="E1" t="s">
@@ -10345,35 +12520,35 @@
   <dimension ref="A1:H27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="9" style="13"/>
+    <col min="2" max="2" width="9" style="14"/>
     <col min="3" max="3" width="30.75" customWidth="1"/>
     <col min="4" max="6" width="44.875" customWidth="1"/>
     <col min="7" max="7" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" spans="1:8">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
+    <row r="1" s="15" customFormat="1" spans="1:8">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>236</v>
       </c>
     </row>
@@ -10381,7 +12556,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>201</v>
       </c>
       <c r="C2" t="s">
@@ -10407,7 +12582,7 @@
       <c r="A3" s="32">
         <v>202</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="15" t="s">
         <v>202</v>
       </c>
       <c r="C3" s="32" t="s">
@@ -10433,7 +12608,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>203</v>
       </c>
       <c r="C4" t="s">
@@ -10459,7 +12634,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>204</v>
       </c>
       <c r="C5" t="s">
@@ -10485,7 +12660,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>205</v>
       </c>
       <c r="C6" t="s">
@@ -10511,7 +12686,7 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>206</v>
       </c>
       <c r="C7" t="s">
@@ -10537,7 +12712,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>207</v>
       </c>
       <c r="C8" t="s">
@@ -10563,7 +12738,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>208</v>
       </c>
       <c r="C9" t="s">
@@ -10589,7 +12764,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>209</v>
       </c>
       <c r="C10" t="s">
@@ -10615,7 +12790,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>210</v>
       </c>
       <c r="C11" t="s">
@@ -10641,7 +12816,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>211</v>
       </c>
       <c r="E12">
@@ -10655,7 +12830,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C13" t="s">
@@ -10681,7 +12856,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>212</v>
       </c>
       <c r="C14" t="s">
@@ -10707,7 +12882,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>213</v>
       </c>
       <c r="C15" t="s">
@@ -10733,7 +12908,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>214</v>
       </c>
       <c r="C16" t="s">
@@ -10759,7 +12934,7 @@
       <c r="A17">
         <v>401</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>265</v>
       </c>
       <c r="C17" t="s">
@@ -10779,7 +12954,7 @@
       <c r="A18">
         <v>402</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>266</v>
       </c>
       <c r="C18" t="s">
@@ -10799,7 +12974,7 @@
       <c r="A19">
         <v>403</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>267</v>
       </c>
       <c r="C19" t="s">
@@ -10819,7 +12994,7 @@
       <c r="A20" s="34">
         <v>404</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>268</v>
       </c>
       <c r="C20" s="32" t="s">
@@ -10845,7 +13020,7 @@
       <c r="A21" s="30">
         <v>405</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>269</v>
       </c>
       <c r="C21" t="s">
@@ -10871,7 +13046,7 @@
       <c r="A22" s="30">
         <v>406</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>270</v>
       </c>
       <c r="C22" t="s">
@@ -10897,7 +13072,7 @@
       <c r="A23" s="31">
         <v>407</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>271</v>
       </c>
       <c r="C23" t="s">
@@ -10923,7 +13098,7 @@
       <c r="A24" s="31">
         <v>408</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>272</v>
       </c>
       <c r="C24" t="s">
@@ -10949,7 +13124,7 @@
       <c r="A25" s="31">
         <v>409</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>273</v>
       </c>
       <c r="C25" t="s">
@@ -10975,7 +13150,7 @@
       <c r="A26" s="31">
         <v>410</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C26" t="s">
@@ -11001,7 +13176,7 @@
       <c r="A27" s="31">
         <v>411</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>275</v>
       </c>
       <c r="C27" t="s">
@@ -11037,7 +13212,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5.125" customWidth="1"/>
-    <col min="2" max="2" width="8.875" style="13" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="14" customWidth="1"/>
     <col min="3" max="4" width="9.875" customWidth="1"/>
     <col min="5" max="6" width="8.125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -11068,7 +13243,7 @@
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="15" t="s">
         <v>194</v>
       </c>
       <c r="C1" s="32" t="s">
@@ -11092,7 +13267,7 @@
       <c r="I1" s="32" t="s">
         <v>282</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="15" t="s">
         <v>283</v>
       </c>
       <c r="K1" s="32" t="s">
@@ -11133,7 +13308,7 @@
       <c r="A2">
         <v>201</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>201</v>
       </c>
       <c r="C2">
@@ -11189,7 +13364,7 @@
       <c r="A3">
         <v>202</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>202</v>
       </c>
       <c r="C3">
@@ -11251,7 +13426,7 @@
       <c r="A4">
         <v>203</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>203</v>
       </c>
       <c r="C4">
@@ -11307,7 +13482,7 @@
       <c r="A5">
         <v>204</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>204</v>
       </c>
       <c r="C5">
@@ -11369,7 +13544,7 @@
       <c r="A6">
         <v>205</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>205</v>
       </c>
       <c r="C6">
@@ -11425,7 +13600,7 @@
       <c r="A7">
         <v>206</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>206</v>
       </c>
       <c r="C7">
@@ -11487,7 +13662,7 @@
       <c r="A8">
         <v>207</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>207</v>
       </c>
       <c r="C8">
@@ -11549,7 +13724,7 @@
       <c r="A9">
         <v>208</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>208</v>
       </c>
       <c r="C9">
@@ -11605,7 +13780,7 @@
       <c r="A10">
         <v>209</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>209</v>
       </c>
       <c r="C10">
@@ -11661,7 +13836,7 @@
       <c r="A11">
         <v>210</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>210</v>
       </c>
       <c r="C11">
@@ -11720,7 +13895,7 @@
       <c r="A12">
         <v>211</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>211</v>
       </c>
       <c r="C12">
@@ -11773,7 +13948,7 @@
       <c r="A13">
         <v>212</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C13">
@@ -11823,7 +13998,7 @@
       <c r="A14">
         <v>213</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>212</v>
       </c>
       <c r="C14">
@@ -11882,7 +14057,7 @@
       <c r="A15">
         <v>214</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>213</v>
       </c>
       <c r="C15">
@@ -11938,7 +14113,7 @@
       <c r="A16">
         <v>215</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>214</v>
       </c>
       <c r="C16">
@@ -12000,7 +14175,7 @@
       <c r="A17" s="33">
         <v>301</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>215</v>
       </c>
       <c r="C17">
@@ -12059,7 +14234,7 @@
       <c r="A18" s="33">
         <v>302</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>216</v>
       </c>
       <c r="C18">
@@ -12118,7 +14293,7 @@
       <c r="A19" s="33">
         <v>303</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>217</v>
       </c>
       <c r="C19">
@@ -12177,7 +14352,7 @@
       <c r="A20" s="33">
         <v>304</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>218</v>
       </c>
       <c r="C20">
@@ -12236,7 +14411,7 @@
       <c r="A21">
         <v>305</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>219</v>
       </c>
       <c r="C21">
@@ -12298,7 +14473,7 @@
       <c r="A22" s="33">
         <v>306</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>220</v>
       </c>
       <c r="C22">
@@ -12357,7 +14532,7 @@
       <c r="A23" s="33">
         <v>307</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>221</v>
       </c>
       <c r="C23">
@@ -12416,7 +14591,7 @@
       <c r="A24" s="33">
         <v>308</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>222</v>
       </c>
       <c r="C24">
@@ -12475,7 +14650,7 @@
       <c r="A25" s="33">
         <v>309</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>168</v>
       </c>
       <c r="C25">
@@ -12534,7 +14709,7 @@
       <c r="A26" s="33">
         <v>310</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>173</v>
       </c>
       <c r="C26">
@@ -12593,7 +14768,7 @@
       <c r="A27" s="33">
         <v>311</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>177</v>
       </c>
       <c r="C27">
@@ -12652,7 +14827,7 @@
       <c r="A28" s="33">
         <v>312</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C28">
@@ -12711,7 +14886,7 @@
       <c r="A29">
         <v>401</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>265</v>
       </c>
       <c r="C29">
@@ -12773,7 +14948,7 @@
       <c r="A30">
         <v>402</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>266</v>
       </c>
       <c r="C30">
@@ -12829,7 +15004,7 @@
       <c r="A31">
         <v>403</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="14" t="s">
         <v>267</v>
       </c>
       <c r="C31">
@@ -12885,7 +15060,7 @@
       <c r="A32" s="30">
         <v>404</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>268</v>
       </c>
       <c r="C32">
@@ -12947,7 +15122,7 @@
       <c r="A33" s="30">
         <v>405</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>269</v>
       </c>
       <c r="C33">
@@ -13003,7 +15178,7 @@
       <c r="A34" s="30">
         <v>406</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>270</v>
       </c>
       <c r="C34">
@@ -13059,7 +15234,7 @@
       <c r="A35" s="31">
         <v>407</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>271</v>
       </c>
       <c r="C35">
@@ -13115,7 +15290,7 @@
       <c r="A36" s="31">
         <v>408</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="14" t="s">
         <v>272</v>
       </c>
       <c r="C36">
@@ -13174,7 +15349,7 @@
       <c r="A37" s="31">
         <v>409</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>273</v>
       </c>
       <c r="C37">
@@ -13233,7 +15408,7 @@
       <c r="A38" s="31">
         <v>410</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="14" t="s">
         <v>274</v>
       </c>
       <c r="C38">
@@ -13283,7 +15458,7 @@
       <c r="A39" s="31">
         <v>411</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
         <v>275</v>
       </c>
       <c r="C39">
@@ -13544,29 +15719,29 @@
     <col min="7" max="8" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="1" spans="1:8">
-      <c r="A1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="14" t="s">
+    <row r="1" s="15" customFormat="1" spans="1:8">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="15" t="s">
         <v>196</v>
       </c>
     </row>
@@ -13794,16 +15969,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="15" t="s">
         <v>196</v>
       </c>
     </row>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="1264">
   <si>
     <t>类型</t>
   </si>
@@ -1652,7 +1652,7 @@
     <t>Tanks and aircraft are expensive to build. Deploy them prudently based on battlefield conditions.</t>
   </si>
   <si>
-    <t>Key资源紧张时不造它们</t>
+    <t>Key资源紧张时不造它们……</t>
   </si>
   <si>
     <t>好。资源紧张时不造它们。</t>
@@ -1661,7 +1661,7 @@
     <t>Got it. Don't build them when resources are tight.</t>
   </si>
   <si>
-    <t>Key使用强行走来手动中断攻击</t>
+    <t>Key使用强行走来手动中断攻击……</t>
   </si>
   <si>
     <r>
@@ -1718,7 +1718,7 @@
     <t>Click to select the aircraft, then click the &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; button below to make the aircraft stop attacking and move outside the gun emplacements' firing range.</t>
   </si>
   <si>
-    <t>Key强行走的过程中不会攻击敌人</t>
+    <t>Key强行走的过程中……</t>
   </si>
   <si>
     <t>强行走的过程中，不会攻击敌人。</t>
@@ -3466,6 +3466,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>当坦克开始攻击前摇时，地面上会出现炸点特效。仔细观察，一旦看到炸点特效出现，立刻使用</t>
     </r>
     <r>
@@ -3554,13 +3560,19 @@
     <t>This disciple shall heed the elder’s teachings.</t>
   </si>
   <si>
-    <t>Key清兵挑坦克胜利……</t>
+    <t>Key兵挑坦克胜利……</t>
   </si>
   <si>
     <t>Key少侠领悟枪兵对抗坦克……</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>，你已领悟枪兵对抗坦克的闪避心法。</t>
     </r>
     <r>
@@ -3601,49 +3613,79 @@
     <t>情报显示：敌人已发现我们的巢穴入口，即将入侵，请做好准备。</t>
   </si>
   <si>
+    <t>Intel indicates: The enemy has located our hive entrance and is launching an invasion. Prepare for combat.</t>
+  </si>
+  <si>
     <t>Key我仅受过简单训练……</t>
   </si>
   <si>
     <t>可是我仅受过简单的指挥训练。</t>
   </si>
   <si>
+    <t>But I only received basic command training.</t>
+  </si>
+  <si>
     <t>Key资源管够……</t>
   </si>
   <si>
     <t>我们会提供足够的初始晶体矿和燃气矿，你&lt;color=#a0ff50&gt;不用再从零开始采集&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>We will provide ample starting Crystalline Minerals and Vespene Gas. You &lt;color=#a0ff50&gt;won’t need to gather resources from scratch&lt;/color&gt;.</t>
+  </si>
+  <si>
     <t>Key还是没把握……</t>
   </si>
   <si>
     <t>我还是没有把握。</t>
   </si>
   <si>
+    <t>I still don’t feel confident.</t>
+  </si>
+  <si>
     <t>Key传授速成口诀……</t>
   </si>
   <si>
     <t>我会传授你指挥实战速成口诀，三分钟即可成为实战高手。</t>
   </si>
   <si>
+    <t>I’ll teach you the Rapid Combat Command Mantra—master real combat skills in just three minutes.</t>
+  </si>
+  <si>
     <t>Key真有这种口诀……</t>
   </si>
   <si>
     <t>真有这种口诀的话就应该在训练战时告诉我啊！</t>
   </si>
   <si>
+    <t>If this mantra exists, you should’ve taught it to me during training drills!</t>
+  </si>
+  <si>
     <t>Key只有在实战中才有用……</t>
   </si>
   <si>
     <t>实战口诀只有在九死一生的实战中才有用！</t>
   </si>
   <si>
+    <t>The mantra only works in do-or-die real battles!</t>
+  </si>
+  <si>
     <t>Key九死一生……</t>
   </si>
   <si>
     <t>九死一生？形势严峻啊，我会全力以赴的!</t>
   </si>
   <si>
+    <t>Do-or-die? The situation is grim. I’ll give it everything I’ve got!</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>Key1</t>
     </r>
     <r>
@@ -3669,94 +3711,165 @@
     <t>1个虫巢只能照顾&lt;color=#a0ff50&gt;3只幼虫&lt;/color&gt;。&lt;color=#a0ff50&gt;让工虫变异更多的虫巢&lt;/color&gt;，才有更多的幼虫可供蜕变。&lt;color=#a0ff50&gt;多蜕变房虫&lt;/color&gt;，增加活动单位上限。</t>
   </si>
   <si>
+    <t>One Hive can only support &lt;color=#a0ff50&gt;3 Larvae&lt;/color&gt;. &lt;color=#a0ff50&gt;Morph Drones into more Hives&lt;/color&gt; to produce additional Larvae for evolution. &lt;color=#a0ff50&gt;Evolve more Nest Worms&lt;/color&gt; to increase your unit supply cap.</t>
+  </si>
+  <si>
     <t>Key一定要在数量……</t>
   </si>
   <si>
     <t>就是一定要在数量上占据优势吗？</t>
   </si>
   <si>
+    <t>So the key is to overwhelm the enemy with sheer numbers?</t>
+  </si>
+  <si>
     <t>Key进攻就是最好的防守……</t>
   </si>
   <si>
     <t>是的，进攻就是最好的防守。派出地面单位堵住敌人的通道，再派出飞虫越过障碍物空袭敌人。</t>
   </si>
   <si>
+    <t>Exactly. The best defense is a relentless offense. Deploy ground units to block enemy chokepoints, then send Flyers over obstacles to bomb enemy positions.</t>
+  </si>
+  <si>
     <t>Key也不是很复杂……</t>
   </si>
   <si>
     <t>OK，也不是很复杂。我有信心完成任务！</t>
   </si>
   <si>
+    <t>Alright, it’s not that complicated. I’m ready to complete the mission!</t>
+  </si>
+  <si>
     <t>Key防守战只要守住……</t>
   </si>
   <si>
     <t>防守战：只要守住，就是胜利！</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Defensive Mission</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Victory belongs to those who hold the line!</t>
+    </r>
+  </si>
+  <si>
     <t>Key多造虫巢……</t>
   </si>
   <si>
     <t>5秒后将出现第1波敌人。多造虫巢和房虫，多造近战虫枪虫和飞虫，一定要在数量上压倒敌人！</t>
   </si>
   <si>
+    <t>Wave 1 incoming in 5 seconds. Build more Hives and Nest Worms. Mass Melee Bugs, Gunners, and Flyers—crush the enemy with superior numbers!</t>
+  </si>
+  <si>
     <t>Key前期不用采集……</t>
   </si>
   <si>
     <t>&lt;color=#a0ff50&gt;前期不用采集资源&lt;/color&gt;。多造虫巢和房虫，多造近战虫枪虫和飞虫，一定要在数量上压制敌人！</t>
   </si>
   <si>
+    <t>&lt;color=#a0ff50&gt;No resource gathering required early-game&lt;/color&gt;. Build more Hives and Nest Worms. Mass Melee Bugs, Gunners, and Flyers—dominate the enemy with sheer quantity!</t>
+  </si>
+  <si>
     <t>Key第{}波敌人正向您走来</t>
   </si>
   <si>
     <t>第{}波敌人正向您走来</t>
   </si>
   <si>
+    <t>Wave {} is approaching your position.</t>
+  </si>
+  <si>
     <t>Key虫族将进攻基地……</t>
   </si>
   <si>
     <t>情报显示：将有大量敌方单位进攻我方基地，请做好准备。</t>
   </si>
   <si>
+    <t>Intel update: A massive enemy battalion is assaulting our base. Stand your ground!</t>
+  </si>
+  <si>
     <t>Key坦克超远超高伤害……</t>
   </si>
   <si>
     <t>&lt;color=#a0ff50&gt;坦克&lt;/color&gt;可以超远距离造成超高伤害，而且是范围伤害，但是坦克锁定炮弹落点后有超长前摇时长，前摇结束后，敌方目标可能已经远离炮弹落点。炮弹落点附近的我方单位也会受到伤害。</t>
   </si>
   <si>
+    <t>&lt;color=#a0ff50&gt;Tanks&lt;/color&gt; deal devastating area damage at extreme range, but they suffer from a long charge-up time after locking onto a target. By the time the shell fires, enemy units may have already moved out of the blast zone. Friendly units near the impact area will also take splash damage.</t>
+  </si>
+  <si>
     <t>Key有点鸡肋的感觉……</t>
   </si>
   <si>
     <t>有点鸡肋的感觉，不是红警中的高速坦克，与星际中的攻城坦克也有些不同。感觉更像帝国里的投石车。</t>
   </si>
   <si>
+    <t>Seems pretty underwhelming. Not like the fast tanks in Red Alert, or even the Siege Tanks in StarCraft. More like the Catapults from Age of Empires.</t>
+  </si>
+  <si>
     <t>Key有一种叫炮台的……</t>
   </si>
   <si>
     <t>…不知道你在说什么…有一种叫&lt;color=#a0ff50&gt;炮台&lt;/color&gt;的建筑单位，攻击距离很远，仅次于坦克；前摇时长很短，可以快速攻击；缺陷是伤害较低；不过多造点集中防守某一块区域还是很实用的。</t>
   </si>
   <si>
+    <t>…Not sure what you’re talking about… There’s a structure unit called the &lt;color=#a0ff50&gt;Battery Turret&lt;/color&gt;. It boasts exceptional range—second only to Tanks—with minimal charge-up time for rapid firing. Its downside is lower damage output, but massing them to defend key chokepoints proves highly effective.</t>
+  </si>
+  <si>
     <t>Key坦克炮台就能……</t>
   </si>
   <si>
     <t>看来&lt;color=#a0ff50&gt;只要有坦克和炮台就能守住&lt;/color&gt;对吗？</t>
   </si>
   <si>
+    <t>So &lt;color=#a0ff50&gt;as long as we have Tanks and Battery Turrets, we can hold the line&lt;/color&gt;, right?</t>
+  </si>
+  <si>
     <t>Key是的能守住……</t>
   </si>
   <si>
     <t>是的，这是其他指挥官总结的经验。大概&lt;color=#a0ff50&gt;10个炮台和5辆坦克沿墙边布置就能守住&lt;/color&gt;。当然还有其他多种可行的防守方法，要靠你自行摸索。</t>
   </si>
   <si>
+    <t>Affirmative. This is a proven strategy from veteran commanders. Position roughly &lt;color=#a0ff50&gt;10 Battery Turrets and 5 Tanks along the perimeter walls&lt;/color&gt; to secure the base. Of course, other viable defensive tactics exist—you’ll need to discover them on your own.</t>
+  </si>
+  <si>
     <t>Key5秒出现虫族怪……</t>
   </si>
   <si>
     <t>5秒后将出现第1波怪。您可以沿右边墙边造炮台、布置坦克、造地堡、让兵进驻地堡。</t>
   </si>
   <si>
+    <t>Wave 1 incoming in 5 seconds. Construct Battery Turrets along the right perimeter wall, deploy Tanks, build Bunkers, and garrison troops inside for fortified defense.</t>
+  </si>
+  <si>
     <t>Key沿右边迷宫出口……</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>&lt;color=#a0ff50&gt;</t>
     </r>
     <r>
@@ -3860,13 +3973,25 @@
     </r>
   </si>
   <si>
+    <t>&lt;color=#a0ff50&gt;No resource gathering required early-game&lt;/color&gt;. Line the right maze exit wall with a row of &lt;color=#a0ff50&gt;Battery Turrets&lt;/color&gt;, then place &lt;color=#a0ff50&gt;Tanks&lt;/color&gt; to reinforce your defenses.</t>
+  </si>
+  <si>
     <t>Key总算报仇了！</t>
   </si>
   <si>
     <t>总算报仇了！</t>
   </si>
   <si>
+    <t>Finally—revenge is ours!</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>Key</t>
     </r>
     <r>
@@ -3892,58 +4017,94 @@
     <t>以后坦克不能再单独行动了，一定要带上步兵。</t>
   </si>
   <si>
+    <t>From now on, Tanks will never operate alone. Infantry escorts are mandatory.</t>
+  </si>
+  <si>
+    <t>Key是指挥官！</t>
+  </si>
+  <si>
     <t>是，指挥官！</t>
   </si>
   <si>
+    <t>Yes, Commander!</t>
+  </si>
+  <si>
     <t>Key该听你的直接回去……</t>
   </si>
   <si>
     <t>早知如此就该听你的直接回去！</t>
   </si>
   <si>
+    <t>If only I’d listened to you and retreated earlier!</t>
+  </si>
+  <si>
     <t>Key现在说什么都……</t>
   </si>
   <si>
     <t>现在说什么都晚了（惨叫）。</t>
   </si>
   <si>
+    <t>It’s too late for regrets now! (Screams)</t>
+  </si>
+  <si>
     <t>Key下次先攻击虫巢……</t>
   </si>
   <si>
     <t>可以试试操作慢一点，先进攻&lt;color=#a0ff50&gt;右下角的虫巢&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>Try slowing your pace of operations. Prioritize attacking the &lt;color=#a0ff50&gt;Hive in the bottom-right corner&lt;/color&gt; first.</t>
+  </si>
+  <si>
     <t>Key只能下次再试试了。</t>
   </si>
   <si>
+    <t>Guess we’ll have to go for the Key next time.</t>
+  </si>
+  <si>
     <t>Key下次先攻击基地……</t>
   </si>
   <si>
     <t>可以试试操作慢一点，先进攻&lt;color=#a0ff50&gt;右下角的基地&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>Try slowing your pace of operations. Prioritize attacking the &lt;color=#a0ff50&gt;enemy base in the bottom-right corner&lt;/color&gt; first.</t>
+  </si>
+  <si>
     <t>Key坦克连失联……</t>
   </si>
   <si>
     <t>，我的一个坦克连在调查&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;时失联，请前往营救。</t>
   </si>
   <si>
+    <t>One of our Tank Companies went missing while investigating an enemy &lt;color=#a0ff50&gt;Hive&lt;/color&gt;. Deploy immediately for search and rescue.</t>
+  </si>
+  <si>
     <t>Key没有步兵保护吗……</t>
   </si>
   <si>
     <t>坦克没有步兵保护吗？</t>
   </si>
   <si>
+    <t>Why weren’t the Tanks accompanied by infantry?</t>
+  </si>
+  <si>
     <t>Key两个班的兵力……</t>
   </si>
   <si>
     <t>是的，步兵刚刚到位，两个班的兵力，现在全部交给你指挥。</t>
   </si>
   <si>
+    <t>Reinforcements just arrived—two infantry squads. They’re now under your full command.</t>
+  </si>
+  <si>
     <t>Key虫巢是什么？</t>
   </si>
   <si>
     <t>虫巢是什么？</t>
+  </si>
+  <si>
+    <t>What exactly is a Hive?</t>
   </si>
   <si>
     <t>Key虫巢苔蔓……</t>
@@ -3953,28 +4114,46 @@
     据1985年《普通话异读词审音表》：\n苔蔓(&lt;color=#a0ff50&gt;wàn&lt;/color&gt;)、蔓(màn)延</t>
   </si>
   <si>
+    <t>Recon drone footage confirms: &lt;color=#a0ff50&gt;Mossy Vines&lt;/color&gt; grow around Hives. Insectoid units on these vines gain increased movement and regeneration speeds. &lt;color=#a0ff50&gt;Avoid engaging insectoid forces while on Mossy Vines&lt;/color&gt;.</t>
+  </si>
+  <si>
     <t>Key坦克凭空消失……</t>
   </si>
   <si>
     <t>一个坦克连应该有10辆坦克吧？这么多钢铁疙瘩能凭空消失吗？</t>
   </si>
   <si>
+    <t>A Tank Company should have 10 Tanks, right? How could an entire unit of steel just vanish without a trace?</t>
+  </si>
+  <si>
     <t>Key不放弃任何人……</t>
   </si>
   <si>
     <t>现在人手紧缺，我不能做任何行动上的承诺。但我个人会竭尽全力，不放弃任何一个人。</t>
   </si>
   <si>
+    <t>We’re short on manpower—no promises can be made for additional support. But personally, I’ll do everything in my power to bring every soldier home.</t>
+  </si>
+  <si>
     <t>Key我会尽力而为的。</t>
   </si>
   <si>
     <t>我会尽力而为的。</t>
   </si>
   <si>
+    <t>I won’t let you down.</t>
+  </si>
+  <si>
     <t>Key多想克制……</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>要多用脑子，要多想。记住兵种克制关系：</t>
     </r>
     <r>
@@ -4033,232 +4212,352 @@
     </r>
   </si>
   <si>
+    <t>Fight smart, not hard. Remember the unit counter rules:
+&lt;color=#a0ff50&gt;Grunts counter Tanks
+Battery Turrets counter Grunts&lt;/color&gt;
+Tanks counter Battery Turrets</t>
+  </si>
+  <si>
     <t>Key早记住坦克步兵……</t>
   </si>
   <si>
     <t>这我早就记住了，否则我也不会疑惑为什么坦克没有步兵保护。</t>
   </si>
   <si>
+    <t>I already memorized them—that’s why I’m confused the Tanks were sent out without infantry support.</t>
+  </si>
+  <si>
     <t>Key相信你归来……</t>
   </si>
   <si>
     <t>我相信你的能力，你一定能平安归来!</t>
   </si>
   <si>
+    <t>I have faith in your abilities. You will return victorious!</t>
+  </si>
+  <si>
     <t>Key无工程车打虫巢……</t>
   </si>
   <si>
     <t>此局没有工程车。&lt;color=#a0ff50&gt;右下方的敌方虫巢防守薄弱&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>No Drones available in this mission. &lt;color=#a0ff50&gt;The enemy Hive in the bottom-right corner is lightly defended&lt;/color&gt;.</t>
+  </si>
+  <si>
     <t>Key谢谢你救了我们。</t>
   </si>
   <si>
     <t>谢谢你救了我们。</t>
   </si>
   <si>
+    <t>Thank you for rescuing us.</t>
+  </si>
+  <si>
     <t>Key你们怎么会在……</t>
   </si>
   <si>
     <t>你们怎么会在虫巢里？</t>
   </si>
   <si>
+    <t>What were you doing inside the Hive?</t>
+  </si>
+  <si>
     <t>Key仿佛做梦……</t>
   </si>
   <si>
     <t>我也不知道，仿佛做了一场梦，什么都不记得了。</t>
   </si>
   <si>
+    <t>I don’t know. It’s like I was in a daze—I can’t remember anything.</t>
+  </si>
+  <si>
     <t>Key我护送你……</t>
   </si>
   <si>
     <t>现在我的部队会护送你们回基地。到时候再仔细回忆一下。</t>
   </si>
   <si>
+    <t>My forces will escort you back to base. We can try to piece together your memories once you’re safe.</t>
+  </si>
+  <si>
     <t>Key两个虫巢……</t>
   </si>
   <si>
     <t>上面还有两个虫巢，我要炸掉它们再回去。</t>
   </si>
   <si>
+    <t>There are two more Hives up ahead. I’m destroying them before we retreat.</t>
+  </si>
+  <si>
     <t>Key虫巢有炮台把守……</t>
   </si>
   <si>
     <t>上面的虫巢有敌方的炮台把守，我们过不去。</t>
   </si>
   <si>
+    <t>Those Hives are guarded by enemy Battery Turrets. We can’t break through.</t>
+  </si>
+  <si>
     <t>Key我的坦克专门……</t>
   </si>
   <si>
     <t>我的坦克专门克制炮台。&lt;color=#a0ff50&gt;坦克的射程略远于炮台&lt;/color&gt;。一辆坦克就能全灭它们，何况我现在有十辆。</t>
   </si>
   <si>
+    <t>My Tanks are specifically designed to counter Battery Turrets. &lt;color=#a0ff50&gt;Tanks outrange Battery Turrets by a small margin&lt;/color&gt;. One Tank alone can wipe them out—now imagine what 10 can do.</t>
+  </si>
+  <si>
     <t>Key坦克接受我指挥……</t>
   </si>
   <si>
     <t>好的，但是坦克要接受我的指挥，我的步兵会保护坦克。</t>
   </si>
   <si>
+    <t>Very well, but the Tanks will follow my orders. My infantry will provide escort.</t>
+  </si>
+  <si>
     <t>Key是明白指挥官……</t>
   </si>
   <si>
     <t>是！明白！指挥官！</t>
   </si>
   <si>
+    <t>Yes! Understood, Commander!</t>
+  </si>
+  <si>
     <t>Key消灭虫巢……</t>
   </si>
   <si>
     <t>消灭上方两个敌方虫巢，控制好步兵保护您的坦克。&lt;color=#a0ff50&gt;让坦克在地方炮台的射程外攻击&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>Eliminate the two enemy Hives ahead. Use your infantry to protect the Tanks. &lt;color=#a0ff50&gt;Keep Tanks outside the Battery Turrets’ firing range&lt;/color&gt; at all times.</t>
+  </si>
+  <si>
     <t>Key好消息拟态……</t>
   </si>
   <si>
     <t>，有一个好消息，我们的幼虫经过千万次的模仿，基本掌握了拟态复制人类三色坦克的方法。</t>
   </si>
   <si>
+    <t>Good news: After thousands of iterations, our Larvae have mastered mimicking human Tri-Color Tank technology.</t>
+  </si>
+  <si>
     <t>Key还有坏消息……</t>
   </si>
   <si>
     <t>太好了……那么接下来肯定还有一个坏消息吧？</t>
   </si>
   <si>
+    <t>That’s great… But I’m guessing there’s a catch, isn’t there?</t>
+  </si>
+  <si>
     <t>Key绿色坦克遭……</t>
   </si>
   <si>
     <t>是的，蜕变出的第一批&lt;color = #a0ff50&gt;绿色坦克&lt;/color&gt;的虫巢已遭人类攻占。</t>
   </si>
   <si>
+    <t>Regrettably, the Hive producing our first batch of &lt;color=#a0ff50&gt;Green Tanks&lt;/color&gt; has been captured by human forces.</t>
+  </si>
+  <si>
     <t>Key绿色坦克打不过……</t>
   </si>
   <si>
     <t>绿色坦克看来仍然打不过人类的部队啊！</t>
   </si>
   <si>
+    <t>So the Green Tanks still can’t stand up to human troops.</t>
+  </si>
+  <si>
     <t>Key绿色坦克劣势……</t>
   </si>
   <si>
     <t>绿色坦克攻击距离远，但是面对贴近的人类步兵却处于劣势。此外绿色坦克发射出的光刺会被障碍物阻挡。现在人类的科学家正在研究我们的绿色坦克。</t>
   </si>
   <si>
+    <t>Green Tanks excel at long-range combat but are vulnerable to enemy infantry at close quarters. Additionally, their energy lances can be blocked by obstacles. Worse yet, human scientists are now reverse-engineering our Green Tank technology.</t>
+  </si>
+  <si>
     <t>Key我现在去救它们。</t>
   </si>
   <si>
     <t>我现在去救它们。</t>
   </si>
   <si>
+    <t>I’m mounting a rescue mission—now!</t>
+  </si>
+  <si>
     <t>Key无工虫打基地……</t>
   </si>
   <si>
     <t>此局没有工虫。&lt;color=#a0ff50&gt;右下方的敌方基地防守薄弱&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>No Drones available in this mission. &lt;color=#a0ff50&gt;The enemy base in the bottom-right corner is lightly defended&lt;/color&gt;.</t>
+  </si>
+  <si>
     <t>Key你们怎么会在基地里？</t>
   </si>
   <si>
     <t>你们怎么会在基地里？</t>
   </si>
   <si>
+    <t>What were you doing inside the enemy base?</t>
+  </si>
+  <si>
     <t>Key护送回虫巢……</t>
   </si>
   <si>
     <t>现在我的部队会护送你们回虫巢。到时候再仔细回忆一下。</t>
   </si>
   <si>
+    <t>My forces will escort you back to the Hive. We can try to recover your memories once you’re safe.</t>
+  </si>
+  <si>
     <t>Key炸掉基地……</t>
   </si>
   <si>
     <t>上面还有两个基地，我要炸掉它们再回去。</t>
   </si>
   <si>
+    <t>There are two more enemy bases up ahead. I’m destroying them before we retreat.</t>
+  </si>
+  <si>
     <t>Key基地有炮台……</t>
   </si>
   <si>
     <t>上面的基地有敌方的炮台把守，我们过不去。</t>
   </si>
   <si>
+    <t>Those bases are guarded by enemy Battery Turrets. We can’t break through.</t>
+  </si>
+  <si>
     <t>Key我克制炮台……</t>
   </si>
   <si>
     <t>我专门克制炮台。&lt;color=#a0ff50&gt;坦克的射程略远于炮台&lt;/color&gt;。一辆坦克就能全灭它们，何况我们现在有十辆。</t>
   </si>
   <si>
+    <t>I specialize in countering Battery Turrets. &lt;color=#a0ff50&gt;Tanks outrange Battery Turrets by a small margin&lt;/color&gt;. One Tank alone can wipe them out—now imagine what 10 can do.</t>
+  </si>
+  <si>
     <t>Key我保护你们……</t>
   </si>
   <si>
     <t>好的，但是你们要接受我的指挥，我的部队会保护你们。</t>
   </si>
   <si>
+    <t>Very well, but you will follow my orders. My forces will provide escort.</t>
+  </si>
+  <si>
     <t>Key消灭上方基地……</t>
   </si>
   <si>
     <t>消灭上方两个敌方基地，控制好其它单位保护您的坦克。坦克的射程略远于炮台，&lt;color=#a0ff50&gt;不要让坦克进入敌方炮台的射程&lt;/color&gt;。</t>
   </si>
   <si>
+    <t>Eliminate the two enemy bases ahead. Use your other units to protect the Tanks. Tanks outrange Battery Turrets by a small margin—&lt;color=#a0ff50&gt;never let Tanks enter the Battery Turrets’ firing range&lt;/color&gt;.</t>
+  </si>
+  <si>
     <t>Key无坦克遇炮台……</t>
   </si>
   <si>
     <t>没有坦克又遇到大片敌方炮台怎么办？</t>
   </si>
   <si>
+    <t>What if we face a large battery of enemy Turrets without any Tanks?</t>
+  </si>
+  <si>
     <t>Key绕道空降……</t>
   </si>
   <si>
     <t>，可以让&lt;color=#a0ff50&gt;房虫&lt;/color&gt;运送战斗单位越过障碍物绕到炮台后方，实施空降作战。</t>
   </si>
   <si>
+    <t>You can use &lt;color=#a0ff50&gt;Nest Worms&lt;/color&gt; to transport combat units over obstacles and deploy them behind enemy Turrets for airborne assaults.</t>
+  </si>
+  <si>
     <t>Key近战虫进房虫……</t>
   </si>
   <si>
     <t>请先点击选中&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再点击一次&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，可让近战虫进入房虫。</t>
   </si>
   <si>
+    <t>First, select the &lt;color=#a0ff50&gt;Melee Bugs&lt;/color&gt;. Then, click on a &lt;color=#a0ff50&gt;Nest Worm&lt;/color&gt; to load the Melee Bugs inside.</t>
+  </si>
+  <si>
     <t>Key放下近战虫……</t>
   </si>
   <si>
     <t>很好，请点击选中&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，让它跃过左侧的障碍物到达左上角的敌方建筑附近，然后点击下方&lt;color=#a0ff50&gt;离开房虫&lt;/color&gt;图标，放下近战虫攻击敌方建筑</t>
   </si>
   <si>
+    <t>Excellent work. Now select the &lt;color=#a0ff50&gt;Nest Worm&lt;/color&gt; and order it to jump over the obstacles on the left, moving near the enemy structures in the top-left corner. Next, click the &lt;color=#a0ff50&gt;Disembark&lt;/color&gt; icon below to unload the Melee Bugs and launch an attack on the enemy buildings.</t>
+  </si>
+  <si>
     <t>Key要远离敌方炮台。</t>
   </si>
   <si>
     <t>要远离敌方炮台。</t>
   </si>
   <si>
+    <t>Maintain distance from enemy Battery Turrets.</t>
+  </si>
+  <si>
     <t>Key已掌握空空降……</t>
   </si>
   <si>
     <t>您已经掌握了空降战术，但此战术风险较高，遭敌方拦截时会非常被动。可在今后的作战中择机运用。</t>
   </si>
   <si>
+    <t>You have mastered the airborne assault tactic. Note that this tactic carries high risks—you will be vulnerable if intercepted by the enemy. Use it strategically in future battles.</t>
+  </si>
+  <si>
     <t>Key没看错你天才……</t>
   </si>
   <si>
     <t>，我果然没有看错你，你是一个指挥天才！</t>
   </si>
   <si>
+    <t>I knew I made the right choice putting you in command—you’re a natural-born tactician!</t>
+  </si>
+  <si>
     <t>Key都快打完了……</t>
   </si>
   <si>
     <t>都快打完了你才来？</t>
   </si>
   <si>
+    <t>Took you long enough to show up—we’re almost done fighting!</t>
+  </si>
+  <si>
     <t>Key兵家常事……</t>
   </si>
   <si>
     <t>胜败乃兵家常事，我仍然看好你的潜力！</t>
   </si>
   <si>
+    <t>Victory and defeat are part of war. I still see great potential in you!</t>
+  </si>
+  <si>
     <t>Key八个方向都……</t>
   </si>
   <si>
     <t>，八个方向都会有敌人向你进攻！</t>
   </si>
   <si>
+    <t>Enemies are closing in on your position from eight directions!</t>
+  </si>
+  <si>
     <t>Key谁敢欺负咱俩……</t>
   </si>
   <si>
     <t>要战便战！谁敢欺负咱俩？</t>
+  </si>
+  <si>
+    <t>Bring it on! No one dares to mess with us!</t>
   </si>
   <si>
     <t>Key星河孤守歌……</t>
@@ -4272,6 +4571,44 @@
                ————文小言AI</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">The Drill Instructor sent 1000 Crystalline Minerals. If that’s not enough, you’ll have to gather more on-site. Hold the line—I’m mobilizing reinforcements right now! I leave you with this poem, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ode to the Lone Star Fortress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, to keep your spirits high:
+Battle drums roar across the starry river, insect swarms blot out the sky.
+The lone fortress stands clad in iron, gunsmoke tears through the clouds.
+Blood stains the backbone of mountains and rivers, bones forge an unyielding monument.
+When I return through wind and snow, the Marshal shall come home with the dawn!
+————By Wen Xiaoyan AI"</t>
+    </r>
+  </si>
+  <si>
     <t>Key像临阵逃脱……</t>
   </si>
   <si>
@@ -4279,12 +4616,18 @@
   好吧，我一定守住！</t>
   </si>
   <si>
+    <t>"!……What kind of nonsense is this? Sounds like an excuse to run away!</t>
+  </si>
+  <si>
     <t>Key守中央基地……</t>
   </si>
   <si>
     <t>守护中央&lt;color=#a0ff50&gt;基地&lt;/color&gt;，否则任务失败。</t>
   </si>
   <si>
+    <t>Fine. I’ll hold the line—no matter what!"</t>
+  </si>
+  <si>
     <t>Key援军来了。</t>
   </si>
   <si>
@@ -4297,10 +4640,363 @@
     <t>来得正是时候，这回定要出口恶气！</t>
   </si>
   <si>
+    <t>Reinforcements have arrived!</t>
+  </si>
+  <si>
     <t>Key胜利就在眼前……</t>
   </si>
   <si>
     <t>守护中央&lt;color=#a0ff50&gt;基地&lt;/color&gt;，胜利就在眼前。</t>
+  </si>
+  <si>
+    <t>About time! This time, we’re settling the score once and for all!</t>
+  </si>
+  <si>
+    <t>Key了解绿色坦克飞虫……</t>
+  </si>
+  <si>
+    <t>这次训练，你将了解&lt;color=#a0ff50&gt;绿色坦克&lt;/color&gt;、&lt;color=#a0ff50&gt;飞虫&lt;/color&gt;的用法。</t>
+  </si>
+  <si>
+    <t>Defend the central &lt;color=#a0ff50&gt;Base&lt;/color&gt;. Victory is within our grasp!</t>
+  </si>
+  <si>
+    <t>Key选近战虫进攻炮台……</t>
+  </si>
+  <si>
+    <t>Key绿色坦克克制炮台……</t>
+  </si>
+  <si>
+    <t>，炮台群对地面单位有压倒性的优势。可以用&lt;color=#a0ff50&gt;绿色坦克&lt;/color&gt;可以在炮台的射程外攻击。</t>
+  </si>
+  <si>
+    <t>Key绿色坦克可以……</t>
+  </si>
+  <si>
+    <t>绿色坦克可以在炮台的射程外攻击</t>
+  </si>
+  <si>
+    <t>Key绿色坦克拥有……</t>
+  </si>
+  <si>
+    <t>，绿色坦克拥有射程优势，可以在炮台的射程外攻击。但是绿色坦克发射的光刺会被障碍物阻挡，会遭到小兵克制。现在请看效果。</t>
+  </si>
+  <si>
+    <t>Key飞虫克制……</t>
+  </si>
+  <si>
+    <t>敌方近战兵无法防空，现在给你刷一个飞虫即可克制它们。</t>
+  </si>
+  <si>
+    <t>Key消灭所有敌方近战兵</t>
+  </si>
+  <si>
+    <t>消灭所有敌方近战兵</t>
+  </si>
+  <si>
+    <t>Key绿色坦克造价……</t>
+  </si>
+  <si>
+    <t>绿色坦克和飞虫的造价很高，要根据战场形势酌情使用。</t>
+  </si>
+  <si>
+    <t>Key飞虫强行走……</t>
+  </si>
+  <si>
+    <t>请单击选中飞虫，然后点击下方的&lt;color=#a0ff50&gt;强行走&lt;/color&gt;按钮，让飞虫停止攻击并移动到指定位置。</t>
+  </si>
+  <si>
+    <t>Key守住指挥天才……</t>
+  </si>
+  <si>
+    <t>您守住了！您真是指挥天才！</t>
+  </si>
+  <si>
+    <t>Key少侠，欢迎来到虫族武学殿堂……</t>
+  </si>
+  <si>
+    <t> 少侠，欢迎来到虫族武学殿堂。今日，老夫要传授你一门重要的保命心法。</t>
+  </si>
+  <si>
+    <t>Key敢问前辈，是何心法？</t>
+  </si>
+  <si>
+    <t>敢问前辈，是何心法？</t>
+  </si>
+  <si>
+    <t>Key看，前方有一座敌方的炮台……</t>
+  </si>
+  <si>
+    <t>看，前方有一座敌方的炮台。你的飞虫虽然身法灵活，但气血较少，若一味硬拼，必败无疑。</t>
+  </si>
+  <si>
+    <t>Key切记观察飞虫的气血……</t>
+  </si>
+  <si>
+    <r>
+      <t>切记观察飞虫的气血。飞虫气血本就较少，当气血低于一半时，立刻施展&lt;color=#a0ff50&gt;强行走&lt;/color&gt;身法，让飞虫回到&lt;color=#a0ff50&gt;苔蔓&lt;/color&gt;之上。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在苔蔓之上，飞虫可快速调息恢复气血。待气血回满之后，点击炮台附近的空白地面，让飞虫继续攻敌。如此反复，方能以弱胜强。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谨记此心法：&lt;color=#a0ff50&gt;气血低于一半 → 强行走回苔蔓 → 调息回满气血 → 点击炮台附近空白地面继续攻敌&lt;/color&gt;。此乃飞虫的生存之道！</t>
+    </r>
+  </si>
+  <si>
+    <t>Key点击选中飞虫……</t>
+  </si>
+  <si>
+    <t>点击选中飞虫，再点击炮台附近的空白地面，让飞虫攻击炮台。当气血低于一半时，使用&lt;color=#a0ff50&gt;强行走&lt;/color&gt;身法回到苔蔓调息回血</t>
+  </si>
+  <si>
+    <t>Key继续练习保命技巧……</t>
+  </si>
+  <si>
+    <t>您失败了！您需要继续练习保命技巧。</t>
+  </si>
+  <si>
+    <t>Key少侠，飞虫已败……</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 少侠，飞虫已败。切记，江湖险恶，保命为先。善用苔蔓调息回血，方能在战场上立于不败之地。</t>
+  </si>
+  <si>
+    <t>Key少侠已领悟飞虫的保命心法……</t>
+  </si>
+  <si>
+    <r>
+      <t>少侠已领悟飞虫的保命心法。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFD6D6DD"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>\n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>切记，江湖之中，保命比硬拼更为重要。善用苔蔓调息回血，你的飞虫便能在这险恶的战场上存活更久。</t>
+    </r>
+  </si>
+  <si>
+    <t>Key训练失败。</t>
+  </si>
+  <si>
+    <t>训练失败。</t>
+  </si>
+  <si>
+    <t>Key你醒了?</t>
+  </si>
+  <si>
+    <t>你醒了?</t>
+  </si>
+  <si>
+    <t>Key我们到家了吗？</t>
+  </si>
+  <si>
+    <t>我们到家了吗？</t>
+  </si>
+  <si>
+    <t>Key我们回到地球……</t>
+  </si>
+  <si>
+    <t>是的，我们回到地球了。但是地球已被人类占据。</t>
+  </si>
+  <si>
+    <t>Key我们仅仅离开……</t>
+  </si>
+  <si>
+    <t>我们仅仅离开了6000万年而已，想不到啊……一定要夺回我们的家园！</t>
+  </si>
+  <si>
+    <t>Key你睡得太久……</t>
+  </si>
+  <si>
+    <t>你睡得太久，需要一些恢复训练才能投入战斗！</t>
+  </si>
+  <si>
+    <t>Key请点击虫巢按钮……</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;按钮，再点击空白地面，工虫会在10秒内变异为虫巢</t>
+  </si>
+  <si>
+    <t>Key虫巢周围会形成……</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  很好。虫巢周围会形成&lt;color=#a0ff50&gt;苔蔓(wàn)&lt;/color&gt;，苔蔓上的虫类单位移动速度会变快，并且回血速度也会加快。应该&lt;color=#a0ff50&gt;尽量在苔蔓上与敌方单位交战&lt;/color&gt;。
+   等虫巢产出&lt;color=#a0ff50&gt;幼虫&lt;/color&gt;后，请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;工虫&lt;/color&gt;按钮，让幼虫蜕变为工虫</t>
+  </si>
+  <si>
+    <t>Key现在您有工虫了……</t>
+  </si>
+  <si>
+    <t>现在您有工虫了，点击选中您的&lt;color=#a0ff50&gt;工虫&lt;/color&gt;，再点击空旷地面，命令它走向目标点</t>
+  </si>
+  <si>
+    <t>Key工虫采集晶体矿……</t>
+  </si>
+  <si>
+    <t>很好！现在给您刷了一个晶体矿，请点击选中&lt;color=#a0ff50&gt;工虫&lt;/color&gt;，再点击一次&lt;color=#a0ff50&gt;晶体矿&lt;/color&gt;，让工虫在晶体矿和虫巢之间搬运晶体矿</t>
+  </si>
+  <si>
+    <t>Key工虫采集燃气矿……</t>
+  </si>
+  <si>
+    <t>很好！您的工虫正在采集晶体矿，请等他把晶体矿运回虫巢。现在，请先点&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;，再蜕变一个工虫去采集&lt;color=#a0ff50&gt;燃气矿&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Key工虫已运晶体矿……</t>
+  </si>
+  <si>
+    <t>您的工虫已把第一车晶体矿运到基地，请查看&lt;color=#a0ff50&gt;左上角&lt;/color&gt;晶体矿数量变化</t>
+  </si>
+  <si>
+    <t>Key蜕变房虫……</t>
+  </si>
+  <si>
+    <t>等您存够20晶体矿后，请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;房虫&lt;/color&gt;按钮，让幼虫蜕变为房虫</t>
+  </si>
+  <si>
+    <t>Key房虫提升……</t>
+  </si>
+  <si>
+    <t>很好，房虫可以提升您的&lt;color=#a0ff50&gt;活动单位数量上限&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>Key变异虫营……</t>
+  </si>
+  <si>
+    <t>等您存够30晶体矿后，请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;虫营&lt;/color&gt;按钮，再点击覆盖有苔蔓(wàn)的地面，就能变异出一个虫营。</t>
+  </si>
+  <si>
+    <t>Key解锁枪虫……</t>
+  </si>
+  <si>
+    <t>很好，虫营可以解锁枪虫和近战虫。虫营只要一个就够了，如果希望出兵更快，应该造更多的虫巢。</t>
+  </si>
+  <si>
+    <t>Key变异近战虫……</t>
+  </si>
+  <si>
+    <t>请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;按钮，让幼虫蜕变为近战虫</t>
+  </si>
+  <si>
+    <t>Key近战虫走……</t>
+  </si>
+  <si>
+    <t>点击选中您的&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再点击地面，可以指挥它走向目标处</t>
+  </si>
+  <si>
+    <t>Key近战虫攻击敌人……</t>
+  </si>
+  <si>
+    <t>现在已在左边给您刷了一个敌人，点击选中您的&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再&lt;color=#a0ff50&gt;点击敌人附近的地面&lt;/color&gt;，近战虫会走向目标并自动攻击。您可以点右下角&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;然后拖动地面看看敌人在哪里</t>
+  </si>
+  <si>
+    <t>Key近战虫阵亡……</t>
+  </si>
+  <si>
+    <t>您的单位阵亡了。可以多造点近战虫和枪虫去围攻敌人</t>
+  </si>
+  <si>
+    <t>Key变异更多虫巢……</t>
+  </si>
+  <si>
+    <t>恭喜您消灭了敌人！现在左边给您刷了更多的敌人。您可以变异更多的&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;加快幼虫的产出，蜕变更多的&lt;color=#a0ff50&gt;房虫&lt;/color&gt;提升活动单位上限，加油</t>
+  </si>
+  <si>
+    <t>Key夺回地球……</t>
+  </si>
+  <si>
+    <t>，很好，夺回地球指日可待！</t>
+  </si>
+  <si>
+    <t>Key期待与人类……</t>
+  </si>
+  <si>
+    <t>期待与人类的实战。</t>
+  </si>
+  <si>
+    <t>Key承蒙谬赞……</t>
+  </si>
+  <si>
+    <t>承蒙谬赞。学生谨遵教诲，自不敢有一丝懈怠，定当不负所望，继续精进。</t>
+  </si>
+  <si>
+    <t>Key兵家常事点击……</t>
+  </si>
+  <si>
+    <t>胜败乃兵家常事，请点击右上角&lt;color=#a0ff50&gt;离开场景&lt;/color&gt;离开，就可以重新来过。</t>
+  </si>
+  <si>
+    <t>Key功败垂成……</t>
+  </si>
+  <si>
+    <t>学生此次功败垂成，定会吸取教训，总结经验，再次努力，定不辜负教官的栽培与期望。</t>
+  </si>
+  <si>
+    <t>Key易万江不用谢……</t>
+  </si>
+  <si>
+    <t>    ……不用谢</t>
+  </si>
+  <si>
+    <t>Key飞虫气血不足……</t>
+  </si>
+  <si>
+    <t>飞虫气血已不足一半！速速施展&lt;color=#a0ff50&gt;强行走&lt;/color&gt;身法，让飞虫回到苔蔓上调息回血！</t>
+  </si>
+  <si>
+    <t>Key飞虫在苔蔓上……</t>
+  </si>
+  <si>
+    <t>飞虫正在苔蔓上调息恢复气血，请静待气血回满。</t>
+  </si>
+  <si>
+    <t>Key飞虫满血……</t>
+  </si>
+  <si>
+    <t>飞虫气血已回满，可以继续攻敌了！</t>
   </si>
 </sst>
 </file>
@@ -4313,7 +5009,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4557,6 +5253,14 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5039,7 +5743,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5100,7 +5804,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5546,20 +6256,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="38" customFormat="1" spans="1:18">
-      <c r="A2" s="38">
+    <row r="2" s="40" customFormat="1" spans="1:18">
+      <c r="A2" s="40">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="38">
-        <v>0</v>
-      </c>
-      <c r="G2" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="38">
+      <c r="C2" s="40">
+        <v>0</v>
+      </c>
+      <c r="G2" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="40">
         <v>1</v>
       </c>
       <c r="J2">
@@ -5568,33 +6278,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="38">
-        <v>1</v>
-      </c>
-      <c r="N2" s="38">
-        <v>0</v>
-      </c>
-      <c r="O2" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="38" customFormat="1" spans="1:18">
-      <c r="A3" s="38">
+      <c r="M2" s="40">
+        <v>1</v>
+      </c>
+      <c r="N2" s="40">
+        <v>0</v>
+      </c>
+      <c r="O2" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="40" customFormat="1" spans="1:18">
+      <c r="A3" s="40">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="38">
-        <v>0</v>
-      </c>
-      <c r="G3" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="38">
+      <c r="C3" s="40">
+        <v>0</v>
+      </c>
+      <c r="G3" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="40">
         <v>1</v>
       </c>
       <c r="J3">
@@ -5603,36 +6313,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="38">
-        <v>1</v>
-      </c>
-      <c r="N3" s="38">
-        <v>0</v>
-      </c>
-      <c r="O3" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="33" customFormat="1" spans="1:18">
-      <c r="A4" s="33">
+      <c r="M3" s="40">
+        <v>1</v>
+      </c>
+      <c r="N3" s="40">
+        <v>0</v>
+      </c>
+      <c r="O3" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="35" customFormat="1" spans="1:18">
+      <c r="A4" s="35">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="35">
         <v>2</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="38">
+      <c r="G4" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="40">
         <v>1</v>
       </c>
       <c r="J4">
@@ -5641,36 +6351,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="38">
-        <v>1</v>
-      </c>
-      <c r="N4" s="38">
-        <v>0</v>
-      </c>
-      <c r="O4" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A5" s="33">
+      <c r="M4" s="40">
+        <v>1</v>
+      </c>
+      <c r="N4" s="40">
+        <v>0</v>
+      </c>
+      <c r="O4" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A5" s="35">
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="33">
-        <v>0</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="35">
+        <v>0</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="38">
+      <c r="G5" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="40">
         <v>1</v>
       </c>
       <c r="J5">
@@ -5679,48 +6389,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="38">
-        <v>1</v>
-      </c>
-      <c r="N5" s="38">
-        <v>0</v>
-      </c>
-      <c r="O5" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="33">
-        <v>0</v>
-      </c>
-      <c r="R5" s="23" t="s">
+      <c r="M5" s="40">
+        <v>1</v>
+      </c>
+      <c r="N5" s="40">
+        <v>0</v>
+      </c>
+      <c r="O5" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="35">
+        <v>0</v>
+      </c>
+      <c r="R5" s="25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="39" customFormat="1" spans="1:18">
-      <c r="A6" s="39">
+    <row r="6" s="41" customFormat="1" spans="1:18">
+      <c r="A6" s="41">
         <v>101</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="39">
-        <v>0</v>
-      </c>
-      <c r="D6" s="39" t="s">
+      <c r="C6" s="41">
+        <v>0</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="38" t="b">
+      <c r="G6" s="40" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="38">
+      <c r="I6" s="40">
         <v>1</v>
       </c>
       <c r="J6">
@@ -5732,39 +6442,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="38">
-        <v>1</v>
-      </c>
-      <c r="N6" s="38">
-        <v>0</v>
-      </c>
-      <c r="O6" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="39" customFormat="1" spans="1:18">
-      <c r="A7" s="39">
+      <c r="M6" s="40">
+        <v>1</v>
+      </c>
+      <c r="N6" s="40">
+        <v>0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="41" customFormat="1" spans="1:18">
+      <c r="A7" s="41">
         <v>102</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="39">
-        <v>0</v>
-      </c>
-      <c r="D7" s="39" t="s">
+      <c r="C7" s="41">
+        <v>0</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="38">
+      <c r="G7" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="40">
         <v>1</v>
       </c>
       <c r="J7">
@@ -5773,16 +6483,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="38">
-        <v>1</v>
-      </c>
-      <c r="N7" s="38">
-        <v>0</v>
-      </c>
-      <c r="O7" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="39">
+      <c r="M7" s="40">
+        <v>1</v>
+      </c>
+      <c r="N7" s="40">
+        <v>0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="41">
         <v>0</v>
       </c>
     </row>
@@ -5805,13 +6515,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="38" t="b">
+      <c r="G8" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="38">
+      <c r="I8" s="40">
         <v>1</v>
       </c>
       <c r="J8">
@@ -5823,13 +6533,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="38">
-        <v>1</v>
-      </c>
-      <c r="N8" s="38">
-        <v>0</v>
-      </c>
-      <c r="O8" s="38">
+      <c r="M8" s="40">
+        <v>1</v>
+      </c>
+      <c r="N8" s="40">
+        <v>0</v>
+      </c>
+      <c r="O8" s="40">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -5838,63 +6548,63 @@
       <c r="Q8">
         <v>3</v>
       </c>
-      <c r="R8" s="23" t="s">
+      <c r="R8" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A9" s="32">
+    <row r="9" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A9" s="34">
         <v>202</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="32">
-        <v>1</v>
-      </c>
-      <c r="D9" s="32" t="s">
+      <c r="C9" s="34">
+        <v>1</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="32" t="s">
+      <c r="G9" s="42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="40">
-        <v>1</v>
-      </c>
-      <c r="J9" s="32">
-        <v>0</v>
-      </c>
-      <c r="K9" s="32">
+      <c r="I9" s="42">
+        <v>1</v>
+      </c>
+      <c r="J9" s="34">
+        <v>0</v>
+      </c>
+      <c r="K9" s="34">
         <v>2</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="40">
-        <v>1</v>
-      </c>
-      <c r="N9" s="40">
-        <v>0</v>
-      </c>
-      <c r="O9" s="40">
-        <v>0</v>
-      </c>
-      <c r="P9" s="32" t="s">
+      <c r="M9" s="42">
+        <v>1</v>
+      </c>
+      <c r="N9" s="42">
+        <v>0</v>
+      </c>
+      <c r="O9" s="42">
+        <v>0</v>
+      </c>
+      <c r="P9" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="34">
         <v>3</v>
       </c>
-      <c r="R9" s="23" t="s">
+      <c r="R9" s="25" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5917,13 +6627,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="38" t="b">
+      <c r="G10" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="38">
+      <c r="I10" s="40">
         <v>1</v>
       </c>
       <c r="J10">
@@ -5935,13 +6645,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="38">
-        <v>1</v>
-      </c>
-      <c r="N10" s="38">
-        <v>0</v>
-      </c>
-      <c r="O10" s="38">
+      <c r="M10" s="40">
+        <v>1</v>
+      </c>
+      <c r="N10" s="40">
+        <v>0</v>
+      </c>
+      <c r="O10" s="40">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -5950,7 +6660,7 @@
       <c r="Q10">
         <v>3</v>
       </c>
-      <c r="R10" s="23" t="s">
+      <c r="R10" s="25" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5970,13 +6680,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="38" t="b">
+      <c r="G11" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="40">
         <v>1</v>
       </c>
       <c r="J11">
@@ -5988,13 +6698,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="38">
-        <v>1</v>
-      </c>
-      <c r="N11" s="38">
-        <v>0</v>
-      </c>
-      <c r="O11" s="38">
+      <c r="M11" s="40">
+        <v>1</v>
+      </c>
+      <c r="N11" s="40">
+        <v>0</v>
+      </c>
+      <c r="O11" s="40">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -6003,7 +6713,7 @@
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="23" t="s">
+      <c r="R11" s="25" t="s">
         <v>57</v>
       </c>
     </row>
@@ -6026,13 +6736,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="38" t="b">
+      <c r="G12" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="40">
         <v>1</v>
       </c>
       <c r="J12">
@@ -6044,13 +6754,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="38">
-        <v>1</v>
-      </c>
-      <c r="N12" s="38">
-        <v>0</v>
-      </c>
-      <c r="O12" s="38">
+      <c r="M12" s="40">
+        <v>1</v>
+      </c>
+      <c r="N12" s="40">
+        <v>0</v>
+      </c>
+      <c r="O12" s="40">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -6059,7 +6769,7 @@
       <c r="Q12">
         <v>2</v>
       </c>
-      <c r="R12" s="23" t="s">
+      <c r="R12" s="25" t="s">
         <v>64</v>
       </c>
     </row>
@@ -6082,13 +6792,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="38" t="b">
+      <c r="G13" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13" s="40">
         <v>1</v>
       </c>
       <c r="J13">
@@ -6100,13 +6810,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="38">
-        <v>1</v>
-      </c>
-      <c r="N13" s="38">
-        <v>1</v>
-      </c>
-      <c r="O13" s="38">
+      <c r="M13" s="40">
+        <v>1</v>
+      </c>
+      <c r="N13" s="40">
+        <v>1</v>
+      </c>
+      <c r="O13" s="40">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -6115,7 +6825,7 @@
       <c r="Q13">
         <v>5</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="R13" s="25" t="s">
         <v>71</v>
       </c>
     </row>
@@ -6135,16 +6845,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="41" t="s">
+      <c r="F14" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="38" t="b">
+      <c r="G14" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="40">
         <v>1</v>
       </c>
       <c r="J14">
@@ -6156,13 +6866,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="38">
-        <v>1</v>
-      </c>
-      <c r="N14" s="38">
-        <v>0</v>
-      </c>
-      <c r="O14" s="38">
+      <c r="M14" s="40">
+        <v>1</v>
+      </c>
+      <c r="N14" s="40">
+        <v>0</v>
+      </c>
+      <c r="O14" s="40">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -6171,7 +6881,7 @@
       <c r="Q14">
         <v>2</v>
       </c>
-      <c r="R14" s="23" t="s">
+      <c r="R14" s="25" t="s">
         <v>77</v>
       </c>
     </row>
@@ -6191,16 +6901,16 @@
       <c r="E15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="38" t="b">
+      <c r="G15" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="40">
         <v>1</v>
       </c>
       <c r="J15">
@@ -6212,13 +6922,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="38">
-        <v>1</v>
-      </c>
-      <c r="N15" s="38">
-        <v>0</v>
-      </c>
-      <c r="O15" s="38">
+      <c r="M15" s="40">
+        <v>1</v>
+      </c>
+      <c r="N15" s="40">
+        <v>0</v>
+      </c>
+      <c r="O15" s="40">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -6227,7 +6937,7 @@
       <c r="Q15">
         <v>2</v>
       </c>
-      <c r="R15" s="23" t="s">
+      <c r="R15" s="25" t="s">
         <v>83</v>
       </c>
     </row>
@@ -6250,13 +6960,13 @@
       <c r="F16" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="38" t="b">
+      <c r="G16" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="40">
         <v>1</v>
       </c>
       <c r="J16">
@@ -6268,13 +6978,13 @@
       <c r="L16" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="38">
-        <v>1</v>
-      </c>
-      <c r="N16" s="38">
-        <v>0</v>
-      </c>
-      <c r="O16" s="38">
+      <c r="M16" s="40">
+        <v>1</v>
+      </c>
+      <c r="N16" s="40">
+        <v>0</v>
+      </c>
+      <c r="O16" s="40">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -6283,7 +6993,7 @@
       <c r="Q16">
         <v>1</v>
       </c>
-      <c r="R16" s="23" t="s">
+      <c r="R16" s="25" t="s">
         <v>91</v>
       </c>
     </row>
@@ -6306,13 +7016,13 @@
       <c r="F17" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="38" t="b">
+      <c r="G17" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="40">
         <v>1</v>
       </c>
       <c r="J17">
@@ -6324,13 +7034,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="38">
-        <v>1</v>
-      </c>
-      <c r="N17" s="38">
-        <v>0</v>
-      </c>
-      <c r="O17" s="38">
+      <c r="M17" s="40">
+        <v>1</v>
+      </c>
+      <c r="N17" s="40">
+        <v>0</v>
+      </c>
+      <c r="O17" s="40">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -6339,7 +7049,7 @@
       <c r="Q17">
         <v>2</v>
       </c>
-      <c r="R17" s="23" t="s">
+      <c r="R17" s="25" t="s">
         <v>96</v>
       </c>
     </row>
@@ -6356,10 +7066,10 @@
       <c r="D18" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="38">
+      <c r="G18" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="40">
         <v>1</v>
       </c>
       <c r="J18">
@@ -6368,13 +7078,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="38">
-        <v>1</v>
-      </c>
-      <c r="N18" s="38">
-        <v>0</v>
-      </c>
-      <c r="O18" s="38">
+      <c r="M18" s="40">
+        <v>1</v>
+      </c>
+      <c r="N18" s="40">
+        <v>0</v>
+      </c>
+      <c r="O18" s="40">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -6400,13 +7110,13 @@
       <c r="F19" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="38" t="b">
+      <c r="G19" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="40">
         <v>1</v>
       </c>
       <c r="J19">
@@ -6418,13 +7128,13 @@
       <c r="L19" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="38">
-        <v>1</v>
-      </c>
-      <c r="N19" s="38">
-        <v>0</v>
-      </c>
-      <c r="O19" s="38">
+      <c r="M19" s="40">
+        <v>1</v>
+      </c>
+      <c r="N19" s="40">
+        <v>0</v>
+      </c>
+      <c r="O19" s="40">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -6433,7 +7143,7 @@
       <c r="Q19">
         <v>4</v>
       </c>
-      <c r="R19" s="23" t="s">
+      <c r="R19" s="25" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6456,13 +7166,13 @@
       <c r="F20" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="38" t="b">
+      <c r="G20" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="40">
         <v>1</v>
       </c>
       <c r="J20">
@@ -6474,13 +7184,13 @@
       <c r="L20" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="38">
-        <v>1</v>
-      </c>
-      <c r="N20" s="38">
-        <v>0</v>
-      </c>
-      <c r="O20" s="38">
+      <c r="M20" s="40">
+        <v>1</v>
+      </c>
+      <c r="N20" s="40">
+        <v>0</v>
+      </c>
+      <c r="O20" s="40">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -6489,7 +7199,7 @@
       <c r="Q20">
         <v>4</v>
       </c>
-      <c r="R20" s="23" t="s">
+      <c r="R20" s="25" t="s">
         <v>112</v>
       </c>
     </row>
@@ -6512,13 +7222,13 @@
       <c r="F21" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="38" t="b">
+      <c r="G21" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="40">
         <v>1</v>
       </c>
       <c r="J21">
@@ -6530,13 +7240,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="38">
-        <v>1</v>
-      </c>
-      <c r="N21" s="38">
-        <v>0</v>
-      </c>
-      <c r="O21" s="38">
+      <c r="M21" s="40">
+        <v>1</v>
+      </c>
+      <c r="N21" s="40">
+        <v>0</v>
+      </c>
+      <c r="O21" s="40">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -6545,7 +7255,7 @@
       <c r="Q21">
         <v>3</v>
       </c>
-      <c r="R21" s="23" t="s">
+      <c r="R21" s="25" t="s">
         <v>118</v>
       </c>
     </row>
@@ -6568,13 +7278,13 @@
       <c r="F22" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="38" t="b">
+      <c r="G22" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="40">
         <v>1</v>
       </c>
       <c r="J22">
@@ -6586,13 +7296,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="38">
-        <v>1</v>
-      </c>
-      <c r="N22" s="38">
-        <v>0</v>
-      </c>
-      <c r="O22" s="38">
+      <c r="M22" s="40">
+        <v>1</v>
+      </c>
+      <c r="N22" s="40">
+        <v>0</v>
+      </c>
+      <c r="O22" s="40">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -6601,36 +7311,36 @@
       <c r="Q22">
         <v>3</v>
       </c>
-      <c r="R22" s="23" t="s">
+      <c r="R22" s="25" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A23" s="33">
+    <row r="23" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A23" s="35">
         <v>301</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="33">
-        <v>1</v>
-      </c>
-      <c r="D23" s="33" t="s">
+      <c r="C23" s="35">
+        <v>1</v>
+      </c>
+      <c r="D23" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="33" t="s">
+      <c r="E23" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="33" t="s">
+      <c r="F23" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="33" t="s">
+      <c r="G23" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23" s="40">
         <v>1</v>
       </c>
       <c r="J23">
@@ -6639,54 +7349,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="33" t="s">
+      <c r="L23" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="M23" s="38">
-        <v>1</v>
-      </c>
-      <c r="N23" s="38">
-        <v>0</v>
-      </c>
-      <c r="O23" s="38">
-        <v>0</v>
-      </c>
-      <c r="P23" s="33" t="s">
+      <c r="M23" s="40">
+        <v>1</v>
+      </c>
+      <c r="N23" s="40">
+        <v>0</v>
+      </c>
+      <c r="O23" s="40">
+        <v>0</v>
+      </c>
+      <c r="P23" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="Q23" s="33">
+      <c r="Q23" s="35">
         <v>3</v>
       </c>
-      <c r="R23" s="23" t="s">
+      <c r="R23" s="25" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A24" s="33">
+    <row r="24" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A24" s="35">
         <v>302</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="33">
-        <v>1</v>
-      </c>
-      <c r="D24" s="33" t="s">
+      <c r="C24" s="35">
+        <v>1</v>
+      </c>
+      <c r="D24" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="33" t="s">
+      <c r="E24" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="33" t="s">
+      <c r="F24" s="35" t="s">
         <v>131</v>
       </c>
-      <c r="G24" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="33" t="s">
+      <c r="G24" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="35" t="s">
         <v>132</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24" s="40">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -6695,51 +7405,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="33" t="s">
+      <c r="L24" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="M24" s="38">
-        <v>1</v>
-      </c>
-      <c r="N24" s="38">
-        <v>0</v>
-      </c>
-      <c r="O24" s="38">
-        <v>0</v>
-      </c>
-      <c r="P24" s="33" t="s">
+      <c r="M24" s="40">
+        <v>1</v>
+      </c>
+      <c r="N24" s="40">
+        <v>0</v>
+      </c>
+      <c r="O24" s="40">
+        <v>0</v>
+      </c>
+      <c r="P24" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="35">
         <v>3</v>
       </c>
-      <c r="R24" s="23" t="s">
+      <c r="R24" s="25" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A25" s="33">
+    <row r="25" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A25" s="35">
         <v>303</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="33">
-        <v>1</v>
-      </c>
-      <c r="D25" s="33" t="s">
+      <c r="C25" s="35">
+        <v>1</v>
+      </c>
+      <c r="D25" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="33" t="s">
+      <c r="E25" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="33" t="s">
+      <c r="G25" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="40">
         <v>1</v>
       </c>
       <c r="J25">
@@ -6748,51 +7458,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="38">
-        <v>1</v>
-      </c>
-      <c r="N25" s="38">
-        <v>0</v>
-      </c>
-      <c r="O25" s="38">
-        <v>0</v>
-      </c>
-      <c r="P25" s="33" t="s">
+      <c r="M25" s="40">
+        <v>1</v>
+      </c>
+      <c r="N25" s="40">
+        <v>0</v>
+      </c>
+      <c r="O25" s="40">
+        <v>0</v>
+      </c>
+      <c r="P25" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="35">
         <v>3</v>
       </c>
-      <c r="R25" s="23" t="s">
+      <c r="R25" s="25" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A26" s="33">
+    <row r="26" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A26" s="35">
         <v>304</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="33">
-        <v>1</v>
-      </c>
-      <c r="D26" s="33" t="s">
+      <c r="C26" s="35">
+        <v>1</v>
+      </c>
+      <c r="D26" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="33" t="s">
+      <c r="E26" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="33" t="s">
+      <c r="G26" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="38">
+      <c r="I26" s="40">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -6801,54 +7511,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="33" t="s">
+      <c r="L26" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="38">
-        <v>1</v>
-      </c>
-      <c r="N26" s="38">
-        <v>0</v>
-      </c>
-      <c r="O26" s="38">
-        <v>0</v>
-      </c>
-      <c r="P26" s="33" t="s">
+      <c r="M26" s="40">
+        <v>1</v>
+      </c>
+      <c r="N26" s="40">
+        <v>0</v>
+      </c>
+      <c r="O26" s="40">
+        <v>0</v>
+      </c>
+      <c r="P26" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="Q26" s="33">
+      <c r="Q26" s="35">
         <v>3</v>
       </c>
-      <c r="R26" s="23" t="s">
+      <c r="R26" s="25" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A27" s="33">
+    <row r="27" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A27" s="35">
         <v>305</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="35">
         <v>3</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="33" t="s">
+      <c r="E27" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="33" t="s">
+      <c r="G27" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="38">
+      <c r="I27" s="40">
         <v>1</v>
       </c>
       <c r="J27">
@@ -6860,51 +7570,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="38">
-        <v>1</v>
-      </c>
-      <c r="N27" s="38">
-        <v>0</v>
-      </c>
-      <c r="O27" s="38">
-        <v>0</v>
-      </c>
-      <c r="P27" s="33" t="s">
+      <c r="M27" s="40">
+        <v>1</v>
+      </c>
+      <c r="N27" s="40">
+        <v>0</v>
+      </c>
+      <c r="O27" s="40">
+        <v>0</v>
+      </c>
+      <c r="P27" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="35">
         <v>3</v>
       </c>
-      <c r="R27" s="23" t="s">
+      <c r="R27" s="25" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="28" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A28" s="33">
+    <row r="28" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A28" s="35">
         <v>306</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="35">
         <v>2</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="33" t="s">
+      <c r="E28" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="33" t="s">
+      <c r="F28" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="G28" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="33">
-        <v>0</v>
-      </c>
-      <c r="I28" s="38">
+      <c r="G28" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="35">
+        <v>0</v>
+      </c>
+      <c r="I28" s="40">
         <v>1</v>
       </c>
       <c r="J28">
@@ -6913,54 +7623,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="33">
-        <v>1</v>
-      </c>
-      <c r="M28" s="38">
-        <v>1</v>
-      </c>
-      <c r="N28" s="38">
-        <v>0</v>
-      </c>
-      <c r="O28" s="38">
-        <v>0</v>
-      </c>
-      <c r="P28" s="33" t="s">
+      <c r="L28" s="35">
+        <v>1</v>
+      </c>
+      <c r="M28" s="40">
+        <v>1</v>
+      </c>
+      <c r="N28" s="40">
+        <v>0</v>
+      </c>
+      <c r="O28" s="40">
+        <v>0</v>
+      </c>
+      <c r="P28" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="35">
         <v>3</v>
       </c>
-      <c r="R28" s="23" t="s">
+      <c r="R28" s="25" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A29" s="33">
+    <row r="29" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A29" s="35">
         <v>307</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="33">
-        <v>1</v>
-      </c>
-      <c r="D29" s="33" t="s">
+      <c r="C29" s="35">
+        <v>1</v>
+      </c>
+      <c r="D29" s="35" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="33" t="s">
+      <c r="E29" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="F29" s="35" t="s">
         <v>157</v>
       </c>
-      <c r="G29" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="33" t="s">
+      <c r="G29" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="40">
         <v>1</v>
       </c>
       <c r="J29">
@@ -6969,54 +7679,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="33" t="s">
+      <c r="L29" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="M29" s="38">
+      <c r="M29" s="40">
         <v>0.1</v>
       </c>
-      <c r="N29" s="38">
-        <v>0</v>
-      </c>
-      <c r="O29" s="38">
+      <c r="N29" s="40">
+        <v>0</v>
+      </c>
+      <c r="O29" s="40">
         <v>0.17</v>
       </c>
-      <c r="P29" s="33" t="s">
+      <c r="P29" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" s="33">
+      <c r="Q29" s="35">
         <v>3</v>
       </c>
-      <c r="R29" s="23" t="s">
+      <c r="R29" s="25" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A30" s="33">
+    <row r="30" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A30" s="35">
         <v>308</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="33">
-        <v>1</v>
-      </c>
-      <c r="D30" s="33" t="s">
+      <c r="C30" s="35">
+        <v>1</v>
+      </c>
+      <c r="D30" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="33" t="s">
+      <c r="E30" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="F30" s="35" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="38" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="33" t="s">
+      <c r="G30" s="40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="40">
         <v>1</v>
       </c>
       <c r="J30">
@@ -7025,54 +7735,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="33" t="s">
+      <c r="L30" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="M30" s="38">
-        <v>1</v>
-      </c>
-      <c r="N30" s="38">
-        <v>0</v>
-      </c>
-      <c r="O30" s="38">
-        <v>0</v>
-      </c>
-      <c r="P30" s="33" t="s">
+      <c r="M30" s="40">
+        <v>1</v>
+      </c>
+      <c r="N30" s="40">
+        <v>0</v>
+      </c>
+      <c r="O30" s="40">
+        <v>0</v>
+      </c>
+      <c r="P30" s="35" t="s">
         <v>134</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="35">
         <v>3</v>
       </c>
-      <c r="R30" s="23" t="s">
+      <c r="R30" s="25" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A31" s="33">
+    <row r="31" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A31" s="35">
         <v>309</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="35">
         <v>2</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="33" t="s">
+      <c r="G31" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31" s="40">
         <v>1</v>
       </c>
       <c r="J31">
@@ -7081,54 +7791,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="33" t="s">
+      <c r="L31" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="M31" s="38">
-        <v>1</v>
-      </c>
-      <c r="N31" s="38">
-        <v>0</v>
-      </c>
-      <c r="O31" s="38">
-        <v>0</v>
-      </c>
-      <c r="P31" s="33" t="s">
+      <c r="M31" s="40">
+        <v>1</v>
+      </c>
+      <c r="N31" s="40">
+        <v>0</v>
+      </c>
+      <c r="O31" s="40">
+        <v>0</v>
+      </c>
+      <c r="P31" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="35">
         <v>3</v>
       </c>
-      <c r="R31" s="23" t="s">
+      <c r="R31" s="25" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="32" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A32" s="33">
+    <row r="32" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A32" s="35">
         <v>310</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="33">
+      <c r="C32" s="35">
         <v>2</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="33" t="s">
+      <c r="E32" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="33" t="s">
+      <c r="F32" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="G32" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="33" t="s">
+      <c r="G32" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32" s="40">
         <v>1</v>
       </c>
       <c r="J32">
@@ -7137,54 +7847,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="33" t="s">
+      <c r="L32" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="M32" s="38">
-        <v>1</v>
-      </c>
-      <c r="N32" s="38">
-        <v>0</v>
-      </c>
-      <c r="O32" s="38">
-        <v>0</v>
-      </c>
-      <c r="P32" s="33" t="s">
+      <c r="M32" s="40">
+        <v>1</v>
+      </c>
+      <c r="N32" s="40">
+        <v>0</v>
+      </c>
+      <c r="O32" s="40">
+        <v>0</v>
+      </c>
+      <c r="P32" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="Q32" s="33">
+      <c r="Q32" s="35">
         <v>4</v>
       </c>
-      <c r="R32" s="23" t="s">
+      <c r="R32" s="25" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="33" s="33" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A33" s="33">
+    <row r="33" s="35" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A33" s="35">
         <v>311</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="35">
         <v>2</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="33" t="s">
+      <c r="E33" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="F33" s="33" t="s">
+      <c r="F33" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="G33" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="33">
-        <v>0</v>
-      </c>
-      <c r="I33" s="38">
+      <c r="G33" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="35">
+        <v>0</v>
+      </c>
+      <c r="I33" s="40">
         <v>1</v>
       </c>
       <c r="J33">
@@ -7193,45 +7903,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="33">
-        <v>1</v>
-      </c>
-      <c r="M33" s="38">
-        <v>1</v>
-      </c>
-      <c r="N33" s="38">
-        <v>0</v>
-      </c>
-      <c r="O33" s="38">
-        <v>0</v>
-      </c>
-      <c r="P33" s="33" t="s">
+      <c r="L33" s="35">
+        <v>1</v>
+      </c>
+      <c r="M33" s="40">
+        <v>1</v>
+      </c>
+      <c r="N33" s="40">
+        <v>0</v>
+      </c>
+      <c r="O33" s="40">
+        <v>0</v>
+      </c>
+      <c r="P33" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="Q33" s="35">
         <v>3</v>
       </c>
-      <c r="R33" s="23" t="s">
+      <c r="R33" s="25" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" s="33" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A34" s="33">
+    <row r="34" s="35" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A34" s="35">
         <v>312</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="35">
         <v>2</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="G34" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="38">
+      <c r="G34" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="40">
         <v>1</v>
       </c>
       <c r="J34">
@@ -7240,45 +7950,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="38">
-        <v>1</v>
-      </c>
-      <c r="N34" s="38">
-        <v>0</v>
-      </c>
-      <c r="O34" s="38">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="33">
-        <v>1</v>
-      </c>
-      <c r="R34" s="23" t="s">
+      <c r="M34" s="40">
+        <v>1</v>
+      </c>
+      <c r="N34" s="40">
+        <v>0</v>
+      </c>
+      <c r="O34" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="35">
+        <v>1</v>
+      </c>
+      <c r="R34" s="25" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="35" s="31" customFormat="1" spans="1:21">
-      <c r="A35" s="31">
+    <row r="35" s="33" customFormat="1" spans="1:21">
+      <c r="A35" s="33">
         <v>401</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="33">
         <v>2</v>
       </c>
-      <c r="D35" s="31" t="s">
+      <c r="D35" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="41" t="s">
+      <c r="F35" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="31" t="s">
+      <c r="G35" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="38">
+      <c r="I35" s="40">
         <v>1</v>
       </c>
       <c r="J35">
@@ -7290,45 +8000,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="38">
-        <v>1</v>
-      </c>
-      <c r="N35" s="38">
-        <v>0</v>
-      </c>
-      <c r="O35" s="38">
-        <v>0</v>
-      </c>
-      <c r="P35" s="31" t="s">
+      <c r="M35" s="40">
+        <v>1</v>
+      </c>
+      <c r="N35" s="40">
+        <v>0</v>
+      </c>
+      <c r="O35" s="40">
+        <v>0</v>
+      </c>
+      <c r="P35" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="31">
+      <c r="Q35" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="31" customFormat="1" spans="1:21">
-      <c r="A36" s="31">
+    <row r="36" s="33" customFormat="1" spans="1:21">
+      <c r="A36" s="33">
         <v>402</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="33">
         <v>2</v>
       </c>
-      <c r="D36" s="31" t="s">
+      <c r="D36" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="31" t="s">
+      <c r="G36" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="38">
+      <c r="I36" s="40">
         <v>1</v>
       </c>
       <c r="J36">
@@ -7340,48 +8050,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="38">
-        <v>1</v>
-      </c>
-      <c r="N36" s="38">
-        <v>0</v>
-      </c>
-      <c r="O36" s="38">
-        <v>0</v>
-      </c>
-      <c r="P36" s="31" t="s">
+      <c r="M36" s="40">
+        <v>1</v>
+      </c>
+      <c r="N36" s="40">
+        <v>0</v>
+      </c>
+      <c r="O36" s="40">
+        <v>0</v>
+      </c>
+      <c r="P36" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="31" customFormat="1" spans="1:21">
-      <c r="A37" s="31">
+    <row r="37" s="33" customFormat="1" spans="1:21">
+      <c r="A37" s="33">
         <v>403</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="33">
         <v>2</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="31" t="s">
+      <c r="G37" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="38">
+      <c r="I37" s="40">
         <v>1</v>
       </c>
       <c r="J37">
@@ -7390,80 +8100,80 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="31" t="s">
+      <c r="L37" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="38">
-        <v>1</v>
-      </c>
-      <c r="N37" s="38">
-        <v>0</v>
-      </c>
-      <c r="O37" s="38">
-        <v>0</v>
-      </c>
-      <c r="P37" s="31" t="s">
+      <c r="M37" s="40">
+        <v>1</v>
+      </c>
+      <c r="N37" s="40">
+        <v>0</v>
+      </c>
+      <c r="O37" s="40">
+        <v>0</v>
+      </c>
+      <c r="P37" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="40" customFormat="1" spans="1:21">
-      <c r="A38" s="40">
+    <row r="38" s="42" customFormat="1" spans="1:21">
+      <c r="A38" s="42">
         <v>404</v>
       </c>
       <c r="B38" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="40">
-        <v>1</v>
-      </c>
-      <c r="D38" s="32" t="s">
+      <c r="C38" s="42">
+        <v>1</v>
+      </c>
+      <c r="D38" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="32" t="s">
+      <c r="F38" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="40" t="s">
+      <c r="G38" s="42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="40">
-        <v>1</v>
-      </c>
-      <c r="J38" s="32">
-        <v>0</v>
-      </c>
-      <c r="K38" s="32">
+      <c r="I38" s="42">
+        <v>1</v>
+      </c>
+      <c r="J38" s="34">
+        <v>0</v>
+      </c>
+      <c r="K38" s="34">
         <v>2</v>
       </c>
-      <c r="L38" s="40" t="s">
+      <c r="L38" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="40">
-        <v>1</v>
-      </c>
-      <c r="N38" s="40">
-        <v>0</v>
-      </c>
-      <c r="O38" s="40">
-        <v>0</v>
-      </c>
-      <c r="P38" s="40" t="s">
+      <c r="M38" s="42">
+        <v>1</v>
+      </c>
+      <c r="N38" s="42">
+        <v>0</v>
+      </c>
+      <c r="O38" s="42">
+        <v>0</v>
+      </c>
+      <c r="P38" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="40">
+      <c r="Q38" s="42">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="31" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A39" s="31">
+    <row r="39" s="33" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A39" s="33">
         <v>405</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -7481,13 +8191,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="38" t="b">
+      <c r="G39" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="38">
+      <c r="I39" s="40">
         <v>1</v>
       </c>
       <c r="J39">
@@ -7499,13 +8209,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="38">
-        <v>1</v>
-      </c>
-      <c r="N39" s="38">
-        <v>0</v>
-      </c>
-      <c r="O39" s="38">
+      <c r="M39" s="40">
+        <v>1</v>
+      </c>
+      <c r="N39" s="40">
+        <v>0</v>
+      </c>
+      <c r="O39" s="40">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -7514,37 +8224,37 @@
       <c r="Q39">
         <v>3</v>
       </c>
-      <c r="R39" s="23"/>
+      <c r="R39" s="25"/>
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="31" customFormat="1" spans="1:21">
-      <c r="A40" s="31">
+    <row r="40" s="33" customFormat="1" spans="1:21">
+      <c r="A40" s="33">
         <v>406</v>
       </c>
       <c r="B40" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="31">
-        <v>1</v>
-      </c>
-      <c r="D40" s="31" t="s">
+      <c r="C40" s="33">
+        <v>1</v>
+      </c>
+      <c r="D40" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="33" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="31">
-        <v>0</v>
-      </c>
-      <c r="I40" s="38">
+      <c r="G40" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="33">
+        <v>0</v>
+      </c>
+      <c r="I40" s="40">
         <v>1</v>
       </c>
       <c r="J40">
@@ -7553,27 +8263,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="31">
+      <c r="L40" s="33">
         <v>3</v>
       </c>
-      <c r="M40" s="38">
-        <v>1</v>
-      </c>
-      <c r="N40" s="38">
-        <v>0</v>
-      </c>
-      <c r="O40" s="38">
-        <v>0</v>
-      </c>
-      <c r="P40" s="31" t="s">
+      <c r="M40" s="40">
+        <v>1</v>
+      </c>
+      <c r="N40" s="40">
+        <v>0</v>
+      </c>
+      <c r="O40" s="40">
+        <v>0</v>
+      </c>
+      <c r="P40" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q40" s="33">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="31">
+      <c r="A41" s="33">
         <v>407</v>
       </c>
       <c r="B41" s="14" t="s">
@@ -7591,13 +8301,13 @@
       <c r="F41" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="38" t="b">
+      <c r="G41" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>88</v>
       </c>
-      <c r="I41" s="38">
+      <c r="I41" s="40">
         <v>1</v>
       </c>
       <c r="J41">
@@ -7609,13 +8319,13 @@
       <c r="L41" t="s">
         <v>89</v>
       </c>
-      <c r="M41" s="38">
-        <v>1</v>
-      </c>
-      <c r="N41" s="38">
-        <v>0</v>
-      </c>
-      <c r="O41" s="38">
+      <c r="M41" s="40">
+        <v>1</v>
+      </c>
+      <c r="N41" s="40">
+        <v>0</v>
+      </c>
+      <c r="O41" s="40">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -7626,7 +8336,7 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="31">
+      <c r="A42" s="33">
         <v>408</v>
       </c>
       <c r="B42" s="14" t="s">
@@ -7644,13 +8354,13 @@
       <c r="F42" t="s">
         <v>110</v>
       </c>
-      <c r="G42" s="38" t="b">
+      <c r="G42" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="38">
+      <c r="I42" s="40">
         <v>1</v>
       </c>
       <c r="J42">
@@ -7662,13 +8372,13 @@
       <c r="L42" t="s">
         <v>104</v>
       </c>
-      <c r="M42" s="38">
-        <v>1</v>
-      </c>
-      <c r="N42" s="38">
-        <v>0</v>
-      </c>
-      <c r="O42" s="38">
+      <c r="M42" s="40">
+        <v>1</v>
+      </c>
+      <c r="N42" s="40">
+        <v>0</v>
+      </c>
+      <c r="O42" s="40">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -7679,7 +8389,7 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="31">
+      <c r="A43" s="33">
         <v>409</v>
       </c>
       <c r="B43" s="14" t="s">
@@ -7697,13 +8407,13 @@
       <c r="F43" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="38" t="b">
+      <c r="G43" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="38">
+      <c r="I43" s="40">
         <v>1</v>
       </c>
       <c r="J43">
@@ -7715,13 +8425,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="38">
-        <v>1</v>
-      </c>
-      <c r="N43" s="38">
-        <v>0</v>
-      </c>
-      <c r="O43" s="38">
+      <c r="M43" s="40">
+        <v>1</v>
+      </c>
+      <c r="N43" s="40">
+        <v>0</v>
+      </c>
+      <c r="O43" s="40">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -7732,7 +8442,7 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="31">
+      <c r="A44" s="33">
         <v>410</v>
       </c>
       <c r="B44" s="14" t="s">
@@ -7750,13 +8460,13 @@
       <c r="F44" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="38" t="b">
+      <c r="G44" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="38">
+      <c r="I44" s="40">
         <v>1</v>
       </c>
       <c r="J44">
@@ -7768,13 +8478,13 @@
       <c r="L44" t="s">
         <v>104</v>
       </c>
-      <c r="M44" s="38">
-        <v>1</v>
-      </c>
-      <c r="N44" s="38">
-        <v>0</v>
-      </c>
-      <c r="O44" s="38">
+      <c r="M44" s="40">
+        <v>1</v>
+      </c>
+      <c r="N44" s="40">
+        <v>0</v>
+      </c>
+      <c r="O44" s="40">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -7785,7 +8495,7 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="31">
+      <c r="A45" s="33">
         <v>411</v>
       </c>
       <c r="B45" s="14" t="s">
@@ -7803,13 +8513,13 @@
       <c r="F45" t="s">
         <v>121</v>
       </c>
-      <c r="G45" s="38" t="b">
+      <c r="G45" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="38">
+      <c r="I45" s="40">
         <v>1</v>
       </c>
       <c r="J45">
@@ -7821,13 +8531,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="38">
-        <v>1</v>
-      </c>
-      <c r="N45" s="38">
-        <v>0</v>
-      </c>
-      <c r="O45" s="38">
+      <c r="M45" s="40">
+        <v>1</v>
+      </c>
+      <c r="N45" s="40">
+        <v>0</v>
+      </c>
+      <c r="O45" s="40">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -7886,10 +8596,10 @@
       </c>
     </row>
     <row r="2" s="14" customFormat="1" spans="1:8">
-      <c r="A2" s="22">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>339</v>
       </c>
       <c r="C2" t="s">
@@ -7898,18 +8608,18 @@
       <c r="D2" t="s">
         <v>341</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="H2" s="22" t="b">
+      <c r="H2" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" s="14" customFormat="1" spans="1:8">
-      <c r="A3" s="22">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>343</v>
       </c>
       <c r="C3" t="s">
@@ -7918,15 +8628,15 @@
       <c r="D3" t="s">
         <v>341</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="28" t="s">
         <v>342</v>
       </c>
-      <c r="H3" s="22" t="b">
+      <c r="H3" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="22">
+      <c r="A4" s="24">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -7938,15 +8648,15 @@
       <c r="D4" t="s">
         <v>346</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="H4" s="22" t="b">
+      <c r="H4" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="22">
+      <c r="A5" s="24">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -7958,15 +8668,15 @@
       <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="28" t="s">
         <v>347</v>
       </c>
-      <c r="H5" s="22" t="b">
+      <c r="H5" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="22">
+      <c r="A6" s="24">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -7981,12 +8691,12 @@
       <c r="E6" t="s">
         <v>350</v>
       </c>
-      <c r="H6" s="22" t="b">
+      <c r="H6" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="22">
+      <c r="A7" s="24">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -8001,12 +8711,12 @@
       <c r="E7" t="s">
         <v>350</v>
       </c>
-      <c r="H7" s="22" t="b">
+      <c r="H7" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="22">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -8021,12 +8731,12 @@
       <c r="E8" t="s">
         <v>355</v>
       </c>
-      <c r="H8" s="22" t="b">
+      <c r="H8" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="22">
+      <c r="A9" s="24">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -8041,12 +8751,12 @@
       <c r="E9" t="s">
         <v>355</v>
       </c>
-      <c r="H9" s="22" t="b">
+      <c r="H9" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="22">
+      <c r="A10" s="24">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -8061,12 +8771,12 @@
       <c r="E10" t="s">
         <v>350</v>
       </c>
-      <c r="H10" s="22" t="b">
+      <c r="H10" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="22">
+      <c r="A11" s="24">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -8081,12 +8791,12 @@
       <c r="E11" t="s">
         <v>350</v>
       </c>
-      <c r="H11" s="22" t="b">
+      <c r="H11" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="22">
+      <c r="A12" s="24">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -8098,21 +8808,21 @@
       <c r="D12" t="s">
         <v>361</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="27" t="s">
         <v>362</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="H12" s="22" t="b">
+      <c r="H12" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="22">
+      <c r="A13" s="24">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -8124,17 +8834,17 @@
       <c r="D13" t="s">
         <v>346</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="28" t="s">
         <v>366</v>
       </c>
       <c r="F13" s="6"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="22" t="b">
+      <c r="G13" s="30"/>
+      <c r="H13" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="22">
+      <c r="A14" s="24">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -8146,17 +8856,17 @@
       <c r="D14" t="s">
         <v>346</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="28" t="s">
         <v>366</v>
       </c>
       <c r="F14" s="6"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="22" t="b">
+      <c r="G14" s="30"/>
+      <c r="H14" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="22">
+      <c r="A15" s="24">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -8168,17 +8878,17 @@
       <c r="D15" t="s">
         <v>346</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="E15" s="28" t="s">
         <v>366</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="22" t="b">
+      <c r="G15" s="30"/>
+      <c r="H15" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="22">
+      <c r="A16" s="24">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -8190,17 +8900,17 @@
       <c r="D16" t="s">
         <v>346</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="E16" s="28" t="s">
         <v>366</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="22" t="b">
+      <c r="G16" s="30"/>
+      <c r="H16" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="22">
+      <c r="A17" s="24">
         <v>101</v>
       </c>
       <c r="B17" t="s">
@@ -8212,15 +8922,15 @@
       <c r="D17" t="s">
         <v>372</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="H17" s="22" t="b">
+      <c r="H17" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="22">
+      <c r="A18" s="24">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -8232,21 +8942,21 @@
       <c r="D18" t="s">
         <v>376</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="28" t="s">
         <v>377</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="31" t="s">
         <v>379</v>
       </c>
-      <c r="H18" s="22" t="b">
+      <c r="H18" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="22">
+      <c r="A19" s="24">
         <v>103</v>
       </c>
       <c r="B19" t="s">
@@ -8258,21 +8968,21 @@
       <c r="D19" t="s">
         <v>361</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="27" t="s">
         <v>362</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="30" t="s">
         <v>364</v>
       </c>
-      <c r="H19" s="22" t="b">
+      <c r="H19" s="24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="22">
+      <c r="A20" s="24">
         <v>201</v>
       </c>
       <c r="B20" t="s">
@@ -8284,15 +8994,15 @@
       <c r="D20" t="s">
         <v>341</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="H20" s="22" t="b">
+      <c r="H20" s="24" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="22">
+      <c r="A21" s="24">
         <v>202</v>
       </c>
       <c r="B21" t="s">
@@ -8304,16 +9014,16 @@
       <c r="D21" t="s">
         <v>384</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="27" t="s">
         <v>385</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="H21" s="22" t="b">
+      <c r="H21" s="24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -8359,10 +9069,10 @@
       <c r="C1" s="14"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="22">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>388</v>
       </c>
     </row>
@@ -8409,50 +9119,50 @@
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
-      <c r="A2" s="22">
-        <v>1</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
         <v>393</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="27" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="22">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="25" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="28" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="22">
+      <c r="A4" s="24">
         <v>3</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="D4" s="25" t="s">
         <v>395</v>
       </c>
       <c r="E4" t="s">
@@ -8460,225 +9170,225 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:5">
-      <c r="A5" s="22">
+      <c r="A5" s="24">
         <v>4</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="25" t="s">
         <v>401</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="28" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:5">
-      <c r="A6" s="22">
+      <c r="A6" s="24">
         <v>5</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="25" t="s">
         <v>403</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="29" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:5">
-      <c r="A7" s="22">
+      <c r="A7" s="24">
         <v>6</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="25" t="s">
         <v>405</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="28" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:5">
-      <c r="A8" s="22">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="28" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:5">
-      <c r="A9" s="22">
+      <c r="A9" s="24">
         <v>8</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="28" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:5">
-      <c r="A10" s="22">
+      <c r="A10" s="24">
         <v>9</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="25" t="s">
         <v>411</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="25" t="s">
         <v>395</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="28" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
-      <c r="A11" s="22">
+      <c r="A11" s="24">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="25" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="27" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:5">
-      <c r="A12" s="22">
+      <c r="A12" s="24">
         <v>11</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="25" t="s">
         <v>417</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="28" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:5">
-      <c r="A13" s="22">
+      <c r="A13" s="24">
         <v>12</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="25" t="s">
         <v>419</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="26" t="s">
         <v>414</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="27" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:5">
-      <c r="A14" s="22">
+      <c r="A14" s="24">
         <v>13</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="25" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="28" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:5">
-      <c r="A15" s="22">
+      <c r="A15" s="24">
         <v>14</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="25" t="s">
         <v>424</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="25" t="s">
         <v>415</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="22"/>
+      <c r="A16" s="24"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="22"/>
+      <c r="A17" s="24"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="22"/>
+      <c r="A18" s="24"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="22"/>
+      <c r="A19" s="24"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="22"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="22"/>
+      <c r="A21" s="24"/>
       <c r="B21" s="3"/>
-      <c r="E21" s="26"/>
+      <c r="E21" s="28"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="22"/>
+      <c r="A22" s="24"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="22"/>
+      <c r="A23" s="24"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="22"/>
-      <c r="E24" s="26"/>
+      <c r="A24" s="24"/>
+      <c r="E24" s="28"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="22"/>
+      <c r="A25" s="24"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8704,7 +9414,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C276"/>
+  <dimension ref="A1:C324"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.875" customWidth="1"/>
@@ -8933,7 +9643,7 @@
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:3">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="6" t="s">
         <v>487</v>
       </c>
       <c r="B21" s="6" t="s">
@@ -8977,7 +9687,7 @@
       </c>
     </row>
     <row r="25" ht="14.25" spans="1:3">
-      <c r="A25" t="s">
+      <c r="A25" s="10" t="s">
         <v>499</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -8988,7 +9698,7 @@
       </c>
     </row>
     <row r="26" ht="27" spans="1:3">
-      <c r="A26" t="s">
+      <c r="A26" s="10" t="s">
         <v>502</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -9010,7 +9720,7 @@
       </c>
     </row>
     <row r="28" ht="14.25" spans="1:3">
-      <c r="A28" t="s">
+      <c r="A28" s="10" t="s">
         <v>508</v>
       </c>
       <c r="B28" s="5" t="s">
@@ -10803,685 +11513,1333 @@
       </c>
     </row>
     <row r="191" ht="14.25" spans="1:3">
-      <c r="A191" s="10" t="s">
+      <c r="A191" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B191" s="6" t="s">
         <v>916</v>
+      </c>
+      <c r="C191" t="s">
+        <v>917</v>
       </c>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" t="s">
-        <v>917</v>
-      </c>
-      <c r="B192" s="10" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="193" ht="14.25" spans="1:2">
+      <c r="B192" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="C192" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="193" ht="14.25" spans="1:3">
       <c r="A193" t="s">
-        <v>919</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
+        <v>921</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="C193" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3">
       <c r="A194" t="s">
-        <v>921</v>
-      </c>
-      <c r="B194" s="10" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="195" ht="14.25" spans="1:2">
-      <c r="A195" s="10" t="s">
-        <v>923</v>
-      </c>
-      <c r="B195" s="10" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="196" ht="14.25" spans="1:2">
-      <c r="A196" s="10" t="s">
+      <c r="B194" s="6" t="s">
         <v>925</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="C194" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="197" ht="14.25" spans="1:2">
-      <c r="A197" s="10" t="s">
+    <row r="195" ht="14.25" spans="1:3">
+      <c r="A195" s="6" t="s">
         <v>927</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B195" s="6" t="s">
         <v>928</v>
       </c>
-    </row>
-    <row r="198" ht="14.25" spans="1:2">
-      <c r="A198" s="10" t="s">
+      <c r="C195" t="s">
         <v>929</v>
       </c>
-      <c r="B198" s="10" t="s">
+    </row>
+    <row r="196" ht="14.25" spans="1:3">
+      <c r="A196" s="6" t="s">
         <v>930</v>
       </c>
-    </row>
-    <row r="199" ht="41.25" spans="1:2">
-      <c r="A199" s="20" t="s">
+      <c r="B196" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="B199" s="10" t="s">
+      <c r="C196" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="200" ht="14.25" spans="1:2">
-      <c r="A200" s="10" t="s">
+    <row r="197" ht="14.25" spans="1:3">
+      <c r="A197" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="B200" s="10" t="s">
+      <c r="B197" s="6" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="201" ht="14.25" spans="1:2">
-      <c r="A201" s="10" t="s">
+      <c r="C197" t="s">
         <v>935</v>
       </c>
-      <c r="B201" s="10" t="s">
+    </row>
+    <row r="198" ht="14.25" spans="1:3">
+      <c r="A198" s="6" t="s">
         <v>936</v>
       </c>
-    </row>
-    <row r="202" ht="14.25" spans="1:2">
-      <c r="A202" s="10" t="s">
+      <c r="B198" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="B202" s="10" t="s">
+      <c r="C198" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="199" ht="41.25" spans="1:3">
+      <c r="A199" s="6" t="s">
+        <v>939</v>
+      </c>
+      <c r="B199" s="6" t="s">
+        <v>940</v>
+      </c>
+      <c r="C199" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="200" ht="14.25" spans="1:3">
+      <c r="A200" s="6" t="s">
+        <v>942</v>
+      </c>
+      <c r="B200" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="C200" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="201" ht="14.25" spans="1:3">
+      <c r="A201" s="6" t="s">
+        <v>945</v>
+      </c>
+      <c r="B201" s="6" t="s">
+        <v>946</v>
+      </c>
+      <c r="C201" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="202" ht="14.25" spans="1:3">
+      <c r="A202" s="6" t="s">
+        <v>948</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>949</v>
+      </c>
+      <c r="C202" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="203" ht="14.25" spans="1:3">
       <c r="A203" t="s">
-        <v>939</v>
-      </c>
-      <c r="B203" s="10" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="204" ht="14.25" spans="1:2">
+        <v>951</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="C203" s="20" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="204" ht="14.25" spans="1:3">
       <c r="A204" t="s">
-        <v>941</v>
-      </c>
-      <c r="B204" s="10" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="205" ht="27" spans="1:2">
+        <v>954</v>
+      </c>
+      <c r="B204" s="6" t="s">
+        <v>955</v>
+      </c>
+      <c r="C204" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="205" ht="27" spans="1:3">
       <c r="A205" t="s">
-        <v>943</v>
-      </c>
-      <c r="B205" s="10" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="206" ht="14.25" spans="1:2">
+        <v>957</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="C205" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="206" ht="14.25" spans="1:3">
       <c r="A206" t="s">
-        <v>945</v>
-      </c>
-      <c r="B206" s="10" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
+        <v>960</v>
+      </c>
+      <c r="B206" s="6" t="s">
+        <v>961</v>
+      </c>
+      <c r="C206" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3">
       <c r="A207" t="s">
-        <v>947</v>
-      </c>
-      <c r="B207" s="10" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="208" ht="39.75" spans="1:2">
+        <v>963</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="C207" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="208" ht="39.75" spans="1:3">
       <c r="A208" t="s">
-        <v>949</v>
-      </c>
-      <c r="B208" s="10" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="209" ht="25.5" spans="1:2">
+        <v>966</v>
+      </c>
+      <c r="B208" s="6" t="s">
+        <v>967</v>
+      </c>
+      <c r="C208" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="209" ht="25.5" spans="1:3">
       <c r="A209" t="s">
-        <v>951</v>
-      </c>
-      <c r="B209" s="10" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="210" ht="39.75" spans="1:2">
+        <v>969</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>970</v>
+      </c>
+      <c r="C209" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="210" ht="39.75" spans="1:3">
       <c r="A210" t="s">
-        <v>953</v>
-      </c>
-      <c r="B210" s="10" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="211" ht="14.25" spans="1:2">
+        <v>972</v>
+      </c>
+      <c r="B210" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="C210" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="211" ht="14.25" spans="1:3">
       <c r="A211" t="s">
-        <v>955</v>
-      </c>
-      <c r="B211" s="10" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="212" ht="28.5" spans="1:2">
+        <v>975</v>
+      </c>
+      <c r="B211" s="6" t="s">
+        <v>976</v>
+      </c>
+      <c r="C211" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="212" ht="28.5" spans="1:3">
       <c r="A212" t="s">
-        <v>957</v>
-      </c>
-      <c r="B212" s="10" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="213" ht="14.25" spans="1:2">
+        <v>978</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>979</v>
+      </c>
+      <c r="C212" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="213" ht="14.25" spans="1:3">
       <c r="A213" t="s">
-        <v>959</v>
-      </c>
-      <c r="B213" s="10" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="214" ht="28.5" spans="1:2">
+        <v>981</v>
+      </c>
+      <c r="B213" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="C213" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="214" ht="28.5" spans="1:3">
       <c r="A214" t="s">
-        <v>961</v>
-      </c>
-      <c r="B214" s="20" t="s">
+        <v>984</v>
+      </c>
+      <c r="B214" s="6" t="s">
+        <v>985</v>
+      </c>
+      <c r="C214" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="215" ht="14.25" spans="1:3">
+      <c r="A215" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>988</v>
+      </c>
+      <c r="C215" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="216" ht="14.25" spans="1:3">
+      <c r="A216" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="B216" s="6" t="s">
+        <v>991</v>
+      </c>
+      <c r="C216" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="217" ht="14.25" spans="1:3">
+      <c r="A217" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="C217" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="218" ht="14.25" spans="1:3">
+      <c r="A218" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="B218" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="C218" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="219" ht="14.25" spans="1:3">
+      <c r="A219" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="220" ht="14.25" spans="1:3">
+      <c r="A220" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="221" ht="14.25" spans="1:3">
+      <c r="A221" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="222" ht="14.25" spans="1:3">
+      <c r="A222" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="223" ht="14.25" spans="1:3">
+      <c r="A223" s="6" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3">
+      <c r="A224" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3">
+      <c r="A225" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3">
+      <c r="A226" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="227" ht="67.5" spans="1:3">
+      <c r="A227" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B227" s="18" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="228" ht="14.25" spans="1:3">
+      <c r="A228" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3">
+      <c r="A229" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3">
+      <c r="A230" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="231" ht="54" spans="1:3">
+      <c r="A231" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C231" s="18" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3">
+      <c r="A232" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C232" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="233" ht="14.25" spans="1:3">
+      <c r="A233" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="234" ht="14.25" spans="1:3">
+      <c r="A234" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3">
+      <c r="A235" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C235" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3">
+      <c r="A236" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C236" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3">
+      <c r="A237" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3">
+      <c r="A238" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3">
+      <c r="A239" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C239" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3">
+      <c r="A240" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C240" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="241" ht="27" spans="1:3">
+      <c r="A241" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C241" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3">
+      <c r="A242" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C242" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3">
+      <c r="A243" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C243" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="244" ht="28.5" spans="1:3">
+      <c r="A244" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C244" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C245" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="246" ht="14.25" spans="1:3">
+      <c r="A246" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C246" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="247" ht="14.25" spans="1:3">
+      <c r="A247" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C247" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C248" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="249" ht="25.5" spans="1:3">
+      <c r="A249" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C249" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C250" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="251" ht="14.25" spans="1:3">
+      <c r="A251" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C251" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C252" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3">
+      <c r="A253" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C253" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3">
+      <c r="A254" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C254" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3">
+      <c r="A255" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C255" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="256" ht="27" spans="1:3">
+      <c r="A256" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C256" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3">
+      <c r="A257" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C257" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="258" ht="28.5" spans="1:3">
+      <c r="A258" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C258" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3">
+      <c r="A259" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C259" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="260" ht="14.25" spans="1:3">
+      <c r="A260" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C260" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="261" ht="27" spans="1:3">
+      <c r="A261" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C261" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="262" ht="28.5" spans="1:3">
+      <c r="A262" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C262" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3">
+      <c r="A263" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C263" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="264" ht="25.5" spans="1:3">
+      <c r="A264" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C264" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3">
+      <c r="A265" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C265" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3">
+      <c r="A266" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C266" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3">
+      <c r="A267" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C267" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3">
+      <c r="A268" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C268" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3">
+      <c r="A269" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C269" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="270" ht="94.5" spans="1:3">
+      <c r="A270" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B270" s="18" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C270" s="21" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="271" ht="27" spans="1:3">
+      <c r="A271" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B271" s="18" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C271" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="272" ht="14.25" spans="1:3">
+      <c r="A272" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C272" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C273" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="215" ht="14.25" spans="1:2">
-      <c r="A215" s="10" t="s">
-        <v>963</v>
-      </c>
-      <c r="B215" s="10" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="216" ht="14.25" spans="1:2">
-      <c r="A216" s="20" t="s">
-        <v>965</v>
-      </c>
-      <c r="B216" s="10" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="B217" s="10" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="218" ht="14.25" spans="1:2">
-      <c r="A218" s="10" t="s">
-        <v>968</v>
-      </c>
-      <c r="B218" s="10" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="219" ht="14.25" spans="1:2">
-      <c r="A219" s="10" t="s">
-        <v>970</v>
-      </c>
-      <c r="B219" s="10" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="220" ht="14.25" spans="1:2">
-      <c r="A220" t="s">
-        <v>972</v>
-      </c>
-      <c r="B220" s="10" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="221" ht="14.25" spans="1:2">
-      <c r="A221" s="10" t="s">
-        <v>974</v>
-      </c>
-      <c r="B221" s="10" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="222" ht="14.25" spans="1:2">
-      <c r="A222" s="10" t="s">
-        <v>975</v>
-      </c>
-      <c r="B222" s="10" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="223" ht="14.25" spans="1:2">
-      <c r="A223" s="10" t="s">
-        <v>977</v>
-      </c>
-      <c r="B223" s="10" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2">
-      <c r="A224" t="s">
-        <v>979</v>
-      </c>
-      <c r="B224" s="10" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2">
-      <c r="A225" t="s">
-        <v>981</v>
-      </c>
-      <c r="B225" s="10" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2">
-      <c r="A226" t="s">
-        <v>983</v>
-      </c>
-      <c r="B226" s="10" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="227" ht="67.5" spans="1:2">
-      <c r="A227" t="s">
-        <v>985</v>
-      </c>
-      <c r="B227" s="21" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="228" ht="14.25" spans="1:2">
-      <c r="A228" s="10" t="s">
-        <v>987</v>
-      </c>
-      <c r="B228" s="10" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="229" spans="1:2">
-      <c r="A229" t="s">
-        <v>989</v>
-      </c>
-      <c r="B229" s="10" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="230" spans="1:2">
-      <c r="A230" t="s">
-        <v>991</v>
-      </c>
-      <c r="B230" s="10" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="231" ht="28.5" spans="1:2">
-      <c r="A231" t="s">
-        <v>993</v>
-      </c>
-      <c r="B231" s="10" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="232" spans="1:2">
-      <c r="A232" t="s">
-        <v>995</v>
-      </c>
-      <c r="B232" s="10" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="233" ht="14.25" spans="1:2">
-      <c r="A233" s="10" t="s">
-        <v>997</v>
-      </c>
-      <c r="B233" s="10" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="234" ht="14.25" spans="1:2">
-      <c r="A234" t="s">
-        <v>999</v>
-      </c>
-      <c r="B234" s="10" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="235" spans="1:2">
-      <c r="A235" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B235" s="10" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="236" spans="1:2">
-      <c r="A236" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B236" s="10" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="237" spans="1:2">
-      <c r="A237" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B237" s="10" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="238" spans="1:2">
-      <c r="A238" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B238" s="10" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="239" spans="1:2">
-      <c r="A239" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B239" s="10" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="240" spans="1:2">
-      <c r="A240" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B240" s="10" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="241" ht="27" spans="1:2">
-      <c r="A241" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B241" s="10" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2">
-      <c r="A242" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B242" s="10" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2">
-      <c r="A243" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B243" s="10" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="244" ht="28.5" spans="1:2">
-      <c r="A244" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B244" s="10" t="s">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2">
-      <c r="A245" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B245" s="10" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="246" ht="14.25" spans="1:2">
-      <c r="A246" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B246" s="10" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="247" ht="14.25" spans="1:2">
-      <c r="A247" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B247" s="10" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2">
-      <c r="A248" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B248" s="10" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="249" ht="25.5" spans="1:2">
-      <c r="A249" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B249" s="10" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2">
-      <c r="A250" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B250" s="10" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="251" ht="14.25" spans="1:2">
-      <c r="A251" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B251" s="10" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2">
-      <c r="A252" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B252" s="10" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="253" spans="1:2">
-      <c r="A253" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B253" s="10" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2">
-      <c r="A254" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B254" s="10" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2">
-      <c r="A255" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B255" s="10" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="256" ht="27" spans="1:2">
-      <c r="A256" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B256" s="10" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2">
-      <c r="A257" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B257" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="258" ht="28.5" spans="1:2">
-      <c r="A258" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B258" s="10" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2">
-      <c r="A259" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B259" s="10" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="260" ht="14.25" spans="1:2">
-      <c r="A260" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B260" s="10" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="261" ht="27" spans="1:2">
-      <c r="A261" t="s">
-        <v>1053</v>
-      </c>
-      <c r="B261" s="10" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="262" ht="28.5" spans="1:2">
-      <c r="A262" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B262" s="10" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2">
-      <c r="A263" t="s">
-        <v>1057</v>
-      </c>
-      <c r="B263" s="10" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="264" ht="25.5" spans="1:2">
-      <c r="A264" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B264" s="10" t="s">
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2">
-      <c r="A265" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B265" s="10" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2">
-      <c r="A266" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B266" s="10" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2">
-      <c r="A267" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B267" s="10" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2">
-      <c r="A268" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B268" s="10" t="s">
-        <v>1068</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2">
-      <c r="A269" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B269" s="10" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="270" ht="94.5" spans="1:2">
-      <c r="A270" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B270" s="21" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="271" ht="27" spans="1:2">
-      <c r="A271" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B271" s="21" t="s">
-        <v>1074</v>
-      </c>
-    </row>
-    <row r="272" ht="14.25" spans="1:2">
-      <c r="A272" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B272" s="10" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="273" ht="14.25" spans="1:2">
-      <c r="B273" s="10" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B274" s="10" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="275" spans="1:2">
+        <v>1162</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C274" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="275" ht="14.25" spans="1:3">
       <c r="A275" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B275" s="10" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="276" ht="14.25" spans="1:2">
+        <v>1165</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C275" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="276" ht="27" spans="1:3">
       <c r="A276" t="s">
-        <v>1081</v>
+        <v>1168</v>
       </c>
       <c r="B276" s="10" t="s">
-        <v>1082</v>
+        <v>1169</v>
+      </c>
+      <c r="C276" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="277" ht="41.25" spans="1:3">
+      <c r="A277" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B277" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="278" ht="27" spans="1:3">
+      <c r="A278" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B278" s="10" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3">
+      <c r="A279" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B279" s="10" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="280" ht="25.5" spans="1:3">
+      <c r="A280" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B280" s="22" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3">
+      <c r="A281" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3">
+      <c r="A282" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B282" s="10" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3">
+      <c r="A283" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B283" s="10" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="284" ht="27" spans="1:3">
+      <c r="A284" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B284" s="10" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3">
+      <c r="A285" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B285" s="10" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="286" ht="14.25" spans="1:3">
+      <c r="A286" s="10" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B286" s="10" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="287" ht="14.25" spans="1:3">
+      <c r="A287" s="10" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B287" s="10" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3">
+      <c r="A288" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B288" s="10" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="289" ht="14.25" spans="1:2">
+      <c r="A289" s="10" t="s">
+        <v>887</v>
+      </c>
+      <c r="B289" s="10" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="290" ht="69.75" spans="1:2">
+      <c r="A290" s="10" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B290" s="10" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="291" ht="27" spans="1:2">
+      <c r="A291" s="10" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B291" s="10" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B292" s="10" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="293" ht="14.25" spans="1:2">
+      <c r="A293" s="10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B293" s="22" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="294" ht="27" spans="1:2">
+      <c r="A294" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B294" s="22" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="22" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B295" s="10" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="296" ht="14.25" spans="1:2">
+      <c r="A296" s="10" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B296" s="10" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="297" ht="14.25" spans="1:2">
+      <c r="A297" s="10" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B297" s="10" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="298" ht="14.25" spans="1:2">
+      <c r="A298" s="10" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B298" s="10" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="299" ht="14.25" spans="1:2">
+      <c r="A299" s="10" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B299" s="10" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="300" ht="14.25" spans="1:2">
+      <c r="A300" s="10" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B300" s="10" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="301" ht="28.5" spans="1:2">
+      <c r="A301" s="10" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B301" s="10" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="302" ht="67.5" spans="1:2">
+      <c r="A302" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B302" s="23" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="303" ht="27" spans="1:2">
+      <c r="A303" s="10" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B303" s="10" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="304" ht="28.5" spans="1:2">
+      <c r="A304" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B304" s="10" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="305" ht="28.5" spans="1:2">
+      <c r="A305" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B305" s="10" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="306" ht="14.25" spans="1:2">
+      <c r="A306" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B306" s="10" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="307" ht="28.5" spans="1:2">
+      <c r="A307" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B307" s="10" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="308" ht="14.25" spans="1:2">
+      <c r="A308" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B308" s="10" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="309" ht="28.5" spans="1:2">
+      <c r="A309" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B309" s="10" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B310" s="10" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="311" ht="27" spans="1:2">
+      <c r="A311" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B311" s="10" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="312" ht="14.25" spans="1:2">
+      <c r="A312" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B312" s="10" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="313" ht="42.75" spans="1:2">
+      <c r="A313" s="10" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B313" s="10" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="314" ht="14.25" spans="1:2">
+      <c r="A314" s="10" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B314" s="10" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="315" ht="28.5" spans="1:2">
+      <c r="A315" s="10" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B315" s="10" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B316" s="10" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B317" s="10" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B318" s="10" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="319" ht="14.25" spans="1:2">
+      <c r="A319" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B319" s="10" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B320" s="10" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="321" ht="14.25" spans="1:2">
+      <c r="A321" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B321" s="10" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="322" ht="27" spans="1:2">
+      <c r="A322" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B322" s="10" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B323" s="10" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B324" s="10" t="s">
+        <v>1263</v>
       </c>
     </row>
   </sheetData>
@@ -11525,25 +12883,25 @@
       </c>
     </row>
     <row r="2" s="14" customFormat="1" spans="1:7">
-      <c r="A2" s="33">
+      <c r="A2" s="35">
         <v>4</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="35">
         <v>20</v>
       </c>
-      <c r="D2" s="33">
-        <v>1</v>
-      </c>
-      <c r="E2" s="22">
-        <v>1</v>
-      </c>
-      <c r="F2" s="22">
-        <v>0</v>
-      </c>
-      <c r="G2" s="22">
+      <c r="D2" s="35">
+        <v>1</v>
+      </c>
+      <c r="E2" s="24">
+        <v>1</v>
+      </c>
+      <c r="F2" s="24">
+        <v>0</v>
+      </c>
+      <c r="G2" s="24">
         <v>200</v>
       </c>
     </row>
@@ -11566,7 +12924,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="24">
         <v>100</v>
       </c>
     </row>
@@ -11589,7 +12947,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="24">
         <v>100</v>
       </c>
     </row>
@@ -11612,7 +12970,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="24">
         <v>110</v>
       </c>
     </row>
@@ -11635,7 +12993,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="24">
         <v>200</v>
       </c>
     </row>
@@ -11658,7 +13016,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="24">
         <v>90</v>
       </c>
     </row>
@@ -11681,7 +13039,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="24">
         <v>200</v>
       </c>
     </row>
@@ -11704,7 +13062,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="24">
         <v>100</v>
       </c>
     </row>
@@ -11727,7 +13085,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="24">
         <v>90</v>
       </c>
     </row>
@@ -11750,7 +13108,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="24">
         <v>0</v>
       </c>
     </row>
@@ -11773,7 +13131,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="24">
         <v>180</v>
       </c>
     </row>
@@ -11796,7 +13154,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="24">
         <v>0</v>
       </c>
     </row>
@@ -11819,7 +13177,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="24">
         <v>100</v>
       </c>
     </row>
@@ -11842,7 +13200,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="24">
         <v>180</v>
       </c>
     </row>
@@ -11865,7 +13223,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="24">
         <v>110</v>
       </c>
     </row>
@@ -11888,288 +13246,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="24">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="35" customFormat="1" spans="1:7">
-      <c r="A18" s="35">
+    <row r="18" s="37" customFormat="1" spans="1:7">
+      <c r="A18" s="37">
         <v>301</v>
       </c>
-      <c r="B18" s="36" t="s">
+      <c r="B18" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="37">
         <v>50</v>
       </c>
-      <c r="D18" s="35">
-        <v>0</v>
-      </c>
-      <c r="E18" s="35">
+      <c r="D18" s="37">
+        <v>0</v>
+      </c>
+      <c r="E18" s="37">
         <v>400</v>
       </c>
-      <c r="F18" s="35">
-        <v>0</v>
-      </c>
-      <c r="G18" s="37">
+      <c r="F18" s="37">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="35" customFormat="1" spans="1:7">
-      <c r="A19" s="35">
+    <row r="19" s="37" customFormat="1" spans="1:7">
+      <c r="A19" s="37">
         <v>302</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="38" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <v>25</v>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="37">
         <v>9</v>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="37">
         <v>100</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="37">
         <v>303</v>
       </c>
-      <c r="G19" s="37">
+      <c r="G19" s="39">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="35" customFormat="1" spans="1:7">
-      <c r="A20" s="35">
+    <row r="20" s="37" customFormat="1" spans="1:7">
+      <c r="A20" s="37">
         <v>303</v>
       </c>
-      <c r="B20" s="36" t="s">
+      <c r="B20" s="38" t="s">
         <v>217</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="37">
         <v>20</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="37">
         <v>3</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="37">
         <v>50</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="37">
         <v>301</v>
       </c>
-      <c r="G20" s="37">
+      <c r="G20" s="39">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="35" customFormat="1" spans="1:7">
-      <c r="A21" s="35">
+    <row r="21" s="37" customFormat="1" spans="1:7">
+      <c r="A21" s="37">
         <v>304</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="38" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="37">
         <v>30</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="37">
         <v>11</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="37">
         <v>300</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="37">
         <v>301</v>
       </c>
-      <c r="G21" s="37">
+      <c r="G21" s="39">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="35" customFormat="1" spans="1:7">
-      <c r="A22" s="35">
+    <row r="22" s="37" customFormat="1" spans="1:7">
+      <c r="A22" s="37">
         <v>305</v>
       </c>
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="37">
         <v>25</v>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="37">
         <v>8</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="37">
         <v>100</v>
       </c>
-      <c r="F22" s="35">
+      <c r="F22" s="37">
         <v>303</v>
       </c>
-      <c r="G22" s="37">
+      <c r="G22" s="39">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="35" customFormat="1" spans="1:7">
-      <c r="A23" s="35">
+    <row r="23" s="37" customFormat="1" spans="1:7">
+      <c r="A23" s="37">
         <v>306</v>
       </c>
-      <c r="B23" s="36" t="s">
+      <c r="B23" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="37">
         <v>35</v>
       </c>
-      <c r="D23" s="35">
-        <v>0</v>
-      </c>
-      <c r="E23" s="35">
+      <c r="D23" s="37">
+        <v>0</v>
+      </c>
+      <c r="E23" s="37">
         <v>200</v>
       </c>
-      <c r="F23" s="35">
-        <v>0</v>
-      </c>
-      <c r="G23" s="37">
+      <c r="F23" s="37">
+        <v>0</v>
+      </c>
+      <c r="G23" s="39">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="35" customFormat="1" spans="1:7">
-      <c r="A24" s="35">
+    <row r="24" s="37" customFormat="1" spans="1:7">
+      <c r="A24" s="37">
         <v>307</v>
       </c>
-      <c r="B24" s="36" t="s">
+      <c r="B24" s="38" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="37">
         <v>35</v>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="37">
         <v>12</v>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="37">
         <v>150</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="37">
         <v>302</v>
       </c>
-      <c r="G24" s="37">
+      <c r="G24" s="39">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="35" customFormat="1" spans="1:7">
-      <c r="A25" s="35">
+    <row r="25" s="37" customFormat="1" spans="1:7">
+      <c r="A25" s="37">
         <v>308</v>
       </c>
-      <c r="B25" s="36" t="s">
+      <c r="B25" s="38" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <v>35</v>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="37">
         <v>12</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="37">
         <v>150</v>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="37">
         <v>302</v>
       </c>
-      <c r="G25" s="37">
+      <c r="G25" s="39">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="35" customFormat="1" spans="1:7">
-      <c r="A26" s="35">
+    <row r="26" s="37" customFormat="1" spans="1:7">
+      <c r="A26" s="37">
         <v>309</v>
       </c>
-      <c r="B26" s="36" t="s">
+      <c r="B26" s="38" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="37">
         <v>20</v>
       </c>
-      <c r="D26" s="35">
+      <c r="D26" s="37">
         <v>10</v>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="37">
         <v>80</v>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="37">
         <v>306</v>
       </c>
-      <c r="G26" s="37">
+      <c r="G26" s="39">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="35" customFormat="1" spans="1:7">
-      <c r="A27" s="35">
+    <row r="27" s="37" customFormat="1" spans="1:7">
+      <c r="A27" s="37">
         <v>310</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <v>30</v>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="37">
         <v>10</v>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="37">
         <v>120</v>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="37">
         <v>309</v>
       </c>
-      <c r="G27" s="37">
+      <c r="G27" s="39">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="35" customFormat="1" spans="1:7">
-      <c r="A28" s="35">
+    <row r="28" s="37" customFormat="1" spans="1:7">
+      <c r="A28" s="37">
         <v>311</v>
       </c>
-      <c r="B28" s="36" t="s">
+      <c r="B28" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="37">
         <v>30</v>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="37">
         <v>10</v>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="37">
         <v>120</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="37">
         <v>309</v>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="39">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="35" customFormat="1" spans="1:7">
-      <c r="A29" s="35">
+    <row r="29" s="37" customFormat="1" spans="1:7">
+      <c r="A29" s="37">
         <v>312</v>
       </c>
-      <c r="B29" s="36" t="s">
+      <c r="B29" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="37">
         <v>15</v>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="37">
         <v>2</v>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="37">
         <v>15</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="37">
         <v>306</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="39">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="35" customFormat="1" spans="1:7">
-      <c r="B30" s="36"/>
+    <row r="30" s="37" customFormat="1" spans="1:7">
+      <c r="B30" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12212,10 +13570,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="33">
+      <c r="A2" s="35">
         <v>3</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="35" t="s">
         <v>229</v>
       </c>
       <c r="C2">
@@ -12232,10 +13590,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="33">
+      <c r="A3" s="35">
         <v>4</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="35" t="s">
         <v>200</v>
       </c>
       <c r="C3">
@@ -12421,10 +13779,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="33">
+      <c r="A12" s="35">
         <v>309</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="35" t="s">
         <v>168</v>
       </c>
       <c r="C12">
@@ -12441,10 +13799,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="33">
+      <c r="A13" s="35">
         <v>310</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="35" t="s">
         <v>173</v>
       </c>
       <c r="C13">
@@ -12461,10 +13819,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="33">
+      <c r="A14" s="35">
         <v>311</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="35" t="s">
         <v>177</v>
       </c>
       <c r="C14">
@@ -12484,10 +13842,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="33">
+      <c r="A15" s="35">
         <v>312</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="35" t="s">
         <v>223</v>
       </c>
       <c r="C15">
@@ -12504,8 +13862,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="33"/>
-      <c r="B16" s="33"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12578,29 +13936,29 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" s="32" customFormat="1" spans="1:8">
-      <c r="A3" s="32">
+    <row r="3" s="34" customFormat="1" spans="1:8">
+      <c r="A3" s="34">
         <v>202</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="32">
-        <v>0</v>
-      </c>
-      <c r="F3" s="32">
+      <c r="E3" s="34">
+        <v>0</v>
+      </c>
+      <c r="F3" s="34">
         <v>0.8</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="34" t="s">
         <v>241</v>
       </c>
     </row>
@@ -12990,34 +14348,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="32" customFormat="1" spans="1:8">
-      <c r="A20" s="34">
+    <row r="20" s="34" customFormat="1" spans="1:8">
+      <c r="A20" s="36">
         <v>404</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="34" t="s">
         <v>239</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="E20" s="32">
-        <v>0</v>
-      </c>
-      <c r="F20" s="32">
+      <c r="E20" s="34">
+        <v>0</v>
+      </c>
+      <c r="F20" s="34">
         <v>0.8</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="34" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="30">
+      <c r="A21" s="32">
         <v>405</v>
       </c>
       <c r="B21" s="14" t="s">
@@ -13043,7 +14401,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="30">
+      <c r="A22" s="32">
         <v>406</v>
       </c>
       <c r="B22" s="14" t="s">
@@ -13069,7 +14427,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="31">
+      <c r="A23" s="33">
         <v>407</v>
       </c>
       <c r="B23" s="14" t="s">
@@ -13095,7 +14453,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="31">
+      <c r="A24" s="33">
         <v>408</v>
       </c>
       <c r="B24" s="14" t="s">
@@ -13121,7 +14479,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="31">
+      <c r="A25" s="33">
         <v>409</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -13147,7 +14505,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="31">
+      <c r="A26" s="33">
         <v>410</v>
       </c>
       <c r="B26" s="14" t="s">
@@ -13173,7 +14531,7 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="31">
+      <c r="A27" s="33">
         <v>411</v>
       </c>
       <c r="B27" s="14" t="s">
@@ -13239,68 +14597,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="32" customFormat="1" spans="1:21">
-      <c r="A1" s="32" t="s">
+    <row r="1" s="34" customFormat="1" spans="1:21">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="E1" s="32" t="s">
+      <c r="E1" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="34" t="s">
         <v>279</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="34" t="s">
         <v>280</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="34" t="s">
         <v>281</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="34" t="s">
         <v>282</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="N1" s="32" t="s">
+      <c r="N1" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="O1" s="32" t="s">
+      <c r="O1" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="Q1" s="32" t="s">
+      <c r="Q1" s="34" t="s">
         <v>290</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="34" t="s">
         <v>291</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="T1" s="32" t="s">
+      <c r="T1" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="U1" s="32" t="s">
+      <c r="U1" s="34" t="s">
         <v>294</v>
       </c>
     </row>
@@ -14172,7 +15530,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="33">
+      <c r="A17" s="35">
         <v>301</v>
       </c>
       <c r="B17" s="12" t="s">
@@ -14231,7 +15589,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="33">
+      <c r="A18" s="35">
         <v>302</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -14290,7 +15648,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="33">
+      <c r="A19" s="35">
         <v>303</v>
       </c>
       <c r="B19" s="12" t="s">
@@ -14349,7 +15707,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="33">
+      <c r="A20" s="35">
         <v>304</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -14470,7 +15828,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="33">
+      <c r="A22" s="35">
         <v>306</v>
       </c>
       <c r="B22" s="12" t="s">
@@ -14529,7 +15887,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="33">
+      <c r="A23" s="35">
         <v>307</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -14588,7 +15946,7 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="33">
+      <c r="A24" s="35">
         <v>308</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -14647,7 +16005,7 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="33">
+      <c r="A25" s="35">
         <v>309</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -14706,7 +16064,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="33">
+      <c r="A26" s="35">
         <v>310</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -14765,7 +16123,7 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="33">
+      <c r="A27" s="35">
         <v>311</v>
       </c>
       <c r="B27" s="12" t="s">
@@ -14824,7 +16182,7 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="33">
+      <c r="A28" s="35">
         <v>312</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -15057,7 +16415,7 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="30">
+      <c r="A32" s="32">
         <v>404</v>
       </c>
       <c r="B32" s="14" t="s">
@@ -15119,7 +16477,7 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="30">
+      <c r="A33" s="32">
         <v>405</v>
       </c>
       <c r="B33" s="14" t="s">
@@ -15175,7 +16533,7 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="30">
+      <c r="A34" s="32">
         <v>406</v>
       </c>
       <c r="B34" s="14" t="s">
@@ -15231,7 +16589,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="31">
+      <c r="A35" s="33">
         <v>407</v>
       </c>
       <c r="B35" s="14" t="s">
@@ -15287,7 +16645,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="31">
+      <c r="A36" s="33">
         <v>408</v>
       </c>
       <c r="B36" s="14" t="s">
@@ -15346,7 +16704,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="31">
+      <c r="A37" s="33">
         <v>409</v>
       </c>
       <c r="B37" s="14" t="s">
@@ -15405,7 +16763,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="31">
+      <c r="A38" s="33">
         <v>410</v>
       </c>
       <c r="B38" s="14" t="s">
@@ -15455,7 +16813,7 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="31">
+      <c r="A39" s="33">
         <v>411</v>
       </c>
       <c r="B39" s="14" t="s">
@@ -15617,7 +16975,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="30">
+      <c r="A9" s="32">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -15628,7 +16986,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="30">
+      <c r="A10" s="32">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -15639,7 +16997,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="30">
+      <c r="A11" s="32">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -15650,7 +17008,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="31">
+      <c r="A12" s="33">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -15661,7 +17019,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="31">
+      <c r="A13" s="33">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -15672,7 +17030,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="31">
+      <c r="A14" s="33">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -15683,7 +17041,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="31">
+      <c r="A15" s="33">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -15694,7 +17052,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="31">
+      <c r="A16" s="33">
         <v>411</v>
       </c>
       <c r="B16" t="s">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -2115,7 +2115,18 @@
     <t>Deleted</t>
   </si>
   <si>
-    <t>Key遭到攻击</t>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>遭到攻击</t>
+    </r>
   </si>
   <si>
     <t>遭到攻击</t>
@@ -3545,7 +3556,7 @@
     <t>，枪兵已败。切记，面对强敌，闪避为先。仔细观察炸点特效，善用强行走身法躲开坦克炸点，方能在战场上立于不败之地。</t>
   </si>
   <si>
-    <t>, your riflemen have been defeated. Remember this: when facing a superior foe, evasion comes first. Watch closely for the blast point visual cue and master the Force March maneuver to dodge the tank’s blasts—only then can you prevail on the battlefield.</t>
+    <t>, your riflemen have been defeated. Remember this: when facing a superior foe, evasion comes first. Watch closely for the blast point visual cue and master the Force Move maneuver to dodge the tank’s blasts—only then can you prevail on the battlefield.</t>
   </si>
   <si>
     <t>Key弟子谨记前辈教诲。</t>
@@ -3789,6 +3800,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>第</t>
     </r>
     <r>
@@ -4738,7 +4755,7 @@
     The lone fortress stands clad in iron, gunsmoke tears through the clouds.
     Blood stains the backbone of mountains and rivers, bones forge an unyielding monument.
     When I return through wind and snow, the Marshal shall come home with the dawn!
-        ————By ERNIE Bot Mini AI"</t>
+        ————By ERNIE Bot Mini AI</t>
     </r>
   </si>
   <si>
@@ -5289,7 +5306,7 @@
     <t>飞虫气血已不足一半！速速施展&lt;color=#a0ff50&gt;强行走&lt;/color&gt;身法，让飞虫回到苔蔓上调息回血！</t>
   </si>
   <si>
-    <t>Your Flying Bug's health is below 50%! Activate the &lt;color=#a0ff50&gt;Force Move&lt;/color&gt; ability immediately and retreat it to the Mossy Vines to regenerate health!</t>
+    <t>Your Flying Bug's health is below 50%! Activate the &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; ability immediately and retreat it to the Mossy Vines to regenerate health!</t>
   </si>
   <si>
     <t>Key飞虫在苔蔓上……</t>

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1326">
   <si>
     <t>类型</t>
   </si>
@@ -2116,6 +2116,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>Key</t>
     </r>
     <r>
@@ -4729,6 +4735,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">The Drill Instructor sent 1000 Crystal Ores. If that’s not enough, you’ll have to gather more on-site. Hold the line—I’m mobilizing reinforcements right now! I leave you with this poem, </t>
     </r>
     <r>
@@ -5136,7 +5149,7 @@
     <t>很好！您的工虫正在采集晶体矿，请等他把晶体矿运回虫巢。现在，请先点&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;，再蜕变一个工虫去采集&lt;color=#a0ff50&gt;燃气矿&lt;/color&gt;</t>
   </si>
   <si>
-    <t>Great! Your Worker Bug is harvesting Crystal Ore. Wait for it to deliver the ore to the Hive. Now, first click &lt;color=#a0ff50&gt;Deselect&lt;/color&gt;, then morph another Worker Bug to harvest the &lt;color=#a0ff50&gt;Gas Vein&lt;/color&gt;.</t>
+    <t>Great! Your Worker Bug is harvesting Crystal Ore. Wait for it to deliver the ore to the Hive. Now, first click &lt;color=#a0ff50 &gt;Deselect&lt;/color&gt;, then morph another Worker Bug to harvest the &lt;color=#a0ff50&gt;Gas Vein&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key工虫已运晶体矿……</t>
@@ -5208,7 +5221,7 @@
     <t>现在已在左边给您刷了一个敌人，点击选中您的&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再&lt;color=#a0ff50&gt;点击敌人附近的地面&lt;/color&gt;，近战虫会走向目标并自动攻击。您可以点右下角&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;然后拖动地面看看敌人在哪里</t>
   </si>
   <si>
-    <t>Enemies have been spawned on the left. Click to select your &lt;color=#a0ff50&gt;Melee Bug&lt;/color&gt;, then &lt;color=#a0ff50&gt;click the ground near the enemies&lt;/color&gt;—the Melee Bug will move to the target and attack automatically. You can click &lt;color=#a0ff50&gt;Deselect&lt;/color&gt; in the bottom-right corner and drag the screen to locate the enemies.</t>
+    <t>Enemies have been spawned on the left. Click to select your &lt;color=#a0ff50&gt;Melee Bug&lt;/color&gt;, then &lt;color=#a0ff50&gt;click the ground near the enemies&lt;/color&gt;—the Melee Bug will move to the target and attack automatically. You can click &lt;color=#a0ff50&gt; Deselect&lt;/color&gt; in the bottom-right corner and drag the screen to locate the enemies.</t>
   </si>
   <si>
     <t>Key近战虫阵亡……</t>
@@ -5353,6 +5366,58 @@
         <charset val="134"/>
       </rPr>
       <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Key燃气矿不足无法建造</t>
+  </si>
+  <si>
+    <t>燃气矿不足，无法建造</t>
+  </si>
+  <si>
+    <t>Key燃气矿不足不能升级</t>
+  </si>
+  <si>
+    <t>燃气矿不足，不能升级</t>
+  </si>
+  <si>
+    <t>Key晶体矿不足不能升级</t>
+  </si>
+  <si>
+    <t>晶体矿不足，不能升级</t>
+  </si>
+  <si>
+    <t>Key已采集{}</t>
+  </si>
+  <si>
+    <r>
+      <t>已采集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Key剩余{}</t>
+  </si>
+  <si>
+    <r>
+      <t>剩余</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}</t>
     </r>
   </si>
 </sst>
@@ -6100,7 +6165,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6162,6 +6227,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -6604,20 +6675,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="37" customFormat="1" spans="1:18">
-      <c r="A2" s="37">
+    <row r="2" s="39" customFormat="1" spans="1:18">
+      <c r="A2" s="39">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="37">
-        <v>0</v>
-      </c>
-      <c r="G2" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="37">
+      <c r="C2" s="39">
+        <v>0</v>
+      </c>
+      <c r="G2" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="39">
         <v>1</v>
       </c>
       <c r="J2">
@@ -6626,33 +6697,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="37">
-        <v>1</v>
-      </c>
-      <c r="N2" s="37">
-        <v>0</v>
-      </c>
-      <c r="O2" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="37" customFormat="1" spans="1:18">
-      <c r="A3" s="37">
+      <c r="M2" s="39">
+        <v>1</v>
+      </c>
+      <c r="N2" s="39">
+        <v>0</v>
+      </c>
+      <c r="O2" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="39" customFormat="1" spans="1:18">
+      <c r="A3" s="39">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="37">
-        <v>0</v>
-      </c>
-      <c r="G3" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="37">
+      <c r="C3" s="39">
+        <v>0</v>
+      </c>
+      <c r="G3" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="39">
         <v>1</v>
       </c>
       <c r="J3">
@@ -6661,36 +6732,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="37">
-        <v>1</v>
-      </c>
-      <c r="N3" s="37">
-        <v>0</v>
-      </c>
-      <c r="O3" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="32" customFormat="1" spans="1:18">
-      <c r="A4" s="32">
+      <c r="M3" s="39">
+        <v>1</v>
+      </c>
+      <c r="N3" s="39">
+        <v>0</v>
+      </c>
+      <c r="O3" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="34" customFormat="1" spans="1:18">
+      <c r="A4" s="34">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="34">
         <v>2</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="37">
+      <c r="G4" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="39">
         <v>1</v>
       </c>
       <c r="J4">
@@ -6699,36 +6770,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="37">
-        <v>1</v>
-      </c>
-      <c r="N4" s="37">
-        <v>0</v>
-      </c>
-      <c r="O4" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A5" s="32">
+      <c r="M4" s="39">
+        <v>1</v>
+      </c>
+      <c r="N4" s="39">
+        <v>0</v>
+      </c>
+      <c r="O4" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A5" s="34">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="32">
-        <v>0</v>
-      </c>
-      <c r="D5" s="32" t="s">
+      <c r="C5" s="34">
+        <v>0</v>
+      </c>
+      <c r="D5" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="37">
+      <c r="G5" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="39">
         <v>1</v>
       </c>
       <c r="J5">
@@ -6737,48 +6808,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="37">
-        <v>1</v>
-      </c>
-      <c r="N5" s="37">
-        <v>0</v>
-      </c>
-      <c r="O5" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="32">
-        <v>0</v>
-      </c>
-      <c r="R5" s="22" t="s">
+      <c r="M5" s="39">
+        <v>1</v>
+      </c>
+      <c r="N5" s="39">
+        <v>0</v>
+      </c>
+      <c r="O5" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="34">
+        <v>0</v>
+      </c>
+      <c r="R5" s="24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="38" customFormat="1" spans="1:18">
-      <c r="A6" s="38">
+    <row r="6" s="40" customFormat="1" spans="1:18">
+      <c r="A6" s="40">
         <v>101</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="38">
-        <v>0</v>
-      </c>
-      <c r="D6" s="38" t="s">
+      <c r="C6" s="40">
+        <v>0</v>
+      </c>
+      <c r="D6" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="37" t="b">
+      <c r="G6" s="39" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="39">
         <v>1</v>
       </c>
       <c r="J6">
@@ -6790,39 +6861,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="37">
-        <v>1</v>
-      </c>
-      <c r="N6" s="37">
-        <v>0</v>
-      </c>
-      <c r="O6" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="38" customFormat="1" spans="1:18">
-      <c r="A7" s="38">
+      <c r="M6" s="39">
+        <v>1</v>
+      </c>
+      <c r="N6" s="39">
+        <v>0</v>
+      </c>
+      <c r="O6" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="40" customFormat="1" spans="1:18">
+      <c r="A7" s="40">
         <v>102</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="38">
-        <v>0</v>
-      </c>
-      <c r="D7" s="38" t="s">
+      <c r="C7" s="40">
+        <v>0</v>
+      </c>
+      <c r="D7" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="37">
+      <c r="G7" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="39">
         <v>1</v>
       </c>
       <c r="J7">
@@ -6831,16 +6902,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="37">
-        <v>1</v>
-      </c>
-      <c r="N7" s="37">
-        <v>0</v>
-      </c>
-      <c r="O7" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="38">
+      <c r="M7" s="39">
+        <v>1</v>
+      </c>
+      <c r="N7" s="39">
+        <v>0</v>
+      </c>
+      <c r="O7" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="40">
         <v>0</v>
       </c>
     </row>
@@ -6863,13 +6934,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="37" t="b">
+      <c r="G8" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="39">
         <v>1</v>
       </c>
       <c r="J8">
@@ -6881,13 +6952,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="37">
-        <v>1</v>
-      </c>
-      <c r="N8" s="37">
-        <v>0</v>
-      </c>
-      <c r="O8" s="37">
+      <c r="M8" s="39">
+        <v>1</v>
+      </c>
+      <c r="N8" s="39">
+        <v>0</v>
+      </c>
+      <c r="O8" s="39">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -6896,63 +6967,63 @@
       <c r="Q8">
         <v>3</v>
       </c>
-      <c r="R8" s="22" t="s">
+      <c r="R8" s="24" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="31" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A9" s="31">
+    <row r="9" s="33" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A9" s="33">
         <v>202</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="31">
-        <v>1</v>
-      </c>
-      <c r="D9" s="31" t="s">
+      <c r="C9" s="33">
+        <v>1</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="G9" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="39">
-        <v>1</v>
-      </c>
-      <c r="J9" s="31">
-        <v>0</v>
-      </c>
-      <c r="K9" s="31">
+      <c r="I9" s="41">
+        <v>1</v>
+      </c>
+      <c r="J9" s="33">
+        <v>0</v>
+      </c>
+      <c r="K9" s="33">
         <v>2</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="L9" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="39">
-        <v>1</v>
-      </c>
-      <c r="N9" s="39">
-        <v>0</v>
-      </c>
-      <c r="O9" s="39">
-        <v>0</v>
-      </c>
-      <c r="P9" s="31" t="s">
+      <c r="M9" s="41">
+        <v>1</v>
+      </c>
+      <c r="N9" s="41">
+        <v>0</v>
+      </c>
+      <c r="O9" s="41">
+        <v>0</v>
+      </c>
+      <c r="P9" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="31">
+      <c r="Q9" s="33">
         <v>3</v>
       </c>
-      <c r="R9" s="22" t="s">
+      <c r="R9" s="24" t="s">
         <v>45</v>
       </c>
     </row>
@@ -6975,13 +7046,13 @@
       <c r="F10" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="37" t="b">
+      <c r="G10" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="37">
+      <c r="I10" s="39">
         <v>1</v>
       </c>
       <c r="J10">
@@ -6993,13 +7064,13 @@
       <c r="L10">
         <v>3</v>
       </c>
-      <c r="M10" s="37">
-        <v>1</v>
-      </c>
-      <c r="N10" s="37">
-        <v>0</v>
-      </c>
-      <c r="O10" s="37">
+      <c r="M10" s="39">
+        <v>1</v>
+      </c>
+      <c r="N10" s="39">
+        <v>0</v>
+      </c>
+      <c r="O10" s="39">
         <v>0</v>
       </c>
       <c r="P10" t="s">
@@ -7008,7 +7079,7 @@
       <c r="Q10">
         <v>3</v>
       </c>
-      <c r="R10" s="22" t="s">
+      <c r="R10" s="24" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7028,13 +7099,13 @@
       <c r="E11" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="37" t="b">
+      <c r="G11" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="37">
+      <c r="I11" s="39">
         <v>1</v>
       </c>
       <c r="J11">
@@ -7046,13 +7117,13 @@
       <c r="L11" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="37">
-        <v>1</v>
-      </c>
-      <c r="N11" s="37">
-        <v>0</v>
-      </c>
-      <c r="O11" s="37">
+      <c r="M11" s="39">
+        <v>1</v>
+      </c>
+      <c r="N11" s="39">
+        <v>0</v>
+      </c>
+      <c r="O11" s="39">
         <v>0</v>
       </c>
       <c r="P11" t="s">
@@ -7061,7 +7132,7 @@
       <c r="Q11">
         <v>2</v>
       </c>
-      <c r="R11" s="22" t="s">
+      <c r="R11" s="24" t="s">
         <v>57</v>
       </c>
     </row>
@@ -7084,13 +7155,13 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="37" t="b">
+      <c r="G12" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="37">
+      <c r="I12" s="39">
         <v>1</v>
       </c>
       <c r="J12">
@@ -7102,13 +7173,13 @@
       <c r="L12" t="s">
         <v>62</v>
       </c>
-      <c r="M12" s="37">
-        <v>1</v>
-      </c>
-      <c r="N12" s="37">
-        <v>0</v>
-      </c>
-      <c r="O12" s="37">
+      <c r="M12" s="39">
+        <v>1</v>
+      </c>
+      <c r="N12" s="39">
+        <v>0</v>
+      </c>
+      <c r="O12" s="39">
         <v>0</v>
       </c>
       <c r="P12" t="s">
@@ -7117,7 +7188,7 @@
       <c r="Q12">
         <v>2</v>
       </c>
-      <c r="R12" s="22" t="s">
+      <c r="R12" s="24" t="s">
         <v>64</v>
       </c>
     </row>
@@ -7140,13 +7211,13 @@
       <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="37" t="b">
+      <c r="G13" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="37">
+      <c r="I13" s="39">
         <v>1</v>
       </c>
       <c r="J13">
@@ -7158,13 +7229,13 @@
       <c r="L13" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="M13" s="37">
-        <v>1</v>
-      </c>
-      <c r="N13" s="37">
-        <v>1</v>
-      </c>
-      <c r="O13" s="37">
+      <c r="M13" s="39">
+        <v>1</v>
+      </c>
+      <c r="N13" s="39">
+        <v>1</v>
+      </c>
+      <c r="O13" s="39">
         <v>2</v>
       </c>
       <c r="P13" t="s">
@@ -7173,7 +7244,7 @@
       <c r="Q13">
         <v>5</v>
       </c>
-      <c r="R13" s="22" t="s">
+      <c r="R13" s="24" t="s">
         <v>71</v>
       </c>
     </row>
@@ -7193,16 +7264,16 @@
       <c r="E14" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="40" t="s">
+      <c r="F14" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="37" t="b">
+      <c r="G14" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>29</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="39">
         <v>1</v>
       </c>
       <c r="J14">
@@ -7214,13 +7285,13 @@
       <c r="L14" t="s">
         <v>30</v>
       </c>
-      <c r="M14" s="37">
-        <v>1</v>
-      </c>
-      <c r="N14" s="37">
-        <v>0</v>
-      </c>
-      <c r="O14" s="37">
+      <c r="M14" s="39">
+        <v>1</v>
+      </c>
+      <c r="N14" s="39">
+        <v>0</v>
+      </c>
+      <c r="O14" s="39">
         <v>0</v>
       </c>
       <c r="P14" t="s">
@@ -7229,7 +7300,7 @@
       <c r="Q14">
         <v>2</v>
       </c>
-      <c r="R14" s="22" t="s">
+      <c r="R14" s="24" t="s">
         <v>77</v>
       </c>
     </row>
@@ -7249,16 +7320,16 @@
       <c r="E15" t="s">
         <v>80</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="G15" s="37" t="b">
+      <c r="G15" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="37">
+      <c r="I15" s="39">
         <v>1</v>
       </c>
       <c r="J15">
@@ -7270,13 +7341,13 @@
       <c r="L15" t="s">
         <v>30</v>
       </c>
-      <c r="M15" s="37">
-        <v>1</v>
-      </c>
-      <c r="N15" s="37">
-        <v>0</v>
-      </c>
-      <c r="O15" s="37">
+      <c r="M15" s="39">
+        <v>1</v>
+      </c>
+      <c r="N15" s="39">
+        <v>0</v>
+      </c>
+      <c r="O15" s="39">
         <v>0</v>
       </c>
       <c r="P15" t="s">
@@ -7285,7 +7356,7 @@
       <c r="Q15">
         <v>2</v>
       </c>
-      <c r="R15" s="22" t="s">
+      <c r="R15" s="24" t="s">
         <v>83</v>
       </c>
     </row>
@@ -7308,13 +7379,13 @@
       <c r="F16" t="s">
         <v>87</v>
       </c>
-      <c r="G16" s="37" t="b">
+      <c r="G16" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>88</v>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="39">
         <v>1</v>
       </c>
       <c r="J16">
@@ -7326,13 +7397,13 @@
       <c r="L16" t="s">
         <v>89</v>
       </c>
-      <c r="M16" s="37">
-        <v>1</v>
-      </c>
-      <c r="N16" s="37">
-        <v>0</v>
-      </c>
-      <c r="O16" s="37">
+      <c r="M16" s="39">
+        <v>1</v>
+      </c>
+      <c r="N16" s="39">
+        <v>0</v>
+      </c>
+      <c r="O16" s="39">
         <v>0</v>
       </c>
       <c r="P16" t="s">
@@ -7341,7 +7412,7 @@
       <c r="Q16">
         <v>1</v>
       </c>
-      <c r="R16" s="22" t="s">
+      <c r="R16" s="24" t="s">
         <v>91</v>
       </c>
     </row>
@@ -7364,13 +7435,13 @@
       <c r="F17" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="37" t="b">
+      <c r="G17" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="37">
+      <c r="I17" s="39">
         <v>1</v>
       </c>
       <c r="J17">
@@ -7382,13 +7453,13 @@
       <c r="L17" t="s">
         <v>55</v>
       </c>
-      <c r="M17" s="37">
-        <v>1</v>
-      </c>
-      <c r="N17" s="37">
-        <v>0</v>
-      </c>
-      <c r="O17" s="37">
+      <c r="M17" s="39">
+        <v>1</v>
+      </c>
+      <c r="N17" s="39">
+        <v>0</v>
+      </c>
+      <c r="O17" s="39">
         <v>0</v>
       </c>
       <c r="P17" t="s">
@@ -7397,7 +7468,7 @@
       <c r="Q17">
         <v>2</v>
       </c>
-      <c r="R17" s="22" t="s">
+      <c r="R17" s="24" t="s">
         <v>96</v>
       </c>
     </row>
@@ -7414,10 +7485,10 @@
       <c r="D18" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="37">
+      <c r="G18" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="39">
         <v>1</v>
       </c>
       <c r="J18">
@@ -7426,13 +7497,13 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="M18" s="37">
-        <v>1</v>
-      </c>
-      <c r="N18" s="37">
-        <v>0</v>
-      </c>
-      <c r="O18" s="37">
+      <c r="M18" s="39">
+        <v>1</v>
+      </c>
+      <c r="N18" s="39">
+        <v>0</v>
+      </c>
+      <c r="O18" s="39">
         <v>0</v>
       </c>
       <c r="Q18">
@@ -7458,13 +7529,13 @@
       <c r="F19" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="37" t="b">
+      <c r="G19" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>103</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="39">
         <v>1</v>
       </c>
       <c r="J19">
@@ -7476,13 +7547,13 @@
       <c r="L19" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="37">
-        <v>1</v>
-      </c>
-      <c r="N19" s="37">
-        <v>0</v>
-      </c>
-      <c r="O19" s="37">
+      <c r="M19" s="39">
+        <v>1</v>
+      </c>
+      <c r="N19" s="39">
+        <v>0</v>
+      </c>
+      <c r="O19" s="39">
         <v>0</v>
       </c>
       <c r="P19" t="s">
@@ -7491,7 +7562,7 @@
       <c r="Q19">
         <v>4</v>
       </c>
-      <c r="R19" s="22" t="s">
+      <c r="R19" s="24" t="s">
         <v>106</v>
       </c>
     </row>
@@ -7514,13 +7585,13 @@
       <c r="F20" t="s">
         <v>110</v>
       </c>
-      <c r="G20" s="37" t="b">
+      <c r="G20" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>103</v>
       </c>
-      <c r="I20" s="37">
+      <c r="I20" s="39">
         <v>1</v>
       </c>
       <c r="J20">
@@ -7532,13 +7603,13 @@
       <c r="L20" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="37">
-        <v>1</v>
-      </c>
-      <c r="N20" s="37">
-        <v>0</v>
-      </c>
-      <c r="O20" s="37">
+      <c r="M20" s="39">
+        <v>1</v>
+      </c>
+      <c r="N20" s="39">
+        <v>0</v>
+      </c>
+      <c r="O20" s="39">
         <v>0</v>
       </c>
       <c r="P20" t="s">
@@ -7547,7 +7618,7 @@
       <c r="Q20">
         <v>4</v>
       </c>
-      <c r="R20" s="22" t="s">
+      <c r="R20" s="24" t="s">
         <v>112</v>
       </c>
     </row>
@@ -7570,13 +7641,13 @@
       <c r="F21" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="37" t="b">
+      <c r="G21" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" s="37">
+      <c r="I21" s="39">
         <v>1</v>
       </c>
       <c r="J21">
@@ -7588,13 +7659,13 @@
       <c r="L21">
         <v>2</v>
       </c>
-      <c r="M21" s="37">
-        <v>1</v>
-      </c>
-      <c r="N21" s="37">
-        <v>0</v>
-      </c>
-      <c r="O21" s="37">
+      <c r="M21" s="39">
+        <v>1</v>
+      </c>
+      <c r="N21" s="39">
+        <v>0</v>
+      </c>
+      <c r="O21" s="39">
         <v>0</v>
       </c>
       <c r="P21" t="s">
@@ -7603,7 +7674,7 @@
       <c r="Q21">
         <v>3</v>
       </c>
-      <c r="R21" s="22" t="s">
+      <c r="R21" s="24" t="s">
         <v>118</v>
       </c>
     </row>
@@ -7626,13 +7697,13 @@
       <c r="F22" t="s">
         <v>121</v>
       </c>
-      <c r="G22" s="37" t="b">
+      <c r="G22" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="37">
+      <c r="I22" s="39">
         <v>1</v>
       </c>
       <c r="J22">
@@ -7644,13 +7715,13 @@
       <c r="L22" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="37">
-        <v>1</v>
-      </c>
-      <c r="N22" s="37">
-        <v>0</v>
-      </c>
-      <c r="O22" s="37">
+      <c r="M22" s="39">
+        <v>1</v>
+      </c>
+      <c r="N22" s="39">
+        <v>0</v>
+      </c>
+      <c r="O22" s="39">
         <v>0</v>
       </c>
       <c r="P22" t="s">
@@ -7659,36 +7730,36 @@
       <c r="Q22">
         <v>3</v>
       </c>
-      <c r="R22" s="22" t="s">
+      <c r="R22" s="24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="23" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A23" s="32">
+    <row r="23" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A23" s="34">
         <v>301</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="32">
-        <v>1</v>
-      </c>
-      <c r="D23" s="32" t="s">
+      <c r="C23" s="34">
+        <v>1</v>
+      </c>
+      <c r="D23" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="32" t="s">
+      <c r="F23" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="G23" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" s="32" t="s">
+      <c r="G23" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="37">
+      <c r="I23" s="39">
         <v>1</v>
       </c>
       <c r="J23">
@@ -7697,54 +7768,54 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23" s="32" t="s">
+      <c r="L23" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="M23" s="37">
-        <v>1</v>
-      </c>
-      <c r="N23" s="37">
-        <v>0</v>
-      </c>
-      <c r="O23" s="37">
-        <v>0</v>
-      </c>
-      <c r="P23" s="32" t="s">
+      <c r="M23" s="39">
+        <v>1</v>
+      </c>
+      <c r="N23" s="39">
+        <v>0</v>
+      </c>
+      <c r="O23" s="39">
+        <v>0</v>
+      </c>
+      <c r="P23" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="34">
         <v>3</v>
       </c>
-      <c r="R23" s="22" t="s">
+      <c r="R23" s="24" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="24" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A24" s="32">
+    <row r="24" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A24" s="34">
         <v>302</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="32">
-        <v>1</v>
-      </c>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="34">
+        <v>1</v>
+      </c>
+      <c r="D24" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="32" t="s">
+      <c r="F24" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="G24" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="32" t="s">
+      <c r="G24" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="39">
         <v>0.1</v>
       </c>
       <c r="J24">
@@ -7753,51 +7824,51 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="34" t="s">
         <v>133</v>
       </c>
-      <c r="M24" s="37">
-        <v>1</v>
-      </c>
-      <c r="N24" s="37">
-        <v>0</v>
-      </c>
-      <c r="O24" s="37">
-        <v>0</v>
-      </c>
-      <c r="P24" s="32" t="s">
+      <c r="M24" s="39">
+        <v>1</v>
+      </c>
+      <c r="N24" s="39">
+        <v>0</v>
+      </c>
+      <c r="O24" s="39">
+        <v>0</v>
+      </c>
+      <c r="P24" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="34">
         <v>3</v>
       </c>
-      <c r="R24" s="22" t="s">
+      <c r="R24" s="24" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="25" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A25" s="32">
+    <row r="25" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A25" s="34">
         <v>303</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="32">
-        <v>1</v>
-      </c>
-      <c r="D25" s="32" t="s">
+      <c r="C25" s="34">
+        <v>1</v>
+      </c>
+      <c r="D25" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="32" t="s">
+      <c r="G25" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="37">
+      <c r="I25" s="39">
         <v>1</v>
       </c>
       <c r="J25">
@@ -7806,51 +7877,51 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="M25" s="37">
-        <v>1</v>
-      </c>
-      <c r="N25" s="37">
-        <v>0</v>
-      </c>
-      <c r="O25" s="37">
-        <v>0</v>
-      </c>
-      <c r="P25" s="32" t="s">
+      <c r="M25" s="39">
+        <v>1</v>
+      </c>
+      <c r="N25" s="39">
+        <v>0</v>
+      </c>
+      <c r="O25" s="39">
+        <v>0</v>
+      </c>
+      <c r="P25" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="34">
         <v>3</v>
       </c>
-      <c r="R25" s="22" t="s">
+      <c r="R25" s="24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A26" s="32">
+    <row r="26" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A26" s="34">
         <v>304</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C26" s="32">
-        <v>1</v>
-      </c>
-      <c r="D26" s="32" t="s">
+      <c r="C26" s="34">
+        <v>1</v>
+      </c>
+      <c r="D26" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="34" t="s">
         <v>141</v>
       </c>
-      <c r="G26" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="32" t="s">
+      <c r="G26" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="I26" s="37">
+      <c r="I26" s="39">
         <v>0.05</v>
       </c>
       <c r="J26">
@@ -7859,54 +7930,54 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26" s="32" t="s">
+      <c r="L26" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="M26" s="37">
-        <v>1</v>
-      </c>
-      <c r="N26" s="37">
-        <v>0</v>
-      </c>
-      <c r="O26" s="37">
-        <v>0</v>
-      </c>
-      <c r="P26" s="32" t="s">
+      <c r="M26" s="39">
+        <v>1</v>
+      </c>
+      <c r="N26" s="39">
+        <v>0</v>
+      </c>
+      <c r="O26" s="39">
+        <v>0</v>
+      </c>
+      <c r="P26" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="Q26" s="32">
+      <c r="Q26" s="34">
         <v>3</v>
       </c>
-      <c r="R26" s="22" t="s">
+      <c r="R26" s="24" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="27" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A27" s="32">
+    <row r="27" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A27" s="34">
         <v>305</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="34">
         <v>3</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="32" t="s">
+      <c r="F27" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="G27" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H27" s="32" t="s">
+      <c r="G27" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" s="34" t="s">
         <v>146</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="39">
         <v>1</v>
       </c>
       <c r="J27">
@@ -7918,51 +7989,51 @@
       <c r="L27" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="37">
-        <v>1</v>
-      </c>
-      <c r="N27" s="37">
-        <v>0</v>
-      </c>
-      <c r="O27" s="37">
-        <v>0</v>
-      </c>
-      <c r="P27" s="32" t="s">
+      <c r="M27" s="39">
+        <v>1</v>
+      </c>
+      <c r="N27" s="39">
+        <v>0</v>
+      </c>
+      <c r="O27" s="39">
+        <v>0</v>
+      </c>
+      <c r="P27" s="34" t="s">
         <v>147</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="34">
         <v>3</v>
       </c>
-      <c r="R27" s="22" t="s">
+      <c r="R27" s="24" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="28" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A28" s="32">
+    <row r="28" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A28" s="34">
         <v>306</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="34">
         <v>2</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="F28" s="32" t="s">
+      <c r="F28" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="G28" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H28" s="32">
-        <v>0</v>
-      </c>
-      <c r="I28" s="37">
+      <c r="G28" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" s="34">
+        <v>0</v>
+      </c>
+      <c r="I28" s="39">
         <v>1</v>
       </c>
       <c r="J28">
@@ -7971,54 +8042,54 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28" s="32">
-        <v>1</v>
-      </c>
-      <c r="M28" s="37">
-        <v>1</v>
-      </c>
-      <c r="N28" s="37">
-        <v>0</v>
-      </c>
-      <c r="O28" s="37">
-        <v>0</v>
-      </c>
-      <c r="P28" s="32" t="s">
+      <c r="L28" s="34">
+        <v>1</v>
+      </c>
+      <c r="M28" s="39">
+        <v>1</v>
+      </c>
+      <c r="N28" s="39">
+        <v>0</v>
+      </c>
+      <c r="O28" s="39">
+        <v>0</v>
+      </c>
+      <c r="P28" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="34">
         <v>3</v>
       </c>
-      <c r="R28" s="22" t="s">
+      <c r="R28" s="24" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="29" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A29" s="32">
+    <row r="29" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A29" s="34">
         <v>307</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C29" s="32">
-        <v>1</v>
-      </c>
-      <c r="D29" s="32" t="s">
+      <c r="C29" s="34">
+        <v>1</v>
+      </c>
+      <c r="D29" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="E29" s="32" t="s">
+      <c r="E29" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F29" s="32" t="s">
+      <c r="F29" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="G29" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="32" t="s">
+      <c r="G29" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="I29" s="37">
+      <c r="I29" s="39">
         <v>1</v>
       </c>
       <c r="J29">
@@ -8027,54 +8098,54 @@
       <c r="K29">
         <v>4.73</v>
       </c>
-      <c r="L29" s="32" t="s">
+      <c r="L29" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="39">
         <v>0.1</v>
       </c>
-      <c r="N29" s="37">
-        <v>0</v>
-      </c>
-      <c r="O29" s="37">
+      <c r="N29" s="39">
+        <v>0</v>
+      </c>
+      <c r="O29" s="39">
         <v>0.17</v>
       </c>
-      <c r="P29" s="32" t="s">
+      <c r="P29" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" s="32">
+      <c r="Q29" s="34">
         <v>3</v>
       </c>
-      <c r="R29" s="22" t="s">
+      <c r="R29" s="24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A30" s="32">
+    <row r="30" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A30" s="34">
         <v>308</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="C30" s="32">
-        <v>1</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="C30" s="34">
+        <v>1</v>
+      </c>
+      <c r="D30" s="34" t="s">
         <v>161</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="32" t="s">
+      <c r="F30" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="G30" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="32" t="s">
+      <c r="G30" s="39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="I30" s="37">
+      <c r="I30" s="39">
         <v>1</v>
       </c>
       <c r="J30">
@@ -8083,54 +8154,54 @@
       <c r="K30">
         <v>0</v>
       </c>
-      <c r="L30" s="32" t="s">
+      <c r="L30" s="34" t="s">
         <v>158</v>
       </c>
-      <c r="M30" s="37">
-        <v>1</v>
-      </c>
-      <c r="N30" s="37">
-        <v>0</v>
-      </c>
-      <c r="O30" s="37">
-        <v>0</v>
-      </c>
-      <c r="P30" s="32" t="s">
+      <c r="M30" s="39">
+        <v>1</v>
+      </c>
+      <c r="N30" s="39">
+        <v>0</v>
+      </c>
+      <c r="O30" s="39">
+        <v>0</v>
+      </c>
+      <c r="P30" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="Q30" s="32">
+      <c r="Q30" s="34">
         <v>3</v>
       </c>
-      <c r="R30" s="22" t="s">
+      <c r="R30" s="24" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="31" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A31" s="32">
+    <row r="31" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A31" s="34">
         <v>309</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="34">
         <v>2</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="32" t="s">
+      <c r="F31" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="G31" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H31" s="32" t="s">
+      <c r="G31" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="39">
         <v>1</v>
       </c>
       <c r="J31">
@@ -8139,54 +8210,54 @@
       <c r="K31">
         <v>0</v>
       </c>
-      <c r="L31" s="32" t="s">
+      <c r="L31" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="M31" s="37">
-        <v>1</v>
-      </c>
-      <c r="N31" s="37">
-        <v>0</v>
-      </c>
-      <c r="O31" s="37">
-        <v>0</v>
-      </c>
-      <c r="P31" s="32" t="s">
+      <c r="M31" s="39">
+        <v>1</v>
+      </c>
+      <c r="N31" s="39">
+        <v>0</v>
+      </c>
+      <c r="O31" s="39">
+        <v>0</v>
+      </c>
+      <c r="P31" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="Q31" s="32">
+      <c r="Q31" s="34">
         <v>3</v>
       </c>
-      <c r="R31" s="22" t="s">
+      <c r="R31" s="24" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="32" s="32" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A32" s="32">
+    <row r="32" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A32" s="34">
         <v>310</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="32">
+      <c r="C32" s="34">
         <v>2</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="34" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="F32" s="32" t="s">
+      <c r="F32" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="G32" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H32" s="32" t="s">
+      <c r="G32" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="I32" s="37">
+      <c r="I32" s="39">
         <v>1</v>
       </c>
       <c r="J32">
@@ -8195,54 +8266,54 @@
       <c r="K32">
         <v>0</v>
       </c>
-      <c r="L32" s="32" t="s">
+      <c r="L32" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="M32" s="37">
-        <v>1</v>
-      </c>
-      <c r="N32" s="37">
-        <v>0</v>
-      </c>
-      <c r="O32" s="37">
-        <v>0</v>
-      </c>
-      <c r="P32" s="32" t="s">
+      <c r="M32" s="39">
+        <v>1</v>
+      </c>
+      <c r="N32" s="39">
+        <v>0</v>
+      </c>
+      <c r="O32" s="39">
+        <v>0</v>
+      </c>
+      <c r="P32" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="Q32" s="32">
+      <c r="Q32" s="34">
         <v>4</v>
       </c>
-      <c r="R32" s="22" t="s">
+      <c r="R32" s="24" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="33" s="32" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A33" s="32">
+    <row r="33" s="34" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A33" s="34">
         <v>311</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="34">
         <v>2</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="E33" s="32" t="s">
+      <c r="E33" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="F33" s="32" t="s">
+      <c r="F33" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="G33" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" s="32">
-        <v>0</v>
-      </c>
-      <c r="I33" s="37">
+      <c r="G33" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" s="34">
+        <v>0</v>
+      </c>
+      <c r="I33" s="39">
         <v>1</v>
       </c>
       <c r="J33">
@@ -8251,45 +8322,45 @@
       <c r="K33">
         <v>0</v>
       </c>
-      <c r="L33" s="32">
-        <v>1</v>
-      </c>
-      <c r="M33" s="37">
-        <v>1</v>
-      </c>
-      <c r="N33" s="37">
-        <v>0</v>
-      </c>
-      <c r="O33" s="37">
-        <v>0</v>
-      </c>
-      <c r="P33" s="32" t="s">
+      <c r="L33" s="34">
+        <v>1</v>
+      </c>
+      <c r="M33" s="39">
+        <v>1</v>
+      </c>
+      <c r="N33" s="39">
+        <v>0</v>
+      </c>
+      <c r="O33" s="39">
+        <v>0</v>
+      </c>
+      <c r="P33" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="34">
         <v>3</v>
       </c>
-      <c r="R33" s="22" t="s">
+      <c r="R33" s="24" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="34" s="32" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A34" s="32">
+    <row r="34" s="34" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A34" s="34">
         <v>312</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="34">
         <v>2</v>
       </c>
-      <c r="D34" s="32" t="s">
+      <c r="D34" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="G34" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" s="37">
+      <c r="G34" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="39">
         <v>1</v>
       </c>
       <c r="J34">
@@ -8298,45 +8369,45 @@
       <c r="K34">
         <v>0</v>
       </c>
-      <c r="M34" s="37">
-        <v>1</v>
-      </c>
-      <c r="N34" s="37">
-        <v>0</v>
-      </c>
-      <c r="O34" s="37">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="32">
-        <v>1</v>
-      </c>
-      <c r="R34" s="22" t="s">
+      <c r="M34" s="39">
+        <v>1</v>
+      </c>
+      <c r="N34" s="39">
+        <v>0</v>
+      </c>
+      <c r="O34" s="39">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="34">
+        <v>1</v>
+      </c>
+      <c r="R34" s="24" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="35" s="30" customFormat="1" spans="1:21">
-      <c r="A35" s="30">
+    <row r="35" s="32" customFormat="1" spans="1:21">
+      <c r="A35" s="32">
         <v>401</v>
       </c>
       <c r="B35" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="32">
         <v>2</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G35" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H35" s="30" t="s">
+      <c r="G35" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I35" s="37">
+      <c r="I35" s="39">
         <v>1</v>
       </c>
       <c r="J35">
@@ -8348,45 +8419,45 @@
       <c r="L35" t="s">
         <v>30</v>
       </c>
-      <c r="M35" s="37">
-        <v>1</v>
-      </c>
-      <c r="N35" s="37">
-        <v>0</v>
-      </c>
-      <c r="O35" s="37">
-        <v>0</v>
-      </c>
-      <c r="P35" s="30" t="s">
+      <c r="M35" s="39">
+        <v>1</v>
+      </c>
+      <c r="N35" s="39">
+        <v>0</v>
+      </c>
+      <c r="O35" s="39">
+        <v>0</v>
+      </c>
+      <c r="P35" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="30">
+      <c r="Q35" s="32">
         <v>2</v>
       </c>
     </row>
-    <row r="36" s="30" customFormat="1" spans="1:21">
-      <c r="A36" s="30">
+    <row r="36" s="32" customFormat="1" spans="1:21">
+      <c r="A36" s="32">
         <v>402</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="32">
         <v>2</v>
       </c>
-      <c r="D36" s="30" t="s">
+      <c r="D36" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="F36" s="41" t="s">
+      <c r="F36" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="G36" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H36" s="30" t="s">
+      <c r="G36" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I36" s="37">
+      <c r="I36" s="39">
         <v>1</v>
       </c>
       <c r="J36">
@@ -8398,48 +8469,48 @@
       <c r="L36" t="s">
         <v>30</v>
       </c>
-      <c r="M36" s="37">
-        <v>1</v>
-      </c>
-      <c r="N36" s="37">
-        <v>0</v>
-      </c>
-      <c r="O36" s="37">
-        <v>0</v>
-      </c>
-      <c r="P36" s="30" t="s">
+      <c r="M36" s="39">
+        <v>1</v>
+      </c>
+      <c r="N36" s="39">
+        <v>0</v>
+      </c>
+      <c r="O36" s="39">
+        <v>0</v>
+      </c>
+      <c r="P36" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="Q36" s="30">
+      <c r="Q36" s="32">
         <v>2</v>
       </c>
     </row>
-    <row r="37" s="30" customFormat="1" spans="1:21">
-      <c r="A37" s="30">
+    <row r="37" s="32" customFormat="1" spans="1:21">
+      <c r="A37" s="32">
         <v>403</v>
       </c>
       <c r="B37" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="32">
         <v>2</v>
       </c>
-      <c r="D37" s="30" t="s">
+      <c r="D37" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="30" t="s">
+      <c r="E37" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="F37" s="30" t="s">
+      <c r="F37" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="G37" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H37" s="30" t="s">
+      <c r="G37" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="I37" s="37">
+      <c r="I37" s="39">
         <v>1</v>
       </c>
       <c r="J37">
@@ -8448,80 +8519,80 @@
       <c r="K37">
         <v>0</v>
       </c>
-      <c r="L37" s="30" t="s">
+      <c r="L37" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="M37" s="37">
-        <v>1</v>
-      </c>
-      <c r="N37" s="37">
-        <v>0</v>
-      </c>
-      <c r="O37" s="37">
-        <v>0</v>
-      </c>
-      <c r="P37" s="30" t="s">
+      <c r="M37" s="39">
+        <v>1</v>
+      </c>
+      <c r="N37" s="39">
+        <v>0</v>
+      </c>
+      <c r="O37" s="39">
+        <v>0</v>
+      </c>
+      <c r="P37" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="Q37" s="30">
+      <c r="Q37" s="32">
         <v>2</v>
       </c>
     </row>
-    <row r="38" s="39" customFormat="1" spans="1:21">
-      <c r="A38" s="39">
+    <row r="38" s="41" customFormat="1" spans="1:21">
+      <c r="A38" s="41">
         <v>404</v>
       </c>
       <c r="B38" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="39">
-        <v>1</v>
-      </c>
-      <c r="D38" s="31" t="s">
+      <c r="C38" s="41">
+        <v>1</v>
+      </c>
+      <c r="D38" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E38" s="39" t="s">
+      <c r="E38" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="G38" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" s="39" t="s">
+      <c r="G38" s="41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="I38" s="39">
-        <v>1</v>
-      </c>
-      <c r="J38" s="31">
-        <v>0</v>
-      </c>
-      <c r="K38" s="31">
+      <c r="I38" s="41">
+        <v>1</v>
+      </c>
+      <c r="J38" s="33">
+        <v>0</v>
+      </c>
+      <c r="K38" s="33">
         <v>2</v>
       </c>
-      <c r="L38" s="39" t="s">
+      <c r="L38" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="M38" s="39">
-        <v>1</v>
-      </c>
-      <c r="N38" s="39">
-        <v>0</v>
-      </c>
-      <c r="O38" s="39">
-        <v>0</v>
-      </c>
-      <c r="P38" s="39" t="s">
+      <c r="M38" s="41">
+        <v>1</v>
+      </c>
+      <c r="N38" s="41">
+        <v>0</v>
+      </c>
+      <c r="O38" s="41">
+        <v>0</v>
+      </c>
+      <c r="P38" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="39">
+      <c r="Q38" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="39" s="30" customFormat="1" ht="14.25" spans="1:21">
-      <c r="A39" s="30">
+    <row r="39" s="32" customFormat="1" ht="14.25" spans="1:21">
+      <c r="A39" s="32">
         <v>405</v>
       </c>
       <c r="B39" s="15" t="s">
@@ -8539,13 +8610,13 @@
       <c r="F39" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="37" t="b">
+      <c r="G39" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="37">
+      <c r="I39" s="39">
         <v>1</v>
       </c>
       <c r="J39">
@@ -8557,13 +8628,13 @@
       <c r="L39">
         <v>3</v>
       </c>
-      <c r="M39" s="37">
-        <v>1</v>
-      </c>
-      <c r="N39" s="37">
-        <v>0</v>
-      </c>
-      <c r="O39" s="37">
+      <c r="M39" s="39">
+        <v>1</v>
+      </c>
+      <c r="N39" s="39">
+        <v>0</v>
+      </c>
+      <c r="O39" s="39">
         <v>0</v>
       </c>
       <c r="P39" t="s">
@@ -8572,37 +8643,37 @@
       <c r="Q39">
         <v>3</v>
       </c>
-      <c r="R39" s="22"/>
+      <c r="R39" s="24"/>
       <c r="S39"/>
       <c r="T39"/>
       <c r="U39"/>
     </row>
-    <row r="40" s="30" customFormat="1" spans="1:21">
-      <c r="A40" s="30">
+    <row r="40" s="32" customFormat="1" spans="1:21">
+      <c r="A40" s="32">
         <v>406</v>
       </c>
       <c r="B40" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="30">
-        <v>1</v>
-      </c>
-      <c r="D40" s="30" t="s">
+      <c r="C40" s="32">
+        <v>1</v>
+      </c>
+      <c r="D40" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="E40" s="30" t="s">
+      <c r="E40" s="32" t="s">
         <v>35</v>
       </c>
       <c r="F40" t="s">
         <v>36</v>
       </c>
-      <c r="G40" s="37" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" s="30">
-        <v>0</v>
-      </c>
-      <c r="I40" s="37">
+      <c r="G40" s="39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" s="32">
+        <v>0</v>
+      </c>
+      <c r="I40" s="39">
         <v>1</v>
       </c>
       <c r="J40">
@@ -8611,27 +8682,27 @@
       <c r="K40">
         <v>0</v>
       </c>
-      <c r="L40" s="30">
+      <c r="L40" s="32">
         <v>3</v>
       </c>
-      <c r="M40" s="37">
-        <v>1</v>
-      </c>
-      <c r="N40" s="37">
-        <v>0</v>
-      </c>
-      <c r="O40" s="37">
-        <v>0</v>
-      </c>
-      <c r="P40" s="30" t="s">
+      <c r="M40" s="39">
+        <v>1</v>
+      </c>
+      <c r="N40" s="39">
+        <v>0</v>
+      </c>
+      <c r="O40" s="39">
+        <v>0</v>
+      </c>
+      <c r="P40" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="Q40" s="30">
+      <c r="Q40" s="32">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:21">
-      <c r="A41" s="30">
+      <c r="A41" s="32">
         <v>407</v>
       </c>
       <c r="B41" s="13" t="s">
@@ -8649,13 +8720,13 @@
       <c r="F41" t="s">
         <v>87</v>
       </c>
-      <c r="G41" s="37" t="b">
+      <c r="G41" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>88</v>
       </c>
-      <c r="I41" s="37">
+      <c r="I41" s="39">
         <v>1</v>
       </c>
       <c r="J41">
@@ -8667,13 +8738,13 @@
       <c r="L41" t="s">
         <v>89</v>
       </c>
-      <c r="M41" s="37">
-        <v>1</v>
-      </c>
-      <c r="N41" s="37">
-        <v>0</v>
-      </c>
-      <c r="O41" s="37">
+      <c r="M41" s="39">
+        <v>1</v>
+      </c>
+      <c r="N41" s="39">
+        <v>0</v>
+      </c>
+      <c r="O41" s="39">
         <v>0</v>
       </c>
       <c r="P41" t="s">
@@ -8684,7 +8755,7 @@
       </c>
     </row>
     <row r="42" spans="1:21">
-      <c r="A42" s="30">
+      <c r="A42" s="32">
         <v>408</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -8702,13 +8773,13 @@
       <c r="F42" t="s">
         <v>110</v>
       </c>
-      <c r="G42" s="37" t="b">
+      <c r="G42" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>103</v>
       </c>
-      <c r="I42" s="37">
+      <c r="I42" s="39">
         <v>1</v>
       </c>
       <c r="J42">
@@ -8720,13 +8791,13 @@
       <c r="L42" t="s">
         <v>104</v>
       </c>
-      <c r="M42" s="37">
-        <v>1</v>
-      </c>
-      <c r="N42" s="37">
-        <v>0</v>
-      </c>
-      <c r="O42" s="37">
+      <c r="M42" s="39">
+        <v>1</v>
+      </c>
+      <c r="N42" s="39">
+        <v>0</v>
+      </c>
+      <c r="O42" s="39">
         <v>0</v>
       </c>
       <c r="P42" t="s">
@@ -8737,7 +8808,7 @@
       </c>
     </row>
     <row r="43" spans="1:21">
-      <c r="A43" s="30">
+      <c r="A43" s="32">
         <v>409</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -8755,13 +8826,13 @@
       <c r="F43" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="37" t="b">
+      <c r="G43" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>29</v>
       </c>
-      <c r="I43" s="37">
+      <c r="I43" s="39">
         <v>1</v>
       </c>
       <c r="J43">
@@ -8773,13 +8844,13 @@
       <c r="L43" t="s">
         <v>55</v>
       </c>
-      <c r="M43" s="37">
-        <v>1</v>
-      </c>
-      <c r="N43" s="37">
-        <v>0</v>
-      </c>
-      <c r="O43" s="37">
+      <c r="M43" s="39">
+        <v>1</v>
+      </c>
+      <c r="N43" s="39">
+        <v>0</v>
+      </c>
+      <c r="O43" s="39">
         <v>0</v>
       </c>
       <c r="P43" t="s">
@@ -8790,7 +8861,7 @@
       </c>
     </row>
     <row r="44" spans="1:21">
-      <c r="A44" s="30">
+      <c r="A44" s="32">
         <v>410</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -8808,13 +8879,13 @@
       <c r="F44" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="37" t="b">
+      <c r="G44" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>103</v>
       </c>
-      <c r="I44" s="37">
+      <c r="I44" s="39">
         <v>1</v>
       </c>
       <c r="J44">
@@ -8826,13 +8897,13 @@
       <c r="L44" t="s">
         <v>104</v>
       </c>
-      <c r="M44" s="37">
-        <v>1</v>
-      </c>
-      <c r="N44" s="37">
-        <v>0</v>
-      </c>
-      <c r="O44" s="37">
+      <c r="M44" s="39">
+        <v>1</v>
+      </c>
+      <c r="N44" s="39">
+        <v>0</v>
+      </c>
+      <c r="O44" s="39">
         <v>0</v>
       </c>
       <c r="P44" t="s">
@@ -8843,7 +8914,7 @@
       </c>
     </row>
     <row r="45" customFormat="1" spans="1:21">
-      <c r="A45" s="30">
+      <c r="A45" s="32">
         <v>411</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -8861,13 +8932,13 @@
       <c r="F45" t="s">
         <v>121</v>
       </c>
-      <c r="G45" s="37" t="b">
+      <c r="G45" s="39" t="b">
         <v>1</v>
       </c>
       <c r="H45" t="s">
         <v>29</v>
       </c>
-      <c r="I45" s="37">
+      <c r="I45" s="39">
         <v>1</v>
       </c>
       <c r="J45">
@@ -8879,13 +8950,13 @@
       <c r="L45" t="s">
         <v>43</v>
       </c>
-      <c r="M45" s="37">
-        <v>1</v>
-      </c>
-      <c r="N45" s="37">
-        <v>0</v>
-      </c>
-      <c r="O45" s="37">
+      <c r="M45" s="39">
+        <v>1</v>
+      </c>
+      <c r="N45" s="39">
+        <v>0</v>
+      </c>
+      <c r="O45" s="39">
         <v>0</v>
       </c>
       <c r="P45" t="s">
@@ -8944,10 +9015,10 @@
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:8">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>339</v>
       </c>
       <c r="C2" t="s">
@@ -8956,18 +9027,18 @@
       <c r="D2" t="s">
         <v>341</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="28" t="s">
         <v>342</v>
       </c>
-      <c r="H2" s="21" t="b">
+      <c r="H2" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3" s="13" customFormat="1" spans="1:8">
-      <c r="A3" s="21">
+      <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>343</v>
       </c>
       <c r="C3" t="s">
@@ -8976,15 +9047,15 @@
       <c r="D3" t="s">
         <v>341</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>342</v>
       </c>
-      <c r="H3" s="21" t="b">
+      <c r="H3" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="21">
+      <c r="A4" s="23">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -8996,15 +9067,15 @@
       <c r="D4" t="s">
         <v>346</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="H4" s="21" t="b">
+      <c r="H4" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="21">
+      <c r="A5" s="23">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -9016,15 +9087,15 @@
       <c r="D5" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="H5" s="21" t="b">
+      <c r="H5" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="21">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -9039,12 +9110,12 @@
       <c r="E6" t="s">
         <v>350</v>
       </c>
-      <c r="H6" s="21" t="b">
+      <c r="H6" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="21">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -9059,12 +9130,12 @@
       <c r="E7" t="s">
         <v>350</v>
       </c>
-      <c r="H7" s="21" t="b">
+      <c r="H7" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="21">
+      <c r="A8" s="23">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -9079,12 +9150,12 @@
       <c r="E8" t="s">
         <v>355</v>
       </c>
-      <c r="H8" s="21" t="b">
+      <c r="H8" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="21">
+      <c r="A9" s="23">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -9099,12 +9170,12 @@
       <c r="E9" t="s">
         <v>355</v>
       </c>
-      <c r="H9" s="21" t="b">
+      <c r="H9" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="21">
+      <c r="A10" s="23">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -9119,12 +9190,12 @@
       <c r="E10" t="s">
         <v>350</v>
       </c>
-      <c r="H10" s="21" t="b">
+      <c r="H10" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="21">
+      <c r="A11" s="23">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -9139,12 +9210,12 @@
       <c r="E11" t="s">
         <v>350</v>
       </c>
-      <c r="H11" s="21" t="b">
+      <c r="H11" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:8">
-      <c r="A12" s="21">
+      <c r="A12" s="23">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -9156,21 +9227,21 @@
       <c r="D12" t="s">
         <v>361</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="26" t="s">
         <v>362</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="H12" s="21" t="b">
+      <c r="H12" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:8">
-      <c r="A13" s="21">
+      <c r="A13" s="23">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -9182,17 +9253,17 @@
       <c r="D13" t="s">
         <v>346</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="27" t="s">
         <v>366</v>
       </c>
       <c r="F13" s="6"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="21" t="b">
+      <c r="G13" s="29"/>
+      <c r="H13" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:8">
-      <c r="A14" s="21">
+      <c r="A14" s="23">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -9204,17 +9275,17 @@
       <c r="D14" t="s">
         <v>346</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="27" t="s">
         <v>366</v>
       </c>
       <c r="F14" s="6"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="21" t="b">
+      <c r="G14" s="29"/>
+      <c r="H14" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:8">
-      <c r="A15" s="21">
+      <c r="A15" s="23">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -9226,17 +9297,17 @@
       <c r="D15" t="s">
         <v>346</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="27" t="s">
         <v>366</v>
       </c>
       <c r="F15" s="6"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="21" t="b">
+      <c r="G15" s="29"/>
+      <c r="H15" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="14.25" spans="1:8">
-      <c r="A16" s="21">
+      <c r="A16" s="23">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -9248,17 +9319,17 @@
       <c r="D16" t="s">
         <v>346</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="27" t="s">
         <v>366</v>
       </c>
       <c r="F16" s="6"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="21" t="b">
+      <c r="G16" s="29"/>
+      <c r="H16" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="21">
+      <c r="A17" s="23">
         <v>101</v>
       </c>
       <c r="B17" t="s">
@@ -9270,15 +9341,15 @@
       <c r="D17" t="s">
         <v>372</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="26" t="s">
         <v>373</v>
       </c>
-      <c r="H17" s="21" t="b">
+      <c r="H17" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="1:8">
-      <c r="A18" s="21">
+      <c r="A18" s="23">
         <v>102</v>
       </c>
       <c r="B18" t="s">
@@ -9290,21 +9361,21 @@
       <c r="D18" t="s">
         <v>376</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="27" t="s">
         <v>377</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="30" t="s">
         <v>379</v>
       </c>
-      <c r="H18" s="21" t="b">
+      <c r="H18" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="1:8">
-      <c r="A19" s="21">
+      <c r="A19" s="23">
         <v>103</v>
       </c>
       <c r="B19" t="s">
@@ -9316,21 +9387,21 @@
       <c r="D19" t="s">
         <v>361</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="26" t="s">
         <v>362</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="G19" s="27" t="s">
+      <c r="G19" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="H19" s="21" t="b">
+      <c r="H19" s="23" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="21">
+      <c r="A20" s="23">
         <v>201</v>
       </c>
       <c r="B20" t="s">
@@ -9342,15 +9413,15 @@
       <c r="D20" t="s">
         <v>341</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="E20" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="H20" s="21" t="b">
+      <c r="H20" s="23" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="1:8">
-      <c r="A21" s="21">
+      <c r="A21" s="23">
         <v>202</v>
       </c>
       <c r="B21" t="s">
@@ -9362,16 +9433,16 @@
       <c r="D21" t="s">
         <v>384</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="26" t="s">
         <v>385</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="27" t="s">
         <v>387</v>
       </c>
-      <c r="H21" s="21" t="b">
+      <c r="H21" s="23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -9417,10 +9488,10 @@
       <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>388</v>
       </c>
     </row>
@@ -9467,50 +9538,50 @@
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
-      <c r="A2" s="21">
-        <v>1</v>
-      </c>
-      <c r="B2" s="22" t="s">
+      <c r="A2" s="23">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>393</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="26" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:5">
-      <c r="A3" s="21">
+      <c r="A3" s="23">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="24" t="s">
         <v>397</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="27" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="4" ht="14.25" spans="1:5">
-      <c r="A4" s="21">
+      <c r="A4" s="23">
         <v>3</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="24" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="24" t="s">
         <v>395</v>
       </c>
       <c r="E4" t="s">
@@ -9518,225 +9589,225 @@
       </c>
     </row>
     <row r="5" ht="14.25" spans="1:5">
-      <c r="A5" s="21">
+      <c r="A5" s="23">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="27" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="6" ht="14.25" spans="1:5">
-      <c r="A6" s="21">
+      <c r="A6" s="23">
         <v>5</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="24" t="s">
         <v>403</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="E6" s="28" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="1:5">
-      <c r="A7" s="21">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="24" t="s">
         <v>405</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="27" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="8" ht="14.25" spans="1:5">
-      <c r="A8" s="21">
+      <c r="A8" s="23">
         <v>7</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="24" t="s">
         <v>407</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="27" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="1:5">
-      <c r="A9" s="21">
+      <c r="A9" s="23">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="27" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="1:5">
-      <c r="A10" s="21">
+      <c r="A10" s="23">
         <v>9</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="24" t="s">
         <v>411</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="27" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="1:5">
-      <c r="A11" s="21">
+      <c r="A11" s="23">
         <v>10</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="24" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="26" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="12" ht="14.25" spans="1:5">
-      <c r="A12" s="21">
+      <c r="A12" s="23">
         <v>11</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="27" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="13" ht="14.25" spans="1:5">
-      <c r="A13" s="21">
+      <c r="A13" s="23">
         <v>12</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="25" t="s">
         <v>414</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="26" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="14" ht="14.25" spans="1:5">
-      <c r="A14" s="21">
+      <c r="A14" s="23">
         <v>13</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="24" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="27" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="1:5">
-      <c r="A15" s="21">
+      <c r="A15" s="23">
         <v>14</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="24" t="s">
         <v>424</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="24" t="s">
         <v>425</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="26" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="21"/>
+      <c r="A16" s="23"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="21"/>
+      <c r="A17" s="23"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="21"/>
+      <c r="A18" s="23"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="21"/>
+      <c r="A19" s="23"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="21"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="3"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="21"/>
+      <c r="A21" s="23"/>
       <c r="B21" s="3"/>
-      <c r="E21" s="25"/>
+      <c r="E21" s="27"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="21"/>
+      <c r="A22" s="23"/>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="21"/>
+      <c r="A23" s="23"/>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="21"/>
-      <c r="E24" s="25"/>
+      <c r="A24" s="23"/>
+      <c r="E24" s="27"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="21"/>
+      <c r="A25" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9762,7 +9833,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C325"/>
+  <dimension ref="A1:C330"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.875" customWidth="1"/>
@@ -13337,6 +13408,46 @@
       </c>
       <c r="B325" s="5" t="s">
         <v>1315</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3">
+      <c r="A326" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B326" s="21" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3">
+      <c r="A327" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B327" s="22" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3">
+      <c r="A328" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B328" s="22" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="329" ht="14.25" spans="1:3">
+      <c r="A329" s="22" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B329" s="21" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="330" ht="14.25" spans="1:3">
+      <c r="A330" s="22" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B330" s="21" t="s">
+        <v>1325</v>
       </c>
     </row>
   </sheetData>
@@ -13380,25 +13491,25 @@
       </c>
     </row>
     <row r="2" s="13" customFormat="1" spans="1:7">
-      <c r="A2" s="32">
+      <c r="A2" s="34">
         <v>4</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="34">
         <v>20</v>
       </c>
-      <c r="D2" s="32">
-        <v>1</v>
-      </c>
-      <c r="E2" s="21">
-        <v>1</v>
-      </c>
-      <c r="F2" s="21">
-        <v>0</v>
-      </c>
-      <c r="G2" s="21">
+      <c r="D2" s="34">
+        <v>1</v>
+      </c>
+      <c r="E2" s="23">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23">
+        <v>0</v>
+      </c>
+      <c r="G2" s="23">
         <v>200</v>
       </c>
     </row>
@@ -13421,7 +13532,7 @@
       <c r="F3">
         <v>301</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="23">
         <v>100</v>
       </c>
     </row>
@@ -13444,7 +13555,7 @@
       <c r="F4">
         <v>302</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="23">
         <v>100</v>
       </c>
     </row>
@@ -13467,7 +13578,7 @@
       <c r="F5">
         <v>302</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="23">
         <v>110</v>
       </c>
     </row>
@@ -13490,7 +13601,7 @@
       <c r="F6">
         <v>308</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="23">
         <v>200</v>
       </c>
     </row>
@@ -13513,7 +13624,7 @@
       <c r="F7">
         <v>306</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="23">
         <v>90</v>
       </c>
     </row>
@@ -13536,7 +13647,7 @@
       <c r="F8">
         <v>307</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="23">
         <v>200</v>
       </c>
     </row>
@@ -13559,7 +13670,7 @@
       <c r="F9">
         <v>309</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="23">
         <v>100</v>
       </c>
     </row>
@@ -13582,7 +13693,7 @@
       <c r="F10">
         <v>309</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="23">
         <v>90</v>
       </c>
     </row>
@@ -13605,7 +13716,7 @@
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="23">
         <v>0</v>
       </c>
     </row>
@@ -13628,7 +13739,7 @@
       <c r="F12">
         <v>311</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="23">
         <v>180</v>
       </c>
     </row>
@@ -13651,7 +13762,7 @@
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="23">
         <v>0</v>
       </c>
     </row>
@@ -13674,7 +13785,7 @@
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="23">
         <v>100</v>
       </c>
     </row>
@@ -13697,7 +13808,7 @@
       <c r="F15">
         <v>310</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="23">
         <v>180</v>
       </c>
     </row>
@@ -13720,7 +13831,7 @@
       <c r="F16">
         <v>301</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="23">
         <v>110</v>
       </c>
     </row>
@@ -13743,288 +13854,288 @@
       <c r="F17">
         <v>307</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="23">
         <v>150</v>
       </c>
     </row>
-    <row r="18" s="34" customFormat="1" spans="1:7">
-      <c r="A18" s="34">
+    <row r="18" s="36" customFormat="1" spans="1:7">
+      <c r="A18" s="36">
         <v>301</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="34">
+      <c r="C18" s="36">
         <v>50</v>
       </c>
-      <c r="D18" s="34">
-        <v>0</v>
-      </c>
-      <c r="E18" s="34">
+      <c r="D18" s="36">
+        <v>0</v>
+      </c>
+      <c r="E18" s="36">
         <v>400</v>
       </c>
-      <c r="F18" s="34">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36">
+      <c r="F18" s="36">
+        <v>0</v>
+      </c>
+      <c r="G18" s="38">
         <v>200</v>
       </c>
     </row>
-    <row r="19" s="34" customFormat="1" spans="1:7">
-      <c r="A19" s="34">
+    <row r="19" s="36" customFormat="1" spans="1:7">
+      <c r="A19" s="36">
         <v>302</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="37" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="36">
         <v>25</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="36">
         <v>9</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="36">
         <v>100</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="36">
         <v>303</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="38">
         <v>120</v>
       </c>
     </row>
-    <row r="20" s="34" customFormat="1" spans="1:7">
-      <c r="A20" s="34">
+    <row r="20" s="36" customFormat="1" spans="1:7">
+      <c r="A20" s="36">
         <v>303</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="36">
         <v>20</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="36">
         <v>3</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="36">
         <v>50</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="36">
         <v>301</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="38">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="34" customFormat="1" spans="1:7">
-      <c r="A21" s="34">
+    <row r="21" s="36" customFormat="1" spans="1:7">
+      <c r="A21" s="36">
         <v>304</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="36">
         <v>30</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="36">
         <v>11</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="36">
         <v>300</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="36">
         <v>301</v>
       </c>
-      <c r="G21" s="36">
+      <c r="G21" s="38">
         <v>150</v>
       </c>
     </row>
-    <row r="22" s="34" customFormat="1" spans="1:7">
-      <c r="A22" s="34">
+    <row r="22" s="36" customFormat="1" spans="1:7">
+      <c r="A22" s="36">
         <v>305</v>
       </c>
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="36">
         <v>25</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="36">
         <v>8</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="36">
         <v>100</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="36">
         <v>303</v>
       </c>
-      <c r="G22" s="36">
+      <c r="G22" s="38">
         <v>120</v>
       </c>
     </row>
-    <row r="23" s="34" customFormat="1" spans="1:7">
-      <c r="A23" s="34">
+    <row r="23" s="36" customFormat="1" spans="1:7">
+      <c r="A23" s="36">
         <v>306</v>
       </c>
-      <c r="B23" s="35" t="s">
+      <c r="B23" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="36">
         <v>35</v>
       </c>
-      <c r="D23" s="34">
-        <v>0</v>
-      </c>
-      <c r="E23" s="34">
+      <c r="D23" s="36">
+        <v>0</v>
+      </c>
+      <c r="E23" s="36">
         <v>200</v>
       </c>
-      <c r="F23" s="34">
-        <v>0</v>
-      </c>
-      <c r="G23" s="36">
+      <c r="F23" s="36">
+        <v>0</v>
+      </c>
+      <c r="G23" s="38">
         <v>150</v>
       </c>
     </row>
-    <row r="24" s="34" customFormat="1" spans="1:7">
-      <c r="A24" s="34">
+    <row r="24" s="36" customFormat="1" spans="1:7">
+      <c r="A24" s="36">
         <v>307</v>
       </c>
-      <c r="B24" s="35" t="s">
+      <c r="B24" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="36">
         <v>35</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="36">
         <v>12</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="36">
         <v>150</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="36">
         <v>302</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="38">
         <v>150</v>
       </c>
     </row>
-    <row r="25" s="34" customFormat="1" spans="1:7">
-      <c r="A25" s="34">
+    <row r="25" s="36" customFormat="1" spans="1:7">
+      <c r="A25" s="36">
         <v>308</v>
       </c>
-      <c r="B25" s="35" t="s">
+      <c r="B25" s="37" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="36">
         <v>35</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="36">
         <v>12</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="36">
         <v>150</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="36">
         <v>302</v>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="38">
         <v>150</v>
       </c>
     </row>
-    <row r="26" s="34" customFormat="1" spans="1:7">
-      <c r="A26" s="34">
+    <row r="26" s="36" customFormat="1" spans="1:7">
+      <c r="A26" s="36">
         <v>309</v>
       </c>
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="36">
         <v>20</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="36">
         <v>10</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="36">
         <v>80</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="36">
         <v>306</v>
       </c>
-      <c r="G26" s="36">
+      <c r="G26" s="38">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="34" customFormat="1" spans="1:7">
-      <c r="A27" s="34">
+    <row r="27" s="36" customFormat="1" spans="1:7">
+      <c r="A27" s="36">
         <v>310</v>
       </c>
-      <c r="B27" s="35" t="s">
+      <c r="B27" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="36">
         <v>30</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="36">
         <v>10</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="36">
         <v>120</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="36">
         <v>309</v>
       </c>
-      <c r="G27" s="36">
+      <c r="G27" s="38">
         <v>120</v>
       </c>
     </row>
-    <row r="28" s="34" customFormat="1" spans="1:7">
-      <c r="A28" s="34">
+    <row r="28" s="36" customFormat="1" spans="1:7">
+      <c r="A28" s="36">
         <v>311</v>
       </c>
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="36">
         <v>30</v>
       </c>
-      <c r="D28" s="34">
+      <c r="D28" s="36">
         <v>10</v>
       </c>
-      <c r="E28" s="34">
+      <c r="E28" s="36">
         <v>120</v>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="36">
         <v>309</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="38">
         <v>120</v>
       </c>
     </row>
-    <row r="29" s="34" customFormat="1" spans="1:7">
-      <c r="A29" s="34">
+    <row r="29" s="36" customFormat="1" spans="1:7">
+      <c r="A29" s="36">
         <v>312</v>
       </c>
-      <c r="B29" s="35" t="s">
+      <c r="B29" s="37" t="s">
         <v>223</v>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="36">
         <v>15</v>
       </c>
-      <c r="D29" s="34">
+      <c r="D29" s="36">
         <v>2</v>
       </c>
-      <c r="E29" s="34">
+      <c r="E29" s="36">
         <v>15</v>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="36">
         <v>306</v>
       </c>
-      <c r="G29" s="36">
+      <c r="G29" s="38">
         <v>80</v>
       </c>
     </row>
-    <row r="30" s="34" customFormat="1" spans="1:7">
-      <c r="B30" s="35"/>
+    <row r="30" s="36" customFormat="1" spans="1:7">
+      <c r="B30" s="37"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14067,10 +14178,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="32">
+      <c r="A2" s="34">
         <v>3</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="34" t="s">
         <v>229</v>
       </c>
       <c r="C2">
@@ -14087,10 +14198,10 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="32">
+      <c r="A3" s="34">
         <v>4</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="34" t="s">
         <v>200</v>
       </c>
       <c r="C3">
@@ -14276,10 +14387,10 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="32">
+      <c r="A12" s="34">
         <v>309</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="34" t="s">
         <v>168</v>
       </c>
       <c r="C12">
@@ -14296,10 +14407,10 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="32">
+      <c r="A13" s="34">
         <v>310</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="34" t="s">
         <v>173</v>
       </c>
       <c r="C13">
@@ -14316,10 +14427,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="32">
+      <c r="A14" s="34">
         <v>311</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="34" t="s">
         <v>177</v>
       </c>
       <c r="C14">
@@ -14339,10 +14450,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="32">
+      <c r="A15" s="34">
         <v>312</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="34" t="s">
         <v>223</v>
       </c>
       <c r="C15">
@@ -14359,8 +14470,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14433,29 +14544,29 @@
         <v>238</v>
       </c>
     </row>
-    <row r="3" s="31" customFormat="1" spans="1:8">
-      <c r="A3" s="31">
+    <row r="3" s="33" customFormat="1" spans="1:8">
+      <c r="A3" s="33">
         <v>202</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C3" s="31" t="s">
+      <c r="C3" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="31">
-        <v>0</v>
-      </c>
-      <c r="F3" s="31">
+      <c r="E3" s="33">
+        <v>0</v>
+      </c>
+      <c r="F3" s="33">
         <v>0.8</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="33" t="s">
         <v>241</v>
       </c>
     </row>
@@ -14845,34 +14956,34 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" s="31" customFormat="1" spans="1:8">
-      <c r="A20" s="33">
+    <row r="20" s="33" customFormat="1" spans="1:8">
+      <c r="A20" s="35">
         <v>404</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="E20" s="31">
-        <v>0</v>
-      </c>
-      <c r="F20" s="31">
+      <c r="E20" s="33">
+        <v>0</v>
+      </c>
+      <c r="F20" s="33">
         <v>0.8</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="33" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="29">
+      <c r="A21" s="31">
         <v>405</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -14898,7 +15009,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="29">
+      <c r="A22" s="31">
         <v>406</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -14924,7 +15035,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="30">
+      <c r="A23" s="32">
         <v>407</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -14950,7 +15061,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="30">
+      <c r="A24" s="32">
         <v>408</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -14976,7 +15087,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="30">
+      <c r="A25" s="32">
         <v>409</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -15002,7 +15113,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="30">
+      <c r="A26" s="32">
         <v>410</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -15028,7 +15139,7 @@
       </c>
     </row>
     <row r="27" customFormat="1" spans="1:8">
-      <c r="A27" s="30">
+      <c r="A27" s="32">
         <v>411</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -15094,68 +15205,68 @@
     <col min="41" max="41" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" spans="1:21">
-      <c r="A1" s="31" t="s">
+    <row r="1" s="33" customFormat="1" spans="1:21">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="G1" s="31" t="s">
+      <c r="G1" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="I1" s="31" t="s">
+      <c r="I1" s="33" t="s">
         <v>282</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="L1" s="31" t="s">
+      <c r="L1" s="33" t="s">
         <v>285</v>
       </c>
-      <c r="M1" s="31" t="s">
+      <c r="M1" s="33" t="s">
         <v>286</v>
       </c>
-      <c r="N1" s="31" t="s">
+      <c r="N1" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="O1" s="31" t="s">
+      <c r="O1" s="33" t="s">
         <v>288</v>
       </c>
-      <c r="P1" s="31" t="s">
+      <c r="P1" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="Q1" s="31" t="s">
+      <c r="Q1" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="T1" s="31" t="s">
+      <c r="T1" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="U1" s="31" t="s">
+      <c r="U1" s="33" t="s">
         <v>294</v>
       </c>
     </row>
@@ -16027,7 +16138,7 @@
       </c>
     </row>
     <row r="17" spans="1:21">
-      <c r="A17" s="32">
+      <c r="A17" s="34">
         <v>301</v>
       </c>
       <c r="B17" s="11" t="s">
@@ -16086,7 +16197,7 @@
       </c>
     </row>
     <row r="18" spans="1:21">
-      <c r="A18" s="32">
+      <c r="A18" s="34">
         <v>302</v>
       </c>
       <c r="B18" s="11" t="s">
@@ -16145,7 +16256,7 @@
       </c>
     </row>
     <row r="19" spans="1:21">
-      <c r="A19" s="32">
+      <c r="A19" s="34">
         <v>303</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -16204,7 +16315,7 @@
       </c>
     </row>
     <row r="20" spans="1:21">
-      <c r="A20" s="32">
+      <c r="A20" s="34">
         <v>304</v>
       </c>
       <c r="B20" s="11" t="s">
@@ -16325,7 +16436,7 @@
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" s="32">
+      <c r="A22" s="34">
         <v>306</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -16384,7 +16495,7 @@
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" s="32">
+      <c r="A23" s="34">
         <v>307</v>
       </c>
       <c r="B23" s="11" t="s">
@@ -16443,7 +16554,7 @@
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" s="32">
+      <c r="A24" s="34">
         <v>308</v>
       </c>
       <c r="B24" s="11" t="s">
@@ -16502,7 +16613,7 @@
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="A25" s="32">
+      <c r="A25" s="34">
         <v>309</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -16561,7 +16672,7 @@
       </c>
     </row>
     <row r="26" spans="1:21">
-      <c r="A26" s="32">
+      <c r="A26" s="34">
         <v>310</v>
       </c>
       <c r="B26" s="11" t="s">
@@ -16620,7 +16731,7 @@
       </c>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" s="32">
+      <c r="A27" s="34">
         <v>311</v>
       </c>
       <c r="B27" s="11" t="s">
@@ -16679,7 +16790,7 @@
       </c>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" s="32">
+      <c r="A28" s="34">
         <v>312</v>
       </c>
       <c r="B28" s="11" t="s">
@@ -16912,7 +17023,7 @@
       </c>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" s="29">
+      <c r="A32" s="31">
         <v>404</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -16974,7 +17085,7 @@
       </c>
     </row>
     <row r="33" spans="1:21">
-      <c r="A33" s="29">
+      <c r="A33" s="31">
         <v>405</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -17030,7 +17141,7 @@
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="29">
+      <c r="A34" s="31">
         <v>406</v>
       </c>
       <c r="B34" s="13" t="s">
@@ -17086,7 +17197,7 @@
       </c>
     </row>
     <row r="35" spans="1:21">
-      <c r="A35" s="30">
+      <c r="A35" s="32">
         <v>407</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -17142,7 +17253,7 @@
       </c>
     </row>
     <row r="36" spans="1:21">
-      <c r="A36" s="30">
+      <c r="A36" s="32">
         <v>408</v>
       </c>
       <c r="B36" s="13" t="s">
@@ -17201,7 +17312,7 @@
       </c>
     </row>
     <row r="37" spans="1:21">
-      <c r="A37" s="30">
+      <c r="A37" s="32">
         <v>409</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -17260,7 +17371,7 @@
       </c>
     </row>
     <row r="38" spans="1:21">
-      <c r="A38" s="30">
+      <c r="A38" s="32">
         <v>410</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -17310,7 +17421,7 @@
       </c>
     </row>
     <row r="39" customFormat="1" spans="1:21">
-      <c r="A39" s="30">
+      <c r="A39" s="32">
         <v>411</v>
       </c>
       <c r="B39" s="13" t="s">
@@ -17472,7 +17583,7 @@
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="29">
+      <c r="A9" s="31">
         <v>404</v>
       </c>
       <c r="B9" t="s">
@@ -17483,7 +17594,7 @@
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="29">
+      <c r="A10" s="31">
         <v>405</v>
       </c>
       <c r="B10" t="s">
@@ -17494,7 +17605,7 @@
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="29">
+      <c r="A11" s="31">
         <v>406</v>
       </c>
       <c r="B11" t="s">
@@ -17505,7 +17616,7 @@
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="30">
+      <c r="A12" s="32">
         <v>407</v>
       </c>
       <c r="B12" t="s">
@@ -17516,7 +17627,7 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="30">
+      <c r="A13" s="32">
         <v>408</v>
       </c>
       <c r="B13" t="s">
@@ -17527,7 +17638,7 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="30">
+      <c r="A14" s="32">
         <v>409</v>
       </c>
       <c r="B14" t="s">
@@ -17538,7 +17649,7 @@
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="30">
+      <c r="A15" s="32">
         <v>410</v>
       </c>
       <c r="B15" t="s">
@@ -17549,7 +17660,7 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="30">
+      <c r="A16" s="32">
         <v>411</v>
       </c>
       <c r="B16" t="s">

--- a/Iocp20Coroutine/表/单位.xlsx
+++ b/Iocp20Coroutine/表/单位.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1820" uniqueCount="1348">
   <si>
     <t>类型</t>
   </si>
@@ -1936,7 +1936,7 @@
     <t>Viewport</t>
   </si>
   <si>
-    <t>Moss Vines</t>
+    <t>Mossy Vines</t>
   </si>
   <si>
     <t>Square Pillar</t>
@@ -2032,7 +2032,7 @@
     <t>Mimic Source</t>
   </si>
   <si>
-    <t>Giant Flesh Mass</t>
+    <t>Taisui</t>
   </si>
   <si>
     <t>Rifle Bug Mutant</t>
@@ -2086,7 +2086,7 @@
     <t>缺少</t>
   </si>
   <si>
-    <t>Missing</t>
+    <t>Insufficient</t>
   </si>
   <si>
     <t>Key已删除</t>
@@ -2138,7 +2138,7 @@
     <t>遭到攻击</t>
   </si>
   <si>
-    <t>Under Attack</t>
+    <t xml:space="preserve"> is Under Attack</t>
   </si>
   <si>
     <t>Key跟随</t>
@@ -2608,7 +2608,7 @@
     <t>听说工程车还可以造&lt;color=#a0ff50&gt;地堡&lt;/color&gt;和&lt;color=#a0ff50&gt;炮台&lt;/color&gt;，我也要试试。</t>
   </si>
   <si>
-    <t>I heard Construction Vehicles can also build &lt;color=#a0ff50&gt; Bunkers&lt;/color&gt; and &lt;color=#a0ff50&gt; Gun Turrets&lt;/color&gt;. I want to give that a shot too.</t>
+    <t>I heard Construction Vehicles can also build &lt;color=#a0ff50&gt; Bunkers&lt;/color&gt; and &lt;color=#a0ff50&gt; Turrets&lt;/color&gt;. I want to give that a shot too.</t>
   </si>
   <si>
     <t>Key造完基地应该……</t>
@@ -3096,7 +3096,33 @@
     <t>Insufficient Crystal Ore. Unlocking unavailable</t>
   </si>
   <si>
-    <t>Key蜕变进度{}/{}</t>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>蜕变进度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}/{}</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3173,6 +3199,26 @@
   </si>
   <si>
     <t>Proceed to Construction Site</t>
+  </si>
+  <si>
+    <t>Key走向{}</t>
+  </si>
+  <si>
+    <r>
+      <t>走向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Move toward {}</t>
   </si>
   <si>
     <t>Key造完了</t>
@@ -3267,7 +3313,7 @@
     </r>
   </si>
   <si>
-    <t>You have been assigned a squad of anti-air units. First &lt;color=#a0ff50&gt; box-select&lt;/color&gt; all of them, then click the empty ground near the flying drones to order an attack. We hold the advantage!</t>
+    <t>You have been assigned a squad of anti-air units. First &lt;color=#a0ff50&gt; box-select&lt;/color&gt; all of them, then click the empty ground near the Flying Bugs to order an attack. We hold the advantage!</t>
   </si>
   <si>
     <t>Key先框选全部防空兵……</t>
@@ -3276,7 +3322,7 @@
     <t>先&lt;color=#a0ff50&gt;框选全部防空兵&lt;/color&gt;，然后点击飞虫附近的空白地面，进攻飞虫。优势在我！</t>
   </si>
   <si>
-    <t>First &lt;color=#a0ff50&gt; box-select all anti-air units&lt;/color&gt;, then click the empty ground near the flying drones to order an attack. We hold the advantage!</t>
+    <t>First &lt;color=#a0ff50&gt; box-select all anti-air units&lt;/color&gt;, then click the empty ground near the Flying Bugs to order an attack. We hold the advantage!</t>
   </si>
   <si>
     <t>Key防空战胜利……</t>
@@ -3312,7 +3358,7 @@
     <t>敌方布置了防空兵，我方飞虫损失惨重。</t>
   </si>
   <si>
-    <t>The enemy has deployed anti-air units, and our flying drones are sustaining heavy casualties.</t>
+    <t>The enemy has deployed anti-air units, and our Flying Bugs are sustaining heavy casualties.</t>
   </si>
   <si>
     <t>Key防空兵移动缓慢……</t>
@@ -3321,7 +3367,7 @@
     <t>防空兵&lt;color=#a0ff50&gt;移动缓慢，攻击前摇时间长，前摇过程中炸点不可改变位置&lt;/color&gt;。只要手动操作飞虫避开空中炸点再找机会攻击，就有希望击败他们。</t>
   </si>
   <si>
-    <t>Anti-air units &lt;color=#a0ff50&gt;move slowly and have a long attack wind-up. Once the wind-up initiates, the blast point cannot be repositioned&lt;/color&gt;. You can defeat them by manually maneuvering your flying drones to dodge the airborne blast points, then seizing the chance to counterattack.</t>
+    <t>Anti-air units &lt;color=#a0ff50&gt;move slowly and have a long attack wind-up. Once the wind-up initiates, the blast point cannot be repositioned&lt;/color&gt;. You can defeat them by manually maneuvering your Flying Bugs to dodge the airborne blast points, then seizing the chance to counterattack.</t>
   </si>
   <si>
     <t>Key具体如何操作呢？</t>
@@ -3339,7 +3385,7 @@
     <t>所有飞虫在后方安全地区聚拢，然后派一只飞虫用&lt;color=#a0ff50&gt;强行走&lt;/color&gt;吸引一个防空兵过来，群起而狙之。然后等飞虫自动恢复血量。如此反复，直至击败所有防空兵。</t>
   </si>
   <si>
-    <t>Gather all flying drones in a safe rear area. Then send a single drone to &lt;color=#a0ff50&gt;force-march&lt;/color&gt; and lure one anti-air unit over, then focus fire to take it down. After that, wait for the flying drones to regenerate HP automatically. Repeat this process until all enemy anti-air units are eliminated.</t>
+    <t>Gather all Flying Bugs in a safe rear area. Then send a single drone to &lt;color=#a0ff50&gt;force-march&lt;/color&gt; and lure one anti-air unit over, then focus fire to take it down. After that, wait for the Flying Bugs to regenerate HP automatically. Repeat this process until all enemy anti-air units are eliminated.</t>
   </si>
   <si>
     <t>Key好的，我试试看。</t>
@@ -3384,7 +3430,7 @@
     <t>您失败了！您需要继续练习反防空技巧。</t>
   </si>
   <si>
-    <t>You lose! You need more practice with anti-AA counter tactics.</t>
+    <t>You lose! You need more practice with anti-anti-air warfare counter tactics.</t>
   </si>
   <si>
     <t>Key再打防空战……</t>
@@ -3393,7 +3439,7 @@
     <t>可以点右上角&lt;color=#a0ff50&gt;离开场景&lt;/color&gt;离开，然后再次点击&lt;color=#a0ff50&gt;反防空战&lt;/color&gt;，就可以重新来过。</t>
   </si>
   <si>
-    <t>You can click &lt;color=#a0ff50&gt;Exit Scene&lt;/color&gt; in the top-right corner to leave, then click &lt;color=#a0ff50&gt;Anti-AA Counter Battle&lt;/color&gt; again to restart the mission.</t>
+    <t>You can click &lt;color=#a0ff50&gt;Leave Scene&lt;/color&gt; in the top-right corner to leave, then click &lt;color=#a0ff50&gt;Anti-Anti-Air Warfare&lt;/color&gt; again to restart the mission.</t>
   </si>
   <si>
     <t>Key敌方飞虫进攻我方炮台……</t>
@@ -3402,7 +3448,7 @@
     <t>，敌方飞虫进攻我方炮台，我方损失惨重。</t>
   </si>
   <si>
-    <t>, Enemy flying drones are assaulting our artillery emplacements; we are sustaining heavy casualties.</t>
+    <t>, Enemy Flying Bugs are assaulting our artillery emplacements; we are sustaining heavy casualties.</t>
   </si>
   <si>
     <t>Key没有吧？</t>
@@ -3429,7 +3475,7 @@
     <t>敌方飞虫进攻我方炮台（此过程您无需操作）</t>
   </si>
   <si>
-    <t>Enemy flying drones are assaulting our artillery emplacements (no action required on your part during this phase)</t>
+    <t>Enemy Flying Bugs are assaulting our artillery emplacements (no action required on your part during this phase)</t>
   </si>
   <si>
     <t>Key传授闪避技巧……</t>
@@ -3609,7 +3655,7 @@
     </r>
   </si>
   <si>
-    <t>, you have mastered the evasion strategy for riflemen against tanks.Remember: when facing a stronger enemy, evasion is far more important than a head-on confrontation. Watch closely for the blast point visual cue and master the Force March maneuver to dodge the tank’s blasts, and your riflemen will survive longer on this perilous battlefield.</t>
+    <t>, you have mastered the evasion strategy for riflemen against tanks.Remember: when facing a stronger enemy, evasion is far more important than a head-on confrontation. Watch closely for the blast point visual cue and master the Force Move maneuver to dodge the tank’s blasts, and your riflemen will survive longer on this perilous battlefield.</t>
   </si>
   <si>
     <t>Key弟子谨记教诲心法……</t>
@@ -4405,7 +4451,7 @@
     <t>此局没有工程车。&lt;color=#a0ff50&gt;右下方的敌方虫巢防守薄弱&lt;/color&gt;。</t>
   </si>
   <si>
-    <t>No Drones available in this mission. &lt;color=#a0ff50&gt;The enemy Hive in the bottom-right corner is lightly defended&lt;/color&gt;.</t>
+    <t>No Construction Vehicle available in this mission. &lt;color=#a0ff50&gt;The enemy Hive in the bottom-right corner is lightly defended&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key谢谢你救了我们。</t>
@@ -4504,7 +4550,7 @@
     <t>，有一个好消息，我们的幼虫经过千万次的模仿，基本掌握了拟态复制人类三色坦克的方法。</t>
   </si>
   <si>
-    <t>Good news: After thousands of iterations, our Larvae have mastered mimicking human Tri-Color Tank technology.</t>
+    <t>,Good news: After thousands of iterations, our Larvae have mastered mimicking human Tri-Color Tank technology.</t>
   </si>
   <si>
     <t>Key还有坏消息……</t>
@@ -4522,7 +4568,7 @@
     <t>是的，蜕变出的第一批&lt;color = #a0ff50&gt;绿色坦克&lt;/color&gt;的虫巢已遭人类攻占。</t>
   </si>
   <si>
-    <t>Regrettably, the Hive producing our first batch of &lt;color=#a0ff50&gt;Green Tanks&lt;/color&gt; has been captured by human forces.</t>
+    <t>Regrettably, the Hive producing our first batch of &lt;color=#a0ff50&gt; Green Tanks&lt;/color&gt; has been captured by human forces.</t>
   </si>
   <si>
     <t>Key绿色坦克打不过……</t>
@@ -4639,7 +4685,7 @@
     <t>，可以让&lt;color=#a0ff50&gt;房虫&lt;/color&gt;运送战斗单位越过障碍物绕到炮台后方，实施空降作战。</t>
   </si>
   <si>
-    <t>You can use &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; to transport combat units over obstacles and deploy them behind enemy Turrets for airborne assaults.</t>
+    <t>,You can use &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; to transport combat units over obstacles and deploy them behind enemy Turrets for airborne assaults.</t>
   </si>
   <si>
     <t>Key近战虫进房虫……</t>
@@ -4648,7 +4694,7 @@
     <t>请先点击选中&lt;color=#a0ff50&gt;近战虫&lt;/color&gt;，再点击一次&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，可让近战虫进入房虫。</t>
   </si>
   <si>
-    <t>First, select the &lt;color=#a0ff50&gt;Melee Bugs&lt;/color&gt;. Then, click on a &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; to load the Melee Bugs inside.</t>
+    <t>First, select the &lt;color=#a0ff50&gt; Melee Bug&lt;/color&gt;. Then, click on a &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; to load the Melee Bugs inside.</t>
   </si>
   <si>
     <t>Key放下近战虫……</t>
@@ -4657,7 +4703,7 @@
     <t>很好，请点击选中&lt;color=#a0ff50&gt;房虫&lt;/color&gt;，让它跃过左侧的障碍物到达左上角的敌方建筑附近，然后点击下方&lt;color=#a0ff50&gt;离开房虫&lt;/color&gt;图标，放下近战虫攻击敌方建筑</t>
   </si>
   <si>
-    <t>Excellent work. Now select the &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; and order it to jump over the obstacles on the left, moving near the enemy structures in the top-left corner. Next, click the &lt;color=#a0ff50&gt;Disembark&lt;/color&gt; icon below to unload the Melee Bugs and launch an attack on the enemy buildings.</t>
+    <t>Excellent work. Now select the &lt;color=#a0ff50&gt; PopuLifter Drone&lt;/color&gt; and order it to jump over the obstacles on the left, moving near the enemy structures in the top-left corner. Next, click the &lt;color=#a0ff50&gt; Disembark&lt;/color&gt; icon below to unload the Melee Bugs and launch an attack on the enemy structures.</t>
   </si>
   <si>
     <t>Key要远离敌方炮台。</t>
@@ -4825,7 +4871,7 @@
     <t>这次训练，你将了解&lt;color=#a0ff50&gt;绿色坦克&lt;/color&gt;、&lt;color=#a0ff50&gt;飞虫&lt;/color&gt;的用法。</t>
   </si>
   <si>
-    <t>In this training, you will learn how to use the &lt;color=#a0ff50&gt;Green Tank&lt;/color&gt; and &lt;color=#a0ff50&gt;Flying Bug&lt;/color&gt;.</t>
+    <t>In this training, you will learn how to use the &lt;color=#a0ff50&gt; Green Tank&lt;/color&gt; and &lt;color=#a0ff50&gt; Flying Bug&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key选近战虫进攻炮台……</t>
@@ -4983,7 +5029,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">  Always monitor your Flying Bugs' health. Their vitality is inherently low. When their health drops below 50%, immediately activate the &lt;color=#a0ff50&gt;Force Move&lt;/color&gt; ability to retreat them to the &lt;color=#a0ff50&gt;Mossy Vines&lt;/color&gt;.
+    <t xml:space="preserve">  Always monitor your Flying Bugs' health. Their vitality is inherently low. When their health drops below 50%, immediately activate the &lt;color=#a0ff50&gt; Force Move&lt;/color&gt; ability to retreat them to the &lt;color=#a0ff50&gt;Mossy Vines&lt;/color&gt;.
   On the Mossy Vines, Flying Bugs recover health rapidly. Once fully healed, click the empty area near the Turret to resume the attack. Repeat this cycle to overcome a stronger foe with a weaker force.
   Remember this core principle: &lt;color=#a0ff50&gt;Health Below 50% → Force Move to Mossy Vines → Regenerate Full Health → Click Turret Vicinity to Attack Again&lt;/color&gt;. This is the way of survival for Flying Bugs!</t>
   </si>
@@ -5012,7 +5058,7 @@
     <t xml:space="preserve"> 少侠，飞虫已败。切记，江湖险恶，保命为先。善用苔蔓调息回血，方能在战场上立于不败之地。</t>
   </si>
   <si>
-    <t>Young warrior, your Flying Bugs have been defeated. Remember—danger lurks everywhere in this battlefield. Survival comes first. Master the use of Mossy Vines for health regeneration, and you will stand invincible in combat.</t>
+    <t xml:space="preserve"> Young warrior, your Flying Bugs have been defeated. Remember—danger lurks everywhere in this battlefield. Survival comes first. Master the use of Mossy Vines for health regeneration, and you will stand invincible in combat.</t>
   </si>
   <si>
     <t>Key少侠已领悟飞虫的保命心法……</t>
@@ -5111,7 +5157,7 @@
     <t>请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;按钮，再点击空白地面，工虫会在10秒内变异为虫巢</t>
   </si>
   <si>
-    <t>Click the &lt;color=#a0ff50&gt;Building Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Hive&lt;/color&gt; button, then click an empty spot on the ground. Worker Bugs will mutate into a Hive within 10 seconds.</t>
+    <t>Click the &lt;color=#a0ff50&gt;Structures&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Hive&lt;/color&gt; button, then click an empty spot on the ground. Worker Drones will mutate into a Hive within 10 seconds.</t>
   </si>
   <si>
     <t>Key虫巢周围会形成……</t>
@@ -5122,7 +5168,7 @@
   </si>
   <si>
     <t>Excellent. &lt;color=#a0ff50&gt;Mossy Vines&lt;/color&gt; will spread around the Hive. Insectoid units on the Mossy Vines gain increased movement speed and health regeneration rate. &lt;color=#a0ff50&gt;Always engage enemy units on the Mossy Vines whenever possible&lt;/color&gt;.
-Once the Hive produces &lt;color=#a0ff50&gt;Larvae&lt;/color&gt;, click the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Worker Bug&lt;/color&gt; button to morph the Larvae into Worker Bugs.</t>
+Once the Hive produces &lt;color=#a0ff50&gt;Larvae&lt;/color&gt;, click the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Worker Drone&lt;/color&gt; button to morph the Larvae into Worker Drones.</t>
   </si>
   <si>
     <t>Key现在您有工虫了……</t>
@@ -5131,7 +5177,7 @@
     <t>现在您有工虫了，点击选中您的&lt;color=#a0ff50&gt;工虫&lt;/color&gt;，再点击空旷地面，命令它走向目标点</t>
   </si>
   <si>
-    <t>Now you have Worker Bugs. Click to select a &lt;color=#a0ff50&gt;Worker Bug&lt;/color&gt;, then click an open area to command it to move to the target location.</t>
+    <t>Now you have Worker Drones. Click to select a &lt;color=#a0ff50&gt;Worker Drone&lt;/color&gt;, then click an open area to command it to move to the target location.</t>
   </si>
   <si>
     <t>Key工虫采集晶体矿……</t>
@@ -5140,7 +5186,7 @@
     <t>很好！现在给您刷了一个晶体矿，请点击选中&lt;color=#a0ff50&gt;工虫&lt;/color&gt;，再点击一次&lt;color=#a0ff50&gt;晶体矿&lt;/color&gt;，让工虫在晶体矿和虫巢之间搬运晶体矿</t>
   </si>
   <si>
-    <t>Well done! A &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; deposit has been spawned for you. Click to select a &lt;color=#a0ff50&gt;Worker Bug&lt;/color&gt;, then click the &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; to order it to transport ore between the deposit and the Hive.</t>
+    <t>Well done! A &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; deposit has been spawned for you. Click to select a &lt;color=#a0ff50&gt;Worker Drone&lt;/color&gt;, then click the &lt;color=#a0ff50&gt;Crystal Ore&lt;/color&gt; to order it to transport ore between the deposit and the Hive.</t>
   </si>
   <si>
     <t>Key工虫采集燃气矿……</t>
@@ -5149,7 +5195,7 @@
     <t>很好！您的工虫正在采集晶体矿，请等他把晶体矿运回虫巢。现在，请先点&lt;color=#a0ff50&gt;取消选中&lt;/color&gt;，再蜕变一个工虫去采集&lt;color=#a0ff50&gt;燃气矿&lt;/color&gt;</t>
   </si>
   <si>
-    <t>Great! Your Worker Bug is harvesting Crystal Ore. Wait for it to deliver the ore to the Hive. Now, first click &lt;color=#a0ff50 &gt;Deselect&lt;/color&gt;, then morph another Worker Bug to harvest the &lt;color=#a0ff50&gt;Gas Vein&lt;/color&gt;.</t>
+    <t>Great! Your Worker Drone is harvesting Crystal Ore. Wait for it to deliver the ore to the Hive. Now, first click &lt;color=#a0ff50 &gt;Deselect&lt;/color&gt;, then morph another Worker Drone to harvest the &lt;color=#a0ff50&gt;Gas Vein&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key工虫已运晶体矿……</t>
@@ -5158,7 +5204,7 @@
     <t>您的工虫已把第一车晶体矿运到基地，请查看&lt;color=#a0ff50&gt;左上角&lt;/color&gt;晶体矿数量变化</t>
   </si>
   <si>
-    <t>Your Worker Bug has delivered the first batch of Crystal Ore to the Command Center. Check the &lt;color=#a0ff50&gt;top-left corner&lt;/color&gt; to see the Crystal Ore count increase.</t>
+    <t>Your Worker Drone has delivered the first batch of Crystal Ore to the Command Center. Check the &lt;color=#a0ff50&gt;top-left corner&lt;/color&gt; to see the Crystal Ore count increase.</t>
   </si>
   <si>
     <t>Key蜕变房虫……</t>
@@ -5167,7 +5213,7 @@
     <t>等您存够20晶体矿后，请点击&lt;color=#a0ff50&gt;活动单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;房虫&lt;/color&gt;按钮，让幼虫蜕变为房虫</t>
   </si>
   <si>
-    <t>Once you have accumulated 20 units of Crystal Ore, click the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Chamber Bug&lt;/color&gt; button to morph Larvae into Chamber Bugs.</t>
+    <t>Once you have accumulated 20 units of Crystal Ore, click the &lt;color=#a0ff50&gt;Mobile Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;PopuLifter Drone&lt;/color&gt; button to morph Larvae into PopuLifter Drones.</t>
   </si>
   <si>
     <t>Key房虫提升……</t>
@@ -5176,7 +5222,7 @@
     <t>很好，房虫可以提升您的&lt;color=#a0ff50&gt;活动单位数量上限&lt;/color&gt;</t>
   </si>
   <si>
-    <t>Excellent. Chamber Bugs increase your &lt;color=#a0ff50&gt;Mobile Unit Cap&lt;/color&gt;.</t>
+    <t>Excellent. PopuLifter Drones increase your &lt;color=#a0ff50&gt; Mobile Unit Cap&lt;/color&gt;.</t>
   </si>
   <si>
     <t>Key变异虫营……</t>
@@ -5185,7 +5231,7 @@
     <t>等您存够30晶体矿后，请点击&lt;color=#a0ff50&gt;建筑单位&lt;/color&gt;=&gt;&lt;color=#a0ff50&gt;虫营&lt;/color&gt;按钮，再点击覆盖有苔蔓(wàn)的地面，就能变异出一个虫营。</t>
   </si>
   <si>
-    <t>When you have 30 units of Crystal Ore, click the &lt;color=#a0ff50&gt;Building Units&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Bug Barracks&lt;/color&gt; button, then click the ground covered by Mossy Vines to mutate a Bug Barracks.</t>
+    <t>When you have 30 units of Crystal Ore, click the &lt;color=#a0ff50&gt;Structures&lt;/color&gt; =&gt; &lt;color=#a0ff50&gt;Bug Barracks&lt;/color&gt; button, then click the ground covered by Mossy Vines to mutate a Bug Barracks.</t>
   </si>
   <si>
     <t>Key解锁枪虫……</t>
@@ -5230,7 +5276,7 @@
     <t>您的单位阵亡了。可以多造点近战虫和枪虫去围攻敌人</t>
   </si>
   <si>
-    <t>Your unit has been destroyed. Produce more Melee Bugs and Gun Bugs to overwhelm the enemy with numbers.</t>
+    <t>Your unit has been destroyed. Produce more Melee Bugs and Rifle Bugs to overwhelm the enemy with numbers.</t>
   </si>
   <si>
     <t>Key变异更多虫巢……</t>
@@ -5239,7 +5285,7 @@
     <t>恭喜您消灭了敌人！现在左边给您刷了更多的敌人。您可以变异更多的&lt;color=#a0ff50&gt;虫巢&lt;/color&gt;加快幼虫的产出，蜕变更多的&lt;color=#a0ff50&gt;房虫&lt;/color&gt;提升活动单位上限，加油</t>
   </si>
   <si>
-    <t>Congratulations on eliminating the enemy! More enemies have been spawned on the left. You can mutate additional &lt;color=#a0ff50&gt;Hives&lt;/color&gt; to speed up Larva production, and morph more &lt;color=#a0ff50&gt;Chamber Bugs&lt;/color&gt; to increase your unit cap. Keep fighting!</t>
+    <t>Congratulations on eliminating the enemy! More enemies have been spawned on the left. You can mutate additional &lt;color=#a0ff50&gt; Hives&lt;/color&gt; to speed up Larva production, and morph more &lt;color=#a0ff50&gt; PopuLifter Drones&lt;/color&gt; to increase your unit cap. Keep fighting!</t>
   </si>
   <si>
     <t>Key夺回地球……</t>
@@ -5275,7 +5321,7 @@
     <t>胜败乃兵家常事，请点击右上角&lt;color=#a0ff50&gt;离开场景&lt;/color&gt;离开，就可以重新来过。</t>
   </si>
   <si>
-    <t>Victory and defeat are common in warfare. Click &lt;color=#a0ff50&gt;Exit Scene&lt;/color&gt; in the top-right corner to restart the mission.</t>
+    <t>Victory and defeat are common in warfare. Click &lt;color=#a0ff50&gt;Leave Scene&lt;/color&gt; in the top-right corner to restart the mission.</t>
   </si>
   <si>
     <t>Key功败垂成……</t>
@@ -5346,9 +5392,18 @@
     <t>变异完成</t>
   </si>
   <si>
-    <t>Key正在变异:</t>
-  </si>
-  <si>
+    <t>Mutation Complete</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Key</t>
+    </r>
     <r>
       <rPr>
         <sz val="10.5"/>
@@ -5369,28 +5424,66 @@
     </r>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>正在变异</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t>Mutating In Progress:</t>
+  </si>
+  <si>
     <t>Key燃气矿不足无法建造</t>
   </si>
   <si>
     <t>燃气矿不足，无法建造</t>
   </si>
   <si>
+    <t>Insufficient Vespene Gas. Construction Unavailable.</t>
+  </si>
+  <si>
     <t>Key燃气矿不足不能升级</t>
   </si>
   <si>
     <t>燃气矿不足，不能升级</t>
   </si>
   <si>
+    <t>Insufficient Vespene Gas. Upgrade Unavailable.</t>
+  </si>
+  <si>
     <t>Key晶体矿不足不能升级</t>
   </si>
   <si>
     <t>晶体矿不足，不能升级</t>
   </si>
   <si>
+    <t>Insufficient Minerals. Upgrade Unavailable.</t>
+  </si>
+  <si>
     <t>Key已采集{}</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>已采集</t>
     </r>
     <r>
@@ -5404,10 +5497,19 @@
     </r>
   </si>
   <si>
+    <t>Harvested: {}</t>
+  </si>
+  <si>
     <t>Key剩余{}</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>剩余</t>
     </r>
     <r>
@@ -5419,6 +5521,67 @@
       </rPr>
       <t>{}</t>
     </r>
+  </si>
+  <si>
+    <t>Remaining: {}</t>
+  </si>
+  <si>
+    <t>Key升级进度{}/{}</t>
+  </si>
+  <si>
+    <r>
+      <t>升级进度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}/{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Upgrade Progress {}/{}</t>
+  </si>
+  <si>
+    <t>Key解锁进度{}/{}</t>
+  </si>
+  <si>
+    <r>
+      <t>解锁进度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFE394DC"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>{}/{}</t>
+    </r>
+  </si>
+  <si>
+    <t>Unlock Progress {}/{}</t>
+  </si>
+  <si>
+    <t>Key已解锁单位</t>
+  </si>
+  <si>
+    <t>已解锁单位</t>
+  </si>
+  <si>
+    <t>Unit Unlocked</t>
+  </si>
+  <si>
+    <t>Key属性已升级</t>
+  </si>
+  <si>
+    <t>属性已升级</t>
+  </si>
+  <si>
+    <t>Attributes Upgraded</t>
   </si>
 </sst>
 </file>
@@ -5684,17 +5847,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="36">
@@ -6165,7 +6328,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6223,16 +6386,19 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -6675,20 +6841,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" s="39" customFormat="1" spans="1:18">
-      <c r="A2" s="39">
+    <row r="2" s="40" customFormat="1" spans="1:18">
+      <c r="A2" s="40">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="39">
-        <v>0</v>
-      </c>
-      <c r="G2" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="39">
+      <c r="C2" s="40">
+        <v>0</v>
+      </c>
+      <c r="G2" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="40">
         <v>1</v>
       </c>
       <c r="J2">
@@ -6697,33 +6863,33 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="M2" s="39">
-        <v>1</v>
-      </c>
-      <c r="N2" s="39">
-        <v>0</v>
-      </c>
-      <c r="O2" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="39" customFormat="1" spans="1:18">
-      <c r="A3" s="39">
+      <c r="M2" s="40">
+        <v>1</v>
+      </c>
+      <c r="N2" s="40">
+        <v>0</v>
+      </c>
+      <c r="O2" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="40" customFormat="1" spans="1:18">
+      <c r="A3" s="40">
         <v>2</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="39">
-        <v>0</v>
-      </c>
-      <c r="G3" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="39">
+      <c r="C3" s="40">
+        <v>0</v>
+      </c>
+      <c r="G3" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="40">
         <v>1</v>
       </c>
       <c r="J3">
@@ -6732,36 +6898,36 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="M3" s="39">
-        <v>1</v>
-      </c>
-      <c r="N3" s="39">
-        <v>0</v>
-      </c>
-      <c r="O3" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="34" customFormat="1" spans="1:18">
-      <c r="A4" s="34">
+      <c r="M3" s="40">
+        <v>1</v>
+      </c>
+      <c r="N3" s="40">
+        <v>0</v>
+      </c>
+      <c r="O3" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="35" customFormat="1" spans="1:18">
+      <c r="A4" s="35">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="35">
         <v>2</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="39">
+      <c r="G4" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="40">
         <v>1</v>
       </c>
       <c r="J4">
@@ -6770,36 +6936,36 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="M4" s="39">
-        <v>1</v>
-      </c>
-      <c r="N4" s="39">
-        <v>0</v>
-      </c>
-      <c r="O4" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="34" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A5" s="34">
+      <c r="M4" s="40">
+        <v>1</v>
+      </c>
+      <c r="N4" s="40">
+        <v>0</v>
+      </c>
+      <c r="O4" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" s="35" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A5" s="35">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="34">
-        <v>0</v>
-      </c>
-      <c r="D5" s="34" t="s">
+      <c r="C5" s="35">
+        <v>0</v>
+      </c>
+      <c r="D5" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="39">
+      <c r="G5" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="40">
         <v>1</v>
       </c>
       <c r="J5">
@@ -6808,48 +6974,48 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="M5" s="39">
-        <v>1</v>
-      </c>
-      <c r="N5" s="39">
-        <v>0</v>
-      </c>
-      <c r="O5" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="34">
-        <v>0</v>
-      </c>
-      <c r="R5" s="24" t="s">
+      <c r="M5" s="40">
+        <v>1</v>
+      </c>
+      <c r="N5" s="40">
+        <v>0</v>
+      </c>
+      <c r="O5" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="35">
+        <v>0</v>
+      </c>
+      <c r="R5" s="25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" s="40" customFormat="1" spans="1:18">
-      <c r="A6" s="40">
+    <row r="6" s="41" customFormat="1" spans="1:18">
+      <c r="A6" s="41">
         <v>101</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="40">
-        <v>0</v>
-      </c>
-      <c r="D6" s="40" t="s">
+      <c r="C6" s="41">
+        <v>0</v>
+      </c>
+      <c r="D6" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="39" t="b">
+      <c r="G6" s="40" t="b">
         <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="39">
+      <c r="I6" s="40">
         <v>1</v>
       </c>
       <c r="J6">
@@ -6861,39 +7027,39 @@
       <c r="L6" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="39">
-        <v>1</v>
-      </c>
-      <c r="N6" s="39">
-        <v>0</v>
-      </c>
-      <c r="O6" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="40" customFormat="1" spans="1:18">
-      <c r="A7" s="40">
+      <c r="M6" s="40">
+        <v>1</v>
+      </c>
+      <c r="N6" s="40">
+        <v>0</v>
+      </c>
+      <c r="O6" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="41" customFormat="1" spans="1:18">
+      <c r="A7" s="41">
         <v>102</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="40">
-        <v>0</v>
-      </c>
-      <c r="D7" s="40" t="s">
+      <c r="C7" s="41">
+        <v>0</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="39">
+      <c r="G7" s="40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="40">
         <v>1</v>
       </c>
       <c r="J7">
@@ -6902,16 +7068,16 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="M7" s="39">
-        <v>1</v>
-      </c>
-      <c r="N7" s="39">
-        <v>0</v>
-      </c>
-      <c r="O7" s="39">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="40">
+      <c r="M7" s="40">
+        <v>1</v>
+      </c>
+      <c r="N7" s="40">
+        <v>0</v>
+      </c>
+      <c r="O7" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="41">
         <v>0</v>
       </c>
     </row>
@@ -6934,13 +7100,13 @@
       <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="39" t="b">
+      <c r="G8" s="40" t="b">
         <v>1</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="I8" s="39">
+      <c r="I8" s="40">
         <v>1</v>
       </c>
       <c r="J8">
@@ -6952,13 +7118,13 @@
       <c r="L8">
         <v>3</v>
       </c>
-      <c r="M8" s="39">
-        <v>1</v>
-      </c>
-      <c r="N8" s="39">
-        <v>0</v>
-      </c>
-      <c r="O8" s="39">
+      <c r="M8" s="40">
+        <v>1</v>
+      </c>
+      <c r="N8" s="40">
+        <v>0</v>
+      </c>
+      <c r="O8" s="40">
         <v>0</v>
       </c>
       <c r="P8" t="s">
@@ -6967,63 +7133,63 @@
       <c r="Q8">
         <v>3</v>
       </c>
-      <c r="R8" s="24" t="s">
+      <c r="R8" s="25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" s="33" customFormat="1" ht="14.25" spans="1:18">
-      <c r="A9" s="33">
+    <row r="9" s="34" customFormat="1" ht="14.25" spans="1:18">
+      <c r="A9" s="34">
         <v>202</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="33">
-        <v>1</v>
- 